--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD1195FF-BF06-4876-B38C-28A3D06E4D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5B63784-3FB9-4F86-A62D-26BA99AA74CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Id</t>
   </si>
@@ -81,16 +81,39 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta/IMG-20260828-WA0115_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>ramon.espinosa@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Ramon Espinosa Macias</t>
+  </si>
+  <si>
+    <t>QR - Qualtrics</t>
+  </si>
+  <si>
+    <t>38456</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta/17879710536332015001691892771562_Ramon%20Espinosa%20Macia.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -113,15 +136,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
@@ -160,8 +188,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:I2" totalsRowShown="0">
-  <autoFilter ref="A1:I2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:I3" totalsRowShown="0">
+  <autoFilter ref="A1:I3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="6">
       <extLst>
@@ -230,7 +258,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1" latestEventMarker="0">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="3" latestEventMarker="2">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -543,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
@@ -584,10 +612,10 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>46262.854942129627</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>46262.856157407405</v>
       </c>
       <c r="D2" t="s">
@@ -605,15 +633,47 @@
       <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="5" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46262.857245370396</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46262.860671296301</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{1E16F861-FB1C-4392-A2AD-23994E20C8D8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5B63784-3FB9-4F86-A62D-26BA99AA74CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D656B54-C64D-463E-A638-2609076F114F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
   <si>
     <t>Id</t>
   </si>
@@ -53,16 +53,34 @@
     <t>Nombre</t>
   </si>
   <si>
+    <t>CeCo</t>
+  </si>
+  <si>
     <t>Selecciona la actividad que deseas registrar</t>
   </si>
   <si>
-    <t>CeCo</t>
-  </si>
-  <si>
-    <t>¿Confirmas que realizaste la actividad seleccionada?</t>
-  </si>
-  <si>
-    <t>Evidencia del avance</t>
+    <t>Evidencia_RollOut</t>
+  </si>
+  <si>
+    <t>Evidencia_Programacion_Hornos_Merry_Focaccia</t>
+  </si>
+  <si>
+    <t>Evidencia_Rack_FHW</t>
+  </si>
+  <si>
+    <t>Evidencia_QR_Qualtrics</t>
+  </si>
+  <si>
+    <t>Evidencia_Max&amp;Min </t>
+  </si>
+  <si>
+    <t>Evidencia_Fotografia_SM</t>
+  </si>
+  <si>
+    <t>Evidencia_Mandil Verde</t>
+  </si>
+  <si>
+    <t>Evidencia_Lay_Out</t>
   </si>
   <si>
     <t>enrique.cesar@starbucks.com.mx</t>
@@ -71,49 +89,77 @@
     <t>Enrique Cesar Flores</t>
   </si>
   <si>
+    <t>38115</t>
+  </si>
+  <si>
     <t>Roll Out</t>
   </si>
   <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/17880180021495194119606447507663_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>38186</t>
+  </si>
+  <si>
+    <t>Programacion Hornos Merry - Focaccia</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17880180440085018616306650996282_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>38590</t>
+  </si>
+  <si>
+    <t>Rack FHW</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17880180703322521840589027014893_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>38965</t>
+  </si>
+  <si>
+    <t>QR - Qualtrics</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta%202/17880180983931200736199228031165_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
     <t>38401</t>
   </si>
   <si>
-    <t>Si</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta/IMG-20260828-WA0115_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>ramon.espinosa@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Ramon Espinosa Macias</t>
-  </si>
-  <si>
-    <t>QR - Qualtrics</t>
-  </si>
-  <si>
-    <t>38456</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta/17879710536332015001691892771562_Ramon%20Espinosa%20Macia.jpg</t>
+    <t>Fotografia - SM</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/17880181272746192969476876419035_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>38811</t>
+  </si>
+  <si>
+    <t>Mandil Verde</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17880181502214283229227654394291_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>38149</t>
+  </si>
+  <si>
+    <t>Lay Out</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17880181854097260014306477506614_Enrique%20Cesar%20Flores.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -136,23 +182,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="13">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -188,10 +247,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:I3" totalsRowShown="0">
-  <autoFilter ref="A1:I3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:O8" totalsRowShown="0">
+  <autoFilter ref="A1:O8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
@@ -212,45 +271,87 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="5">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="3">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="9">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="re5684d75187446048a57d8ab2351a703"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfa200a7d03cc4a5fa91df03bac2ecf7a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="CeCo" dataDxfId="2">
-      <extLst>
-        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
-          <xlmsforms:question id="r61702b52a5014c9387fe982df775507f"/>
-        </ext>
-      </extLst>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="¿Confirmas que realizaste la actividad seleccionada?" dataDxfId="1">
-      <extLst>
-        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
-          <xlmsforms:question id="r3729c9809dc0437f92a27dcf9bb6544b"/>
-        </ext>
-      </extLst>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia del avance" dataDxfId="0">
-      <extLst>
-        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
-          <xlmsforms:question id="r443a4f12fee340e89a4608f5936b3d6e"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Evidencia_RollOut" dataDxfId="7">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r1122b5cac1cb4eff8da7818c6fc7b42b"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Programacion_Hornos_Merry_Focaccia" dataDxfId="6">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="rf5169ef365594c67bd63f38ea0df71c8"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Rack_FHW" dataDxfId="5">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r722c7f4f41104c68940ef96a05bac24d"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_QR_Qualtrics" dataDxfId="4">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r9b0f18f43c16454ca5151a4c7c7f429d"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Max&amp;Min " dataDxfId="3">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r7e20bda30db04cc2a60f0888364bbb7b"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Evidencia_Fotografia_SM" dataDxfId="2">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r6f36155dea9a4116b90cecef4dfb40a2"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Mandil Verde" dataDxfId="1">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r9b9e86be8d8a48a79e9701b423e28c21"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Lay_Out" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r5be890f9c9be4de4ba1736dba059b880"/>
         </ext>
       </extLst>
     </tableColumn>
@@ -258,16 +359,22 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="3" latestEventMarker="2">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="11" latestEventMarker="208">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>responder</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>responderName</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>re5684d75187446048a57d8ab2351a703</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>rfa200a7d03cc4a5fa91df03bac2ecf7a</xlmsforms:syncedQuestionId>
-        <xlmsforms:syncedQuestionId>r61702b52a5014c9387fe982df775507f</xlmsforms:syncedQuestionId>
-        <xlmsforms:syncedQuestionId>r3729c9809dc0437f92a27dcf9bb6544b</xlmsforms:syncedQuestionId>
-        <xlmsforms:syncedQuestionId>r443a4f12fee340e89a4608f5936b3d6e</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r1122b5cac1cb4eff8da7818c6fc7b42b</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>rf5169ef365594c67bd63f38ea0df71c8</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r722c7f4f41104c68940ef96a05bac24d</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r9b0f18f43c16454ca5151a4c7c7f429d</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r7e20bda30db04cc2a60f0888364bbb7b</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r6f36155dea9a4116b90cecef4dfb40a2</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r9b9e86be8d8a48a79e9701b423e28c21</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r5be890f9c9be4de4ba1736dba059b880</xlmsforms:syncedQuestionId>
       </xlmsforms:msForm>
     </ext>
   </extLst>
@@ -571,15 +678,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="233" bestFit="1" customWidth="1"/>
+    <col min="1" max="15" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -607,73 +712,212 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:15">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
-        <v>46262.854942129627</v>
-      </c>
-      <c r="C2" s="3">
-        <v>46262.856157407405</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46263.402662037035</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46263.403009259258</v>
       </c>
       <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46263.403078703705</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46263.403402777774</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46263.403425925928</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46263.403703703705</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46263.403761574074</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46263.404016203705</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B6" s="2">
+        <v>46263.404108796298</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46263.404340277775</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B7" s="2">
+        <v>46263.404409722221</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46263.404618055552</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3">
-        <v>46262.857245370396</v>
-      </c>
-      <c r="C3" s="3">
-        <v>46262.860671296301</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B8" s="2">
+        <v>46263.404652777775</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46263.405034722222</v>
+      </c>
+      <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E8" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
+      <c r="F8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="O8" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{1E16F861-FB1C-4392-A2AD-23994E20C8D8}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D656B54-C64D-463E-A638-2609076F114F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4E0D5B1-61FB-4649-896B-7F0B58B1F4CB}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>Id</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17880181854097260014306477506614_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>38136</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta%202/17880193792221894187441724490144_Enrique%20Cesar%20Flores.jpg</t>
   </si>
 </sst>
 </file>
@@ -185,10 +191,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -247,8 +256,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:O8" totalsRowShown="0">
-  <autoFilter ref="A1:O8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:O9" totalsRowShown="0">
+  <autoFilter ref="A1:O9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="12">
       <extLst>
@@ -359,7 +368,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="11" latestEventMarker="208">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="12" latestEventMarker="209">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -678,10 +687,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="15" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -735,10 +746,10 @@
       <c r="A2">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>46263.402662037035</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>46263.403009259258</v>
       </c>
       <c r="D2" t="s">
@@ -761,10 +772,10 @@
       <c r="A3">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>46263.403078703705</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>46263.403402777774</v>
       </c>
       <c r="D3" t="s">
@@ -787,10 +798,10 @@
       <c r="A4">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>46263.403425925928</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>46263.403703703705</v>
       </c>
       <c r="D4" t="s">
@@ -813,10 +824,10 @@
       <c r="A5">
         <v>8</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>46263.403761574074</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>46263.404016203705</v>
       </c>
       <c r="D5" t="s">
@@ -839,10 +850,10 @@
       <c r="A6">
         <v>9</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>46263.404108796298</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>46263.404340277775</v>
       </c>
       <c r="D6" t="s">
@@ -865,10 +876,10 @@
       <c r="A7">
         <v>10</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>46263.404409722221</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>46263.404618055552</v>
       </c>
       <c r="D7" t="s">
@@ -891,10 +902,10 @@
       <c r="A8">
         <v>11</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>46263.404652777775</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>46263.405034722222</v>
       </c>
       <c r="D8" t="s">
@@ -912,6 +923,39 @@
       <c r="O8" t="s">
         <v>37</v>
       </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="4">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46263.418622685203</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46263.418854166703</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4E0D5B1-61FB-4649-896B-7F0B58B1F4CB}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F7B0542-1674-46FF-B265-E4049BDD2B18}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Id</t>
   </si>
@@ -83,79 +83,19 @@
     <t>Evidencia_Lay_Out</t>
   </si>
   <si>
-    <t>enrique.cesar@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Enrique Cesar Flores</t>
-  </si>
-  <si>
-    <t>38115</t>
+    <t>SBMX38333@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Mega Izcalli</t>
+  </si>
+  <si>
+    <t>38333</t>
   </si>
   <si>
     <t>Roll Out</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/17880180021495194119606447507663_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>38186</t>
-  </si>
-  <si>
-    <t>Programacion Hornos Merry - Focaccia</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17880180440085018616306650996282_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>38590</t>
-  </si>
-  <si>
-    <t>Rack FHW</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17880180703322521840589027014893_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>38965</t>
-  </si>
-  <si>
-    <t>QR - Qualtrics</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta%202/17880180983931200736199228031165_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>38401</t>
-  </si>
-  <si>
-    <t>Fotografia - SM</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/17880181272746192969476876419035_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>38811</t>
-  </si>
-  <si>
-    <t>Mandil Verde</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17880181502214283229227654394291_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>38149</t>
-  </si>
-  <si>
-    <t>Lay Out</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17880181854097260014306477506614_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>38136</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta%202/17880193792221894187441724490144_Enrique%20Cesar%20Flores.jpg</t>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/FALL%2026_Starbucks%20Mega%20Izcal.jpeg</t>
   </si>
 </sst>
 </file>
@@ -191,13 +131,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -256,8 +195,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:O9" totalsRowShown="0">
-  <autoFilter ref="A1:O9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:O2" totalsRowShown="0">
+  <autoFilter ref="A1:O2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="12">
       <extLst>
@@ -368,7 +307,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="12" latestEventMarker="209">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="15" latestEventMarker="212">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -687,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="20" bestFit="1" customWidth="1"/>
@@ -743,219 +682,37 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3">
-        <v>46263.402662037035</v>
-      </c>
-      <c r="C2" s="3">
-        <v>46263.403009259258</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="A2" s="4">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46263.477222222202</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46263.477986111102</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3">
-        <v>46263.403078703705</v>
-      </c>
-      <c r="C3" s="3">
-        <v>46263.403402777774</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3">
-        <v>46263.403425925928</v>
-      </c>
-      <c r="C4" s="3">
-        <v>46263.403703703705</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3">
-        <v>46263.403761574074</v>
-      </c>
-      <c r="C5" s="3">
-        <v>46263.404016203705</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3">
-        <v>46263.404108796298</v>
-      </c>
-      <c r="C6" s="3">
-        <v>46263.404340277775</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3">
-        <v>46263.404409722221</v>
-      </c>
-      <c r="C7" s="3">
-        <v>46263.404618055552</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8">
-        <v>11</v>
-      </c>
-      <c r="B8" s="3">
-        <v>46263.404652777775</v>
-      </c>
-      <c r="C8" s="3">
-        <v>46263.405034722222</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" t="s">
-        <v>36</v>
-      </c>
-      <c r="O8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="4">
-        <v>12</v>
-      </c>
-      <c r="B9" s="3">
-        <v>46263.418622685203</v>
-      </c>
-      <c r="C9" s="3">
-        <v>46263.418854166703</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F7B0542-1674-46FF-B265-E4049BDD2B18}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3601901-0130-4873-A33E-351BE8303BE7}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Id</t>
   </si>
@@ -96,13 +96,25 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/FALL%2026_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38894@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Galerias Perinorte</t>
+  </si>
+  <si>
+    <t>38894</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/e7d9be1f-bc24-43e4-a2c9-b07664317954_Starbucks%20Galerias%20P.jpeg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,10 +145,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -182,7 +194,9 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{F5ED5226-C975-4633-8D0E-2AC1483F5B64}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -195,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:O2" totalsRowShown="0">
-  <autoFilter ref="A1:O2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:O3" totalsRowShown="0">
+  <autoFilter ref="A1:O3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="12">
       <extLst>
@@ -307,7 +321,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="15" latestEventMarker="212">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="16" latestEventMarker="213">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -626,15 +640,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="15" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -681,38 +693,64 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>13</v>
       </c>
       <c r="B2" s="2">
-        <v>46263.477222222202</v>
+        <v>46263.477222222224</v>
       </c>
       <c r="C2" s="2">
-        <v>46263.477986111102</v>
-      </c>
-      <c r="D2" s="1" t="s">
+        <v>46263.477986111109</v>
+      </c>
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46263.507662037002</v>
+      </c>
+      <c r="C3" s="2">
+        <v>46263.509398148097</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3601901-0130-4873-A33E-351BE8303BE7}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C77A0BDD-86D2-4F88-A235-582EE4093A70}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -62,6 +62,9 @@
     <t>Evidencia_RollOut</t>
   </si>
   <si>
+    <t>¿ Tienes Horno Merry Chef ?</t>
+  </si>
+  <si>
     <t>Evidencia_Programacion_Hornos_Merry_Focaccia</t>
   </si>
   <si>
@@ -81,6 +84,12 @@
   </si>
   <si>
     <t>Evidencia_Lay_Out</t>
+  </si>
+  <si>
+    <t>¿Cuentas con Community Board?</t>
+  </si>
+  <si>
+    <t>Evidencia_Community_Board</t>
   </si>
   <si>
     <t>SBMX38333@starbucks.com.mx</t>
@@ -114,7 +123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,37 +152,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+  <dxfs count="16">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -209,10 +228,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:O3" totalsRowShown="0">
-  <autoFilter ref="A1:O3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R3" totalsRowShown="0">
+  <autoFilter ref="A1:R3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
@@ -233,87 +252,108 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="11">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="10">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="9">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re5684d75187446048a57d8ab2351a703"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="8">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfa200a7d03cc4a5fa91df03bac2ecf7a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Evidencia_RollOut" dataDxfId="7">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Evidencia_RollOut" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1122b5cac1cb4eff8da7818c6fc7b42b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Programacion_Hornos_Merry_Focaccia" dataDxfId="6">
+    <tableColumn id="16" xr3:uid="{1277AD17-A3AC-49E0-841E-4D4035BFD4D3}" name="¿ Tienes Horno Merry Chef ?" dataDxfId="9">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="rfa62d4c051494e7682d75d2cbdf57e90"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Programacion_Hornos_Merry_Focaccia" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rf5169ef365594c67bd63f38ea0df71c8"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Rack_FHW" dataDxfId="5">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Rack_FHW" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r722c7f4f41104c68940ef96a05bac24d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_QR_Qualtrics" dataDxfId="4">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_QR_Qualtrics" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9b0f18f43c16454ca5151a4c7c7f429d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Max&amp;Min " dataDxfId="3">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Max&amp;Min " dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7e20bda30db04cc2a60f0888364bbb7b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Evidencia_Fotografia_SM" dataDxfId="2">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Evidencia_Fotografia_SM" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6f36155dea9a4116b90cecef4dfb40a2"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Mandil Verde" dataDxfId="1">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Mandil Verde" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9b9e86be8d8a48a79e9701b423e28c21"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Lay_Out" dataDxfId="0">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Lay_Out" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5be890f9c9be4de4ba1736dba059b880"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{73C9F7D3-3EB8-4169-BE15-327F5E69A55D}" name="¿Cuentas con Community Board?" dataDxfId="1">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r142174aa4f64470ba655c0b540426c92"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="18" xr3:uid="{2B38EDF8-2ADC-46EB-94B2-87B30C98AE1D}" name="Evidencia_Community_Board" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r31182c58e8f644128524d5583789a1ac"/>
         </ext>
       </extLst>
     </tableColumn>
@@ -321,7 +361,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="16" latestEventMarker="213">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="16" latestEventMarker="228">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -337,6 +377,9 @@
         <xlmsforms:syncedQuestionId>r6f36155dea9a4116b90cecef4dfb40a2</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r9b9e86be8d8a48a79e9701b423e28c21</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r5be890f9c9be4de4ba1736dba059b880</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>rfa62d4c051494e7682d75d2cbdf57e90</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r142174aa4f64470ba655c0b540426c92</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r31182c58e8f644128524d5583789a1ac</xlmsforms:syncedQuestionId>
       </xlmsforms:msForm>
     </ext>
   </extLst>
@@ -640,13 +683,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -671,7 +717,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -692,8 +738,17 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="15">
       <c r="A2">
         <v>13</v>
       </c>
@@ -704,22 +759,25 @@
         <v>46263.477986111109</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="15">
       <c r="A3">
         <v>16</v>
       </c>
@@ -730,27 +788,30 @@
         <v>46263.509398148097</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="I3" s="5"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C77A0BDD-86D2-4F88-A235-582EE4093A70}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{256A1621-5626-40D6-9140-289368A2E902}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
@@ -92,6 +92,9 @@
     <t>Evidencia_Community_Board</t>
   </si>
   <si>
+    <t>Evidencia_ACtivacion_PSL_Sharpie</t>
+  </si>
+  <si>
     <t>SBMX38333@starbucks.com.mx</t>
   </si>
   <si>
@@ -117,6 +120,51 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/e7d9be1f-bc24-43e4-a2c9-b07664317954_Starbucks%20Galerias%20P.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx43194@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Atana Lindavista</t>
+  </si>
+  <si>
+    <t>43194</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/ab544637-f78d-4059-ac80-1a1426688537_Starbucks%20Atana%20Lind.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38862@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks San Miguel Izcalli</t>
+  </si>
+  <si>
+    <t>38862</t>
+  </si>
+  <si>
+    <t>Mandil Verde</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17880337596294213442656647095211_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>Rack FHW</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17880338415158301924124629037929_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Galerias%20P.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260829-WA0000_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>Lay Out</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/20260829_142749-COLLAGE_Starbucks%20San%20Miguel.jpg</t>
   </si>
 </sst>
 </file>
@@ -163,7 +211,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="17">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -228,10 +279,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:R3" totalsRowShown="0">
-  <autoFilter ref="A1:R3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S9" totalsRowShown="0">
+  <autoFilter ref="A1:S9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
@@ -252,108 +303,115 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="14">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="13">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="12">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re5684d75187446048a57d8ab2351a703"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="11">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfa200a7d03cc4a5fa91df03bac2ecf7a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Evidencia_RollOut" dataDxfId="10">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Evidencia_RollOut" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1122b5cac1cb4eff8da7818c6fc7b42b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1277AD17-A3AC-49E0-841E-4D4035BFD4D3}" name="¿ Tienes Horno Merry Chef ?" dataDxfId="9">
+    <tableColumn id="16" xr3:uid="{1277AD17-A3AC-49E0-841E-4D4035BFD4D3}" name="¿ Tienes Horno Merry Chef ?" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfa62d4c051494e7682d75d2cbdf57e90"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Programacion_Hornos_Merry_Focaccia" dataDxfId="8">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Programacion_Hornos_Merry_Focaccia" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rf5169ef365594c67bd63f38ea0df71c8"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Rack_FHW" dataDxfId="7">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Rack_FHW" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r722c7f4f41104c68940ef96a05bac24d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_QR_Qualtrics" dataDxfId="6">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_QR_Qualtrics" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9b0f18f43c16454ca5151a4c7c7f429d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Max&amp;Min " dataDxfId="5">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Max&amp;Min " dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7e20bda30db04cc2a60f0888364bbb7b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Evidencia_Fotografia_SM" dataDxfId="4">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Evidencia_Fotografia_SM" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6f36155dea9a4116b90cecef4dfb40a2"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Mandil Verde" dataDxfId="3">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Mandil Verde" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9b9e86be8d8a48a79e9701b423e28c21"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Lay_Out" dataDxfId="2">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Lay_Out" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5be890f9c9be4de4ba1736dba059b880"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{73C9F7D3-3EB8-4169-BE15-327F5E69A55D}" name="¿Cuentas con Community Board?" dataDxfId="1">
+    <tableColumn id="17" xr3:uid="{73C9F7D3-3EB8-4169-BE15-327F5E69A55D}" name="¿Cuentas con Community Board?" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r142174aa4f64470ba655c0b540426c92"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{2B38EDF8-2ADC-46EB-94B2-87B30C98AE1D}" name="Evidencia_Community_Board" dataDxfId="0">
+    <tableColumn id="18" xr3:uid="{2B38EDF8-2ADC-46EB-94B2-87B30C98AE1D}" name="Evidencia_Community_Board" dataDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r31182c58e8f644128524d5583789a1ac"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="19" xr3:uid="{2481D1ED-0923-463A-9844-953EC81748EE}" name="Evidencia_ACtivacion_PSL_Sharpie" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r11debcaacf20446fb636cd1accf9e03b"/>
         </ext>
       </extLst>
     </tableColumn>
@@ -361,7 +419,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="16" latestEventMarker="228">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="22" latestEventMarker="244">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -380,6 +438,7 @@
         <xlmsforms:syncedQuestionId>rfa62d4c051494e7682d75d2cbdf57e90</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r142174aa4f64470ba655c0b540426c92</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r31182c58e8f644128524d5583789a1ac</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r11debcaacf20446fb636cd1accf9e03b</xlmsforms:syncedQuestionId>
       </xlmsforms:msForm>
     </ext>
   </extLst>
@@ -683,16 +742,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="8" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="6" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="19" customWidth="1"/>
+    <col min="17" max="19" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15">
+    <row r="1" spans="1:19" ht="15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -717,7 +778,7 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -741,14 +802,17 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" ht="15">
+    <row r="2" spans="1:19" ht="15">
       <c r="A2">
         <v>13</v>
       </c>
@@ -759,25 +823,23 @@
         <v>46263.477986111109</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
+        <v>23</v>
+      </c>
+      <c r="S2" s="5"/>
     </row>
-    <row r="3" spans="1:18" ht="15">
+    <row r="3" spans="1:19" ht="15">
       <c r="A3">
         <v>16</v>
       </c>
@@ -788,21 +850,20 @@
         <v>46263.509398148097</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="5"/>
+        <v>27</v>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -810,8 +871,226 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46263.560555555603</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46263.561458333301</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="S4" s="5"/>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="5">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46263.583425925899</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46263.585462962998</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="5">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46263.585497685199</v>
+      </c>
+      <c r="C6" s="2">
+        <v>46263.586550925902</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="5">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46263.590254629598</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46263.590648148202</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="5">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46263.600185185198</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46263.6006597222</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="5">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46263.601550925901</v>
+      </c>
+      <c r="C9" s="2">
+        <v>46263.602928240703</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{256A1621-5626-40D6-9140-289368A2E902}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73B6F669-9947-494F-8C95-A9D4B49CE164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>Id</t>
   </si>
@@ -165,6 +165,33 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/20260829_142749-COLLAGE_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38925@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Star Medica Lomas Verdes</t>
+  </si>
+  <si>
+    <t>38925</t>
+  </si>
+  <si>
+    <t>Activacion PSL Sharpie</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_9898_Starbucks%20Star%20Medic.jpeg</t>
+  </si>
+  <si>
+    <t>hector.estevez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Hector Ruben Estevez Torres</t>
+  </si>
+  <si>
+    <t>38142</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/475806a8-ee33-4297-b735-bb82ecbeb249_Hector%20Ruben%20Estevez.jpeg</t>
   </si>
 </sst>
 </file>
@@ -279,8 +306,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S9" totalsRowShown="0">
-  <autoFilter ref="A1:S9" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S11" totalsRowShown="0">
+  <autoFilter ref="A1:S11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -419,7 +446,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="22" latestEventMarker="244">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="24" latestEventMarker="247">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -742,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -808,7 +835,7 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -837,7 +864,6 @@
       <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="S2" s="5"/>
     </row>
     <row r="3" spans="1:19" ht="15">
       <c r="A3">
@@ -871,7 +897,6 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="S3" s="5"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4">
@@ -905,10 +930,9 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-      <c r="S4" s="5"/>
     </row>
     <row r="5" spans="1:19">
-      <c r="A5" s="5">
+      <c r="A5">
         <v>18</v>
       </c>
       <c r="B5" s="2">
@@ -930,7 +954,6 @@
         <v>35</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="5"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -940,12 +963,9 @@
         <v>36</v>
       </c>
       <c r="P5" s="3"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="5">
+      <c r="A6">
         <v>19</v>
       </c>
       <c r="B6" s="2">
@@ -967,7 +987,6 @@
         <v>37</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="5"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>38</v>
@@ -977,12 +996,9 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="5">
+      <c r="A7">
         <v>20</v>
       </c>
       <c r="B7" s="2">
@@ -1004,7 +1020,6 @@
         <v>37</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="5"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3" t="s">
         <v>39</v>
@@ -1014,12 +1029,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="5">
+      <c r="A8">
         <v>21</v>
       </c>
       <c r="B8" s="2">
@@ -1043,7 +1055,6 @@
       <c r="H8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="5"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1051,12 +1062,9 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="5">
+      <c r="A9">
         <v>22</v>
       </c>
       <c r="B9" s="2">
@@ -1078,7 +1086,6 @@
         <v>41</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="5"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -1088,9 +1095,77 @@
       <c r="P9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46263.634525463</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46263.635069444397</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="S10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="5">
+        <v>24</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46263.639826388899</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46263.6403125</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5" t="s">
+        <v>51</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73B6F669-9947-494F-8C95-A9D4B49CE164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B920B7F8-6117-4DFD-BF9B-51D8AB75555F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,9 +92,6 @@
     <t>Evidencia_Community_Board</t>
   </si>
   <si>
-    <t>Evidencia_ACtivacion_PSL_Sharpie</t>
-  </si>
-  <si>
     <t>SBMX38333@starbucks.com.mx</t>
   </si>
   <si>
@@ -192,13 +189,16 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/475806a8-ee33-4297-b735-bb82ecbeb249_Hector%20Ruben%20Estevez.jpeg</t>
+  </si>
+  <si>
+    <t>Evidencia_Activacion_PSL_Sharpie</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,13 +227,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +434,7 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{2481D1ED-0923-463A-9844-953EC81748EE}" name="Evidencia_ACtivacion_PSL_Sharpie" dataDxfId="0">
+    <tableColumn id="19" xr3:uid="{2481D1ED-0923-463A-9844-953EC81748EE}" name="Evidencia_Activacion_PSL_Sharpie" dataDxfId="0">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r11debcaacf20446fb636cd1accf9e03b"/>
@@ -770,17 +769,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="5" max="5" width="35.1796875" customWidth="1"/>
     <col min="6" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="19" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -836,10 +835,10 @@
         <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>13</v>
       </c>
@@ -850,22 +849,22 @@
         <v>46263.477986111109</v>
       </c>
       <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="3" spans="1:19" ht="15">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>16</v>
       </c>
@@ -876,19 +875,19 @@
         <v>46263.509398148097</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -898,7 +897,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>17</v>
       </c>
@@ -909,19 +908,19 @@
         <v>46263.561458333301</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -931,7 +930,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>18</v>
       </c>
@@ -942,16 +941,16 @@
         <v>46263.585462962998</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="H5" s="3"/>
       <c r="J5" s="3"/>
@@ -960,11 +959,11 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>19</v>
       </c>
@@ -975,21 +974,21 @@
         <v>46263.586550925902</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -997,7 +996,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>20</v>
       </c>
@@ -1008,21 +1007,21 @@
         <v>46263.590648148202</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -1030,7 +1029,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>21</v>
       </c>
@@ -1041,19 +1040,19 @@
         <v>46263.6006597222</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -1063,7 +1062,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>22</v>
       </c>
@@ -1074,16 +1073,16 @@
         <v>46263.602928240703</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H9" s="3"/>
       <c r="J9" s="3"/>
@@ -1093,10 +1092,10 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>23</v>
       </c>
@@ -1107,16 +1106,16 @@
         <v>46263.635069444397</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="H10" s="3"/>
       <c r="J10" s="3"/>
@@ -1127,11 +1126,11 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="S10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
-      <c r="A11" s="5">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>24</v>
       </c>
       <c r="B11" s="2">
@@ -1141,19 +1140,18 @@
         <v>46263.6403125</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="G11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="5"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1161,10 +1159,8 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5" t="s">
-        <v>51</v>
+      <c r="S11" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B920B7F8-6117-4DFD-BF9B-51D8AB75555F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05CC10E1-DB87-460F-86C2-9F432E844E57}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
   <si>
     <t>Id</t>
   </si>
@@ -92,6 +92,9 @@
     <t>Evidencia_Community_Board</t>
   </si>
   <si>
+    <t>Evidencia_ACtivacion_PSL_Sharpie</t>
+  </si>
+  <si>
     <t>SBMX38333@starbucks.com.mx</t>
   </si>
   <si>
@@ -149,9 +152,6 @@
     <t>Rack FHW</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17880338415158301924124629037929_Starbucks%20San%20Miguel.jpg</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Galerias%20P.jpg</t>
   </si>
   <si>
@@ -189,9 +189,6 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/475806a8-ee33-4297-b735-bb82ecbeb249_Hector%20Ruben%20Estevez.jpeg</t>
-  </si>
-  <si>
-    <t>Evidencia_Activacion_PSL_Sharpie</t>
   </si>
 </sst>
 </file>
@@ -305,8 +302,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S11" totalsRowShown="0">
-  <autoFilter ref="A1:S11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S10" totalsRowShown="0">
+  <autoFilter ref="A1:S10" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -434,7 +431,7 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{2481D1ED-0923-463A-9844-953EC81748EE}" name="Evidencia_Activacion_PSL_Sharpie" dataDxfId="0">
+    <tableColumn id="19" xr3:uid="{2481D1ED-0923-463A-9844-953EC81748EE}" name="Evidencia_ACtivacion_PSL_Sharpie" dataDxfId="0">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r11debcaacf20446fb636cd1accf9e03b"/>
@@ -768,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -835,7 +832,7 @@
         <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
@@ -849,19 +846,19 @@
         <v>46263.477986111109</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
@@ -875,19 +872,19 @@
         <v>46263.509398148097</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -908,19 +905,19 @@
         <v>46263.561458333301</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -941,16 +938,16 @@
         <v>46263.585462962998</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5" s="3"/>
       <c r="J5" s="3"/>
@@ -959,36 +956,36 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P5" s="3"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2">
-        <v>46263.585497685199</v>
+        <v>46263.590254629598</v>
       </c>
       <c r="C6" s="2">
-        <v>46263.586550925902</v>
+        <v>46263.590648148202</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -998,31 +995,31 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="2">
-        <v>46263.590254629598</v>
+        <v>46263.600185185198</v>
       </c>
       <c r="C7" s="2">
-        <v>46263.590648148202</v>
+        <v>46263.6006597222</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -1031,58 +1028,58 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2">
-        <v>46263.600185185198</v>
+        <v>46263.601550925901</v>
       </c>
       <c r="C8" s="2">
-        <v>46263.6006597222</v>
+        <v>46263.602928240703</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>39</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="H8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
+      <c r="P8" s="3" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="2">
-        <v>46263.601550925901</v>
+        <v>46263.634525463</v>
       </c>
       <c r="C9" s="2">
-        <v>46263.602928240703</v>
+        <v>46263.635069444397</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H9" s="3"/>
       <c r="J9" s="3"/>
@@ -1091,28 +1088,29 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
-      <c r="P9" s="3" t="s">
-        <v>41</v>
+      <c r="P9" s="3"/>
+      <c r="S9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2">
-        <v>46263.634525463</v>
+        <v>46263.639826388899</v>
       </c>
       <c r="C10" s="2">
-        <v>46263.635069444397</v>
+        <v>46263.6403125</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>45</v>
@@ -1126,40 +1124,6 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="S10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2">
-        <v>46263.639826388899</v>
-      </c>
-      <c r="C11" s="2">
-        <v>46263.6403125</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="S11" t="s">
         <v>50</v>
       </c>
     </row>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05CC10E1-DB87-460F-86C2-9F432E844E57}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C744C29D-1080-4DEB-BF59-3F44F46445CC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>Id</t>
   </si>
@@ -189,13 +189,37 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/475806a8-ee33-4297-b735-bb82ecbeb249_Hector%20Ruben%20Estevez.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38394@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks CC Lomas Verdes</t>
+  </si>
+  <si>
+    <t>38394</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_0530_Starbucks%20CC%20Lomas%20V.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38456@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Las Flores</t>
+  </si>
+  <si>
+    <t>38456</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260829-WA0000_Starbucks%20Plaza%20Las.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,12 +248,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -302,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S10" totalsRowShown="0">
-  <autoFilter ref="A1:S10" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S12" totalsRowShown="0">
+  <autoFilter ref="A1:S12" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -442,7 +467,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="24" latestEventMarker="247">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="26" latestEventMarker="249">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -765,18 +790,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:S12"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.1796875" customWidth="1"/>
+    <col min="5" max="5" width="35.140625" customWidth="1"/>
     <col min="6" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="19" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -835,7 +860,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19">
       <c r="A2">
         <v>13</v>
       </c>
@@ -861,7 +886,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>16</v>
       </c>
@@ -894,7 +919,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>17</v>
       </c>
@@ -927,7 +952,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>18</v>
       </c>
@@ -960,7 +985,7 @@
       </c>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>20</v>
       </c>
@@ -993,7 +1018,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>21</v>
       </c>
@@ -1026,7 +1051,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>22</v>
       </c>
@@ -1059,7 +1084,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>23</v>
       </c>
@@ -1093,7 +1118,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>24</v>
       </c>
@@ -1127,6 +1152,80 @@
         <v>50</v>
       </c>
     </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="5">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46263.660752314798</v>
+      </c>
+      <c r="C11" s="2">
+        <v>46263.661296296297</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="5">
+        <v>26</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46263.660555555602</v>
+      </c>
+      <c r="C12" s="2">
+        <v>46263.6644675926</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C744C29D-1080-4DEB-BF59-3F44F46445CC}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E58BC3D-8F6E-4605-8DF3-F950C9C0436A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
   <si>
     <t>Id</t>
   </si>
@@ -213,6 +213,27 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260829-WA0000_Starbucks%20Plaza%20Las.jpg</t>
+  </si>
+  <si>
+    <t>Programacion Hornos Merry - Focaccia</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG_4957_Starbucks%20Galerias%20P.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38368@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Luna Park</t>
+  </si>
+  <si>
+    <t>38368</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_0012_Starbucks%20Luna%20Park.jpeg</t>
   </si>
 </sst>
 </file>
@@ -327,8 +348,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S12" totalsRowShown="0">
-  <autoFilter ref="A1:S12" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S14" totalsRowShown="0">
+  <autoFilter ref="A1:S14" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -467,7 +488,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="26" latestEventMarker="249">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="28" latestEventMarker="251">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -790,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -798,7 +819,8 @@
     <col min="6" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="19" customWidth="1"/>
+    <col min="17" max="18" width="19" customWidth="1"/>
+    <col min="19" max="19" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -1153,7 +1175,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="5">
+      <c r="A11">
         <v>25</v>
       </c>
       <c r="B11" s="2">
@@ -1175,7 +1197,6 @@
         <v>45</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="5"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1183,14 +1204,12 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5" t="s">
+      <c r="S11" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="5">
+      <c r="A12">
         <v>26</v>
       </c>
       <c r="B12" s="2">
@@ -1214,7 +1233,6 @@
       <c r="H12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I12" s="5"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1222,9 +1240,79 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46263.718784722201</v>
+      </c>
+      <c r="C13" s="2">
+        <v>46263.750277777799</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="5">
+        <v>28</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46263.939942129597</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46263.940856481502</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E58BC3D-8F6E-4605-8DF3-F950C9C0436A}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86AA3B54-4EF3-435D-B185-5754F7A02894}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="144">
   <si>
     <t>Id</t>
   </si>
@@ -234,6 +234,240 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_0012_Starbucks%20Luna%20Park.jpeg</t>
+  </si>
+  <si>
+    <t>jaime.correa@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Jaime Arath Correa Sepulveda</t>
+  </si>
+  <si>
+    <t>38590</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/018B7A6B-C28B-4D68-B28B-65F26214B427_Jaime%20Arath%20Correa%20S.jpeg</t>
+  </si>
+  <si>
+    <t>sergio.parra@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Sergio Daniel Parra Barrera</t>
+  </si>
+  <si>
+    <t>38561</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG20260830080930_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17881093687519018223576355074947_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38695@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks CEMTRAM 4 Caminos carso</t>
+  </si>
+  <si>
+    <t>38695</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Starbucks%20CEMTRAM%204.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17881094439622693380620315597672_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_3720_Starbucks%20CEMTRAM%204.png</t>
+  </si>
+  <si>
+    <t>Max &amp; Min </t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/17881094997846654326704292984852_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20CEMTRAM%204.jpg</t>
+  </si>
+  <si>
+    <t>maria.reyesr@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Reyes Rivera</t>
+  </si>
+  <si>
+    <t>38535</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/D7CBA719-6439-4BC0-B409-EB3FF11BF333_Maria%20Fernanda%20Reyes.jpeg</t>
+  </si>
+  <si>
+    <t>vanessa.carreno@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Vanessa Carreño Rios</t>
+  </si>
+  <si>
+    <t>43195</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/parque%20jardin%20sharpies_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>38527</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/camarones%20sharpies_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>43132</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/vista%20norte%20sharpies_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>QR - Qualtrics</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta%202/IMG_3815_Starbucks%20CEMTRAM%204.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38656@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Viveros Santa Monica</t>
+  </si>
+  <si>
+    <t>38656</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/20260830_110752_Starbucks%20Viveros%20Sa.jpg</t>
+  </si>
+  <si>
+    <t>sbmx43193@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Cosmopol N1</t>
+  </si>
+  <si>
+    <t>43193</t>
+  </si>
+  <si>
+    <t>Community Board</t>
+  </si>
+  <si>
+    <t>No </t>
+  </si>
+  <si>
+    <t>alejandro.castro@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Alejandro Josue Castro Maya</t>
+  </si>
+  <si>
+    <t>38661</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/5519cf44-8e7f-4d67-895f-b78d895dbab6_Alejandro%20Josue%20Cast.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38117@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Satelite</t>
+  </si>
+  <si>
+    <t>38117</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Starbucks%20Satelite.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38937@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Parque Tepeyac</t>
+  </si>
+  <si>
+    <t>38937</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_20260830_121328351_HDR_Starbucks%20Parque%20Tep.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260829-WA0027_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38475@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Satélite Centro Cívico</t>
+  </si>
+  <si>
+    <t>38475</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17881150585098535935541666187592_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38197@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Echegaray</t>
+  </si>
+  <si>
+    <t>38197</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/BEF5905E-3E9B-4FBC-8088-1B753F1E8974_Starbucks%20Echegaray.png</t>
+  </si>
+  <si>
+    <t>SBMX38149@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Bellavista</t>
+  </si>
+  <si>
+    <t>38149</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/1788116994099344564503079909352_Starbucks%20Bellavista.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38266@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks San Mateo</t>
+  </si>
+  <si>
+    <t>38266</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881170455719090746443719375904_Starbucks%20San%20Mateo.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38339@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks San Marcos</t>
+  </si>
+  <si>
+    <t>38339</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/1788117533182266819632014442179_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>38363</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/17881180025888881029859821743595_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/1788118152321876332634985288754_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17881192077501792090407606630974_Starbucks%20San%20Marcos.jpg</t>
   </si>
 </sst>
 </file>
@@ -348,8 +582,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S14" totalsRowShown="0">
-  <autoFilter ref="A1:S14" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S41" totalsRowShown="0">
+  <autoFilter ref="A1:S41" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -488,7 +722,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="28" latestEventMarker="251">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="55" latestEventMarker="278">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -811,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -1278,7 +1512,7 @@
       <c r="P13" s="3"/>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="5">
+      <c r="A14">
         <v>28</v>
       </c>
       <c r="B14" s="2">
@@ -1302,7 +1536,6 @@
       <c r="H14" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="5"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1310,9 +1543,1005 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="5">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46264.456967592603</v>
+      </c>
+      <c r="C15" s="2">
+        <v>46264.457650463002</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" s="5">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46264.458229166703</v>
+      </c>
+      <c r="C16" s="2">
+        <v>46264.4588657407</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="5">
+        <v>31</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46264.459953703699</v>
+      </c>
+      <c r="C17" s="2">
+        <v>46264.460682870398</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" s="5">
+        <v>32</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46264.456678240698</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46264.460810185199</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" s="5">
+        <v>33</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46264.460879629602</v>
+      </c>
+      <c r="C19" s="2">
+        <v>46264.461331018501</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" s="5">
+        <v>34</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46264.461099537002</v>
+      </c>
+      <c r="C20" s="2">
+        <v>46264.461631944403</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" s="5">
+        <v>35</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46264.4614814815</v>
+      </c>
+      <c r="C21" s="2">
+        <v>46264.462083333303</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="5">
+        <v>36</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46264.461689814802</v>
+      </c>
+      <c r="C22" s="2">
+        <v>46264.463194444397</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="5">
+        <v>37</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46264.464918981503</v>
+      </c>
+      <c r="C23" s="2">
+        <v>46264.465567129599</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="5">
+        <v>38</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46264.462222222202</v>
+      </c>
+      <c r="C24" s="2">
+        <v>46264.466273148202</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="5">
+        <v>39</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46264.467141203699</v>
+      </c>
+      <c r="C25" s="2">
+        <v>46264.468124999999</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" s="5">
+        <v>40</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46264.4682523148</v>
+      </c>
+      <c r="C26" s="2">
+        <v>46264.468564814801</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="5">
+        <v>41</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46264.463252314803</v>
+      </c>
+      <c r="C27" s="2">
+        <v>46264.468680555598</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" s="5">
+        <v>42</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46264.466886574097</v>
+      </c>
+      <c r="C28" s="2">
+        <v>46264.4688425926</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" s="3"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" s="5">
+        <v>43</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46264.483124999999</v>
+      </c>
+      <c r="C29" s="2">
+        <v>46264.483715277798</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" s="5">
+        <v>44</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46264.489918981497</v>
+      </c>
+      <c r="C30" s="2">
+        <v>46264.490428240701</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" s="5">
+        <v>45</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46264.503553240698</v>
+      </c>
+      <c r="C31" s="2">
+        <v>46264.504108796304</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H31" s="3"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" s="5">
+        <v>46</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46264.501273148097</v>
+      </c>
+      <c r="C32" s="2">
+        <v>46264.5157175926</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" s="5">
+        <v>47</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46264.524537037003</v>
+      </c>
+      <c r="C33" s="2">
+        <v>46264.525266203702</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H33" s="3"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" s="5">
+        <v>48</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46264.526053240697</v>
+      </c>
+      <c r="C34" s="2">
+        <v>46264.526550925897</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H34" s="3"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" s="5">
+        <v>49</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46264.527280092603</v>
+      </c>
+      <c r="C35" s="2">
+        <v>46264.5301273148</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H35" s="3"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" s="5">
+        <v>50</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46264.548101851797</v>
+      </c>
+      <c r="C36" s="2">
+        <v>46264.548877314803</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" s="3"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19">
+      <c r="A37" s="5">
+        <v>51</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46264.545902777798</v>
+      </c>
+      <c r="C37" s="2">
+        <v>46264.549687500003</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" s="5">
+        <v>52</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46264.554525462998</v>
+      </c>
+      <c r="C38" s="2">
+        <v>46264.555729166699</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I38" s="5"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" s="5">
+        <v>53</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46264.559629629599</v>
+      </c>
+      <c r="C39" s="2">
+        <v>46264.561261574097</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I39" s="5"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" s="5">
+        <v>54</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46264.5613310185</v>
+      </c>
+      <c r="C40" s="2">
+        <v>46264.562534722201</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H40" s="3"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+    </row>
+    <row r="41" spans="1:19">
+      <c r="A41" s="5">
+        <v>55</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46264.573425925897</v>
+      </c>
+      <c r="C41" s="2">
+        <v>46264.574652777803</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H41" s="3"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86AA3B54-4EF3-435D-B185-5754F7A02894}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D677282-BFB4-40B2-B35F-063BAAFCC5FF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="150">
   <si>
     <t>Id</t>
   </si>
@@ -458,26 +458,52 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/1788117533182266819632014442179_Starbucks%20San%20Marcos.jpg</t>
   </si>
   <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/1788118152321876332634985288754_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17881192077501792090407606630974_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38604@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Cosmopol</t>
+  </si>
+  <si>
+    <t>38604</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_20260830_143227_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>carlos.cortes@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Carlos Cortes Aguilar</t>
+  </si>
+  <si>
     <t>38363</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/17881180025888881029859821743595_Starbucks%20San%20Marcos.jpg</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/1788118152321876332634985288754_Starbucks%20San%20Marcos.jpg</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17881192077501792090407606630974_Starbucks%20San%20Marcos.jpg</t>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_20260830_145340_941_Carlos%20Cortes%20Aguila.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -500,8 +526,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -509,9 +536,10 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
@@ -582,8 +610,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S41" totalsRowShown="0">
-  <autoFilter ref="A1:S41" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S42" totalsRowShown="0">
+  <autoFilter ref="A1:S42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -722,7 +750,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="55" latestEventMarker="278">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="57" latestEventMarker="280">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1045,10 +1073,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
     <col min="5" max="5" width="35.140625" customWidth="1"/>
     <col min="6" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
@@ -1545,7 +1574,7 @@
       <c r="P14" s="3"/>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="5">
+      <c r="A15">
         <v>29</v>
       </c>
       <c r="B15" s="2">
@@ -1567,7 +1596,6 @@
         <v>45</v>
       </c>
       <c r="H15" s="3"/>
-      <c r="I15" s="5"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1575,14 +1603,12 @@
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5" t="s">
+      <c r="S15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="5">
+      <c r="A16">
         <v>30</v>
       </c>
       <c r="B16" s="2">
@@ -1606,7 +1632,6 @@
       <c r="H16" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="5"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1614,12 +1639,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="5">
+      <c r="A17">
         <v>31</v>
       </c>
       <c r="B17" s="2">
@@ -1641,7 +1663,6 @@
         <v>37</v>
       </c>
       <c r="H17" s="3"/>
-      <c r="I17" s="5"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
         <v>74</v>
@@ -1651,12 +1672,9 @@
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="5">
+      <c r="A18">
         <v>32</v>
       </c>
       <c r="B18" s="2">
@@ -1678,7 +1696,6 @@
         <v>45</v>
       </c>
       <c r="H18" s="3"/>
-      <c r="I18" s="5"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -1686,14 +1703,12 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5" t="s">
+      <c r="S18" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="5">
+      <c r="A19">
         <v>33</v>
       </c>
       <c r="B19" s="2">
@@ -1715,7 +1730,6 @@
         <v>35</v>
       </c>
       <c r="H19" s="3"/>
-      <c r="I19" s="5"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
@@ -1725,12 +1739,9 @@
         <v>79</v>
       </c>
       <c r="P19" s="3"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="5">
+      <c r="A20">
         <v>34</v>
       </c>
       <c r="B20" s="2">
@@ -1754,7 +1765,6 @@
       <c r="H20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I20" s="5"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
@@ -1762,12 +1772,9 @@
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="5">
+      <c r="A21">
         <v>35</v>
       </c>
       <c r="B21" s="2">
@@ -1789,7 +1796,6 @@
         <v>81</v>
       </c>
       <c r="H21" s="3"/>
-      <c r="I21" s="5"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
@@ -1799,12 +1805,9 @@
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
     </row>
     <row r="22" spans="1:19">
-      <c r="A22" s="5">
+      <c r="A22">
         <v>36</v>
       </c>
       <c r="B22" s="2">
@@ -1826,7 +1829,6 @@
         <v>37</v>
       </c>
       <c r="H22" s="3"/>
-      <c r="I22" s="5"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
         <v>83</v>
@@ -1836,12 +1838,9 @@
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
     </row>
     <row r="23" spans="1:19">
-      <c r="A23" s="5">
+      <c r="A23">
         <v>37</v>
       </c>
       <c r="B23" s="2">
@@ -1863,7 +1862,6 @@
         <v>45</v>
       </c>
       <c r="H23" s="3"/>
-      <c r="I23" s="5"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
@@ -1871,14 +1869,12 @@
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5" t="s">
+      <c r="S23" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="5">
+      <c r="A24">
         <v>38</v>
       </c>
       <c r="B24" s="2">
@@ -1900,7 +1896,6 @@
         <v>45</v>
       </c>
       <c r="H24" s="3"/>
-      <c r="I24" s="5"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
@@ -1908,14 +1903,12 @@
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5" t="s">
+      <c r="S24" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="5">
+      <c r="A25">
         <v>39</v>
       </c>
       <c r="B25" s="2">
@@ -1937,7 +1930,6 @@
         <v>45</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="5"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
@@ -1945,14 +1937,12 @@
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5" t="s">
+      <c r="S25" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="5">
+      <c r="A26">
         <v>40</v>
       </c>
       <c r="B26" s="2">
@@ -1974,7 +1964,6 @@
         <v>45</v>
       </c>
       <c r="H26" s="3"/>
-      <c r="I26" s="5"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
@@ -1982,14 +1971,12 @@
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5" t="s">
+      <c r="S26" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="5">
+      <c r="A27">
         <v>41</v>
       </c>
       <c r="B27" s="2">
@@ -2011,7 +1998,6 @@
         <v>96</v>
       </c>
       <c r="H27" s="3"/>
-      <c r="I27" s="5"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3" t="s">
@@ -2021,12 +2007,9 @@
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
     </row>
     <row r="28" spans="1:19">
-      <c r="A28" s="5">
+      <c r="A28">
         <v>42</v>
       </c>
       <c r="B28" s="2">
@@ -2048,7 +2031,6 @@
         <v>45</v>
       </c>
       <c r="H28" s="3"/>
-      <c r="I28" s="5"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
@@ -2056,14 +2038,12 @@
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5" t="s">
+      <c r="S28" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:19">
-      <c r="A29" s="5">
+      <c r="A29">
         <v>43</v>
       </c>
       <c r="B29" s="2">
@@ -2085,7 +2065,6 @@
         <v>105</v>
       </c>
       <c r="H29" s="3"/>
-      <c r="I29" s="5"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -2093,14 +2072,12 @@
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
-      <c r="Q29" s="5" t="s">
+      <c r="Q29" t="s">
         <v>106</v>
       </c>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
     </row>
     <row r="30" spans="1:19">
-      <c r="A30" s="5">
+      <c r="A30">
         <v>44</v>
       </c>
       <c r="B30" s="2">
@@ -2122,7 +2099,6 @@
         <v>45</v>
       </c>
       <c r="H30" s="3"/>
-      <c r="I30" s="5"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
@@ -2130,14 +2106,12 @@
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5" t="s">
+      <c r="S30" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:19">
-      <c r="A31" s="5">
+      <c r="A31">
         <v>45</v>
       </c>
       <c r="B31" s="2">
@@ -2159,7 +2133,6 @@
         <v>45</v>
       </c>
       <c r="H31" s="3"/>
-      <c r="I31" s="5"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
@@ -2167,14 +2140,12 @@
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5" t="s">
+      <c r="S31" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:19">
-      <c r="A32" s="5">
+      <c r="A32">
         <v>46</v>
       </c>
       <c r="B32" s="2">
@@ -2196,7 +2167,6 @@
         <v>45</v>
       </c>
       <c r="H32" s="3"/>
-      <c r="I32" s="5"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -2204,14 +2174,12 @@
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5" t="s">
+      <c r="S32" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="5">
+      <c r="A33">
         <v>47</v>
       </c>
       <c r="B33" s="2">
@@ -2233,7 +2201,6 @@
         <v>45</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="5"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -2241,14 +2208,12 @@
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5" t="s">
+      <c r="S33" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:19">
-      <c r="A34" s="5">
+      <c r="A34">
         <v>48</v>
       </c>
       <c r="B34" s="2">
@@ -2270,7 +2235,6 @@
         <v>40</v>
       </c>
       <c r="H34" s="3"/>
-      <c r="I34" s="5"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -2280,12 +2244,9 @@
       <c r="P34" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
-      <c r="S34" s="5"/>
     </row>
     <row r="35" spans="1:19">
-      <c r="A35" s="5">
+      <c r="A35">
         <v>49</v>
       </c>
       <c r="B35" s="2">
@@ -2307,7 +2268,6 @@
         <v>45</v>
       </c>
       <c r="H35" s="3"/>
-      <c r="I35" s="5"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -2315,14 +2275,12 @@
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
-      <c r="S35" s="5" t="s">
+      <c r="S35" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="5">
+      <c r="A36">
         <v>50</v>
       </c>
       <c r="B36" s="2">
@@ -2344,7 +2302,6 @@
         <v>45</v>
       </c>
       <c r="H36" s="3"/>
-      <c r="I36" s="5"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -2352,14 +2309,12 @@
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
-      <c r="S36" s="5" t="s">
+      <c r="S36" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="5">
+      <c r="A37">
         <v>51</v>
       </c>
       <c r="B37" s="2">
@@ -2381,7 +2336,6 @@
         <v>45</v>
       </c>
       <c r="H37" s="3"/>
-      <c r="I37" s="5"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
@@ -2389,14 +2343,12 @@
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5" t="s">
+      <c r="S37" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
-      <c r="A38" s="5">
+    <row r="38" spans="1:19" ht="15">
+      <c r="A38">
         <v>52</v>
       </c>
       <c r="B38" s="2">
@@ -2417,10 +2369,9 @@
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I38" s="5"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
@@ -2428,19 +2379,16 @@
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
     </row>
     <row r="39" spans="1:19">
-      <c r="A39" s="5">
-        <v>53</v>
+      <c r="A39">
+        <v>54</v>
       </c>
       <c r="B39" s="2">
-        <v>46264.559629629599</v>
+        <v>46264.5613310185</v>
       </c>
       <c r="C39" s="2">
-        <v>46264.561261574097</v>
+        <v>46264.562534722201</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>136</v>
@@ -2449,35 +2397,31 @@
         <v>137</v>
       </c>
       <c r="F39" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I39" s="5"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
     </row>
     <row r="40" spans="1:19">
-      <c r="A40" s="5">
-        <v>54</v>
+      <c r="A40">
+        <v>55</v>
       </c>
       <c r="B40" s="2">
-        <v>46264.5613310185</v>
+        <v>46264.573425925897</v>
       </c>
       <c r="C40" s="2">
-        <v>46264.562534722201</v>
+        <v>46264.574652777803</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>136</v>
@@ -2489,65 +2433,96 @@
         <v>138</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H40" s="3"/>
-      <c r="I40" s="5"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3" t="s">
-        <v>142</v>
-      </c>
+      <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
+      <c r="O40" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="P40" s="3"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="5"/>
     </row>
     <row r="41" spans="1:19">
-      <c r="A41" s="5">
-        <v>55</v>
+      <c r="A41">
+        <v>56</v>
       </c>
       <c r="B41" s="2">
-        <v>46264.573425925897</v>
+        <v>46264.606041666702</v>
       </c>
       <c r="C41" s="2">
-        <v>46264.574652777803</v>
+        <v>46264.606446759302</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H41" s="3"/>
-      <c r="I41" s="5"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
-      <c r="O41" s="3" t="s">
-        <v>143</v>
-      </c>
+      <c r="O41" s="3"/>
       <c r="P41" s="3"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
-    </row>
+      <c r="S41" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="15">
+      <c r="A42">
+        <v>57</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46264.623680555596</v>
+      </c>
+      <c r="C42" s="2">
+        <v>46264.624201388899</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="S42" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="15"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D677282-BFB4-40B2-B35F-063BAAFCC5FF}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9EF8C40-343D-4346-AB1E-29731B719335}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="168">
   <si>
     <t>Id</t>
   </si>
@@ -486,6 +486,60 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_20260830_145340_941_Carlos%20Cortes%20Aguila.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Starbucks%20Luna%20Park.jpg</t>
+  </si>
+  <si>
+    <t>juan.santiago@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Juan Jose Santiago Del Angel</t>
+  </si>
+  <si>
+    <t>38119</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/67333_Juan%20Jose%20Santiago%20D.jpg</t>
+  </si>
+  <si>
+    <t>38411</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/5f0ecd71-358c-4bf4-ad69-e0ad133d1c28_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>38651</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/fcbf3801-9c7a-4c67-843c-c4579cc9cfd3_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>38205</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/3ac11f1b-506c-4757-8051-c9fb8a9eff4a_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>38546</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/c7d2f1c5-5959-41ae-a712-59c8594bd02c_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_7697_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>38677</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/22ad3577-87a2-439b-915e-0b4eafc2871e_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>43111</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/8a1e142b-2f6f-4bb1-9160-16341ee3dd42_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
   </si>
 </sst>
 </file>
@@ -530,13 +584,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -610,8 +665,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S42" totalsRowShown="0">
-  <autoFilter ref="A1:S42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S51" totalsRowShown="0">
+  <autoFilter ref="A1:S51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -750,7 +805,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="57" latestEventMarker="280">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="66" latestEventMarker="289">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1073,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -2514,7 +2569,337 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15"/>
+    <row r="43" spans="1:19" ht="15">
+      <c r="A43">
+        <v>58</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46264.655775462998</v>
+      </c>
+      <c r="C43" s="2">
+        <v>46264.662546296298</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="S43" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="15">
+      <c r="A44" s="6">
+        <v>59</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46264.675925925898</v>
+      </c>
+      <c r="C44" s="2">
+        <v>46264.676365740699</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19">
+      <c r="A45" s="6">
+        <v>60</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46264.6768981481</v>
+      </c>
+      <c r="C45" s="2">
+        <v>46264.677418981497</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H45" s="3"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="6"/>
+      <c r="R45" s="6"/>
+      <c r="S45" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19">
+      <c r="A46" s="6">
+        <v>61</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46264.677881944401</v>
+      </c>
+      <c r="C46" s="2">
+        <v>46264.678506944401</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
+      <c r="A47" s="6">
+        <v>62</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46264.679108796299</v>
+      </c>
+      <c r="C47" s="2">
+        <v>46264.679386574098</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="6"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" s="6">
+        <v>63</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46264.679988425902</v>
+      </c>
+      <c r="C48" s="2">
+        <v>46264.680462962999</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H48" s="3"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19">
+      <c r="A49" s="6">
+        <v>64</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46264.680335648103</v>
+      </c>
+      <c r="C49" s="2">
+        <v>46264.680706018502</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H49" s="3"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="6"/>
+      <c r="R49" s="6"/>
+      <c r="S49" s="6"/>
+    </row>
+    <row r="50" spans="1:19">
+      <c r="A50" s="6">
+        <v>65</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46264.680925925903</v>
+      </c>
+      <c r="C50" s="2">
+        <v>46264.681180555599</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H50" s="3"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="6"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="15">
+      <c r="A51" s="6">
+        <v>66</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46264.681273148097</v>
+      </c>
+      <c r="C51" s="2">
+        <v>46264.681481481501</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H51" s="3"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="6"/>
+      <c r="R51" s="6"/>
+      <c r="S51" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9EF8C40-343D-4346-AB1E-29731B719335}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CD15316-0A72-4D4A-9890-EE7A453589D7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -527,9 +527,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/c7d2f1c5-5959-41ae-a712-59c8594bd02c_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_7697_Starbucks%20Mega%20Izcal.jpeg</t>
-  </si>
-  <si>
     <t>38677</t>
   </si>
   <si>
@@ -540,6 +537,9 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/8a1e142b-2f6f-4bb1-9160-16341ee3dd42_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_7697_Starbucks%20Mega%20Izcal%201.jpeg</t>
   </si>
 </sst>
 </file>
@@ -805,7 +805,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="66" latestEventMarker="289">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="67" latestEventMarker="290">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1128,7 +1128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -2790,32 +2790,30 @@
     </row>
     <row r="49" spans="1:19">
       <c r="A49" s="6">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B49" s="2">
-        <v>46264.680335648103</v>
+        <v>46264.680925925903</v>
       </c>
       <c r="C49" s="2">
-        <v>46264.680706018502</v>
+        <v>46264.681180555599</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="6"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="3" t="s">
-        <v>163</v>
-      </c>
+      <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
@@ -2823,17 +2821,19 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="6"/>
       <c r="R49" s="6"/>
-      <c r="S49" s="6"/>
-    </row>
-    <row r="50" spans="1:19">
+      <c r="S49" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="15">
       <c r="A50" s="6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B50" s="2">
-        <v>46264.680925925903</v>
+        <v>46264.681273148097</v>
       </c>
       <c r="C50" s="2">
-        <v>46264.681180555599</v>
+        <v>46264.681481481501</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>88</v>
@@ -2842,7 +2842,7 @@
         <v>89</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>45</v>
@@ -2859,35 +2859,37 @@
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
       <c r="S50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="15">
       <c r="A51" s="6">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B51" s="2">
-        <v>46264.681273148097</v>
+        <v>46264.6847569444</v>
       </c>
       <c r="C51" s="2">
-        <v>46264.681481481501</v>
+        <v>46264.685092592597</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="6"/>
       <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
+      <c r="K51" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
@@ -2895,19 +2897,19 @@
       <c r="P51" s="3"/>
       <c r="Q51" s="6"/>
       <c r="R51" s="6"/>
-      <c r="S51" s="6" t="s">
-        <v>167</v>
-      </c>
+      <c r="S51" s="6"/>
     </row>
     <row r="52" spans="1:19" ht="15"/>
+    <row r="53" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>
+    <hyperlink ref="K51" r:id="rId2" xr:uid="{C4821E21-FAA0-46D2-B8E3-D3BB8AD6B775}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CD15316-0A72-4D4A-9890-EE7A453589D7}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C7D5C58-BDF3-47A4-BF89-78A10EBF4AB7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="172">
   <si>
     <t>Id</t>
   </si>
@@ -540,6 +540,18 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_7697_Starbucks%20Mega%20Izcal%201.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38606@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Tlalnepantla Carso</t>
+  </si>
+  <si>
+    <t>38606</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_2695_Starbucks%20Tlalnepant.jpeg</t>
   </si>
 </sst>
 </file>
@@ -665,8 +677,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S51" totalsRowShown="0">
-  <autoFilter ref="A1:S51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S52" totalsRowShown="0">
+  <autoFilter ref="A1:S52" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -805,7 +817,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="67" latestEventMarker="290">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="68" latestEventMarker="291">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1128,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -2899,8 +2911,45 @@
       <c r="R51" s="6"/>
       <c r="S51" s="6"/>
     </row>
-    <row r="52" spans="1:19" ht="15"/>
+    <row r="52" spans="1:19" ht="15">
+      <c r="A52" s="6">
+        <v>68</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46264.691377314797</v>
+      </c>
+      <c r="C52" s="2">
+        <v>46264.691782407397</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I52" s="6"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="6"/>
+      <c r="R52" s="6"/>
+      <c r="S52" s="6"/>
+    </row>
     <row r="53" spans="1:19" ht="15"/>
+    <row r="54" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C7D5C58-BDF3-47A4-BF89-78A10EBF4AB7}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DE4DCD9-C8A4-4020-9B50-D4FE7DADA8F4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="181">
   <si>
     <t>Id</t>
   </si>
@@ -552,6 +552,33 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_2695_Starbucks%20Tlalnepant.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_2788_Starbucks%20Tlalnepant.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx43152@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Samara Satélite</t>
+  </si>
+  <si>
+    <t>43152</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/DAAA8494-3683-4C53-BDE3-BB265A9142D6_Starbucks%20Samara%20Sat.png</t>
+  </si>
+  <si>
+    <t>ricardo.romo@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Ricardo Romo Morales</t>
+  </si>
+  <si>
+    <t>38431</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/a17f3023-aea8-4ab9-90ce-f9cfb251e14b_Ricardo%20Romo%20Morales.jpeg</t>
   </si>
 </sst>
 </file>
@@ -677,8 +704,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S52" totalsRowShown="0">
-  <autoFilter ref="A1:S52" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S55" totalsRowShown="0">
+  <autoFilter ref="A1:S55" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -817,7 +844,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="68" latestEventMarker="291">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="71" latestEventMarker="294">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1140,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -2948,8 +2975,119 @@
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
     </row>
-    <row r="53" spans="1:19" ht="15"/>
-    <row r="54" spans="1:19" ht="15"/>
+    <row r="53" spans="1:19" ht="15">
+      <c r="A53" s="6">
+        <v>69</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46264.691990740699</v>
+      </c>
+      <c r="C53" s="2">
+        <v>46264.692291666703</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H53" s="3"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+      <c r="Q53" s="6"/>
+      <c r="R53" s="6"/>
+      <c r="S53" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="15">
+      <c r="A54" s="6">
+        <v>70</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46264.688379629602</v>
+      </c>
+      <c r="C54" s="2">
+        <v>46264.693749999999</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H54" s="3"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="6"/>
+      <c r="R54" s="6"/>
+      <c r="S54" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="15">
+      <c r="A55" s="6">
+        <v>71</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46264.692800925899</v>
+      </c>
+      <c r="C55" s="2">
+        <v>46264.6941898148</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H55" s="3"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="6"/>
+      <c r="R55" s="6"/>
+      <c r="S55" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="15"/>
+    <row r="57" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DE4DCD9-C8A4-4020-9B50-D4FE7DADA8F4}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE101DBD-0083-4312-9DCD-BCFDF02B7518}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="189">
   <si>
     <t>Id</t>
   </si>
@@ -579,6 +579,30 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/a17f3023-aea8-4ab9-90ce-f9cfb251e14b_Ricardo%20Romo%20Morales.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38770@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Gustavo Baz 29</t>
+  </si>
+  <si>
+    <t>38770</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Starbucks%20Gustavo%20Ba.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38427@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks CC Plaza Satélite</t>
+  </si>
+  <si>
+    <t>38427</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Starbucks%20CC%20Plaza%20S.jpg</t>
   </si>
 </sst>
 </file>
@@ -704,8 +728,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S55" totalsRowShown="0">
-  <autoFilter ref="A1:S55" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S57" totalsRowShown="0">
+  <autoFilter ref="A1:S57" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -844,7 +868,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="71" latestEventMarker="294">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="73" latestEventMarker="296">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1167,7 +1191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:S59"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3086,8 +3110,82 @@
         <v>180</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15"/>
-    <row r="57" spans="1:19" ht="15"/>
+    <row r="56" spans="1:19" ht="15">
+      <c r="A56" s="6">
+        <v>72</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46264.701539351903</v>
+      </c>
+      <c r="C56" s="2">
+        <v>46264.702349537001</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H56" s="3"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="15">
+      <c r="A57" s="6">
+        <v>73</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46264.702962962998</v>
+      </c>
+      <c r="C57" s="2">
+        <v>46264.703969907401</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H57" s="3"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="6"/>
+      <c r="R57" s="6"/>
+      <c r="S57" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="15"/>
+    <row r="59" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE101DBD-0083-4312-9DCD-BCFDF02B7518}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F685CD0-F628-45A9-89C7-62C9ADA9858F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="193">
   <si>
     <t>Id</t>
   </si>
@@ -603,6 +603,18 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Starbucks%20CC%20Plaza%20S.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38458@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks El Rosario</t>
+  </si>
+  <si>
+    <t>38458</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/515AC9EF-8E43-402A-BB95-2CFA3C1130AB_Starbucks%20El%20Rosario.png</t>
   </si>
 </sst>
 </file>
@@ -728,8 +740,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S57" totalsRowShown="0">
-  <autoFilter ref="A1:S57" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S58" totalsRowShown="0">
+  <autoFilter ref="A1:S58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -868,7 +880,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="73" latestEventMarker="296">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="74" latestEventMarker="297">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1191,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:S60"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3184,8 +3196,45 @@
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="15"/>
+    <row r="58" spans="1:19" ht="15">
+      <c r="A58" s="6">
+        <v>74</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46264.708877314799</v>
+      </c>
+      <c r="C58" s="2">
+        <v>46264.709583333301</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H58" s="3"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
     <row r="59" spans="1:19" ht="15"/>
+    <row r="60" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F685CD0-F628-45A9-89C7-62C9ADA9858F}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8787BAC4-1ACE-46A0-81B7-2EC89A95710F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="218">
   <si>
     <t>Id</t>
   </si>
@@ -615,6 +615,81 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/515AC9EF-8E43-402A-BB95-2CFA3C1130AB_Starbucks%20El%20Rosario.png</t>
+  </si>
+  <si>
+    <t>kevin.suarez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Kevin Arturo Suarez Gonzalez</t>
+  </si>
+  <si>
+    <t>43130</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881312421266013797927664876544_Kevin%20Arturo%20Suarez.jpg</t>
+  </si>
+  <si>
+    <t>38207</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/48dceb70-c7c3-44fd-ac35-5ef43802bbe2_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20CEMTRAM%204.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38694@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Villas de la Hacienda</t>
+  </si>
+  <si>
+    <t>38694</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/AC05D239-2F70-4C7E-83E4-27F4FC8AD883_Starbucks%20Villas%20de.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38115@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Zona Azul</t>
+  </si>
+  <si>
+    <t>38115</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/940b3c25-338a-489a-807a-b0d1cfd57fb3_Starbucks%20Zona%20Azul.JPG</t>
+  </si>
+  <si>
+    <t>SBMX38186@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Arboledas</t>
+  </si>
+  <si>
+    <t>38186</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Starbucks%20Arboledas.jpg</t>
+  </si>
+  <si>
+    <t>enrique.cesar@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Enrique Cesar Flores</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0093_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0086_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260829-WA0169_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881192969132117885562748587632_Starbucks%20San%20Marcos.jpg</t>
   </si>
 </sst>
 </file>
@@ -740,8 +815,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S58" totalsRowShown="0">
-  <autoFilter ref="A1:S58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S68" totalsRowShown="0">
+  <autoFilter ref="A1:S68" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -880,7 +955,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="74" latestEventMarker="297">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="84" latestEventMarker="307">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1203,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S60"/>
+  <dimension ref="A1:S70"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -2679,7 +2754,7 @@
       </c>
     </row>
     <row r="44" spans="1:19" ht="15">
-      <c r="A44" s="6">
+      <c r="A44">
         <v>59</v>
       </c>
       <c r="B44" s="2">
@@ -2701,7 +2776,6 @@
         <v>45</v>
       </c>
       <c r="H44" s="3"/>
-      <c r="I44" s="6"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
@@ -2709,14 +2783,12 @@
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6" t="s">
+      <c r="S44" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:19">
-      <c r="A45" s="6">
+      <c r="A45">
         <v>60</v>
       </c>
       <c r="B45" s="2">
@@ -2738,7 +2810,6 @@
         <v>45</v>
       </c>
       <c r="H45" s="3"/>
-      <c r="I45" s="6"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
@@ -2746,14 +2817,12 @@
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="6" t="s">
+      <c r="S45" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:19">
-      <c r="A46" s="6">
+      <c r="A46">
         <v>61</v>
       </c>
       <c r="B46" s="2">
@@ -2775,7 +2844,6 @@
         <v>45</v>
       </c>
       <c r="H46" s="3"/>
-      <c r="I46" s="6"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
@@ -2783,14 +2851,12 @@
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6" t="s">
+      <c r="S46" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="6">
+      <c r="A47">
         <v>62</v>
       </c>
       <c r="B47" s="2">
@@ -2812,7 +2878,6 @@
         <v>45</v>
       </c>
       <c r="H47" s="3"/>
-      <c r="I47" s="6"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
@@ -2820,14 +2885,12 @@
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6" t="s">
+      <c r="S47" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:19">
-      <c r="A48" s="6">
+      <c r="A48">
         <v>63</v>
       </c>
       <c r="B48" s="2">
@@ -2849,7 +2912,6 @@
         <v>45</v>
       </c>
       <c r="H48" s="3"/>
-      <c r="I48" s="6"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
@@ -2857,14 +2919,12 @@
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
-      <c r="S48" s="6" t="s">
+      <c r="S48" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:19">
-      <c r="A49" s="6">
+      <c r="A49">
         <v>65</v>
       </c>
       <c r="B49" s="2">
@@ -2886,7 +2946,6 @@
         <v>45</v>
       </c>
       <c r="H49" s="3"/>
-      <c r="I49" s="6"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
@@ -2894,14 +2953,12 @@
       <c r="N49" s="3"/>
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="6"/>
-      <c r="S49" s="6" t="s">
+      <c r="S49" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="15">
-      <c r="A50" s="6">
+      <c r="A50">
         <v>66</v>
       </c>
       <c r="B50" s="2">
@@ -2923,7 +2980,6 @@
         <v>45</v>
       </c>
       <c r="H50" s="3"/>
-      <c r="I50" s="6"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
@@ -2931,14 +2987,12 @@
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6" t="s">
+      <c r="S50" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="15">
-      <c r="A51" s="6">
+      <c r="A51">
         <v>67</v>
       </c>
       <c r="B51" s="2">
@@ -2960,7 +3014,6 @@
         <v>37</v>
       </c>
       <c r="H51" s="3"/>
-      <c r="I51" s="6"/>
       <c r="J51" s="3"/>
       <c r="K51" s="5" t="s">
         <v>167</v>
@@ -2970,12 +3023,9 @@
       <c r="N51" s="3"/>
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="6"/>
-      <c r="S51" s="6"/>
     </row>
     <row r="52" spans="1:19" ht="15">
-      <c r="A52" s="6">
+      <c r="A52">
         <v>68</v>
       </c>
       <c r="B52" s="2">
@@ -2999,7 +3049,6 @@
       <c r="H52" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I52" s="6"/>
       <c r="J52" s="3"/>
       <c r="K52" s="5"/>
       <c r="L52" s="3"/>
@@ -3007,12 +3056,9 @@
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
     </row>
     <row r="53" spans="1:19" ht="15">
-      <c r="A53" s="6">
+      <c r="A53">
         <v>69</v>
       </c>
       <c r="B53" s="2">
@@ -3034,7 +3080,6 @@
         <v>45</v>
       </c>
       <c r="H53" s="3"/>
-      <c r="I53" s="6"/>
       <c r="J53" s="3"/>
       <c r="K53" s="5"/>
       <c r="L53" s="3"/>
@@ -3042,14 +3087,12 @@
       <c r="N53" s="3"/>
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="6"/>
-      <c r="S53" s="6" t="s">
+      <c r="S53" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="15">
-      <c r="A54" s="6">
+      <c r="A54">
         <v>70</v>
       </c>
       <c r="B54" s="2">
@@ -3071,7 +3114,6 @@
         <v>45</v>
       </c>
       <c r="H54" s="3"/>
-      <c r="I54" s="6"/>
       <c r="J54" s="3"/>
       <c r="K54" s="5"/>
       <c r="L54" s="3"/>
@@ -3079,14 +3121,12 @@
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6" t="s">
+      <c r="S54" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="15">
-      <c r="A55" s="6">
+      <c r="A55">
         <v>71</v>
       </c>
       <c r="B55" s="2">
@@ -3108,7 +3148,6 @@
         <v>45</v>
       </c>
       <c r="H55" s="3"/>
-      <c r="I55" s="6"/>
       <c r="J55" s="3"/>
       <c r="K55" s="5"/>
       <c r="L55" s="3"/>
@@ -3116,14 +3155,12 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
-      <c r="S55" s="6" t="s">
+      <c r="S55" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="15">
-      <c r="A56" s="6">
+      <c r="A56">
         <v>72</v>
       </c>
       <c r="B56" s="2">
@@ -3145,7 +3182,6 @@
         <v>45</v>
       </c>
       <c r="H56" s="3"/>
-      <c r="I56" s="6"/>
       <c r="J56" s="3"/>
       <c r="K56" s="5"/>
       <c r="L56" s="3"/>
@@ -3153,14 +3189,12 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6" t="s">
+      <c r="S56" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="15">
-      <c r="A57" s="6">
+      <c r="A57">
         <v>73</v>
       </c>
       <c r="B57" s="2">
@@ -3182,7 +3216,6 @@
         <v>45</v>
       </c>
       <c r="H57" s="3"/>
-      <c r="I57" s="6"/>
       <c r="J57" s="3"/>
       <c r="K57" s="5"/>
       <c r="L57" s="3"/>
@@ -3190,14 +3223,12 @@
       <c r="N57" s="3"/>
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
-      <c r="Q57" s="6"/>
-      <c r="R57" s="6"/>
-      <c r="S57" s="6" t="s">
+      <c r="S57" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="15">
-      <c r="A58" s="6">
+      <c r="A58">
         <v>74</v>
       </c>
       <c r="B58" s="2">
@@ -3219,7 +3250,6 @@
         <v>45</v>
       </c>
       <c r="H58" s="3"/>
-      <c r="I58" s="6"/>
       <c r="J58" s="3"/>
       <c r="K58" s="5"/>
       <c r="L58" s="3"/>
@@ -3227,14 +3257,382 @@
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
       <c r="P58" s="3"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="6"/>
-      <c r="S58" s="6" t="s">
+      <c r="S58" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="15"/>
-    <row r="60" spans="1:19" ht="15"/>
+    <row r="59" spans="1:19" ht="15">
+      <c r="A59" s="6">
+        <v>75</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46264.712905092601</v>
+      </c>
+      <c r="C59" s="2">
+        <v>46264.713773148098</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H59" s="3"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="6"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="15">
+      <c r="A60" s="6">
+        <v>76</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46264.714699074102</v>
+      </c>
+      <c r="C60" s="2">
+        <v>46264.714976851901</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H60" s="3"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="3"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="3"/>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="6"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="15">
+      <c r="A61" s="6">
+        <v>77</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46264.715590277803</v>
+      </c>
+      <c r="C61" s="2">
+        <v>46264.716030092597</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H61" s="3"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q61" s="6"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="6"/>
+    </row>
+    <row r="62" spans="1:19" ht="15">
+      <c r="A62" s="6">
+        <v>78</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46264.7164583333</v>
+      </c>
+      <c r="C62" s="2">
+        <v>46264.717071759304</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H62" s="3"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="3"/>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="15">
+      <c r="A63" s="6">
+        <v>79</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46264.717766203699</v>
+      </c>
+      <c r="C63" s="2">
+        <v>46264.719548611101</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H63" s="3"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="6"/>
+      <c r="R63" s="6"/>
+      <c r="S63" s="6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="15">
+      <c r="A64" s="6">
+        <v>80</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46264.717604166697</v>
+      </c>
+      <c r="C64" s="2">
+        <v>46264.719861111102</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H64" s="3"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="15">
+      <c r="A65" s="6">
+        <v>81</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46264.720381944397</v>
+      </c>
+      <c r="C65" s="2">
+        <v>46264.720914351899</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H65" s="3"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+      <c r="Q65" s="6"/>
+      <c r="R65" s="6"/>
+      <c r="S65" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="15">
+      <c r="A66" s="6">
+        <v>82</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46264.721238425896</v>
+      </c>
+      <c r="C66" s="2">
+        <v>46264.721585648098</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H66" s="3"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="6"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="15">
+      <c r="A67" s="6">
+        <v>83</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46264.721620370401</v>
+      </c>
+      <c r="C67" s="2">
+        <v>46264.722164351901</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H67" s="3"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="6"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="15">
+      <c r="A68" s="6">
+        <v>84</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46264.7252546296</v>
+      </c>
+      <c r="C68" s="2">
+        <v>46264.725405092599</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H68" s="3"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="15"/>
+    <row r="70" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8787BAC4-1ACE-46A0-81B7-2EC89A95710F}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBB205AD-CBA5-41D5-B2CA-5ECB3FF270D0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="217">
   <si>
     <t>Id</t>
   </si>
@@ -684,9 +684,6 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0086_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260829-WA0169_Enrique%20Cesar%20Flores.jpg</t>
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881192969132117885562748587632_Starbucks%20San%20Marcos.jpg</t>
@@ -815,8 +812,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S68" totalsRowShown="0">
-  <autoFilter ref="A1:S68" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S67" totalsRowShown="0">
+  <autoFilter ref="A1:S67" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -3559,19 +3556,19 @@
     </row>
     <row r="67" spans="1:19" ht="15">
       <c r="A67" s="6">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B67" s="2">
-        <v>46264.721620370401</v>
+        <v>46264.7252546296</v>
       </c>
       <c r="C67" s="2">
-        <v>46264.722164351901</v>
+        <v>46264.725405092599</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>212</v>
+        <v>136</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>213</v>
+        <v>137</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>138</v>
@@ -3594,43 +3591,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="15">
-      <c r="A68" s="6">
-        <v>84</v>
-      </c>
-      <c r="B68" s="2">
-        <v>46264.7252546296</v>
-      </c>
-      <c r="C68" s="2">
-        <v>46264.725405092599</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H68" s="3"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6" t="s">
-        <v>217</v>
-      </c>
-    </row>
+    <row r="68" spans="1:19" ht="15"/>
     <row r="69" spans="1:19" ht="15"/>
     <row r="70" spans="1:19" ht="15"/>
   </sheetData>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBB205AD-CBA5-41D5-B2CA-5ECB3FF270D0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{920E4ADB-2DAA-4BC1-83A2-1C334DB5B7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="229">
   <si>
     <t>Id</t>
   </si>
@@ -687,6 +687,42 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881192969132117885562748587632_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>Fotografia - SM</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG-20260830-WA0043_Starbucks%20Luna%20Park.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38401@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks CC Coalcalco</t>
+  </si>
+  <si>
+    <t>38401</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_8155_Starbucks%20CC%20Coalcal.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/db66538b-b3f2-4bef-8848-e84e5cde9117_Starbucks%20CC%20Coalcal.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38859@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Satelite II (N1)</t>
+  </si>
+  <si>
+    <t>38859</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_9938_Starbucks%20Plaza%20Sate.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/4116896b-80d4-4b02-9c85-3a241516fd23_Starbucks%20CC%20Coalcal.jpeg</t>
   </si>
 </sst>
 </file>
@@ -812,8 +848,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S67" totalsRowShown="0">
-  <autoFilter ref="A1:S67" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S72" totalsRowShown="0">
+  <autoFilter ref="A1:S72" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -952,7 +988,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="84" latestEventMarker="307">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="89" latestEventMarker="312">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1275,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S70"/>
+  <dimension ref="A1:S75"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3259,7 +3295,7 @@
       </c>
     </row>
     <row r="59" spans="1:19" ht="15">
-      <c r="A59" s="6">
+      <c r="A59">
         <v>75</v>
       </c>
       <c r="B59" s="2">
@@ -3281,7 +3317,6 @@
         <v>45</v>
       </c>
       <c r="H59" s="3"/>
-      <c r="I59" s="6"/>
       <c r="J59" s="3"/>
       <c r="K59" s="5"/>
       <c r="L59" s="3"/>
@@ -3289,14 +3324,12 @@
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
-      <c r="Q59" s="6"/>
-      <c r="R59" s="6"/>
-      <c r="S59" s="6" t="s">
+      <c r="S59" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:19" ht="15">
-      <c r="A60" s="6">
+      <c r="A60">
         <v>76</v>
       </c>
       <c r="B60" s="2">
@@ -3318,7 +3351,6 @@
         <v>45</v>
       </c>
       <c r="H60" s="3"/>
-      <c r="I60" s="6"/>
       <c r="J60" s="3"/>
       <c r="K60" s="5"/>
       <c r="L60" s="3"/>
@@ -3326,14 +3358,12 @@
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
       <c r="P60" s="3"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="6"/>
-      <c r="S60" s="6" t="s">
+      <c r="S60" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="15">
-      <c r="A61" s="6">
+      <c r="A61">
         <v>77</v>
       </c>
       <c r="B61" s="2">
@@ -3355,7 +3385,6 @@
         <v>40</v>
       </c>
       <c r="H61" s="3"/>
-      <c r="I61" s="6"/>
       <c r="J61" s="3"/>
       <c r="K61" s="5"/>
       <c r="L61" s="3"/>
@@ -3365,12 +3394,9 @@
       <c r="P61" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="Q61" s="6"/>
-      <c r="R61" s="6"/>
-      <c r="S61" s="6"/>
     </row>
     <row r="62" spans="1:19" ht="15">
-      <c r="A62" s="6">
+      <c r="A62">
         <v>78</v>
       </c>
       <c r="B62" s="2">
@@ -3392,7 +3418,6 @@
         <v>45</v>
       </c>
       <c r="H62" s="3"/>
-      <c r="I62" s="6"/>
       <c r="J62" s="3"/>
       <c r="K62" s="5"/>
       <c r="L62" s="3"/>
@@ -3400,14 +3425,12 @@
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6" t="s">
+      <c r="S62" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:19" ht="15">
-      <c r="A63" s="6">
+      <c r="A63">
         <v>79</v>
       </c>
       <c r="B63" s="2">
@@ -3429,7 +3452,6 @@
         <v>45</v>
       </c>
       <c r="H63" s="3"/>
-      <c r="I63" s="6"/>
       <c r="J63" s="3"/>
       <c r="K63" s="5"/>
       <c r="L63" s="3"/>
@@ -3437,14 +3459,12 @@
       <c r="N63" s="3"/>
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="6"/>
-      <c r="S63" s="6" t="s">
+      <c r="S63" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="15">
-      <c r="A64" s="6">
+      <c r="A64">
         <v>80</v>
       </c>
       <c r="B64" s="2">
@@ -3466,7 +3486,6 @@
         <v>45</v>
       </c>
       <c r="H64" s="3"/>
-      <c r="I64" s="6"/>
       <c r="J64" s="3"/>
       <c r="K64" s="5"/>
       <c r="L64" s="3"/>
@@ -3474,14 +3493,12 @@
       <c r="N64" s="3"/>
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6" t="s">
+      <c r="S64" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="65" spans="1:19" ht="15">
-      <c r="A65" s="6">
+      <c r="A65">
         <v>81</v>
       </c>
       <c r="B65" s="2">
@@ -3503,7 +3520,6 @@
         <v>45</v>
       </c>
       <c r="H65" s="3"/>
-      <c r="I65" s="6"/>
       <c r="J65" s="3"/>
       <c r="K65" s="5"/>
       <c r="L65" s="3"/>
@@ -3511,14 +3527,12 @@
       <c r="N65" s="3"/>
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
-      <c r="Q65" s="6"/>
-      <c r="R65" s="6"/>
-      <c r="S65" s="6" t="s">
+      <c r="S65" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="66" spans="1:19" ht="15">
-      <c r="A66" s="6">
+      <c r="A66">
         <v>82</v>
       </c>
       <c r="B66" s="2">
@@ -3540,7 +3554,6 @@
         <v>45</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="I66" s="6"/>
       <c r="J66" s="3"/>
       <c r="K66" s="5"/>
       <c r="L66" s="3"/>
@@ -3548,14 +3561,12 @@
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
-      <c r="Q66" s="6"/>
-      <c r="R66" s="6"/>
-      <c r="S66" s="6" t="s">
+      <c r="S66" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="67" spans="1:19" ht="15">
-      <c r="A67" s="6">
+      <c r="A67">
         <v>84</v>
       </c>
       <c r="B67" s="2">
@@ -3577,7 +3588,6 @@
         <v>45</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="I67" s="6"/>
       <c r="J67" s="3"/>
       <c r="K67" s="5"/>
       <c r="L67" s="3"/>
@@ -3585,15 +3595,198 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-      <c r="Q67" s="6"/>
-      <c r="R67" s="6"/>
-      <c r="S67" s="6" t="s">
+      <c r="S67" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="15"/>
-    <row r="69" spans="1:19" ht="15"/>
-    <row r="70" spans="1:19" ht="15"/>
+    <row r="68" spans="1:19" ht="15">
+      <c r="A68" s="6">
+        <v>85</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46264.7253472222</v>
+      </c>
+      <c r="C68" s="2">
+        <v>46264.729895833298</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H68" s="3"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6"/>
+    </row>
+    <row r="69" spans="1:19" ht="15">
+      <c r="A69" s="6">
+        <v>86</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46264.735532407401</v>
+      </c>
+      <c r="C69" s="2">
+        <v>46264.735752314802</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I69" s="6"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="6"/>
+      <c r="R69" s="6"/>
+      <c r="S69" s="6"/>
+    </row>
+    <row r="70" spans="1:19" ht="15">
+      <c r="A70" s="6">
+        <v>87</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46264.735833333303</v>
+      </c>
+      <c r="C70" s="2">
+        <v>46264.739432870403</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H70" s="3"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="6"/>
+      <c r="R70" s="6"/>
+      <c r="S70" s="6"/>
+    </row>
+    <row r="71" spans="1:19" ht="15">
+      <c r="A71" s="6">
+        <v>88</v>
+      </c>
+      <c r="B71" s="2">
+        <v>46264.739976851903</v>
+      </c>
+      <c r="C71" s="2">
+        <v>46264.741909722201</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H71" s="3"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q71" s="6"/>
+      <c r="R71" s="6"/>
+      <c r="S71" s="6"/>
+    </row>
+    <row r="72" spans="1:19" ht="15">
+      <c r="A72" s="6">
+        <v>89</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46264.739456018498</v>
+      </c>
+      <c r="C72" s="2">
+        <v>46264.748414351903</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H72" s="3"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="3"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+    </row>
+    <row r="73" spans="1:19" ht="15"/>
+    <row r="74" spans="1:19" ht="15"/>
+    <row r="75" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{920E4ADB-2DAA-4BC1-83A2-1C334DB5B7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33F1DFBF-94A4-4DA5-8E5B-AA730C100BC9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33F1DFBF-94A4-4DA5-8E5B-AA730C100BC9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF0FAB4D-B0BF-4953-85F7-664CCAC5B3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="235">
   <si>
     <t>Id</t>
   </si>
@@ -683,9 +683,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0093_Enrique%20Cesar%20Flores.jpg</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0086_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881192969132117885562748587632_Starbucks%20San%20Marcos.jpg</t>
   </si>
   <si>
@@ -723,6 +720,27 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/4116896b-80d4-4b02-9c85-3a241516fd23_Starbucks%20CC%20Coalcal.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_2205_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38442@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Sor Juana</t>
+  </si>
+  <si>
+    <t>38442</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/a55f0344-4a43-47d6-acaf-8581f47d223e_Starbucks%20Sor%20Juana.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG-20260830-WA0107_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG_7701_Starbucks%20Mega%20Izcal.jpeg</t>
   </si>
 </sst>
 </file>
@@ -767,14 +785,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -848,8 +865,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S72" totalsRowShown="0">
-  <autoFilter ref="A1:S72" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S75" totalsRowShown="0">
+  <autoFilter ref="A1:S75" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -988,7 +1005,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="89" latestEventMarker="312">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="93" latestEventMarker="316">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1311,7 +1328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S75"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3533,22 +3550,22 @@
     </row>
     <row r="66" spans="1:19" ht="15">
       <c r="A66">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B66" s="2">
-        <v>46264.721238425896</v>
+        <v>46264.7252546296</v>
       </c>
       <c r="C66" s="2">
-        <v>46264.721585648098</v>
+        <v>46264.725405092599</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>212</v>
+        <v>136</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>213</v>
+        <v>137</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>45</v>
@@ -3567,226 +3584,310 @@
     </row>
     <row r="67" spans="1:19" ht="15">
       <c r="A67">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B67" s="2">
-        <v>46264.7252546296</v>
+        <v>46264.7253472222</v>
       </c>
       <c r="C67" s="2">
-        <v>46264.725405092599</v>
+        <v>46264.729895833298</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>137</v>
+        <v>63</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>45</v>
+        <v>216</v>
       </c>
       <c r="H67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="5"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
+      <c r="N67" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-      <c r="S67" t="s">
-        <v>216</v>
-      </c>
     </row>
     <row r="68" spans="1:19" ht="15">
-      <c r="A68" s="6">
-        <v>85</v>
+      <c r="A68">
+        <v>86</v>
       </c>
       <c r="B68" s="2">
-        <v>46264.7253472222</v>
+        <v>46264.735532407401</v>
       </c>
       <c r="C68" s="2">
-        <v>46264.729895833298</v>
+        <v>46264.735752314802</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>62</v>
+        <v>218</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>64</v>
+        <v>220</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="H68" s="3"/>
-      <c r="I68" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="J68" s="3"/>
       <c r="K68" s="5"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
-      <c r="N68" s="3" t="s">
-        <v>218</v>
-      </c>
+      <c r="N68" s="3"/>
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
     </row>
     <row r="69" spans="1:19" ht="15">
-      <c r="A69" s="6">
-        <v>86</v>
+      <c r="A69">
+        <v>87</v>
       </c>
       <c r="B69" s="2">
-        <v>46264.735532407401</v>
+        <v>46264.735833333303</v>
       </c>
       <c r="C69" s="2">
-        <v>46264.735752314802</v>
+        <v>46264.739432870403</v>
       </c>
       <c r="D69" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="F69" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>221</v>
-      </c>
       <c r="G69" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="I69" s="6"/>
+        <v>81</v>
+      </c>
+      <c r="H69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="5"/>
       <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
+      <c r="M69" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
-      <c r="Q69" s="6"/>
-      <c r="R69" s="6"/>
-      <c r="S69" s="6"/>
     </row>
     <row r="70" spans="1:19" ht="15">
-      <c r="A70" s="6">
-        <v>87</v>
+      <c r="A70">
+        <v>88</v>
       </c>
       <c r="B70" s="2">
-        <v>46264.735833333303</v>
+        <v>46264.739976851903</v>
       </c>
       <c r="C70" s="2">
-        <v>46264.739432870403</v>
+        <v>46264.741909722201</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="H70" s="3"/>
-      <c r="I70" s="6"/>
       <c r="J70" s="3"/>
       <c r="K70" s="5"/>
       <c r="L70" s="3"/>
-      <c r="M70" s="3" t="s">
-        <v>223</v>
-      </c>
+      <c r="M70" s="3"/>
       <c r="N70" s="3"/>
       <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="6"/>
-      <c r="S70" s="6"/>
+      <c r="P70" s="3" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="71" spans="1:19" ht="15">
-      <c r="A71" s="6">
-        <v>88</v>
+      <c r="A71">
+        <v>89</v>
       </c>
       <c r="B71" s="2">
-        <v>46264.739976851903</v>
+        <v>46264.739456018498</v>
       </c>
       <c r="C71" s="2">
-        <v>46264.741909722201</v>
+        <v>46264.748414351903</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="H71" s="3"/>
-      <c r="I71" s="6"/>
       <c r="J71" s="3"/>
       <c r="K71" s="5"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
+      <c r="N71" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="O71" s="3"/>
-      <c r="P71" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="6"/>
-      <c r="S71" s="6"/>
+      <c r="P71" s="3"/>
     </row>
     <row r="72" spans="1:19" ht="15">
-      <c r="A72" s="6">
-        <v>89</v>
+      <c r="A72">
+        <v>90</v>
       </c>
       <c r="B72" s="2">
-        <v>46264.739456018498</v>
+        <v>46264.749710648102</v>
       </c>
       <c r="C72" s="2">
-        <v>46264.748414351903</v>
+        <v>46264.750347222202</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>219</v>
+        <v>19</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>217</v>
+        <v>45</v>
       </c>
       <c r="H72" s="3"/>
-      <c r="I72" s="6"/>
       <c r="J72" s="3"/>
       <c r="K72" s="5"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
-      <c r="N72" s="3" t="s">
-        <v>228</v>
-      </c>
+      <c r="N72" s="3"/>
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-    </row>
-    <row r="73" spans="1:19" ht="15"/>
-    <row r="74" spans="1:19" ht="15"/>
-    <row r="75" spans="1:19" ht="15"/>
+      <c r="S72" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="15">
+      <c r="A73">
+        <v>91</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46264.754189814797</v>
+      </c>
+      <c r="C73" s="2">
+        <v>46264.755752314799</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+      <c r="S73" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="15">
+      <c r="A74">
+        <v>92</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46264.759201388901</v>
+      </c>
+      <c r="C74" s="2">
+        <v>46264.759594907402</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H74" s="3"/>
+      <c r="I74" t="s">
+        <v>60</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K74" s="5"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="1:19" ht="15">
+      <c r="A75">
+        <v>93</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46264.750381944403</v>
+      </c>
+      <c r="C75" s="2">
+        <v>46264.760208333297</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="1:19" ht="15"/>
+    <row r="77" spans="1:19" ht="15"/>
+    <row r="78" spans="1:19" ht="15"/>
+    <row r="79" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF0FAB4D-B0BF-4953-85F7-664CCAC5B3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1D5B2D7-A47F-4AC4-A742-626906C00598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="240">
   <si>
     <t>Id</t>
   </si>
@@ -741,6 +741,21 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG_7701_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/f89cc0e6-4b88-4f8f-8e54-10d7c64c2a63_Starbucks%20CC%20Coalcal.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38515@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Patio Ecatepec</t>
+  </si>
+  <si>
+    <t>38515</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/20260828_224711_Starbucks%20Patio%20Ecat.jpg</t>
   </si>
 </sst>
 </file>
@@ -785,13 +800,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -865,8 +881,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S75" totalsRowShown="0">
-  <autoFilter ref="A1:S75" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S77" totalsRowShown="0">
+  <autoFilter ref="A1:S77" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -1005,7 +1021,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="93" latestEventMarker="316">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="95" latestEventMarker="318">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1328,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:S81"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3884,10 +3900,84 @@
       </c>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="1:19" ht="15"/>
-    <row r="77" spans="1:19" ht="15"/>
+    <row r="76" spans="1:19" ht="15">
+      <c r="A76" s="6">
+        <v>94</v>
+      </c>
+      <c r="B76" s="2">
+        <v>46264.766643518502</v>
+      </c>
+      <c r="C76" s="2">
+        <v>46264.767731481501</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H76" s="3"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+    </row>
+    <row r="77" spans="1:19" ht="15">
+      <c r="A77" s="6">
+        <v>95</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46264.767962963</v>
+      </c>
+      <c r="C77" s="2">
+        <v>46264.768379629597</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="I77" s="6"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="6"/>
+      <c r="R77" s="6"/>
+      <c r="S77" s="6"/>
+    </row>
     <row r="78" spans="1:19" ht="15"/>
     <row r="79" spans="1:19" ht="15"/>
+    <row r="80" spans="1:19" ht="15"/>
+    <row r="81" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1D5B2D7-A47F-4AC4-A742-626906C00598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40401416-1FEF-4EA1-B637-AFE132EB2CBD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="251">
   <si>
     <t>Id</t>
   </si>
@@ -756,6 +756,39 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/20260828_224711_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>maria.cardenas@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Maria Veronica Cardenas Pedraza</t>
+  </si>
+  <si>
+    <t>38270</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881378328556814544357533682971_Maria%20Veronica%20Carde.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta%202/36484835-F9BF-4A74-968E-2556B7B33E50_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38845@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Mundo E II</t>
+  </si>
+  <si>
+    <t>38845</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0058_Starbucks%20Mundo%20E%20II.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta%202/EE797329-A411-4DF9-883D-D7743D2BB0B3_Starbucks%20CC%20Coalcal.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0116_Enrique%20Cesar%20Flores.jpg</t>
   </si>
 </sst>
 </file>
@@ -881,8 +914,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S77" totalsRowShown="0">
-  <autoFilter ref="A1:S77" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S82" totalsRowShown="0">
+  <autoFilter ref="A1:S82" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -1021,7 +1054,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="95" latestEventMarker="318">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="100" latestEventMarker="323">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1344,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S81"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3901,7 +3934,7 @@
       <c r="P75" s="3"/>
     </row>
     <row r="76" spans="1:19" ht="15">
-      <c r="A76" s="6">
+      <c r="A76">
         <v>94</v>
       </c>
       <c r="B76" s="2">
@@ -3923,7 +3956,6 @@
         <v>37</v>
       </c>
       <c r="H76" s="3"/>
-      <c r="I76" s="6"/>
       <c r="J76" s="3"/>
       <c r="K76" s="5" t="s">
         <v>235</v>
@@ -3933,12 +3965,9 @@
       <c r="N76" s="3"/>
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="6"/>
-      <c r="S76" s="6"/>
     </row>
     <row r="77" spans="1:19" ht="15">
-      <c r="A77" s="6">
+      <c r="A77">
         <v>95</v>
       </c>
       <c r="B77" s="2">
@@ -3962,7 +3991,6 @@
       <c r="H77" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="I77" s="6"/>
       <c r="J77" s="3"/>
       <c r="K77" s="5"/>
       <c r="L77" s="3"/>
@@ -3970,14 +3998,182 @@
       <c r="N77" s="3"/>
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
-      <c r="Q77" s="6"/>
-      <c r="R77" s="6"/>
-      <c r="S77" s="6"/>
-    </row>
-    <row r="78" spans="1:19" ht="15"/>
-    <row r="79" spans="1:19" ht="15"/>
-    <row r="80" spans="1:19" ht="15"/>
-    <row r="81" ht="15"/>
+    </row>
+    <row r="78" spans="1:19" ht="15">
+      <c r="A78">
+        <v>96</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46264.789224537002</v>
+      </c>
+      <c r="C78" s="2">
+        <v>46264.790752314802</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+      <c r="S78" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="15">
+      <c r="A79">
+        <v>97</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46264.792453703703</v>
+      </c>
+      <c r="C79" s="2">
+        <v>46264.792766203696</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+    </row>
+    <row r="80" spans="1:19" ht="15">
+      <c r="A80">
+        <v>98</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46264.8121875</v>
+      </c>
+      <c r="C80" s="2">
+        <v>46264.827511574098</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+      <c r="S80" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="15">
+      <c r="A81">
+        <v>99</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46264.828611111101</v>
+      </c>
+      <c r="C81" s="2">
+        <v>46264.828715277799</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="1:19" ht="15">
+      <c r="A82" s="6">
+        <v>100</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46264.831979166702</v>
+      </c>
+      <c r="C82" s="2">
+        <v>46264.832534722198</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H82" s="3"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="6"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="15"/>
+    <row r="84" spans="1:19" ht="15"/>
+    <row r="85" spans="1:19" ht="15"/>
+    <row r="86" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40401416-1FEF-4EA1-B637-AFE132EB2CBD}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24C23181-A7EA-4562-AAEB-DABD179189F8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="266">
   <si>
     <t>Id</t>
   </si>
@@ -789,6 +789,51 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0116_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/original%202026-08-27%202232117D1C7967E522_Starbucks%20Galerias%20P.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG_4957_Starbucks%20Galerias%20P%201.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_4923_Starbucks%20Galerias%20P.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881426119646851605493931736582_Starbucks%20Cosmopol%20N.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17881438028408495805671975867611_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38674@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Mundo E</t>
+  </si>
+  <si>
+    <t>38674</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881437686817183439079620359993_Starbucks%20Mundo%20E.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG-20260830-WA0044_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0043_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38136@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Punta Norte</t>
+  </si>
+  <si>
+    <t>38136</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/f53f7538-8f6a-480d-887a-f705a4989323_Starbucks%20Punta%20Nort.jpeg</t>
   </si>
 </sst>
 </file>
@@ -914,8 +959,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S82" totalsRowShown="0">
-  <autoFilter ref="A1:S82" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S91" totalsRowShown="0">
+  <autoFilter ref="A1:S91" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -1054,7 +1099,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="100" latestEventMarker="323">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="109" latestEventMarker="332">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1377,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S86"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -4000,7 +4045,7 @@
       <c r="P77" s="3"/>
     </row>
     <row r="78" spans="1:19" ht="15">
-      <c r="A78">
+      <c r="A78" s="6">
         <v>96</v>
       </c>
       <c r="B78" s="2">
@@ -4022,6 +4067,7 @@
         <v>45</v>
       </c>
       <c r="H78" s="3"/>
+      <c r="I78" s="6"/>
       <c r="J78" s="3"/>
       <c r="K78" s="5"/>
       <c r="L78" s="3"/>
@@ -4029,12 +4075,14 @@
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
-      <c r="S78" t="s">
+      <c r="Q78" s="6"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="15">
-      <c r="A79">
+      <c r="A79" s="6">
         <v>97</v>
       </c>
       <c r="B79" s="2">
@@ -4056,6 +4104,7 @@
         <v>96</v>
       </c>
       <c r="H79" s="3"/>
+      <c r="I79" s="6"/>
       <c r="J79" s="3"/>
       <c r="K79" s="5"/>
       <c r="L79" s="3" t="s">
@@ -4065,9 +4114,12 @@
       <c r="N79" s="3"/>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
+      <c r="Q79" s="6"/>
+      <c r="R79" s="6"/>
+      <c r="S79" s="6"/>
     </row>
     <row r="80" spans="1:19" ht="15">
-      <c r="A80">
+      <c r="A80" s="6">
         <v>98</v>
       </c>
       <c r="B80" s="2">
@@ -4089,6 +4141,7 @@
         <v>45</v>
       </c>
       <c r="H80" s="3"/>
+      <c r="I80" s="6"/>
       <c r="J80" s="3"/>
       <c r="K80" s="5"/>
       <c r="L80" s="3"/>
@@ -4096,12 +4149,14 @@
       <c r="N80" s="3"/>
       <c r="O80" s="3"/>
       <c r="P80" s="3"/>
-      <c r="S80" t="s">
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="15">
-      <c r="A81">
+      <c r="A81" s="6">
         <v>99</v>
       </c>
       <c r="B81" s="2">
@@ -4123,6 +4178,7 @@
         <v>96</v>
       </c>
       <c r="H81" s="3"/>
+      <c r="I81" s="6"/>
       <c r="J81" s="3"/>
       <c r="K81" s="5"/>
       <c r="L81" s="3" t="s">
@@ -4132,6 +4188,9 @@
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
+      <c r="Q81" s="6"/>
+      <c r="R81" s="6"/>
+      <c r="S81" s="6"/>
     </row>
     <row r="82" spans="1:19" ht="15">
       <c r="A82" s="6">
@@ -4170,10 +4229,347 @@
         <v>250</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="15"/>
-    <row r="84" spans="1:19" ht="15"/>
-    <row r="85" spans="1:19" ht="15"/>
-    <row r="86" spans="1:19" ht="15"/>
+    <row r="83" spans="1:19" ht="15">
+      <c r="A83" s="6">
+        <v>101</v>
+      </c>
+      <c r="B83" s="2">
+        <v>46264.842476851903</v>
+      </c>
+      <c r="C83" s="2">
+        <v>46264.843240740702</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="I83" s="6"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
+      <c r="O83" s="3"/>
+      <c r="P83" s="3"/>
+      <c r="Q83" s="6"/>
+      <c r="R83" s="6"/>
+      <c r="S83" s="6"/>
+    </row>
+    <row r="84" spans="1:19" ht="15">
+      <c r="A84" s="6">
+        <v>102</v>
+      </c>
+      <c r="B84" s="2">
+        <v>46264.843287037002</v>
+      </c>
+      <c r="C84" s="2">
+        <v>46264.843715277799</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H84" s="3"/>
+      <c r="I84" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="K84" s="5"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="6"/>
+    </row>
+    <row r="85" spans="1:19" ht="15">
+      <c r="A85" s="6">
+        <v>103</v>
+      </c>
+      <c r="B85" s="2">
+        <v>46264.844143518501</v>
+      </c>
+      <c r="C85" s="2">
+        <v>46264.844490740703</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I85" s="6"/>
+      <c r="J85" s="3"/>
+      <c r="K85" s="5"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="3"/>
+      <c r="P85" s="3"/>
+      <c r="Q85" s="6"/>
+      <c r="R85" s="6"/>
+      <c r="S85" s="6"/>
+    </row>
+    <row r="86" spans="1:19" ht="15">
+      <c r="A86" s="6">
+        <v>104</v>
+      </c>
+      <c r="B86" s="2">
+        <v>46264.844687500001</v>
+      </c>
+      <c r="C86" s="2">
+        <v>46264.845312500001</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H86" s="3"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="5"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="6"/>
+      <c r="R86" s="6"/>
+      <c r="S86" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" ht="15">
+      <c r="A87" s="6">
+        <v>105</v>
+      </c>
+      <c r="B87" s="2">
+        <v>46264.857696759304</v>
+      </c>
+      <c r="C87" s="2">
+        <v>46264.859178240702</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H87" s="3"/>
+      <c r="I87" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="K87" s="5"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3"/>
+      <c r="P87" s="3"/>
+      <c r="Q87" s="6"/>
+      <c r="R87" s="6"/>
+      <c r="S87" s="6"/>
+    </row>
+    <row r="88" spans="1:19" ht="15">
+      <c r="A88" s="6">
+        <v>106</v>
+      </c>
+      <c r="B88" s="2">
+        <v>46264.707870370403</v>
+      </c>
+      <c r="C88" s="2">
+        <v>46264.859189814801</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H88" s="3"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3"/>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" ht="15">
+      <c r="A89" s="6">
+        <v>107</v>
+      </c>
+      <c r="B89" s="2">
+        <v>46264.866122685198</v>
+      </c>
+      <c r="C89" s="2">
+        <v>46264.866412037001</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H89" s="3"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="P89" s="3"/>
+      <c r="Q89" s="6"/>
+      <c r="R89" s="6"/>
+      <c r="S89" s="6"/>
+    </row>
+    <row r="90" spans="1:19" ht="15">
+      <c r="A90" s="6">
+        <v>108</v>
+      </c>
+      <c r="B90" s="2">
+        <v>46264.866493055597</v>
+      </c>
+      <c r="C90" s="2">
+        <v>46264.866817129601</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H90" s="3"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="5"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" ht="15">
+      <c r="A91" s="6">
+        <v>109</v>
+      </c>
+      <c r="B91" s="2">
+        <v>46264.866238425901</v>
+      </c>
+      <c r="C91" s="2">
+        <v>46264.867002314801</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H91" s="3"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+      <c r="O91" s="3"/>
+      <c r="P91" s="3"/>
+      <c r="Q91" s="6"/>
+      <c r="R91" s="6"/>
+      <c r="S91" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" ht="15"/>
+    <row r="93" spans="1:19" ht="15"/>
+    <row r="94" spans="1:19" ht="15"/>
+    <row r="95" spans="1:19" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24C23181-A7EA-4562-AAEB-DABD179189F8}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05961EF1-9DBD-42D6-9B77-96DB0548A646}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="267">
   <si>
     <t>Id</t>
   </si>
@@ -834,6 +834,9 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/f53f7538-8f6a-480d-887a-f705a4989323_Starbucks%20Punta%20Nort.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_0078_Starbucks%20Luna%20Park.jpeg</t>
   </si>
 </sst>
 </file>
@@ -959,8 +962,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S91" totalsRowShown="0">
-  <autoFilter ref="A1:S91" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S93" totalsRowShown="0">
+  <autoFilter ref="A1:S93" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -1099,7 +1102,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="109" latestEventMarker="332">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="111" latestEventMarker="334">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1422,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S95"/>
+  <dimension ref="A1:S97"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -4566,10 +4569,84 @@
         <v>265</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="15"/>
-    <row r="93" spans="1:19" ht="15"/>
+    <row r="92" spans="1:19" ht="15">
+      <c r="A92" s="6">
+        <v>110</v>
+      </c>
+      <c r="B92" s="2">
+        <v>46264.883055555598</v>
+      </c>
+      <c r="C92" s="2">
+        <v>46264.883680555598</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H92" s="3"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3"/>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="6"/>
+      <c r="R92" s="6"/>
+      <c r="S92" s="6"/>
+    </row>
+    <row r="93" spans="1:19" ht="15">
+      <c r="A93" s="6">
+        <v>111</v>
+      </c>
+      <c r="B93" s="2">
+        <v>46264.854363425897</v>
+      </c>
+      <c r="C93" s="2">
+        <v>46264.888043981497</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H93" s="3"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="3"/>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="3"/>
+      <c r="P93" s="3"/>
+      <c r="Q93" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="R93" s="6"/>
+      <c r="S93" s="6"/>
+    </row>
     <row r="94" spans="1:19" ht="15"/>
     <row r="95" spans="1:19" ht="15"/>
+    <row r="96" spans="1:19" ht="15"/>
+    <row r="97" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05961EF1-9DBD-42D6-9B77-96DB0548A646}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80F95044-94DF-4686-AB26-E0F83FFBB9AB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="269">
   <si>
     <t>Id</t>
   </si>
@@ -837,6 +837,12 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_0078_Starbucks%20Luna%20Park.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Luna%20Park.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0133_Enrique%20Cesar%20Flores.jpg</t>
   </si>
 </sst>
 </file>
@@ -962,8 +968,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S93" totalsRowShown="0">
-  <autoFilter ref="A1:S93" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S95" totalsRowShown="0">
+  <autoFilter ref="A1:S95" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
       <extLst>
@@ -1102,7 +1108,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="111" latestEventMarker="334">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="113" latestEventMarker="336">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1425,13 +1431,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S97"/>
+  <dimension ref="A1:S99"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.140625" customWidth="1"/>
     <col min="5" max="5" width="35.140625" customWidth="1"/>
-    <col min="6" max="8" width="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="19" customWidth="1"/>
@@ -4048,7 +4055,7 @@
       <c r="P77" s="3"/>
     </row>
     <row r="78" spans="1:19" ht="15">
-      <c r="A78" s="6">
+      <c r="A78">
         <v>96</v>
       </c>
       <c r="B78" s="2">
@@ -4070,7 +4077,6 @@
         <v>45</v>
       </c>
       <c r="H78" s="3"/>
-      <c r="I78" s="6"/>
       <c r="J78" s="3"/>
       <c r="K78" s="5"/>
       <c r="L78" s="3"/>
@@ -4078,14 +4084,12 @@
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6" t="s">
+      <c r="S78" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="15">
-      <c r="A79" s="6">
+      <c r="A79">
         <v>97</v>
       </c>
       <c r="B79" s="2">
@@ -4107,7 +4111,6 @@
         <v>96</v>
       </c>
       <c r="H79" s="3"/>
-      <c r="I79" s="6"/>
       <c r="J79" s="3"/>
       <c r="K79" s="5"/>
       <c r="L79" s="3" t="s">
@@ -4117,12 +4120,9 @@
       <c r="N79" s="3"/>
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
-      <c r="Q79" s="6"/>
-      <c r="R79" s="6"/>
-      <c r="S79" s="6"/>
     </row>
     <row r="80" spans="1:19" ht="15">
-      <c r="A80" s="6">
+      <c r="A80">
         <v>98</v>
       </c>
       <c r="B80" s="2">
@@ -4144,7 +4144,6 @@
         <v>45</v>
       </c>
       <c r="H80" s="3"/>
-      <c r="I80" s="6"/>
       <c r="J80" s="3"/>
       <c r="K80" s="5"/>
       <c r="L80" s="3"/>
@@ -4152,14 +4151,12 @@
       <c r="N80" s="3"/>
       <c r="O80" s="3"/>
       <c r="P80" s="3"/>
-      <c r="Q80" s="6"/>
-      <c r="R80" s="6"/>
-      <c r="S80" s="6" t="s">
+      <c r="S80" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="15">
-      <c r="A81" s="6">
+      <c r="A81">
         <v>99</v>
       </c>
       <c r="B81" s="2">
@@ -4181,7 +4178,6 @@
         <v>96</v>
       </c>
       <c r="H81" s="3"/>
-      <c r="I81" s="6"/>
       <c r="J81" s="3"/>
       <c r="K81" s="5"/>
       <c r="L81" s="3" t="s">
@@ -4191,12 +4187,9 @@
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
-      <c r="Q81" s="6"/>
-      <c r="R81" s="6"/>
-      <c r="S81" s="6"/>
     </row>
     <row r="82" spans="1:19" ht="15">
-      <c r="A82" s="6">
+      <c r="A82">
         <v>100</v>
       </c>
       <c r="B82" s="2">
@@ -4218,7 +4211,6 @@
         <v>45</v>
       </c>
       <c r="H82" s="3"/>
-      <c r="I82" s="6"/>
       <c r="J82" s="3"/>
       <c r="K82" s="5"/>
       <c r="L82" s="3"/>
@@ -4226,14 +4218,12 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-      <c r="Q82" s="6"/>
-      <c r="R82" s="6"/>
-      <c r="S82" s="6" t="s">
+      <c r="S82" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="83" spans="1:19" ht="15">
-      <c r="A83" s="6">
+      <c r="A83">
         <v>101</v>
       </c>
       <c r="B83" s="2">
@@ -4257,7 +4247,6 @@
       <c r="H83" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="I83" s="6"/>
       <c r="J83" s="3"/>
       <c r="K83" s="5"/>
       <c r="L83" s="3"/>
@@ -4265,12 +4254,9 @@
       <c r="N83" s="3"/>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
-      <c r="Q83" s="6"/>
-      <c r="R83" s="6"/>
-      <c r="S83" s="6"/>
     </row>
     <row r="84" spans="1:19" ht="15">
-      <c r="A84" s="6">
+      <c r="A84">
         <v>102</v>
       </c>
       <c r="B84" s="2">
@@ -4292,7 +4278,7 @@
         <v>59</v>
       </c>
       <c r="H84" s="3"/>
-      <c r="I84" s="6" t="s">
+      <c r="I84" t="s">
         <v>60</v>
       </c>
       <c r="J84" s="3" t="s">
@@ -4304,12 +4290,9 @@
       <c r="N84" s="3"/>
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
     </row>
     <row r="85" spans="1:19" ht="15">
-      <c r="A85" s="6">
+      <c r="A85">
         <v>103</v>
       </c>
       <c r="B85" s="2">
@@ -4333,7 +4316,6 @@
       <c r="H85" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="I85" s="6"/>
       <c r="J85" s="3"/>
       <c r="K85" s="5"/>
       <c r="L85" s="3"/>
@@ -4341,12 +4323,9 @@
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
-      <c r="Q85" s="6"/>
-      <c r="R85" s="6"/>
-      <c r="S85" s="6"/>
     </row>
     <row r="86" spans="1:19" ht="15">
-      <c r="A86" s="6">
+      <c r="A86">
         <v>104</v>
       </c>
       <c r="B86" s="2">
@@ -4368,7 +4347,6 @@
         <v>45</v>
       </c>
       <c r="H86" s="3"/>
-      <c r="I86" s="6"/>
       <c r="J86" s="3"/>
       <c r="K86" s="5"/>
       <c r="L86" s="3"/>
@@ -4376,14 +4354,12 @@
       <c r="N86" s="3"/>
       <c r="O86" s="3"/>
       <c r="P86" s="3"/>
-      <c r="Q86" s="6"/>
-      <c r="R86" s="6"/>
-      <c r="S86" s="6" t="s">
+      <c r="S86" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="15">
-      <c r="A87" s="6">
+      <c r="A87">
         <v>105</v>
       </c>
       <c r="B87" s="2">
@@ -4405,7 +4381,7 @@
         <v>59</v>
       </c>
       <c r="H87" s="3"/>
-      <c r="I87" s="6" t="s">
+      <c r="I87" t="s">
         <v>60</v>
       </c>
       <c r="J87" s="3" t="s">
@@ -4417,12 +4393,9 @@
       <c r="N87" s="3"/>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
-      <c r="Q87" s="6"/>
-      <c r="R87" s="6"/>
-      <c r="S87" s="6"/>
     </row>
     <row r="88" spans="1:19" ht="15">
-      <c r="A88" s="6">
+      <c r="A88">
         <v>106</v>
       </c>
       <c r="B88" s="2">
@@ -4444,7 +4417,6 @@
         <v>45</v>
       </c>
       <c r="H88" s="3"/>
-      <c r="I88" s="6"/>
       <c r="J88" s="3"/>
       <c r="K88" s="5"/>
       <c r="L88" s="3"/>
@@ -4452,14 +4424,12 @@
       <c r="N88" s="3"/>
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6" t="s">
+      <c r="S88" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="89" spans="1:19" ht="15">
-      <c r="A89" s="6">
+      <c r="A89">
         <v>107</v>
       </c>
       <c r="B89" s="2">
@@ -4481,7 +4451,6 @@
         <v>35</v>
       </c>
       <c r="H89" s="3"/>
-      <c r="I89" s="6"/>
       <c r="J89" s="3"/>
       <c r="K89" s="5"/>
       <c r="L89" s="3"/>
@@ -4491,12 +4460,9 @@
         <v>260</v>
       </c>
       <c r="P89" s="3"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="6"/>
-      <c r="S89" s="6"/>
     </row>
     <row r="90" spans="1:19" ht="15">
-      <c r="A90" s="6">
+      <c r="A90">
         <v>108</v>
       </c>
       <c r="B90" s="2">
@@ -4518,7 +4484,6 @@
         <v>45</v>
       </c>
       <c r="H90" s="3"/>
-      <c r="I90" s="6"/>
       <c r="J90" s="3"/>
       <c r="K90" s="5"/>
       <c r="L90" s="3"/>
@@ -4526,14 +4491,12 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6"/>
-      <c r="S90" s="6" t="s">
+      <c r="S90" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="91" spans="1:19" ht="15">
-      <c r="A91" s="6">
+      <c r="A91">
         <v>109</v>
       </c>
       <c r="B91" s="2">
@@ -4555,7 +4518,6 @@
         <v>45</v>
       </c>
       <c r="H91" s="3"/>
-      <c r="I91" s="6"/>
       <c r="J91" s="3"/>
       <c r="K91" s="5"/>
       <c r="L91" s="3"/>
@@ -4563,14 +4525,12 @@
       <c r="N91" s="3"/>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
-      <c r="Q91" s="6"/>
-      <c r="R91" s="6"/>
-      <c r="S91" s="6" t="s">
+      <c r="S91" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="15">
-      <c r="A92" s="6">
+      <c r="A92">
         <v>110</v>
       </c>
       <c r="B92" s="2">
@@ -4592,7 +4552,6 @@
         <v>37</v>
       </c>
       <c r="H92" s="3"/>
-      <c r="I92" s="6"/>
       <c r="J92" s="3"/>
       <c r="K92" s="5" t="s">
         <v>266</v>
@@ -4602,12 +4561,9 @@
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
-      <c r="Q92" s="6"/>
-      <c r="R92" s="6"/>
-      <c r="S92" s="6"/>
     </row>
     <row r="93" spans="1:19" ht="15">
-      <c r="A93" s="6">
+      <c r="A93">
         <v>111</v>
       </c>
       <c r="B93" s="2">
@@ -4629,7 +4585,6 @@
         <v>105</v>
       </c>
       <c r="H93" s="3"/>
-      <c r="I93" s="6"/>
       <c r="J93" s="3"/>
       <c r="K93" s="5"/>
       <c r="L93" s="3"/>
@@ -4637,16 +4592,88 @@
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
-      <c r="Q93" s="6" t="s">
+      <c r="Q93" t="s">
         <v>106</v>
       </c>
-      <c r="R93" s="6"/>
-      <c r="S93" s="6"/>
-    </row>
-    <row r="94" spans="1:19" ht="15"/>
-    <row r="95" spans="1:19" ht="15"/>
+    </row>
+    <row r="94" spans="1:19" ht="15">
+      <c r="A94" s="6">
+        <v>112</v>
+      </c>
+      <c r="B94" s="2">
+        <v>46264.892268518503</v>
+      </c>
+      <c r="C94" s="2">
+        <v>46264.893101851798</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H94" s="3"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+    </row>
+    <row r="95" spans="1:19" ht="15">
+      <c r="A95" s="6">
+        <v>113</v>
+      </c>
+      <c r="B95" s="2">
+        <v>46264.897106481498</v>
+      </c>
+      <c r="C95" s="2">
+        <v>46264.897395833301</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H95" s="3"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="6"/>
+      <c r="R95" s="6"/>
+      <c r="S95" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
     <row r="96" spans="1:19" ht="15"/>
     <row r="97" ht="15"/>
+    <row r="98" ht="15"/>
+    <row r="99" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80F95044-94DF-4686-AB26-E0F83FFBB9AB}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8CA0FA1-CDD6-4629-9AD5-5195C032049F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="278">
   <si>
     <t>Id</t>
   </si>
@@ -95,6 +95,12 @@
     <t>Evidencia_ACtivacion_PSL_Sharpie</t>
   </si>
   <si>
+    <t>Evidencia_Señaletica_Back</t>
+  </si>
+  <si>
+    <t>Evidencia_Señaletica_Lobby</t>
+  </si>
+  <si>
     <t>SBMX38333@starbucks.com.mx</t>
   </si>
   <si>
@@ -110,6 +116,33 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/FALL%2026_Starbucks%20Mega%20Izcal.jpeg</t>
   </si>
   <si>
+    <t>sbmx43194@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Atana Lindavista</t>
+  </si>
+  <si>
+    <t>43194</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/ab544637-f78d-4059-ac80-1a1426688537_Starbucks%20Atana%20Lind.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38862@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks San Miguel Izcalli</t>
+  </si>
+  <si>
+    <t>38862</t>
+  </si>
+  <si>
+    <t>Mandil Verde</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17880337596294213442656647095211_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
     <t>sbmx38894@starbucks.com.mx</t>
   </si>
   <si>
@@ -119,36 +152,6 @@
     <t>38894</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/e7d9be1f-bc24-43e4-a2c9-b07664317954_Starbucks%20Galerias%20P.jpeg</t>
-  </si>
-  <si>
-    <t>sbmx43194@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Atana Lindavista</t>
-  </si>
-  <si>
-    <t>43194</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/ab544637-f78d-4059-ac80-1a1426688537_Starbucks%20Atana%20Lind.jpeg</t>
-  </si>
-  <si>
-    <t>sbmx38862@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks San Miguel Izcalli</t>
-  </si>
-  <si>
-    <t>38862</t>
-  </si>
-  <si>
-    <t>Mandil Verde</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17880337596294213442656647095211_Starbucks%20San%20Miguel.jpg</t>
-  </si>
-  <si>
     <t>Rack FHW</t>
   </si>
   <si>
@@ -704,9 +707,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_8155_Starbucks%20CC%20Coalcal.jpeg</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/db66538b-b3f2-4bef-8848-e84e5cde9117_Starbucks%20CC%20Coalcal.jpeg</t>
-  </si>
-  <si>
     <t>sbmx38859@starbucks.com.mx</t>
   </si>
   <si>
@@ -791,9 +791,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0116_Enrique%20Cesar%20Flores.jpg</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/original%202026-08-27%202232117D1C7967E522_Starbucks%20Galerias%20P.jpeg</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG_4957_Starbucks%20Galerias%20P%201.jpeg</t>
   </si>
   <si>
@@ -843,6 +840,36 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG-20260830-WA0133_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>dennise.villasenor@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Dennise Villasenor Alonso</t>
+  </si>
+  <si>
+    <t>38176</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/WhatsApp%20Image_Dennise%20Villasenor%20A.jpg</t>
+  </si>
+  <si>
+    <t>hector.martinez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Hector Martinez Uribe</t>
+  </si>
+  <si>
+    <t>38719</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_9766_Hector%20Martinez%20Urib.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_9789_Hector%20Martinez%20Urib.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG_9791_Hector%20Martinez%20Urib.jpeg</t>
   </si>
 </sst>
 </file>
@@ -900,7 +927,13 @@
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -968,10 +1001,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:S95" totalsRowShown="0">
-  <autoFilter ref="A1:S95" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="19">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U96" totalsRowShown="0">
+  <autoFilter ref="A1:U96" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
@@ -992,115 +1025,129 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="15">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="14">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="13">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re5684d75187446048a57d8ab2351a703"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="12">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfa200a7d03cc4a5fa91df03bac2ecf7a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Evidencia_RollOut" dataDxfId="11">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Evidencia_RollOut" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1122b5cac1cb4eff8da7818c6fc7b42b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1277AD17-A3AC-49E0-841E-4D4035BFD4D3}" name="¿ Tienes Horno Merry Chef ?" dataDxfId="10">
+    <tableColumn id="16" xr3:uid="{1277AD17-A3AC-49E0-841E-4D4035BFD4D3}" name="¿ Tienes Horno Merry Chef ?" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfa62d4c051494e7682d75d2cbdf57e90"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Programacion_Hornos_Merry_Focaccia" dataDxfId="9">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Programacion_Hornos_Merry_Focaccia" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rf5169ef365594c67bd63f38ea0df71c8"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Rack_FHW" dataDxfId="8">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Rack_FHW" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r722c7f4f41104c68940ef96a05bac24d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_QR_Qualtrics" dataDxfId="7">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_QR_Qualtrics" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9b0f18f43c16454ca5151a4c7c7f429d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Max&amp;Min " dataDxfId="6">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Max&amp;Min " dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7e20bda30db04cc2a60f0888364bbb7b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Evidencia_Fotografia_SM" dataDxfId="5">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Evidencia_Fotografia_SM" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6f36155dea9a4116b90cecef4dfb40a2"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Mandil Verde" dataDxfId="4">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Mandil Verde" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9b9e86be8d8a48a79e9701b423e28c21"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Lay_Out" dataDxfId="3">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Lay_Out" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5be890f9c9be4de4ba1736dba059b880"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{73C9F7D3-3EB8-4169-BE15-327F5E69A55D}" name="¿Cuentas con Community Board?" dataDxfId="2">
+    <tableColumn id="17" xr3:uid="{73C9F7D3-3EB8-4169-BE15-327F5E69A55D}" name="¿Cuentas con Community Board?" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r142174aa4f64470ba655c0b540426c92"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{2B38EDF8-2ADC-46EB-94B2-87B30C98AE1D}" name="Evidencia_Community_Board" dataDxfId="1">
+    <tableColumn id="18" xr3:uid="{2B38EDF8-2ADC-46EB-94B2-87B30C98AE1D}" name="Evidencia_Community_Board" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r31182c58e8f644128524d5583789a1ac"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{2481D1ED-0923-463A-9844-953EC81748EE}" name="Evidencia_ACtivacion_PSL_Sharpie" dataDxfId="0">
+    <tableColumn id="19" xr3:uid="{2481D1ED-0923-463A-9844-953EC81748EE}" name="Evidencia_ACtivacion_PSL_Sharpie" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r11debcaacf20446fb636cd1accf9e03b"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="20" xr3:uid="{AEB1A9BE-A7F5-40DA-A010-79D7BC8FA3EB}" name="Evidencia_Señaletica_Back" dataDxfId="1">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="ra7c6c4f162914976b398169c5d7ab4d9"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{68268D13-0B17-41C1-99E9-AAF866047A25}" name="Evidencia_Señaletica_Lobby" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="rcc34e060c9c54a4080b7790436eec34b"/>
         </ext>
       </extLst>
     </tableColumn>
@@ -1108,7 +1155,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="113" latestEventMarker="336">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="117" latestEventMarker="350">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1128,6 +1175,8 @@
         <xlmsforms:syncedQuestionId>r142174aa4f64470ba655c0b540426c92</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r31182c58e8f644128524d5583789a1ac</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r11debcaacf20446fb636cd1accf9e03b</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>ra7c6c4f162914976b398169c5d7ab4d9</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>rcc34e060c9c54a4080b7790436eec34b</xlmsforms:syncedQuestionId>
       </xlmsforms:msForm>
     </ext>
   </extLst>
@@ -1431,7 +1480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S99"/>
+  <dimension ref="A1:U100"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -1442,10 +1491,11 @@
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="19" customWidth="1"/>
-    <col min="19" max="19" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="42.140625" customWidth="1"/>
+    <col min="20" max="21" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1503,8 +1553,14 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>13</v>
       </c>
@@ -1515,45 +1571,45 @@
         <v>46263.477986111109</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2">
-        <v>46263.507662037002</v>
+        <v>46263.560555555603</v>
       </c>
       <c r="C3" s="2">
-        <v>46263.509398148097</v>
+        <v>46263.561458333301</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -1563,159 +1619,159 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:21">
       <c r="A4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
-        <v>46263.560555555603</v>
+        <v>46263.583425925899</v>
       </c>
       <c r="C4" s="2">
-        <v>46263.561458333301</v>
+        <v>46263.585462962998</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="H4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="O4" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:21">
       <c r="A5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2">
-        <v>46263.583425925899</v>
+        <v>46263.590254629598</v>
       </c>
       <c r="C5" s="2">
-        <v>46263.585462962998</v>
+        <v>46263.590648148202</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:21">
       <c r="A6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2">
-        <v>46263.590254629598</v>
+        <v>46263.600185185198</v>
       </c>
       <c r="C6" s="2">
-        <v>46263.590648148202</v>
+        <v>46263.6006597222</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:21">
       <c r="A7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2">
-        <v>46263.600185185198</v>
+        <v>46263.601550925901</v>
       </c>
       <c r="C7" s="2">
-        <v>46263.6006597222</v>
+        <v>46263.602928240703</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>39</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="H7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="P7" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="2">
-        <v>46263.601550925901</v>
+        <v>46263.634525463</v>
       </c>
       <c r="C8" s="2">
-        <v>46263.602928240703</v>
+        <v>46263.635069444397</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H8" s="3"/>
       <c r="J8" s="3"/>
@@ -1724,31 +1780,32 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="P8" s="3"/>
+      <c r="S8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="2">
-        <v>46263.634525463</v>
+        <v>46263.639826388899</v>
       </c>
       <c r="C9" s="2">
-        <v>46263.635069444397</v>
+        <v>46263.6403125</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H9" s="3"/>
       <c r="J9" s="3"/>
@@ -1759,30 +1816,30 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="S9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2">
-        <v>46263.639826388899</v>
+        <v>46263.660752314798</v>
       </c>
       <c r="C10" s="2">
-        <v>46263.6403125</v>
+        <v>46263.661296296297</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" s="3"/>
       <c r="J10" s="3"/>
@@ -1793,32 +1850,34 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="S10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2">
-        <v>46263.660752314798</v>
+        <v>46263.660555555602</v>
       </c>
       <c r="C11" s="2">
-        <v>46263.661296296297</v>
+        <v>46263.6644675926</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1826,36 +1885,36 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="S11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2">
-        <v>46263.660555555602</v>
+        <v>46263.718784722201</v>
       </c>
       <c r="C12" s="2">
-        <v>46263.6644675926</v>
+        <v>46263.750277777799</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -1863,35 +1922,32 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:21">
       <c r="A13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2">
-        <v>46263.718784722201</v>
+        <v>46263.939942129597</v>
       </c>
       <c r="C13" s="2">
-        <v>46263.750277777799</v>
+        <v>46263.940856481502</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>61</v>
-      </c>
+      <c r="H13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -1899,31 +1955,29 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:21">
       <c r="A14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2">
-        <v>46263.939942129597</v>
+        <v>46264.456967592603</v>
       </c>
       <c r="C14" s="2">
-        <v>46263.940856481502</v>
+        <v>46264.457650463002</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>65</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="H14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1931,30 +1985,35 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="S14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2">
-        <v>46264.456967592603</v>
+        <v>46264.458229166703</v>
       </c>
       <c r="C15" s="2">
-        <v>46264.457650463002</v>
+        <v>46264.4588657407</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1962,37 +2021,34 @@
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
-      <c r="S15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="2">
-        <v>46264.458229166703</v>
+        <v>46264.459953703699</v>
       </c>
       <c r="C16" s="2">
-        <v>46264.4588657407</v>
+        <v>46264.460682870398</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>73</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="H16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -2001,58 +2057,59 @@
     </row>
     <row r="17" spans="1:19">
       <c r="A17">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2">
-        <v>46264.459953703699</v>
+        <v>46264.456678240698</v>
       </c>
       <c r="C17" s="2">
-        <v>46264.460682870398</v>
+        <v>46264.460810185199</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
+      <c r="S17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="18" spans="1:19">
       <c r="A18">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2">
-        <v>46264.456678240698</v>
+        <v>46264.460879629602</v>
       </c>
       <c r="C18" s="2">
-        <v>46264.460810185199</v>
+        <v>46264.461331018501</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H18" s="3"/>
       <c r="J18" s="3"/>
@@ -2060,165 +2117,165 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
+      <c r="O18" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="P18" s="3"/>
-      <c r="S18" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="19" spans="1:19">
       <c r="A19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2">
-        <v>46264.460879629602</v>
+        <v>46264.461099537002</v>
       </c>
       <c r="C19" s="2">
-        <v>46264.461331018501</v>
+        <v>46264.461631944403</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="3" t="s">
-        <v>79</v>
-      </c>
+      <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
     <row r="20" spans="1:19">
       <c r="A20">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2">
-        <v>46264.461099537002</v>
+        <v>46264.4614814815</v>
       </c>
       <c r="C20" s="2">
-        <v>46264.461631944403</v>
+        <v>46264.462083333303</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>80</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="H20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
+      <c r="M20" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
     <row r="21" spans="1:19">
       <c r="A21">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21" s="2">
-        <v>46264.4614814815</v>
+        <v>46264.461689814802</v>
       </c>
       <c r="C21" s="2">
-        <v>46264.462083333303</v>
+        <v>46264.463194444397</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="H21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="L21" s="3"/>
-      <c r="M21" s="3" t="s">
-        <v>82</v>
-      </c>
+      <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
     <row r="22" spans="1:19">
       <c r="A22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2">
-        <v>46264.461689814802</v>
+        <v>46264.464918981503</v>
       </c>
       <c r="C22" s="2">
-        <v>46264.463194444397</v>
+        <v>46264.465567129599</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
+      <c r="S22" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="23" spans="1:19">
       <c r="A23">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2">
-        <v>46264.464918981503</v>
+        <v>46264.462222222202</v>
       </c>
       <c r="C23" s="2">
-        <v>46264.465567129599</v>
+        <v>46264.466273148202</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H23" s="3"/>
       <c r="J23" s="3"/>
@@ -2229,30 +2286,30 @@
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="S23" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:19">
       <c r="A24">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2">
-        <v>46264.462222222202</v>
+        <v>46264.467141203699</v>
       </c>
       <c r="C24" s="2">
-        <v>46264.466273148202</v>
+        <v>46264.468124999999</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H24" s="3"/>
       <c r="J24" s="3"/>
@@ -2263,30 +2320,30 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
       <c r="S24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:19">
       <c r="A25">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="2">
-        <v>46264.467141203699</v>
+        <v>46264.4682523148</v>
       </c>
       <c r="C25" s="2">
-        <v>46264.468124999999</v>
+        <v>46264.468564814801</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H25" s="3"/>
       <c r="J25" s="3"/>
@@ -2297,97 +2354,97 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="S25" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:19">
       <c r="A26">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="2">
-        <v>46264.4682523148</v>
+        <v>46264.463252314803</v>
       </c>
       <c r="C26" s="2">
-        <v>46264.468564814801</v>
+        <v>46264.468680555598</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="H26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+      <c r="L26" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
-      <c r="S26" t="s">
-        <v>95</v>
-      </c>
     </row>
     <row r="27" spans="1:19">
       <c r="A27">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2">
-        <v>46264.463252314803</v>
+        <v>46264.466886574097</v>
       </c>
       <c r="C27" s="2">
-        <v>46264.468680555598</v>
+        <v>46264.4688425926</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="H27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
-      <c r="L27" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
+      <c r="S27" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="28" spans="1:19">
       <c r="A28">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2">
-        <v>46264.466886574097</v>
+        <v>46264.483124999999</v>
       </c>
       <c r="C28" s="2">
-        <v>46264.4688425926</v>
+        <v>46264.483715277798</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="H28" s="3"/>
       <c r="J28" s="3"/>
@@ -2397,31 +2454,31 @@
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
-      <c r="S28" t="s">
-        <v>101</v>
+      <c r="Q28" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:19">
       <c r="A29">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29" s="2">
-        <v>46264.483124999999</v>
+        <v>46264.489918981497</v>
       </c>
       <c r="C29" s="2">
-        <v>46264.483715277798</v>
+        <v>46264.490428240701</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="H29" s="3"/>
       <c r="J29" s="3"/>
@@ -2431,31 +2488,31 @@
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
-      <c r="Q29" t="s">
-        <v>106</v>
+      <c r="S29" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:19">
       <c r="A30">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B30" s="2">
-        <v>46264.489918981497</v>
+        <v>46264.503553240698</v>
       </c>
       <c r="C30" s="2">
-        <v>46264.490428240701</v>
+        <v>46264.504108796304</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H30" s="3"/>
       <c r="J30" s="3"/>
@@ -2466,30 +2523,30 @@
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="S30" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:19">
       <c r="A31">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B31" s="2">
-        <v>46264.503553240698</v>
+        <v>46264.501273148097</v>
       </c>
       <c r="C31" s="2">
-        <v>46264.504108796304</v>
+        <v>46264.5157175926</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H31" s="3"/>
       <c r="J31" s="3"/>
@@ -2500,30 +2557,30 @@
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="S31" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:19">
       <c r="A32">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B32" s="2">
-        <v>46264.501273148097</v>
+        <v>46264.524537037003</v>
       </c>
       <c r="C32" s="2">
-        <v>46264.5157175926</v>
+        <v>46264.525266203702</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H32" s="3"/>
       <c r="J32" s="3"/>
@@ -2534,30 +2591,30 @@
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="S32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:19">
       <c r="A33">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B33" s="2">
-        <v>46264.524537037003</v>
+        <v>46264.526053240697</v>
       </c>
       <c r="C33" s="2">
-        <v>46264.525266203702</v>
+        <v>46264.526550925897</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H33" s="3"/>
       <c r="J33" s="3"/>
@@ -2566,32 +2623,31 @@
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="S33" t="s">
-        <v>119</v>
+      <c r="P33" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:19">
       <c r="A34">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B34" s="2">
-        <v>46264.526053240697</v>
+        <v>46264.527280092603</v>
       </c>
       <c r="C34" s="2">
-        <v>46264.526550925897</v>
+        <v>46264.5301273148</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H34" s="3"/>
       <c r="J34" s="3"/>
@@ -2600,31 +2656,32 @@
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
-      <c r="P34" s="3" t="s">
-        <v>123</v>
+      <c r="P34" s="3"/>
+      <c r="S34" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:19">
       <c r="A35">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B35" s="2">
-        <v>46264.527280092603</v>
+        <v>46264.548101851797</v>
       </c>
       <c r="C35" s="2">
-        <v>46264.5301273148</v>
+        <v>46264.548877314803</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H35" s="3"/>
       <c r="J35" s="3"/>
@@ -2635,30 +2692,30 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
       <c r="S35" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:19">
       <c r="A36">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B36" s="2">
-        <v>46264.548101851797</v>
+        <v>46264.545902777798</v>
       </c>
       <c r="C36" s="2">
-        <v>46264.548877314803</v>
+        <v>46264.549687500003</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H36" s="3"/>
       <c r="J36" s="3"/>
@@ -2669,32 +2726,34 @@
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
       <c r="S36" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="15">
       <c r="A37">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B37" s="2">
-        <v>46264.545902777798</v>
+        <v>46264.554525462998</v>
       </c>
       <c r="C37" s="2">
-        <v>46264.549687500003</v>
+        <v>46264.555729166699</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>140</v>
+      </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
@@ -2702,37 +2761,34 @@
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
-      <c r="S37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" ht="15">
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B38" s="2">
-        <v>46264.554525462998</v>
+        <v>46264.5613310185</v>
       </c>
       <c r="C38" s="2">
-        <v>46264.555729166699</v>
+        <v>46264.562534722201</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>139</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="H38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
+      <c r="K38" s="3" t="s">
+        <v>141</v>
+      </c>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
@@ -2741,58 +2797,58 @@
     </row>
     <row r="39" spans="1:19">
       <c r="A39">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B39" s="2">
-        <v>46264.5613310185</v>
+        <v>46264.573425925897</v>
       </c>
       <c r="C39" s="2">
-        <v>46264.562534722201</v>
+        <v>46264.574652777803</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3" t="s">
-        <v>140</v>
-      </c>
+      <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
+      <c r="O39" s="3" t="s">
+        <v>142</v>
+      </c>
       <c r="P39" s="3"/>
     </row>
     <row r="40" spans="1:19">
       <c r="A40">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B40" s="2">
-        <v>46264.573425925897</v>
+        <v>46264.606041666702</v>
       </c>
       <c r="C40" s="2">
-        <v>46264.574652777803</v>
+        <v>46264.606446759302</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H40" s="3"/>
       <c r="J40" s="3"/>
@@ -2800,32 +2856,33 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-      <c r="O40" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="1:19">
+      <c r="S40" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="15">
       <c r="A41">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B41" s="2">
-        <v>46264.606041666702</v>
+        <v>46264.623680555596</v>
       </c>
       <c r="C41" s="2">
-        <v>46264.606446759302</v>
+        <v>46264.624201388899</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H41" s="3"/>
       <c r="J41" s="3"/>
@@ -2836,30 +2893,30 @@
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
       <c r="S41" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="15">
       <c r="A42">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B42" s="2">
-        <v>46264.623680555596</v>
+        <v>46264.655775462998</v>
       </c>
       <c r="C42" s="2">
-        <v>46264.624201388899</v>
+        <v>46264.662546296298</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>146</v>
+        <v>63</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H42" s="3"/>
       <c r="J42" s="3"/>
@@ -2870,30 +2927,30 @@
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
       <c r="S42" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15">
       <c r="A43">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B43" s="2">
-        <v>46264.655775462998</v>
+        <v>46264.675925925898</v>
       </c>
       <c r="C43" s="2">
-        <v>46264.662546296298</v>
+        <v>46264.676365740699</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H43" s="3"/>
       <c r="J43" s="3"/>
@@ -2904,30 +2961,30 @@
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
       <c r="S43" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="15">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19">
       <c r="A44">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B44" s="2">
-        <v>46264.675925925898</v>
+        <v>46264.6768981481</v>
       </c>
       <c r="C44" s="2">
-        <v>46264.676365740699</v>
+        <v>46264.677418981497</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>151</v>
+        <v>89</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H44" s="3"/>
       <c r="J44" s="3"/>
@@ -2938,30 +2995,30 @@
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
       <c r="S44" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:19">
       <c r="A45">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B45" s="2">
-        <v>46264.6768981481</v>
+        <v>46264.677881944401</v>
       </c>
       <c r="C45" s="2">
-        <v>46264.677418981497</v>
+        <v>46264.678506944401</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H45" s="3"/>
       <c r="J45" s="3"/>
@@ -2972,30 +3029,30 @@
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
       <c r="S45" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:19">
       <c r="A46">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B46" s="2">
-        <v>46264.677881944401</v>
+        <v>46264.679108796299</v>
       </c>
       <c r="C46" s="2">
-        <v>46264.678506944401</v>
+        <v>46264.679386574098</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H46" s="3"/>
       <c r="J46" s="3"/>
@@ -3006,30 +3063,30 @@
       <c r="O46" s="3"/>
       <c r="P46" s="3"/>
       <c r="S46" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:19">
       <c r="A47">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B47" s="2">
-        <v>46264.679108796299</v>
+        <v>46264.679988425902</v>
       </c>
       <c r="C47" s="2">
-        <v>46264.679386574098</v>
+        <v>46264.680462962999</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H47" s="3"/>
       <c r="J47" s="3"/>
@@ -3040,30 +3097,30 @@
       <c r="O47" s="3"/>
       <c r="P47" s="3"/>
       <c r="S47" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:19">
       <c r="A48">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B48" s="2">
-        <v>46264.679988425902</v>
+        <v>46264.680925925903</v>
       </c>
       <c r="C48" s="2">
-        <v>46264.680462962999</v>
+        <v>46264.681180555599</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H48" s="3"/>
       <c r="J48" s="3"/>
@@ -3074,30 +3131,30 @@
       <c r="O48" s="3"/>
       <c r="P48" s="3"/>
       <c r="S48" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="15">
       <c r="A49">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B49" s="2">
-        <v>46264.680925925903</v>
+        <v>46264.681273148097</v>
       </c>
       <c r="C49" s="2">
-        <v>46264.681180555599</v>
+        <v>46264.681481481501</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H49" s="3"/>
       <c r="J49" s="3"/>
@@ -3108,70 +3165,69 @@
       <c r="O49" s="3"/>
       <c r="P49" s="3"/>
       <c r="S49" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="15">
       <c r="A50">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B50" s="2">
-        <v>46264.681273148097</v>
+        <v>46264.6847569444</v>
       </c>
       <c r="C50" s="2">
-        <v>46264.681481481501</v>
+        <v>46264.685092592597</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H50" s="3"/>
       <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
+      <c r="K50" s="5" t="s">
+        <v>168</v>
+      </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
-      <c r="S50" t="s">
-        <v>166</v>
-      </c>
     </row>
     <row r="51" spans="1:19" ht="15">
       <c r="A51">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B51" s="2">
-        <v>46264.6847569444</v>
+        <v>46264.691377314797</v>
       </c>
       <c r="C51" s="2">
-        <v>46264.685092592597</v>
+        <v>46264.691782407397</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H51" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="J51" s="3"/>
-      <c r="K51" s="5" t="s">
-        <v>167</v>
-      </c>
+      <c r="K51" s="5"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
@@ -3180,29 +3236,27 @@
     </row>
     <row r="52" spans="1:19" ht="15">
       <c r="A52">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B52" s="2">
-        <v>46264.691377314797</v>
+        <v>46264.691990740699</v>
       </c>
       <c r="C52" s="2">
-        <v>46264.691782407397</v>
+        <v>46264.692291666703</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="H52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="5"/>
       <c r="L52" s="3"/>
@@ -3210,28 +3264,31 @@
       <c r="N52" s="3"/>
       <c r="O52" s="3"/>
       <c r="P52" s="3"/>
+      <c r="S52" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="53" spans="1:19" ht="15">
       <c r="A53">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B53" s="2">
-        <v>46264.691990740699</v>
+        <v>46264.688379629602</v>
       </c>
       <c r="C53" s="2">
-        <v>46264.692291666703</v>
+        <v>46264.693749999999</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H53" s="3"/>
       <c r="J53" s="3"/>
@@ -3242,30 +3299,30 @@
       <c r="O53" s="3"/>
       <c r="P53" s="3"/>
       <c r="S53" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="15">
       <c r="A54">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B54" s="2">
-        <v>46264.688379629602</v>
+        <v>46264.692800925899</v>
       </c>
       <c r="C54" s="2">
-        <v>46264.693749999999</v>
+        <v>46264.6941898148</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H54" s="3"/>
       <c r="J54" s="3"/>
@@ -3276,30 +3333,30 @@
       <c r="O54" s="3"/>
       <c r="P54" s="3"/>
       <c r="S54" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="15">
       <c r="A55">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B55" s="2">
-        <v>46264.692800925899</v>
+        <v>46264.701539351903</v>
       </c>
       <c r="C55" s="2">
-        <v>46264.6941898148</v>
+        <v>46264.702349537001</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H55" s="3"/>
       <c r="J55" s="3"/>
@@ -3310,30 +3367,30 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="S55" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="15">
       <c r="A56">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B56" s="2">
-        <v>46264.701539351903</v>
+        <v>46264.702962962998</v>
       </c>
       <c r="C56" s="2">
-        <v>46264.702349537001</v>
+        <v>46264.703969907401</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H56" s="3"/>
       <c r="J56" s="3"/>
@@ -3344,30 +3401,30 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="S56" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="15">
       <c r="A57">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B57" s="2">
-        <v>46264.702962962998</v>
+        <v>46264.708877314799</v>
       </c>
       <c r="C57" s="2">
-        <v>46264.703969907401</v>
+        <v>46264.709583333301</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H57" s="3"/>
       <c r="J57" s="3"/>
@@ -3378,30 +3435,30 @@
       <c r="O57" s="3"/>
       <c r="P57" s="3"/>
       <c r="S57" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="15">
       <c r="A58">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B58" s="2">
-        <v>46264.708877314799</v>
+        <v>46264.712905092601</v>
       </c>
       <c r="C58" s="2">
-        <v>46264.709583333301</v>
+        <v>46264.713773148098</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H58" s="3"/>
       <c r="J58" s="3"/>
@@ -3412,30 +3469,30 @@
       <c r="O58" s="3"/>
       <c r="P58" s="3"/>
       <c r="S58" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="15">
       <c r="A59">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B59" s="2">
-        <v>46264.712905092601</v>
+        <v>46264.714699074102</v>
       </c>
       <c r="C59" s="2">
-        <v>46264.713773148098</v>
+        <v>46264.714976851901</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>193</v>
+        <v>89</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>194</v>
+        <v>90</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H59" s="3"/>
       <c r="J59" s="3"/>
@@ -3446,30 +3503,30 @@
       <c r="O59" s="3"/>
       <c r="P59" s="3"/>
       <c r="S59" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" spans="1:19" ht="15">
       <c r="A60">
+        <v>77</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46264.715590277803</v>
+      </c>
+      <c r="C60" s="2">
+        <v>46264.716030092597</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B60" s="2">
-        <v>46264.714699074102</v>
-      </c>
-      <c r="C60" s="2">
-        <v>46264.714976851901</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="E60" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H60" s="3"/>
       <c r="J60" s="3"/>
@@ -3478,32 +3535,31 @@
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
       <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
-      <c r="S60" t="s">
-        <v>198</v>
+      <c r="P60" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="15">
       <c r="A61">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B61" s="2">
-        <v>46264.715590277803</v>
+        <v>46264.7164583333</v>
       </c>
       <c r="C61" s="2">
-        <v>46264.716030092597</v>
+        <v>46264.717071759304</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>75</v>
+        <v>201</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>76</v>
+        <v>202</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H61" s="3"/>
       <c r="J61" s="3"/>
@@ -3512,31 +3568,32 @@
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
       <c r="O61" s="3"/>
-      <c r="P61" s="3" t="s">
-        <v>199</v>
+      <c r="P61" s="3"/>
+      <c r="S61" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="15">
       <c r="A62">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B62" s="2">
-        <v>46264.7164583333</v>
+        <v>46264.717766203699</v>
       </c>
       <c r="C62" s="2">
-        <v>46264.717071759304</v>
+        <v>46264.719548611101</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H62" s="3"/>
       <c r="J62" s="3"/>
@@ -3547,30 +3604,30 @@
       <c r="O62" s="3"/>
       <c r="P62" s="3"/>
       <c r="S62" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="63" spans="1:19" ht="15">
       <c r="A63">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B63" s="2">
-        <v>46264.717766203699</v>
+        <v>46264.717604166697</v>
       </c>
       <c r="C63" s="2">
-        <v>46264.719548611101</v>
+        <v>46264.719861111102</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H63" s="3"/>
       <c r="J63" s="3"/>
@@ -3581,30 +3638,30 @@
       <c r="O63" s="3"/>
       <c r="P63" s="3"/>
       <c r="S63" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="15">
       <c r="A64">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B64" s="2">
-        <v>46264.717604166697</v>
+        <v>46264.720381944397</v>
       </c>
       <c r="C64" s="2">
-        <v>46264.719861111102</v>
+        <v>46264.720914351899</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H64" s="3"/>
       <c r="J64" s="3"/>
@@ -3615,30 +3672,30 @@
       <c r="O64" s="3"/>
       <c r="P64" s="3"/>
       <c r="S64" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="65" spans="1:19" ht="15">
       <c r="A65">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B65" s="2">
-        <v>46264.720381944397</v>
+        <v>46264.7252546296</v>
       </c>
       <c r="C65" s="2">
-        <v>46264.720914351899</v>
+        <v>46264.725405092599</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H65" s="3"/>
       <c r="J65" s="3"/>
@@ -3649,163 +3706,162 @@
       <c r="O65" s="3"/>
       <c r="P65" s="3"/>
       <c r="S65" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66" spans="1:19" ht="15">
       <c r="A66">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B66" s="2">
-        <v>46264.7252546296</v>
+        <v>46264.7253472222</v>
       </c>
       <c r="C66" s="2">
-        <v>46264.725405092599</v>
+        <v>46264.729895833298</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>45</v>
+        <v>217</v>
       </c>
       <c r="H66" s="3"/>
       <c r="J66" s="3"/>
       <c r="K66" s="5"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
+      <c r="N66" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
-      <c r="S66" t="s">
-        <v>215</v>
-      </c>
     </row>
     <row r="67" spans="1:19" ht="15">
       <c r="A67">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B67" s="2">
-        <v>46264.7253472222</v>
+        <v>46264.735532407401</v>
       </c>
       <c r="C67" s="2">
-        <v>46264.729895833298</v>
+        <v>46264.735752314802</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>62</v>
+        <v>219</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>63</v>
+        <v>220</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>64</v>
+        <v>221</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H67" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="J67" s="3"/>
       <c r="K67" s="5"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-      <c r="N67" s="3" t="s">
-        <v>217</v>
-      </c>
+      <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
     <row r="68" spans="1:19" ht="15">
       <c r="A68">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B68" s="2">
-        <v>46264.735532407401</v>
+        <v>46264.739976851903</v>
       </c>
       <c r="C68" s="2">
-        <v>46264.735752314802</v>
+        <v>46264.741909722201</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>221</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="H68" s="3"/>
       <c r="J68" s="3"/>
       <c r="K68" s="5"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
+      <c r="P68" s="3" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="69" spans="1:19" ht="15">
       <c r="A69">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B69" s="2">
-        <v>46264.735833333303</v>
+        <v>46264.739456018498</v>
       </c>
       <c r="C69" s="2">
-        <v>46264.739432870403</v>
+        <v>46264.748414351903</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>81</v>
+        <v>217</v>
       </c>
       <c r="H69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="5"/>
       <c r="L69" s="3"/>
-      <c r="M69" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="N69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
     <row r="70" spans="1:19" ht="15">
       <c r="A70">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B70" s="2">
-        <v>46264.739976851903</v>
+        <v>46264.749710648102</v>
       </c>
       <c r="C70" s="2">
-        <v>46264.741909722201</v>
+        <v>46264.750347222202</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>224</v>
+        <v>22</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>225</v>
+        <v>23</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H70" s="3"/>
       <c r="J70" s="3"/>
@@ -3814,98 +3870,102 @@
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
       <c r="O70" s="3"/>
-      <c r="P70" s="3" t="s">
-        <v>226</v>
+      <c r="P70" s="3"/>
+      <c r="S70" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:19" ht="15">
       <c r="A71">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B71" s="2">
-        <v>46264.739456018498</v>
+        <v>46264.754189814797</v>
       </c>
       <c r="C71" s="2">
-        <v>46264.748414351903</v>
+        <v>46264.755752314799</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>216</v>
+        <v>46</v>
       </c>
       <c r="H71" s="3"/>
       <c r="J71" s="3"/>
       <c r="K71" s="5"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
-      <c r="N71" s="3" t="s">
-        <v>227</v>
-      </c>
+      <c r="N71" s="3"/>
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
+      <c r="S71" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="72" spans="1:19" ht="15">
       <c r="A72">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B72" s="2">
-        <v>46264.749710648102</v>
+        <v>46264.759201388901</v>
       </c>
       <c r="C72" s="2">
-        <v>46264.750347222202</v>
+        <v>46264.759594907402</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H72" s="3"/>
-      <c r="J72" s="3"/>
+      <c r="I72" t="s">
+        <v>61</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="K72" s="5"/>
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
-      <c r="S72" t="s">
-        <v>228</v>
-      </c>
     </row>
     <row r="73" spans="1:19" ht="15">
       <c r="A73">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B73" s="2">
-        <v>46264.754189814797</v>
+        <v>46264.750381944403</v>
       </c>
       <c r="C73" s="2">
-        <v>46264.755752314799</v>
+        <v>46264.760208333297</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>230</v>
+        <v>22</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>231</v>
+        <v>23</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H73" s="3"/>
       <c r="J73" s="3"/>
@@ -3913,42 +3973,38 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
+      <c r="O73" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="P73" s="3"/>
-      <c r="S73" t="s">
-        <v>232</v>
-      </c>
     </row>
     <row r="74" spans="1:19" ht="15">
       <c r="A74">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B74" s="2">
-        <v>46264.759201388901</v>
+        <v>46264.766643518502</v>
       </c>
       <c r="C74" s="2">
-        <v>46264.759594907402</v>
+        <v>46264.767731481501</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>144</v>
+        <v>221</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="H74" s="3"/>
-      <c r="I74" t="s">
-        <v>60</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="K74" s="5"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="5" t="s">
+        <v>235</v>
+      </c>
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
@@ -3957,98 +4013,99 @@
     </row>
     <row r="75" spans="1:19" ht="15">
       <c r="A75">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B75" s="2">
-        <v>46264.750381944403</v>
+        <v>46264.767962963</v>
       </c>
       <c r="C75" s="2">
-        <v>46264.760208333297</v>
+        <v>46264.768379629597</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H75" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="J75" s="3"/>
       <c r="K75" s="5"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
-      <c r="O75" s="3" t="s">
-        <v>234</v>
-      </c>
+      <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
     <row r="76" spans="1:19" ht="15">
       <c r="A76">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B76" s="2">
-        <v>46264.766643518502</v>
+        <v>46264.789224537002</v>
       </c>
       <c r="C76" s="2">
-        <v>46264.767731481501</v>
+        <v>46264.790752314802</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H76" s="3"/>
       <c r="J76" s="3"/>
-      <c r="K76" s="5" t="s">
-        <v>235</v>
-      </c>
+      <c r="K76" s="5"/>
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
       <c r="O76" s="3"/>
       <c r="P76" s="3"/>
+      <c r="S76" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="77" spans="1:19" ht="15">
       <c r="A77">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B77" s="2">
-        <v>46264.767962963</v>
+        <v>46264.792453703703</v>
       </c>
       <c r="C77" s="2">
-        <v>46264.768379629597</v>
+        <v>46264.792766203696</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>237</v>
+        <v>22</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>238</v>
+        <v>23</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>239</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="H77" s="3"/>
       <c r="J77" s="3"/>
       <c r="K77" s="5"/>
-      <c r="L77" s="3"/>
+      <c r="L77" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
       <c r="O77" s="3"/>
@@ -4056,25 +4113,25 @@
     </row>
     <row r="78" spans="1:19" ht="15">
       <c r="A78">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B78" s="2">
-        <v>46264.789224537002</v>
+        <v>46264.8121875</v>
       </c>
       <c r="C78" s="2">
-        <v>46264.790752314802</v>
+        <v>46264.827511574098</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H78" s="3"/>
       <c r="J78" s="3"/>
@@ -4085,36 +4142,36 @@
       <c r="O78" s="3"/>
       <c r="P78" s="3"/>
       <c r="S78" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="15">
       <c r="A79">
+        <v>99</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46264.828611111101</v>
+      </c>
+      <c r="C79" s="2">
+        <v>46264.828715277799</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G79" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B79" s="2">
-        <v>46264.792453703703</v>
-      </c>
-      <c r="C79" s="2">
-        <v>46264.792766203696</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="H79" s="3"/>
       <c r="J79" s="3"/>
       <c r="K79" s="5"/>
       <c r="L79" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
@@ -4123,25 +4180,25 @@
     </row>
     <row r="80" spans="1:19" ht="15">
       <c r="A80">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B80" s="2">
-        <v>46264.8121875</v>
+        <v>46264.831979166702</v>
       </c>
       <c r="C80" s="2">
-        <v>46264.827511574098</v>
+        <v>46264.832534722198</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H80" s="3"/>
       <c r="J80" s="3"/>
@@ -4152,65 +4209,70 @@
       <c r="O80" s="3"/>
       <c r="P80" s="3"/>
       <c r="S80" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" ht="15">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" ht="15">
       <c r="A81">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B81" s="2">
-        <v>46264.828611111101</v>
+        <v>46264.843287037002</v>
       </c>
       <c r="C81" s="2">
-        <v>46264.828715277799</v>
+        <v>46264.843715277799</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>218</v>
+        <v>35</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>219</v>
+        <v>36</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>220</v>
+        <v>37</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="H81" s="3"/>
-      <c r="J81" s="3"/>
+      <c r="I81" t="s">
+        <v>61</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>251</v>
+      </c>
       <c r="K81" s="5"/>
-      <c r="L81" s="3" t="s">
-        <v>249</v>
-      </c>
+      <c r="L81" s="3"/>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:19" ht="15">
+    <row r="82" spans="1:21" ht="15">
       <c r="A82">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B82" s="2">
-        <v>46264.831979166702</v>
+        <v>46264.844143518501</v>
       </c>
       <c r="C82" s="2">
-        <v>46264.832534722198</v>
+        <v>46264.844490740703</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>213</v>
+        <v>36</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>220</v>
+        <v>37</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H82" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>252</v>
+      </c>
       <c r="J82" s="3"/>
       <c r="K82" s="5"/>
       <c r="L82" s="3"/>
@@ -4218,35 +4280,30 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-      <c r="S82" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" ht="15">
+    </row>
+    <row r="83" spans="1:21" ht="15">
       <c r="A83">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B83" s="2">
-        <v>46264.842476851903</v>
+        <v>46264.844687500001</v>
       </c>
       <c r="C83" s="2">
-        <v>46264.843240740702</v>
+        <v>46264.845312500001</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>251</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="H83" s="3"/>
       <c r="J83" s="3"/>
       <c r="K83" s="5"/>
       <c r="L83" s="3"/>
@@ -4254,35 +4311,38 @@
       <c r="N83" s="3"/>
       <c r="O83" s="3"/>
       <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="1:19" ht="15">
+      <c r="S83" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="15">
       <c r="A84">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B84" s="2">
-        <v>46264.843287037002</v>
+        <v>46264.857696759304</v>
       </c>
       <c r="C84" s="2">
-        <v>46264.843715277799</v>
+        <v>46264.859178240702</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K84" s="5"/>
       <c r="L84" s="3"/>
@@ -4291,31 +4351,29 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:19" ht="15">
+    <row r="85" spans="1:21" ht="15">
       <c r="A85">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B85" s="2">
-        <v>46264.844143518501</v>
+        <v>46264.707870370403</v>
       </c>
       <c r="C85" s="2">
-        <v>46264.844490740703</v>
+        <v>46264.859189814801</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>24</v>
+        <v>255</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>25</v>
+        <v>256</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>26</v>
+        <v>257</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>253</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="H85" s="3"/>
       <c r="J85" s="3"/>
       <c r="K85" s="5"/>
       <c r="L85" s="3"/>
@@ -4323,28 +4381,31 @@
       <c r="N85" s="3"/>
       <c r="O85" s="3"/>
       <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="1:19" ht="15">
+      <c r="S85" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="15">
       <c r="A86">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B86" s="2">
-        <v>46264.844687500001</v>
+        <v>46264.866122685198</v>
       </c>
       <c r="C86" s="2">
-        <v>46264.845312500001</v>
+        <v>46264.866412037001</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>102</v>
+        <v>236</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>103</v>
+        <v>237</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>104</v>
+        <v>238</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H86" s="3"/>
       <c r="J86" s="3"/>
@@ -4352,69 +4413,66 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
-      <c r="O86" s="3"/>
+      <c r="O86" s="3" t="s">
+        <v>259</v>
+      </c>
       <c r="P86" s="3"/>
-      <c r="S86" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" ht="15">
+    </row>
+    <row r="87" spans="1:21" ht="15">
       <c r="A87">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B87" s="2">
-        <v>46264.857696759304</v>
+        <v>46264.866493055597</v>
       </c>
       <c r="C87" s="2">
-        <v>46264.859178240702</v>
+        <v>46264.866817129601</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>142</v>
+        <v>236</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>144</v>
+        <v>238</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="H87" s="3"/>
-      <c r="I87" t="s">
-        <v>60</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>255</v>
-      </c>
+      <c r="J87" s="3"/>
       <c r="K87" s="5"/>
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
       <c r="O87" s="3"/>
       <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="1:19" ht="15">
+      <c r="S87" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" ht="15">
       <c r="A88">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B88" s="2">
-        <v>46264.707870370403</v>
+        <v>46264.866238425901</v>
       </c>
       <c r="C88" s="2">
-        <v>46264.859189814801</v>
+        <v>46264.867002314801</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H88" s="3"/>
       <c r="J88" s="3"/>
@@ -4425,63 +4483,63 @@
       <c r="O88" s="3"/>
       <c r="P88" s="3"/>
       <c r="S88" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" ht="15">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" ht="15">
       <c r="A89">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B89" s="2">
-        <v>46264.866122685198</v>
+        <v>46264.883055555598</v>
       </c>
       <c r="C89" s="2">
-        <v>46264.866412037001</v>
+        <v>46264.883680555598</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>236</v>
+        <v>63</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>237</v>
+        <v>64</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>238</v>
+        <v>65</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H89" s="3"/>
       <c r="J89" s="3"/>
-      <c r="K89" s="5"/>
+      <c r="K89" s="5" t="s">
+        <v>265</v>
+      </c>
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
-      <c r="O89" s="3" t="s">
-        <v>260</v>
-      </c>
+      <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:19" ht="15">
+    <row r="90" spans="1:21" ht="15">
       <c r="A90">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B90" s="2">
-        <v>46264.866493055597</v>
+        <v>46264.854363425897</v>
       </c>
       <c r="C90" s="2">
-        <v>46264.866817129601</v>
+        <v>46264.888043981497</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>238</v>
+        <v>58</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="H90" s="3"/>
       <c r="J90" s="3"/>
@@ -4491,31 +4549,31 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-      <c r="S90" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19" ht="15">
+      <c r="Q90" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" ht="15">
       <c r="A91">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B91" s="2">
-        <v>46264.866238425901</v>
+        <v>46264.892268518503</v>
       </c>
       <c r="C91" s="2">
-        <v>46264.867002314801</v>
+        <v>46264.893101851798</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>262</v>
+        <v>63</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>264</v>
+        <v>65</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H91" s="3"/>
       <c r="J91" s="3"/>
@@ -4523,68 +4581,69 @@
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
-      <c r="O91" s="3"/>
+      <c r="O91" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="P91" s="3"/>
-      <c r="S91" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" ht="15">
+    </row>
+    <row r="92" spans="1:21" ht="15">
       <c r="A92">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B92" s="2">
-        <v>46264.883055555598</v>
+        <v>46264.897106481498</v>
       </c>
       <c r="C92" s="2">
-        <v>46264.883680555598</v>
+        <v>46264.897395833301</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>63</v>
+        <v>214</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="H92" s="3"/>
       <c r="J92" s="3"/>
-      <c r="K92" s="5" t="s">
-        <v>266</v>
-      </c>
+      <c r="K92" s="5"/>
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="1:19" ht="15">
-      <c r="A93">
-        <v>111</v>
+      <c r="S92" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" ht="15">
+      <c r="A93" s="6">
+        <v>114</v>
       </c>
       <c r="B93" s="2">
-        <v>46264.854363425897</v>
+        <v>46264.950474537</v>
       </c>
       <c r="C93" s="2">
-        <v>46264.888043981497</v>
+        <v>46264.951446759304</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>213</v>
+        <v>269</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>57</v>
+        <v>270</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="H93" s="3"/>
+      <c r="I93" s="6"/>
       <c r="J93" s="3"/>
       <c r="K93" s="5"/>
       <c r="L93" s="3"/>
@@ -4592,68 +4651,74 @@
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
-      <c r="Q93" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19" ht="15">
+      <c r="Q93" s="6"/>
+      <c r="R93" s="6"/>
+      <c r="S93" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="T93" s="6"/>
+      <c r="U93" s="6"/>
+    </row>
+    <row r="94" spans="1:21" ht="15">
       <c r="A94" s="6">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B94" s="2">
-        <v>46264.892268518503</v>
+        <v>46264.960775462998</v>
       </c>
       <c r="C94" s="2">
-        <v>46264.893101851798</v>
+        <v>46264.9614814815</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>62</v>
+        <v>272</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>63</v>
+        <v>273</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>64</v>
+        <v>274</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H94" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="I94" s="6"/>
       <c r="J94" s="3"/>
       <c r="K94" s="5"/>
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
-      <c r="O94" s="3" t="s">
-        <v>267</v>
-      </c>
+      <c r="O94" s="3"/>
       <c r="P94" s="3"/>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
       <c r="S94" s="6"/>
-    </row>
-    <row r="95" spans="1:19" ht="15">
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
+    </row>
+    <row r="95" spans="1:21" ht="15">
       <c r="A95" s="6">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B95" s="2">
-        <v>46264.897106481498</v>
+        <v>46264.961666666699</v>
       </c>
       <c r="C95" s="2">
-        <v>46264.897395833301</v>
+        <v>46264.963888888902</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>212</v>
+        <v>272</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>26</v>
+        <v>274</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>45</v>
+        <v>217</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="6"/>
@@ -4661,28 +4726,70 @@
       <c r="K95" s="5"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-      <c r="N95" s="3"/>
+      <c r="N95" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="6"/>
       <c r="R95" s="6"/>
-      <c r="S95" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" ht="15"/>
+      <c r="S95" s="6"/>
+      <c r="T95" s="6"/>
+      <c r="U95" s="6"/>
+    </row>
+    <row r="96" spans="1:21" ht="15">
+      <c r="A96" s="6">
+        <v>117</v>
+      </c>
+      <c r="B96" s="2">
+        <v>46264.964143518497</v>
+      </c>
+      <c r="C96" s="2">
+        <v>46264.965416666702</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H96" s="3"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="6"/>
+      <c r="R96" s="6"/>
+      <c r="S96" s="6"/>
+      <c r="T96" s="6"/>
+      <c r="U96" s="6"/>
+    </row>
     <row r="97" ht="15"/>
     <row r="98" ht="15"/>
     <row r="99" ht="15"/>
+    <row r="100" ht="15"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H38" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>
-    <hyperlink ref="K51" r:id="rId2" xr:uid="{C4821E21-FAA0-46D2-B8E3-D3BB8AD6B775}"/>
+    <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>
+    <hyperlink ref="K50" r:id="rId2" xr:uid="{C4821E21-FAA0-46D2-B8E3-D3BB8AD6B775}"/>
+    <hyperlink ref="H82" r:id="rId3" xr:uid="{766FA421-DC55-43DC-BB00-3D4CF619CA37}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8CA0FA1-CDD6-4629-9AD5-5195C032049F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4F09C91-BF10-4426-9876-68BF75AF0E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="281">
   <si>
     <t>Id</t>
   </si>
@@ -870,6 +870,15 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG_9791_Hector%20Martinez%20Urib.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Pregunta%202/6a52bc92-29ff-42ef-8a06-50e8b46572e9_Hector%20Martinez%20Urib.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/17881535430474872562945685645360_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/AAD33D9C-E878-44A6-8D80-D4A1367DCD9D_Hector%20Martinez%20Urib.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1001,8 +1010,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U96" totalsRowShown="0">
-  <autoFilter ref="A1:U96" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U99" totalsRowShown="0">
+  <autoFilter ref="A1:U99" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1155,7 +1164,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="117" latestEventMarker="350">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="120" latestEventMarker="353">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1480,7 +1489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U100"/>
+  <dimension ref="A1:U103"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -4776,10 +4785,127 @@
       <c r="T96" s="6"/>
       <c r="U96" s="6"/>
     </row>
-    <row r="97" ht="15"/>
-    <row r="98" ht="15"/>
-    <row r="99" ht="15"/>
-    <row r="100" ht="15"/>
+    <row r="97" spans="1:21" ht="15">
+      <c r="A97" s="6">
+        <v>118</v>
+      </c>
+      <c r="B97" s="2">
+        <v>46264.965879629599</v>
+      </c>
+      <c r="C97" s="2">
+        <v>46264.970266203702</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H97" s="3"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="3"/>
+      <c r="K97" s="5"/>
+      <c r="L97" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="3"/>
+      <c r="P97" s="3"/>
+      <c r="Q97" s="6"/>
+      <c r="R97" s="6"/>
+      <c r="S97" s="6"/>
+      <c r="T97" s="6"/>
+      <c r="U97" s="6"/>
+    </row>
+    <row r="98" spans="1:21" ht="15">
+      <c r="A98" s="6">
+        <v>119</v>
+      </c>
+      <c r="B98" s="2">
+        <v>46264.971377314803</v>
+      </c>
+      <c r="C98" s="2">
+        <v>46264.971770833297</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="I98" s="6"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="6"/>
+      <c r="R98" s="6"/>
+      <c r="S98" s="6"/>
+      <c r="T98" s="6"/>
+      <c r="U98" s="6"/>
+    </row>
+    <row r="99" spans="1:21" ht="15">
+      <c r="A99" s="6">
+        <v>120</v>
+      </c>
+      <c r="B99" s="2">
+        <v>46264.970613425903</v>
+      </c>
+      <c r="C99" s="2">
+        <v>46264.972662036998</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H99" s="3"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="6"/>
+      <c r="R99" s="6"/>
+      <c r="S99" s="6"/>
+      <c r="T99" s="6"/>
+      <c r="U99" s="6"/>
+    </row>
+    <row r="100" spans="1:21" ht="15"/>
+    <row r="101" spans="1:21" ht="15"/>
+    <row r="102" spans="1:21" ht="15"/>
+    <row r="103" spans="1:21" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4F09C91-BF10-4426-9876-68BF75AF0E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B76ABF8-3690-45E5-99DD-A1E04C1647FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B76ABF8-3690-45E5-99DD-A1E04C1647FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{965333AC-38F4-4322-BB9A-0EBB95118ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1492,7 +1492,8 @@
   <dimension ref="A1:U103"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.140625" customWidth="1"/>
     <col min="5" max="5" width="35.140625" customWidth="1"/>
     <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{965333AC-38F4-4322-BB9A-0EBB95118ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DF52423-868C-45E2-A3FB-3AB6F35F1C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DF52423-868C-45E2-A3FB-3AB6F35F1C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{001DB62E-46A4-4673-AFC9-6238E247DBF6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="290">
   <si>
     <t>Id</t>
   </si>
@@ -879,6 +879,33 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/AAD33D9C-E878-44A6-8D80-D4A1367DCD9D_Hector%20Martinez%20Urib.jpeg</t>
+  </si>
+  <si>
+    <t>dulce.guzman@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Dulce Maria Guzman Silva</t>
+  </si>
+  <si>
+    <t>38924</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881840918583520154375163778648_Dulce%20Maria%20Guzman%20S.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/20260831_075046-COLLAGE_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>Señaletica Back</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/20260831_075640-COLLAGE_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>Señaletica Lobby</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/20260831_075913-COLLAGE_Starbucks%20San%20Miguel.jpg</t>
   </si>
 </sst>
 </file>
@@ -1010,8 +1037,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U99" totalsRowShown="0">
-  <autoFilter ref="A1:U99" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U103" totalsRowShown="0">
+  <autoFilter ref="A1:U103" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1164,7 +1191,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="120" latestEventMarker="353">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="124" latestEventMarker="357">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1489,7 +1516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U103"/>
+  <dimension ref="A1:U107"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -4222,7 +4249,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="15">
+    <row r="81" spans="1:19" ht="15">
       <c r="A81">
         <v>102</v>
       </c>
@@ -4258,7 +4285,7 @@
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:21" ht="15">
+    <row r="82" spans="1:19" ht="15">
       <c r="A82">
         <v>103</v>
       </c>
@@ -4291,7 +4318,7 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="1:21" ht="15">
+    <row r="83" spans="1:19" ht="15">
       <c r="A83">
         <v>104</v>
       </c>
@@ -4325,7 +4352,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="15">
+    <row r="84" spans="1:19" ht="15">
       <c r="A84">
         <v>105</v>
       </c>
@@ -4361,7 +4388,7 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:21" ht="15">
+    <row r="85" spans="1:19" ht="15">
       <c r="A85">
         <v>106</v>
       </c>
@@ -4395,7 +4422,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="86" spans="1:21" ht="15">
+    <row r="86" spans="1:19" ht="15">
       <c r="A86">
         <v>107</v>
       </c>
@@ -4428,7 +4455,7 @@
       </c>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="1:21" ht="15">
+    <row r="87" spans="1:19" ht="15">
       <c r="A87">
         <v>108</v>
       </c>
@@ -4462,7 +4489,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:21" ht="15">
+    <row r="88" spans="1:19" ht="15">
       <c r="A88">
         <v>109</v>
       </c>
@@ -4496,7 +4523,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:21" ht="15">
+    <row r="89" spans="1:19" ht="15">
       <c r="A89">
         <v>110</v>
       </c>
@@ -4529,7 +4556,7 @@
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:21" ht="15">
+    <row r="90" spans="1:19" ht="15">
       <c r="A90">
         <v>111</v>
       </c>
@@ -4563,7 +4590,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:21" ht="15">
+    <row r="91" spans="1:19" ht="15">
       <c r="A91">
         <v>112</v>
       </c>
@@ -4596,7 +4623,7 @@
       </c>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:21" ht="15">
+    <row r="92" spans="1:19" ht="15">
       <c r="A92">
         <v>113</v>
       </c>
@@ -4630,8 +4657,8 @@
         <v>267</v>
       </c>
     </row>
-    <row r="93" spans="1:21" ht="15">
-      <c r="A93" s="6">
+    <row r="93" spans="1:19" ht="15">
+      <c r="A93">
         <v>114</v>
       </c>
       <c r="B93" s="2">
@@ -4653,7 +4680,6 @@
         <v>46</v>
       </c>
       <c r="H93" s="3"/>
-      <c r="I93" s="6"/>
       <c r="J93" s="3"/>
       <c r="K93" s="5"/>
       <c r="L93" s="3"/>
@@ -4661,16 +4687,12 @@
       <c r="N93" s="3"/>
       <c r="O93" s="3"/>
       <c r="P93" s="3"/>
-      <c r="Q93" s="6"/>
-      <c r="R93" s="6"/>
-      <c r="S93" s="6" t="s">
+      <c r="S93" t="s">
         <v>271</v>
       </c>
-      <c r="T93" s="6"/>
-      <c r="U93" s="6"/>
-    </row>
-    <row r="94" spans="1:21" ht="15">
-      <c r="A94" s="6">
+    </row>
+    <row r="94" spans="1:19" ht="15">
+      <c r="A94">
         <v>115</v>
       </c>
       <c r="B94" s="2">
@@ -4694,7 +4716,6 @@
       <c r="H94" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="I94" s="6"/>
       <c r="J94" s="3"/>
       <c r="K94" s="5"/>
       <c r="L94" s="3"/>
@@ -4702,14 +4723,9 @@
       <c r="N94" s="3"/>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
-    </row>
-    <row r="95" spans="1:21" ht="15">
-      <c r="A95" s="6">
+    </row>
+    <row r="95" spans="1:19" ht="15">
+      <c r="A95">
         <v>116</v>
       </c>
       <c r="B95" s="2">
@@ -4731,7 +4747,6 @@
         <v>217</v>
       </c>
       <c r="H95" s="3"/>
-      <c r="I95" s="6"/>
       <c r="J95" s="3"/>
       <c r="K95" s="5"/>
       <c r="L95" s="3"/>
@@ -4741,14 +4756,9 @@
       </c>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-      <c r="Q95" s="6"/>
-      <c r="R95" s="6"/>
-      <c r="S95" s="6"/>
-      <c r="T95" s="6"/>
-      <c r="U95" s="6"/>
-    </row>
-    <row r="96" spans="1:21" ht="15">
-      <c r="A96" s="6">
+    </row>
+    <row r="96" spans="1:19" ht="15">
+      <c r="A96">
         <v>117</v>
       </c>
       <c r="B96" s="2">
@@ -4770,7 +4780,6 @@
         <v>33</v>
       </c>
       <c r="H96" s="3"/>
-      <c r="I96" s="6"/>
       <c r="J96" s="3"/>
       <c r="K96" s="5"/>
       <c r="L96" s="3"/>
@@ -4780,14 +4789,9 @@
         <v>277</v>
       </c>
       <c r="P96" s="3"/>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
-      <c r="S96" s="6"/>
-      <c r="T96" s="6"/>
-      <c r="U96" s="6"/>
     </row>
     <row r="97" spans="1:21" ht="15">
-      <c r="A97" s="6">
+      <c r="A97">
         <v>118</v>
       </c>
       <c r="B97" s="2">
@@ -4809,7 +4813,6 @@
         <v>97</v>
       </c>
       <c r="H97" s="3"/>
-      <c r="I97" s="6"/>
       <c r="J97" s="3"/>
       <c r="K97" s="5"/>
       <c r="L97" s="3" t="s">
@@ -4819,14 +4822,9 @@
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
-      <c r="Q97" s="6"/>
-      <c r="R97" s="6"/>
-      <c r="S97" s="6"/>
-      <c r="T97" s="6"/>
-      <c r="U97" s="6"/>
     </row>
     <row r="98" spans="1:21" ht="15">
-      <c r="A98" s="6">
+      <c r="A98">
         <v>119</v>
       </c>
       <c r="B98" s="2">
@@ -4850,7 +4848,6 @@
       <c r="H98" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="I98" s="6"/>
       <c r="J98" s="3"/>
       <c r="K98" s="5"/>
       <c r="L98" s="3"/>
@@ -4858,14 +4855,9 @@
       <c r="N98" s="3"/>
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
-      <c r="Q98" s="6"/>
-      <c r="R98" s="6"/>
-      <c r="S98" s="6"/>
-      <c r="T98" s="6"/>
-      <c r="U98" s="6"/>
     </row>
     <row r="99" spans="1:21" ht="15">
-      <c r="A99" s="6">
+      <c r="A99">
         <v>120</v>
       </c>
       <c r="B99" s="2">
@@ -4887,7 +4879,6 @@
         <v>38</v>
       </c>
       <c r="H99" s="3"/>
-      <c r="I99" s="6"/>
       <c r="J99" s="3"/>
       <c r="K99" s="5" t="s">
         <v>280</v>
@@ -4897,16 +4888,167 @@
       <c r="N99" s="3"/>
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
-      <c r="Q99" s="6"/>
-      <c r="R99" s="6"/>
-      <c r="S99" s="6"/>
-      <c r="T99" s="6"/>
-      <c r="U99" s="6"/>
-    </row>
-    <row r="100" spans="1:21" ht="15"/>
-    <row r="101" spans="1:21" ht="15"/>
-    <row r="102" spans="1:21" ht="15"/>
-    <row r="103" spans="1:21" ht="15"/>
+    </row>
+    <row r="100" spans="1:21" ht="15">
+      <c r="A100" s="6">
+        <v>121</v>
+      </c>
+      <c r="B100" s="2">
+        <v>46265.325115740699</v>
+      </c>
+      <c r="C100" s="2">
+        <v>46265.325451388897</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H100" s="3"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="5"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="T100" s="6"/>
+      <c r="U100" s="6"/>
+    </row>
+    <row r="101" spans="1:21" ht="15">
+      <c r="A101" s="6">
+        <v>122</v>
+      </c>
+      <c r="B101" s="2">
+        <v>46265.326215277797</v>
+      </c>
+      <c r="C101" s="2">
+        <v>46265.327511574098</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H101" s="3"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="3"/>
+      <c r="K101" s="5"/>
+      <c r="L101" s="3"/>
+      <c r="M101" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+      <c r="P101" s="3"/>
+      <c r="Q101" s="6"/>
+      <c r="R101" s="6"/>
+      <c r="S101" s="6"/>
+      <c r="T101" s="6"/>
+      <c r="U101" s="6"/>
+    </row>
+    <row r="102" spans="1:21" ht="15">
+      <c r="A102" s="6">
+        <v>123</v>
+      </c>
+      <c r="B102" s="2">
+        <v>46265.328298611101</v>
+      </c>
+      <c r="C102" s="2">
+        <v>46265.3311805556</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H102" s="3"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="3"/>
+      <c r="K102" s="5"/>
+      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="6"/>
+      <c r="R102" s="6"/>
+      <c r="S102" s="6"/>
+      <c r="T102" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="U102" s="6"/>
+    </row>
+    <row r="103" spans="1:21" ht="15">
+      <c r="A103" s="6">
+        <v>124</v>
+      </c>
+      <c r="B103" s="2">
+        <v>46265.331215277802</v>
+      </c>
+      <c r="C103" s="2">
+        <v>46265.332962963003</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H103" s="3"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="5"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3"/>
+      <c r="O103" s="3"/>
+      <c r="P103" s="3"/>
+      <c r="Q103" s="6"/>
+      <c r="R103" s="6"/>
+      <c r="S103" s="6"/>
+      <c r="T103" s="6"/>
+      <c r="U103" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" ht="15"/>
+    <row r="105" spans="1:21" ht="15"/>
+    <row r="106" spans="1:21" ht="15"/>
+    <row r="107" spans="1:21" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{001DB62E-46A4-4673-AFC9-6238E247DBF6}"/>
+  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76162C23-5121-42EA-B472-8410FB201CF0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="302">
   <si>
     <t>Id</t>
   </si>
@@ -906,6 +906,42 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/20260831_075913-COLLAGE_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38930@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Boulevard Aeropuerto DT</t>
+  </si>
+  <si>
+    <t>38930</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_3375_Starbucks%20Boulevard.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17881927390126821430048920525675_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17881929453986704796599683113203_Starbucks%20Cosmopol%20N.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/bce54434-ccdb-47c1-93ad-c0513bc0aac6_Hector%20Martinez%20Urib.jpeg</t>
+  </si>
+  <si>
+    <t>daniel.bustos@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Daniel Bustos Martinez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/9c834f7d-549e-4265-b499-86e5c7553138_Daniel%20Bustos%20Martin.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/1788199873673996911419940705417_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/IMG_9805_Hector%20Martinez%20Urib.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1037,8 +1073,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U103" totalsRowShown="0">
-  <autoFilter ref="A1:U103" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U110" totalsRowShown="0">
+  <autoFilter ref="A1:U110" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1191,7 +1227,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="124" latestEventMarker="357">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="131" latestEventMarker="364">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1516,7 +1552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U107"/>
+  <dimension ref="A1:U114"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -4890,7 +4926,7 @@
       <c r="P99" s="3"/>
     </row>
     <row r="100" spans="1:21" ht="15">
-      <c r="A100" s="6">
+      <c r="A100">
         <v>121</v>
       </c>
       <c r="B100" s="2">
@@ -4912,7 +4948,6 @@
         <v>46</v>
       </c>
       <c r="H100" s="3"/>
-      <c r="I100" s="6"/>
       <c r="J100" s="3"/>
       <c r="K100" s="5"/>
       <c r="L100" s="3"/>
@@ -4920,16 +4955,12 @@
       <c r="N100" s="3"/>
       <c r="O100" s="3"/>
       <c r="P100" s="3"/>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="6"/>
-      <c r="S100" s="6" t="s">
+      <c r="S100" t="s">
         <v>284</v>
       </c>
-      <c r="T100" s="6"/>
-      <c r="U100" s="6"/>
     </row>
     <row r="101" spans="1:21" ht="15">
-      <c r="A101" s="6">
+      <c r="A101">
         <v>122</v>
       </c>
       <c r="B101" s="2">
@@ -4951,7 +4982,6 @@
         <v>82</v>
       </c>
       <c r="H101" s="3"/>
-      <c r="I101" s="6"/>
       <c r="J101" s="3"/>
       <c r="K101" s="5"/>
       <c r="L101" s="3"/>
@@ -4961,14 +4991,9 @@
       <c r="N101" s="3"/>
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
-      <c r="Q101" s="6"/>
-      <c r="R101" s="6"/>
-      <c r="S101" s="6"/>
-      <c r="T101" s="6"/>
-      <c r="U101" s="6"/>
     </row>
     <row r="102" spans="1:21" ht="15">
-      <c r="A102" s="6">
+      <c r="A102">
         <v>123</v>
       </c>
       <c r="B102" s="2">
@@ -4990,7 +5015,6 @@
         <v>286</v>
       </c>
       <c r="H102" s="3"/>
-      <c r="I102" s="6"/>
       <c r="J102" s="3"/>
       <c r="K102" s="5"/>
       <c r="L102" s="3"/>
@@ -4998,16 +5022,12 @@
       <c r="N102" s="3"/>
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="6"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6" t="s">
+      <c r="T102" t="s">
         <v>287</v>
       </c>
-      <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" ht="15">
-      <c r="A103" s="6">
+      <c r="A103">
         <v>124</v>
       </c>
       <c r="B103" s="2">
@@ -5029,7 +5049,6 @@
         <v>288</v>
       </c>
       <c r="H103" s="3"/>
-      <c r="I103" s="6"/>
       <c r="J103" s="3"/>
       <c r="K103" s="5"/>
       <c r="L103" s="3"/>
@@ -5037,18 +5056,291 @@
       <c r="N103" s="3"/>
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
-      <c r="Q103" s="6"/>
-      <c r="R103" s="6"/>
-      <c r="S103" s="6"/>
-      <c r="T103" s="6"/>
-      <c r="U103" s="6" t="s">
+      <c r="U103" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="104" spans="1:21" ht="15"/>
-    <row r="105" spans="1:21" ht="15"/>
-    <row r="106" spans="1:21" ht="15"/>
-    <row r="107" spans="1:21" ht="15"/>
+    <row r="104" spans="1:21" ht="15">
+      <c r="A104" s="6">
+        <v>125</v>
+      </c>
+      <c r="B104" s="2">
+        <v>46265.415219907401</v>
+      </c>
+      <c r="C104" s="2">
+        <v>46265.415902777801</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H104" s="3"/>
+      <c r="I104" s="6"/>
+      <c r="J104" s="3"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="3"/>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="3"/>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="6"/>
+      <c r="R104" s="6"/>
+      <c r="S104" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="T104" s="6"/>
+      <c r="U104" s="6"/>
+    </row>
+    <row r="105" spans="1:21" ht="15">
+      <c r="A105" s="6">
+        <v>126</v>
+      </c>
+      <c r="B105" s="2">
+        <v>46265.424861111103</v>
+      </c>
+      <c r="C105" s="2">
+        <v>46265.425555555601</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H105" s="3"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="3"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="3"/>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3"/>
+      <c r="O105" s="3"/>
+      <c r="P105" s="3"/>
+      <c r="Q105" s="6"/>
+      <c r="R105" s="6"/>
+      <c r="S105" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="T105" s="6"/>
+      <c r="U105" s="6"/>
+    </row>
+    <row r="106" spans="1:21" ht="15">
+      <c r="A106" s="6">
+        <v>127</v>
+      </c>
+      <c r="B106" s="2">
+        <v>46265.427245370403</v>
+      </c>
+      <c r="C106" s="2">
+        <v>46265.427881944401</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H106" s="3"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="3"/>
+      <c r="K106" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="L106" s="3"/>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3"/>
+      <c r="O106" s="3"/>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="6"/>
+      <c r="R106" s="6"/>
+      <c r="S106" s="6"/>
+      <c r="T106" s="6"/>
+      <c r="U106" s="6"/>
+    </row>
+    <row r="107" spans="1:21" ht="15">
+      <c r="A107" s="6">
+        <v>128</v>
+      </c>
+      <c r="B107" s="2">
+        <v>46265.442222222198</v>
+      </c>
+      <c r="C107" s="2">
+        <v>46265.442581018498</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H107" s="3"/>
+      <c r="I107" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="K107" s="5"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="3"/>
+      <c r="N107" s="3"/>
+      <c r="O107" s="3"/>
+      <c r="P107" s="3"/>
+      <c r="Q107" s="6"/>
+      <c r="R107" s="6"/>
+      <c r="S107" s="6"/>
+      <c r="T107" s="6"/>
+      <c r="U107" s="6"/>
+    </row>
+    <row r="108" spans="1:21" ht="15">
+      <c r="A108" s="6">
+        <v>129</v>
+      </c>
+      <c r="B108" s="2">
+        <v>46265.452187499999</v>
+      </c>
+      <c r="C108" s="2">
+        <v>46265.452557870398</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H108" s="3"/>
+      <c r="I108" s="6"/>
+      <c r="J108" s="3"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="3"/>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3"/>
+      <c r="O108" s="3"/>
+      <c r="P108" s="3"/>
+      <c r="Q108" s="6"/>
+      <c r="R108" s="6"/>
+      <c r="S108" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="T108" s="6"/>
+      <c r="U108" s="6"/>
+    </row>
+    <row r="109" spans="1:21" ht="15">
+      <c r="A109" s="6">
+        <v>130</v>
+      </c>
+      <c r="B109" s="2">
+        <v>46265.507581018501</v>
+      </c>
+      <c r="C109" s="2">
+        <v>46265.507997685199</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H109" s="3"/>
+      <c r="I109" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="K109" s="5"/>
+      <c r="L109" s="3"/>
+      <c r="M109" s="3"/>
+      <c r="N109" s="3"/>
+      <c r="O109" s="3"/>
+      <c r="P109" s="3"/>
+      <c r="Q109" s="6"/>
+      <c r="R109" s="6"/>
+      <c r="S109" s="6"/>
+      <c r="T109" s="6"/>
+      <c r="U109" s="6"/>
+    </row>
+    <row r="110" spans="1:21" ht="15">
+      <c r="A110" s="6">
+        <v>131</v>
+      </c>
+      <c r="B110" s="2">
+        <v>46265.518842592603</v>
+      </c>
+      <c r="C110" s="2">
+        <v>46265.519652777803</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H110" s="3"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="N110" s="3"/>
+      <c r="O110" s="3"/>
+      <c r="P110" s="3"/>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="6"/>
+      <c r="T110" s="6"/>
+      <c r="U110" s="6"/>
+    </row>
+    <row r="111" spans="1:21" ht="15"/>
+    <row r="112" spans="1:21" ht="15"/>
+    <row r="113" ht="15"/>
+    <row r="114" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76162C23-5121-42EA-B472-8410FB201CF0}"/>
+  <xr:revisionPtr revIDLastSave="292" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DCED3F9-CE5D-4E27-875C-959E62561C88}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="309">
   <si>
     <t>Id</t>
   </si>
@@ -942,6 +942,27 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/IMG_9805_Hector%20Martinez%20Urib.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38992@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Tapo puerta Oriente</t>
+  </si>
+  <si>
+    <t>38992</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/1788201869665846146572077266121_Starbucks%20Tapo%20puert.jpg</t>
+  </si>
+  <si>
+    <t>38371</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/3a450334-8e66-4060-88b5-874ba17e9e33_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Hector%20Martinez%20Urib.jpg</t>
   </si>
 </sst>
 </file>
@@ -1073,8 +1094,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U110" totalsRowShown="0">
-  <autoFilter ref="A1:U110" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U113" totalsRowShown="0">
+  <autoFilter ref="A1:U113" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1227,7 +1248,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="131" latestEventMarker="364">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="134" latestEventMarker="367">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1552,7 +1573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U114"/>
+  <dimension ref="A1:U117"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -5061,7 +5082,7 @@
       </c>
     </row>
     <row r="104" spans="1:21" ht="15">
-      <c r="A104" s="6">
+      <c r="A104">
         <v>125</v>
       </c>
       <c r="B104" s="2">
@@ -5083,7 +5104,6 @@
         <v>46</v>
       </c>
       <c r="H104" s="3"/>
-      <c r="I104" s="6"/>
       <c r="J104" s="3"/>
       <c r="K104" s="5"/>
       <c r="L104" s="3"/>
@@ -5091,16 +5111,12 @@
       <c r="N104" s="3"/>
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
-      <c r="Q104" s="6"/>
-      <c r="R104" s="6"/>
-      <c r="S104" s="6" t="s">
+      <c r="S104" t="s">
         <v>293</v>
       </c>
-      <c r="T104" s="6"/>
-      <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" ht="15">
-      <c r="A105" s="6">
+      <c r="A105">
         <v>126</v>
       </c>
       <c r="B105" s="2">
@@ -5122,7 +5138,6 @@
         <v>46</v>
       </c>
       <c r="H105" s="3"/>
-      <c r="I105" s="6"/>
       <c r="J105" s="3"/>
       <c r="K105" s="5"/>
       <c r="L105" s="3"/>
@@ -5130,16 +5145,12 @@
       <c r="N105" s="3"/>
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
-      <c r="Q105" s="6"/>
-      <c r="R105" s="6"/>
-      <c r="S105" s="6" t="s">
+      <c r="S105" t="s">
         <v>294</v>
       </c>
-      <c r="T105" s="6"/>
-      <c r="U105" s="6"/>
     </row>
     <row r="106" spans="1:21" ht="15">
-      <c r="A106" s="6">
+      <c r="A106">
         <v>127</v>
       </c>
       <c r="B106" s="2">
@@ -5161,7 +5172,6 @@
         <v>38</v>
       </c>
       <c r="H106" s="3"/>
-      <c r="I106" s="6"/>
       <c r="J106" s="3"/>
       <c r="K106" s="5" t="s">
         <v>295</v>
@@ -5171,14 +5181,9 @@
       <c r="N106" s="3"/>
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="6"/>
-      <c r="S106" s="6"/>
-      <c r="T106" s="6"/>
-      <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" ht="15">
-      <c r="A107" s="6">
+      <c r="A107">
         <v>128</v>
       </c>
       <c r="B107" s="2">
@@ -5200,7 +5205,7 @@
         <v>60</v>
       </c>
       <c r="H107" s="3"/>
-      <c r="I107" s="6" t="s">
+      <c r="I107" t="s">
         <v>61</v>
       </c>
       <c r="J107" s="3" t="s">
@@ -5212,14 +5217,9 @@
       <c r="N107" s="3"/>
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
-      <c r="Q107" s="6"/>
-      <c r="R107" s="6"/>
-      <c r="S107" s="6"/>
-      <c r="T107" s="6"/>
-      <c r="U107" s="6"/>
     </row>
     <row r="108" spans="1:21" ht="15">
-      <c r="A108" s="6">
+      <c r="A108">
         <v>129</v>
       </c>
       <c r="B108" s="2">
@@ -5241,7 +5241,6 @@
         <v>46</v>
       </c>
       <c r="H108" s="3"/>
-      <c r="I108" s="6"/>
       <c r="J108" s="3"/>
       <c r="K108" s="5"/>
       <c r="L108" s="3"/>
@@ -5249,16 +5248,12 @@
       <c r="N108" s="3"/>
       <c r="O108" s="3"/>
       <c r="P108" s="3"/>
-      <c r="Q108" s="6"/>
-      <c r="R108" s="6"/>
-      <c r="S108" s="6" t="s">
+      <c r="S108" t="s">
         <v>299</v>
       </c>
-      <c r="T108" s="6"/>
-      <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="15">
-      <c r="A109" s="6">
+      <c r="A109">
         <v>130</v>
       </c>
       <c r="B109" s="2">
@@ -5280,7 +5275,7 @@
         <v>60</v>
       </c>
       <c r="H109" s="3"/>
-      <c r="I109" s="6" t="s">
+      <c r="I109" t="s">
         <v>61</v>
       </c>
       <c r="J109" s="3" t="s">
@@ -5292,14 +5287,9 @@
       <c r="N109" s="3"/>
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="6"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-      <c r="U109" s="6"/>
     </row>
     <row r="110" spans="1:21" ht="15">
-      <c r="A110" s="6">
+      <c r="A110">
         <v>131</v>
       </c>
       <c r="B110" s="2">
@@ -5321,7 +5311,6 @@
         <v>82</v>
       </c>
       <c r="H110" s="3"/>
-      <c r="I110" s="6"/>
       <c r="J110" s="3"/>
       <c r="K110" s="5"/>
       <c r="L110" s="3"/>
@@ -5331,16 +5320,123 @@
       <c r="N110" s="3"/>
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
-      <c r="Q110" s="6"/>
-      <c r="R110" s="6"/>
-      <c r="S110" s="6"/>
-      <c r="T110" s="6"/>
-      <c r="U110" s="6"/>
-    </row>
-    <row r="111" spans="1:21" ht="15"/>
-    <row r="112" spans="1:21" ht="15"/>
-    <row r="113" ht="15"/>
-    <row r="114" ht="15"/>
+    </row>
+    <row r="111" spans="1:21" ht="15">
+      <c r="A111">
+        <v>132</v>
+      </c>
+      <c r="B111" s="2">
+        <v>46265.530497685198</v>
+      </c>
+      <c r="C111" s="2">
+        <v>46265.531168981499</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H111" s="3"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3"/>
+      <c r="O111" s="3"/>
+      <c r="P111" s="3"/>
+      <c r="S111" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" ht="15">
+      <c r="A112" s="6">
+        <v>133</v>
+      </c>
+      <c r="B112" s="2">
+        <v>46265.531064814801</v>
+      </c>
+      <c r="C112" s="2">
+        <v>46265.531423611101</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H112" s="3"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="3"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="3"/>
+      <c r="M112" s="3"/>
+      <c r="N112" s="3"/>
+      <c r="O112" s="3"/>
+      <c r="P112" s="3"/>
+      <c r="Q112" s="6"/>
+      <c r="R112" s="6"/>
+      <c r="S112" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="T112" s="6"/>
+      <c r="U112" s="6"/>
+    </row>
+    <row r="113" spans="1:21" ht="15">
+      <c r="A113" s="6">
+        <v>134</v>
+      </c>
+      <c r="B113" s="2">
+        <v>46265.5304861111</v>
+      </c>
+      <c r="C113" s="2">
+        <v>46265.531932870399</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H113" s="3"/>
+      <c r="I113" s="6"/>
+      <c r="J113" s="3"/>
+      <c r="K113" s="5"/>
+      <c r="L113" s="3"/>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3"/>
+      <c r="O113" s="3"/>
+      <c r="P113" s="3"/>
+      <c r="Q113" s="6"/>
+      <c r="R113" s="6"/>
+      <c r="S113" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="T113" s="6"/>
+      <c r="U113" s="6"/>
+    </row>
+    <row r="114" spans="1:21" ht="15"/>
+    <row r="115" spans="1:21" ht="15"/>
+    <row r="116" spans="1:21" ht="15"/>
+    <row r="117" spans="1:21" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="292" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DCED3F9-CE5D-4E27-875C-959E62561C88}"/>
+  <xr:revisionPtr revIDLastSave="295" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8032D076-6078-47C4-A115-ED4A12014AA3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="340">
   <si>
     <t>Id</t>
   </si>
@@ -963,6 +963,99 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Hector%20Martinez%20Urib.jpg</t>
+  </si>
+  <si>
+    <t>38837</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/d2296900-c040-4c9a-9f54-d2f58252f2e2_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/445473a2-bed1-4768-b450-6b9d7f26f7f0_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38374@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Valle Dorado</t>
+  </si>
+  <si>
+    <t>38374</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/d6c1d756-d2a2-437c-a8ae-e6d583f9bdd8_Starbucks%20Valle%20Dora.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx43043@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Atizapan</t>
+  </si>
+  <si>
+    <t>43043</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/bddd1bfe-4ba7-4119-acf9-d9c2892ac1ce_Starbucks%20Atizapan.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38965@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Parque Tepeyac ll</t>
+  </si>
+  <si>
+    <t>38965</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17882065187641706708315795680076_Starbucks%20Parque%20Tep.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17882083990364110948795396710553_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38460@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Santa Monica</t>
+  </si>
+  <si>
+    <t>38460</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Starbucks%20Santa%20Moni.jpg</t>
+  </si>
+  <si>
+    <t>itzel.llamas@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Itzel Dayana Llamas Ramirez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/yooo_Itzel%20Dayana%20Llamas.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38811@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Tepeyac</t>
+  </si>
+  <si>
+    <t>38811</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/1788210592769911956211683940132_Starbucks%20Plaza%20Tepe.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG-20260831-WA0029_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_9960_Starbucks%20Plaza%20Sate.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/465EC501-DE39-43F9-9184-4C3FB567C49C-COLLAGE_Starbucks%20Valle%20Dora.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1094,8 +1187,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U113" totalsRowShown="0">
-  <autoFilter ref="A1:U113" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U126" totalsRowShown="0">
+  <autoFilter ref="A1:U126" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1248,7 +1341,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="134" latestEventMarker="367">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="147" latestEventMarker="380">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1573,7 +1666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U117"/>
+  <dimension ref="A1:U130"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -5356,7 +5449,7 @@
       </c>
     </row>
     <row r="112" spans="1:21" ht="15">
-      <c r="A112" s="6">
+      <c r="A112">
         <v>133</v>
       </c>
       <c r="B112" s="2">
@@ -5378,7 +5471,6 @@
         <v>46</v>
       </c>
       <c r="H112" s="3"/>
-      <c r="I112" s="6"/>
       <c r="J112" s="3"/>
       <c r="K112" s="5"/>
       <c r="L112" s="3"/>
@@ -5386,16 +5478,12 @@
       <c r="N112" s="3"/>
       <c r="O112" s="3"/>
       <c r="P112" s="3"/>
-      <c r="Q112" s="6"/>
-      <c r="R112" s="6"/>
-      <c r="S112" s="6" t="s">
+      <c r="S112" t="s">
         <v>307</v>
       </c>
-      <c r="T112" s="6"/>
-      <c r="U112" s="6"/>
     </row>
     <row r="113" spans="1:21" ht="15">
-      <c r="A113" s="6">
+      <c r="A113">
         <v>134</v>
       </c>
       <c r="B113" s="2">
@@ -5417,7 +5505,6 @@
         <v>46</v>
       </c>
       <c r="H113" s="3"/>
-      <c r="I113" s="6"/>
       <c r="J113" s="3"/>
       <c r="K113" s="5"/>
       <c r="L113" s="3"/>
@@ -5425,18 +5512,521 @@
       <c r="N113" s="3"/>
       <c r="O113" s="3"/>
       <c r="P113" s="3"/>
-      <c r="Q113" s="6"/>
-      <c r="R113" s="6"/>
-      <c r="S113" s="6" t="s">
+      <c r="S113" t="s">
         <v>308</v>
       </c>
-      <c r="T113" s="6"/>
-      <c r="U113" s="6"/>
-    </row>
-    <row r="114" spans="1:21" ht="15"/>
-    <row r="115" spans="1:21" ht="15"/>
-    <row r="116" spans="1:21" ht="15"/>
-    <row r="117" spans="1:21" ht="15"/>
+    </row>
+    <row r="114" spans="1:21" ht="15">
+      <c r="A114" s="6">
+        <v>135</v>
+      </c>
+      <c r="B114" s="2">
+        <v>46265.535150463002</v>
+      </c>
+      <c r="C114" s="2">
+        <v>46265.539687500001</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H114" s="3"/>
+      <c r="I114" s="6"/>
+      <c r="J114" s="3"/>
+      <c r="K114" s="5"/>
+      <c r="L114" s="3"/>
+      <c r="M114" s="3"/>
+      <c r="N114" s="3"/>
+      <c r="O114" s="3"/>
+      <c r="P114" s="3"/>
+      <c r="Q114" s="6"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="T114" s="6"/>
+      <c r="U114" s="6"/>
+    </row>
+    <row r="115" spans="1:21" ht="15">
+      <c r="A115" s="6">
+        <v>136</v>
+      </c>
+      <c r="B115" s="2">
+        <v>46265.543182870402</v>
+      </c>
+      <c r="C115" s="2">
+        <v>46265.544513888897</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H115" s="3"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="5"/>
+      <c r="L115" s="3"/>
+      <c r="M115" s="3"/>
+      <c r="N115" s="3"/>
+      <c r="O115" s="3"/>
+      <c r="P115" s="3"/>
+      <c r="Q115" s="6"/>
+      <c r="R115" s="6"/>
+      <c r="S115" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="T115" s="6"/>
+      <c r="U115" s="6"/>
+    </row>
+    <row r="116" spans="1:21" ht="15">
+      <c r="A116" s="6">
+        <v>137</v>
+      </c>
+      <c r="B116" s="2">
+        <v>46265.543483796297</v>
+      </c>
+      <c r="C116" s="2">
+        <v>46265.545104166697</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H116" s="3"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="3"/>
+      <c r="K116" s="5"/>
+      <c r="L116" s="3"/>
+      <c r="M116" s="3"/>
+      <c r="N116" s="3"/>
+      <c r="O116" s="3"/>
+      <c r="P116" s="3"/>
+      <c r="Q116" s="6"/>
+      <c r="R116" s="6"/>
+      <c r="S116" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="T116" s="6"/>
+      <c r="U116" s="6"/>
+    </row>
+    <row r="117" spans="1:21" ht="15">
+      <c r="A117" s="6">
+        <v>138</v>
+      </c>
+      <c r="B117" s="2">
+        <v>46265.563449074099</v>
+      </c>
+      <c r="C117" s="2">
+        <v>46265.567534722199</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H117" s="3"/>
+      <c r="I117" s="6"/>
+      <c r="J117" s="3"/>
+      <c r="K117" s="5"/>
+      <c r="L117" s="3"/>
+      <c r="M117" s="3"/>
+      <c r="N117" s="3"/>
+      <c r="O117" s="3"/>
+      <c r="P117" s="3"/>
+      <c r="Q117" s="6"/>
+      <c r="R117" s="6"/>
+      <c r="S117" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="T117" s="6"/>
+      <c r="U117" s="6"/>
+    </row>
+    <row r="118" spans="1:21" ht="15">
+      <c r="A118" s="6">
+        <v>139</v>
+      </c>
+      <c r="B118" s="2">
+        <v>46265.581388888902</v>
+      </c>
+      <c r="C118" s="2">
+        <v>46265.582719907397</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H118" s="3"/>
+      <c r="I118" s="6"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="5"/>
+      <c r="L118" s="3"/>
+      <c r="M118" s="3"/>
+      <c r="N118" s="3"/>
+      <c r="O118" s="3"/>
+      <c r="P118" s="3"/>
+      <c r="Q118" s="6"/>
+      <c r="R118" s="6"/>
+      <c r="S118" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="T118" s="6"/>
+      <c r="U118" s="6"/>
+    </row>
+    <row r="119" spans="1:21" ht="15">
+      <c r="A119" s="6">
+        <v>140</v>
+      </c>
+      <c r="B119" s="2">
+        <v>46265.5840046296</v>
+      </c>
+      <c r="C119" s="2">
+        <v>46265.585462962998</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H119" s="3"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="5"/>
+      <c r="L119" s="3"/>
+      <c r="M119" s="3"/>
+      <c r="N119" s="3"/>
+      <c r="O119" s="3"/>
+      <c r="P119" s="3"/>
+      <c r="Q119" s="6"/>
+      <c r="R119" s="6"/>
+      <c r="S119" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="T119" s="6"/>
+      <c r="U119" s="6"/>
+    </row>
+    <row r="120" spans="1:21" ht="15">
+      <c r="A120" s="6">
+        <v>141</v>
+      </c>
+      <c r="B120" s="2">
+        <v>46265.606226851902</v>
+      </c>
+      <c r="C120" s="2">
+        <v>46265.606793981497</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H120" s="3"/>
+      <c r="I120" s="6"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="L120" s="3"/>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3"/>
+      <c r="O120" s="3"/>
+      <c r="P120" s="3"/>
+      <c r="Q120" s="6"/>
+      <c r="R120" s="6"/>
+      <c r="S120" s="6"/>
+      <c r="T120" s="6"/>
+      <c r="U120" s="6"/>
+    </row>
+    <row r="121" spans="1:21" ht="15">
+      <c r="A121" s="6">
+        <v>142</v>
+      </c>
+      <c r="B121" s="2">
+        <v>46265.6150694444</v>
+      </c>
+      <c r="C121" s="2">
+        <v>46265.615694444401</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H121" s="3"/>
+      <c r="I121" s="6"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="5"/>
+      <c r="L121" s="3"/>
+      <c r="M121" s="3"/>
+      <c r="N121" s="3"/>
+      <c r="O121" s="3"/>
+      <c r="P121" s="3"/>
+      <c r="Q121" s="6"/>
+      <c r="R121" s="6"/>
+      <c r="S121" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="T121" s="6"/>
+      <c r="U121" s="6"/>
+    </row>
+    <row r="122" spans="1:21" ht="15">
+      <c r="A122" s="6">
+        <v>143</v>
+      </c>
+      <c r="B122" s="2">
+        <v>46265.616770833301</v>
+      </c>
+      <c r="C122" s="2">
+        <v>46265.618425925903</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H122" s="3"/>
+      <c r="I122" s="6"/>
+      <c r="J122" s="3"/>
+      <c r="K122" s="5"/>
+      <c r="L122" s="3"/>
+      <c r="M122" s="3"/>
+      <c r="N122" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="O122" s="3"/>
+      <c r="P122" s="3"/>
+      <c r="Q122" s="6"/>
+      <c r="R122" s="6"/>
+      <c r="S122" s="6"/>
+      <c r="T122" s="6"/>
+      <c r="U122" s="6"/>
+    </row>
+    <row r="123" spans="1:21" ht="15">
+      <c r="A123" s="6">
+        <v>144</v>
+      </c>
+      <c r="B123" s="2">
+        <v>46265.623680555596</v>
+      </c>
+      <c r="C123" s="2">
+        <v>46265.632581018501</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H123" s="3"/>
+      <c r="I123" s="6"/>
+      <c r="J123" s="3"/>
+      <c r="K123" s="5"/>
+      <c r="L123" s="3"/>
+      <c r="M123" s="3"/>
+      <c r="N123" s="3"/>
+      <c r="O123" s="3"/>
+      <c r="P123" s="3"/>
+      <c r="Q123" s="6"/>
+      <c r="R123" s="6"/>
+      <c r="S123" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="T123" s="6"/>
+      <c r="U123" s="6"/>
+    </row>
+    <row r="124" spans="1:21" ht="15">
+      <c r="A124" s="6">
+        <v>145</v>
+      </c>
+      <c r="B124" s="2">
+        <v>46265.629699074103</v>
+      </c>
+      <c r="C124" s="2">
+        <v>46265.633333333302</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H124" s="3"/>
+      <c r="I124" s="6"/>
+      <c r="J124" s="3"/>
+      <c r="K124" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="L124" s="3"/>
+      <c r="M124" s="3"/>
+      <c r="N124" s="3"/>
+      <c r="O124" s="3"/>
+      <c r="P124" s="3"/>
+      <c r="Q124" s="6"/>
+      <c r="R124" s="6"/>
+      <c r="S124" s="6"/>
+      <c r="T124" s="6"/>
+      <c r="U124" s="6"/>
+    </row>
+    <row r="125" spans="1:21" ht="15">
+      <c r="A125" s="6">
+        <v>146</v>
+      </c>
+      <c r="B125" s="2">
+        <v>46265.637604166703</v>
+      </c>
+      <c r="C125" s="2">
+        <v>46265.638668981497</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H125" s="3"/>
+      <c r="I125" s="6"/>
+      <c r="J125" s="3"/>
+      <c r="K125" s="5"/>
+      <c r="L125" s="3"/>
+      <c r="M125" s="3"/>
+      <c r="N125" s="3"/>
+      <c r="O125" s="3"/>
+      <c r="P125" s="3"/>
+      <c r="Q125" s="6"/>
+      <c r="R125" s="6"/>
+      <c r="S125" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="T125" s="6"/>
+      <c r="U125" s="6"/>
+    </row>
+    <row r="126" spans="1:21" ht="15">
+      <c r="A126" s="6">
+        <v>147</v>
+      </c>
+      <c r="B126" s="2">
+        <v>46265.659791666701</v>
+      </c>
+      <c r="C126" s="2">
+        <v>46265.662141203698</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H126" s="3"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="3"/>
+      <c r="K126" s="5"/>
+      <c r="L126" s="3"/>
+      <c r="M126" s="3"/>
+      <c r="N126" s="3"/>
+      <c r="O126" s="3"/>
+      <c r="P126" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q126" s="6"/>
+      <c r="R126" s="6"/>
+      <c r="S126" s="6"/>
+      <c r="T126" s="6"/>
+      <c r="U126" s="6"/>
+    </row>
+    <row r="127" spans="1:21" ht="15"/>
+    <row r="128" spans="1:21" ht="15"/>
+    <row r="129" ht="15"/>
+    <row r="130" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8032D076-6078-47C4-A115-ED4A12014AA3}"/>
+  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3293F565-83D5-439E-85E8-9727490F2888}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="341">
   <si>
     <t>Id</t>
   </si>
@@ -1056,13 +1056,16 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/465EC501-DE39-43F9-9184-4C3FB567C49C-COLLAGE_Starbucks%20Valle%20Dora.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Starbucks%20Galerias%20P.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1096,11 +1099,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1108,8 +1112,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1187,8 +1193,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U126" totalsRowShown="0">
-  <autoFilter ref="A1:U126" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U127" totalsRowShown="0">
+  <autoFilter ref="A1:U127" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1341,7 +1347,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="147" latestEventMarker="380">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="148" latestEventMarker="381">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1666,23 +1672,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U130"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <dimension ref="A1:U127"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" customWidth="1"/>
     <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.1796875" customWidth="1"/>
+    <col min="5" max="5" width="35.1796875" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="19" customWidth="1"/>
-    <col min="19" max="19" width="42.140625" customWidth="1"/>
+    <col min="19" max="19" width="42.1796875" customWidth="1"/>
     <col min="20" max="21" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1747,7 +1753,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>13</v>
       </c>
@@ -1773,7 +1779,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>17</v>
       </c>
@@ -1806,7 +1812,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>18</v>
       </c>
@@ -1839,7 +1845,7 @@
       </c>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>20</v>
       </c>
@@ -1872,7 +1878,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>21</v>
       </c>
@@ -1905,7 +1911,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>22</v>
       </c>
@@ -1938,7 +1944,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>23</v>
       </c>
@@ -1972,7 +1978,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>24</v>
       </c>
@@ -2006,7 +2012,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>25</v>
       </c>
@@ -2040,7 +2046,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>26</v>
       </c>
@@ -2073,7 +2079,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>27</v>
       </c>
@@ -2109,7 +2115,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>28</v>
       </c>
@@ -2142,7 +2148,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>29</v>
       </c>
@@ -2176,7 +2182,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>30</v>
       </c>
@@ -2209,7 +2215,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>31</v>
       </c>
@@ -2242,7 +2248,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>32</v>
       </c>
@@ -2276,7 +2282,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>33</v>
       </c>
@@ -2309,7 +2315,7 @@
       </c>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>34</v>
       </c>
@@ -2342,7 +2348,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>35</v>
       </c>
@@ -2375,7 +2381,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>36</v>
       </c>
@@ -2408,7 +2414,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>37</v>
       </c>
@@ -2442,7 +2448,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>38</v>
       </c>
@@ -2476,7 +2482,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>39</v>
       </c>
@@ -2510,7 +2516,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>40</v>
       </c>
@@ -2544,7 +2550,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>41</v>
       </c>
@@ -2577,7 +2583,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>42</v>
       </c>
@@ -2611,7 +2617,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>43</v>
       </c>
@@ -2645,7 +2651,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>44</v>
       </c>
@@ -2679,7 +2685,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>45</v>
       </c>
@@ -2713,7 +2719,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>46</v>
       </c>
@@ -2747,7 +2753,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>47</v>
       </c>
@@ -2781,7 +2787,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>48</v>
       </c>
@@ -2814,7 +2820,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>49</v>
       </c>
@@ -2848,7 +2854,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>50</v>
       </c>
@@ -2882,7 +2888,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>51</v>
       </c>
@@ -2916,7 +2922,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="15">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>52</v>
       </c>
@@ -2949,7 +2955,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>54</v>
       </c>
@@ -2982,7 +2988,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>55</v>
       </c>
@@ -3015,7 +3021,7 @@
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>56</v>
       </c>
@@ -3049,7 +3055,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="15">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>57</v>
       </c>
@@ -3083,7 +3089,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="15">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>58</v>
       </c>
@@ -3117,7 +3123,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="15">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>59</v>
       </c>
@@ -3151,7 +3157,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>60</v>
       </c>
@@ -3185,7 +3191,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>61</v>
       </c>
@@ -3219,7 +3225,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>62</v>
       </c>
@@ -3253,7 +3259,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>63</v>
       </c>
@@ -3287,7 +3293,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>65</v>
       </c>
@@ -3321,7 +3327,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="15">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>66</v>
       </c>
@@ -3355,7 +3361,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="15">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>67</v>
       </c>
@@ -3388,7 +3394,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:19" ht="15">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>68</v>
       </c>
@@ -3421,7 +3427,7 @@
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:19" ht="15">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>69</v>
       </c>
@@ -3455,7 +3461,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="15">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>70</v>
       </c>
@@ -3489,7 +3495,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="15">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>71</v>
       </c>
@@ -3523,7 +3529,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="15">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>72</v>
       </c>
@@ -3557,7 +3563,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="15">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>73</v>
       </c>
@@ -3591,7 +3597,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="15">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>74</v>
       </c>
@@ -3625,7 +3631,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="15">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>75</v>
       </c>
@@ -3659,7 +3665,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="15">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>76</v>
       </c>
@@ -3693,7 +3699,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="15">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>77</v>
       </c>
@@ -3726,7 +3732,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="15">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>78</v>
       </c>
@@ -3760,7 +3766,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="15">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>79</v>
       </c>
@@ -3794,7 +3800,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="15">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>80</v>
       </c>
@@ -3828,7 +3834,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="15">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>81</v>
       </c>
@@ -3862,7 +3868,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="15">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>84</v>
       </c>
@@ -3896,7 +3902,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="15">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>85</v>
       </c>
@@ -3929,7 +3935,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:19" ht="15">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>86</v>
       </c>
@@ -3962,7 +3968,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:19" ht="15">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>88</v>
       </c>
@@ -3995,7 +4001,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="15">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>89</v>
       </c>
@@ -4028,7 +4034,7 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:19" ht="15">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>90</v>
       </c>
@@ -4062,7 +4068,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="15">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>91</v>
       </c>
@@ -4096,7 +4102,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="15">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>92</v>
       </c>
@@ -4132,7 +4138,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="1:19" ht="15">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>93</v>
       </c>
@@ -4165,7 +4171,7 @@
       </c>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:19" ht="15">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>94</v>
       </c>
@@ -4198,7 +4204,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:19" ht="15">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>95</v>
       </c>
@@ -4231,7 +4237,7 @@
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="1:19" ht="15">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>96</v>
       </c>
@@ -4265,7 +4271,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="15">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>97</v>
       </c>
@@ -4298,7 +4304,7 @@
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:19" ht="15">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>98</v>
       </c>
@@ -4332,7 +4338,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="15">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>99</v>
       </c>
@@ -4365,7 +4371,7 @@
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:19" ht="15">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>100</v>
       </c>
@@ -4399,7 +4405,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="15">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>102</v>
       </c>
@@ -4435,7 +4441,7 @@
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:19" ht="15">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>103</v>
       </c>
@@ -4468,7 +4474,7 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="1:19" ht="15">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>104</v>
       </c>
@@ -4502,7 +4508,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="15">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>105</v>
       </c>
@@ -4538,7 +4544,7 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:19" ht="15">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>106</v>
       </c>
@@ -4572,7 +4578,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="15">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>107</v>
       </c>
@@ -4605,7 +4611,7 @@
       </c>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="1:19" ht="15">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>108</v>
       </c>
@@ -4639,7 +4645,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="15">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>109</v>
       </c>
@@ -4673,7 +4679,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="15">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>110</v>
       </c>
@@ -4706,7 +4712,7 @@
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:19" ht="15">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>111</v>
       </c>
@@ -4740,7 +4746,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="15">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>112</v>
       </c>
@@ -4773,7 +4779,7 @@
       </c>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:19" ht="15">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>113</v>
       </c>
@@ -4807,7 +4813,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="15">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>114</v>
       </c>
@@ -4841,7 +4847,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="15">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>115</v>
       </c>
@@ -4874,7 +4880,7 @@
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:19" ht="15">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>116</v>
       </c>
@@ -4907,7 +4913,7 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:19" ht="15">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>117</v>
       </c>
@@ -4940,7 +4946,7 @@
       </c>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:21" ht="15">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>118</v>
       </c>
@@ -4973,7 +4979,7 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:21" ht="15">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>119</v>
       </c>
@@ -5006,7 +5012,7 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
     </row>
-    <row r="99" spans="1:21" ht="15">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>120</v>
       </c>
@@ -5039,7 +5045,7 @@
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
     </row>
-    <row r="100" spans="1:21" ht="15">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>121</v>
       </c>
@@ -5073,7 +5079,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="15">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>122</v>
       </c>
@@ -5106,7 +5112,7 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:21" ht="15">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>123</v>
       </c>
@@ -5140,7 +5146,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="103" spans="1:21" ht="15">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>124</v>
       </c>
@@ -5174,7 +5180,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="104" spans="1:21" ht="15">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>125</v>
       </c>
@@ -5208,7 +5214,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:21" ht="15">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>126</v>
       </c>
@@ -5242,7 +5248,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="106" spans="1:21" ht="15">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>127</v>
       </c>
@@ -5275,7 +5281,7 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:21" ht="15">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>128</v>
       </c>
@@ -5311,7 +5317,7 @@
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
     </row>
-    <row r="108" spans="1:21" ht="15">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>129</v>
       </c>
@@ -5345,7 +5351,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="15">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>130</v>
       </c>
@@ -5381,7 +5387,7 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:21" ht="15">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>131</v>
       </c>
@@ -5414,7 +5420,7 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:21" ht="15">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>132</v>
       </c>
@@ -5448,7 +5454,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="112" spans="1:21" ht="15">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>133</v>
       </c>
@@ -5482,7 +5488,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="15">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>134</v>
       </c>
@@ -5516,8 +5522,8 @@
         <v>308</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="15">
-      <c r="A114" s="6">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A114">
         <v>135</v>
       </c>
       <c r="B114" s="2">
@@ -5539,7 +5545,6 @@
         <v>46</v>
       </c>
       <c r="H114" s="3"/>
-      <c r="I114" s="6"/>
       <c r="J114" s="3"/>
       <c r="K114" s="5"/>
       <c r="L114" s="3"/>
@@ -5547,16 +5552,12 @@
       <c r="N114" s="3"/>
       <c r="O114" s="3"/>
       <c r="P114" s="3"/>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="6"/>
-      <c r="S114" s="6" t="s">
+      <c r="S114" t="s">
         <v>310</v>
       </c>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
-    </row>
-    <row r="115" spans="1:21" ht="15">
-      <c r="A115" s="6">
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A115">
         <v>136</v>
       </c>
       <c r="B115" s="2">
@@ -5578,7 +5579,6 @@
         <v>46</v>
       </c>
       <c r="H115" s="3"/>
-      <c r="I115" s="6"/>
       <c r="J115" s="3"/>
       <c r="K115" s="5"/>
       <c r="L115" s="3"/>
@@ -5586,16 +5586,12 @@
       <c r="N115" s="3"/>
       <c r="O115" s="3"/>
       <c r="P115" s="3"/>
-      <c r="Q115" s="6"/>
-      <c r="R115" s="6"/>
-      <c r="S115" s="6" t="s">
+      <c r="S115" t="s">
         <v>311</v>
       </c>
-      <c r="T115" s="6"/>
-      <c r="U115" s="6"/>
-    </row>
-    <row r="116" spans="1:21" ht="15">
-      <c r="A116" s="6">
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A116">
         <v>137</v>
       </c>
       <c r="B116" s="2">
@@ -5617,7 +5613,6 @@
         <v>46</v>
       </c>
       <c r="H116" s="3"/>
-      <c r="I116" s="6"/>
       <c r="J116" s="3"/>
       <c r="K116" s="5"/>
       <c r="L116" s="3"/>
@@ -5625,16 +5620,12 @@
       <c r="N116" s="3"/>
       <c r="O116" s="3"/>
       <c r="P116" s="3"/>
-      <c r="Q116" s="6"/>
-      <c r="R116" s="6"/>
-      <c r="S116" s="6" t="s">
+      <c r="S116" t="s">
         <v>312</v>
       </c>
-      <c r="T116" s="6"/>
-      <c r="U116" s="6"/>
-    </row>
-    <row r="117" spans="1:21" ht="15">
-      <c r="A117" s="6">
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A117">
         <v>138</v>
       </c>
       <c r="B117" s="2">
@@ -5656,7 +5647,6 @@
         <v>46</v>
       </c>
       <c r="H117" s="3"/>
-      <c r="I117" s="6"/>
       <c r="J117" s="3"/>
       <c r="K117" s="5"/>
       <c r="L117" s="3"/>
@@ -5664,16 +5654,12 @@
       <c r="N117" s="3"/>
       <c r="O117" s="3"/>
       <c r="P117" s="3"/>
-      <c r="Q117" s="6"/>
-      <c r="R117" s="6"/>
-      <c r="S117" s="6" t="s">
+      <c r="S117" t="s">
         <v>316</v>
       </c>
-      <c r="T117" s="6"/>
-      <c r="U117" s="6"/>
-    </row>
-    <row r="118" spans="1:21" ht="15">
-      <c r="A118" s="6">
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A118">
         <v>139</v>
       </c>
       <c r="B118" s="2">
@@ -5695,7 +5681,6 @@
         <v>46</v>
       </c>
       <c r="H118" s="3"/>
-      <c r="I118" s="6"/>
       <c r="J118" s="3"/>
       <c r="K118" s="5"/>
       <c r="L118" s="3"/>
@@ -5703,16 +5688,12 @@
       <c r="N118" s="3"/>
       <c r="O118" s="3"/>
       <c r="P118" s="3"/>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="6"/>
-      <c r="S118" s="6" t="s">
+      <c r="S118" t="s">
         <v>320</v>
       </c>
-      <c r="T118" s="6"/>
-      <c r="U118" s="6"/>
-    </row>
-    <row r="119" spans="1:21" ht="15">
-      <c r="A119" s="6">
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A119">
         <v>140</v>
       </c>
       <c r="B119" s="2">
@@ -5734,7 +5715,6 @@
         <v>46</v>
       </c>
       <c r="H119" s="3"/>
-      <c r="I119" s="6"/>
       <c r="J119" s="3"/>
       <c r="K119" s="5"/>
       <c r="L119" s="3"/>
@@ -5742,16 +5722,12 @@
       <c r="N119" s="3"/>
       <c r="O119" s="3"/>
       <c r="P119" s="3"/>
-      <c r="Q119" s="6"/>
-      <c r="R119" s="6"/>
-      <c r="S119" s="6" t="s">
+      <c r="S119" t="s">
         <v>324</v>
       </c>
-      <c r="T119" s="6"/>
-      <c r="U119" s="6"/>
-    </row>
-    <row r="120" spans="1:21" ht="15">
-      <c r="A120" s="6">
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A120">
         <v>141</v>
       </c>
       <c r="B120" s="2">
@@ -5773,7 +5749,6 @@
         <v>38</v>
       </c>
       <c r="H120" s="3"/>
-      <c r="I120" s="6"/>
       <c r="J120" s="3"/>
       <c r="K120" s="5" t="s">
         <v>325</v>
@@ -5783,14 +5758,9 @@
       <c r="N120" s="3"/>
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
-      <c r="Q120" s="6"/>
-      <c r="R120" s="6"/>
-      <c r="S120" s="6"/>
-      <c r="T120" s="6"/>
-      <c r="U120" s="6"/>
-    </row>
-    <row r="121" spans="1:21" ht="15">
-      <c r="A121" s="6">
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A121">
         <v>142</v>
       </c>
       <c r="B121" s="2">
@@ -5812,7 +5782,6 @@
         <v>46</v>
       </c>
       <c r="H121" s="3"/>
-      <c r="I121" s="6"/>
       <c r="J121" s="3"/>
       <c r="K121" s="5"/>
       <c r="L121" s="3"/>
@@ -5820,16 +5789,12 @@
       <c r="N121" s="3"/>
       <c r="O121" s="3"/>
       <c r="P121" s="3"/>
-      <c r="Q121" s="6"/>
-      <c r="R121" s="6"/>
-      <c r="S121" s="6" t="s">
+      <c r="S121" t="s">
         <v>329</v>
       </c>
-      <c r="T121" s="6"/>
-      <c r="U121" s="6"/>
-    </row>
-    <row r="122" spans="1:21" ht="15">
-      <c r="A122" s="6">
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A122">
         <v>143</v>
       </c>
       <c r="B122" s="2">
@@ -5851,7 +5816,6 @@
         <v>217</v>
       </c>
       <c r="H122" s="3"/>
-      <c r="I122" s="6"/>
       <c r="J122" s="3"/>
       <c r="K122" s="5"/>
       <c r="L122" s="3"/>
@@ -5861,14 +5825,9 @@
       </c>
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
-      <c r="Q122" s="6"/>
-      <c r="R122" s="6"/>
-      <c r="S122" s="6"/>
-      <c r="T122" s="6"/>
-      <c r="U122" s="6"/>
-    </row>
-    <row r="123" spans="1:21" ht="15">
-      <c r="A123" s="6">
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A123">
         <v>144</v>
       </c>
       <c r="B123" s="2">
@@ -5890,7 +5849,6 @@
         <v>46</v>
       </c>
       <c r="H123" s="3"/>
-      <c r="I123" s="6"/>
       <c r="J123" s="3"/>
       <c r="K123" s="5"/>
       <c r="L123" s="3"/>
@@ -5898,16 +5856,12 @@
       <c r="N123" s="3"/>
       <c r="O123" s="3"/>
       <c r="P123" s="3"/>
-      <c r="Q123" s="6"/>
-      <c r="R123" s="6"/>
-      <c r="S123" s="6" t="s">
+      <c r="S123" t="s">
         <v>336</v>
       </c>
-      <c r="T123" s="6"/>
-      <c r="U123" s="6"/>
-    </row>
-    <row r="124" spans="1:21" ht="15">
-      <c r="A124" s="6">
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A124">
         <v>145</v>
       </c>
       <c r="B124" s="2">
@@ -5929,7 +5883,6 @@
         <v>38</v>
       </c>
       <c r="H124" s="3"/>
-      <c r="I124" s="6"/>
       <c r="J124" s="3"/>
       <c r="K124" s="5" t="s">
         <v>337</v>
@@ -5939,14 +5892,9 @@
       <c r="N124" s="3"/>
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
-      <c r="Q124" s="6"/>
-      <c r="R124" s="6"/>
-      <c r="S124" s="6"/>
-      <c r="T124" s="6"/>
-      <c r="U124" s="6"/>
-    </row>
-    <row r="125" spans="1:21" ht="15">
-      <c r="A125" s="6">
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A125">
         <v>146</v>
       </c>
       <c r="B125" s="2">
@@ -5968,7 +5916,6 @@
         <v>46</v>
       </c>
       <c r="H125" s="3"/>
-      <c r="I125" s="6"/>
       <c r="J125" s="3"/>
       <c r="K125" s="5"/>
       <c r="L125" s="3"/>
@@ -5976,16 +5923,12 @@
       <c r="N125" s="3"/>
       <c r="O125" s="3"/>
       <c r="P125" s="3"/>
-      <c r="Q125" s="6"/>
-      <c r="R125" s="6"/>
-      <c r="S125" s="6" t="s">
+      <c r="S125" t="s">
         <v>338</v>
       </c>
-      <c r="T125" s="6"/>
-      <c r="U125" s="6"/>
-    </row>
-    <row r="126" spans="1:21" ht="15">
-      <c r="A126" s="6">
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A126">
         <v>147</v>
       </c>
       <c r="B126" s="2">
@@ -6007,7 +5950,6 @@
         <v>41</v>
       </c>
       <c r="H126" s="3"/>
-      <c r="I126" s="6"/>
       <c r="J126" s="3"/>
       <c r="K126" s="5"/>
       <c r="L126" s="3"/>
@@ -6017,16 +5959,48 @@
       <c r="P126" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="6"/>
-      <c r="S126" s="6"/>
-      <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
-    </row>
-    <row r="127" spans="1:21" ht="15"/>
-    <row r="128" spans="1:21" ht="15"/>
-    <row r="129" ht="15"/>
-    <row r="130" ht="15"/>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A127" s="6">
+        <v>148</v>
+      </c>
+      <c r="B127" s="2">
+        <v>46265.665706018503</v>
+      </c>
+      <c r="C127" s="2">
+        <v>46265.667048611103</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H127" s="3"/>
+      <c r="I127" s="6"/>
+      <c r="J127" s="3"/>
+      <c r="K127" s="7"/>
+      <c r="L127" s="3"/>
+      <c r="M127" s="3"/>
+      <c r="N127" s="3"/>
+      <c r="O127" s="3"/>
+      <c r="P127" s="3"/>
+      <c r="Q127" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="R127" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="S127" s="6"/>
+      <c r="T127" s="6"/>
+      <c r="U127" s="6"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3293F565-83D5-439E-85E8-9727490F2888}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22CA0463-1288-484D-B526-363ECC1C1A14}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="372">
   <si>
     <t>Id</t>
   </si>
@@ -1059,13 +1059,106 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Starbucks%20Galerias%20P.jpg</t>
+  </si>
+  <si>
+    <t>cristian.posadas@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Cristian Alexis Posadas Lorenzo</t>
+  </si>
+  <si>
+    <t>38792</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/1CA83E1A-2E7F-417E-B43E-7AE597662ABC_Cristian%20Alexis%20Posa.jpeg</t>
+  </si>
+  <si>
+    <t>eduardo.reyes@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Eduardo David Reyes Chavez</t>
+  </si>
+  <si>
+    <t>38507</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/image_Eduardo%20David%20Reyes.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38903@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks ENCUENTRO OCEANIA PB</t>
+  </si>
+  <si>
+    <t>38903</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17882190955107206503585646954031_Starbucks%20ENCUENTRO.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38230@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks ITESM Estado de Mexico</t>
+  </si>
+  <si>
+    <t>38230</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/1788219984526812148918871491364_Starbucks%20ITESM%20Esta.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17882221160672822207562542757613_Dulce%20Maria%20Guzman%20S.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38995@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Encuentro Oceania II</t>
+  </si>
+  <si>
+    <t>38995</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17882225517942084554201654839000_Starbucks%20Encuentro.jpg</t>
+  </si>
+  <si>
+    <t>fany.jeovana@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Fany Jeovana Echeverria Beristain</t>
+  </si>
+  <si>
+    <t>38529</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17882233961481322064211549309613_Fany%20Jeovana%20Echever.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Hector%20Martinez%20Urib.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Hector%20Martinez%20Urib.jpg</t>
+  </si>
+  <si>
+    <t>ramon.espinosa@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Ramon Espinosa Macias</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/17882271606346828283724662549841_Ramon%20Espinosa%20Macia.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/20260831_200509_Starbucks%20Patio%20Ecat.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1111,8 +1204,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1193,8 +1286,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U127" totalsRowShown="0">
-  <autoFilter ref="A1:U127" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U138" totalsRowShown="0">
+  <autoFilter ref="A1:U138" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1347,7 +1440,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="148" latestEventMarker="381">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="159" latestEventMarker="394">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1672,23 +1765,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:U138"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.7265625" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
     <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" customWidth="1"/>
-    <col min="5" max="5" width="35.1796875" customWidth="1"/>
-    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="19" customWidth="1"/>
-    <col min="19" max="19" width="42.1796875" customWidth="1"/>
+    <col min="19" max="19" width="42.140625" customWidth="1"/>
     <col min="20" max="21" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1753,7 +1846,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>13</v>
       </c>
@@ -1779,7 +1872,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>17</v>
       </c>
@@ -1812,7 +1905,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21">
       <c r="A4">
         <v>18</v>
       </c>
@@ -1845,7 +1938,7 @@
       </c>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21">
       <c r="A5">
         <v>20</v>
       </c>
@@ -1878,7 +1971,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>21</v>
       </c>
@@ -1911,7 +2004,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>22</v>
       </c>
@@ -1944,7 +2037,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>23</v>
       </c>
@@ -1978,7 +2071,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>24</v>
       </c>
@@ -2012,7 +2105,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>25</v>
       </c>
@@ -2046,7 +2139,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21">
       <c r="A11">
         <v>26</v>
       </c>
@@ -2079,7 +2172,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21">
       <c r="A12">
         <v>27</v>
       </c>
@@ -2115,7 +2208,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21">
       <c r="A13">
         <v>28</v>
       </c>
@@ -2148,7 +2241,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21">
       <c r="A14">
         <v>29</v>
       </c>
@@ -2182,7 +2275,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21">
       <c r="A15">
         <v>30</v>
       </c>
@@ -2215,7 +2308,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21">
       <c r="A16">
         <v>31</v>
       </c>
@@ -2248,7 +2341,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19">
       <c r="A17">
         <v>32</v>
       </c>
@@ -2282,7 +2375,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19">
       <c r="A18">
         <v>33</v>
       </c>
@@ -2315,7 +2408,7 @@
       </c>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>34</v>
       </c>
@@ -2348,7 +2441,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>35</v>
       </c>
@@ -2381,7 +2474,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>36</v>
       </c>
@@ -2414,7 +2507,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>37</v>
       </c>
@@ -2448,7 +2541,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>38</v>
       </c>
@@ -2482,7 +2575,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>39</v>
       </c>
@@ -2516,7 +2609,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>40</v>
       </c>
@@ -2550,7 +2643,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>41</v>
       </c>
@@ -2583,7 +2676,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>42</v>
       </c>
@@ -2617,7 +2710,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>43</v>
       </c>
@@ -2651,7 +2744,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19">
       <c r="A29">
         <v>44</v>
       </c>
@@ -2685,7 +2778,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19">
       <c r="A30">
         <v>45</v>
       </c>
@@ -2719,7 +2812,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19">
       <c r="A31">
         <v>46</v>
       </c>
@@ -2753,7 +2846,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19">
       <c r="A32">
         <v>47</v>
       </c>
@@ -2787,7 +2880,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19">
       <c r="A33">
         <v>48</v>
       </c>
@@ -2820,7 +2913,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>49</v>
       </c>
@@ -2854,7 +2947,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>50</v>
       </c>
@@ -2888,7 +2981,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>51</v>
       </c>
@@ -2922,7 +3015,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>52</v>
       </c>
@@ -2955,7 +3048,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>54</v>
       </c>
@@ -2988,7 +3081,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>55</v>
       </c>
@@ -3021,7 +3114,7 @@
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>56</v>
       </c>
@@ -3055,7 +3148,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>57</v>
       </c>
@@ -3089,7 +3182,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>58</v>
       </c>
@@ -3123,7 +3216,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>59</v>
       </c>
@@ -3157,7 +3250,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19">
       <c r="A44">
         <v>60</v>
       </c>
@@ -3191,7 +3284,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19">
       <c r="A45">
         <v>61</v>
       </c>
@@ -3225,7 +3318,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19">
       <c r="A46">
         <v>62</v>
       </c>
@@ -3259,7 +3352,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19">
       <c r="A47">
         <v>63</v>
       </c>
@@ -3293,7 +3386,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19">
       <c r="A48">
         <v>65</v>
       </c>
@@ -3327,7 +3420,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>66</v>
       </c>
@@ -3361,7 +3454,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>67</v>
       </c>
@@ -3394,7 +3487,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>68</v>
       </c>
@@ -3427,7 +3520,7 @@
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>69</v>
       </c>
@@ -3461,7 +3554,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>70</v>
       </c>
@@ -3495,7 +3588,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>71</v>
       </c>
@@ -3529,7 +3622,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>72</v>
       </c>
@@ -3563,7 +3656,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>73</v>
       </c>
@@ -3597,7 +3690,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>74</v>
       </c>
@@ -3631,7 +3724,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>75</v>
       </c>
@@ -3665,7 +3758,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19">
       <c r="A59">
         <v>76</v>
       </c>
@@ -3699,7 +3792,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19">
       <c r="A60">
         <v>77</v>
       </c>
@@ -3732,7 +3825,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19">
       <c r="A61">
         <v>78</v>
       </c>
@@ -3766,7 +3859,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19">
       <c r="A62">
         <v>79</v>
       </c>
@@ -3800,7 +3893,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19">
       <c r="A63">
         <v>80</v>
       </c>
@@ -3834,7 +3927,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>81</v>
       </c>
@@ -3868,7 +3961,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>84</v>
       </c>
@@ -3902,7 +3995,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>85</v>
       </c>
@@ -3935,7 +4028,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>86</v>
       </c>
@@ -3968,7 +4061,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>88</v>
       </c>
@@ -4001,7 +4094,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>89</v>
       </c>
@@ -4034,7 +4127,7 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>90</v>
       </c>
@@ -4068,7 +4161,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>91</v>
       </c>
@@ -4102,7 +4195,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>92</v>
       </c>
@@ -4138,7 +4231,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>93</v>
       </c>
@@ -4171,7 +4264,7 @@
       </c>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:19">
       <c r="A74">
         <v>94</v>
       </c>
@@ -4204,7 +4297,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19">
       <c r="A75">
         <v>95</v>
       </c>
@@ -4237,7 +4330,7 @@
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19">
       <c r="A76">
         <v>96</v>
       </c>
@@ -4271,7 +4364,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19">
       <c r="A77">
         <v>97</v>
       </c>
@@ -4304,7 +4397,7 @@
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19">
       <c r="A78">
         <v>98</v>
       </c>
@@ -4338,7 +4431,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>99</v>
       </c>
@@ -4371,7 +4464,7 @@
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>100</v>
       </c>
@@ -4405,7 +4498,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>102</v>
       </c>
@@ -4441,7 +4534,7 @@
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>103</v>
       </c>
@@ -4474,7 +4567,7 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>104</v>
       </c>
@@ -4508,7 +4601,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>105</v>
       </c>
@@ -4544,7 +4637,7 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>106</v>
       </c>
@@ -4578,7 +4671,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>107</v>
       </c>
@@ -4611,7 +4704,7 @@
       </c>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>108</v>
       </c>
@@ -4645,7 +4738,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>109</v>
       </c>
@@ -4679,7 +4772,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19">
       <c r="A89">
         <v>110</v>
       </c>
@@ -4712,7 +4805,7 @@
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19">
       <c r="A90">
         <v>111</v>
       </c>
@@ -4746,7 +4839,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19">
       <c r="A91">
         <v>112</v>
       </c>
@@ -4779,7 +4872,7 @@
       </c>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19">
       <c r="A92">
         <v>113</v>
       </c>
@@ -4813,7 +4906,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19">
       <c r="A93">
         <v>114</v>
       </c>
@@ -4847,7 +4940,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19">
       <c r="A94">
         <v>115</v>
       </c>
@@ -4880,7 +4973,7 @@
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19">
       <c r="A95">
         <v>116</v>
       </c>
@@ -4913,7 +5006,7 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19">
       <c r="A96">
         <v>117</v>
       </c>
@@ -4946,7 +5039,7 @@
       </c>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21">
       <c r="A97">
         <v>118</v>
       </c>
@@ -4979,7 +5072,7 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21">
       <c r="A98">
         <v>119</v>
       </c>
@@ -5012,7 +5105,7 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21">
       <c r="A99">
         <v>120</v>
       </c>
@@ -5045,7 +5138,7 @@
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21">
       <c r="A100">
         <v>121</v>
       </c>
@@ -5079,7 +5172,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21">
       <c r="A101">
         <v>122</v>
       </c>
@@ -5112,7 +5205,7 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21">
       <c r="A102">
         <v>123</v>
       </c>
@@ -5146,7 +5239,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21">
       <c r="A103">
         <v>124</v>
       </c>
@@ -5180,7 +5273,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21">
       <c r="A104">
         <v>125</v>
       </c>
@@ -5214,7 +5307,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21">
       <c r="A105">
         <v>126</v>
       </c>
@@ -5248,7 +5341,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21">
       <c r="A106">
         <v>127</v>
       </c>
@@ -5281,7 +5374,7 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21">
       <c r="A107">
         <v>128</v>
       </c>
@@ -5317,7 +5410,7 @@
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21">
       <c r="A108">
         <v>129</v>
       </c>
@@ -5351,7 +5444,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21">
       <c r="A109">
         <v>130</v>
       </c>
@@ -5387,7 +5480,7 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21">
       <c r="A110">
         <v>131</v>
       </c>
@@ -5420,7 +5513,7 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21">
       <c r="A111">
         <v>132</v>
       </c>
@@ -5454,7 +5547,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21">
       <c r="A112">
         <v>133</v>
       </c>
@@ -5488,7 +5581,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:19">
       <c r="A113">
         <v>134</v>
       </c>
@@ -5522,7 +5615,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:19">
       <c r="A114">
         <v>135</v>
       </c>
@@ -5556,7 +5649,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:19">
       <c r="A115">
         <v>136</v>
       </c>
@@ -5590,7 +5683,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:19">
       <c r="A116">
         <v>137</v>
       </c>
@@ -5624,7 +5717,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:19">
       <c r="A117">
         <v>138</v>
       </c>
@@ -5658,7 +5751,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:19">
       <c r="A118">
         <v>139</v>
       </c>
@@ -5692,7 +5785,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:19">
       <c r="A119">
         <v>140</v>
       </c>
@@ -5726,7 +5819,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:19">
       <c r="A120">
         <v>141</v>
       </c>
@@ -5759,7 +5852,7 @@
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:19">
       <c r="A121">
         <v>142</v>
       </c>
@@ -5793,7 +5886,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:19">
       <c r="A122">
         <v>143</v>
       </c>
@@ -5826,7 +5919,7 @@
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:19">
       <c r="A123">
         <v>144</v>
       </c>
@@ -5860,7 +5953,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:19">
       <c r="A124">
         <v>145</v>
       </c>
@@ -5893,7 +5986,7 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:19">
       <c r="A125">
         <v>146</v>
       </c>
@@ -5927,7 +6020,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:19">
       <c r="A126">
         <v>147</v>
       </c>
@@ -5960,8 +6053,8 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A127" s="6">
+    <row r="127" spans="1:19">
+      <c r="A127">
         <v>148</v>
       </c>
       <c r="B127" s="2">
@@ -5983,23 +6076,447 @@
         <v>106</v>
       </c>
       <c r="H127" s="3"/>
-      <c r="I127" s="6"/>
       <c r="J127" s="3"/>
-      <c r="K127" s="7"/>
+      <c r="K127" s="6"/>
       <c r="L127" s="3"/>
       <c r="M127" s="3"/>
       <c r="N127" s="3"/>
       <c r="O127" s="3"/>
       <c r="P127" s="3"/>
-      <c r="Q127" s="6" t="s">
+      <c r="Q127" t="s">
         <v>61</v>
       </c>
-      <c r="R127" s="6" t="s">
+      <c r="R127" t="s">
         <v>340</v>
       </c>
-      <c r="S127" s="6"/>
-      <c r="T127" s="6"/>
-      <c r="U127" s="6"/>
+    </row>
+    <row r="128" spans="1:19" ht="15">
+      <c r="A128">
+        <v>149</v>
+      </c>
+      <c r="B128" s="2">
+        <v>46265.698530092603</v>
+      </c>
+      <c r="C128" s="2">
+        <v>46265.699085648099</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H128" s="3"/>
+      <c r="J128" s="3"/>
+      <c r="K128" s="6"/>
+      <c r="L128" s="3"/>
+      <c r="M128" s="3"/>
+      <c r="N128" s="3"/>
+      <c r="O128" s="3"/>
+      <c r="P128" s="3"/>
+      <c r="S128" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" ht="15">
+      <c r="A129" s="7">
+        <v>150</v>
+      </c>
+      <c r="B129" s="2">
+        <v>46265.728703703702</v>
+      </c>
+      <c r="C129" s="2">
+        <v>46265.729236111103</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H129" s="3"/>
+      <c r="I129" s="7"/>
+      <c r="J129" s="3"/>
+      <c r="K129" s="6"/>
+      <c r="L129" s="3"/>
+      <c r="M129" s="3"/>
+      <c r="N129" s="3"/>
+      <c r="O129" s="3"/>
+      <c r="P129" s="3"/>
+      <c r="Q129" s="7"/>
+      <c r="R129" s="7"/>
+      <c r="S129" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="T129" s="7"/>
+      <c r="U129" s="7"/>
+    </row>
+    <row r="130" spans="1:21" ht="15">
+      <c r="A130" s="7">
+        <v>151</v>
+      </c>
+      <c r="B130" s="2">
+        <v>46265.729270833297</v>
+      </c>
+      <c r="C130" s="2">
+        <v>46265.730706018498</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H130" s="3"/>
+      <c r="I130" s="7"/>
+      <c r="J130" s="3"/>
+      <c r="K130" s="6"/>
+      <c r="L130" s="3"/>
+      <c r="M130" s="3"/>
+      <c r="N130" s="3"/>
+      <c r="O130" s="3"/>
+      <c r="P130" s="3"/>
+      <c r="Q130" s="7"/>
+      <c r="R130" s="7"/>
+      <c r="S130" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="T130" s="7"/>
+      <c r="U130" s="7"/>
+    </row>
+    <row r="131" spans="1:21" ht="15">
+      <c r="A131" s="7">
+        <v>152</v>
+      </c>
+      <c r="B131" s="2">
+        <v>46265.740266203698</v>
+      </c>
+      <c r="C131" s="2">
+        <v>46265.741481481498</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H131" s="3"/>
+      <c r="I131" s="7"/>
+      <c r="J131" s="3"/>
+      <c r="K131" s="6"/>
+      <c r="L131" s="3"/>
+      <c r="M131" s="3"/>
+      <c r="N131" s="3"/>
+      <c r="O131" s="3"/>
+      <c r="P131" s="3"/>
+      <c r="Q131" s="7"/>
+      <c r="R131" s="7"/>
+      <c r="S131" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="T131" s="7"/>
+      <c r="U131" s="7"/>
+    </row>
+    <row r="132" spans="1:21" ht="15">
+      <c r="A132" s="7">
+        <v>153</v>
+      </c>
+      <c r="B132" s="2">
+        <v>46265.764467592599</v>
+      </c>
+      <c r="C132" s="2">
+        <v>46265.765520833302</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H132" s="3"/>
+      <c r="I132" s="7"/>
+      <c r="J132" s="3"/>
+      <c r="K132" s="6"/>
+      <c r="L132" s="3"/>
+      <c r="M132" s="3"/>
+      <c r="N132" s="3"/>
+      <c r="O132" s="3"/>
+      <c r="P132" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q132" s="7"/>
+      <c r="R132" s="7"/>
+      <c r="S132" s="7"/>
+      <c r="T132" s="7"/>
+      <c r="U132" s="7"/>
+    </row>
+    <row r="133" spans="1:21" ht="15">
+      <c r="A133" s="7">
+        <v>154</v>
+      </c>
+      <c r="B133" s="2">
+        <v>46265.769930555602</v>
+      </c>
+      <c r="C133" s="2">
+        <v>46265.770474536999</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H133" s="3"/>
+      <c r="I133" s="7"/>
+      <c r="J133" s="3"/>
+      <c r="K133" s="6"/>
+      <c r="L133" s="3"/>
+      <c r="M133" s="3"/>
+      <c r="N133" s="3"/>
+      <c r="O133" s="3"/>
+      <c r="P133" s="3"/>
+      <c r="Q133" s="7"/>
+      <c r="R133" s="7"/>
+      <c r="S133" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="T133" s="7"/>
+      <c r="U133" s="7"/>
+    </row>
+    <row r="134" spans="1:21" ht="15">
+      <c r="A134" s="7">
+        <v>155</v>
+      </c>
+      <c r="B134" s="2">
+        <v>46265.710706018501</v>
+      </c>
+      <c r="C134" s="2">
+        <v>46265.7804398148</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H134" s="3"/>
+      <c r="I134" s="7"/>
+      <c r="J134" s="3"/>
+      <c r="K134" s="6"/>
+      <c r="L134" s="3"/>
+      <c r="M134" s="3"/>
+      <c r="N134" s="3"/>
+      <c r="O134" s="3"/>
+      <c r="P134" s="3"/>
+      <c r="Q134" s="7"/>
+      <c r="R134" s="7"/>
+      <c r="S134" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="T134" s="7"/>
+      <c r="U134" s="7"/>
+    </row>
+    <row r="135" spans="1:21" ht="15">
+      <c r="A135" s="7">
+        <v>156</v>
+      </c>
+      <c r="B135" s="2">
+        <v>46265.796446759297</v>
+      </c>
+      <c r="C135" s="2">
+        <v>46265.797025462998</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H135" s="3"/>
+      <c r="I135" s="7"/>
+      <c r="J135" s="3"/>
+      <c r="K135" s="6"/>
+      <c r="L135" s="3"/>
+      <c r="M135" s="3"/>
+      <c r="N135" s="3"/>
+      <c r="O135" s="3"/>
+      <c r="P135" s="3"/>
+      <c r="Q135" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R135" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="S135" s="7"/>
+      <c r="T135" s="7"/>
+      <c r="U135" s="7"/>
+    </row>
+    <row r="136" spans="1:21" ht="15">
+      <c r="A136" s="7">
+        <v>157</v>
+      </c>
+      <c r="B136" s="2">
+        <v>46265.797164351898</v>
+      </c>
+      <c r="C136" s="2">
+        <v>46265.797500000001</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H136" s="3"/>
+      <c r="I136" s="7"/>
+      <c r="J136" s="3"/>
+      <c r="K136" s="6"/>
+      <c r="L136" s="3"/>
+      <c r="M136" s="3"/>
+      <c r="N136" s="3"/>
+      <c r="O136" s="3"/>
+      <c r="P136" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q136" s="7"/>
+      <c r="R136" s="7"/>
+      <c r="S136" s="7"/>
+      <c r="T136" s="7"/>
+      <c r="U136" s="7"/>
+    </row>
+    <row r="137" spans="1:21" ht="15">
+      <c r="A137" s="7">
+        <v>158</v>
+      </c>
+      <c r="B137" s="2">
+        <v>46265.721400463</v>
+      </c>
+      <c r="C137" s="2">
+        <v>46265.824525463002</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H137" s="3"/>
+      <c r="I137" s="7"/>
+      <c r="J137" s="3"/>
+      <c r="K137" s="6"/>
+      <c r="L137" s="3"/>
+      <c r="M137" s="3"/>
+      <c r="N137" s="3"/>
+      <c r="O137" s="3"/>
+      <c r="P137" s="3"/>
+      <c r="Q137" s="7"/>
+      <c r="R137" s="7"/>
+      <c r="S137" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="T137" s="7"/>
+      <c r="U137" s="7"/>
+    </row>
+    <row r="138" spans="1:21" ht="15">
+      <c r="A138" s="7">
+        <v>159</v>
+      </c>
+      <c r="B138" s="2">
+        <v>46265.8371527778</v>
+      </c>
+      <c r="C138" s="2">
+        <v>46265.837650463</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H138" s="3"/>
+      <c r="I138" s="7"/>
+      <c r="J138" s="3"/>
+      <c r="K138" s="6"/>
+      <c r="L138" s="3"/>
+      <c r="M138" s="3"/>
+      <c r="N138" s="3"/>
+      <c r="O138" s="3"/>
+      <c r="P138" s="3"/>
+      <c r="Q138" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R138" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="S138" s="7"/>
+      <c r="T138" s="7"/>
+      <c r="U138" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22CA0463-1288-484D-B526-363ECC1C1A14}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA31799E-2B65-45A0-8D55-8382E6F73BCC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="401">
   <si>
     <t>Id</t>
   </si>
@@ -1152,6 +1152,93 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/20260831_200509_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/WhatsApp%20Image%202026-08-31%20at%209.06.29%20PM_Enrique%20Cesar%20Flores.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Parque%20Tep.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG-20260831-WA0210_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG-20260831-WA0315_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/1788242797354386927621937644928_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/17882708459818066679798728223287_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882773868982178287074442690652_Starbucks%20Luna%20Park.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882774717123075601308672399951_Starbucks%20Encuentro.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Vanessa%20Carre%C3%B1o%20Rios.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/95EF8D44-DE07-41F0-8A29-66A4D3DD7D03_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>berenice.sanchez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Berenice Ivon Sanchez Lopez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Berenice%20Ivon%20Sanche.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/373901AF-36F9-458C-934C-4D6BF248C85C_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882776771466347530649565081323_Starbucks%20Mundo%20E.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17A71B1E-4BD6-44CF-9B84-B81E5E8E3B2B_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/8B8C3A3E-C1E8-4EF7-AB51-33B4DDBB9220_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/d8ee69ba-87ef-4d1f-bef1-811b4f2c8eca_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/91966053-5DA9-444C-8997-7CBB124B20AE_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/0FA97F77-EE63-46D1-9BC2-D64E4CD8E2F6_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG_1141_Starbucks%20Atizapan.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/ACA9CDFD-10DA-49AF-BD04-77E865112E3B_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/68EB9EF7-B3D9-49AE-93B5-C73400F74CE9_Vanessa%20Carre%C3%B1o%20Rios.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882783697874848171061432187232_Starbucks%20Boulevard.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/373901AF-36F9-458C-934C-4D6BF248C85C_Vanessa%20Carre%C3%B1o%20Rios%201.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/8B8C3A3E-C1E8-4EF7-AB51-33B4DDBB9220_Vanessa%20Carre%C3%B1o%20Rios%201.jpeg</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Daniel%20Bustos%20Martin.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG-20260901-WA0002_Starbucks%20Parque%20Tep.jpg</t>
   </si>
 </sst>
 </file>
@@ -1286,8 +1373,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U138" totalsRowShown="0">
-  <autoFilter ref="A1:U138" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U165" totalsRowShown="0">
+  <autoFilter ref="A1:U165" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1440,7 +1527,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="159" latestEventMarker="394">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="186" latestEventMarker="421">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1765,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U138"/>
+  <dimension ref="A1:U165"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -6125,7 +6212,7 @@
       </c>
     </row>
     <row r="129" spans="1:21" ht="15">
-      <c r="A129" s="7">
+      <c r="A129">
         <v>150</v>
       </c>
       <c r="B129" s="2">
@@ -6147,7 +6234,6 @@
         <v>46</v>
       </c>
       <c r="H129" s="3"/>
-      <c r="I129" s="7"/>
       <c r="J129" s="3"/>
       <c r="K129" s="6"/>
       <c r="L129" s="3"/>
@@ -6155,16 +6241,12 @@
       <c r="N129" s="3"/>
       <c r="O129" s="3"/>
       <c r="P129" s="3"/>
-      <c r="Q129" s="7"/>
-      <c r="R129" s="7"/>
-      <c r="S129" s="7" t="s">
+      <c r="S129" t="s">
         <v>348</v>
       </c>
-      <c r="T129" s="7"/>
-      <c r="U129" s="7"/>
     </row>
     <row r="130" spans="1:21" ht="15">
-      <c r="A130" s="7">
+      <c r="A130">
         <v>151</v>
       </c>
       <c r="B130" s="2">
@@ -6186,7 +6268,6 @@
         <v>46</v>
       </c>
       <c r="H130" s="3"/>
-      <c r="I130" s="7"/>
       <c r="J130" s="3"/>
       <c r="K130" s="6"/>
       <c r="L130" s="3"/>
@@ -6194,16 +6275,12 @@
       <c r="N130" s="3"/>
       <c r="O130" s="3"/>
       <c r="P130" s="3"/>
-      <c r="Q130" s="7"/>
-      <c r="R130" s="7"/>
-      <c r="S130" s="7" t="s">
+      <c r="S130" t="s">
         <v>352</v>
       </c>
-      <c r="T130" s="7"/>
-      <c r="U130" s="7"/>
     </row>
     <row r="131" spans="1:21" ht="15">
-      <c r="A131" s="7">
+      <c r="A131">
         <v>152</v>
       </c>
       <c r="B131" s="2">
@@ -6225,7 +6302,6 @@
         <v>46</v>
       </c>
       <c r="H131" s="3"/>
-      <c r="I131" s="7"/>
       <c r="J131" s="3"/>
       <c r="K131" s="6"/>
       <c r="L131" s="3"/>
@@ -6233,16 +6309,12 @@
       <c r="N131" s="3"/>
       <c r="O131" s="3"/>
       <c r="P131" s="3"/>
-      <c r="Q131" s="7"/>
-      <c r="R131" s="7"/>
-      <c r="S131" s="7" t="s">
+      <c r="S131" t="s">
         <v>356</v>
       </c>
-      <c r="T131" s="7"/>
-      <c r="U131" s="7"/>
     </row>
     <row r="132" spans="1:21" ht="15">
-      <c r="A132" s="7">
+      <c r="A132">
         <v>153</v>
       </c>
       <c r="B132" s="2">
@@ -6264,24 +6336,18 @@
         <v>41</v>
       </c>
       <c r="H132" s="3"/>
-      <c r="I132" s="7"/>
       <c r="J132" s="3"/>
       <c r="K132" s="6"/>
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
       <c r="O132" s="3"/>
-      <c r="P132" s="3" t="s">
+      <c r="P132" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="Q132" s="7"/>
-      <c r="R132" s="7"/>
-      <c r="S132" s="7"/>
-      <c r="T132" s="7"/>
-      <c r="U132" s="7"/>
     </row>
     <row r="133" spans="1:21" ht="15">
-      <c r="A133" s="7">
+      <c r="A133">
         <v>154</v>
       </c>
       <c r="B133" s="2">
@@ -6303,7 +6369,6 @@
         <v>46</v>
       </c>
       <c r="H133" s="3"/>
-      <c r="I133" s="7"/>
       <c r="J133" s="3"/>
       <c r="K133" s="6"/>
       <c r="L133" s="3"/>
@@ -6311,16 +6376,12 @@
       <c r="N133" s="3"/>
       <c r="O133" s="3"/>
       <c r="P133" s="3"/>
-      <c r="Q133" s="7"/>
-      <c r="R133" s="7"/>
-      <c r="S133" s="7" t="s">
+      <c r="S133" t="s">
         <v>361</v>
       </c>
-      <c r="T133" s="7"/>
-      <c r="U133" s="7"/>
     </row>
     <row r="134" spans="1:21" ht="15">
-      <c r="A134" s="7">
+      <c r="A134">
         <v>155</v>
       </c>
       <c r="B134" s="2">
@@ -6342,7 +6403,6 @@
         <v>46</v>
       </c>
       <c r="H134" s="3"/>
-      <c r="I134" s="7"/>
       <c r="J134" s="3"/>
       <c r="K134" s="6"/>
       <c r="L134" s="3"/>
@@ -6350,16 +6410,12 @@
       <c r="N134" s="3"/>
       <c r="O134" s="3"/>
       <c r="P134" s="3"/>
-      <c r="Q134" s="7"/>
-      <c r="R134" s="7"/>
-      <c r="S134" s="7" t="s">
+      <c r="S134" t="s">
         <v>365</v>
       </c>
-      <c r="T134" s="7"/>
-      <c r="U134" s="7"/>
     </row>
     <row r="135" spans="1:21" ht="15">
-      <c r="A135" s="7">
+      <c r="A135">
         <v>156</v>
       </c>
       <c r="B135" s="2">
@@ -6381,7 +6437,6 @@
         <v>106</v>
       </c>
       <c r="H135" s="3"/>
-      <c r="I135" s="7"/>
       <c r="J135" s="3"/>
       <c r="K135" s="6"/>
       <c r="L135" s="3"/>
@@ -6389,18 +6444,15 @@
       <c r="N135" s="3"/>
       <c r="O135" s="3"/>
       <c r="P135" s="3"/>
-      <c r="Q135" s="7" t="s">
+      <c r="Q135" t="s">
         <v>61</v>
       </c>
-      <c r="R135" s="7" t="s">
+      <c r="R135" t="s">
         <v>366</v>
       </c>
-      <c r="S135" s="7"/>
-      <c r="T135" s="7"/>
-      <c r="U135" s="7"/>
     </row>
     <row r="136" spans="1:21" ht="15">
-      <c r="A136" s="7">
+      <c r="A136">
         <v>157</v>
       </c>
       <c r="B136" s="2">
@@ -6422,24 +6474,18 @@
         <v>41</v>
       </c>
       <c r="H136" s="3"/>
-      <c r="I136" s="7"/>
       <c r="J136" s="3"/>
       <c r="K136" s="6"/>
       <c r="L136" s="3"/>
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
       <c r="O136" s="3"/>
-      <c r="P136" s="3" t="s">
+      <c r="P136" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="Q136" s="7"/>
-      <c r="R136" s="7"/>
-      <c r="S136" s="7"/>
-      <c r="T136" s="7"/>
-      <c r="U136" s="7"/>
     </row>
     <row r="137" spans="1:21" ht="15">
-      <c r="A137" s="7">
+      <c r="A137">
         <v>158</v>
       </c>
       <c r="B137" s="2">
@@ -6461,7 +6507,6 @@
         <v>46</v>
       </c>
       <c r="H137" s="3"/>
-      <c r="I137" s="7"/>
       <c r="J137" s="3"/>
       <c r="K137" s="6"/>
       <c r="L137" s="3"/>
@@ -6469,16 +6514,12 @@
       <c r="N137" s="3"/>
       <c r="O137" s="3"/>
       <c r="P137" s="3"/>
-      <c r="Q137" s="7"/>
-      <c r="R137" s="7"/>
-      <c r="S137" s="7" t="s">
+      <c r="S137" t="s">
         <v>370</v>
       </c>
-      <c r="T137" s="7"/>
-      <c r="U137" s="7"/>
     </row>
     <row r="138" spans="1:21" ht="15">
-      <c r="A138" s="7">
+      <c r="A138">
         <v>159</v>
       </c>
       <c r="B138" s="2">
@@ -6500,7 +6541,6 @@
         <v>106</v>
       </c>
       <c r="H138" s="3"/>
-      <c r="I138" s="7"/>
       <c r="J138" s="3"/>
       <c r="K138" s="6"/>
       <c r="L138" s="3"/>
@@ -6508,26 +6548,1115 @@
       <c r="N138" s="3"/>
       <c r="O138" s="3"/>
       <c r="P138" s="3"/>
-      <c r="Q138" s="7" t="s">
+      <c r="Q138" t="s">
         <v>61</v>
       </c>
-      <c r="R138" s="7" t="s">
+      <c r="R138" t="s">
         <v>371</v>
       </c>
-      <c r="S138" s="7"/>
-      <c r="T138" s="7"/>
-      <c r="U138" s="7"/>
+    </row>
+    <row r="139" spans="1:21" ht="15">
+      <c r="A139">
+        <v>160</v>
+      </c>
+      <c r="B139" s="2">
+        <v>46265.879895833299</v>
+      </c>
+      <c r="C139" s="2">
+        <v>46265.8801157407</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H139" s="3"/>
+      <c r="I139" t="s">
+        <v>61</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="K139" s="6"/>
+      <c r="L139" s="3"/>
+      <c r="M139" s="3"/>
+      <c r="N139" s="3"/>
+      <c r="O139" s="3"/>
+      <c r="P139" s="3"/>
+    </row>
+    <row r="140" spans="1:21" ht="15">
+      <c r="A140">
+        <v>161</v>
+      </c>
+      <c r="B140" s="2">
+        <v>46265.9140625</v>
+      </c>
+      <c r="C140" s="2">
+        <v>46265.915405092601</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H140" s="3"/>
+      <c r="J140" s="3"/>
+      <c r="K140" s="6"/>
+      <c r="L140" s="3"/>
+      <c r="M140" s="3"/>
+      <c r="N140" s="3"/>
+      <c r="O140" s="3"/>
+      <c r="P140" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" ht="15">
+      <c r="A141" s="7">
+        <v>162</v>
+      </c>
+      <c r="B141" s="2">
+        <v>46265.993541666699</v>
+      </c>
+      <c r="C141" s="2">
+        <v>46265.9941203704</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H141" s="3"/>
+      <c r="I141" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="K141" s="6"/>
+      <c r="L141" s="3"/>
+      <c r="M141" s="3"/>
+      <c r="N141" s="3"/>
+      <c r="O141" s="3"/>
+      <c r="P141" s="3"/>
+      <c r="Q141" s="7"/>
+      <c r="R141" s="7"/>
+      <c r="S141" s="7"/>
+      <c r="T141" s="7"/>
+      <c r="U141" s="7"/>
+    </row>
+    <row r="142" spans="1:21" ht="15">
+      <c r="A142" s="7">
+        <v>163</v>
+      </c>
+      <c r="B142" s="2">
+        <v>46265.994155092601</v>
+      </c>
+      <c r="C142" s="2">
+        <v>46265.994548611103</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H142" s="3"/>
+      <c r="I142" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J142" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="K142" s="6"/>
+      <c r="L142" s="3"/>
+      <c r="M142" s="3"/>
+      <c r="N142" s="3"/>
+      <c r="O142" s="3"/>
+      <c r="P142" s="3"/>
+      <c r="Q142" s="7"/>
+      <c r="R142" s="7"/>
+      <c r="S142" s="7"/>
+      <c r="T142" s="7"/>
+      <c r="U142" s="7"/>
+    </row>
+    <row r="143" spans="1:21" ht="15">
+      <c r="A143" s="7">
+        <v>164</v>
+      </c>
+      <c r="B143" s="2">
+        <v>46266.002673611103</v>
+      </c>
+      <c r="C143" s="2">
+        <v>46266.004872685196</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H143" s="3"/>
+      <c r="I143" s="7"/>
+      <c r="J143" s="3"/>
+      <c r="K143" s="6"/>
+      <c r="L143" s="3"/>
+      <c r="M143" s="3"/>
+      <c r="N143" s="3"/>
+      <c r="O143" s="3"/>
+      <c r="P143" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q143" s="7"/>
+      <c r="R143" s="7"/>
+      <c r="S143" s="7"/>
+      <c r="T143" s="7"/>
+      <c r="U143" s="7"/>
+    </row>
+    <row r="144" spans="1:21" ht="15">
+      <c r="A144" s="7">
+        <v>165</v>
+      </c>
+      <c r="B144" s="2">
+        <v>46266.328784722202</v>
+      </c>
+      <c r="C144" s="2">
+        <v>46266.329409722202</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H144" s="3"/>
+      <c r="I144" s="7"/>
+      <c r="J144" s="3"/>
+      <c r="K144" s="6"/>
+      <c r="L144" s="3"/>
+      <c r="M144" s="3"/>
+      <c r="N144" s="3"/>
+      <c r="O144" s="3"/>
+      <c r="P144" s="3"/>
+      <c r="Q144" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R144" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="S144" s="7"/>
+      <c r="T144" s="7"/>
+      <c r="U144" s="7"/>
+    </row>
+    <row r="145" spans="1:21" ht="15">
+      <c r="A145" s="7">
+        <v>166</v>
+      </c>
+      <c r="B145" s="2">
+        <v>46266.404456018499</v>
+      </c>
+      <c r="C145" s="2">
+        <v>46266.405613425901</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H145" s="3"/>
+      <c r="I145" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="K145" s="6"/>
+      <c r="L145" s="3"/>
+      <c r="M145" s="3"/>
+      <c r="N145" s="3"/>
+      <c r="O145" s="3"/>
+      <c r="P145" s="3"/>
+      <c r="Q145" s="7"/>
+      <c r="R145" s="7"/>
+      <c r="S145" s="7"/>
+      <c r="T145" s="7"/>
+      <c r="U145" s="7"/>
+    </row>
+    <row r="146" spans="1:21" ht="15">
+      <c r="A146" s="7">
+        <v>167</v>
+      </c>
+      <c r="B146" s="2">
+        <v>46266.405659722201</v>
+      </c>
+      <c r="C146" s="2">
+        <v>46266.4061574074</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H146" s="3"/>
+      <c r="I146" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="K146" s="6"/>
+      <c r="L146" s="3"/>
+      <c r="M146" s="3"/>
+      <c r="N146" s="3"/>
+      <c r="O146" s="3"/>
+      <c r="P146" s="3"/>
+      <c r="Q146" s="7"/>
+      <c r="R146" s="7"/>
+      <c r="S146" s="7"/>
+      <c r="T146" s="7"/>
+      <c r="U146" s="7"/>
+    </row>
+    <row r="147" spans="1:21" ht="15">
+      <c r="A147" s="7">
+        <v>168</v>
+      </c>
+      <c r="B147" s="2">
+        <v>46266.406284722201</v>
+      </c>
+      <c r="C147" s="2">
+        <v>46266.407037037003</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H147" s="3"/>
+      <c r="I147" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="K147" s="6"/>
+      <c r="L147" s="3"/>
+      <c r="M147" s="3"/>
+      <c r="N147" s="3"/>
+      <c r="O147" s="3"/>
+      <c r="P147" s="3"/>
+      <c r="Q147" s="7"/>
+      <c r="R147" s="7"/>
+      <c r="S147" s="7"/>
+      <c r="T147" s="7"/>
+      <c r="U147" s="7"/>
+    </row>
+    <row r="148" spans="1:21" ht="15">
+      <c r="A148" s="7">
+        <v>169</v>
+      </c>
+      <c r="B148" s="2">
+        <v>46266.4071527778</v>
+      </c>
+      <c r="C148" s="2">
+        <v>46266.407962963</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H148" s="3"/>
+      <c r="I148" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J148" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="K148" s="6"/>
+      <c r="L148" s="3"/>
+      <c r="M148" s="3"/>
+      <c r="N148" s="3"/>
+      <c r="O148" s="3"/>
+      <c r="P148" s="3"/>
+      <c r="Q148" s="7"/>
+      <c r="R148" s="7"/>
+      <c r="S148" s="7"/>
+      <c r="T148" s="7"/>
+      <c r="U148" s="7"/>
+    </row>
+    <row r="149" spans="1:21" ht="15">
+      <c r="A149" s="7">
+        <v>170</v>
+      </c>
+      <c r="B149" s="2">
+        <v>46266.407673611102</v>
+      </c>
+      <c r="C149" s="2">
+        <v>46266.408287036997</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H149" s="3"/>
+      <c r="I149" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J149" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="K149" s="6"/>
+      <c r="L149" s="3"/>
+      <c r="M149" s="3"/>
+      <c r="N149" s="3"/>
+      <c r="O149" s="3"/>
+      <c r="P149" s="3"/>
+      <c r="Q149" s="7"/>
+      <c r="R149" s="7"/>
+      <c r="S149" s="7"/>
+      <c r="T149" s="7"/>
+      <c r="U149" s="7"/>
+    </row>
+    <row r="150" spans="1:21" ht="15">
+      <c r="A150" s="7">
+        <v>171</v>
+      </c>
+      <c r="B150" s="2">
+        <v>46266.408113425903</v>
+      </c>
+      <c r="C150" s="2">
+        <v>46266.408587963</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H150" s="3"/>
+      <c r="I150" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J150" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="K150" s="6"/>
+      <c r="L150" s="3"/>
+      <c r="M150" s="3"/>
+      <c r="N150" s="3"/>
+      <c r="O150" s="3"/>
+      <c r="P150" s="3"/>
+      <c r="Q150" s="7"/>
+      <c r="R150" s="7"/>
+      <c r="S150" s="7"/>
+      <c r="T150" s="7"/>
+      <c r="U150" s="7"/>
+    </row>
+    <row r="151" spans="1:21" ht="15">
+      <c r="A151" s="7">
+        <v>172</v>
+      </c>
+      <c r="B151" s="2">
+        <v>46266.407743055599</v>
+      </c>
+      <c r="C151" s="2">
+        <v>46266.408599536997</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H151" s="3"/>
+      <c r="I151" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J151" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="K151" s="6"/>
+      <c r="L151" s="3"/>
+      <c r="M151" s="3"/>
+      <c r="N151" s="3"/>
+      <c r="O151" s="3"/>
+      <c r="P151" s="3"/>
+      <c r="Q151" s="7"/>
+      <c r="R151" s="7"/>
+      <c r="S151" s="7"/>
+      <c r="T151" s="7"/>
+      <c r="U151" s="7"/>
+    </row>
+    <row r="152" spans="1:21" ht="15">
+      <c r="A152" s="7">
+        <v>173</v>
+      </c>
+      <c r="B152" s="2">
+        <v>46266.408703703702</v>
+      </c>
+      <c r="C152" s="2">
+        <v>46266.409247685202</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H152" s="3"/>
+      <c r="I152" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J152" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="K152" s="6"/>
+      <c r="L152" s="3"/>
+      <c r="M152" s="3"/>
+      <c r="N152" s="3"/>
+      <c r="O152" s="3"/>
+      <c r="P152" s="3"/>
+      <c r="Q152" s="7"/>
+      <c r="R152" s="7"/>
+      <c r="S152" s="7"/>
+      <c r="T152" s="7"/>
+      <c r="U152" s="7"/>
+    </row>
+    <row r="153" spans="1:21" ht="15">
+      <c r="A153" s="7">
+        <v>174</v>
+      </c>
+      <c r="B153" s="2">
+        <v>46266.409502314797</v>
+      </c>
+      <c r="C153" s="2">
+        <v>46266.410613425898</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H153" s="3"/>
+      <c r="I153" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J153" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="K153" s="6"/>
+      <c r="L153" s="3"/>
+      <c r="M153" s="3"/>
+      <c r="N153" s="3"/>
+      <c r="O153" s="3"/>
+      <c r="P153" s="3"/>
+      <c r="Q153" s="7"/>
+      <c r="R153" s="7"/>
+      <c r="S153" s="7"/>
+      <c r="T153" s="7"/>
+      <c r="U153" s="7"/>
+    </row>
+    <row r="154" spans="1:21" ht="15">
+      <c r="A154" s="7">
+        <v>175</v>
+      </c>
+      <c r="B154" s="2">
+        <v>46266.411180555602</v>
+      </c>
+      <c r="C154" s="2">
+        <v>46266.411643518499</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H154" s="3"/>
+      <c r="I154" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J154" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="K154" s="6"/>
+      <c r="L154" s="3"/>
+      <c r="M154" s="3"/>
+      <c r="N154" s="3"/>
+      <c r="O154" s="3"/>
+      <c r="P154" s="3"/>
+      <c r="Q154" s="7"/>
+      <c r="R154" s="7"/>
+      <c r="S154" s="7"/>
+      <c r="T154" s="7"/>
+      <c r="U154" s="7"/>
+    </row>
+    <row r="155" spans="1:21" ht="15">
+      <c r="A155" s="7">
+        <v>176</v>
+      </c>
+      <c r="B155" s="2">
+        <v>46266.4125347222</v>
+      </c>
+      <c r="C155" s="2">
+        <v>46266.4129861111</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H155" s="3"/>
+      <c r="I155" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="K155" s="6"/>
+      <c r="L155" s="3"/>
+      <c r="M155" s="3"/>
+      <c r="N155" s="3"/>
+      <c r="O155" s="3"/>
+      <c r="P155" s="3"/>
+      <c r="Q155" s="7"/>
+      <c r="R155" s="7"/>
+      <c r="S155" s="7"/>
+      <c r="T155" s="7"/>
+      <c r="U155" s="7"/>
+    </row>
+    <row r="156" spans="1:21" ht="15">
+      <c r="A156" s="7">
+        <v>177</v>
+      </c>
+      <c r="B156" s="2">
+        <v>46266.413101851896</v>
+      </c>
+      <c r="C156" s="2">
+        <v>46266.413958333302</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H156" s="3"/>
+      <c r="I156" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J156" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="K156" s="6"/>
+      <c r="L156" s="3"/>
+      <c r="M156" s="3"/>
+      <c r="N156" s="3"/>
+      <c r="O156" s="3"/>
+      <c r="P156" s="3"/>
+      <c r="Q156" s="7"/>
+      <c r="R156" s="7"/>
+      <c r="S156" s="7"/>
+      <c r="T156" s="7"/>
+      <c r="U156" s="7"/>
+    </row>
+    <row r="157" spans="1:21" ht="15">
+      <c r="A157" s="7">
+        <v>178</v>
+      </c>
+      <c r="B157" s="2">
+        <v>46266.413888888899</v>
+      </c>
+      <c r="C157" s="2">
+        <v>46266.414398148103</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H157" s="3"/>
+      <c r="I157" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J157" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="K157" s="6"/>
+      <c r="L157" s="3"/>
+      <c r="M157" s="3"/>
+      <c r="N157" s="3"/>
+      <c r="O157" s="3"/>
+      <c r="P157" s="3"/>
+      <c r="Q157" s="7"/>
+      <c r="R157" s="7"/>
+      <c r="S157" s="7"/>
+      <c r="T157" s="7"/>
+      <c r="U157" s="7"/>
+    </row>
+    <row r="158" spans="1:21" ht="15">
+      <c r="A158" s="7">
+        <v>179</v>
+      </c>
+      <c r="B158" s="2">
+        <v>46266.414050925901</v>
+      </c>
+      <c r="C158" s="2">
+        <v>46266.414756944403</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H158" s="3"/>
+      <c r="I158" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J158" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K158" s="6"/>
+      <c r="L158" s="3"/>
+      <c r="M158" s="3"/>
+      <c r="N158" s="3"/>
+      <c r="O158" s="3"/>
+      <c r="P158" s="3"/>
+      <c r="Q158" s="7"/>
+      <c r="R158" s="7"/>
+      <c r="S158" s="7"/>
+      <c r="T158" s="7"/>
+      <c r="U158" s="7"/>
+    </row>
+    <row r="159" spans="1:21" ht="15">
+      <c r="A159" s="7">
+        <v>180</v>
+      </c>
+      <c r="B159" s="2">
+        <v>46266.415081018502</v>
+      </c>
+      <c r="C159" s="2">
+        <v>46266.4156828704</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H159" s="3"/>
+      <c r="I159" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J159" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="K159" s="6"/>
+      <c r="L159" s="3"/>
+      <c r="M159" s="3"/>
+      <c r="N159" s="3"/>
+      <c r="O159" s="3"/>
+      <c r="P159" s="3"/>
+      <c r="Q159" s="7"/>
+      <c r="R159" s="7"/>
+      <c r="S159" s="7"/>
+      <c r="T159" s="7"/>
+      <c r="U159" s="7"/>
+    </row>
+    <row r="160" spans="1:21" ht="15">
+      <c r="A160" s="7">
+        <v>181</v>
+      </c>
+      <c r="B160" s="2">
+        <v>46266.415740740696</v>
+      </c>
+      <c r="C160" s="2">
+        <v>46266.416608796302</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H160" s="3"/>
+      <c r="I160" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J160" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="K160" s="6"/>
+      <c r="L160" s="3"/>
+      <c r="M160" s="3"/>
+      <c r="N160" s="3"/>
+      <c r="O160" s="3"/>
+      <c r="P160" s="3"/>
+      <c r="Q160" s="7"/>
+      <c r="R160" s="7"/>
+      <c r="S160" s="7"/>
+      <c r="T160" s="7"/>
+      <c r="U160" s="7"/>
+    </row>
+    <row r="161" spans="1:21" ht="15">
+      <c r="A161" s="7">
+        <v>182</v>
+      </c>
+      <c r="B161" s="2">
+        <v>46266.415763888901</v>
+      </c>
+      <c r="C161" s="2">
+        <v>46266.416689814803</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H161" s="3"/>
+      <c r="I161" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J161" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="K161" s="6"/>
+      <c r="L161" s="3"/>
+      <c r="M161" s="3"/>
+      <c r="N161" s="3"/>
+      <c r="O161" s="3"/>
+      <c r="P161" s="3"/>
+      <c r="Q161" s="7"/>
+      <c r="R161" s="7"/>
+      <c r="S161" s="7"/>
+      <c r="T161" s="7"/>
+      <c r="U161" s="7"/>
+    </row>
+    <row r="162" spans="1:21" ht="15">
+      <c r="A162" s="7">
+        <v>183</v>
+      </c>
+      <c r="B162" s="2">
+        <v>46266.416828703703</v>
+      </c>
+      <c r="C162" s="2">
+        <v>46266.417407407404</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H162" s="3"/>
+      <c r="I162" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J162" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="K162" s="6"/>
+      <c r="L162" s="3"/>
+      <c r="M162" s="3"/>
+      <c r="N162" s="3"/>
+      <c r="O162" s="3"/>
+      <c r="P162" s="3"/>
+      <c r="Q162" s="7"/>
+      <c r="R162" s="7"/>
+      <c r="S162" s="7"/>
+      <c r="T162" s="7"/>
+      <c r="U162" s="7"/>
+    </row>
+    <row r="163" spans="1:21" ht="15">
+      <c r="A163" s="7">
+        <v>184</v>
+      </c>
+      <c r="B163" s="2">
+        <v>46266.417557870402</v>
+      </c>
+      <c r="C163" s="2">
+        <v>46266.417743055601</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H163" s="3"/>
+      <c r="I163" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="J163" s="3"/>
+      <c r="K163" s="6"/>
+      <c r="L163" s="3"/>
+      <c r="M163" s="3"/>
+      <c r="N163" s="3"/>
+      <c r="O163" s="3"/>
+      <c r="P163" s="3"/>
+      <c r="Q163" s="7"/>
+      <c r="R163" s="7"/>
+      <c r="S163" s="7"/>
+      <c r="T163" s="7"/>
+      <c r="U163" s="7"/>
+    </row>
+    <row r="164" spans="1:21" ht="15">
+      <c r="A164" s="7">
+        <v>185</v>
+      </c>
+      <c r="B164" s="2">
+        <v>46266.419571759303</v>
+      </c>
+      <c r="C164" s="2">
+        <v>46266.420162037</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H164" s="3"/>
+      <c r="I164" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J164" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="K164" s="6"/>
+      <c r="L164" s="3"/>
+      <c r="M164" s="3"/>
+      <c r="N164" s="3"/>
+      <c r="O164" s="3"/>
+      <c r="P164" s="3"/>
+      <c r="Q164" s="7"/>
+      <c r="R164" s="7"/>
+      <c r="S164" s="7"/>
+      <c r="T164" s="7"/>
+      <c r="U164" s="7"/>
+    </row>
+    <row r="165" spans="1:21" ht="15">
+      <c r="A165" s="7">
+        <v>186</v>
+      </c>
+      <c r="B165" s="2">
+        <v>46266.4198958333</v>
+      </c>
+      <c r="C165" s="2">
+        <v>46266.420196759304</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H165" s="3"/>
+      <c r="I165" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="K165" s="6"/>
+      <c r="L165" s="3"/>
+      <c r="M165" s="3"/>
+      <c r="N165" s="3"/>
+      <c r="O165" s="3"/>
+      <c r="P165" s="3"/>
+      <c r="Q165" s="7"/>
+      <c r="R165" s="7"/>
+      <c r="S165" s="7"/>
+      <c r="T165" s="7"/>
+      <c r="U165" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>
     <hyperlink ref="K50" r:id="rId2" xr:uid="{C4821E21-FAA0-46D2-B8E3-D3BB8AD6B775}"/>
     <hyperlink ref="H82" r:id="rId3" xr:uid="{766FA421-DC55-43DC-BB00-3D4CF619CA37}"/>
+    <hyperlink ref="P136" r:id="rId4" xr:uid="{1BA36E7B-9450-4CD1-9379-C168FD19A9E8}"/>
+    <hyperlink ref="P132" r:id="rId5" xr:uid="{6BE0C189-008F-4C0A-B789-924C4EC76AA2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="319" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA31799E-2B65-45A0-8D55-8382E6F73BCC}"/>
+  <xr:revisionPtr revIDLastSave="322" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2471BD2C-7F70-437A-AF5D-2A010F93F850}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="430">
   <si>
     <t>Id</t>
   </si>
@@ -1239,6 +1239,93 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG-20260901-WA0002_Starbucks%20Parque%20Tep.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882799027096190624538676631300_Starbucks%20Bellavista.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Arboledas.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Cristian%20Alexis%20Posa.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38661@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Jinetes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882810514496896218310335395746_Starbucks%20Jinetes.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Galerias%20P.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Sor%20Juana.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG_2819_Starbucks%20Tlalnepant.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Hector%20Ruben%20Estevez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Santa%20Moni.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG-20260901-WA0016_Starbucks%20Plaza%20Tepe.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG-20260901-WA0016_Starbucks%20Plaza%20Tepe%201.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38431@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Eduardo Molina</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/1788282934704343433703110682576_Starbucks%20Eduardo%20Mo.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38924@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza aeropuerto</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882847004754201235200003934342_Starbucks%20Plaza%20aero.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Punta%20Nort.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20CC%20Lomas%20V.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882866205521275562548286061682_Carlos%20Cortes%20Aguila.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Eduardo%20David%20Reyes.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Star%20Medic.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38529@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Bosques de Aragón</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882897149035280869101751805964_Starbucks%20Bosques%20de.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/70F44357-D5E6-41DD-8E07-39CFF43C1C64_Maria%20Fernanda%20Reyes.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG-20260901-WA0000_Starbucks%20San%20Miguel.jpg</t>
   </si>
 </sst>
 </file>
@@ -1373,8 +1460,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U165" totalsRowShown="0">
-  <autoFilter ref="A1:U165" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U186" totalsRowShown="0">
+  <autoFilter ref="A1:U186" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1527,7 +1614,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="186" latestEventMarker="421">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="207" latestEventMarker="442">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1852,7 +1939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U165"/>
+  <dimension ref="A1:U186"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -6211,7 +6298,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="15">
+    <row r="129" spans="1:19" ht="15">
       <c r="A129">
         <v>150</v>
       </c>
@@ -6245,7 +6332,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="15">
+    <row r="130" spans="1:19" ht="15">
       <c r="A130">
         <v>151</v>
       </c>
@@ -6279,7 +6366,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="15">
+    <row r="131" spans="1:19" ht="15">
       <c r="A131">
         <v>152</v>
       </c>
@@ -6313,7 +6400,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="15">
+    <row r="132" spans="1:19" ht="15">
       <c r="A132">
         <v>153</v>
       </c>
@@ -6346,7 +6433,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="133" spans="1:21" ht="15">
+    <row r="133" spans="1:19" ht="15">
       <c r="A133">
         <v>154</v>
       </c>
@@ -6380,7 +6467,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="15">
+    <row r="134" spans="1:19" ht="15">
       <c r="A134">
         <v>155</v>
       </c>
@@ -6414,7 +6501,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="135" spans="1:21" ht="15">
+    <row r="135" spans="1:19" ht="15">
       <c r="A135">
         <v>156</v>
       </c>
@@ -6451,7 +6538,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="15">
+    <row r="136" spans="1:19" ht="15">
       <c r="A136">
         <v>157</v>
       </c>
@@ -6484,7 +6571,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="15">
+    <row r="137" spans="1:19" ht="15">
       <c r="A137">
         <v>158</v>
       </c>
@@ -6518,7 +6605,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="138" spans="1:21" ht="15">
+    <row r="138" spans="1:19" ht="15">
       <c r="A138">
         <v>159</v>
       </c>
@@ -6555,7 +6642,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="139" spans="1:21" ht="15">
+    <row r="139" spans="1:19" ht="15">
       <c r="A139">
         <v>160</v>
       </c>
@@ -6591,7 +6678,7 @@
       <c r="O139" s="3"/>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="1:21" ht="15">
+    <row r="140" spans="1:19" ht="15">
       <c r="A140">
         <v>161</v>
       </c>
@@ -6624,8 +6711,8 @@
         <v>373</v>
       </c>
     </row>
-    <row r="141" spans="1:21" ht="15">
-      <c r="A141" s="7">
+    <row r="141" spans="1:19" ht="15">
+      <c r="A141">
         <v>162</v>
       </c>
       <c r="B141" s="2">
@@ -6647,7 +6734,7 @@
         <v>60</v>
       </c>
       <c r="H141" s="3"/>
-      <c r="I141" s="7" t="s">
+      <c r="I141" t="s">
         <v>61</v>
       </c>
       <c r="J141" s="3" t="s">
@@ -6659,14 +6746,9 @@
       <c r="N141" s="3"/>
       <c r="O141" s="3"/>
       <c r="P141" s="3"/>
-      <c r="Q141" s="7"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="7"/>
-      <c r="T141" s="7"/>
-      <c r="U141" s="7"/>
-    </row>
-    <row r="142" spans="1:21" ht="15">
-      <c r="A142" s="7">
+    </row>
+    <row r="142" spans="1:19" ht="15">
+      <c r="A142">
         <v>163</v>
       </c>
       <c r="B142" s="2">
@@ -6688,7 +6770,7 @@
         <v>60</v>
       </c>
       <c r="H142" s="3"/>
-      <c r="I142" s="7" t="s">
+      <c r="I142" t="s">
         <v>61</v>
       </c>
       <c r="J142" s="3" t="s">
@@ -6700,14 +6782,9 @@
       <c r="N142" s="3"/>
       <c r="O142" s="3"/>
       <c r="P142" s="3"/>
-      <c r="Q142" s="7"/>
-      <c r="R142" s="7"/>
-      <c r="S142" s="7"/>
-      <c r="T142" s="7"/>
-      <c r="U142" s="7"/>
-    </row>
-    <row r="143" spans="1:21" ht="15">
-      <c r="A143" s="7">
+    </row>
+    <row r="143" spans="1:19" ht="15">
+      <c r="A143">
         <v>164</v>
       </c>
       <c r="B143" s="2">
@@ -6729,7 +6806,6 @@
         <v>41</v>
       </c>
       <c r="H143" s="3"/>
-      <c r="I143" s="7"/>
       <c r="J143" s="3"/>
       <c r="K143" s="6"/>
       <c r="L143" s="3"/>
@@ -6739,14 +6815,9 @@
       <c r="P143" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="Q143" s="7"/>
-      <c r="R143" s="7"/>
-      <c r="S143" s="7"/>
-      <c r="T143" s="7"/>
-      <c r="U143" s="7"/>
-    </row>
-    <row r="144" spans="1:21" ht="15">
-      <c r="A144" s="7">
+    </row>
+    <row r="144" spans="1:19" ht="15">
+      <c r="A144">
         <v>165</v>
       </c>
       <c r="B144" s="2">
@@ -6768,7 +6839,6 @@
         <v>106</v>
       </c>
       <c r="H144" s="3"/>
-      <c r="I144" s="7"/>
       <c r="J144" s="3"/>
       <c r="K144" s="6"/>
       <c r="L144" s="3"/>
@@ -6776,18 +6846,15 @@
       <c r="N144" s="3"/>
       <c r="O144" s="3"/>
       <c r="P144" s="3"/>
-      <c r="Q144" s="7" t="s">
+      <c r="Q144" t="s">
         <v>61</v>
       </c>
-      <c r="R144" s="7" t="s">
+      <c r="R144" t="s">
         <v>377</v>
       </c>
-      <c r="S144" s="7"/>
-      <c r="T144" s="7"/>
-      <c r="U144" s="7"/>
-    </row>
-    <row r="145" spans="1:21" ht="15">
-      <c r="A145" s="7">
+    </row>
+    <row r="145" spans="1:16" ht="15">
+      <c r="A145">
         <v>166</v>
       </c>
       <c r="B145" s="2">
@@ -6809,7 +6876,7 @@
         <v>60</v>
       </c>
       <c r="H145" s="3"/>
-      <c r="I145" s="7" t="s">
+      <c r="I145" t="s">
         <v>61</v>
       </c>
       <c r="J145" s="3" t="s">
@@ -6821,14 +6888,9 @@
       <c r="N145" s="3"/>
       <c r="O145" s="3"/>
       <c r="P145" s="3"/>
-      <c r="Q145" s="7"/>
-      <c r="R145" s="7"/>
-      <c r="S145" s="7"/>
-      <c r="T145" s="7"/>
-      <c r="U145" s="7"/>
-    </row>
-    <row r="146" spans="1:21" ht="15">
-      <c r="A146" s="7">
+    </row>
+    <row r="146" spans="1:16" ht="15">
+      <c r="A146">
         <v>167</v>
       </c>
       <c r="B146" s="2">
@@ -6850,7 +6912,7 @@
         <v>60</v>
       </c>
       <c r="H146" s="3"/>
-      <c r="I146" s="7" t="s">
+      <c r="I146" t="s">
         <v>61</v>
       </c>
       <c r="J146" s="3" t="s">
@@ -6862,14 +6924,9 @@
       <c r="N146" s="3"/>
       <c r="O146" s="3"/>
       <c r="P146" s="3"/>
-      <c r="Q146" s="7"/>
-      <c r="R146" s="7"/>
-      <c r="S146" s="7"/>
-      <c r="T146" s="7"/>
-      <c r="U146" s="7"/>
-    </row>
-    <row r="147" spans="1:21" ht="15">
-      <c r="A147" s="7">
+    </row>
+    <row r="147" spans="1:16" ht="15">
+      <c r="A147">
         <v>168</v>
       </c>
       <c r="B147" s="2">
@@ -6891,7 +6948,7 @@
         <v>60</v>
       </c>
       <c r="H147" s="3"/>
-      <c r="I147" s="7" t="s">
+      <c r="I147" t="s">
         <v>61</v>
       </c>
       <c r="J147" s="3" t="s">
@@ -6903,14 +6960,9 @@
       <c r="N147" s="3"/>
       <c r="O147" s="3"/>
       <c r="P147" s="3"/>
-      <c r="Q147" s="7"/>
-      <c r="R147" s="7"/>
-      <c r="S147" s="7"/>
-      <c r="T147" s="7"/>
-      <c r="U147" s="7"/>
-    </row>
-    <row r="148" spans="1:21" ht="15">
-      <c r="A148" s="7">
+    </row>
+    <row r="148" spans="1:16" ht="15">
+      <c r="A148">
         <v>169</v>
       </c>
       <c r="B148" s="2">
@@ -6932,7 +6984,7 @@
         <v>60</v>
       </c>
       <c r="H148" s="3"/>
-      <c r="I148" s="7" t="s">
+      <c r="I148" t="s">
         <v>61</v>
       </c>
       <c r="J148" s="3" t="s">
@@ -6944,14 +6996,9 @@
       <c r="N148" s="3"/>
       <c r="O148" s="3"/>
       <c r="P148" s="3"/>
-      <c r="Q148" s="7"/>
-      <c r="R148" s="7"/>
-      <c r="S148" s="7"/>
-      <c r="T148" s="7"/>
-      <c r="U148" s="7"/>
-    </row>
-    <row r="149" spans="1:21" ht="15">
-      <c r="A149" s="7">
+    </row>
+    <row r="149" spans="1:16" ht="15">
+      <c r="A149">
         <v>170</v>
       </c>
       <c r="B149" s="2">
@@ -6973,7 +7020,7 @@
         <v>60</v>
       </c>
       <c r="H149" s="3"/>
-      <c r="I149" s="7" t="s">
+      <c r="I149" t="s">
         <v>61</v>
       </c>
       <c r="J149" s="3" t="s">
@@ -6985,14 +7032,9 @@
       <c r="N149" s="3"/>
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
-      <c r="Q149" s="7"/>
-      <c r="R149" s="7"/>
-      <c r="S149" s="7"/>
-      <c r="T149" s="7"/>
-      <c r="U149" s="7"/>
-    </row>
-    <row r="150" spans="1:21" ht="15">
-      <c r="A150" s="7">
+    </row>
+    <row r="150" spans="1:16" ht="15">
+      <c r="A150">
         <v>171</v>
       </c>
       <c r="B150" s="2">
@@ -7014,7 +7056,7 @@
         <v>60</v>
       </c>
       <c r="H150" s="3"/>
-      <c r="I150" s="7" t="s">
+      <c r="I150" t="s">
         <v>61</v>
       </c>
       <c r="J150" s="3" t="s">
@@ -7026,14 +7068,9 @@
       <c r="N150" s="3"/>
       <c r="O150" s="3"/>
       <c r="P150" s="3"/>
-      <c r="Q150" s="7"/>
-      <c r="R150" s="7"/>
-      <c r="S150" s="7"/>
-      <c r="T150" s="7"/>
-      <c r="U150" s="7"/>
-    </row>
-    <row r="151" spans="1:21" ht="15">
-      <c r="A151" s="7">
+    </row>
+    <row r="151" spans="1:16" ht="15">
+      <c r="A151">
         <v>172</v>
       </c>
       <c r="B151" s="2">
@@ -7055,7 +7092,7 @@
         <v>60</v>
       </c>
       <c r="H151" s="3"/>
-      <c r="I151" s="7" t="s">
+      <c r="I151" t="s">
         <v>61</v>
       </c>
       <c r="J151" s="3" t="s">
@@ -7067,14 +7104,9 @@
       <c r="N151" s="3"/>
       <c r="O151" s="3"/>
       <c r="P151" s="3"/>
-      <c r="Q151" s="7"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="7"/>
-      <c r="T151" s="7"/>
-      <c r="U151" s="7"/>
-    </row>
-    <row r="152" spans="1:21" ht="15">
-      <c r="A152" s="7">
+    </row>
+    <row r="152" spans="1:16" ht="15">
+      <c r="A152">
         <v>173</v>
       </c>
       <c r="B152" s="2">
@@ -7096,7 +7128,7 @@
         <v>60</v>
       </c>
       <c r="H152" s="3"/>
-      <c r="I152" s="7" t="s">
+      <c r="I152" t="s">
         <v>61</v>
       </c>
       <c r="J152" s="3" t="s">
@@ -7108,14 +7140,9 @@
       <c r="N152" s="3"/>
       <c r="O152" s="3"/>
       <c r="P152" s="3"/>
-      <c r="Q152" s="7"/>
-      <c r="R152" s="7"/>
-      <c r="S152" s="7"/>
-      <c r="T152" s="7"/>
-      <c r="U152" s="7"/>
-    </row>
-    <row r="153" spans="1:21" ht="15">
-      <c r="A153" s="7">
+    </row>
+    <row r="153" spans="1:16" ht="15">
+      <c r="A153">
         <v>174</v>
       </c>
       <c r="B153" s="2">
@@ -7137,7 +7164,7 @@
         <v>60</v>
       </c>
       <c r="H153" s="3"/>
-      <c r="I153" s="7" t="s">
+      <c r="I153" t="s">
         <v>61</v>
       </c>
       <c r="J153" s="3" t="s">
@@ -7149,14 +7176,9 @@
       <c r="N153" s="3"/>
       <c r="O153" s="3"/>
       <c r="P153" s="3"/>
-      <c r="Q153" s="7"/>
-      <c r="R153" s="7"/>
-      <c r="S153" s="7"/>
-      <c r="T153" s="7"/>
-      <c r="U153" s="7"/>
-    </row>
-    <row r="154" spans="1:21" ht="15">
-      <c r="A154" s="7">
+    </row>
+    <row r="154" spans="1:16" ht="15">
+      <c r="A154">
         <v>175</v>
       </c>
       <c r="B154" s="2">
@@ -7178,7 +7200,7 @@
         <v>60</v>
       </c>
       <c r="H154" s="3"/>
-      <c r="I154" s="7" t="s">
+      <c r="I154" t="s">
         <v>61</v>
       </c>
       <c r="J154" s="3" t="s">
@@ -7190,14 +7212,9 @@
       <c r="N154" s="3"/>
       <c r="O154" s="3"/>
       <c r="P154" s="3"/>
-      <c r="Q154" s="7"/>
-      <c r="R154" s="7"/>
-      <c r="S154" s="7"/>
-      <c r="T154" s="7"/>
-      <c r="U154" s="7"/>
-    </row>
-    <row r="155" spans="1:21" ht="15">
-      <c r="A155" s="7">
+    </row>
+    <row r="155" spans="1:16" ht="15">
+      <c r="A155">
         <v>176</v>
       </c>
       <c r="B155" s="2">
@@ -7219,7 +7236,7 @@
         <v>60</v>
       </c>
       <c r="H155" s="3"/>
-      <c r="I155" s="7" t="s">
+      <c r="I155" t="s">
         <v>61</v>
       </c>
       <c r="J155" s="3" t="s">
@@ -7231,14 +7248,9 @@
       <c r="N155" s="3"/>
       <c r="O155" s="3"/>
       <c r="P155" s="3"/>
-      <c r="Q155" s="7"/>
-      <c r="R155" s="7"/>
-      <c r="S155" s="7"/>
-      <c r="T155" s="7"/>
-      <c r="U155" s="7"/>
-    </row>
-    <row r="156" spans="1:21" ht="15">
-      <c r="A156" s="7">
+    </row>
+    <row r="156" spans="1:16" ht="15">
+      <c r="A156">
         <v>177</v>
       </c>
       <c r="B156" s="2">
@@ -7260,7 +7272,7 @@
         <v>60</v>
       </c>
       <c r="H156" s="3"/>
-      <c r="I156" s="7" t="s">
+      <c r="I156" t="s">
         <v>61</v>
       </c>
       <c r="J156" s="3" t="s">
@@ -7272,14 +7284,9 @@
       <c r="N156" s="3"/>
       <c r="O156" s="3"/>
       <c r="P156" s="3"/>
-      <c r="Q156" s="7"/>
-      <c r="R156" s="7"/>
-      <c r="S156" s="7"/>
-      <c r="T156" s="7"/>
-      <c r="U156" s="7"/>
-    </row>
-    <row r="157" spans="1:21" ht="15">
-      <c r="A157" s="7">
+    </row>
+    <row r="157" spans="1:16" ht="15">
+      <c r="A157">
         <v>178</v>
       </c>
       <c r="B157" s="2">
@@ -7301,7 +7308,7 @@
         <v>60</v>
       </c>
       <c r="H157" s="3"/>
-      <c r="I157" s="7" t="s">
+      <c r="I157" t="s">
         <v>61</v>
       </c>
       <c r="J157" s="3" t="s">
@@ -7313,14 +7320,9 @@
       <c r="N157" s="3"/>
       <c r="O157" s="3"/>
       <c r="P157" s="3"/>
-      <c r="Q157" s="7"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="7"/>
-      <c r="T157" s="7"/>
-      <c r="U157" s="7"/>
-    </row>
-    <row r="158" spans="1:21" ht="15">
-      <c r="A158" s="7">
+    </row>
+    <row r="158" spans="1:16" ht="15">
+      <c r="A158">
         <v>179</v>
       </c>
       <c r="B158" s="2">
@@ -7342,7 +7344,7 @@
         <v>60</v>
       </c>
       <c r="H158" s="3"/>
-      <c r="I158" s="7" t="s">
+      <c r="I158" t="s">
         <v>61</v>
       </c>
       <c r="J158" s="3" t="s">
@@ -7354,14 +7356,9 @@
       <c r="N158" s="3"/>
       <c r="O158" s="3"/>
       <c r="P158" s="3"/>
-      <c r="Q158" s="7"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="7"/>
-      <c r="T158" s="7"/>
-      <c r="U158" s="7"/>
-    </row>
-    <row r="159" spans="1:21" ht="15">
-      <c r="A159" s="7">
+    </row>
+    <row r="159" spans="1:16" ht="15">
+      <c r="A159">
         <v>180</v>
       </c>
       <c r="B159" s="2">
@@ -7383,7 +7380,7 @@
         <v>60</v>
       </c>
       <c r="H159" s="3"/>
-      <c r="I159" s="7" t="s">
+      <c r="I159" t="s">
         <v>61</v>
       </c>
       <c r="J159" s="3" t="s">
@@ -7395,14 +7392,9 @@
       <c r="N159" s="3"/>
       <c r="O159" s="3"/>
       <c r="P159" s="3"/>
-      <c r="Q159" s="7"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="7"/>
-      <c r="T159" s="7"/>
-      <c r="U159" s="7"/>
-    </row>
-    <row r="160" spans="1:21" ht="15">
-      <c r="A160" s="7">
+    </row>
+    <row r="160" spans="1:16" ht="15">
+      <c r="A160">
         <v>181</v>
       </c>
       <c r="B160" s="2">
@@ -7424,7 +7416,7 @@
         <v>60</v>
       </c>
       <c r="H160" s="3"/>
-      <c r="I160" s="7" t="s">
+      <c r="I160" t="s">
         <v>61</v>
       </c>
       <c r="J160" s="3" t="s">
@@ -7436,14 +7428,9 @@
       <c r="N160" s="3"/>
       <c r="O160" s="3"/>
       <c r="P160" s="3"/>
-      <c r="Q160" s="7"/>
-      <c r="R160" s="7"/>
-      <c r="S160" s="7"/>
-      <c r="T160" s="7"/>
-      <c r="U160" s="7"/>
     </row>
     <row r="161" spans="1:21" ht="15">
-      <c r="A161" s="7">
+      <c r="A161">
         <v>182</v>
       </c>
       <c r="B161" s="2">
@@ -7465,7 +7452,7 @@
         <v>60</v>
       </c>
       <c r="H161" s="3"/>
-      <c r="I161" s="7" t="s">
+      <c r="I161" t="s">
         <v>61</v>
       </c>
       <c r="J161" s="3" t="s">
@@ -7477,14 +7464,9 @@
       <c r="N161" s="3"/>
       <c r="O161" s="3"/>
       <c r="P161" s="3"/>
-      <c r="Q161" s="7"/>
-      <c r="R161" s="7"/>
-      <c r="S161" s="7"/>
-      <c r="T161" s="7"/>
-      <c r="U161" s="7"/>
     </row>
     <row r="162" spans="1:21" ht="15">
-      <c r="A162" s="7">
+      <c r="A162">
         <v>183</v>
       </c>
       <c r="B162" s="2">
@@ -7506,7 +7488,7 @@
         <v>60</v>
       </c>
       <c r="H162" s="3"/>
-      <c r="I162" s="7" t="s">
+      <c r="I162" t="s">
         <v>61</v>
       </c>
       <c r="J162" s="3" t="s">
@@ -7518,14 +7500,9 @@
       <c r="N162" s="3"/>
       <c r="O162" s="3"/>
       <c r="P162" s="3"/>
-      <c r="Q162" s="7"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="7"/>
-      <c r="T162" s="7"/>
-      <c r="U162" s="7"/>
     </row>
     <row r="163" spans="1:21" ht="15">
-      <c r="A163" s="7">
+      <c r="A163">
         <v>184</v>
       </c>
       <c r="B163" s="2">
@@ -7547,7 +7524,7 @@
         <v>60</v>
       </c>
       <c r="H163" s="3"/>
-      <c r="I163" s="7" t="s">
+      <c r="I163" t="s">
         <v>398</v>
       </c>
       <c r="J163" s="3"/>
@@ -7557,14 +7534,9 @@
       <c r="N163" s="3"/>
       <c r="O163" s="3"/>
       <c r="P163" s="3"/>
-      <c r="Q163" s="7"/>
-      <c r="R163" s="7"/>
-      <c r="S163" s="7"/>
-      <c r="T163" s="7"/>
-      <c r="U163" s="7"/>
     </row>
     <row r="164" spans="1:21" ht="15">
-      <c r="A164" s="7">
+      <c r="A164">
         <v>185</v>
       </c>
       <c r="B164" s="2">
@@ -7586,7 +7558,7 @@
         <v>60</v>
       </c>
       <c r="H164" s="3"/>
-      <c r="I164" s="7" t="s">
+      <c r="I164" t="s">
         <v>61</v>
       </c>
       <c r="J164" s="3" t="s">
@@ -7598,14 +7570,9 @@
       <c r="N164" s="3"/>
       <c r="O164" s="3"/>
       <c r="P164" s="3"/>
-      <c r="Q164" s="7"/>
-      <c r="R164" s="7"/>
-      <c r="S164" s="7"/>
-      <c r="T164" s="7"/>
-      <c r="U164" s="7"/>
     </row>
     <row r="165" spans="1:21" ht="15">
-      <c r="A165" s="7">
+      <c r="A165">
         <v>186</v>
       </c>
       <c r="B165" s="2">
@@ -7627,7 +7594,7 @@
         <v>60</v>
       </c>
       <c r="H165" s="3"/>
-      <c r="I165" s="7" t="s">
+      <c r="I165" t="s">
         <v>61</v>
       </c>
       <c r="J165" s="3" t="s">
@@ -7639,11 +7606,865 @@
       <c r="N165" s="3"/>
       <c r="O165" s="3"/>
       <c r="P165" s="3"/>
-      <c r="Q165" s="7"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="7"/>
-      <c r="T165" s="7"/>
-      <c r="U165" s="7"/>
+    </row>
+    <row r="166" spans="1:21" ht="15">
+      <c r="A166" s="7">
+        <v>187</v>
+      </c>
+      <c r="B166" s="2">
+        <v>46266.433321759301</v>
+      </c>
+      <c r="C166" s="2">
+        <v>46266.434432870403</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H166" s="3"/>
+      <c r="I166" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J166" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K166" s="6"/>
+      <c r="L166" s="3"/>
+      <c r="M166" s="3"/>
+      <c r="N166" s="3"/>
+      <c r="O166" s="3"/>
+      <c r="P166" s="3"/>
+      <c r="Q166" s="7"/>
+      <c r="R166" s="7"/>
+      <c r="S166" s="7"/>
+      <c r="T166" s="7"/>
+      <c r="U166" s="7"/>
+    </row>
+    <row r="167" spans="1:21" ht="15">
+      <c r="A167" s="7">
+        <v>188</v>
+      </c>
+      <c r="B167" s="2">
+        <v>46266.434537036999</v>
+      </c>
+      <c r="C167" s="2">
+        <v>46266.436562499999</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H167" s="3"/>
+      <c r="I167" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J167" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="K167" s="6"/>
+      <c r="L167" s="3"/>
+      <c r="M167" s="3"/>
+      <c r="N167" s="3"/>
+      <c r="O167" s="3"/>
+      <c r="P167" s="3"/>
+      <c r="Q167" s="7"/>
+      <c r="R167" s="7"/>
+      <c r="S167" s="7"/>
+      <c r="T167" s="7"/>
+      <c r="U167" s="7"/>
+    </row>
+    <row r="168" spans="1:21" ht="15">
+      <c r="A168" s="7">
+        <v>189</v>
+      </c>
+      <c r="B168" s="2">
+        <v>46266.440763888902</v>
+      </c>
+      <c r="C168" s="2">
+        <v>46266.441597222198</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H168" s="3"/>
+      <c r="I168" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J168" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="K168" s="6"/>
+      <c r="L168" s="3"/>
+      <c r="M168" s="3"/>
+      <c r="N168" s="3"/>
+      <c r="O168" s="3"/>
+      <c r="P168" s="3"/>
+      <c r="Q168" s="7"/>
+      <c r="R168" s="7"/>
+      <c r="S168" s="7"/>
+      <c r="T168" s="7"/>
+      <c r="U168" s="7"/>
+    </row>
+    <row r="169" spans="1:21" ht="15">
+      <c r="A169" s="7">
+        <v>190</v>
+      </c>
+      <c r="B169" s="2">
+        <v>46266.4466203704</v>
+      </c>
+      <c r="C169" s="2">
+        <v>46266.448750000003</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H169" s="3"/>
+      <c r="I169" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J169" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="K169" s="6"/>
+      <c r="L169" s="3"/>
+      <c r="M169" s="3"/>
+      <c r="N169" s="3"/>
+      <c r="O169" s="3"/>
+      <c r="P169" s="3"/>
+      <c r="Q169" s="7"/>
+      <c r="R169" s="7"/>
+      <c r="S169" s="7"/>
+      <c r="T169" s="7"/>
+      <c r="U169" s="7"/>
+    </row>
+    <row r="170" spans="1:21" ht="15">
+      <c r="A170" s="7">
+        <v>191</v>
+      </c>
+      <c r="B170" s="2">
+        <v>46266.448796296303</v>
+      </c>
+      <c r="C170" s="2">
+        <v>46266.449502314797</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H170" s="3"/>
+      <c r="I170" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J170" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="K170" s="6"/>
+      <c r="L170" s="3"/>
+      <c r="M170" s="3"/>
+      <c r="N170" s="3"/>
+      <c r="O170" s="3"/>
+      <c r="P170" s="3"/>
+      <c r="Q170" s="7"/>
+      <c r="R170" s="7"/>
+      <c r="S170" s="7"/>
+      <c r="T170" s="7"/>
+      <c r="U170" s="7"/>
+    </row>
+    <row r="171" spans="1:21" ht="15">
+      <c r="A171" s="7">
+        <v>192</v>
+      </c>
+      <c r="B171" s="2">
+        <v>46266.451782407399</v>
+      </c>
+      <c r="C171" s="2">
+        <v>46266.4526273148</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H171" s="3"/>
+      <c r="I171" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J171" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="K171" s="6"/>
+      <c r="L171" s="3"/>
+      <c r="M171" s="3"/>
+      <c r="N171" s="3"/>
+      <c r="O171" s="3"/>
+      <c r="P171" s="3"/>
+      <c r="Q171" s="7"/>
+      <c r="R171" s="7"/>
+      <c r="S171" s="7"/>
+      <c r="T171" s="7"/>
+      <c r="U171" s="7"/>
+    </row>
+    <row r="172" spans="1:21" ht="15">
+      <c r="A172" s="7">
+        <v>193</v>
+      </c>
+      <c r="B172" s="2">
+        <v>46266.4532175926</v>
+      </c>
+      <c r="C172" s="2">
+        <v>46266.454803240696</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H172" s="3"/>
+      <c r="I172" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J172" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="K172" s="6"/>
+      <c r="L172" s="3"/>
+      <c r="M172" s="3"/>
+      <c r="N172" s="3"/>
+      <c r="O172" s="3"/>
+      <c r="P172" s="3"/>
+      <c r="Q172" s="7"/>
+      <c r="R172" s="7"/>
+      <c r="S172" s="7"/>
+      <c r="T172" s="7"/>
+      <c r="U172" s="7"/>
+    </row>
+    <row r="173" spans="1:21" ht="15">
+      <c r="A173" s="7">
+        <v>194</v>
+      </c>
+      <c r="B173" s="2">
+        <v>46266.459467592598</v>
+      </c>
+      <c r="C173" s="2">
+        <v>46266.4600810185</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H173" s="3"/>
+      <c r="I173" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J173" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K173" s="6"/>
+      <c r="L173" s="3"/>
+      <c r="M173" s="3"/>
+      <c r="N173" s="3"/>
+      <c r="O173" s="3"/>
+      <c r="P173" s="3"/>
+      <c r="Q173" s="7"/>
+      <c r="R173" s="7"/>
+      <c r="S173" s="7"/>
+      <c r="T173" s="7"/>
+      <c r="U173" s="7"/>
+    </row>
+    <row r="174" spans="1:21" ht="15">
+      <c r="A174" s="7">
+        <v>195</v>
+      </c>
+      <c r="B174" s="2">
+        <v>46266.453240740702</v>
+      </c>
+      <c r="C174" s="2">
+        <v>46266.460729166698</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H174" s="3"/>
+      <c r="I174" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J174" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="K174" s="6"/>
+      <c r="L174" s="3"/>
+      <c r="M174" s="3"/>
+      <c r="N174" s="3"/>
+      <c r="O174" s="3"/>
+      <c r="P174" s="3"/>
+      <c r="Q174" s="7"/>
+      <c r="R174" s="7"/>
+      <c r="S174" s="7"/>
+      <c r="T174" s="7"/>
+      <c r="U174" s="7"/>
+    </row>
+    <row r="175" spans="1:21" ht="15">
+      <c r="A175" s="7">
+        <v>196</v>
+      </c>
+      <c r="B175" s="2">
+        <v>46266.464641203696</v>
+      </c>
+      <c r="C175" s="2">
+        <v>46266.464953703697</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H175" s="3"/>
+      <c r="I175" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J175" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="K175" s="6"/>
+      <c r="L175" s="3"/>
+      <c r="M175" s="3"/>
+      <c r="N175" s="3"/>
+      <c r="O175" s="3"/>
+      <c r="P175" s="3"/>
+      <c r="Q175" s="7"/>
+      <c r="R175" s="7"/>
+      <c r="S175" s="7"/>
+      <c r="T175" s="7"/>
+      <c r="U175" s="7"/>
+    </row>
+    <row r="176" spans="1:21" ht="15">
+      <c r="A176" s="7">
+        <v>197</v>
+      </c>
+      <c r="B176" s="2">
+        <v>46266.465567129599</v>
+      </c>
+      <c r="C176" s="2">
+        <v>46266.466215277796</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H176" s="3"/>
+      <c r="I176" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J176" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="K176" s="6"/>
+      <c r="L176" s="3"/>
+      <c r="M176" s="3"/>
+      <c r="N176" s="3"/>
+      <c r="O176" s="3"/>
+      <c r="P176" s="3"/>
+      <c r="Q176" s="7"/>
+      <c r="R176" s="7"/>
+      <c r="S176" s="7"/>
+      <c r="T176" s="7"/>
+      <c r="U176" s="7"/>
+    </row>
+    <row r="177" spans="1:21" ht="15">
+      <c r="A177" s="7">
+        <v>198</v>
+      </c>
+      <c r="B177" s="2">
+        <v>46266.468368055597</v>
+      </c>
+      <c r="C177" s="2">
+        <v>46266.469664351898</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H177" s="3"/>
+      <c r="I177" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J177" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="K177" s="6"/>
+      <c r="L177" s="3"/>
+      <c r="M177" s="3"/>
+      <c r="N177" s="3"/>
+      <c r="O177" s="3"/>
+      <c r="P177" s="3"/>
+      <c r="Q177" s="7"/>
+      <c r="R177" s="7"/>
+      <c r="S177" s="7"/>
+      <c r="T177" s="7"/>
+      <c r="U177" s="7"/>
+    </row>
+    <row r="178" spans="1:21" ht="15">
+      <c r="A178" s="7">
+        <v>199</v>
+      </c>
+      <c r="B178" s="2">
+        <v>46266.486018518503</v>
+      </c>
+      <c r="C178" s="2">
+        <v>46266.490219907399</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H178" s="3"/>
+      <c r="I178" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J178" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K178" s="6"/>
+      <c r="L178" s="3"/>
+      <c r="M178" s="3"/>
+      <c r="N178" s="3"/>
+      <c r="O178" s="3"/>
+      <c r="P178" s="3"/>
+      <c r="Q178" s="7"/>
+      <c r="R178" s="7"/>
+      <c r="S178" s="7"/>
+      <c r="T178" s="7"/>
+      <c r="U178" s="7"/>
+    </row>
+    <row r="179" spans="1:21" ht="15">
+      <c r="A179" s="7">
+        <v>200</v>
+      </c>
+      <c r="B179" s="2">
+        <v>46266.503125000003</v>
+      </c>
+      <c r="C179" s="2">
+        <v>46266.503587963001</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H179" s="3"/>
+      <c r="I179" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J179" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="K179" s="6"/>
+      <c r="L179" s="3"/>
+      <c r="M179" s="3"/>
+      <c r="N179" s="3"/>
+      <c r="O179" s="3"/>
+      <c r="P179" s="3"/>
+      <c r="Q179" s="7"/>
+      <c r="R179" s="7"/>
+      <c r="S179" s="7"/>
+      <c r="T179" s="7"/>
+      <c r="U179" s="7"/>
+    </row>
+    <row r="180" spans="1:21" ht="15">
+      <c r="A180" s="7">
+        <v>201</v>
+      </c>
+      <c r="B180" s="2">
+        <v>46266.507685185199</v>
+      </c>
+      <c r="C180" s="2">
+        <v>46266.508773148104</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H180" s="3"/>
+      <c r="I180" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J180" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="K180" s="6"/>
+      <c r="L180" s="3"/>
+      <c r="M180" s="3"/>
+      <c r="N180" s="3"/>
+      <c r="O180" s="3"/>
+      <c r="P180" s="3"/>
+      <c r="Q180" s="7"/>
+      <c r="R180" s="7"/>
+      <c r="S180" s="7"/>
+      <c r="T180" s="7"/>
+      <c r="U180" s="7"/>
+    </row>
+    <row r="181" spans="1:21" ht="15">
+      <c r="A181" s="7">
+        <v>202</v>
+      </c>
+      <c r="B181" s="2">
+        <v>46266.511030092603</v>
+      </c>
+      <c r="C181" s="2">
+        <v>46266.512546296297</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H181" s="3"/>
+      <c r="I181" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J181" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="K181" s="6"/>
+      <c r="L181" s="3"/>
+      <c r="M181" s="3"/>
+      <c r="N181" s="3"/>
+      <c r="O181" s="3"/>
+      <c r="P181" s="3"/>
+      <c r="Q181" s="7"/>
+      <c r="R181" s="7"/>
+      <c r="S181" s="7"/>
+      <c r="T181" s="7"/>
+      <c r="U181" s="7"/>
+    </row>
+    <row r="182" spans="1:21" ht="15">
+      <c r="A182" s="7">
+        <v>203</v>
+      </c>
+      <c r="B182" s="2">
+        <v>46266.515254629601</v>
+      </c>
+      <c r="C182" s="2">
+        <v>46266.516597222202</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F182" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H182" s="3"/>
+      <c r="I182" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J182" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="K182" s="6"/>
+      <c r="L182" s="3"/>
+      <c r="M182" s="3"/>
+      <c r="N182" s="3"/>
+      <c r="O182" s="3"/>
+      <c r="P182" s="3"/>
+      <c r="Q182" s="7"/>
+      <c r="R182" s="7"/>
+      <c r="S182" s="7"/>
+      <c r="T182" s="7"/>
+      <c r="U182" s="7"/>
+    </row>
+    <row r="183" spans="1:21" ht="15">
+      <c r="A183" s="7">
+        <v>204</v>
+      </c>
+      <c r="B183" s="2">
+        <v>46266.5312037037</v>
+      </c>
+      <c r="C183" s="2">
+        <v>46266.5316087963</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H183" s="3"/>
+      <c r="I183" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J183" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K183" s="6"/>
+      <c r="L183" s="3"/>
+      <c r="M183" s="3"/>
+      <c r="N183" s="3"/>
+      <c r="O183" s="3"/>
+      <c r="P183" s="3"/>
+      <c r="Q183" s="7"/>
+      <c r="R183" s="7"/>
+      <c r="S183" s="7"/>
+      <c r="T183" s="7"/>
+      <c r="U183" s="7"/>
+    </row>
+    <row r="184" spans="1:21" ht="15">
+      <c r="A184" s="7">
+        <v>205</v>
+      </c>
+      <c r="B184" s="2">
+        <v>46266.546643518501</v>
+      </c>
+      <c r="C184" s="2">
+        <v>46266.547974537003</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H184" s="3"/>
+      <c r="I184" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J184" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K184" s="6"/>
+      <c r="L184" s="3"/>
+      <c r="M184" s="3"/>
+      <c r="N184" s="3"/>
+      <c r="O184" s="3"/>
+      <c r="P184" s="3"/>
+      <c r="Q184" s="7"/>
+      <c r="R184" s="7"/>
+      <c r="S184" s="7"/>
+      <c r="T184" s="7"/>
+      <c r="U184" s="7"/>
+    </row>
+    <row r="185" spans="1:21" ht="15">
+      <c r="A185" s="7">
+        <v>206</v>
+      </c>
+      <c r="B185" s="2">
+        <v>46266.5457060185</v>
+      </c>
+      <c r="C185" s="2">
+        <v>46266.5492592593</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H185" s="3"/>
+      <c r="I185" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J185" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="K185" s="6"/>
+      <c r="L185" s="3"/>
+      <c r="M185" s="3"/>
+      <c r="N185" s="3"/>
+      <c r="O185" s="3"/>
+      <c r="P185" s="3"/>
+      <c r="Q185" s="7"/>
+      <c r="R185" s="7"/>
+      <c r="S185" s="7"/>
+      <c r="T185" s="7"/>
+      <c r="U185" s="7"/>
+    </row>
+    <row r="186" spans="1:21" ht="15">
+      <c r="A186" s="7">
+        <v>207</v>
+      </c>
+      <c r="B186" s="2">
+        <v>46266.553680555597</v>
+      </c>
+      <c r="C186" s="2">
+        <v>46266.557268518503</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H186" s="3"/>
+      <c r="I186" s="7"/>
+      <c r="J186" s="3"/>
+      <c r="K186" s="6"/>
+      <c r="L186" s="3"/>
+      <c r="M186" s="3"/>
+      <c r="N186" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="O186" s="3"/>
+      <c r="P186" s="3"/>
+      <c r="Q186" s="7"/>
+      <c r="R186" s="7"/>
+      <c r="S186" s="7"/>
+      <c r="T186" s="7"/>
+      <c r="U186" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="322" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2471BD2C-7F70-437A-AF5D-2A010F93F850}"/>
+  <xr:revisionPtr revIDLastSave="325" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{279D6B72-57BF-43AA-827D-137F335F6C30}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="454">
   <si>
     <t>Id</t>
   </si>
@@ -1326,6 +1326,78 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG-20260901-WA0000_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Valle%20Dora.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/Screenshot_20260901_145459_WhatsAppBusiness_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>luis.perez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Luis Javier Perez Mojica</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Luis%20Javier%20Perez%20Mo.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/Screenshot_20260901_150150_WhatsAppBusiness_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_9174_Luis%20Javier%20Perez%20Mo.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/5C2536AD-8833-4769-8DFA-9DDF77E24AB5_Luis%20Javier%20Perez%20Mo.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882973776037976531615778835772_Starbucks%20Parque%20Tep.jpg</t>
+  </si>
+  <si>
+    <t>martin-gerardo.martin@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Martin Gerardo Herrera Vazquez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG-20260901-WA0035_Martin%20Gerardo%20Herre.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17882974982627719039250112761852_Starbucks%20ENCUENTRO.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Villas%20de.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/5C25D055-56E2-44E9-A466-2DF30DA4A64D_Starbucks%20El%20Rosario.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/0aef0e63-a94c-48f2-bc1e-3afe11597ed4_Starbucks%20Jinetes.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17883009254807620066804435116282_Starbucks%20ITESM%20Esta.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_7940_Starbucks%20Jinetes.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/092AD514-2AC6-41E9-A511-9F963CEFE45D_Starbucks%20Zona%20Azul.JPG</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17883014074244777866701588342633_Kevin%20Arturo%20Suarez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260826-WA0011_Starbucks%20ENCUENTRO.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_3971_Starbucks%20El%20Rosario.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/88FCA030-1230-4A2F-8422-DDA72285CEE6_Starbucks%20El%20Rosario.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/IMG_3984_Starbucks%20El%20Rosario.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1460,8 +1532,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U186" totalsRowShown="0">
-  <autoFilter ref="A1:U186" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U208" totalsRowShown="0">
+  <autoFilter ref="A1:U208" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1614,7 +1686,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="207" latestEventMarker="442">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="229" latestEventMarker="464">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1939,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U186"/>
+  <dimension ref="A1:U208"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -7429,7 +7501,7 @@
       <c r="O160" s="3"/>
       <c r="P160" s="3"/>
     </row>
-    <row r="161" spans="1:21" ht="15">
+    <row r="161" spans="1:16" ht="15">
       <c r="A161">
         <v>182</v>
       </c>
@@ -7465,7 +7537,7 @@
       <c r="O161" s="3"/>
       <c r="P161" s="3"/>
     </row>
-    <row r="162" spans="1:21" ht="15">
+    <row r="162" spans="1:16" ht="15">
       <c r="A162">
         <v>183</v>
       </c>
@@ -7501,7 +7573,7 @@
       <c r="O162" s="3"/>
       <c r="P162" s="3"/>
     </row>
-    <row r="163" spans="1:21" ht="15">
+    <row r="163" spans="1:16" ht="15">
       <c r="A163">
         <v>184</v>
       </c>
@@ -7535,7 +7607,7 @@
       <c r="O163" s="3"/>
       <c r="P163" s="3"/>
     </row>
-    <row r="164" spans="1:21" ht="15">
+    <row r="164" spans="1:16" ht="15">
       <c r="A164">
         <v>185</v>
       </c>
@@ -7571,7 +7643,7 @@
       <c r="O164" s="3"/>
       <c r="P164" s="3"/>
     </row>
-    <row r="165" spans="1:21" ht="15">
+    <row r="165" spans="1:16" ht="15">
       <c r="A165">
         <v>186</v>
       </c>
@@ -7607,8 +7679,8 @@
       <c r="O165" s="3"/>
       <c r="P165" s="3"/>
     </row>
-    <row r="166" spans="1:21" ht="15">
-      <c r="A166" s="7">
+    <row r="166" spans="1:16" ht="15">
+      <c r="A166">
         <v>187</v>
       </c>
       <c r="B166" s="2">
@@ -7630,7 +7702,7 @@
         <v>60</v>
       </c>
       <c r="H166" s="3"/>
-      <c r="I166" s="7" t="s">
+      <c r="I166" t="s">
         <v>61</v>
       </c>
       <c r="J166" s="3" t="s">
@@ -7642,14 +7714,9 @@
       <c r="N166" s="3"/>
       <c r="O166" s="3"/>
       <c r="P166" s="3"/>
-      <c r="Q166" s="7"/>
-      <c r="R166" s="7"/>
-      <c r="S166" s="7"/>
-      <c r="T166" s="7"/>
-      <c r="U166" s="7"/>
-    </row>
-    <row r="167" spans="1:21" ht="15">
-      <c r="A167" s="7">
+    </row>
+    <row r="167" spans="1:16" ht="15">
+      <c r="A167">
         <v>188</v>
       </c>
       <c r="B167" s="2">
@@ -7671,7 +7738,7 @@
         <v>60</v>
       </c>
       <c r="H167" s="3"/>
-      <c r="I167" s="7" t="s">
+      <c r="I167" t="s">
         <v>61</v>
       </c>
       <c r="J167" s="3" t="s">
@@ -7683,14 +7750,9 @@
       <c r="N167" s="3"/>
       <c r="O167" s="3"/>
       <c r="P167" s="3"/>
-      <c r="Q167" s="7"/>
-      <c r="R167" s="7"/>
-      <c r="S167" s="7"/>
-      <c r="T167" s="7"/>
-      <c r="U167" s="7"/>
-    </row>
-    <row r="168" spans="1:21" ht="15">
-      <c r="A168" s="7">
+    </row>
+    <row r="168" spans="1:16" ht="15">
+      <c r="A168">
         <v>189</v>
       </c>
       <c r="B168" s="2">
@@ -7712,7 +7774,7 @@
         <v>60</v>
       </c>
       <c r="H168" s="3"/>
-      <c r="I168" s="7" t="s">
+      <c r="I168" t="s">
         <v>61</v>
       </c>
       <c r="J168" s="3" t="s">
@@ -7724,14 +7786,9 @@
       <c r="N168" s="3"/>
       <c r="O168" s="3"/>
       <c r="P168" s="3"/>
-      <c r="Q168" s="7"/>
-      <c r="R168" s="7"/>
-      <c r="S168" s="7"/>
-      <c r="T168" s="7"/>
-      <c r="U168" s="7"/>
-    </row>
-    <row r="169" spans="1:21" ht="15">
-      <c r="A169" s="7">
+    </row>
+    <row r="169" spans="1:16" ht="15">
+      <c r="A169">
         <v>190</v>
       </c>
       <c r="B169" s="2">
@@ -7753,7 +7810,7 @@
         <v>60</v>
       </c>
       <c r="H169" s="3"/>
-      <c r="I169" s="7" t="s">
+      <c r="I169" t="s">
         <v>61</v>
       </c>
       <c r="J169" s="3" t="s">
@@ -7765,14 +7822,9 @@
       <c r="N169" s="3"/>
       <c r="O169" s="3"/>
       <c r="P169" s="3"/>
-      <c r="Q169" s="7"/>
-      <c r="R169" s="7"/>
-      <c r="S169" s="7"/>
-      <c r="T169" s="7"/>
-      <c r="U169" s="7"/>
-    </row>
-    <row r="170" spans="1:21" ht="15">
-      <c r="A170" s="7">
+    </row>
+    <row r="170" spans="1:16" ht="15">
+      <c r="A170">
         <v>191</v>
       </c>
       <c r="B170" s="2">
@@ -7794,7 +7846,7 @@
         <v>60</v>
       </c>
       <c r="H170" s="3"/>
-      <c r="I170" s="7" t="s">
+      <c r="I170" t="s">
         <v>61</v>
       </c>
       <c r="J170" s="3" t="s">
@@ -7806,14 +7858,9 @@
       <c r="N170" s="3"/>
       <c r="O170" s="3"/>
       <c r="P170" s="3"/>
-      <c r="Q170" s="7"/>
-      <c r="R170" s="7"/>
-      <c r="S170" s="7"/>
-      <c r="T170" s="7"/>
-      <c r="U170" s="7"/>
-    </row>
-    <row r="171" spans="1:21" ht="15">
-      <c r="A171" s="7">
+    </row>
+    <row r="171" spans="1:16" ht="15">
+      <c r="A171">
         <v>192</v>
       </c>
       <c r="B171" s="2">
@@ -7835,7 +7882,7 @@
         <v>60</v>
       </c>
       <c r="H171" s="3"/>
-      <c r="I171" s="7" t="s">
+      <c r="I171" t="s">
         <v>61</v>
       </c>
       <c r="J171" s="3" t="s">
@@ -7847,14 +7894,9 @@
       <c r="N171" s="3"/>
       <c r="O171" s="3"/>
       <c r="P171" s="3"/>
-      <c r="Q171" s="7"/>
-      <c r="R171" s="7"/>
-      <c r="S171" s="7"/>
-      <c r="T171" s="7"/>
-      <c r="U171" s="7"/>
-    </row>
-    <row r="172" spans="1:21" ht="15">
-      <c r="A172" s="7">
+    </row>
+    <row r="172" spans="1:16" ht="15">
+      <c r="A172">
         <v>193</v>
       </c>
       <c r="B172" s="2">
@@ -7876,7 +7918,7 @@
         <v>60</v>
       </c>
       <c r="H172" s="3"/>
-      <c r="I172" s="7" t="s">
+      <c r="I172" t="s">
         <v>61</v>
       </c>
       <c r="J172" s="3" t="s">
@@ -7888,14 +7930,9 @@
       <c r="N172" s="3"/>
       <c r="O172" s="3"/>
       <c r="P172" s="3"/>
-      <c r="Q172" s="7"/>
-      <c r="R172" s="7"/>
-      <c r="S172" s="7"/>
-      <c r="T172" s="7"/>
-      <c r="U172" s="7"/>
-    </row>
-    <row r="173" spans="1:21" ht="15">
-      <c r="A173" s="7">
+    </row>
+    <row r="173" spans="1:16" ht="15">
+      <c r="A173">
         <v>194</v>
       </c>
       <c r="B173" s="2">
@@ -7917,7 +7954,7 @@
         <v>60</v>
       </c>
       <c r="H173" s="3"/>
-      <c r="I173" s="7" t="s">
+      <c r="I173" t="s">
         <v>61</v>
       </c>
       <c r="J173" s="3" t="s">
@@ -7929,14 +7966,9 @@
       <c r="N173" s="3"/>
       <c r="O173" s="3"/>
       <c r="P173" s="3"/>
-      <c r="Q173" s="7"/>
-      <c r="R173" s="7"/>
-      <c r="S173" s="7"/>
-      <c r="T173" s="7"/>
-      <c r="U173" s="7"/>
-    </row>
-    <row r="174" spans="1:21" ht="15">
-      <c r="A174" s="7">
+    </row>
+    <row r="174" spans="1:16" ht="15">
+      <c r="A174">
         <v>195</v>
       </c>
       <c r="B174" s="2">
@@ -7958,7 +7990,7 @@
         <v>60</v>
       </c>
       <c r="H174" s="3"/>
-      <c r="I174" s="7" t="s">
+      <c r="I174" t="s">
         <v>61</v>
       </c>
       <c r="J174" s="3" t="s">
@@ -7970,14 +8002,9 @@
       <c r="N174" s="3"/>
       <c r="O174" s="3"/>
       <c r="P174" s="3"/>
-      <c r="Q174" s="7"/>
-      <c r="R174" s="7"/>
-      <c r="S174" s="7"/>
-      <c r="T174" s="7"/>
-      <c r="U174" s="7"/>
-    </row>
-    <row r="175" spans="1:21" ht="15">
-      <c r="A175" s="7">
+    </row>
+    <row r="175" spans="1:16" ht="15">
+      <c r="A175">
         <v>196</v>
       </c>
       <c r="B175" s="2">
@@ -7999,7 +8026,7 @@
         <v>60</v>
       </c>
       <c r="H175" s="3"/>
-      <c r="I175" s="7" t="s">
+      <c r="I175" t="s">
         <v>61</v>
       </c>
       <c r="J175" s="3" t="s">
@@ -8011,14 +8038,9 @@
       <c r="N175" s="3"/>
       <c r="O175" s="3"/>
       <c r="P175" s="3"/>
-      <c r="Q175" s="7"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="7"/>
-      <c r="T175" s="7"/>
-      <c r="U175" s="7"/>
-    </row>
-    <row r="176" spans="1:21" ht="15">
-      <c r="A176" s="7">
+    </row>
+    <row r="176" spans="1:16" ht="15">
+      <c r="A176">
         <v>197</v>
       </c>
       <c r="B176" s="2">
@@ -8040,7 +8062,7 @@
         <v>60</v>
       </c>
       <c r="H176" s="3"/>
-      <c r="I176" s="7" t="s">
+      <c r="I176" t="s">
         <v>61</v>
       </c>
       <c r="J176" s="3" t="s">
@@ -8052,14 +8074,9 @@
       <c r="N176" s="3"/>
       <c r="O176" s="3"/>
       <c r="P176" s="3"/>
-      <c r="Q176" s="7"/>
-      <c r="R176" s="7"/>
-      <c r="S176" s="7"/>
-      <c r="T176" s="7"/>
-      <c r="U176" s="7"/>
     </row>
     <row r="177" spans="1:21" ht="15">
-      <c r="A177" s="7">
+      <c r="A177">
         <v>198</v>
       </c>
       <c r="B177" s="2">
@@ -8081,7 +8098,7 @@
         <v>60</v>
       </c>
       <c r="H177" s="3"/>
-      <c r="I177" s="7" t="s">
+      <c r="I177" t="s">
         <v>61</v>
       </c>
       <c r="J177" s="3" t="s">
@@ -8093,14 +8110,9 @@
       <c r="N177" s="3"/>
       <c r="O177" s="3"/>
       <c r="P177" s="3"/>
-      <c r="Q177" s="7"/>
-      <c r="R177" s="7"/>
-      <c r="S177" s="7"/>
-      <c r="T177" s="7"/>
-      <c r="U177" s="7"/>
     </row>
     <row r="178" spans="1:21" ht="15">
-      <c r="A178" s="7">
+      <c r="A178">
         <v>199</v>
       </c>
       <c r="B178" s="2">
@@ -8122,7 +8134,7 @@
         <v>60</v>
       </c>
       <c r="H178" s="3"/>
-      <c r="I178" s="7" t="s">
+      <c r="I178" t="s">
         <v>61</v>
       </c>
       <c r="J178" s="3" t="s">
@@ -8134,14 +8146,9 @@
       <c r="N178" s="3"/>
       <c r="O178" s="3"/>
       <c r="P178" s="3"/>
-      <c r="Q178" s="7"/>
-      <c r="R178" s="7"/>
-      <c r="S178" s="7"/>
-      <c r="T178" s="7"/>
-      <c r="U178" s="7"/>
     </row>
     <row r="179" spans="1:21" ht="15">
-      <c r="A179" s="7">
+      <c r="A179">
         <v>200</v>
       </c>
       <c r="B179" s="2">
@@ -8163,7 +8170,7 @@
         <v>60</v>
       </c>
       <c r="H179" s="3"/>
-      <c r="I179" s="7" t="s">
+      <c r="I179" t="s">
         <v>61</v>
       </c>
       <c r="J179" s="3" t="s">
@@ -8175,14 +8182,9 @@
       <c r="N179" s="3"/>
       <c r="O179" s="3"/>
       <c r="P179" s="3"/>
-      <c r="Q179" s="7"/>
-      <c r="R179" s="7"/>
-      <c r="S179" s="7"/>
-      <c r="T179" s="7"/>
-      <c r="U179" s="7"/>
     </row>
     <row r="180" spans="1:21" ht="15">
-      <c r="A180" s="7">
+      <c r="A180">
         <v>201</v>
       </c>
       <c r="B180" s="2">
@@ -8204,7 +8206,7 @@
         <v>60</v>
       </c>
       <c r="H180" s="3"/>
-      <c r="I180" s="7" t="s">
+      <c r="I180" t="s">
         <v>61</v>
       </c>
       <c r="J180" s="3" t="s">
@@ -8216,14 +8218,9 @@
       <c r="N180" s="3"/>
       <c r="O180" s="3"/>
       <c r="P180" s="3"/>
-      <c r="Q180" s="7"/>
-      <c r="R180" s="7"/>
-      <c r="S180" s="7"/>
-      <c r="T180" s="7"/>
-      <c r="U180" s="7"/>
     </row>
     <row r="181" spans="1:21" ht="15">
-      <c r="A181" s="7">
+      <c r="A181">
         <v>202</v>
       </c>
       <c r="B181" s="2">
@@ -8245,7 +8242,7 @@
         <v>60</v>
       </c>
       <c r="H181" s="3"/>
-      <c r="I181" s="7" t="s">
+      <c r="I181" t="s">
         <v>61</v>
       </c>
       <c r="J181" s="3" t="s">
@@ -8257,14 +8254,9 @@
       <c r="N181" s="3"/>
       <c r="O181" s="3"/>
       <c r="P181" s="3"/>
-      <c r="Q181" s="7"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="7"/>
-      <c r="T181" s="7"/>
-      <c r="U181" s="7"/>
     </row>
     <row r="182" spans="1:21" ht="15">
-      <c r="A182" s="7">
+      <c r="A182">
         <v>203</v>
       </c>
       <c r="B182" s="2">
@@ -8286,7 +8278,7 @@
         <v>60</v>
       </c>
       <c r="H182" s="3"/>
-      <c r="I182" s="7" t="s">
+      <c r="I182" t="s">
         <v>61</v>
       </c>
       <c r="J182" s="3" t="s">
@@ -8298,14 +8290,9 @@
       <c r="N182" s="3"/>
       <c r="O182" s="3"/>
       <c r="P182" s="3"/>
-      <c r="Q182" s="7"/>
-      <c r="R182" s="7"/>
-      <c r="S182" s="7"/>
-      <c r="T182" s="7"/>
-      <c r="U182" s="7"/>
     </row>
     <row r="183" spans="1:21" ht="15">
-      <c r="A183" s="7">
+      <c r="A183">
         <v>204</v>
       </c>
       <c r="B183" s="2">
@@ -8327,7 +8314,7 @@
         <v>60</v>
       </c>
       <c r="H183" s="3"/>
-      <c r="I183" s="7" t="s">
+      <c r="I183" t="s">
         <v>61</v>
       </c>
       <c r="J183" s="3" t="s">
@@ -8339,14 +8326,9 @@
       <c r="N183" s="3"/>
       <c r="O183" s="3"/>
       <c r="P183" s="3"/>
-      <c r="Q183" s="7"/>
-      <c r="R183" s="7"/>
-      <c r="S183" s="7"/>
-      <c r="T183" s="7"/>
-      <c r="U183" s="7"/>
     </row>
     <row r="184" spans="1:21" ht="15">
-      <c r="A184" s="7">
+      <c r="A184">
         <v>205</v>
       </c>
       <c r="B184" s="2">
@@ -8368,7 +8350,7 @@
         <v>60</v>
       </c>
       <c r="H184" s="3"/>
-      <c r="I184" s="7" t="s">
+      <c r="I184" t="s">
         <v>61</v>
       </c>
       <c r="J184" s="3" t="s">
@@ -8380,14 +8362,9 @@
       <c r="N184" s="3"/>
       <c r="O184" s="3"/>
       <c r="P184" s="3"/>
-      <c r="Q184" s="7"/>
-      <c r="R184" s="7"/>
-      <c r="S184" s="7"/>
-      <c r="T184" s="7"/>
-      <c r="U184" s="7"/>
     </row>
     <row r="185" spans="1:21" ht="15">
-      <c r="A185" s="7">
+      <c r="A185">
         <v>206</v>
       </c>
       <c r="B185" s="2">
@@ -8409,7 +8386,7 @@
         <v>60</v>
       </c>
       <c r="H185" s="3"/>
-      <c r="I185" s="7" t="s">
+      <c r="I185" t="s">
         <v>61</v>
       </c>
       <c r="J185" s="3" t="s">
@@ -8421,14 +8398,9 @@
       <c r="N185" s="3"/>
       <c r="O185" s="3"/>
       <c r="P185" s="3"/>
-      <c r="Q185" s="7"/>
-      <c r="R185" s="7"/>
-      <c r="S185" s="7"/>
-      <c r="T185" s="7"/>
-      <c r="U185" s="7"/>
     </row>
     <row r="186" spans="1:21" ht="15">
-      <c r="A186" s="7">
+      <c r="A186">
         <v>207</v>
       </c>
       <c r="B186" s="2">
@@ -8450,7 +8422,6 @@
         <v>217</v>
       </c>
       <c r="H186" s="3"/>
-      <c r="I186" s="7"/>
       <c r="J186" s="3"/>
       <c r="K186" s="6"/>
       <c r="L186" s="3"/>
@@ -8460,11 +8431,890 @@
       </c>
       <c r="O186" s="3"/>
       <c r="P186" s="3"/>
-      <c r="Q186" s="7"/>
-      <c r="R186" s="7"/>
-      <c r="S186" s="7"/>
-      <c r="T186" s="7"/>
-      <c r="U186" s="7"/>
+    </row>
+    <row r="187" spans="1:21" ht="15">
+      <c r="A187" s="7">
+        <v>208</v>
+      </c>
+      <c r="B187" s="2">
+        <v>46266.587337962999</v>
+      </c>
+      <c r="C187" s="2">
+        <v>46266.596365740697</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H187" s="3"/>
+      <c r="I187" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J187" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="K187" s="6"/>
+      <c r="L187" s="3"/>
+      <c r="M187" s="3"/>
+      <c r="N187" s="3"/>
+      <c r="O187" s="3"/>
+      <c r="P187" s="3"/>
+      <c r="Q187" s="7"/>
+      <c r="R187" s="7"/>
+      <c r="S187" s="7"/>
+      <c r="T187" s="7"/>
+      <c r="U187" s="7"/>
+    </row>
+    <row r="188" spans="1:21" ht="15">
+      <c r="A188" s="7">
+        <v>209</v>
+      </c>
+      <c r="B188" s="2">
+        <v>46266.609722222202</v>
+      </c>
+      <c r="C188" s="2">
+        <v>46266.610196759299</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H188" s="3"/>
+      <c r="I188" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="J188" s="3"/>
+      <c r="K188" s="6"/>
+      <c r="L188" s="3"/>
+      <c r="M188" s="3"/>
+      <c r="N188" s="3"/>
+      <c r="O188" s="3"/>
+      <c r="P188" s="3"/>
+      <c r="Q188" s="7"/>
+      <c r="R188" s="7"/>
+      <c r="S188" s="7"/>
+      <c r="T188" s="7"/>
+      <c r="U188" s="7"/>
+    </row>
+    <row r="189" spans="1:21" ht="15">
+      <c r="A189" s="7">
+        <v>210</v>
+      </c>
+      <c r="B189" s="2">
+        <v>46266.621724536999</v>
+      </c>
+      <c r="C189" s="2">
+        <v>46266.622175925899</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H189" s="3"/>
+      <c r="I189" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J189" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="K189" s="6"/>
+      <c r="L189" s="3"/>
+      <c r="M189" s="3"/>
+      <c r="N189" s="3"/>
+      <c r="O189" s="3"/>
+      <c r="P189" s="3"/>
+      <c r="Q189" s="7"/>
+      <c r="R189" s="7"/>
+      <c r="S189" s="7"/>
+      <c r="T189" s="7"/>
+      <c r="U189" s="7"/>
+    </row>
+    <row r="190" spans="1:21" ht="15">
+      <c r="A190" s="7">
+        <v>211</v>
+      </c>
+      <c r="B190" s="2">
+        <v>46266.622418981497</v>
+      </c>
+      <c r="C190" s="2">
+        <v>46266.624166666697</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H190" s="3"/>
+      <c r="I190" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J190" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="K190" s="6"/>
+      <c r="L190" s="3"/>
+      <c r="M190" s="3"/>
+      <c r="N190" s="3"/>
+      <c r="O190" s="3"/>
+      <c r="P190" s="3"/>
+      <c r="Q190" s="7"/>
+      <c r="R190" s="7"/>
+      <c r="S190" s="7"/>
+      <c r="T190" s="7"/>
+      <c r="U190" s="7"/>
+    </row>
+    <row r="191" spans="1:21" ht="15">
+      <c r="A191" s="7">
+        <v>212</v>
+      </c>
+      <c r="B191" s="2">
+        <v>46266.622222222199</v>
+      </c>
+      <c r="C191" s="2">
+        <v>46266.626597222203</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H191" s="3"/>
+      <c r="I191" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J191" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="K191" s="6"/>
+      <c r="L191" s="3"/>
+      <c r="M191" s="3"/>
+      <c r="N191" s="3"/>
+      <c r="O191" s="3"/>
+      <c r="P191" s="3"/>
+      <c r="Q191" s="7"/>
+      <c r="R191" s="7"/>
+      <c r="S191" s="7"/>
+      <c r="T191" s="7"/>
+      <c r="U191" s="7"/>
+    </row>
+    <row r="192" spans="1:21" ht="15">
+      <c r="A192" s="7">
+        <v>213</v>
+      </c>
+      <c r="B192" s="2">
+        <v>46266.626469907402</v>
+      </c>
+      <c r="C192" s="2">
+        <v>46266.627268518503</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="I192" s="7"/>
+      <c r="J192" s="3"/>
+      <c r="K192" s="6"/>
+      <c r="L192" s="3"/>
+      <c r="M192" s="3"/>
+      <c r="N192" s="3"/>
+      <c r="O192" s="3"/>
+      <c r="P192" s="3"/>
+      <c r="Q192" s="7"/>
+      <c r="R192" s="7"/>
+      <c r="S192" s="7"/>
+      <c r="T192" s="7"/>
+      <c r="U192" s="7"/>
+    </row>
+    <row r="193" spans="1:21" ht="15">
+      <c r="A193" s="7">
+        <v>214</v>
+      </c>
+      <c r="B193" s="2">
+        <v>46266.627407407403</v>
+      </c>
+      <c r="C193" s="2">
+        <v>46266.630868055603</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H193" s="3"/>
+      <c r="I193" s="7"/>
+      <c r="J193" s="3"/>
+      <c r="K193" s="6"/>
+      <c r="L193" s="3"/>
+      <c r="M193" s="3"/>
+      <c r="N193" s="3"/>
+      <c r="O193" s="3"/>
+      <c r="P193" s="3"/>
+      <c r="Q193" s="7"/>
+      <c r="R193" s="7"/>
+      <c r="S193" s="7"/>
+      <c r="T193" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="U193" s="7"/>
+    </row>
+    <row r="194" spans="1:21" ht="15">
+      <c r="A194" s="7">
+        <v>215</v>
+      </c>
+      <c r="B194" s="2">
+        <v>46266.636168981502</v>
+      </c>
+      <c r="C194" s="2">
+        <v>46266.636932870402</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F194" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H194" s="3"/>
+      <c r="I194" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J194" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="K194" s="6"/>
+      <c r="L194" s="3"/>
+      <c r="M194" s="3"/>
+      <c r="N194" s="3"/>
+      <c r="O194" s="3"/>
+      <c r="P194" s="3"/>
+      <c r="Q194" s="7"/>
+      <c r="R194" s="7"/>
+      <c r="S194" s="7"/>
+      <c r="T194" s="7"/>
+      <c r="U194" s="7"/>
+    </row>
+    <row r="195" spans="1:21" ht="15">
+      <c r="A195" s="7">
+        <v>216</v>
+      </c>
+      <c r="B195" s="2">
+        <v>46266.637476851902</v>
+      </c>
+      <c r="C195" s="2">
+        <v>46266.637858796297</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H195" s="3"/>
+      <c r="I195" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J195" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="K195" s="6"/>
+      <c r="L195" s="3"/>
+      <c r="M195" s="3"/>
+      <c r="N195" s="3"/>
+      <c r="O195" s="3"/>
+      <c r="P195" s="3"/>
+      <c r="Q195" s="7"/>
+      <c r="R195" s="7"/>
+      <c r="S195" s="7"/>
+      <c r="T195" s="7"/>
+      <c r="U195" s="7"/>
+    </row>
+    <row r="196" spans="1:21" ht="15">
+      <c r="A196" s="7">
+        <v>217</v>
+      </c>
+      <c r="B196" s="2">
+        <v>46266.637326388904</v>
+      </c>
+      <c r="C196" s="2">
+        <v>46266.638217592597</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H196" s="3"/>
+      <c r="I196" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J196" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="K196" s="6"/>
+      <c r="L196" s="3"/>
+      <c r="M196" s="3"/>
+      <c r="N196" s="3"/>
+      <c r="O196" s="3"/>
+      <c r="P196" s="3"/>
+      <c r="Q196" s="7"/>
+      <c r="R196" s="7"/>
+      <c r="S196" s="7"/>
+      <c r="T196" s="7"/>
+      <c r="U196" s="7"/>
+    </row>
+    <row r="197" spans="1:21" ht="15">
+      <c r="A197" s="7">
+        <v>218</v>
+      </c>
+      <c r="B197" s="2">
+        <v>46266.645312499997</v>
+      </c>
+      <c r="C197" s="2">
+        <v>46266.646539351903</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H197" s="3"/>
+      <c r="I197" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J197" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="K197" s="6"/>
+      <c r="L197" s="3"/>
+      <c r="M197" s="3"/>
+      <c r="N197" s="3"/>
+      <c r="O197" s="3"/>
+      <c r="P197" s="3"/>
+      <c r="Q197" s="7"/>
+      <c r="R197" s="7"/>
+      <c r="S197" s="7"/>
+      <c r="T197" s="7"/>
+      <c r="U197" s="7"/>
+    </row>
+    <row r="198" spans="1:21" ht="15">
+      <c r="A198" s="7">
+        <v>219</v>
+      </c>
+      <c r="B198" s="2">
+        <v>46266.6542708333</v>
+      </c>
+      <c r="C198" s="2">
+        <v>46266.656458333302</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H198" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="I198" s="7"/>
+      <c r="J198" s="3"/>
+      <c r="K198" s="6"/>
+      <c r="L198" s="3"/>
+      <c r="M198" s="3"/>
+      <c r="N198" s="3"/>
+      <c r="O198" s="3"/>
+      <c r="P198" s="3"/>
+      <c r="Q198" s="7"/>
+      <c r="R198" s="7"/>
+      <c r="S198" s="7"/>
+      <c r="T198" s="7"/>
+      <c r="U198" s="7"/>
+    </row>
+    <row r="199" spans="1:21" ht="15">
+      <c r="A199" s="7">
+        <v>220</v>
+      </c>
+      <c r="B199" s="2">
+        <v>46266.6581828704</v>
+      </c>
+      <c r="C199" s="2">
+        <v>46266.658333333296</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H199" s="3"/>
+      <c r="I199" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="J199" s="3"/>
+      <c r="K199" s="6"/>
+      <c r="L199" s="3"/>
+      <c r="M199" s="3"/>
+      <c r="N199" s="3"/>
+      <c r="O199" s="3"/>
+      <c r="P199" s="3"/>
+      <c r="Q199" s="7"/>
+      <c r="R199" s="7"/>
+      <c r="S199" s="7"/>
+      <c r="T199" s="7"/>
+      <c r="U199" s="7"/>
+    </row>
+    <row r="200" spans="1:21" ht="15">
+      <c r="A200" s="7">
+        <v>221</v>
+      </c>
+      <c r="B200" s="2">
+        <v>46266.671481481499</v>
+      </c>
+      <c r="C200" s="2">
+        <v>46266.672129629602</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H200" s="3"/>
+      <c r="I200" s="7"/>
+      <c r="J200" s="3"/>
+      <c r="K200" s="6"/>
+      <c r="L200" s="3"/>
+      <c r="M200" s="3"/>
+      <c r="N200" s="3"/>
+      <c r="O200" s="3"/>
+      <c r="P200" s="3"/>
+      <c r="Q200" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R200" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="S200" s="7"/>
+      <c r="T200" s="7"/>
+      <c r="U200" s="7"/>
+    </row>
+    <row r="201" spans="1:21" ht="15">
+      <c r="A201" s="7">
+        <v>222</v>
+      </c>
+      <c r="B201" s="2">
+        <v>46266.676712963003</v>
+      </c>
+      <c r="C201" s="2">
+        <v>46266.677650463003</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H201" s="3"/>
+      <c r="I201" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J201" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="K201" s="6"/>
+      <c r="L201" s="3"/>
+      <c r="M201" s="3"/>
+      <c r="N201" s="3"/>
+      <c r="O201" s="3"/>
+      <c r="P201" s="3"/>
+      <c r="Q201" s="7"/>
+      <c r="R201" s="7"/>
+      <c r="S201" s="7"/>
+      <c r="T201" s="7"/>
+      <c r="U201" s="7"/>
+    </row>
+    <row r="202" spans="1:21" ht="15">
+      <c r="A202" s="7">
+        <v>223</v>
+      </c>
+      <c r="B202" s="2">
+        <v>46266.679062499999</v>
+      </c>
+      <c r="C202" s="2">
+        <v>46266.680208333302</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H202" s="3"/>
+      <c r="I202" s="7"/>
+      <c r="J202" s="3"/>
+      <c r="K202" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="L202" s="3"/>
+      <c r="M202" s="3"/>
+      <c r="N202" s="3"/>
+      <c r="O202" s="3"/>
+      <c r="P202" s="3"/>
+      <c r="Q202" s="7"/>
+      <c r="R202" s="7"/>
+      <c r="S202" s="7"/>
+      <c r="T202" s="7"/>
+      <c r="U202" s="7"/>
+    </row>
+    <row r="203" spans="1:21" ht="15">
+      <c r="A203" s="7">
+        <v>224</v>
+      </c>
+      <c r="B203" s="2">
+        <v>46266.679872685199</v>
+      </c>
+      <c r="C203" s="2">
+        <v>46266.680486111101</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H203" s="3"/>
+      <c r="I203" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J203" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="K203" s="6"/>
+      <c r="L203" s="3"/>
+      <c r="M203" s="3"/>
+      <c r="N203" s="3"/>
+      <c r="O203" s="3"/>
+      <c r="P203" s="3"/>
+      <c r="Q203" s="7"/>
+      <c r="R203" s="7"/>
+      <c r="S203" s="7"/>
+      <c r="T203" s="7"/>
+      <c r="U203" s="7"/>
+    </row>
+    <row r="204" spans="1:21" ht="15">
+      <c r="A204" s="7">
+        <v>225</v>
+      </c>
+      <c r="B204" s="2">
+        <v>46266.681539351797</v>
+      </c>
+      <c r="C204" s="2">
+        <v>46266.683287036998</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H204" s="3"/>
+      <c r="I204" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J204" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="K204" s="6"/>
+      <c r="L204" s="3"/>
+      <c r="M204" s="3"/>
+      <c r="N204" s="3"/>
+      <c r="O204" s="3"/>
+      <c r="P204" s="3"/>
+      <c r="Q204" s="7"/>
+      <c r="R204" s="7"/>
+      <c r="S204" s="7"/>
+      <c r="T204" s="7"/>
+      <c r="U204" s="7"/>
+    </row>
+    <row r="205" spans="1:21" ht="15">
+      <c r="A205" s="7">
+        <v>226</v>
+      </c>
+      <c r="B205" s="2">
+        <v>46266.686655092599</v>
+      </c>
+      <c r="C205" s="2">
+        <v>46266.687442129602</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="I205" s="7"/>
+      <c r="J205" s="3"/>
+      <c r="K205" s="6"/>
+      <c r="L205" s="3"/>
+      <c r="M205" s="3"/>
+      <c r="N205" s="3"/>
+      <c r="O205" s="3"/>
+      <c r="P205" s="3"/>
+      <c r="Q205" s="7"/>
+      <c r="R205" s="7"/>
+      <c r="S205" s="7"/>
+      <c r="T205" s="7"/>
+      <c r="U205" s="7"/>
+    </row>
+    <row r="206" spans="1:21" ht="15">
+      <c r="A206" s="7">
+        <v>227</v>
+      </c>
+      <c r="B206" s="2">
+        <v>46266.677592592598</v>
+      </c>
+      <c r="C206" s="2">
+        <v>46266.7011458333</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H206" s="3"/>
+      <c r="I206" s="7"/>
+      <c r="J206" s="3"/>
+      <c r="K206" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="L206" s="3"/>
+      <c r="M206" s="3"/>
+      <c r="N206" s="3"/>
+      <c r="O206" s="3"/>
+      <c r="P206" s="3"/>
+      <c r="Q206" s="7"/>
+      <c r="R206" s="7"/>
+      <c r="S206" s="7"/>
+      <c r="T206" s="7"/>
+      <c r="U206" s="7"/>
+    </row>
+    <row r="207" spans="1:21" ht="15">
+      <c r="A207" s="7">
+        <v>228</v>
+      </c>
+      <c r="B207" s="2">
+        <v>46266.722847222198</v>
+      </c>
+      <c r="C207" s="2">
+        <v>46266.723668981504</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H207" s="3"/>
+      <c r="I207" s="7"/>
+      <c r="J207" s="3"/>
+      <c r="K207" s="6"/>
+      <c r="L207" s="3"/>
+      <c r="M207" s="3"/>
+      <c r="N207" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="O207" s="3"/>
+      <c r="P207" s="3"/>
+      <c r="Q207" s="7"/>
+      <c r="R207" s="7"/>
+      <c r="S207" s="7"/>
+      <c r="T207" s="7"/>
+      <c r="U207" s="7"/>
+    </row>
+    <row r="208" spans="1:21" ht="15">
+      <c r="A208" s="7">
+        <v>229</v>
+      </c>
+      <c r="B208" s="2">
+        <v>46266.779236111099</v>
+      </c>
+      <c r="C208" s="2">
+        <v>46266.779710648101</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H208" s="3"/>
+      <c r="I208" s="7"/>
+      <c r="J208" s="3"/>
+      <c r="K208" s="6"/>
+      <c r="L208" s="3"/>
+      <c r="M208" s="3"/>
+      <c r="N208" s="3"/>
+      <c r="O208" s="3"/>
+      <c r="P208" s="3"/>
+      <c r="Q208" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R208" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="S208" s="7"/>
+      <c r="T208" s="7"/>
+      <c r="U208" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="325" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{279D6B72-57BF-43AA-827D-137F335F6C30}"/>
+  <xr:revisionPtr revIDLastSave="328" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F27D59FF-ED99-4E25-AAC6-B99A0E1957C5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="460">
   <si>
     <t>Id</t>
   </si>
@@ -1398,6 +1398,24 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/IMG_3984_Starbucks%20El%20Rosario.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38119@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Lomas Verdes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Community_Board/IMG_1060_Starbucks%20Lomas%20Verd.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/IMG-20260901-WA0164_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/IMG-20260901-WA0112_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/IMG-20260901-WA0105_Enrique%20Cesar%20Flores.jpg</t>
   </si>
 </sst>
 </file>
@@ -1532,8 +1550,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U208" totalsRowShown="0">
-  <autoFilter ref="A1:U208" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U213" totalsRowShown="0">
+  <autoFilter ref="A1:U213" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1686,7 +1704,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="229" latestEventMarker="464">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="234" latestEventMarker="469">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2011,7 +2029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U208"/>
+  <dimension ref="A1:U213"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -8075,7 +8093,7 @@
       <c r="O176" s="3"/>
       <c r="P176" s="3"/>
     </row>
-    <row r="177" spans="1:21" ht="15">
+    <row r="177" spans="1:16" ht="15">
       <c r="A177">
         <v>198</v>
       </c>
@@ -8111,7 +8129,7 @@
       <c r="O177" s="3"/>
       <c r="P177" s="3"/>
     </row>
-    <row r="178" spans="1:21" ht="15">
+    <row r="178" spans="1:16" ht="15">
       <c r="A178">
         <v>199</v>
       </c>
@@ -8147,7 +8165,7 @@
       <c r="O178" s="3"/>
       <c r="P178" s="3"/>
     </row>
-    <row r="179" spans="1:21" ht="15">
+    <row r="179" spans="1:16" ht="15">
       <c r="A179">
         <v>200</v>
       </c>
@@ -8183,7 +8201,7 @@
       <c r="O179" s="3"/>
       <c r="P179" s="3"/>
     </row>
-    <row r="180" spans="1:21" ht="15">
+    <row r="180" spans="1:16" ht="15">
       <c r="A180">
         <v>201</v>
       </c>
@@ -8219,7 +8237,7 @@
       <c r="O180" s="3"/>
       <c r="P180" s="3"/>
     </row>
-    <row r="181" spans="1:21" ht="15">
+    <row r="181" spans="1:16" ht="15">
       <c r="A181">
         <v>202</v>
       </c>
@@ -8255,7 +8273,7 @@
       <c r="O181" s="3"/>
       <c r="P181" s="3"/>
     </row>
-    <row r="182" spans="1:21" ht="15">
+    <row r="182" spans="1:16" ht="15">
       <c r="A182">
         <v>203</v>
       </c>
@@ -8291,7 +8309,7 @@
       <c r="O182" s="3"/>
       <c r="P182" s="3"/>
     </row>
-    <row r="183" spans="1:21" ht="15">
+    <row r="183" spans="1:16" ht="15">
       <c r="A183">
         <v>204</v>
       </c>
@@ -8327,7 +8345,7 @@
       <c r="O183" s="3"/>
       <c r="P183" s="3"/>
     </row>
-    <row r="184" spans="1:21" ht="15">
+    <row r="184" spans="1:16" ht="15">
       <c r="A184">
         <v>205</v>
       </c>
@@ -8363,7 +8381,7 @@
       <c r="O184" s="3"/>
       <c r="P184" s="3"/>
     </row>
-    <row r="185" spans="1:21" ht="15">
+    <row r="185" spans="1:16" ht="15">
       <c r="A185">
         <v>206</v>
       </c>
@@ -8399,7 +8417,7 @@
       <c r="O185" s="3"/>
       <c r="P185" s="3"/>
     </row>
-    <row r="186" spans="1:21" ht="15">
+    <row r="186" spans="1:16" ht="15">
       <c r="A186">
         <v>207</v>
       </c>
@@ -8432,8 +8450,8 @@
       <c r="O186" s="3"/>
       <c r="P186" s="3"/>
     </row>
-    <row r="187" spans="1:21" ht="15">
-      <c r="A187" s="7">
+    <row r="187" spans="1:16" ht="15">
+      <c r="A187">
         <v>208</v>
       </c>
       <c r="B187" s="2">
@@ -8455,7 +8473,7 @@
         <v>60</v>
       </c>
       <c r="H187" s="3"/>
-      <c r="I187" s="7" t="s">
+      <c r="I187" t="s">
         <v>61</v>
       </c>
       <c r="J187" s="3" t="s">
@@ -8467,14 +8485,9 @@
       <c r="N187" s="3"/>
       <c r="O187" s="3"/>
       <c r="P187" s="3"/>
-      <c r="Q187" s="7"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="7"/>
-      <c r="T187" s="7"/>
-      <c r="U187" s="7"/>
-    </row>
-    <row r="188" spans="1:21" ht="15">
-      <c r="A188" s="7">
+    </row>
+    <row r="188" spans="1:16" ht="15">
+      <c r="A188">
         <v>209</v>
       </c>
       <c r="B188" s="2">
@@ -8496,7 +8509,7 @@
         <v>60</v>
       </c>
       <c r="H188" s="3"/>
-      <c r="I188" s="7" t="s">
+      <c r="I188" t="s">
         <v>398</v>
       </c>
       <c r="J188" s="3"/>
@@ -8506,14 +8519,9 @@
       <c r="N188" s="3"/>
       <c r="O188" s="3"/>
       <c r="P188" s="3"/>
-      <c r="Q188" s="7"/>
-      <c r="R188" s="7"/>
-      <c r="S188" s="7"/>
-      <c r="T188" s="7"/>
-      <c r="U188" s="7"/>
-    </row>
-    <row r="189" spans="1:21" ht="15">
-      <c r="A189" s="7">
+    </row>
+    <row r="189" spans="1:16" ht="15">
+      <c r="A189">
         <v>210</v>
       </c>
       <c r="B189" s="2">
@@ -8535,7 +8543,7 @@
         <v>60</v>
       </c>
       <c r="H189" s="3"/>
-      <c r="I189" s="7" t="s">
+      <c r="I189" t="s">
         <v>61</v>
       </c>
       <c r="J189" s="3" t="s">
@@ -8547,14 +8555,9 @@
       <c r="N189" s="3"/>
       <c r="O189" s="3"/>
       <c r="P189" s="3"/>
-      <c r="Q189" s="7"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="7"/>
-      <c r="T189" s="7"/>
-      <c r="U189" s="7"/>
-    </row>
-    <row r="190" spans="1:21" ht="15">
-      <c r="A190" s="7">
+    </row>
+    <row r="190" spans="1:16" ht="15">
+      <c r="A190">
         <v>211</v>
       </c>
       <c r="B190" s="2">
@@ -8576,7 +8579,7 @@
         <v>60</v>
       </c>
       <c r="H190" s="3"/>
-      <c r="I190" s="7" t="s">
+      <c r="I190" t="s">
         <v>61</v>
       </c>
       <c r="J190" s="3" t="s">
@@ -8588,14 +8591,9 @@
       <c r="N190" s="3"/>
       <c r="O190" s="3"/>
       <c r="P190" s="3"/>
-      <c r="Q190" s="7"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="7"/>
-      <c r="T190" s="7"/>
-      <c r="U190" s="7"/>
-    </row>
-    <row r="191" spans="1:21" ht="15">
-      <c r="A191" s="7">
+    </row>
+    <row r="191" spans="1:16" ht="15">
+      <c r="A191">
         <v>212</v>
       </c>
       <c r="B191" s="2">
@@ -8617,7 +8615,7 @@
         <v>60</v>
       </c>
       <c r="H191" s="3"/>
-      <c r="I191" s="7" t="s">
+      <c r="I191" t="s">
         <v>61</v>
       </c>
       <c r="J191" s="3" t="s">
@@ -8629,14 +8627,9 @@
       <c r="N191" s="3"/>
       <c r="O191" s="3"/>
       <c r="P191" s="3"/>
-      <c r="Q191" s="7"/>
-      <c r="R191" s="7"/>
-      <c r="S191" s="7"/>
-      <c r="T191" s="7"/>
-      <c r="U191" s="7"/>
-    </row>
-    <row r="192" spans="1:21" ht="15">
-      <c r="A192" s="7">
+    </row>
+    <row r="192" spans="1:16" ht="15">
+      <c r="A192">
         <v>213</v>
       </c>
       <c r="B192" s="2">
@@ -8660,7 +8653,6 @@
       <c r="H192" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="I192" s="7"/>
       <c r="J192" s="3"/>
       <c r="K192" s="6"/>
       <c r="L192" s="3"/>
@@ -8668,14 +8660,9 @@
       <c r="N192" s="3"/>
       <c r="O192" s="3"/>
       <c r="P192" s="3"/>
-      <c r="Q192" s="7"/>
-      <c r="R192" s="7"/>
-      <c r="S192" s="7"/>
-      <c r="T192" s="7"/>
-      <c r="U192" s="7"/>
-    </row>
-    <row r="193" spans="1:21" ht="15">
-      <c r="A193" s="7">
+    </row>
+    <row r="193" spans="1:20" ht="15">
+      <c r="A193">
         <v>214</v>
       </c>
       <c r="B193" s="2">
@@ -8697,7 +8684,6 @@
         <v>286</v>
       </c>
       <c r="H193" s="3"/>
-      <c r="I193" s="7"/>
       <c r="J193" s="3"/>
       <c r="K193" s="6"/>
       <c r="L193" s="3"/>
@@ -8705,16 +8691,12 @@
       <c r="N193" s="3"/>
       <c r="O193" s="3"/>
       <c r="P193" s="3"/>
-      <c r="Q193" s="7"/>
-      <c r="R193" s="7"/>
-      <c r="S193" s="7"/>
-      <c r="T193" s="7" t="s">
+      <c r="T193" t="s">
         <v>437</v>
       </c>
-      <c r="U193" s="7"/>
-    </row>
-    <row r="194" spans="1:21" ht="15">
-      <c r="A194" s="7">
+    </row>
+    <row r="194" spans="1:20" ht="15">
+      <c r="A194">
         <v>215</v>
       </c>
       <c r="B194" s="2">
@@ -8736,7 +8718,7 @@
         <v>60</v>
       </c>
       <c r="H194" s="3"/>
-      <c r="I194" s="7" t="s">
+      <c r="I194" t="s">
         <v>61</v>
       </c>
       <c r="J194" s="3" t="s">
@@ -8748,14 +8730,9 @@
       <c r="N194" s="3"/>
       <c r="O194" s="3"/>
       <c r="P194" s="3"/>
-      <c r="Q194" s="7"/>
-      <c r="R194" s="7"/>
-      <c r="S194" s="7"/>
-      <c r="T194" s="7"/>
-      <c r="U194" s="7"/>
-    </row>
-    <row r="195" spans="1:21" ht="15">
-      <c r="A195" s="7">
+    </row>
+    <row r="195" spans="1:20" ht="15">
+      <c r="A195">
         <v>216</v>
       </c>
       <c r="B195" s="2">
@@ -8777,7 +8754,7 @@
         <v>60</v>
       </c>
       <c r="H195" s="3"/>
-      <c r="I195" s="7" t="s">
+      <c r="I195" t="s">
         <v>61</v>
       </c>
       <c r="J195" s="3" t="s">
@@ -8789,14 +8766,9 @@
       <c r="N195" s="3"/>
       <c r="O195" s="3"/>
       <c r="P195" s="3"/>
-      <c r="Q195" s="7"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="7"/>
-      <c r="T195" s="7"/>
-      <c r="U195" s="7"/>
-    </row>
-    <row r="196" spans="1:21" ht="15">
-      <c r="A196" s="7">
+    </row>
+    <row r="196" spans="1:20" ht="15">
+      <c r="A196">
         <v>217</v>
       </c>
       <c r="B196" s="2">
@@ -8818,7 +8790,7 @@
         <v>60</v>
       </c>
       <c r="H196" s="3"/>
-      <c r="I196" s="7" t="s">
+      <c r="I196" t="s">
         <v>61</v>
       </c>
       <c r="J196" s="3" t="s">
@@ -8830,14 +8802,9 @@
       <c r="N196" s="3"/>
       <c r="O196" s="3"/>
       <c r="P196" s="3"/>
-      <c r="Q196" s="7"/>
-      <c r="R196" s="7"/>
-      <c r="S196" s="7"/>
-      <c r="T196" s="7"/>
-      <c r="U196" s="7"/>
-    </row>
-    <row r="197" spans="1:21" ht="15">
-      <c r="A197" s="7">
+    </row>
+    <row r="197" spans="1:20" ht="15">
+      <c r="A197">
         <v>218</v>
       </c>
       <c r="B197" s="2">
@@ -8859,7 +8826,7 @@
         <v>60</v>
       </c>
       <c r="H197" s="3"/>
-      <c r="I197" s="7" t="s">
+      <c r="I197" t="s">
         <v>61</v>
       </c>
       <c r="J197" s="3" t="s">
@@ -8871,14 +8838,9 @@
       <c r="N197" s="3"/>
       <c r="O197" s="3"/>
       <c r="P197" s="3"/>
-      <c r="Q197" s="7"/>
-      <c r="R197" s="7"/>
-      <c r="S197" s="7"/>
-      <c r="T197" s="7"/>
-      <c r="U197" s="7"/>
-    </row>
-    <row r="198" spans="1:21" ht="15">
-      <c r="A198" s="7">
+    </row>
+    <row r="198" spans="1:20" ht="15">
+      <c r="A198">
         <v>219</v>
       </c>
       <c r="B198" s="2">
@@ -8902,7 +8864,6 @@
       <c r="H198" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="I198" s="7"/>
       <c r="J198" s="3"/>
       <c r="K198" s="6"/>
       <c r="L198" s="3"/>
@@ -8910,14 +8871,9 @@
       <c r="N198" s="3"/>
       <c r="O198" s="3"/>
       <c r="P198" s="3"/>
-      <c r="Q198" s="7"/>
-      <c r="R198" s="7"/>
-      <c r="S198" s="7"/>
-      <c r="T198" s="7"/>
-      <c r="U198" s="7"/>
-    </row>
-    <row r="199" spans="1:21" ht="15">
-      <c r="A199" s="7">
+    </row>
+    <row r="199" spans="1:20" ht="15">
+      <c r="A199">
         <v>220</v>
       </c>
       <c r="B199" s="2">
@@ -8939,7 +8895,7 @@
         <v>60</v>
       </c>
       <c r="H199" s="3"/>
-      <c r="I199" s="7" t="s">
+      <c r="I199" t="s">
         <v>398</v>
       </c>
       <c r="J199" s="3"/>
@@ -8949,14 +8905,9 @@
       <c r="N199" s="3"/>
       <c r="O199" s="3"/>
       <c r="P199" s="3"/>
-      <c r="Q199" s="7"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="7"/>
-      <c r="T199" s="7"/>
-      <c r="U199" s="7"/>
-    </row>
-    <row r="200" spans="1:21" ht="15">
-      <c r="A200" s="7">
+    </row>
+    <row r="200" spans="1:20" ht="15">
+      <c r="A200">
         <v>221</v>
       </c>
       <c r="B200" s="2">
@@ -8978,7 +8929,6 @@
         <v>106</v>
       </c>
       <c r="H200" s="3"/>
-      <c r="I200" s="7"/>
       <c r="J200" s="3"/>
       <c r="K200" s="6"/>
       <c r="L200" s="3"/>
@@ -8986,18 +8936,15 @@
       <c r="N200" s="3"/>
       <c r="O200" s="3"/>
       <c r="P200" s="3"/>
-      <c r="Q200" s="7" t="s">
+      <c r="Q200" t="s">
         <v>61</v>
       </c>
-      <c r="R200" s="7" t="s">
+      <c r="R200" t="s">
         <v>445</v>
       </c>
-      <c r="S200" s="7"/>
-      <c r="T200" s="7"/>
-      <c r="U200" s="7"/>
-    </row>
-    <row r="201" spans="1:21" ht="15">
-      <c r="A201" s="7">
+    </row>
+    <row r="201" spans="1:20" ht="15">
+      <c r="A201">
         <v>222</v>
       </c>
       <c r="B201" s="2">
@@ -9019,7 +8966,7 @@
         <v>60</v>
       </c>
       <c r="H201" s="3"/>
-      <c r="I201" s="7" t="s">
+      <c r="I201" t="s">
         <v>61</v>
       </c>
       <c r="J201" s="3" t="s">
@@ -9031,14 +8978,9 @@
       <c r="N201" s="3"/>
       <c r="O201" s="3"/>
       <c r="P201" s="3"/>
-      <c r="Q201" s="7"/>
-      <c r="R201" s="7"/>
-      <c r="S201" s="7"/>
-      <c r="T201" s="7"/>
-      <c r="U201" s="7"/>
-    </row>
-    <row r="202" spans="1:21" ht="15">
-      <c r="A202" s="7">
+    </row>
+    <row r="202" spans="1:20" ht="15">
+      <c r="A202">
         <v>223</v>
       </c>
       <c r="B202" s="2">
@@ -9060,7 +9002,6 @@
         <v>38</v>
       </c>
       <c r="H202" s="3"/>
-      <c r="I202" s="7"/>
       <c r="J202" s="3"/>
       <c r="K202" s="6" t="s">
         <v>447</v>
@@ -9070,14 +9011,9 @@
       <c r="N202" s="3"/>
       <c r="O202" s="3"/>
       <c r="P202" s="3"/>
-      <c r="Q202" s="7"/>
-      <c r="R202" s="7"/>
-      <c r="S202" s="7"/>
-      <c r="T202" s="7"/>
-      <c r="U202" s="7"/>
-    </row>
-    <row r="203" spans="1:21" ht="15">
-      <c r="A203" s="7">
+    </row>
+    <row r="203" spans="1:20" ht="15">
+      <c r="A203">
         <v>224</v>
       </c>
       <c r="B203" s="2">
@@ -9099,7 +9035,7 @@
         <v>60</v>
       </c>
       <c r="H203" s="3"/>
-      <c r="I203" s="7" t="s">
+      <c r="I203" t="s">
         <v>61</v>
       </c>
       <c r="J203" s="3" t="s">
@@ -9111,14 +9047,9 @@
       <c r="N203" s="3"/>
       <c r="O203" s="3"/>
       <c r="P203" s="3"/>
-      <c r="Q203" s="7"/>
-      <c r="R203" s="7"/>
-      <c r="S203" s="7"/>
-      <c r="T203" s="7"/>
-      <c r="U203" s="7"/>
-    </row>
-    <row r="204" spans="1:21" ht="15">
-      <c r="A204" s="7">
+    </row>
+    <row r="204" spans="1:20" ht="15">
+      <c r="A204">
         <v>225</v>
       </c>
       <c r="B204" s="2">
@@ -9140,7 +9071,7 @@
         <v>60</v>
       </c>
       <c r="H204" s="3"/>
-      <c r="I204" s="7" t="s">
+      <c r="I204" t="s">
         <v>61</v>
       </c>
       <c r="J204" s="3" t="s">
@@ -9152,14 +9083,9 @@
       <c r="N204" s="3"/>
       <c r="O204" s="3"/>
       <c r="P204" s="3"/>
-      <c r="Q204" s="7"/>
-      <c r="R204" s="7"/>
-      <c r="S204" s="7"/>
-      <c r="T204" s="7"/>
-      <c r="U204" s="7"/>
-    </row>
-    <row r="205" spans="1:21" ht="15">
-      <c r="A205" s="7">
+    </row>
+    <row r="205" spans="1:20" ht="15">
+      <c r="A205">
         <v>226</v>
       </c>
       <c r="B205" s="2">
@@ -9183,7 +9109,6 @@
       <c r="H205" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="I205" s="7"/>
       <c r="J205" s="3"/>
       <c r="K205" s="6"/>
       <c r="L205" s="3"/>
@@ -9191,14 +9116,9 @@
       <c r="N205" s="3"/>
       <c r="O205" s="3"/>
       <c r="P205" s="3"/>
-      <c r="Q205" s="7"/>
-      <c r="R205" s="7"/>
-      <c r="S205" s="7"/>
-      <c r="T205" s="7"/>
-      <c r="U205" s="7"/>
-    </row>
-    <row r="206" spans="1:21" ht="15">
-      <c r="A206" s="7">
+    </row>
+    <row r="206" spans="1:20" ht="15">
+      <c r="A206">
         <v>227</v>
       </c>
       <c r="B206" s="2">
@@ -9220,7 +9140,6 @@
         <v>38</v>
       </c>
       <c r="H206" s="3"/>
-      <c r="I206" s="7"/>
       <c r="J206" s="3"/>
       <c r="K206" s="6" t="s">
         <v>451</v>
@@ -9230,14 +9149,9 @@
       <c r="N206" s="3"/>
       <c r="O206" s="3"/>
       <c r="P206" s="3"/>
-      <c r="Q206" s="7"/>
-      <c r="R206" s="7"/>
-      <c r="S206" s="7"/>
-      <c r="T206" s="7"/>
-      <c r="U206" s="7"/>
-    </row>
-    <row r="207" spans="1:21" ht="15">
-      <c r="A207" s="7">
+    </row>
+    <row r="207" spans="1:20" ht="15">
+      <c r="A207">
         <v>228</v>
       </c>
       <c r="B207" s="2">
@@ -9259,7 +9173,6 @@
         <v>217</v>
       </c>
       <c r="H207" s="3"/>
-      <c r="I207" s="7"/>
       <c r="J207" s="3"/>
       <c r="K207" s="6"/>
       <c r="L207" s="3"/>
@@ -9269,14 +9182,9 @@
       </c>
       <c r="O207" s="3"/>
       <c r="P207" s="3"/>
-      <c r="Q207" s="7"/>
-      <c r="R207" s="7"/>
-      <c r="S207" s="7"/>
-      <c r="T207" s="7"/>
-      <c r="U207" s="7"/>
-    </row>
-    <row r="208" spans="1:21" ht="15">
-      <c r="A208" s="7">
+    </row>
+    <row r="208" spans="1:20" ht="15">
+      <c r="A208">
         <v>229</v>
       </c>
       <c r="B208" s="2">
@@ -9298,7 +9206,6 @@
         <v>106</v>
       </c>
       <c r="H208" s="3"/>
-      <c r="I208" s="7"/>
       <c r="J208" s="3"/>
       <c r="K208" s="6"/>
       <c r="L208" s="3"/>
@@ -9306,15 +9213,213 @@
       <c r="N208" s="3"/>
       <c r="O208" s="3"/>
       <c r="P208" s="3"/>
-      <c r="Q208" s="7" t="s">
+      <c r="Q208" t="s">
         <v>61</v>
       </c>
-      <c r="R208" s="7" t="s">
+      <c r="R208" t="s">
         <v>453</v>
       </c>
-      <c r="S208" s="7"/>
-      <c r="T208" s="7"/>
-      <c r="U208" s="7"/>
+    </row>
+    <row r="209" spans="1:21" ht="15">
+      <c r="A209" s="7">
+        <v>230</v>
+      </c>
+      <c r="B209" s="2">
+        <v>46266.824201388903</v>
+      </c>
+      <c r="C209" s="2">
+        <v>46266.824756944399</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H209" s="3"/>
+      <c r="I209" s="7"/>
+      <c r="J209" s="3"/>
+      <c r="K209" s="6"/>
+      <c r="L209" s="3"/>
+      <c r="M209" s="3"/>
+      <c r="N209" s="3"/>
+      <c r="O209" s="3"/>
+      <c r="P209" s="3"/>
+      <c r="Q209" s="7"/>
+      <c r="R209" s="7"/>
+      <c r="S209" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="T209" s="7"/>
+      <c r="U209" s="7"/>
+    </row>
+    <row r="210" spans="1:21" ht="15">
+      <c r="A210" s="7">
+        <v>231</v>
+      </c>
+      <c r="B210" s="2">
+        <v>46266.847962963002</v>
+      </c>
+      <c r="C210" s="2">
+        <v>46266.848321759302</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H210" s="3"/>
+      <c r="I210" s="7"/>
+      <c r="J210" s="3"/>
+      <c r="K210" s="6"/>
+      <c r="L210" s="3"/>
+      <c r="M210" s="3"/>
+      <c r="N210" s="3"/>
+      <c r="O210" s="3"/>
+      <c r="P210" s="3"/>
+      <c r="Q210" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R210" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="S210" s="7"/>
+      <c r="T210" s="7"/>
+      <c r="U210" s="7"/>
+    </row>
+    <row r="211" spans="1:21" ht="15">
+      <c r="A211" s="7">
+        <v>232</v>
+      </c>
+      <c r="B211" s="2">
+        <v>46266.848368055602</v>
+      </c>
+      <c r="C211" s="2">
+        <v>46266.848796296297</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H211" s="3"/>
+      <c r="I211" s="7"/>
+      <c r="J211" s="3"/>
+      <c r="K211" s="6"/>
+      <c r="L211" s="3"/>
+      <c r="M211" s="3"/>
+      <c r="N211" s="3"/>
+      <c r="O211" s="3"/>
+      <c r="P211" s="3"/>
+      <c r="Q211" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R211" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="S211" s="7"/>
+      <c r="T211" s="7"/>
+      <c r="U211" s="7"/>
+    </row>
+    <row r="212" spans="1:21" ht="15">
+      <c r="A212" s="7">
+        <v>233</v>
+      </c>
+      <c r="B212" s="2">
+        <v>46266.849212963003</v>
+      </c>
+      <c r="C212" s="2">
+        <v>46266.849421296298</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H212" s="3"/>
+      <c r="I212" s="7"/>
+      <c r="J212" s="3"/>
+      <c r="K212" s="6"/>
+      <c r="L212" s="3"/>
+      <c r="M212" s="3"/>
+      <c r="N212" s="3"/>
+      <c r="O212" s="3"/>
+      <c r="P212" s="3"/>
+      <c r="Q212" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R212" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="S212" s="7"/>
+      <c r="T212" s="7"/>
+      <c r="U212" s="7"/>
+    </row>
+    <row r="213" spans="1:21" ht="15">
+      <c r="A213" s="7">
+        <v>234</v>
+      </c>
+      <c r="B213" s="2">
+        <v>46266.851400462998</v>
+      </c>
+      <c r="C213" s="2">
+        <v>46266.8515625</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H213" s="3"/>
+      <c r="I213" s="7"/>
+      <c r="J213" s="3"/>
+      <c r="K213" s="6"/>
+      <c r="L213" s="3"/>
+      <c r="M213" s="3"/>
+      <c r="N213" s="3"/>
+      <c r="O213" s="3"/>
+      <c r="P213" s="3"/>
+      <c r="Q213" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="R213" s="7"/>
+      <c r="S213" s="7"/>
+      <c r="T213" s="7"/>
+      <c r="U213" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="328" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F27D59FF-ED99-4E25-AAC6-B99A0E1957C5}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF8FD984-1A50-4DEB-9FCA-014E392873F2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="466">
   <si>
     <t>Id</t>
   </si>
@@ -1416,13 +1416,31 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/IMG-20260901-WA0105_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/IMG-20260901-WA0238_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260901-WA0021_Starbucks%20Eduardo%20Mo.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17883585899558884053275389821232_Starbucks%20ITESM%20Esta.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/20260828_232410_Martin%20Gerardo%20Herre.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Punta%20Nort.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17883675463346775160730658457831_Enrique%20Cesar%20Flores.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1550,8 +1568,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U213" totalsRowShown="0">
-  <autoFilter ref="A1:U213" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U219" totalsRowShown="0">
+  <autoFilter ref="A1:U219" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1704,7 +1722,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="234" latestEventMarker="469">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="240" latestEventMarker="475">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2029,23 +2047,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U213"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <dimension ref="A1:U219"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" customWidth="1"/>
     <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.1796875" customWidth="1"/>
+    <col min="5" max="5" width="35.1796875" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="19" customWidth="1"/>
-    <col min="19" max="19" width="42.140625" customWidth="1"/>
+    <col min="19" max="19" width="42.1796875" customWidth="1"/>
     <col min="20" max="21" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2110,7 +2128,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>13</v>
       </c>
@@ -2136,7 +2154,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>17</v>
       </c>
@@ -2169,7 +2187,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2202,7 +2220,7 @@
       </c>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>20</v>
       </c>
@@ -2235,7 +2253,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>21</v>
       </c>
@@ -2268,7 +2286,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>22</v>
       </c>
@@ -2301,7 +2319,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>23</v>
       </c>
@@ -2335,7 +2353,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>24</v>
       </c>
@@ -2369,7 +2387,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>25</v>
       </c>
@@ -2403,7 +2421,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>26</v>
       </c>
@@ -2436,7 +2454,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>27</v>
       </c>
@@ -2472,7 +2490,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>28</v>
       </c>
@@ -2505,7 +2523,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>29</v>
       </c>
@@ -2539,7 +2557,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>30</v>
       </c>
@@ -2572,7 +2590,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>31</v>
       </c>
@@ -2605,7 +2623,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>32</v>
       </c>
@@ -2639,7 +2657,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>33</v>
       </c>
@@ -2672,7 +2690,7 @@
       </c>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>34</v>
       </c>
@@ -2705,7 +2723,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>35</v>
       </c>
@@ -2738,7 +2756,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>36</v>
       </c>
@@ -2771,7 +2789,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>37</v>
       </c>
@@ -2805,7 +2823,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>38</v>
       </c>
@@ -2839,7 +2857,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>39</v>
       </c>
@@ -2873,7 +2891,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>40</v>
       </c>
@@ -2907,7 +2925,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>41</v>
       </c>
@@ -2940,7 +2958,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>42</v>
       </c>
@@ -2974,7 +2992,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>43</v>
       </c>
@@ -3008,7 +3026,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>44</v>
       </c>
@@ -3042,7 +3060,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>45</v>
       </c>
@@ -3076,7 +3094,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>46</v>
       </c>
@@ -3110,7 +3128,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>47</v>
       </c>
@@ -3144,7 +3162,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>48</v>
       </c>
@@ -3177,7 +3195,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>49</v>
       </c>
@@ -3211,7 +3229,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>50</v>
       </c>
@@ -3245,7 +3263,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>51</v>
       </c>
@@ -3279,7 +3297,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>52</v>
       </c>
@@ -3312,7 +3330,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>54</v>
       </c>
@@ -3345,7 +3363,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>55</v>
       </c>
@@ -3378,7 +3396,7 @@
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>56</v>
       </c>
@@ -3412,7 +3430,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>57</v>
       </c>
@@ -3446,7 +3464,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>58</v>
       </c>
@@ -3480,7 +3498,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>59</v>
       </c>
@@ -3514,7 +3532,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>60</v>
       </c>
@@ -3548,7 +3566,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>61</v>
       </c>
@@ -3582,7 +3600,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>62</v>
       </c>
@@ -3616,7 +3634,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>63</v>
       </c>
@@ -3650,7 +3668,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>65</v>
       </c>
@@ -3684,7 +3702,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>66</v>
       </c>
@@ -3718,7 +3736,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>67</v>
       </c>
@@ -3751,7 +3769,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>68</v>
       </c>
@@ -3784,7 +3802,7 @@
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>69</v>
       </c>
@@ -3818,7 +3836,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>70</v>
       </c>
@@ -3852,7 +3870,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>71</v>
       </c>
@@ -3886,7 +3904,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>72</v>
       </c>
@@ -3920,7 +3938,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>73</v>
       </c>
@@ -3954,7 +3972,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>74</v>
       </c>
@@ -3988,7 +4006,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>75</v>
       </c>
@@ -4022,7 +4040,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>76</v>
       </c>
@@ -4056,7 +4074,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>77</v>
       </c>
@@ -4089,7 +4107,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>78</v>
       </c>
@@ -4123,7 +4141,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>79</v>
       </c>
@@ -4157,7 +4175,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>80</v>
       </c>
@@ -4191,7 +4209,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>81</v>
       </c>
@@ -4225,7 +4243,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>84</v>
       </c>
@@ -4259,7 +4277,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>85</v>
       </c>
@@ -4292,7 +4310,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>86</v>
       </c>
@@ -4325,7 +4343,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>88</v>
       </c>
@@ -4358,7 +4376,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>89</v>
       </c>
@@ -4391,7 +4409,7 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>90</v>
       </c>
@@ -4425,7 +4443,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>91</v>
       </c>
@@ -4459,7 +4477,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>92</v>
       </c>
@@ -4495,7 +4513,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>93</v>
       </c>
@@ -4528,7 +4546,7 @@
       </c>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>94</v>
       </c>
@@ -4561,7 +4579,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>95</v>
       </c>
@@ -4594,7 +4612,7 @@
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>96</v>
       </c>
@@ -4628,7 +4646,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>97</v>
       </c>
@@ -4661,7 +4679,7 @@
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>98</v>
       </c>
@@ -4695,7 +4713,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>99</v>
       </c>
@@ -4728,7 +4746,7 @@
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>100</v>
       </c>
@@ -4762,7 +4780,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>102</v>
       </c>
@@ -4798,7 +4816,7 @@
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>103</v>
       </c>
@@ -4831,7 +4849,7 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>104</v>
       </c>
@@ -4865,7 +4883,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>105</v>
       </c>
@@ -4901,7 +4919,7 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>106</v>
       </c>
@@ -4935,7 +4953,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>107</v>
       </c>
@@ -4968,7 +4986,7 @@
       </c>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>108</v>
       </c>
@@ -5002,7 +5020,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>109</v>
       </c>
@@ -5036,7 +5054,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>110</v>
       </c>
@@ -5069,7 +5087,7 @@
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>111</v>
       </c>
@@ -5103,7 +5121,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>112</v>
       </c>
@@ -5136,7 +5154,7 @@
       </c>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>113</v>
       </c>
@@ -5170,7 +5188,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>114</v>
       </c>
@@ -5204,7 +5222,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>115</v>
       </c>
@@ -5237,7 +5255,7 @@
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>116</v>
       </c>
@@ -5270,7 +5288,7 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>117</v>
       </c>
@@ -5303,7 +5321,7 @@
       </c>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:21">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>118</v>
       </c>
@@ -5336,7 +5354,7 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:21">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>119</v>
       </c>
@@ -5369,7 +5387,7 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
     </row>
-    <row r="99" spans="1:21">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>120</v>
       </c>
@@ -5402,7 +5420,7 @@
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
     </row>
-    <row r="100" spans="1:21">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>121</v>
       </c>
@@ -5436,7 +5454,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="101" spans="1:21">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>122</v>
       </c>
@@ -5469,7 +5487,7 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:21">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>123</v>
       </c>
@@ -5503,7 +5521,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="103" spans="1:21">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>124</v>
       </c>
@@ -5537,7 +5555,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="104" spans="1:21">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>125</v>
       </c>
@@ -5571,7 +5589,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:21">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>126</v>
       </c>
@@ -5605,7 +5623,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="106" spans="1:21">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>127</v>
       </c>
@@ -5638,7 +5656,7 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:21">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>128</v>
       </c>
@@ -5674,7 +5692,7 @@
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
     </row>
-    <row r="108" spans="1:21">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>129</v>
       </c>
@@ -5708,7 +5726,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="109" spans="1:21">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>130</v>
       </c>
@@ -5744,7 +5762,7 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:21">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>131</v>
       </c>
@@ -5777,7 +5795,7 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:21">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>132</v>
       </c>
@@ -5811,7 +5829,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="112" spans="1:21">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>133</v>
       </c>
@@ -5845,7 +5863,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>134</v>
       </c>
@@ -5879,7 +5897,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>135</v>
       </c>
@@ -5913,7 +5931,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>136</v>
       </c>
@@ -5947,7 +5965,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>137</v>
       </c>
@@ -5981,7 +5999,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>138</v>
       </c>
@@ -6015,7 +6033,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>139</v>
       </c>
@@ -6049,7 +6067,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>140</v>
       </c>
@@ -6083,7 +6101,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>141</v>
       </c>
@@ -6116,7 +6134,7 @@
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>142</v>
       </c>
@@ -6150,7 +6168,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="122" spans="1:19">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>143</v>
       </c>
@@ -6183,7 +6201,7 @@
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>144</v>
       </c>
@@ -6217,7 +6235,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>145</v>
       </c>
@@ -6250,7 +6268,7 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:19">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>146</v>
       </c>
@@ -6284,7 +6302,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="126" spans="1:19">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>147</v>
       </c>
@@ -6317,7 +6335,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>148</v>
       </c>
@@ -6354,7 +6372,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="128" spans="1:19" ht="15">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>149</v>
       </c>
@@ -6388,7 +6406,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="129" spans="1:19" ht="15">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>150</v>
       </c>
@@ -6422,7 +6440,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="130" spans="1:19" ht="15">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>151</v>
       </c>
@@ -6456,7 +6474,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="131" spans="1:19" ht="15">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>152</v>
       </c>
@@ -6490,7 +6508,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="132" spans="1:19" ht="15">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>153</v>
       </c>
@@ -6523,7 +6541,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="133" spans="1:19" ht="15">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>154</v>
       </c>
@@ -6557,7 +6575,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="134" spans="1:19" ht="15">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>155</v>
       </c>
@@ -6591,7 +6609,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="135" spans="1:19" ht="15">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>156</v>
       </c>
@@ -6628,7 +6646,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="136" spans="1:19" ht="15">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>157</v>
       </c>
@@ -6661,7 +6679,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="137" spans="1:19" ht="15">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>158</v>
       </c>
@@ -6695,7 +6713,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="138" spans="1:19" ht="15">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>159</v>
       </c>
@@ -6732,7 +6750,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="139" spans="1:19" ht="15">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>160</v>
       </c>
@@ -6768,7 +6786,7 @@
       <c r="O139" s="3"/>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="1:19" ht="15">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>161</v>
       </c>
@@ -6801,7 +6819,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="141" spans="1:19" ht="15">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>162</v>
       </c>
@@ -6837,7 +6855,7 @@
       <c r="O141" s="3"/>
       <c r="P141" s="3"/>
     </row>
-    <row r="142" spans="1:19" ht="15">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>163</v>
       </c>
@@ -6873,7 +6891,7 @@
       <c r="O142" s="3"/>
       <c r="P142" s="3"/>
     </row>
-    <row r="143" spans="1:19" ht="15">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>164</v>
       </c>
@@ -6906,7 +6924,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="144" spans="1:19" ht="15">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>165</v>
       </c>
@@ -6943,7 +6961,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="145" spans="1:16" ht="15">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>166</v>
       </c>
@@ -6979,7 +6997,7 @@
       <c r="O145" s="3"/>
       <c r="P145" s="3"/>
     </row>
-    <row r="146" spans="1:16" ht="15">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>167</v>
       </c>
@@ -7015,7 +7033,7 @@
       <c r="O146" s="3"/>
       <c r="P146" s="3"/>
     </row>
-    <row r="147" spans="1:16" ht="15">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>168</v>
       </c>
@@ -7051,7 +7069,7 @@
       <c r="O147" s="3"/>
       <c r="P147" s="3"/>
     </row>
-    <row r="148" spans="1:16" ht="15">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>169</v>
       </c>
@@ -7087,7 +7105,7 @@
       <c r="O148" s="3"/>
       <c r="P148" s="3"/>
     </row>
-    <row r="149" spans="1:16" ht="15">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>170</v>
       </c>
@@ -7123,7 +7141,7 @@
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
     </row>
-    <row r="150" spans="1:16" ht="15">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>171</v>
       </c>
@@ -7159,7 +7177,7 @@
       <c r="O150" s="3"/>
       <c r="P150" s="3"/>
     </row>
-    <row r="151" spans="1:16" ht="15">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>172</v>
       </c>
@@ -7195,7 +7213,7 @@
       <c r="O151" s="3"/>
       <c r="P151" s="3"/>
     </row>
-    <row r="152" spans="1:16" ht="15">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>173</v>
       </c>
@@ -7231,7 +7249,7 @@
       <c r="O152" s="3"/>
       <c r="P152" s="3"/>
     </row>
-    <row r="153" spans="1:16" ht="15">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>174</v>
       </c>
@@ -7267,7 +7285,7 @@
       <c r="O153" s="3"/>
       <c r="P153" s="3"/>
     </row>
-    <row r="154" spans="1:16" ht="15">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>175</v>
       </c>
@@ -7303,7 +7321,7 @@
       <c r="O154" s="3"/>
       <c r="P154" s="3"/>
     </row>
-    <row r="155" spans="1:16" ht="15">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>176</v>
       </c>
@@ -7339,7 +7357,7 @@
       <c r="O155" s="3"/>
       <c r="P155" s="3"/>
     </row>
-    <row r="156" spans="1:16" ht="15">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>177</v>
       </c>
@@ -7375,7 +7393,7 @@
       <c r="O156" s="3"/>
       <c r="P156" s="3"/>
     </row>
-    <row r="157" spans="1:16" ht="15">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>178</v>
       </c>
@@ -7411,7 +7429,7 @@
       <c r="O157" s="3"/>
       <c r="P157" s="3"/>
     </row>
-    <row r="158" spans="1:16" ht="15">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>179</v>
       </c>
@@ -7447,7 +7465,7 @@
       <c r="O158" s="3"/>
       <c r="P158" s="3"/>
     </row>
-    <row r="159" spans="1:16" ht="15">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>180</v>
       </c>
@@ -7483,7 +7501,7 @@
       <c r="O159" s="3"/>
       <c r="P159" s="3"/>
     </row>
-    <row r="160" spans="1:16" ht="15">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>181</v>
       </c>
@@ -7519,7 +7537,7 @@
       <c r="O160" s="3"/>
       <c r="P160" s="3"/>
     </row>
-    <row r="161" spans="1:16" ht="15">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>182</v>
       </c>
@@ -7555,7 +7573,7 @@
       <c r="O161" s="3"/>
       <c r="P161" s="3"/>
     </row>
-    <row r="162" spans="1:16" ht="15">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>183</v>
       </c>
@@ -7591,7 +7609,7 @@
       <c r="O162" s="3"/>
       <c r="P162" s="3"/>
     </row>
-    <row r="163" spans="1:16" ht="15">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>184</v>
       </c>
@@ -7625,7 +7643,7 @@
       <c r="O163" s="3"/>
       <c r="P163" s="3"/>
     </row>
-    <row r="164" spans="1:16" ht="15">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>185</v>
       </c>
@@ -7661,7 +7679,7 @@
       <c r="O164" s="3"/>
       <c r="P164" s="3"/>
     </row>
-    <row r="165" spans="1:16" ht="15">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>186</v>
       </c>
@@ -7697,7 +7715,7 @@
       <c r="O165" s="3"/>
       <c r="P165" s="3"/>
     </row>
-    <row r="166" spans="1:16" ht="15">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>187</v>
       </c>
@@ -7733,7 +7751,7 @@
       <c r="O166" s="3"/>
       <c r="P166" s="3"/>
     </row>
-    <row r="167" spans="1:16" ht="15">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>188</v>
       </c>
@@ -7769,7 +7787,7 @@
       <c r="O167" s="3"/>
       <c r="P167" s="3"/>
     </row>
-    <row r="168" spans="1:16" ht="15">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>189</v>
       </c>
@@ -7805,7 +7823,7 @@
       <c r="O168" s="3"/>
       <c r="P168" s="3"/>
     </row>
-    <row r="169" spans="1:16" ht="15">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>190</v>
       </c>
@@ -7841,7 +7859,7 @@
       <c r="O169" s="3"/>
       <c r="P169" s="3"/>
     </row>
-    <row r="170" spans="1:16" ht="15">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>191</v>
       </c>
@@ -7877,7 +7895,7 @@
       <c r="O170" s="3"/>
       <c r="P170" s="3"/>
     </row>
-    <row r="171" spans="1:16" ht="15">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>192</v>
       </c>
@@ -7913,7 +7931,7 @@
       <c r="O171" s="3"/>
       <c r="P171" s="3"/>
     </row>
-    <row r="172" spans="1:16" ht="15">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>193</v>
       </c>
@@ -7949,7 +7967,7 @@
       <c r="O172" s="3"/>
       <c r="P172" s="3"/>
     </row>
-    <row r="173" spans="1:16" ht="15">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>194</v>
       </c>
@@ -7985,7 +8003,7 @@
       <c r="O173" s="3"/>
       <c r="P173" s="3"/>
     </row>
-    <row r="174" spans="1:16" ht="15">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>195</v>
       </c>
@@ -8021,7 +8039,7 @@
       <c r="O174" s="3"/>
       <c r="P174" s="3"/>
     </row>
-    <row r="175" spans="1:16" ht="15">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>196</v>
       </c>
@@ -8057,7 +8075,7 @@
       <c r="O175" s="3"/>
       <c r="P175" s="3"/>
     </row>
-    <row r="176" spans="1:16" ht="15">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>197</v>
       </c>
@@ -8093,7 +8111,7 @@
       <c r="O176" s="3"/>
       <c r="P176" s="3"/>
     </row>
-    <row r="177" spans="1:16" ht="15">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>198</v>
       </c>
@@ -8129,7 +8147,7 @@
       <c r="O177" s="3"/>
       <c r="P177" s="3"/>
     </row>
-    <row r="178" spans="1:16" ht="15">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>199</v>
       </c>
@@ -8165,7 +8183,7 @@
       <c r="O178" s="3"/>
       <c r="P178" s="3"/>
     </row>
-    <row r="179" spans="1:16" ht="15">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>200</v>
       </c>
@@ -8201,7 +8219,7 @@
       <c r="O179" s="3"/>
       <c r="P179" s="3"/>
     </row>
-    <row r="180" spans="1:16" ht="15">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>201</v>
       </c>
@@ -8237,7 +8255,7 @@
       <c r="O180" s="3"/>
       <c r="P180" s="3"/>
     </row>
-    <row r="181" spans="1:16" ht="15">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>202</v>
       </c>
@@ -8273,7 +8291,7 @@
       <c r="O181" s="3"/>
       <c r="P181" s="3"/>
     </row>
-    <row r="182" spans="1:16" ht="15">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>203</v>
       </c>
@@ -8309,7 +8327,7 @@
       <c r="O182" s="3"/>
       <c r="P182" s="3"/>
     </row>
-    <row r="183" spans="1:16" ht="15">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>204</v>
       </c>
@@ -8345,7 +8363,7 @@
       <c r="O183" s="3"/>
       <c r="P183" s="3"/>
     </row>
-    <row r="184" spans="1:16" ht="15">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>205</v>
       </c>
@@ -8381,7 +8399,7 @@
       <c r="O184" s="3"/>
       <c r="P184" s="3"/>
     </row>
-    <row r="185" spans="1:16" ht="15">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>206</v>
       </c>
@@ -8417,7 +8435,7 @@
       <c r="O185" s="3"/>
       <c r="P185" s="3"/>
     </row>
-    <row r="186" spans="1:16" ht="15">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>207</v>
       </c>
@@ -8450,7 +8468,7 @@
       <c r="O186" s="3"/>
       <c r="P186" s="3"/>
     </row>
-    <row r="187" spans="1:16" ht="15">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>208</v>
       </c>
@@ -8486,7 +8504,7 @@
       <c r="O187" s="3"/>
       <c r="P187" s="3"/>
     </row>
-    <row r="188" spans="1:16" ht="15">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>209</v>
       </c>
@@ -8520,7 +8538,7 @@
       <c r="O188" s="3"/>
       <c r="P188" s="3"/>
     </row>
-    <row r="189" spans="1:16" ht="15">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>210</v>
       </c>
@@ -8556,7 +8574,7 @@
       <c r="O189" s="3"/>
       <c r="P189" s="3"/>
     </row>
-    <row r="190" spans="1:16" ht="15">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>211</v>
       </c>
@@ -8592,7 +8610,7 @@
       <c r="O190" s="3"/>
       <c r="P190" s="3"/>
     </row>
-    <row r="191" spans="1:16" ht="15">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>212</v>
       </c>
@@ -8628,7 +8646,7 @@
       <c r="O191" s="3"/>
       <c r="P191" s="3"/>
     </row>
-    <row r="192" spans="1:16" ht="15">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>213</v>
       </c>
@@ -8661,7 +8679,7 @@
       <c r="O192" s="3"/>
       <c r="P192" s="3"/>
     </row>
-    <row r="193" spans="1:20" ht="15">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>214</v>
       </c>
@@ -8695,7 +8713,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="194" spans="1:20" ht="15">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>215</v>
       </c>
@@ -8731,7 +8749,7 @@
       <c r="O194" s="3"/>
       <c r="P194" s="3"/>
     </row>
-    <row r="195" spans="1:20" ht="15">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>216</v>
       </c>
@@ -8767,7 +8785,7 @@
       <c r="O195" s="3"/>
       <c r="P195" s="3"/>
     </row>
-    <row r="196" spans="1:20" ht="15">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>217</v>
       </c>
@@ -8803,7 +8821,7 @@
       <c r="O196" s="3"/>
       <c r="P196" s="3"/>
     </row>
-    <row r="197" spans="1:20" ht="15">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>218</v>
       </c>
@@ -8839,7 +8857,7 @@
       <c r="O197" s="3"/>
       <c r="P197" s="3"/>
     </row>
-    <row r="198" spans="1:20" ht="15">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>219</v>
       </c>
@@ -8872,7 +8890,7 @@
       <c r="O198" s="3"/>
       <c r="P198" s="3"/>
     </row>
-    <row r="199" spans="1:20" ht="15">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>220</v>
       </c>
@@ -8906,7 +8924,7 @@
       <c r="O199" s="3"/>
       <c r="P199" s="3"/>
     </row>
-    <row r="200" spans="1:20" ht="15">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>221</v>
       </c>
@@ -8943,7 +8961,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="201" spans="1:20" ht="15">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>222</v>
       </c>
@@ -8979,7 +8997,7 @@
       <c r="O201" s="3"/>
       <c r="P201" s="3"/>
     </row>
-    <row r="202" spans="1:20" ht="15">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>223</v>
       </c>
@@ -9012,7 +9030,7 @@
       <c r="O202" s="3"/>
       <c r="P202" s="3"/>
     </row>
-    <row r="203" spans="1:20" ht="15">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>224</v>
       </c>
@@ -9048,7 +9066,7 @@
       <c r="O203" s="3"/>
       <c r="P203" s="3"/>
     </row>
-    <row r="204" spans="1:20" ht="15">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>225</v>
       </c>
@@ -9084,7 +9102,7 @@
       <c r="O204" s="3"/>
       <c r="P204" s="3"/>
     </row>
-    <row r="205" spans="1:20" ht="15">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>226</v>
       </c>
@@ -9117,7 +9135,7 @@
       <c r="O205" s="3"/>
       <c r="P205" s="3"/>
     </row>
-    <row r="206" spans="1:20" ht="15">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>227</v>
       </c>
@@ -9150,7 +9168,7 @@
       <c r="O206" s="3"/>
       <c r="P206" s="3"/>
     </row>
-    <row r="207" spans="1:20" ht="15">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>228</v>
       </c>
@@ -9183,7 +9201,7 @@
       <c r="O207" s="3"/>
       <c r="P207" s="3"/>
     </row>
-    <row r="208" spans="1:20" ht="15">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>229</v>
       </c>
@@ -9220,8 +9238,8 @@
         <v>453</v>
       </c>
     </row>
-    <row r="209" spans="1:21" ht="15">
-      <c r="A209" s="7">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A209">
         <v>230</v>
       </c>
       <c r="B209" s="2">
@@ -9243,7 +9261,6 @@
         <v>46</v>
       </c>
       <c r="H209" s="3"/>
-      <c r="I209" s="7"/>
       <c r="J209" s="3"/>
       <c r="K209" s="6"/>
       <c r="L209" s="3"/>
@@ -9251,16 +9268,12 @@
       <c r="N209" s="3"/>
       <c r="O209" s="3"/>
       <c r="P209" s="3"/>
-      <c r="Q209" s="7"/>
-      <c r="R209" s="7"/>
-      <c r="S209" s="7" t="s">
+      <c r="S209" t="s">
         <v>456</v>
       </c>
-      <c r="T209" s="7"/>
-      <c r="U209" s="7"/>
-    </row>
-    <row r="210" spans="1:21" ht="15">
-      <c r="A210" s="7">
+    </row>
+    <row r="210" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A210">
         <v>231</v>
       </c>
       <c r="B210" s="2">
@@ -9282,7 +9295,6 @@
         <v>106</v>
       </c>
       <c r="H210" s="3"/>
-      <c r="I210" s="7"/>
       <c r="J210" s="3"/>
       <c r="K210" s="6"/>
       <c r="L210" s="3"/>
@@ -9290,18 +9302,15 @@
       <c r="N210" s="3"/>
       <c r="O210" s="3"/>
       <c r="P210" s="3"/>
-      <c r="Q210" s="7" t="s">
+      <c r="Q210" t="s">
         <v>61</v>
       </c>
-      <c r="R210" s="7" t="s">
+      <c r="R210" t="s">
         <v>457</v>
       </c>
-      <c r="S210" s="7"/>
-      <c r="T210" s="7"/>
-      <c r="U210" s="7"/>
-    </row>
-    <row r="211" spans="1:21" ht="15">
-      <c r="A211" s="7">
+    </row>
+    <row r="211" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A211">
         <v>232</v>
       </c>
       <c r="B211" s="2">
@@ -9323,7 +9332,6 @@
         <v>106</v>
       </c>
       <c r="H211" s="3"/>
-      <c r="I211" s="7"/>
       <c r="J211" s="3"/>
       <c r="K211" s="6"/>
       <c r="L211" s="3"/>
@@ -9331,18 +9339,15 @@
       <c r="N211" s="3"/>
       <c r="O211" s="3"/>
       <c r="P211" s="3"/>
-      <c r="Q211" s="7" t="s">
+      <c r="Q211" t="s">
         <v>61</v>
       </c>
-      <c r="R211" s="7" t="s">
+      <c r="R211" t="s">
         <v>458</v>
       </c>
-      <c r="S211" s="7"/>
-      <c r="T211" s="7"/>
-      <c r="U211" s="7"/>
-    </row>
-    <row r="212" spans="1:21" ht="15">
-      <c r="A212" s="7">
+    </row>
+    <row r="212" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A212">
         <v>233</v>
       </c>
       <c r="B212" s="2">
@@ -9364,7 +9369,6 @@
         <v>106</v>
       </c>
       <c r="H212" s="3"/>
-      <c r="I212" s="7"/>
       <c r="J212" s="3"/>
       <c r="K212" s="6"/>
       <c r="L212" s="3"/>
@@ -9372,18 +9376,15 @@
       <c r="N212" s="3"/>
       <c r="O212" s="3"/>
       <c r="P212" s="3"/>
-      <c r="Q212" s="7" t="s">
+      <c r="Q212" t="s">
         <v>61</v>
       </c>
-      <c r="R212" s="7" t="s">
+      <c r="R212" t="s">
         <v>459</v>
       </c>
-      <c r="S212" s="7"/>
-      <c r="T212" s="7"/>
-      <c r="U212" s="7"/>
-    </row>
-    <row r="213" spans="1:21" ht="15">
-      <c r="A213" s="7">
+    </row>
+    <row r="213" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A213">
         <v>234</v>
       </c>
       <c r="B213" s="2">
@@ -9405,7 +9406,6 @@
         <v>106</v>
       </c>
       <c r="H213" s="3"/>
-      <c r="I213" s="7"/>
       <c r="J213" s="3"/>
       <c r="K213" s="6"/>
       <c r="L213" s="3"/>
@@ -9413,13 +9413,247 @@
       <c r="N213" s="3"/>
       <c r="O213" s="3"/>
       <c r="P213" s="3"/>
-      <c r="Q213" s="7" t="s">
+      <c r="Q213" t="s">
         <v>107</v>
       </c>
-      <c r="R213" s="7"/>
-      <c r="S213" s="7"/>
-      <c r="T213" s="7"/>
-      <c r="U213" s="7"/>
+    </row>
+    <row r="214" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A214" s="7">
+        <v>235</v>
+      </c>
+      <c r="B214" s="2">
+        <v>46266.861898148098</v>
+      </c>
+      <c r="C214" s="2">
+        <v>46266.862187500003</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H214" s="3"/>
+      <c r="I214" s="7"/>
+      <c r="J214" s="3"/>
+      <c r="K214" s="6"/>
+      <c r="L214" s="3"/>
+      <c r="M214" s="3"/>
+      <c r="N214" s="3"/>
+      <c r="O214" s="3"/>
+      <c r="P214" s="3"/>
+      <c r="Q214" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R214" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="S214" s="7"/>
+      <c r="T214" s="7"/>
+      <c r="U214" s="7"/>
+    </row>
+    <row r="215" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A215" s="7">
+        <v>236</v>
+      </c>
+      <c r="B215" s="2">
+        <v>46266.945138888899</v>
+      </c>
+      <c r="C215" s="2">
+        <v>46266.9458564815</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="I215" s="7"/>
+      <c r="J215" s="3"/>
+      <c r="K215" s="6"/>
+      <c r="L215" s="3"/>
+      <c r="M215" s="3"/>
+      <c r="N215" s="3"/>
+      <c r="O215" s="3"/>
+      <c r="P215" s="3"/>
+      <c r="Q215" s="7"/>
+      <c r="R215" s="7"/>
+      <c r="S215" s="7"/>
+      <c r="T215" s="7"/>
+      <c r="U215" s="7"/>
+    </row>
+    <row r="216" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A216" s="7">
+        <v>237</v>
+      </c>
+      <c r="B216" s="2">
+        <v>46267.344571759299</v>
+      </c>
+      <c r="C216" s="2">
+        <v>46267.345312500001</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H216" s="3"/>
+      <c r="I216" s="7"/>
+      <c r="J216" s="3"/>
+      <c r="K216" s="6"/>
+      <c r="L216" s="3"/>
+      <c r="M216" s="3"/>
+      <c r="N216" s="3"/>
+      <c r="O216" s="3"/>
+      <c r="P216" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="Q216" s="7"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="7"/>
+      <c r="T216" s="7"/>
+      <c r="U216" s="7"/>
+    </row>
+    <row r="217" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A217" s="7">
+        <v>238</v>
+      </c>
+      <c r="B217" s="2">
+        <v>46267.371585648099</v>
+      </c>
+      <c r="C217" s="2">
+        <v>46267.372071759302</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H217" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="I217" s="7"/>
+      <c r="J217" s="3"/>
+      <c r="K217" s="6"/>
+      <c r="L217" s="3"/>
+      <c r="M217" s="3"/>
+      <c r="N217" s="3"/>
+      <c r="O217" s="3"/>
+      <c r="P217" s="3"/>
+      <c r="Q217" s="7"/>
+      <c r="R217" s="7"/>
+      <c r="S217" s="7"/>
+      <c r="T217" s="7"/>
+      <c r="U217" s="7"/>
+    </row>
+    <row r="218" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A218" s="7">
+        <v>239</v>
+      </c>
+      <c r="B218" s="2">
+        <v>46267.410995370403</v>
+      </c>
+      <c r="C218" s="2">
+        <v>46267.411620370403</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H218" s="3"/>
+      <c r="I218" s="7"/>
+      <c r="J218" s="3"/>
+      <c r="K218" s="6"/>
+      <c r="L218" s="3"/>
+      <c r="M218" s="3"/>
+      <c r="N218" s="3"/>
+      <c r="O218" s="3"/>
+      <c r="P218" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q218" s="7"/>
+      <c r="R218" s="7"/>
+      <c r="S218" s="7"/>
+      <c r="T218" s="7"/>
+      <c r="U218" s="7"/>
+    </row>
+    <row r="219" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A219" s="7">
+        <v>240</v>
+      </c>
+      <c r="B219" s="2">
+        <v>46267.448240740698</v>
+      </c>
+      <c r="C219" s="2">
+        <v>46267.448668981502</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H219" s="3"/>
+      <c r="I219" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J219" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="K219" s="6"/>
+      <c r="L219" s="3"/>
+      <c r="M219" s="3"/>
+      <c r="N219" s="3"/>
+      <c r="O219" s="3"/>
+      <c r="P219" s="3"/>
+      <c r="Q219" s="7"/>
+      <c r="R219" s="7"/>
+      <c r="S219" s="7"/>
+      <c r="T219" s="7"/>
+      <c r="U219" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF8FD984-1A50-4DEB-9FCA-014E392873F2}"/>
+  <xr:revisionPtr revIDLastSave="345" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F187C74B-4F6D-4931-8B8F-C92DC49DD869}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="536">
   <si>
     <t>Id</t>
   </si>
@@ -1434,13 +1434,223 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17883675463346775160730658457831_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_0762_Starbucks%20Plaza%20Tepe.jpeg</t>
+  </si>
+  <si>
+    <t>jessica.mendoza@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Jessica Mendoza Garcia</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/e56ca8ef-3c20-44ef-8632-0377fa238de2_Jessica%20Mendoza%20Garc.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Cristian%20Alexis%20Posa.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260826-WA0022_Starbucks%20Mundo%20E.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/20260902_114107_Starbucks%20Mundo%20E.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260902-WA0021_Fany%20Jeovana%20Echever.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_7968_Starbucks%20Jinetes.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_3263_Starbucks%20Boulevard.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/20260902_125517_Starbucks%20Mundo%20E.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/1788375634932190202213584791844_Starbucks%20Parque%20Tep.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260826-WA0022_Starbucks%20Mundo%20E%201.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17883779104005387599610901335484_Starbucks%20Mundo%20E.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_0947_Starbucks%20Valle%20Dora.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Starbucks%20Valle%20Dora.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/68785_Juan%20Jose%20Santiago%20D.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38561@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Parque Toreo</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17883801756897368214557940334839_Starbucks%20Parque%20Tor.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/17883806883878055902246261152848_Starbucks%20Parque%20Tor.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/1788380777934647963397618757368_Starbucks%20Parque%20Tor.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38590@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Parque Toreo ll</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/955B824F-65F7-4E6C-8B9C-5E919EC1BC00_Starbucks%20Parque%20Tor.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_6868_Starbucks%20Parque%20Tor.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Parque%20Tor.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_7029_Starbucks%20Parque%20Tor.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20CEMTRAM%204.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG_7037_Starbucks%20Parque%20Tor.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/Captura%20de%20pantalla%202026-09-02%20a%20las%202.37.17_Starbucks%20Tlalnepant.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/20260902_144749_Starbucks%20Mundo%20E.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/Captura%20de%20pantalla%202026-09-02%20a%20las%202.52.47_Starbucks%20Tlalnepant.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_4734_Starbucks%20Satelite.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38270@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Lomas Verdes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Plaza%20Loma.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Satelite.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_5433_Starbucks%20Satelite.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_9767_Starbucks%20Plaza%20Sate.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_0592_Starbucks%20Gustavo%20Ba.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Plaza%20Sate.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_0592_Starbucks%20Gustavo%20Ba%201.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Plaza%20Sate.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Starbucks%20Gustavo%20Ba.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/image_Starbucks%20Plaza%20Sate.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Satelite.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Satelite.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/17883879213636823761632255576731_Starbucks%20Mundo%20E.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG_7044_Starbucks%20Parque%20Tor.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17883879486043482090661419109628_Starbucks%20ENCUENTRO.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_5276_Starbucks%20CC%20Plaza%20S.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17883880729711023111038830987681_Starbucks%20ENCUENTRO.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/17883881303554922457392122912565_Starbucks%20ENCUENTRO.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20CC%20Plaza%20S.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/B5DE4D75-9AEF-4BA6-BE11-3F61F98FA01C_Starbucks%20Plaza%20Sate.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/20260902_163303_Starbucks%20ENCUENTRO.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/IMG_5522_Starbucks%20CC%20Plaza%20S.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/20260902_163626_Starbucks%20ENCUENTRO.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/2761a433-e891-4147-9871-59df57668ae8_Starbucks%20CEMTRAM%204.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/57c52e25-c96f-4393-b5fb-8e4b0fa4aff4_Starbucks%20Sat%C3%A9lite%20C.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG_3997_Starbucks%20El%20Rosario.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20CEMTRAM%204%201.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_3905_Starbucks%20CEMTRAM%204.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/bed5599b-04f3-4e98-803b-3b0e0e1da5ac_Starbucks%20Samara%20Sat.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/IMG_4825_Starbucks%20Samara%20Sat.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/4712379c-d19f-4ec7-abdf-95c073eea671_Starbucks%20El%20Rosario%201.jpeg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1568,8 +1778,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U219" totalsRowShown="0">
-  <autoFilter ref="A1:U219" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U284" totalsRowShown="0">
+  <autoFilter ref="A1:U284" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1722,7 +1932,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="240" latestEventMarker="475">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="306" latestEventMarker="541">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2047,23 +2257,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U219"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:U285"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.7265625" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
     <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" customWidth="1"/>
-    <col min="5" max="5" width="35.1796875" customWidth="1"/>
-    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="19" customWidth="1"/>
-    <col min="19" max="19" width="42.1796875" customWidth="1"/>
+    <col min="19" max="19" width="42.140625" customWidth="1"/>
     <col min="20" max="21" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2128,7 +2338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>13</v>
       </c>
@@ -2154,7 +2364,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>17</v>
       </c>
@@ -2187,7 +2397,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2220,7 +2430,7 @@
       </c>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21">
       <c r="A5">
         <v>20</v>
       </c>
@@ -2253,7 +2463,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>21</v>
       </c>
@@ -2286,7 +2496,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>22</v>
       </c>
@@ -2319,7 +2529,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>23</v>
       </c>
@@ -2353,7 +2563,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>24</v>
       </c>
@@ -2387,7 +2597,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>25</v>
       </c>
@@ -2421,7 +2631,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21">
       <c r="A11">
         <v>26</v>
       </c>
@@ -2454,7 +2664,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21">
       <c r="A12">
         <v>27</v>
       </c>
@@ -2490,7 +2700,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21">
       <c r="A13">
         <v>28</v>
       </c>
@@ -2523,7 +2733,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21">
       <c r="A14">
         <v>29</v>
       </c>
@@ -2557,7 +2767,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21">
       <c r="A15">
         <v>30</v>
       </c>
@@ -2590,7 +2800,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21">
       <c r="A16">
         <v>31</v>
       </c>
@@ -2623,7 +2833,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19">
       <c r="A17">
         <v>32</v>
       </c>
@@ -2657,7 +2867,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19">
       <c r="A18">
         <v>33</v>
       </c>
@@ -2690,7 +2900,7 @@
       </c>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>34</v>
       </c>
@@ -2723,7 +2933,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>35</v>
       </c>
@@ -2756,7 +2966,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>36</v>
       </c>
@@ -2789,7 +2999,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>37</v>
       </c>
@@ -2823,7 +3033,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>38</v>
       </c>
@@ -2857,7 +3067,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>39</v>
       </c>
@@ -2891,7 +3101,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>40</v>
       </c>
@@ -2925,7 +3135,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>41</v>
       </c>
@@ -2958,7 +3168,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>42</v>
       </c>
@@ -2992,7 +3202,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>43</v>
       </c>
@@ -3026,7 +3236,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19">
       <c r="A29">
         <v>44</v>
       </c>
@@ -3060,7 +3270,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19">
       <c r="A30">
         <v>45</v>
       </c>
@@ -3094,7 +3304,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19">
       <c r="A31">
         <v>46</v>
       </c>
@@ -3128,7 +3338,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19">
       <c r="A32">
         <v>47</v>
       </c>
@@ -3162,7 +3372,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19">
       <c r="A33">
         <v>48</v>
       </c>
@@ -3195,7 +3405,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>49</v>
       </c>
@@ -3229,7 +3439,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>50</v>
       </c>
@@ -3263,7 +3473,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>51</v>
       </c>
@@ -3297,7 +3507,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>52</v>
       </c>
@@ -3330,7 +3540,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>54</v>
       </c>
@@ -3363,7 +3573,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>55</v>
       </c>
@@ -3396,7 +3606,7 @@
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>56</v>
       </c>
@@ -3430,7 +3640,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>57</v>
       </c>
@@ -3464,7 +3674,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>58</v>
       </c>
@@ -3498,7 +3708,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>59</v>
       </c>
@@ -3532,7 +3742,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19">
       <c r="A44">
         <v>60</v>
       </c>
@@ -3566,7 +3776,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19">
       <c r="A45">
         <v>61</v>
       </c>
@@ -3600,7 +3810,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19">
       <c r="A46">
         <v>62</v>
       </c>
@@ -3634,7 +3844,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19">
       <c r="A47">
         <v>63</v>
       </c>
@@ -3668,7 +3878,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19">
       <c r="A48">
         <v>65</v>
       </c>
@@ -3702,7 +3912,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>66</v>
       </c>
@@ -3736,7 +3946,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>67</v>
       </c>
@@ -3769,7 +3979,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>68</v>
       </c>
@@ -3802,7 +4012,7 @@
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>69</v>
       </c>
@@ -3836,7 +4046,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>70</v>
       </c>
@@ -3870,7 +4080,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>71</v>
       </c>
@@ -3904,7 +4114,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>72</v>
       </c>
@@ -3938,7 +4148,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>73</v>
       </c>
@@ -3972,7 +4182,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>74</v>
       </c>
@@ -4006,7 +4216,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>75</v>
       </c>
@@ -4040,7 +4250,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19">
       <c r="A59">
         <v>76</v>
       </c>
@@ -4074,7 +4284,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19">
       <c r="A60">
         <v>77</v>
       </c>
@@ -4107,7 +4317,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19">
       <c r="A61">
         <v>78</v>
       </c>
@@ -4141,7 +4351,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19">
       <c r="A62">
         <v>79</v>
       </c>
@@ -4175,7 +4385,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19">
       <c r="A63">
         <v>80</v>
       </c>
@@ -4209,7 +4419,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>81</v>
       </c>
@@ -4243,7 +4453,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>84</v>
       </c>
@@ -4277,7 +4487,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>85</v>
       </c>
@@ -4310,7 +4520,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>86</v>
       </c>
@@ -4343,7 +4553,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>88</v>
       </c>
@@ -4376,7 +4586,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>89</v>
       </c>
@@ -4409,7 +4619,7 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>90</v>
       </c>
@@ -4443,7 +4653,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>91</v>
       </c>
@@ -4477,7 +4687,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>92</v>
       </c>
@@ -4513,7 +4723,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>93</v>
       </c>
@@ -4546,7 +4756,7 @@
       </c>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:19">
       <c r="A74">
         <v>94</v>
       </c>
@@ -4579,7 +4789,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19">
       <c r="A75">
         <v>95</v>
       </c>
@@ -4612,7 +4822,7 @@
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19">
       <c r="A76">
         <v>96</v>
       </c>
@@ -4646,7 +4856,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19">
       <c r="A77">
         <v>97</v>
       </c>
@@ -4679,7 +4889,7 @@
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19">
       <c r="A78">
         <v>98</v>
       </c>
@@ -4713,7 +4923,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>99</v>
       </c>
@@ -4746,7 +4956,7 @@
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>100</v>
       </c>
@@ -4780,7 +4990,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>102</v>
       </c>
@@ -4816,7 +5026,7 @@
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>103</v>
       </c>
@@ -4849,7 +5059,7 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>104</v>
       </c>
@@ -4883,7 +5093,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>105</v>
       </c>
@@ -4919,7 +5129,7 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>106</v>
       </c>
@@ -4953,7 +5163,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>107</v>
       </c>
@@ -4986,7 +5196,7 @@
       </c>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>108</v>
       </c>
@@ -5020,7 +5230,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>109</v>
       </c>
@@ -5054,7 +5264,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19">
       <c r="A89">
         <v>110</v>
       </c>
@@ -5087,7 +5297,7 @@
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19">
       <c r="A90">
         <v>111</v>
       </c>
@@ -5121,7 +5331,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19">
       <c r="A91">
         <v>112</v>
       </c>
@@ -5154,7 +5364,7 @@
       </c>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19">
       <c r="A92">
         <v>113</v>
       </c>
@@ -5188,7 +5398,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19">
       <c r="A93">
         <v>114</v>
       </c>
@@ -5222,7 +5432,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19">
       <c r="A94">
         <v>115</v>
       </c>
@@ -5255,7 +5465,7 @@
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19">
       <c r="A95">
         <v>116</v>
       </c>
@@ -5288,7 +5498,7 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19">
       <c r="A96">
         <v>117</v>
       </c>
@@ -5321,7 +5531,7 @@
       </c>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21">
       <c r="A97">
         <v>118</v>
       </c>
@@ -5354,7 +5564,7 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21">
       <c r="A98">
         <v>119</v>
       </c>
@@ -5387,7 +5597,7 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21">
       <c r="A99">
         <v>120</v>
       </c>
@@ -5420,7 +5630,7 @@
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21">
       <c r="A100">
         <v>121</v>
       </c>
@@ -5454,7 +5664,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21">
       <c r="A101">
         <v>122</v>
       </c>
@@ -5487,7 +5697,7 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21">
       <c r="A102">
         <v>123</v>
       </c>
@@ -5521,7 +5731,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21">
       <c r="A103">
         <v>124</v>
       </c>
@@ -5555,7 +5765,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21">
       <c r="A104">
         <v>125</v>
       </c>
@@ -5589,7 +5799,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21">
       <c r="A105">
         <v>126</v>
       </c>
@@ -5623,7 +5833,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21">
       <c r="A106">
         <v>127</v>
       </c>
@@ -5656,7 +5866,7 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21">
       <c r="A107">
         <v>128</v>
       </c>
@@ -5692,7 +5902,7 @@
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21">
       <c r="A108">
         <v>129</v>
       </c>
@@ -5726,7 +5936,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21">
       <c r="A109">
         <v>130</v>
       </c>
@@ -5762,7 +5972,7 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21">
       <c r="A110">
         <v>131</v>
       </c>
@@ -5795,7 +6005,7 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21">
       <c r="A111">
         <v>132</v>
       </c>
@@ -5829,7 +6039,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21">
       <c r="A112">
         <v>133</v>
       </c>
@@ -5863,7 +6073,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:19">
       <c r="A113">
         <v>134</v>
       </c>
@@ -5897,7 +6107,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:19">
       <c r="A114">
         <v>135</v>
       </c>
@@ -5931,7 +6141,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:19">
       <c r="A115">
         <v>136</v>
       </c>
@@ -5965,7 +6175,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:19">
       <c r="A116">
         <v>137</v>
       </c>
@@ -5999,7 +6209,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:19">
       <c r="A117">
         <v>138</v>
       </c>
@@ -6033,7 +6243,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:19">
       <c r="A118">
         <v>139</v>
       </c>
@@ -6067,7 +6277,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:19">
       <c r="A119">
         <v>140</v>
       </c>
@@ -6101,7 +6311,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:19">
       <c r="A120">
         <v>141</v>
       </c>
@@ -6134,7 +6344,7 @@
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:19">
       <c r="A121">
         <v>142</v>
       </c>
@@ -6168,7 +6378,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:19">
       <c r="A122">
         <v>143</v>
       </c>
@@ -6201,7 +6411,7 @@
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:19">
       <c r="A123">
         <v>144</v>
       </c>
@@ -6235,7 +6445,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:19">
       <c r="A124">
         <v>145</v>
       </c>
@@ -6268,7 +6478,7 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:19">
       <c r="A125">
         <v>146</v>
       </c>
@@ -6302,7 +6512,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:19">
       <c r="A126">
         <v>147</v>
       </c>
@@ -6335,7 +6545,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:19">
       <c r="A127">
         <v>148</v>
       </c>
@@ -6372,7 +6582,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:19">
       <c r="A128">
         <v>149</v>
       </c>
@@ -6406,7 +6616,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:19">
       <c r="A129">
         <v>150</v>
       </c>
@@ -6440,7 +6650,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:19">
       <c r="A130">
         <v>151</v>
       </c>
@@ -6474,7 +6684,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:19">
       <c r="A131">
         <v>152</v>
       </c>
@@ -6508,7 +6718,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:19">
       <c r="A132">
         <v>153</v>
       </c>
@@ -6541,7 +6751,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:19">
       <c r="A133">
         <v>154</v>
       </c>
@@ -6575,7 +6785,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:19">
       <c r="A134">
         <v>155</v>
       </c>
@@ -6609,7 +6819,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:19">
       <c r="A135">
         <v>156</v>
       </c>
@@ -6646,7 +6856,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:19">
       <c r="A136">
         <v>157</v>
       </c>
@@ -6679,7 +6889,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:19">
       <c r="A137">
         <v>158</v>
       </c>
@@ -6713,7 +6923,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:19">
       <c r="A138">
         <v>159</v>
       </c>
@@ -6750,7 +6960,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:19">
       <c r="A139">
         <v>160</v>
       </c>
@@ -6786,7 +6996,7 @@
       <c r="O139" s="3"/>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:19">
       <c r="A140">
         <v>161</v>
       </c>
@@ -6819,7 +7029,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:19">
       <c r="A141">
         <v>162</v>
       </c>
@@ -6855,7 +7065,7 @@
       <c r="O141" s="3"/>
       <c r="P141" s="3"/>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:19">
       <c r="A142">
         <v>163</v>
       </c>
@@ -6891,7 +7101,7 @@
       <c r="O142" s="3"/>
       <c r="P142" s="3"/>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:19">
       <c r="A143">
         <v>164</v>
       </c>
@@ -6924,7 +7134,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:19">
       <c r="A144">
         <v>165</v>
       </c>
@@ -6961,7 +7171,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16">
       <c r="A145">
         <v>166</v>
       </c>
@@ -6997,7 +7207,7 @@
       <c r="O145" s="3"/>
       <c r="P145" s="3"/>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16">
       <c r="A146">
         <v>167</v>
       </c>
@@ -7033,7 +7243,7 @@
       <c r="O146" s="3"/>
       <c r="P146" s="3"/>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16">
       <c r="A147">
         <v>168</v>
       </c>
@@ -7069,7 +7279,7 @@
       <c r="O147" s="3"/>
       <c r="P147" s="3"/>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16">
       <c r="A148">
         <v>169</v>
       </c>
@@ -7105,7 +7315,7 @@
       <c r="O148" s="3"/>
       <c r="P148" s="3"/>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16">
       <c r="A149">
         <v>170</v>
       </c>
@@ -7141,7 +7351,7 @@
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16">
       <c r="A150">
         <v>171</v>
       </c>
@@ -7177,7 +7387,7 @@
       <c r="O150" s="3"/>
       <c r="P150" s="3"/>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16">
       <c r="A151">
         <v>172</v>
       </c>
@@ -7213,7 +7423,7 @@
       <c r="O151" s="3"/>
       <c r="P151" s="3"/>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16">
       <c r="A152">
         <v>173</v>
       </c>
@@ -7249,7 +7459,7 @@
       <c r="O152" s="3"/>
       <c r="P152" s="3"/>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16">
       <c r="A153">
         <v>174</v>
       </c>
@@ -7285,7 +7495,7 @@
       <c r="O153" s="3"/>
       <c r="P153" s="3"/>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16">
       <c r="A154">
         <v>175</v>
       </c>
@@ -7321,7 +7531,7 @@
       <c r="O154" s="3"/>
       <c r="P154" s="3"/>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16">
       <c r="A155">
         <v>176</v>
       </c>
@@ -7357,7 +7567,7 @@
       <c r="O155" s="3"/>
       <c r="P155" s="3"/>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16">
       <c r="A156">
         <v>177</v>
       </c>
@@ -7393,7 +7603,7 @@
       <c r="O156" s="3"/>
       <c r="P156" s="3"/>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16">
       <c r="A157">
         <v>178</v>
       </c>
@@ -7429,7 +7639,7 @@
       <c r="O157" s="3"/>
       <c r="P157" s="3"/>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16">
       <c r="A158">
         <v>179</v>
       </c>
@@ -7465,7 +7675,7 @@
       <c r="O158" s="3"/>
       <c r="P158" s="3"/>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16">
       <c r="A159">
         <v>180</v>
       </c>
@@ -7501,7 +7711,7 @@
       <c r="O159" s="3"/>
       <c r="P159" s="3"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16">
       <c r="A160">
         <v>181</v>
       </c>
@@ -7537,7 +7747,7 @@
       <c r="O160" s="3"/>
       <c r="P160" s="3"/>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16">
       <c r="A161">
         <v>182</v>
       </c>
@@ -7573,7 +7783,7 @@
       <c r="O161" s="3"/>
       <c r="P161" s="3"/>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16">
       <c r="A162">
         <v>183</v>
       </c>
@@ -7609,7 +7819,7 @@
       <c r="O162" s="3"/>
       <c r="P162" s="3"/>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16">
       <c r="A163">
         <v>184</v>
       </c>
@@ -7643,7 +7853,7 @@
       <c r="O163" s="3"/>
       <c r="P163" s="3"/>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16">
       <c r="A164">
         <v>185</v>
       </c>
@@ -7679,7 +7889,7 @@
       <c r="O164" s="3"/>
       <c r="P164" s="3"/>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16">
       <c r="A165">
         <v>186</v>
       </c>
@@ -7715,7 +7925,7 @@
       <c r="O165" s="3"/>
       <c r="P165" s="3"/>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:16">
       <c r="A166">
         <v>187</v>
       </c>
@@ -7751,7 +7961,7 @@
       <c r="O166" s="3"/>
       <c r="P166" s="3"/>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16">
       <c r="A167">
         <v>188</v>
       </c>
@@ -7787,7 +7997,7 @@
       <c r="O167" s="3"/>
       <c r="P167" s="3"/>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16">
       <c r="A168">
         <v>189</v>
       </c>
@@ -7823,7 +8033,7 @@
       <c r="O168" s="3"/>
       <c r="P168" s="3"/>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16">
       <c r="A169">
         <v>190</v>
       </c>
@@ -7859,7 +8069,7 @@
       <c r="O169" s="3"/>
       <c r="P169" s="3"/>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16">
       <c r="A170">
         <v>191</v>
       </c>
@@ -7895,7 +8105,7 @@
       <c r="O170" s="3"/>
       <c r="P170" s="3"/>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16">
       <c r="A171">
         <v>192</v>
       </c>
@@ -7931,7 +8141,7 @@
       <c r="O171" s="3"/>
       <c r="P171" s="3"/>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16">
       <c r="A172">
         <v>193</v>
       </c>
@@ -7967,7 +8177,7 @@
       <c r="O172" s="3"/>
       <c r="P172" s="3"/>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16">
       <c r="A173">
         <v>194</v>
       </c>
@@ -8003,7 +8213,7 @@
       <c r="O173" s="3"/>
       <c r="P173" s="3"/>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16">
       <c r="A174">
         <v>195</v>
       </c>
@@ -8039,7 +8249,7 @@
       <c r="O174" s="3"/>
       <c r="P174" s="3"/>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16">
       <c r="A175">
         <v>196</v>
       </c>
@@ -8075,7 +8285,7 @@
       <c r="O175" s="3"/>
       <c r="P175" s="3"/>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16">
       <c r="A176">
         <v>197</v>
       </c>
@@ -8111,7 +8321,7 @@
       <c r="O176" s="3"/>
       <c r="P176" s="3"/>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16">
       <c r="A177">
         <v>198</v>
       </c>
@@ -8147,7 +8357,7 @@
       <c r="O177" s="3"/>
       <c r="P177" s="3"/>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16">
       <c r="A178">
         <v>199</v>
       </c>
@@ -8183,7 +8393,7 @@
       <c r="O178" s="3"/>
       <c r="P178" s="3"/>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16">
       <c r="A179">
         <v>200</v>
       </c>
@@ -8219,7 +8429,7 @@
       <c r="O179" s="3"/>
       <c r="P179" s="3"/>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:16">
       <c r="A180">
         <v>201</v>
       </c>
@@ -8255,7 +8465,7 @@
       <c r="O180" s="3"/>
       <c r="P180" s="3"/>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:16">
       <c r="A181">
         <v>202</v>
       </c>
@@ -8291,7 +8501,7 @@
       <c r="O181" s="3"/>
       <c r="P181" s="3"/>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16">
       <c r="A182">
         <v>203</v>
       </c>
@@ -8327,7 +8537,7 @@
       <c r="O182" s="3"/>
       <c r="P182" s="3"/>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16">
       <c r="A183">
         <v>204</v>
       </c>
@@ -8363,7 +8573,7 @@
       <c r="O183" s="3"/>
       <c r="P183" s="3"/>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16">
       <c r="A184">
         <v>205</v>
       </c>
@@ -8399,7 +8609,7 @@
       <c r="O184" s="3"/>
       <c r="P184" s="3"/>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16">
       <c r="A185">
         <v>206</v>
       </c>
@@ -8435,7 +8645,7 @@
       <c r="O185" s="3"/>
       <c r="P185" s="3"/>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16">
       <c r="A186">
         <v>207</v>
       </c>
@@ -8468,7 +8678,7 @@
       <c r="O186" s="3"/>
       <c r="P186" s="3"/>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16">
       <c r="A187">
         <v>208</v>
       </c>
@@ -8504,7 +8714,7 @@
       <c r="O187" s="3"/>
       <c r="P187" s="3"/>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16">
       <c r="A188">
         <v>209</v>
       </c>
@@ -8538,7 +8748,7 @@
       <c r="O188" s="3"/>
       <c r="P188" s="3"/>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16">
       <c r="A189">
         <v>210</v>
       </c>
@@ -8574,7 +8784,7 @@
       <c r="O189" s="3"/>
       <c r="P189" s="3"/>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16">
       <c r="A190">
         <v>211</v>
       </c>
@@ -8610,7 +8820,7 @@
       <c r="O190" s="3"/>
       <c r="P190" s="3"/>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16">
       <c r="A191">
         <v>212</v>
       </c>
@@ -8646,7 +8856,7 @@
       <c r="O191" s="3"/>
       <c r="P191" s="3"/>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16">
       <c r="A192">
         <v>213</v>
       </c>
@@ -8679,7 +8889,7 @@
       <c r="O192" s="3"/>
       <c r="P192" s="3"/>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:20">
       <c r="A193">
         <v>214</v>
       </c>
@@ -8713,7 +8923,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:20">
       <c r="A194">
         <v>215</v>
       </c>
@@ -8749,7 +8959,7 @@
       <c r="O194" s="3"/>
       <c r="P194" s="3"/>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:20">
       <c r="A195">
         <v>216</v>
       </c>
@@ -8785,7 +8995,7 @@
       <c r="O195" s="3"/>
       <c r="P195" s="3"/>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:20">
       <c r="A196">
         <v>217</v>
       </c>
@@ -8821,7 +9031,7 @@
       <c r="O196" s="3"/>
       <c r="P196" s="3"/>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:20">
       <c r="A197">
         <v>218</v>
       </c>
@@ -8857,7 +9067,7 @@
       <c r="O197" s="3"/>
       <c r="P197" s="3"/>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:20">
       <c r="A198">
         <v>219</v>
       </c>
@@ -8890,7 +9100,7 @@
       <c r="O198" s="3"/>
       <c r="P198" s="3"/>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:20">
       <c r="A199">
         <v>220</v>
       </c>
@@ -8924,7 +9134,7 @@
       <c r="O199" s="3"/>
       <c r="P199" s="3"/>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:20">
       <c r="A200">
         <v>221</v>
       </c>
@@ -8961,7 +9171,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:20">
       <c r="A201">
         <v>222</v>
       </c>
@@ -8997,7 +9207,7 @@
       <c r="O201" s="3"/>
       <c r="P201" s="3"/>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:20">
       <c r="A202">
         <v>223</v>
       </c>
@@ -9030,7 +9240,7 @@
       <c r="O202" s="3"/>
       <c r="P202" s="3"/>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:20">
       <c r="A203">
         <v>224</v>
       </c>
@@ -9066,7 +9276,7 @@
       <c r="O203" s="3"/>
       <c r="P203" s="3"/>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:20">
       <c r="A204">
         <v>225</v>
       </c>
@@ -9102,7 +9312,7 @@
       <c r="O204" s="3"/>
       <c r="P204" s="3"/>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:20">
       <c r="A205">
         <v>226</v>
       </c>
@@ -9135,7 +9345,7 @@
       <c r="O205" s="3"/>
       <c r="P205" s="3"/>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:20">
       <c r="A206">
         <v>227</v>
       </c>
@@ -9168,7 +9378,7 @@
       <c r="O206" s="3"/>
       <c r="P206" s="3"/>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:20">
       <c r="A207">
         <v>228</v>
       </c>
@@ -9201,7 +9411,7 @@
       <c r="O207" s="3"/>
       <c r="P207" s="3"/>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:20">
       <c r="A208">
         <v>229</v>
       </c>
@@ -9238,7 +9448,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:21">
       <c r="A209">
         <v>230</v>
       </c>
@@ -9272,7 +9482,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:21">
       <c r="A210">
         <v>231</v>
       </c>
@@ -9309,7 +9519,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:21">
       <c r="A211">
         <v>232</v>
       </c>
@@ -9346,7 +9556,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:21">
       <c r="A212">
         <v>233</v>
       </c>
@@ -9383,7 +9593,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:21">
       <c r="A213">
         <v>234</v>
       </c>
@@ -9417,8 +9627,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A214" s="7">
+    <row r="214" spans="1:21">
+      <c r="A214">
         <v>235</v>
       </c>
       <c r="B214" s="2">
@@ -9440,7 +9650,6 @@
         <v>106</v>
       </c>
       <c r="H214" s="3"/>
-      <c r="I214" s="7"/>
       <c r="J214" s="3"/>
       <c r="K214" s="6"/>
       <c r="L214" s="3"/>
@@ -9448,18 +9657,15 @@
       <c r="N214" s="3"/>
       <c r="O214" s="3"/>
       <c r="P214" s="3"/>
-      <c r="Q214" s="7" t="s">
+      <c r="Q214" t="s">
         <v>61</v>
       </c>
-      <c r="R214" s="7" t="s">
+      <c r="R214" t="s">
         <v>460</v>
       </c>
-      <c r="S214" s="7"/>
-      <c r="T214" s="7"/>
-      <c r="U214" s="7"/>
-    </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A215" s="7">
+    </row>
+    <row r="215" spans="1:21">
+      <c r="A215">
         <v>236</v>
       </c>
       <c r="B215" s="2">
@@ -9483,7 +9689,6 @@
       <c r="H215" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="I215" s="7"/>
       <c r="J215" s="3"/>
       <c r="K215" s="6"/>
       <c r="L215" s="3"/>
@@ -9491,14 +9696,9 @@
       <c r="N215" s="3"/>
       <c r="O215" s="3"/>
       <c r="P215" s="3"/>
-      <c r="Q215" s="7"/>
-      <c r="R215" s="7"/>
-      <c r="S215" s="7"/>
-      <c r="T215" s="7"/>
-      <c r="U215" s="7"/>
-    </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A216" s="7">
+    </row>
+    <row r="216" spans="1:21">
+      <c r="A216">
         <v>237</v>
       </c>
       <c r="B216" s="2">
@@ -9520,7 +9720,6 @@
         <v>41</v>
       </c>
       <c r="H216" s="3"/>
-      <c r="I216" s="7"/>
       <c r="J216" s="3"/>
       <c r="K216" s="6"/>
       <c r="L216" s="3"/>
@@ -9530,14 +9729,9 @@
       <c r="P216" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="Q216" s="7"/>
-      <c r="R216" s="7"/>
-      <c r="S216" s="7"/>
-      <c r="T216" s="7"/>
-      <c r="U216" s="7"/>
-    </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A217" s="7">
+    </row>
+    <row r="217" spans="1:21">
+      <c r="A217">
         <v>238</v>
       </c>
       <c r="B217" s="2">
@@ -9561,7 +9755,6 @@
       <c r="H217" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="I217" s="7"/>
       <c r="J217" s="3"/>
       <c r="K217" s="6"/>
       <c r="L217" s="3"/>
@@ -9569,14 +9762,9 @@
       <c r="N217" s="3"/>
       <c r="O217" s="3"/>
       <c r="P217" s="3"/>
-      <c r="Q217" s="7"/>
-      <c r="R217" s="7"/>
-      <c r="S217" s="7"/>
-      <c r="T217" s="7"/>
-      <c r="U217" s="7"/>
-    </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A218" s="7">
+    </row>
+    <row r="218" spans="1:21">
+      <c r="A218">
         <v>239</v>
       </c>
       <c r="B218" s="2">
@@ -9598,7 +9786,6 @@
         <v>41</v>
       </c>
       <c r="H218" s="3"/>
-      <c r="I218" s="7"/>
       <c r="J218" s="3"/>
       <c r="K218" s="6"/>
       <c r="L218" s="3"/>
@@ -9608,14 +9795,9 @@
       <c r="P218" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="Q218" s="7"/>
-      <c r="R218" s="7"/>
-      <c r="S218" s="7"/>
-      <c r="T218" s="7"/>
-      <c r="U218" s="7"/>
-    </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A219" s="7">
+    </row>
+    <row r="219" spans="1:21">
+      <c r="A219">
         <v>240</v>
       </c>
       <c r="B219" s="2">
@@ -9637,7 +9819,7 @@
         <v>60</v>
       </c>
       <c r="H219" s="3"/>
-      <c r="I219" s="7" t="s">
+      <c r="I219" t="s">
         <v>61</v>
       </c>
       <c r="J219" s="3" t="s">
@@ -9649,12 +9831,2577 @@
       <c r="N219" s="3"/>
       <c r="O219" s="3"/>
       <c r="P219" s="3"/>
-      <c r="Q219" s="7"/>
-      <c r="R219" s="7"/>
-      <c r="S219" s="7"/>
-      <c r="T219" s="7"/>
-      <c r="U219" s="7"/>
-    </row>
+    </row>
+    <row r="220" spans="1:21" ht="15">
+      <c r="A220" s="7">
+        <v>241</v>
+      </c>
+      <c r="B220" s="2">
+        <v>46267.464097222197</v>
+      </c>
+      <c r="C220" s="2">
+        <v>46267.464618055601</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F220" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H220" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="I220" s="7"/>
+      <c r="J220" s="3"/>
+      <c r="K220" s="6"/>
+      <c r="L220" s="3"/>
+      <c r="M220" s="3"/>
+      <c r="N220" s="3"/>
+      <c r="O220" s="3"/>
+      <c r="P220" s="3"/>
+      <c r="Q220" s="7"/>
+      <c r="R220" s="7"/>
+      <c r="S220" s="7"/>
+      <c r="T220" s="7"/>
+      <c r="U220" s="7"/>
+    </row>
+    <row r="221" spans="1:21" ht="15">
+      <c r="A221" s="7">
+        <v>242</v>
+      </c>
+      <c r="B221" s="2">
+        <v>46267.469456018502</v>
+      </c>
+      <c r="C221" s="2">
+        <v>46267.470648148097</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="F221" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="I221" s="7"/>
+      <c r="J221" s="3"/>
+      <c r="K221" s="6"/>
+      <c r="L221" s="3"/>
+      <c r="M221" s="3"/>
+      <c r="N221" s="3"/>
+      <c r="O221" s="3"/>
+      <c r="P221" s="3"/>
+      <c r="Q221" s="7"/>
+      <c r="R221" s="7"/>
+      <c r="S221" s="7"/>
+      <c r="T221" s="7"/>
+      <c r="U221" s="7"/>
+    </row>
+    <row r="222" spans="1:21" ht="15">
+      <c r="A222" s="7">
+        <v>243</v>
+      </c>
+      <c r="B222" s="2">
+        <v>46267.473171296297</v>
+      </c>
+      <c r="C222" s="2">
+        <v>46267.473831018498</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F222" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H222" s="3"/>
+      <c r="I222" s="7"/>
+      <c r="J222" s="3"/>
+      <c r="K222" s="6"/>
+      <c r="L222" s="3"/>
+      <c r="M222" s="3"/>
+      <c r="N222" s="3"/>
+      <c r="O222" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="P222" s="3"/>
+      <c r="Q222" s="7"/>
+      <c r="R222" s="7"/>
+      <c r="S222" s="7"/>
+      <c r="T222" s="7"/>
+      <c r="U222" s="7"/>
+    </row>
+    <row r="223" spans="1:21" ht="15">
+      <c r="A223" s="7">
+        <v>244</v>
+      </c>
+      <c r="B223" s="2">
+        <v>46267.474432870396</v>
+      </c>
+      <c r="C223" s="2">
+        <v>46267.4750810185</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F223" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="I223" s="7"/>
+      <c r="J223" s="3"/>
+      <c r="K223" s="6"/>
+      <c r="L223" s="3"/>
+      <c r="M223" s="3"/>
+      <c r="N223" s="3"/>
+      <c r="O223" s="3"/>
+      <c r="P223" s="3"/>
+      <c r="Q223" s="7"/>
+      <c r="R223" s="7"/>
+      <c r="S223" s="7"/>
+      <c r="T223" s="7"/>
+      <c r="U223" s="7"/>
+    </row>
+    <row r="224" spans="1:21" ht="15">
+      <c r="A224" s="7">
+        <v>245</v>
+      </c>
+      <c r="B224" s="2">
+        <v>46267.475543981498</v>
+      </c>
+      <c r="C224" s="2">
+        <v>46267.488506944399</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F224" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H224" s="3"/>
+      <c r="I224" s="7"/>
+      <c r="J224" s="3"/>
+      <c r="K224" s="6"/>
+      <c r="L224" s="3"/>
+      <c r="M224" s="3"/>
+      <c r="N224" s="3"/>
+      <c r="O224" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="P224" s="3"/>
+      <c r="Q224" s="7"/>
+      <c r="R224" s="7"/>
+      <c r="S224" s="7"/>
+      <c r="T224" s="7"/>
+      <c r="U224" s="7"/>
+    </row>
+    <row r="225" spans="1:21" ht="15">
+      <c r="A225" s="7">
+        <v>246</v>
+      </c>
+      <c r="B225" s="2">
+        <v>46267.494143518503</v>
+      </c>
+      <c r="C225" s="2">
+        <v>46267.494803240697</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="F225" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="I225" s="7"/>
+      <c r="J225" s="3"/>
+      <c r="K225" s="6"/>
+      <c r="L225" s="3"/>
+      <c r="M225" s="3"/>
+      <c r="N225" s="3"/>
+      <c r="O225" s="3"/>
+      <c r="P225" s="3"/>
+      <c r="Q225" s="7"/>
+      <c r="R225" s="7"/>
+      <c r="S225" s="7"/>
+      <c r="T225" s="7"/>
+      <c r="U225" s="7"/>
+    </row>
+    <row r="226" spans="1:21" ht="15">
+      <c r="A226" s="7">
+        <v>247</v>
+      </c>
+      <c r="B226" s="2">
+        <v>46267.497719907398</v>
+      </c>
+      <c r="C226" s="2">
+        <v>46267.498506944401</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="F226" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H226" s="3"/>
+      <c r="I226" s="7"/>
+      <c r="J226" s="3"/>
+      <c r="K226" s="6"/>
+      <c r="L226" s="3"/>
+      <c r="M226" s="3"/>
+      <c r="N226" s="3"/>
+      <c r="O226" s="3"/>
+      <c r="P226" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q226" s="7"/>
+      <c r="R226" s="7"/>
+      <c r="S226" s="7"/>
+      <c r="T226" s="7"/>
+      <c r="U226" s="7"/>
+    </row>
+    <row r="227" spans="1:21" ht="15">
+      <c r="A227" s="7">
+        <v>248</v>
+      </c>
+      <c r="B227" s="2">
+        <v>46267.532974537004</v>
+      </c>
+      <c r="C227" s="2">
+        <v>46267.534421296303</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F227" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="I227" s="7"/>
+      <c r="J227" s="3"/>
+      <c r="K227" s="6"/>
+      <c r="L227" s="3"/>
+      <c r="M227" s="3"/>
+      <c r="N227" s="3"/>
+      <c r="O227" s="3"/>
+      <c r="P227" s="3"/>
+      <c r="Q227" s="7"/>
+      <c r="R227" s="7"/>
+      <c r="S227" s="7"/>
+      <c r="T227" s="7"/>
+      <c r="U227" s="7"/>
+    </row>
+    <row r="228" spans="1:21" ht="15">
+      <c r="A228" s="7">
+        <v>249</v>
+      </c>
+      <c r="B228" s="2">
+        <v>46267.499722222201</v>
+      </c>
+      <c r="C228" s="2">
+        <v>46267.539363425902</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F228" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H228" s="3"/>
+      <c r="I228" s="7"/>
+      <c r="J228" s="3"/>
+      <c r="K228" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="L228" s="3"/>
+      <c r="M228" s="3"/>
+      <c r="N228" s="3"/>
+      <c r="O228" s="3"/>
+      <c r="P228" s="3"/>
+      <c r="Q228" s="7"/>
+      <c r="R228" s="7"/>
+      <c r="S228" s="7"/>
+      <c r="T228" s="7"/>
+      <c r="U228" s="7"/>
+    </row>
+    <row r="229" spans="1:21" ht="15">
+      <c r="A229" s="7">
+        <v>250</v>
+      </c>
+      <c r="B229" s="2">
+        <v>46267.541828703703</v>
+      </c>
+      <c r="C229" s="2">
+        <v>46267.542280092603</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F229" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H229" s="3"/>
+      <c r="I229" s="7"/>
+      <c r="J229" s="3"/>
+      <c r="K229" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="L229" s="3"/>
+      <c r="M229" s="3"/>
+      <c r="N229" s="3"/>
+      <c r="O229" s="3"/>
+      <c r="P229" s="3"/>
+      <c r="Q229" s="7"/>
+      <c r="R229" s="7"/>
+      <c r="S229" s="7"/>
+      <c r="T229" s="7"/>
+      <c r="U229" s="7"/>
+    </row>
+    <row r="230" spans="1:21" ht="15">
+      <c r="A230" s="7">
+        <v>251</v>
+      </c>
+      <c r="B230" s="2">
+        <v>46267.5635763889</v>
+      </c>
+      <c r="C230" s="2">
+        <v>46267.564016203702</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F230" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H230" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="I230" s="7"/>
+      <c r="J230" s="3"/>
+      <c r="K230" s="6"/>
+      <c r="L230" s="3"/>
+      <c r="M230" s="3"/>
+      <c r="N230" s="3"/>
+      <c r="O230" s="3"/>
+      <c r="P230" s="3"/>
+      <c r="Q230" s="7"/>
+      <c r="R230" s="7"/>
+      <c r="S230" s="7"/>
+      <c r="T230" s="7"/>
+      <c r="U230" s="7"/>
+    </row>
+    <row r="231" spans="1:21" ht="15">
+      <c r="A231" s="7">
+        <v>252</v>
+      </c>
+      <c r="B231" s="2">
+        <v>46267.568032407398</v>
+      </c>
+      <c r="C231" s="2">
+        <v>46267.568807870397</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H231" s="3"/>
+      <c r="I231" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J231" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="K231" s="6"/>
+      <c r="L231" s="3"/>
+      <c r="M231" s="3"/>
+      <c r="N231" s="3"/>
+      <c r="O231" s="3"/>
+      <c r="P231" s="3"/>
+      <c r="Q231" s="7"/>
+      <c r="R231" s="7"/>
+      <c r="S231" s="7"/>
+      <c r="T231" s="7"/>
+      <c r="U231" s="7"/>
+    </row>
+    <row r="232" spans="1:21" ht="15">
+      <c r="A232" s="7">
+        <v>253</v>
+      </c>
+      <c r="B232" s="2">
+        <v>46267.584062499998</v>
+      </c>
+      <c r="C232" s="2">
+        <v>46267.584745370397</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H232" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="I232" s="7"/>
+      <c r="J232" s="3"/>
+      <c r="K232" s="6"/>
+      <c r="L232" s="3"/>
+      <c r="M232" s="3"/>
+      <c r="N232" s="3"/>
+      <c r="O232" s="3"/>
+      <c r="P232" s="3"/>
+      <c r="Q232" s="7"/>
+      <c r="R232" s="7"/>
+      <c r="S232" s="7"/>
+      <c r="T232" s="7"/>
+      <c r="U232" s="7"/>
+    </row>
+    <row r="233" spans="1:21" ht="15">
+      <c r="A233" s="7">
+        <v>254</v>
+      </c>
+      <c r="B233" s="2">
+        <v>46267.584837962997</v>
+      </c>
+      <c r="C233" s="2">
+        <v>46267.585462962998</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H233" s="3"/>
+      <c r="I233" s="7"/>
+      <c r="J233" s="3"/>
+      <c r="K233" s="6"/>
+      <c r="L233" s="3"/>
+      <c r="M233" s="3"/>
+      <c r="N233" s="3"/>
+      <c r="O233" s="3"/>
+      <c r="P233" s="3"/>
+      <c r="Q233" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R233" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="S233" s="7"/>
+      <c r="T233" s="7"/>
+      <c r="U233" s="7"/>
+    </row>
+    <row r="234" spans="1:21" ht="15">
+      <c r="A234" s="7">
+        <v>255</v>
+      </c>
+      <c r="B234" s="2">
+        <v>46267.589004629597</v>
+      </c>
+      <c r="C234" s="2">
+        <v>46267.591249999998</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H234" s="3"/>
+      <c r="I234" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J234" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K234" s="6"/>
+      <c r="L234" s="3"/>
+      <c r="M234" s="3"/>
+      <c r="N234" s="3"/>
+      <c r="O234" s="3"/>
+      <c r="P234" s="3"/>
+      <c r="Q234" s="7"/>
+      <c r="R234" s="7"/>
+      <c r="S234" s="7"/>
+      <c r="T234" s="7"/>
+      <c r="U234" s="7"/>
+    </row>
+    <row r="235" spans="1:21" ht="15">
+      <c r="A235" s="7">
+        <v>256</v>
+      </c>
+      <c r="B235" s="2">
+        <v>46267.5944212963</v>
+      </c>
+      <c r="C235" s="2">
+        <v>46267.594814814802</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F235" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H235" s="3"/>
+      <c r="I235" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J235" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="K235" s="6"/>
+      <c r="L235" s="3"/>
+      <c r="M235" s="3"/>
+      <c r="N235" s="3"/>
+      <c r="O235" s="3"/>
+      <c r="P235" s="3"/>
+      <c r="Q235" s="7"/>
+      <c r="R235" s="7"/>
+      <c r="S235" s="7"/>
+      <c r="T235" s="7"/>
+      <c r="U235" s="7"/>
+    </row>
+    <row r="236" spans="1:21" ht="15">
+      <c r="A236" s="7">
+        <v>257</v>
+      </c>
+      <c r="B236" s="2">
+        <v>46267.597199074102</v>
+      </c>
+      <c r="C236" s="2">
+        <v>46267.600763888899</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H236" s="3"/>
+      <c r="I236" s="7"/>
+      <c r="J236" s="3"/>
+      <c r="K236" s="6"/>
+      <c r="L236" s="3"/>
+      <c r="M236" s="3"/>
+      <c r="N236" s="3"/>
+      <c r="O236" s="3"/>
+      <c r="P236" s="3"/>
+      <c r="Q236" s="7"/>
+      <c r="R236" s="7"/>
+      <c r="S236" s="7"/>
+      <c r="T236" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="U236" s="7"/>
+    </row>
+    <row r="237" spans="1:21" ht="15">
+      <c r="A237" s="7">
+        <v>258</v>
+      </c>
+      <c r="B237" s="2">
+        <v>46267.601076388899</v>
+      </c>
+      <c r="C237" s="2">
+        <v>46267.601886574099</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F237" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H237" s="3"/>
+      <c r="I237" s="7"/>
+      <c r="J237" s="3"/>
+      <c r="K237" s="6"/>
+      <c r="L237" s="3"/>
+      <c r="M237" s="3"/>
+      <c r="N237" s="3"/>
+      <c r="O237" s="3"/>
+      <c r="P237" s="3"/>
+      <c r="Q237" s="7"/>
+      <c r="R237" s="7"/>
+      <c r="S237" s="7"/>
+      <c r="T237" s="7"/>
+      <c r="U237" s="7" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="238" spans="1:21" ht="15">
+      <c r="A238" s="7">
+        <v>259</v>
+      </c>
+      <c r="B238" s="2">
+        <v>46267.597581018497</v>
+      </c>
+      <c r="C238" s="2">
+        <v>46267.602812500001</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F238" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H238" s="3"/>
+      <c r="I238" s="7"/>
+      <c r="J238" s="3"/>
+      <c r="K238" s="6"/>
+      <c r="L238" s="3"/>
+      <c r="M238" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="N238" s="3"/>
+      <c r="O238" s="3"/>
+      <c r="P238" s="3"/>
+      <c r="Q238" s="7"/>
+      <c r="R238" s="7"/>
+      <c r="S238" s="7"/>
+      <c r="T238" s="7"/>
+      <c r="U238" s="7"/>
+    </row>
+    <row r="239" spans="1:21" ht="15">
+      <c r="A239" s="7">
+        <v>260</v>
+      </c>
+      <c r="B239" s="2">
+        <v>46267.603726851899</v>
+      </c>
+      <c r="C239" s="2">
+        <v>46267.604583333297</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F239" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H239" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="I239" s="7"/>
+      <c r="J239" s="3"/>
+      <c r="K239" s="6"/>
+      <c r="L239" s="3"/>
+      <c r="M239" s="3"/>
+      <c r="N239" s="3"/>
+      <c r="O239" s="3"/>
+      <c r="P239" s="3"/>
+      <c r="Q239" s="7"/>
+      <c r="R239" s="7"/>
+      <c r="S239" s="7"/>
+      <c r="T239" s="7"/>
+      <c r="U239" s="7"/>
+    </row>
+    <row r="240" spans="1:21" ht="15">
+      <c r="A240" s="7">
+        <v>261</v>
+      </c>
+      <c r="B240" s="2">
+        <v>46267.604687500003</v>
+      </c>
+      <c r="C240" s="2">
+        <v>46267.605509259301</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F240" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H240" s="3"/>
+      <c r="I240" s="7"/>
+      <c r="J240" s="3"/>
+      <c r="K240" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="L240" s="3"/>
+      <c r="M240" s="3"/>
+      <c r="N240" s="3"/>
+      <c r="O240" s="3"/>
+      <c r="P240" s="3"/>
+      <c r="Q240" s="7"/>
+      <c r="R240" s="7"/>
+      <c r="S240" s="7"/>
+      <c r="T240" s="7"/>
+      <c r="U240" s="7"/>
+    </row>
+    <row r="241" spans="1:21" ht="15">
+      <c r="A241" s="7">
+        <v>262</v>
+      </c>
+      <c r="B241" s="2">
+        <v>46267.605567129598</v>
+      </c>
+      <c r="C241" s="2">
+        <v>46267.607280092598</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H241" s="3"/>
+      <c r="I241" s="7"/>
+      <c r="J241" s="3"/>
+      <c r="K241" s="6"/>
+      <c r="L241" s="3"/>
+      <c r="M241" s="3"/>
+      <c r="N241" s="3"/>
+      <c r="O241" s="3"/>
+      <c r="P241" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q241" s="7"/>
+      <c r="R241" s="7"/>
+      <c r="S241" s="7"/>
+      <c r="T241" s="7"/>
+      <c r="U241" s="7"/>
+    </row>
+    <row r="242" spans="1:21" ht="15">
+      <c r="A242" s="7">
+        <v>263</v>
+      </c>
+      <c r="B242" s="2">
+        <v>46267.607430555603</v>
+      </c>
+      <c r="C242" s="2">
+        <v>46267.608645833301</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H242" s="3"/>
+      <c r="I242" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J242" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="K242" s="6"/>
+      <c r="L242" s="3"/>
+      <c r="M242" s="3"/>
+      <c r="N242" s="3"/>
+      <c r="O242" s="3"/>
+      <c r="P242" s="3"/>
+      <c r="Q242" s="7"/>
+      <c r="R242" s="7"/>
+      <c r="S242" s="7"/>
+      <c r="T242" s="7"/>
+      <c r="U242" s="7"/>
+    </row>
+    <row r="243" spans="1:21" ht="15">
+      <c r="A243" s="7">
+        <v>264</v>
+      </c>
+      <c r="B243" s="2">
+        <v>46267.607337963003</v>
+      </c>
+      <c r="C243" s="2">
+        <v>46267.609479166698</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H243" s="3"/>
+      <c r="I243" s="7"/>
+      <c r="J243" s="3"/>
+      <c r="K243" s="6"/>
+      <c r="L243" s="3"/>
+      <c r="M243" s="3"/>
+      <c r="N243" s="3"/>
+      <c r="O243" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="P243" s="3"/>
+      <c r="Q243" s="7"/>
+      <c r="R243" s="7"/>
+      <c r="S243" s="7"/>
+      <c r="T243" s="7"/>
+      <c r="U243" s="7"/>
+    </row>
+    <row r="244" spans="1:21" ht="15">
+      <c r="A244" s="7">
+        <v>265</v>
+      </c>
+      <c r="B244" s="2">
+        <v>46267.603599536997</v>
+      </c>
+      <c r="C244" s="2">
+        <v>46267.609895833302</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F244" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H244" s="3"/>
+      <c r="I244" s="7"/>
+      <c r="J244" s="3"/>
+      <c r="K244" s="6"/>
+      <c r="L244" s="3"/>
+      <c r="M244" s="3"/>
+      <c r="N244" s="3"/>
+      <c r="O244" s="3"/>
+      <c r="P244" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="Q244" s="7"/>
+      <c r="R244" s="7"/>
+      <c r="S244" s="7"/>
+      <c r="T244" s="7"/>
+      <c r="U244" s="7"/>
+    </row>
+    <row r="245" spans="1:21" ht="15">
+      <c r="A245" s="7">
+        <v>266</v>
+      </c>
+      <c r="B245" s="2">
+        <v>46267.617372685199</v>
+      </c>
+      <c r="C245" s="2">
+        <v>46267.6175</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F245" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H245" s="3"/>
+      <c r="I245" s="7"/>
+      <c r="J245" s="3"/>
+      <c r="K245" s="6"/>
+      <c r="L245" s="3"/>
+      <c r="M245" s="3"/>
+      <c r="N245" s="3"/>
+      <c r="O245" s="3"/>
+      <c r="P245" s="3"/>
+      <c r="Q245" s="7"/>
+      <c r="R245" s="7"/>
+      <c r="S245" s="7"/>
+      <c r="T245" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="U245" s="7"/>
+    </row>
+    <row r="246" spans="1:21" ht="15">
+      <c r="A246" s="7">
+        <v>267</v>
+      </c>
+      <c r="B246" s="2">
+        <v>46267.614317129599</v>
+      </c>
+      <c r="C246" s="2">
+        <v>46267.627094907402</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F246" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H246" s="3"/>
+      <c r="I246" s="7"/>
+      <c r="J246" s="3"/>
+      <c r="K246" s="6"/>
+      <c r="L246" s="3"/>
+      <c r="M246" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="N246" s="3"/>
+      <c r="O246" s="3"/>
+      <c r="P246" s="3"/>
+      <c r="Q246" s="7"/>
+      <c r="R246" s="7"/>
+      <c r="S246" s="7"/>
+      <c r="T246" s="7"/>
+      <c r="U246" s="7"/>
+    </row>
+    <row r="247" spans="1:21" ht="15">
+      <c r="A247" s="7">
+        <v>268</v>
+      </c>
+      <c r="B247" s="2">
+        <v>46267.6463657407</v>
+      </c>
+      <c r="C247" s="2">
+        <v>46267.649212962999</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F247" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H247" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="I247" s="7"/>
+      <c r="J247" s="3"/>
+      <c r="K247" s="6"/>
+      <c r="L247" s="3"/>
+      <c r="M247" s="3"/>
+      <c r="N247" s="3"/>
+      <c r="O247" s="3"/>
+      <c r="P247" s="3"/>
+      <c r="Q247" s="7"/>
+      <c r="R247" s="7"/>
+      <c r="S247" s="7"/>
+      <c r="T247" s="7"/>
+      <c r="U247" s="7"/>
+    </row>
+    <row r="248" spans="1:21" ht="15">
+      <c r="A248" s="7">
+        <v>269</v>
+      </c>
+      <c r="B248" s="2">
+        <v>46267.647303240701</v>
+      </c>
+      <c r="C248" s="2">
+        <v>46267.6496990741</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="F248" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H248" s="3"/>
+      <c r="I248" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J248" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K248" s="6"/>
+      <c r="L248" s="3"/>
+      <c r="M248" s="3"/>
+      <c r="N248" s="3"/>
+      <c r="O248" s="3"/>
+      <c r="P248" s="3"/>
+      <c r="Q248" s="7"/>
+      <c r="R248" s="7"/>
+      <c r="S248" s="7"/>
+      <c r="T248" s="7"/>
+      <c r="U248" s="7"/>
+    </row>
+    <row r="249" spans="1:21" ht="15">
+      <c r="A249" s="7">
+        <v>270</v>
+      </c>
+      <c r="B249" s="2">
+        <v>46267.649444444403</v>
+      </c>
+      <c r="C249" s="2">
+        <v>46267.649826388901</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F249" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H249" s="3"/>
+      <c r="I249" s="7"/>
+      <c r="J249" s="3"/>
+      <c r="K249" s="6"/>
+      <c r="L249" s="3"/>
+      <c r="M249" s="3"/>
+      <c r="N249" s="3"/>
+      <c r="O249" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="P249" s="3"/>
+      <c r="Q249" s="7"/>
+      <c r="R249" s="7"/>
+      <c r="S249" s="7"/>
+      <c r="T249" s="7"/>
+      <c r="U249" s="7"/>
+    </row>
+    <row r="250" spans="1:21" ht="15">
+      <c r="A250" s="7">
+        <v>271</v>
+      </c>
+      <c r="B250" s="2">
+        <v>46267.649837962999</v>
+      </c>
+      <c r="C250" s="2">
+        <v>46267.650023148097</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F250" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H250" s="3"/>
+      <c r="I250" s="7"/>
+      <c r="J250" s="3"/>
+      <c r="K250" s="6"/>
+      <c r="L250" s="3"/>
+      <c r="M250" s="3"/>
+      <c r="N250" s="3"/>
+      <c r="O250" s="3"/>
+      <c r="P250" s="3"/>
+      <c r="Q250" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="R250" s="7"/>
+      <c r="S250" s="7"/>
+      <c r="T250" s="7"/>
+      <c r="U250" s="7"/>
+    </row>
+    <row r="251" spans="1:21" ht="15">
+      <c r="A251" s="7">
+        <v>272</v>
+      </c>
+      <c r="B251" s="2">
+        <v>46267.652245370402</v>
+      </c>
+      <c r="C251" s="2">
+        <v>46267.652638888903</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F251" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H251" s="3"/>
+      <c r="I251" s="7"/>
+      <c r="J251" s="3"/>
+      <c r="K251" s="6"/>
+      <c r="L251" s="3"/>
+      <c r="M251" s="3"/>
+      <c r="N251" s="3"/>
+      <c r="O251" s="3"/>
+      <c r="P251" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q251" s="7"/>
+      <c r="R251" s="7"/>
+      <c r="S251" s="7"/>
+      <c r="T251" s="7"/>
+      <c r="U251" s="7"/>
+    </row>
+    <row r="252" spans="1:21" ht="15">
+      <c r="A252" s="7">
+        <v>273</v>
+      </c>
+      <c r="B252" s="2">
+        <v>46267.672199074099</v>
+      </c>
+      <c r="C252" s="2">
+        <v>46267.673472222203</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F252" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H252" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="I252" s="7"/>
+      <c r="J252" s="3"/>
+      <c r="K252" s="6"/>
+      <c r="L252" s="3"/>
+      <c r="M252" s="3"/>
+      <c r="N252" s="3"/>
+      <c r="O252" s="3"/>
+      <c r="P252" s="3"/>
+      <c r="Q252" s="7"/>
+      <c r="R252" s="7"/>
+      <c r="S252" s="7"/>
+      <c r="T252" s="7"/>
+      <c r="U252" s="7"/>
+    </row>
+    <row r="253" spans="1:21" ht="15">
+      <c r="A253" s="7">
+        <v>274</v>
+      </c>
+      <c r="B253" s="2">
+        <v>46267.6722800926</v>
+      </c>
+      <c r="C253" s="2">
+        <v>46267.673506944397</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H253" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="I253" s="7"/>
+      <c r="J253" s="3"/>
+      <c r="K253" s="6"/>
+      <c r="L253" s="3"/>
+      <c r="M253" s="3"/>
+      <c r="N253" s="3"/>
+      <c r="O253" s="3"/>
+      <c r="P253" s="3"/>
+      <c r="Q253" s="7"/>
+      <c r="R253" s="7"/>
+      <c r="S253" s="7"/>
+      <c r="T253" s="7"/>
+      <c r="U253" s="7"/>
+    </row>
+    <row r="254" spans="1:21" ht="15">
+      <c r="A254" s="7">
+        <v>275</v>
+      </c>
+      <c r="B254" s="2">
+        <v>46267.6737615741</v>
+      </c>
+      <c r="C254" s="2">
+        <v>46267.674004629604</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F254" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H254" s="3"/>
+      <c r="I254" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="J254" s="3"/>
+      <c r="K254" s="6"/>
+      <c r="L254" s="3"/>
+      <c r="M254" s="3"/>
+      <c r="N254" s="3"/>
+      <c r="O254" s="3"/>
+      <c r="P254" s="3"/>
+      <c r="Q254" s="7"/>
+      <c r="R254" s="7"/>
+      <c r="S254" s="7"/>
+      <c r="T254" s="7"/>
+      <c r="U254" s="7"/>
+    </row>
+    <row r="255" spans="1:21" ht="15">
+      <c r="A255" s="7">
+        <v>276</v>
+      </c>
+      <c r="B255" s="2">
+        <v>46267.6739467593</v>
+      </c>
+      <c r="C255" s="2">
+        <v>46267.674444444398</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F255" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H255" s="3"/>
+      <c r="I255" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J255" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="K255" s="6"/>
+      <c r="L255" s="3"/>
+      <c r="M255" s="3"/>
+      <c r="N255" s="3"/>
+      <c r="O255" s="3"/>
+      <c r="P255" s="3"/>
+      <c r="Q255" s="7"/>
+      <c r="R255" s="7"/>
+      <c r="S255" s="7"/>
+      <c r="T255" s="7"/>
+      <c r="U255" s="7"/>
+    </row>
+    <row r="256" spans="1:21" ht="15">
+      <c r="A256" s="7">
+        <v>277</v>
+      </c>
+      <c r="B256" s="2">
+        <v>46267.674224536997</v>
+      </c>
+      <c r="C256" s="2">
+        <v>46267.674560185202</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H256" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="I256" s="7"/>
+      <c r="J256" s="3"/>
+      <c r="K256" s="6"/>
+      <c r="L256" s="3"/>
+      <c r="M256" s="3"/>
+      <c r="N256" s="3"/>
+      <c r="O256" s="3"/>
+      <c r="P256" s="3"/>
+      <c r="Q256" s="7"/>
+      <c r="R256" s="7"/>
+      <c r="S256" s="7"/>
+      <c r="T256" s="7"/>
+      <c r="U256" s="7"/>
+    </row>
+    <row r="257" spans="1:21" ht="15">
+      <c r="A257" s="7">
+        <v>278</v>
+      </c>
+      <c r="B257" s="2">
+        <v>46267.674502314803</v>
+      </c>
+      <c r="C257" s="2">
+        <v>46267.675138888902</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F257" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H257" s="3"/>
+      <c r="I257" s="7"/>
+      <c r="J257" s="3"/>
+      <c r="K257" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="L257" s="3"/>
+      <c r="M257" s="3"/>
+      <c r="N257" s="3"/>
+      <c r="O257" s="3"/>
+      <c r="P257" s="3"/>
+      <c r="Q257" s="7"/>
+      <c r="R257" s="7"/>
+      <c r="S257" s="7"/>
+      <c r="T257" s="7"/>
+      <c r="U257" s="7"/>
+    </row>
+    <row r="258" spans="1:21" ht="15">
+      <c r="A258" s="7">
+        <v>279</v>
+      </c>
+      <c r="B258" s="2">
+        <v>46267.674710648098</v>
+      </c>
+      <c r="C258" s="2">
+        <v>46267.675335648099</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F258" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H258" s="3"/>
+      <c r="I258" s="7"/>
+      <c r="J258" s="3"/>
+      <c r="K258" s="6"/>
+      <c r="L258" s="3"/>
+      <c r="M258" s="3"/>
+      <c r="N258" s="3"/>
+      <c r="O258" s="3"/>
+      <c r="P258" s="3"/>
+      <c r="Q258" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R258" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="S258" s="7"/>
+      <c r="T258" s="7"/>
+      <c r="U258" s="7"/>
+    </row>
+    <row r="259" spans="1:21" ht="15">
+      <c r="A259" s="7">
+        <v>280</v>
+      </c>
+      <c r="B259" s="2">
+        <v>46267.675208333298</v>
+      </c>
+      <c r="C259" s="2">
+        <v>46267.6792361111</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F259" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H259" s="3"/>
+      <c r="I259" s="7"/>
+      <c r="J259" s="3"/>
+      <c r="K259" s="6"/>
+      <c r="L259" s="3"/>
+      <c r="M259" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="N259" s="3"/>
+      <c r="O259" s="3"/>
+      <c r="P259" s="3"/>
+      <c r="Q259" s="7"/>
+      <c r="R259" s="7"/>
+      <c r="S259" s="7"/>
+      <c r="T259" s="7"/>
+      <c r="U259" s="7"/>
+    </row>
+    <row r="260" spans="1:21" ht="15">
+      <c r="A260" s="7">
+        <v>281</v>
+      </c>
+      <c r="B260" s="2">
+        <v>46267.681701388901</v>
+      </c>
+      <c r="C260" s="2">
+        <v>46267.683703703697</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F260" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H260" s="3"/>
+      <c r="I260" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J260" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="K260" s="6"/>
+      <c r="L260" s="3"/>
+      <c r="M260" s="3"/>
+      <c r="N260" s="3"/>
+      <c r="O260" s="3"/>
+      <c r="P260" s="3"/>
+      <c r="Q260" s="7"/>
+      <c r="R260" s="7"/>
+      <c r="S260" s="7"/>
+      <c r="T260" s="7"/>
+      <c r="U260" s="7"/>
+    </row>
+    <row r="261" spans="1:21" ht="15">
+      <c r="A261" s="7">
+        <v>282</v>
+      </c>
+      <c r="B261" s="2">
+        <v>46267.652766203697</v>
+      </c>
+      <c r="C261" s="2">
+        <v>46267.684351851902</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F261" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H261" s="3"/>
+      <c r="I261" s="7"/>
+      <c r="J261" s="3"/>
+      <c r="K261" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="L261" s="3"/>
+      <c r="M261" s="3"/>
+      <c r="N261" s="3"/>
+      <c r="O261" s="3"/>
+      <c r="P261" s="3"/>
+      <c r="Q261" s="7"/>
+      <c r="R261" s="7"/>
+      <c r="S261" s="7"/>
+      <c r="T261" s="7"/>
+      <c r="U261" s="7"/>
+    </row>
+    <row r="262" spans="1:21" ht="15">
+      <c r="A262" s="7">
+        <v>283</v>
+      </c>
+      <c r="B262" s="2">
+        <v>46267.684490740699</v>
+      </c>
+      <c r="C262" s="2">
+        <v>46267.684895833299</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F262" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H262" s="3"/>
+      <c r="I262" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J262" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="K262" s="6"/>
+      <c r="L262" s="3"/>
+      <c r="M262" s="3"/>
+      <c r="N262" s="3"/>
+      <c r="O262" s="3"/>
+      <c r="P262" s="3"/>
+      <c r="Q262" s="7"/>
+      <c r="R262" s="7"/>
+      <c r="S262" s="7"/>
+      <c r="T262" s="7"/>
+      <c r="U262" s="7"/>
+    </row>
+    <row r="263" spans="1:21" ht="15">
+      <c r="A263" s="7">
+        <v>284</v>
+      </c>
+      <c r="B263" s="2">
+        <v>46267.682893518497</v>
+      </c>
+      <c r="C263" s="2">
+        <v>46267.684988425899</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F263" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H263" s="3"/>
+      <c r="I263" s="7"/>
+      <c r="J263" s="3"/>
+      <c r="K263" s="6"/>
+      <c r="L263" s="3"/>
+      <c r="M263" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="N263" s="3"/>
+      <c r="O263" s="3"/>
+      <c r="P263" s="3"/>
+      <c r="Q263" s="7"/>
+      <c r="R263" s="7"/>
+      <c r="S263" s="7"/>
+      <c r="T263" s="7"/>
+      <c r="U263" s="7"/>
+    </row>
+    <row r="264" spans="1:21" ht="15">
+      <c r="A264" s="7">
+        <v>285</v>
+      </c>
+      <c r="B264" s="2">
+        <v>46267.684745370403</v>
+      </c>
+      <c r="C264" s="2">
+        <v>46267.685127314799</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F264" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H264" s="3"/>
+      <c r="I264" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J264" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="K264" s="6"/>
+      <c r="L264" s="3"/>
+      <c r="M264" s="3"/>
+      <c r="N264" s="3"/>
+      <c r="O264" s="3"/>
+      <c r="P264" s="3"/>
+      <c r="Q264" s="7"/>
+      <c r="R264" s="7"/>
+      <c r="S264" s="7"/>
+      <c r="T264" s="7"/>
+      <c r="U264" s="7"/>
+    </row>
+    <row r="265" spans="1:21" ht="15">
+      <c r="A265" s="7">
+        <v>286</v>
+      </c>
+      <c r="B265" s="2">
+        <v>46267.684166666702</v>
+      </c>
+      <c r="C265" s="2">
+        <v>46267.685335648101</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F265" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H265" s="3"/>
+      <c r="I265" s="7"/>
+      <c r="J265" s="3"/>
+      <c r="K265" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="L265" s="3"/>
+      <c r="M265" s="3"/>
+      <c r="N265" s="3"/>
+      <c r="O265" s="3"/>
+      <c r="P265" s="3"/>
+      <c r="Q265" s="7"/>
+      <c r="R265" s="7"/>
+      <c r="S265" s="7"/>
+      <c r="T265" s="7"/>
+      <c r="U265" s="7"/>
+    </row>
+    <row r="266" spans="1:21" ht="15">
+      <c r="A266" s="7">
+        <v>287</v>
+      </c>
+      <c r="B266" s="2">
+        <v>46267.6854282407</v>
+      </c>
+      <c r="C266" s="2">
+        <v>46267.686111111099</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F266" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H266" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="I266" s="7"/>
+      <c r="J266" s="3"/>
+      <c r="K266" s="6"/>
+      <c r="L266" s="3"/>
+      <c r="M266" s="3"/>
+      <c r="N266" s="3"/>
+      <c r="O266" s="3"/>
+      <c r="P266" s="3"/>
+      <c r="Q266" s="7"/>
+      <c r="R266" s="7"/>
+      <c r="S266" s="7"/>
+      <c r="T266" s="7"/>
+      <c r="U266" s="7"/>
+    </row>
+    <row r="267" spans="1:21" ht="15">
+      <c r="A267" s="7">
+        <v>288</v>
+      </c>
+      <c r="B267" s="2">
+        <v>46267.685624999998</v>
+      </c>
+      <c r="C267" s="2">
+        <v>46267.6863773148</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F267" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H267" s="3"/>
+      <c r="I267" s="7"/>
+      <c r="J267" s="3"/>
+      <c r="K267" s="6"/>
+      <c r="L267" s="3"/>
+      <c r="M267" s="3"/>
+      <c r="N267" s="3"/>
+      <c r="O267" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="P267" s="3"/>
+      <c r="Q267" s="7"/>
+      <c r="R267" s="7"/>
+      <c r="S267" s="7"/>
+      <c r="T267" s="7"/>
+      <c r="U267" s="7"/>
+    </row>
+    <row r="268" spans="1:21" ht="15">
+      <c r="A268" s="7">
+        <v>289</v>
+      </c>
+      <c r="B268" s="2">
+        <v>46267.686446759297</v>
+      </c>
+      <c r="C268" s="2">
+        <v>46267.6871412037</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F268" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H268" s="3"/>
+      <c r="I268" s="7"/>
+      <c r="J268" s="3"/>
+      <c r="K268" s="6"/>
+      <c r="L268" s="3"/>
+      <c r="M268" s="3"/>
+      <c r="N268" s="3"/>
+      <c r="O268" s="3"/>
+      <c r="P268" s="3"/>
+      <c r="Q268" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R268" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="S268" s="7"/>
+      <c r="T268" s="7"/>
+      <c r="U268" s="7"/>
+    </row>
+    <row r="269" spans="1:21" ht="15">
+      <c r="A269" s="7">
+        <v>290</v>
+      </c>
+      <c r="B269" s="2">
+        <v>46267.686215277798</v>
+      </c>
+      <c r="C269" s="2">
+        <v>46267.687222222201</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F269" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H269" s="3"/>
+      <c r="I269" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J269" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="K269" s="6"/>
+      <c r="L269" s="3"/>
+      <c r="M269" s="3"/>
+      <c r="N269" s="3"/>
+      <c r="O269" s="3"/>
+      <c r="P269" s="3"/>
+      <c r="Q269" s="7"/>
+      <c r="R269" s="7"/>
+      <c r="S269" s="7"/>
+      <c r="T269" s="7"/>
+      <c r="U269" s="7"/>
+    </row>
+    <row r="270" spans="1:21" ht="15">
+      <c r="A270" s="7">
+        <v>291</v>
+      </c>
+      <c r="B270" s="2">
+        <v>46267.680381944403</v>
+      </c>
+      <c r="C270" s="2">
+        <v>46267.687557870398</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F270" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H270" s="3"/>
+      <c r="I270" s="7"/>
+      <c r="J270" s="3"/>
+      <c r="K270" s="6"/>
+      <c r="L270" s="3"/>
+      <c r="M270" s="3"/>
+      <c r="N270" s="3"/>
+      <c r="O270" s="3"/>
+      <c r="P270" s="3"/>
+      <c r="Q270" s="7"/>
+      <c r="R270" s="7"/>
+      <c r="S270" s="7"/>
+      <c r="T270" s="7"/>
+      <c r="U270" s="7" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="271" spans="1:21" ht="15">
+      <c r="A271" s="7">
+        <v>292</v>
+      </c>
+      <c r="B271" s="2">
+        <v>46267.6862384259</v>
+      </c>
+      <c r="C271" s="2">
+        <v>46267.687847222202</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F271" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H271" s="3"/>
+      <c r="I271" s="7"/>
+      <c r="J271" s="3"/>
+      <c r="K271" s="6"/>
+      <c r="L271" s="3"/>
+      <c r="M271" s="3"/>
+      <c r="N271" s="3"/>
+      <c r="O271" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="P271" s="3"/>
+      <c r="Q271" s="7"/>
+      <c r="R271" s="7"/>
+      <c r="S271" s="7"/>
+      <c r="T271" s="7"/>
+      <c r="U271" s="7"/>
+    </row>
+    <row r="272" spans="1:21" ht="15">
+      <c r="A272" s="7">
+        <v>293</v>
+      </c>
+      <c r="B272" s="2">
+        <v>46267.688182870399</v>
+      </c>
+      <c r="C272" s="2">
+        <v>46267.690393518496</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F272" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H272" s="3"/>
+      <c r="I272" s="7"/>
+      <c r="J272" s="3"/>
+      <c r="K272" s="6"/>
+      <c r="L272" s="3"/>
+      <c r="M272" s="3"/>
+      <c r="N272" s="3"/>
+      <c r="O272" s="3"/>
+      <c r="P272" s="3"/>
+      <c r="Q272" s="7"/>
+      <c r="R272" s="7"/>
+      <c r="S272" s="7"/>
+      <c r="T272" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="U272" s="7"/>
+    </row>
+    <row r="273" spans="1:21" ht="15">
+      <c r="A273" s="7">
+        <v>294</v>
+      </c>
+      <c r="B273" s="2">
+        <v>46267.6875462963</v>
+      </c>
+      <c r="C273" s="2">
+        <v>46267.691342592603</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F273" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H273" s="3"/>
+      <c r="I273" s="7"/>
+      <c r="J273" s="3"/>
+      <c r="K273" s="6"/>
+      <c r="L273" s="3"/>
+      <c r="M273" s="3"/>
+      <c r="N273" s="3"/>
+      <c r="O273" s="3"/>
+      <c r="P273" s="3"/>
+      <c r="Q273" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R273" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="S273" s="7"/>
+      <c r="T273" s="7"/>
+      <c r="U273" s="7"/>
+    </row>
+    <row r="274" spans="1:21" ht="15">
+      <c r="A274" s="7">
+        <v>295</v>
+      </c>
+      <c r="B274" s="2">
+        <v>46267.692060185203</v>
+      </c>
+      <c r="C274" s="2">
+        <v>46267.692465277803</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F274" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H274" s="3"/>
+      <c r="I274" s="7"/>
+      <c r="J274" s="3"/>
+      <c r="K274" s="6"/>
+      <c r="L274" s="3"/>
+      <c r="M274" s="3"/>
+      <c r="N274" s="3"/>
+      <c r="O274" s="3"/>
+      <c r="P274" s="3"/>
+      <c r="Q274" s="7"/>
+      <c r="R274" s="7"/>
+      <c r="S274" s="7"/>
+      <c r="T274" s="7"/>
+      <c r="U274" s="7" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="275" spans="1:21" ht="15">
+      <c r="A275" s="7">
+        <v>296</v>
+      </c>
+      <c r="B275" s="2">
+        <v>46267.693506944401</v>
+      </c>
+      <c r="C275" s="2">
+        <v>46267.693796296298</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F275" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H275" s="3"/>
+      <c r="I275" s="7"/>
+      <c r="J275" s="3"/>
+      <c r="K275" s="6"/>
+      <c r="L275" s="3"/>
+      <c r="M275" s="3"/>
+      <c r="N275" s="3"/>
+      <c r="O275" s="3"/>
+      <c r="P275" s="3"/>
+      <c r="Q275" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R275" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="S275" s="7"/>
+      <c r="T275" s="7"/>
+      <c r="U275" s="7"/>
+    </row>
+    <row r="276" spans="1:21" ht="15">
+      <c r="A276" s="7">
+        <v>297</v>
+      </c>
+      <c r="B276" s="2">
+        <v>46267.691550925898</v>
+      </c>
+      <c r="C276" s="2">
+        <v>46267.694571759297</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F276" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H276" s="3"/>
+      <c r="I276" s="7"/>
+      <c r="J276" s="3"/>
+      <c r="K276" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="L276" s="3"/>
+      <c r="M276" s="3"/>
+      <c r="N276" s="3"/>
+      <c r="O276" s="3"/>
+      <c r="P276" s="3"/>
+      <c r="Q276" s="7"/>
+      <c r="R276" s="7"/>
+      <c r="S276" s="7"/>
+      <c r="T276" s="7"/>
+      <c r="U276" s="7"/>
+    </row>
+    <row r="277" spans="1:21" ht="15">
+      <c r="A277" s="7">
+        <v>298</v>
+      </c>
+      <c r="B277" s="2">
+        <v>46267.696458333303</v>
+      </c>
+      <c r="C277" s="2">
+        <v>46267.701423611099</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F277" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H277" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="I277" s="7"/>
+      <c r="J277" s="3"/>
+      <c r="K277" s="6"/>
+      <c r="L277" s="3"/>
+      <c r="M277" s="3"/>
+      <c r="N277" s="3"/>
+      <c r="O277" s="3"/>
+      <c r="P277" s="3"/>
+      <c r="Q277" s="7"/>
+      <c r="R277" s="7"/>
+      <c r="S277" s="7"/>
+      <c r="T277" s="7"/>
+      <c r="U277" s="7"/>
+    </row>
+    <row r="278" spans="1:21" ht="15">
+      <c r="A278" s="7">
+        <v>299</v>
+      </c>
+      <c r="B278" s="2">
+        <v>46267.707013888903</v>
+      </c>
+      <c r="C278" s="2">
+        <v>46267.707430555602</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F278" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H278" s="3"/>
+      <c r="I278" s="7"/>
+      <c r="J278" s="3"/>
+      <c r="K278" s="6"/>
+      <c r="L278" s="3"/>
+      <c r="M278" s="3"/>
+      <c r="N278" s="3"/>
+      <c r="O278" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="P278" s="3"/>
+      <c r="Q278" s="7"/>
+      <c r="R278" s="7"/>
+      <c r="S278" s="7"/>
+      <c r="T278" s="7"/>
+      <c r="U278" s="7"/>
+    </row>
+    <row r="279" spans="1:21" ht="15">
+      <c r="A279" s="7">
+        <v>300</v>
+      </c>
+      <c r="B279" s="2">
+        <v>46267.707511574103</v>
+      </c>
+      <c r="C279" s="2">
+        <v>46267.707928240699</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F279" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H279" s="3"/>
+      <c r="I279" s="7"/>
+      <c r="J279" s="3"/>
+      <c r="K279" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="L279" s="3"/>
+      <c r="M279" s="3"/>
+      <c r="N279" s="3"/>
+      <c r="O279" s="3"/>
+      <c r="P279" s="3"/>
+      <c r="Q279" s="7"/>
+      <c r="R279" s="7"/>
+      <c r="S279" s="7"/>
+      <c r="T279" s="7"/>
+      <c r="U279" s="7"/>
+    </row>
+    <row r="280" spans="1:21" ht="15">
+      <c r="A280" s="7">
+        <v>301</v>
+      </c>
+      <c r="B280" s="2">
+        <v>46267.729085648098</v>
+      </c>
+      <c r="C280" s="2">
+        <v>46267.729444444398</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F280" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H280" s="3"/>
+      <c r="I280" s="7"/>
+      <c r="J280" s="3"/>
+      <c r="K280" s="6"/>
+      <c r="L280" s="3"/>
+      <c r="M280" s="3"/>
+      <c r="N280" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="O280" s="3"/>
+      <c r="P280" s="3"/>
+      <c r="Q280" s="7"/>
+      <c r="R280" s="7"/>
+      <c r="S280" s="7"/>
+      <c r="T280" s="7"/>
+      <c r="U280" s="7"/>
+    </row>
+    <row r="281" spans="1:21" ht="15">
+      <c r="A281" s="7">
+        <v>302</v>
+      </c>
+      <c r="B281" s="2">
+        <v>46267.6871412037</v>
+      </c>
+      <c r="C281" s="2">
+        <v>46267.7335648148</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F281" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H281" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="I281" s="7"/>
+      <c r="J281" s="3"/>
+      <c r="K281" s="6"/>
+      <c r="L281" s="3"/>
+      <c r="M281" s="3"/>
+      <c r="N281" s="3"/>
+      <c r="O281" s="3"/>
+      <c r="P281" s="3"/>
+      <c r="Q281" s="7"/>
+      <c r="R281" s="7"/>
+      <c r="S281" s="7"/>
+      <c r="T281" s="7"/>
+      <c r="U281" s="7"/>
+    </row>
+    <row r="282" spans="1:21" ht="15">
+      <c r="A282" s="7">
+        <v>303</v>
+      </c>
+      <c r="B282" s="2">
+        <v>46267.736898148098</v>
+      </c>
+      <c r="C282" s="2">
+        <v>46267.747696759303</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F282" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H282" s="3"/>
+      <c r="I282" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J282" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="K282" s="6"/>
+      <c r="L282" s="3"/>
+      <c r="M282" s="3"/>
+      <c r="N282" s="3"/>
+      <c r="O282" s="3"/>
+      <c r="P282" s="3"/>
+      <c r="Q282" s="7"/>
+      <c r="R282" s="7"/>
+      <c r="S282" s="7"/>
+      <c r="T282" s="7"/>
+      <c r="U282" s="7"/>
+    </row>
+    <row r="283" spans="1:21" ht="15">
+      <c r="A283" s="7">
+        <v>304</v>
+      </c>
+      <c r="B283" s="2">
+        <v>46267.822314814803</v>
+      </c>
+      <c r="C283" s="2">
+        <v>46267.822615740697</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F283" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H283" s="3"/>
+      <c r="I283" s="7"/>
+      <c r="J283" s="3"/>
+      <c r="K283" s="6"/>
+      <c r="L283" s="3"/>
+      <c r="M283" s="3"/>
+      <c r="N283" s="3"/>
+      <c r="O283" s="3"/>
+      <c r="P283" s="3"/>
+      <c r="Q283" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="R283" s="7"/>
+      <c r="S283" s="7"/>
+      <c r="T283" s="7"/>
+      <c r="U283" s="7"/>
+    </row>
+    <row r="284" spans="1:21" ht="15">
+      <c r="A284" s="7">
+        <v>306</v>
+      </c>
+      <c r="B284" s="2">
+        <v>46267.8491319444</v>
+      </c>
+      <c r="C284" s="2">
+        <v>46267.849409722199</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F284" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H284" s="3"/>
+      <c r="I284" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J284" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="K284" s="6"/>
+      <c r="L284" s="3"/>
+      <c r="M284" s="3"/>
+      <c r="N284" s="3"/>
+      <c r="O284" s="3"/>
+      <c r="P284" s="3"/>
+      <c r="Q284" s="7"/>
+      <c r="R284" s="7"/>
+      <c r="S284" s="7"/>
+      <c r="T284" s="7"/>
+      <c r="U284" s="7"/>
+    </row>
+    <row r="285" spans="1:21" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="345" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F187C74B-4F6D-4931-8B8F-C92DC49DD869}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7A9C1B7-E6EC-4B93-A9E3-29178CDA3E68}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="543">
   <si>
     <t>Id</t>
   </si>
@@ -1644,6 +1644,27 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/4712379c-d19f-4ec7-abdf-95c073eea671_Starbucks%20El%20Rosario%201.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG20260822153336_Starbucks%20ITESM%20Esta.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Boulevard.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260902-WA0014_Starbucks%20Encuentro.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17884631063699144949272502441436_Starbucks%20Encuentro.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/8E17B469-D09A-4C7F-9FF0-7C153FFB61E7_Starbucks%20El%20Rosario.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG-20260903-WA0047_Martin%20Gerardo%20Herre.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Echegaray.jpg</t>
   </si>
 </sst>
 </file>
@@ -1778,8 +1799,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U284" totalsRowShown="0">
-  <autoFilter ref="A1:U284" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U293" totalsRowShown="0">
+  <autoFilter ref="A1:U293" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1932,7 +1953,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="306" latestEventMarker="541">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="315" latestEventMarker="550">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2257,7 +2278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U285"/>
+  <dimension ref="A1:U294"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -9448,7 +9469,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="209" spans="1:21">
+    <row r="209" spans="1:19">
       <c r="A209">
         <v>230</v>
       </c>
@@ -9482,7 +9503,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="210" spans="1:21">
+    <row r="210" spans="1:19">
       <c r="A210">
         <v>231</v>
       </c>
@@ -9519,7 +9540,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="211" spans="1:21">
+    <row r="211" spans="1:19">
       <c r="A211">
         <v>232</v>
       </c>
@@ -9556,7 +9577,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="212" spans="1:21">
+    <row r="212" spans="1:19">
       <c r="A212">
         <v>233</v>
       </c>
@@ -9593,7 +9614,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="213" spans="1:21">
+    <row r="213" spans="1:19">
       <c r="A213">
         <v>234</v>
       </c>
@@ -9627,7 +9648,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="214" spans="1:21">
+    <row r="214" spans="1:19">
       <c r="A214">
         <v>235</v>
       </c>
@@ -9664,7 +9685,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="215" spans="1:21">
+    <row r="215" spans="1:19">
       <c r="A215">
         <v>236</v>
       </c>
@@ -9697,7 +9718,7 @@
       <c r="O215" s="3"/>
       <c r="P215" s="3"/>
     </row>
-    <row r="216" spans="1:21">
+    <row r="216" spans="1:19">
       <c r="A216">
         <v>237</v>
       </c>
@@ -9730,7 +9751,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="217" spans="1:21">
+    <row r="217" spans="1:19">
       <c r="A217">
         <v>238</v>
       </c>
@@ -9763,7 +9784,7 @@
       <c r="O217" s="3"/>
       <c r="P217" s="3"/>
     </row>
-    <row r="218" spans="1:21">
+    <row r="218" spans="1:19">
       <c r="A218">
         <v>239</v>
       </c>
@@ -9796,7 +9817,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="219" spans="1:21">
+    <row r="219" spans="1:19">
       <c r="A219">
         <v>240</v>
       </c>
@@ -9832,8 +9853,8 @@
       <c r="O219" s="3"/>
       <c r="P219" s="3"/>
     </row>
-    <row r="220" spans="1:21" ht="15">
-      <c r="A220" s="7">
+    <row r="220" spans="1:19" ht="15">
+      <c r="A220">
         <v>241</v>
       </c>
       <c r="B220" s="2">
@@ -9857,7 +9878,6 @@
       <c r="H220" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="I220" s="7"/>
       <c r="J220" s="3"/>
       <c r="K220" s="6"/>
       <c r="L220" s="3"/>
@@ -9865,14 +9885,9 @@
       <c r="N220" s="3"/>
       <c r="O220" s="3"/>
       <c r="P220" s="3"/>
-      <c r="Q220" s="7"/>
-      <c r="R220" s="7"/>
-      <c r="S220" s="7"/>
-      <c r="T220" s="7"/>
-      <c r="U220" s="7"/>
-    </row>
-    <row r="221" spans="1:21" ht="15">
-      <c r="A221" s="7">
+    </row>
+    <row r="221" spans="1:19" ht="15">
+      <c r="A221">
         <v>242</v>
       </c>
       <c r="B221" s="2">
@@ -9896,7 +9911,6 @@
       <c r="H221" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="I221" s="7"/>
       <c r="J221" s="3"/>
       <c r="K221" s="6"/>
       <c r="L221" s="3"/>
@@ -9904,14 +9918,9 @@
       <c r="N221" s="3"/>
       <c r="O221" s="3"/>
       <c r="P221" s="3"/>
-      <c r="Q221" s="7"/>
-      <c r="R221" s="7"/>
-      <c r="S221" s="7"/>
-      <c r="T221" s="7"/>
-      <c r="U221" s="7"/>
-    </row>
-    <row r="222" spans="1:21" ht="15">
-      <c r="A222" s="7">
+    </row>
+    <row r="222" spans="1:19" ht="15">
+      <c r="A222">
         <v>243</v>
       </c>
       <c r="B222" s="2">
@@ -9933,7 +9942,6 @@
         <v>33</v>
       </c>
       <c r="H222" s="3"/>
-      <c r="I222" s="7"/>
       <c r="J222" s="3"/>
       <c r="K222" s="6"/>
       <c r="L222" s="3"/>
@@ -9943,14 +9951,9 @@
         <v>470</v>
       </c>
       <c r="P222" s="3"/>
-      <c r="Q222" s="7"/>
-      <c r="R222" s="7"/>
-      <c r="S222" s="7"/>
-      <c r="T222" s="7"/>
-      <c r="U222" s="7"/>
-    </row>
-    <row r="223" spans="1:21" ht="15">
-      <c r="A223" s="7">
+    </row>
+    <row r="223" spans="1:19" ht="15">
+      <c r="A223">
         <v>244</v>
       </c>
       <c r="B223" s="2">
@@ -9974,7 +9977,6 @@
       <c r="H223" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="I223" s="7"/>
       <c r="J223" s="3"/>
       <c r="K223" s="6"/>
       <c r="L223" s="3"/>
@@ -9982,14 +9984,9 @@
       <c r="N223" s="3"/>
       <c r="O223" s="3"/>
       <c r="P223" s="3"/>
-      <c r="Q223" s="7"/>
-      <c r="R223" s="7"/>
-      <c r="S223" s="7"/>
-      <c r="T223" s="7"/>
-      <c r="U223" s="7"/>
-    </row>
-    <row r="224" spans="1:21" ht="15">
-      <c r="A224" s="7">
+    </row>
+    <row r="224" spans="1:19" ht="15">
+      <c r="A224">
         <v>245</v>
       </c>
       <c r="B224" s="2">
@@ -10011,7 +10008,6 @@
         <v>33</v>
       </c>
       <c r="H224" s="3"/>
-      <c r="I224" s="7"/>
       <c r="J224" s="3"/>
       <c r="K224" s="6"/>
       <c r="L224" s="3"/>
@@ -10021,14 +10017,9 @@
         <v>472</v>
       </c>
       <c r="P224" s="3"/>
-      <c r="Q224" s="7"/>
-      <c r="R224" s="7"/>
-      <c r="S224" s="7"/>
-      <c r="T224" s="7"/>
-      <c r="U224" s="7"/>
     </row>
     <row r="225" spans="1:21" ht="15">
-      <c r="A225" s="7">
+      <c r="A225">
         <v>246</v>
       </c>
       <c r="B225" s="2">
@@ -10052,7 +10043,6 @@
       <c r="H225" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="I225" s="7"/>
       <c r="J225" s="3"/>
       <c r="K225" s="6"/>
       <c r="L225" s="3"/>
@@ -10060,14 +10050,9 @@
       <c r="N225" s="3"/>
       <c r="O225" s="3"/>
       <c r="P225" s="3"/>
-      <c r="Q225" s="7"/>
-      <c r="R225" s="7"/>
-      <c r="S225" s="7"/>
-      <c r="T225" s="7"/>
-      <c r="U225" s="7"/>
     </row>
     <row r="226" spans="1:21" ht="15">
-      <c r="A226" s="7">
+      <c r="A226">
         <v>247</v>
       </c>
       <c r="B226" s="2">
@@ -10089,7 +10074,6 @@
         <v>41</v>
       </c>
       <c r="H226" s="3"/>
-      <c r="I226" s="7"/>
       <c r="J226" s="3"/>
       <c r="K226" s="6"/>
       <c r="L226" s="3"/>
@@ -10099,14 +10083,9 @@
       <c r="P226" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="Q226" s="7"/>
-      <c r="R226" s="7"/>
-      <c r="S226" s="7"/>
-      <c r="T226" s="7"/>
-      <c r="U226" s="7"/>
     </row>
     <row r="227" spans="1:21" ht="15">
-      <c r="A227" s="7">
+      <c r="A227">
         <v>248</v>
       </c>
       <c r="B227" s="2">
@@ -10130,7 +10109,6 @@
       <c r="H227" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="I227" s="7"/>
       <c r="J227" s="3"/>
       <c r="K227" s="6"/>
       <c r="L227" s="3"/>
@@ -10138,14 +10116,9 @@
       <c r="N227" s="3"/>
       <c r="O227" s="3"/>
       <c r="P227" s="3"/>
-      <c r="Q227" s="7"/>
-      <c r="R227" s="7"/>
-      <c r="S227" s="7"/>
-      <c r="T227" s="7"/>
-      <c r="U227" s="7"/>
     </row>
     <row r="228" spans="1:21" ht="15">
-      <c r="A228" s="7">
+      <c r="A228">
         <v>249</v>
       </c>
       <c r="B228" s="2">
@@ -10167,7 +10140,6 @@
         <v>38</v>
       </c>
       <c r="H228" s="3"/>
-      <c r="I228" s="7"/>
       <c r="J228" s="3"/>
       <c r="K228" s="6" t="s">
         <v>476</v>
@@ -10177,14 +10149,9 @@
       <c r="N228" s="3"/>
       <c r="O228" s="3"/>
       <c r="P228" s="3"/>
-      <c r="Q228" s="7"/>
-      <c r="R228" s="7"/>
-      <c r="S228" s="7"/>
-      <c r="T228" s="7"/>
-      <c r="U228" s="7"/>
     </row>
     <row r="229" spans="1:21" ht="15">
-      <c r="A229" s="7">
+      <c r="A229">
         <v>250</v>
       </c>
       <c r="B229" s="2">
@@ -10206,7 +10173,6 @@
         <v>38</v>
       </c>
       <c r="H229" s="3"/>
-      <c r="I229" s="7"/>
       <c r="J229" s="3"/>
       <c r="K229" s="6" t="s">
         <v>477</v>
@@ -10216,14 +10182,9 @@
       <c r="N229" s="3"/>
       <c r="O229" s="3"/>
       <c r="P229" s="3"/>
-      <c r="Q229" s="7"/>
-      <c r="R229" s="7"/>
-      <c r="S229" s="7"/>
-      <c r="T229" s="7"/>
-      <c r="U229" s="7"/>
     </row>
     <row r="230" spans="1:21" ht="15">
-      <c r="A230" s="7">
+      <c r="A230">
         <v>251</v>
       </c>
       <c r="B230" s="2">
@@ -10247,7 +10208,6 @@
       <c r="H230" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="I230" s="7"/>
       <c r="J230" s="3"/>
       <c r="K230" s="6"/>
       <c r="L230" s="3"/>
@@ -10255,14 +10215,9 @@
       <c r="N230" s="3"/>
       <c r="O230" s="3"/>
       <c r="P230" s="3"/>
-      <c r="Q230" s="7"/>
-      <c r="R230" s="7"/>
-      <c r="S230" s="7"/>
-      <c r="T230" s="7"/>
-      <c r="U230" s="7"/>
     </row>
     <row r="231" spans="1:21" ht="15">
-      <c r="A231" s="7">
+      <c r="A231">
         <v>252</v>
       </c>
       <c r="B231" s="2">
@@ -10284,7 +10239,7 @@
         <v>60</v>
       </c>
       <c r="H231" s="3"/>
-      <c r="I231" s="7" t="s">
+      <c r="I231" t="s">
         <v>61</v>
       </c>
       <c r="J231" s="3" t="s">
@@ -10296,14 +10251,9 @@
       <c r="N231" s="3"/>
       <c r="O231" s="3"/>
       <c r="P231" s="3"/>
-      <c r="Q231" s="7"/>
-      <c r="R231" s="7"/>
-      <c r="S231" s="7"/>
-      <c r="T231" s="7"/>
-      <c r="U231" s="7"/>
     </row>
     <row r="232" spans="1:21" ht="15">
-      <c r="A232" s="7">
+      <c r="A232">
         <v>253</v>
       </c>
       <c r="B232" s="2">
@@ -10327,7 +10277,6 @@
       <c r="H232" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="I232" s="7"/>
       <c r="J232" s="3"/>
       <c r="K232" s="6"/>
       <c r="L232" s="3"/>
@@ -10335,14 +10284,9 @@
       <c r="N232" s="3"/>
       <c r="O232" s="3"/>
       <c r="P232" s="3"/>
-      <c r="Q232" s="7"/>
-      <c r="R232" s="7"/>
-      <c r="S232" s="7"/>
-      <c r="T232" s="7"/>
-      <c r="U232" s="7"/>
     </row>
     <row r="233" spans="1:21" ht="15">
-      <c r="A233" s="7">
+      <c r="A233">
         <v>254</v>
       </c>
       <c r="B233" s="2">
@@ -10364,7 +10308,6 @@
         <v>106</v>
       </c>
       <c r="H233" s="3"/>
-      <c r="I233" s="7"/>
       <c r="J233" s="3"/>
       <c r="K233" s="6"/>
       <c r="L233" s="3"/>
@@ -10372,18 +10315,15 @@
       <c r="N233" s="3"/>
       <c r="O233" s="3"/>
       <c r="P233" s="3"/>
-      <c r="Q233" s="7" t="s">
+      <c r="Q233" t="s">
         <v>61</v>
       </c>
-      <c r="R233" s="7" t="s">
+      <c r="R233" t="s">
         <v>481</v>
       </c>
-      <c r="S233" s="7"/>
-      <c r="T233" s="7"/>
-      <c r="U233" s="7"/>
     </row>
     <row r="234" spans="1:21" ht="15">
-      <c r="A234" s="7">
+      <c r="A234">
         <v>255</v>
       </c>
       <c r="B234" s="2">
@@ -10405,7 +10345,7 @@
         <v>60</v>
       </c>
       <c r="H234" s="3"/>
-      <c r="I234" s="7" t="s">
+      <c r="I234" t="s">
         <v>61</v>
       </c>
       <c r="J234" s="3" t="s">
@@ -10417,14 +10357,9 @@
       <c r="N234" s="3"/>
       <c r="O234" s="3"/>
       <c r="P234" s="3"/>
-      <c r="Q234" s="7"/>
-      <c r="R234" s="7"/>
-      <c r="S234" s="7"/>
-      <c r="T234" s="7"/>
-      <c r="U234" s="7"/>
     </row>
     <row r="235" spans="1:21" ht="15">
-      <c r="A235" s="7">
+      <c r="A235">
         <v>256</v>
       </c>
       <c r="B235" s="2">
@@ -10446,7 +10381,7 @@
         <v>60</v>
       </c>
       <c r="H235" s="3"/>
-      <c r="I235" s="7" t="s">
+      <c r="I235" t="s">
         <v>61</v>
       </c>
       <c r="J235" s="3" t="s">
@@ -10458,14 +10393,9 @@
       <c r="N235" s="3"/>
       <c r="O235" s="3"/>
       <c r="P235" s="3"/>
-      <c r="Q235" s="7"/>
-      <c r="R235" s="7"/>
-      <c r="S235" s="7"/>
-      <c r="T235" s="7"/>
-      <c r="U235" s="7"/>
     </row>
     <row r="236" spans="1:21" ht="15">
-      <c r="A236" s="7">
+      <c r="A236">
         <v>257</v>
       </c>
       <c r="B236" s="2">
@@ -10487,7 +10417,6 @@
         <v>286</v>
       </c>
       <c r="H236" s="3"/>
-      <c r="I236" s="7"/>
       <c r="J236" s="3"/>
       <c r="K236" s="6"/>
       <c r="L236" s="3"/>
@@ -10495,16 +10424,12 @@
       <c r="N236" s="3"/>
       <c r="O236" s="3"/>
       <c r="P236" s="3"/>
-      <c r="Q236" s="7"/>
-      <c r="R236" s="7"/>
-      <c r="S236" s="7"/>
-      <c r="T236" s="7" t="s">
+      <c r="T236" t="s">
         <v>486</v>
       </c>
-      <c r="U236" s="7"/>
     </row>
     <row r="237" spans="1:21" ht="15">
-      <c r="A237" s="7">
+      <c r="A237">
         <v>258</v>
       </c>
       <c r="B237" s="2">
@@ -10526,7 +10451,6 @@
         <v>288</v>
       </c>
       <c r="H237" s="3"/>
-      <c r="I237" s="7"/>
       <c r="J237" s="3"/>
       <c r="K237" s="6"/>
       <c r="L237" s="3"/>
@@ -10534,16 +10458,12 @@
       <c r="N237" s="3"/>
       <c r="O237" s="3"/>
       <c r="P237" s="3"/>
-      <c r="Q237" s="7"/>
-      <c r="R237" s="7"/>
-      <c r="S237" s="7"/>
-      <c r="T237" s="7"/>
-      <c r="U237" s="7" t="s">
+      <c r="U237" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="238" spans="1:21" ht="15">
-      <c r="A238" s="7">
+      <c r="A238">
         <v>259</v>
       </c>
       <c r="B238" s="2">
@@ -10565,7 +10485,6 @@
         <v>82</v>
       </c>
       <c r="H238" s="3"/>
-      <c r="I238" s="7"/>
       <c r="J238" s="3"/>
       <c r="K238" s="6"/>
       <c r="L238" s="3"/>
@@ -10575,14 +10494,9 @@
       <c r="N238" s="3"/>
       <c r="O238" s="3"/>
       <c r="P238" s="3"/>
-      <c r="Q238" s="7"/>
-      <c r="R238" s="7"/>
-      <c r="S238" s="7"/>
-      <c r="T238" s="7"/>
-      <c r="U238" s="7"/>
     </row>
     <row r="239" spans="1:21" ht="15">
-      <c r="A239" s="7">
+      <c r="A239">
         <v>260</v>
       </c>
       <c r="B239" s="2">
@@ -10606,7 +10520,6 @@
       <c r="H239" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="I239" s="7"/>
       <c r="J239" s="3"/>
       <c r="K239" s="6"/>
       <c r="L239" s="3"/>
@@ -10614,14 +10527,9 @@
       <c r="N239" s="3"/>
       <c r="O239" s="3"/>
       <c r="P239" s="3"/>
-      <c r="Q239" s="7"/>
-      <c r="R239" s="7"/>
-      <c r="S239" s="7"/>
-      <c r="T239" s="7"/>
-      <c r="U239" s="7"/>
     </row>
     <row r="240" spans="1:21" ht="15">
-      <c r="A240" s="7">
+      <c r="A240">
         <v>261</v>
       </c>
       <c r="B240" s="2">
@@ -10643,7 +10551,6 @@
         <v>38</v>
       </c>
       <c r="H240" s="3"/>
-      <c r="I240" s="7"/>
       <c r="J240" s="3"/>
       <c r="K240" s="6" t="s">
         <v>492</v>
@@ -10653,14 +10560,9 @@
       <c r="N240" s="3"/>
       <c r="O240" s="3"/>
       <c r="P240" s="3"/>
-      <c r="Q240" s="7"/>
-      <c r="R240" s="7"/>
-      <c r="S240" s="7"/>
-      <c r="T240" s="7"/>
-      <c r="U240" s="7"/>
-    </row>
-    <row r="241" spans="1:21" ht="15">
-      <c r="A241" s="7">
+    </row>
+    <row r="241" spans="1:20" ht="15">
+      <c r="A241">
         <v>262</v>
       </c>
       <c r="B241" s="2">
@@ -10682,7 +10584,6 @@
         <v>41</v>
       </c>
       <c r="H241" s="3"/>
-      <c r="I241" s="7"/>
       <c r="J241" s="3"/>
       <c r="K241" s="6"/>
       <c r="L241" s="3"/>
@@ -10692,14 +10593,9 @@
       <c r="P241" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="Q241" s="7"/>
-      <c r="R241" s="7"/>
-      <c r="S241" s="7"/>
-      <c r="T241" s="7"/>
-      <c r="U241" s="7"/>
-    </row>
-    <row r="242" spans="1:21" ht="15">
-      <c r="A242" s="7">
+    </row>
+    <row r="242" spans="1:20" ht="15">
+      <c r="A242">
         <v>263</v>
       </c>
       <c r="B242" s="2">
@@ -10721,7 +10617,7 @@
         <v>60</v>
       </c>
       <c r="H242" s="3"/>
-      <c r="I242" s="7" t="s">
+      <c r="I242" t="s">
         <v>61</v>
       </c>
       <c r="J242" s="3" t="s">
@@ -10733,14 +10629,9 @@
       <c r="N242" s="3"/>
       <c r="O242" s="3"/>
       <c r="P242" s="3"/>
-      <c r="Q242" s="7"/>
-      <c r="R242" s="7"/>
-      <c r="S242" s="7"/>
-      <c r="T242" s="7"/>
-      <c r="U242" s="7"/>
-    </row>
-    <row r="243" spans="1:21" ht="15">
-      <c r="A243" s="7">
+    </row>
+    <row r="243" spans="1:20" ht="15">
+      <c r="A243">
         <v>264</v>
       </c>
       <c r="B243" s="2">
@@ -10762,7 +10653,6 @@
         <v>33</v>
       </c>
       <c r="H243" s="3"/>
-      <c r="I243" s="7"/>
       <c r="J243" s="3"/>
       <c r="K243" s="6"/>
       <c r="L243" s="3"/>
@@ -10772,14 +10662,9 @@
         <v>495</v>
       </c>
       <c r="P243" s="3"/>
-      <c r="Q243" s="7"/>
-      <c r="R243" s="7"/>
-      <c r="S243" s="7"/>
-      <c r="T243" s="7"/>
-      <c r="U243" s="7"/>
-    </row>
-    <row r="244" spans="1:21" ht="15">
-      <c r="A244" s="7">
+    </row>
+    <row r="244" spans="1:20" ht="15">
+      <c r="A244">
         <v>265</v>
       </c>
       <c r="B244" s="2">
@@ -10801,7 +10686,6 @@
         <v>41</v>
       </c>
       <c r="H244" s="3"/>
-      <c r="I244" s="7"/>
       <c r="J244" s="3"/>
       <c r="K244" s="6"/>
       <c r="L244" s="3"/>
@@ -10811,14 +10695,9 @@
       <c r="P244" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="Q244" s="7"/>
-      <c r="R244" s="7"/>
-      <c r="S244" s="7"/>
-      <c r="T244" s="7"/>
-      <c r="U244" s="7"/>
-    </row>
-    <row r="245" spans="1:21" ht="15">
-      <c r="A245" s="7">
+    </row>
+    <row r="245" spans="1:20" ht="15">
+      <c r="A245">
         <v>266</v>
       </c>
       <c r="B245" s="2">
@@ -10840,7 +10719,6 @@
         <v>286</v>
       </c>
       <c r="H245" s="3"/>
-      <c r="I245" s="7"/>
       <c r="J245" s="3"/>
       <c r="K245" s="6"/>
       <c r="L245" s="3"/>
@@ -10848,16 +10726,12 @@
       <c r="N245" s="3"/>
       <c r="O245" s="3"/>
       <c r="P245" s="3"/>
-      <c r="Q245" s="7"/>
-      <c r="R245" s="7"/>
-      <c r="S245" s="7"/>
-      <c r="T245" s="7" t="s">
+      <c r="T245" t="s">
         <v>497</v>
       </c>
-      <c r="U245" s="7"/>
-    </row>
-    <row r="246" spans="1:21" ht="15">
-      <c r="A246" s="7">
+    </row>
+    <row r="246" spans="1:20" ht="15">
+      <c r="A246">
         <v>267</v>
       </c>
       <c r="B246" s="2">
@@ -10879,7 +10753,6 @@
         <v>82</v>
       </c>
       <c r="H246" s="3"/>
-      <c r="I246" s="7"/>
       <c r="J246" s="3"/>
       <c r="K246" s="6"/>
       <c r="L246" s="3"/>
@@ -10889,14 +10762,9 @@
       <c r="N246" s="3"/>
       <c r="O246" s="3"/>
       <c r="P246" s="3"/>
-      <c r="Q246" s="7"/>
-      <c r="R246" s="7"/>
-      <c r="S246" s="7"/>
-      <c r="T246" s="7"/>
-      <c r="U246" s="7"/>
-    </row>
-    <row r="247" spans="1:21" ht="15">
-      <c r="A247" s="7">
+    </row>
+    <row r="247" spans="1:20" ht="15">
+      <c r="A247">
         <v>268</v>
       </c>
       <c r="B247" s="2">
@@ -10920,7 +10788,6 @@
       <c r="H247" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="I247" s="7"/>
       <c r="J247" s="3"/>
       <c r="K247" s="6"/>
       <c r="L247" s="3"/>
@@ -10928,14 +10795,9 @@
       <c r="N247" s="3"/>
       <c r="O247" s="3"/>
       <c r="P247" s="3"/>
-      <c r="Q247" s="7"/>
-      <c r="R247" s="7"/>
-      <c r="S247" s="7"/>
-      <c r="T247" s="7"/>
-      <c r="U247" s="7"/>
-    </row>
-    <row r="248" spans="1:21" ht="15">
-      <c r="A248" s="7">
+    </row>
+    <row r="248" spans="1:20" ht="15">
+      <c r="A248">
         <v>269</v>
       </c>
       <c r="B248" s="2">
@@ -10957,7 +10819,7 @@
         <v>60</v>
       </c>
       <c r="H248" s="3"/>
-      <c r="I248" s="7" t="s">
+      <c r="I248" t="s">
         <v>61</v>
       </c>
       <c r="J248" s="3" t="s">
@@ -10969,14 +10831,9 @@
       <c r="N248" s="3"/>
       <c r="O248" s="3"/>
       <c r="P248" s="3"/>
-      <c r="Q248" s="7"/>
-      <c r="R248" s="7"/>
-      <c r="S248" s="7"/>
-      <c r="T248" s="7"/>
-      <c r="U248" s="7"/>
-    </row>
-    <row r="249" spans="1:21" ht="15">
-      <c r="A249" s="7">
+    </row>
+    <row r="249" spans="1:20" ht="15">
+      <c r="A249">
         <v>270</v>
       </c>
       <c r="B249" s="2">
@@ -10998,7 +10855,6 @@
         <v>33</v>
       </c>
       <c r="H249" s="3"/>
-      <c r="I249" s="7"/>
       <c r="J249" s="3"/>
       <c r="K249" s="6"/>
       <c r="L249" s="3"/>
@@ -11008,14 +10864,9 @@
         <v>503</v>
       </c>
       <c r="P249" s="3"/>
-      <c r="Q249" s="7"/>
-      <c r="R249" s="7"/>
-      <c r="S249" s="7"/>
-      <c r="T249" s="7"/>
-      <c r="U249" s="7"/>
-    </row>
-    <row r="250" spans="1:21" ht="15">
-      <c r="A250" s="7">
+    </row>
+    <row r="250" spans="1:20" ht="15">
+      <c r="A250">
         <v>271</v>
       </c>
       <c r="B250" s="2">
@@ -11037,7 +10888,6 @@
         <v>106</v>
       </c>
       <c r="H250" s="3"/>
-      <c r="I250" s="7"/>
       <c r="J250" s="3"/>
       <c r="K250" s="6"/>
       <c r="L250" s="3"/>
@@ -11045,16 +10895,12 @@
       <c r="N250" s="3"/>
       <c r="O250" s="3"/>
       <c r="P250" s="3"/>
-      <c r="Q250" s="7" t="s">
+      <c r="Q250" t="s">
         <v>107</v>
       </c>
-      <c r="R250" s="7"/>
-      <c r="S250" s="7"/>
-      <c r="T250" s="7"/>
-      <c r="U250" s="7"/>
-    </row>
-    <row r="251" spans="1:21" ht="15">
-      <c r="A251" s="7">
+    </row>
+    <row r="251" spans="1:20" ht="15">
+      <c r="A251">
         <v>272</v>
       </c>
       <c r="B251" s="2">
@@ -11076,7 +10922,6 @@
         <v>41</v>
       </c>
       <c r="H251" s="3"/>
-      <c r="I251" s="7"/>
       <c r="J251" s="3"/>
       <c r="K251" s="6"/>
       <c r="L251" s="3"/>
@@ -11086,14 +10931,9 @@
       <c r="P251" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="Q251" s="7"/>
-      <c r="R251" s="7"/>
-      <c r="S251" s="7"/>
-      <c r="T251" s="7"/>
-      <c r="U251" s="7"/>
-    </row>
-    <row r="252" spans="1:21" ht="15">
-      <c r="A252" s="7">
+    </row>
+    <row r="252" spans="1:20" ht="15">
+      <c r="A252">
         <v>273</v>
       </c>
       <c r="B252" s="2">
@@ -11117,7 +10957,6 @@
       <c r="H252" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="I252" s="7"/>
       <c r="J252" s="3"/>
       <c r="K252" s="6"/>
       <c r="L252" s="3"/>
@@ -11125,14 +10964,9 @@
       <c r="N252" s="3"/>
       <c r="O252" s="3"/>
       <c r="P252" s="3"/>
-      <c r="Q252" s="7"/>
-      <c r="R252" s="7"/>
-      <c r="S252" s="7"/>
-      <c r="T252" s="7"/>
-      <c r="U252" s="7"/>
-    </row>
-    <row r="253" spans="1:21" ht="15">
-      <c r="A253" s="7">
+    </row>
+    <row r="253" spans="1:20" ht="15">
+      <c r="A253">
         <v>274</v>
       </c>
       <c r="B253" s="2">
@@ -11156,7 +10990,6 @@
       <c r="H253" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="I253" s="7"/>
       <c r="J253" s="3"/>
       <c r="K253" s="6"/>
       <c r="L253" s="3"/>
@@ -11164,14 +10997,9 @@
       <c r="N253" s="3"/>
       <c r="O253" s="3"/>
       <c r="P253" s="3"/>
-      <c r="Q253" s="7"/>
-      <c r="R253" s="7"/>
-      <c r="S253" s="7"/>
-      <c r="T253" s="7"/>
-      <c r="U253" s="7"/>
-    </row>
-    <row r="254" spans="1:21" ht="15">
-      <c r="A254" s="7">
+    </row>
+    <row r="254" spans="1:20" ht="15">
+      <c r="A254">
         <v>275</v>
       </c>
       <c r="B254" s="2">
@@ -11193,7 +11021,7 @@
         <v>60</v>
       </c>
       <c r="H254" s="3"/>
-      <c r="I254" s="7" t="s">
+      <c r="I254" t="s">
         <v>398</v>
       </c>
       <c r="J254" s="3"/>
@@ -11203,14 +11031,9 @@
       <c r="N254" s="3"/>
       <c r="O254" s="3"/>
       <c r="P254" s="3"/>
-      <c r="Q254" s="7"/>
-      <c r="R254" s="7"/>
-      <c r="S254" s="7"/>
-      <c r="T254" s="7"/>
-      <c r="U254" s="7"/>
-    </row>
-    <row r="255" spans="1:21" ht="15">
-      <c r="A255" s="7">
+    </row>
+    <row r="255" spans="1:20" ht="15">
+      <c r="A255">
         <v>276</v>
       </c>
       <c r="B255" s="2">
@@ -11232,7 +11055,7 @@
         <v>60</v>
       </c>
       <c r="H255" s="3"/>
-      <c r="I255" s="7" t="s">
+      <c r="I255" t="s">
         <v>61</v>
       </c>
       <c r="J255" s="3" t="s">
@@ -11244,14 +11067,9 @@
       <c r="N255" s="3"/>
       <c r="O255" s="3"/>
       <c r="P255" s="3"/>
-      <c r="Q255" s="7"/>
-      <c r="R255" s="7"/>
-      <c r="S255" s="7"/>
-      <c r="T255" s="7"/>
-      <c r="U255" s="7"/>
-    </row>
-    <row r="256" spans="1:21" ht="15">
-      <c r="A256" s="7">
+    </row>
+    <row r="256" spans="1:20" ht="15">
+      <c r="A256">
         <v>277</v>
       </c>
       <c r="B256" s="2">
@@ -11275,7 +11093,6 @@
       <c r="H256" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="I256" s="7"/>
       <c r="J256" s="3"/>
       <c r="K256" s="6"/>
       <c r="L256" s="3"/>
@@ -11283,14 +11100,9 @@
       <c r="N256" s="3"/>
       <c r="O256" s="3"/>
       <c r="P256" s="3"/>
-      <c r="Q256" s="7"/>
-      <c r="R256" s="7"/>
-      <c r="S256" s="7"/>
-      <c r="T256" s="7"/>
-      <c r="U256" s="7"/>
     </row>
     <row r="257" spans="1:21" ht="15">
-      <c r="A257" s="7">
+      <c r="A257">
         <v>278</v>
       </c>
       <c r="B257" s="2">
@@ -11312,7 +11124,6 @@
         <v>38</v>
       </c>
       <c r="H257" s="3"/>
-      <c r="I257" s="7"/>
       <c r="J257" s="3"/>
       <c r="K257" s="6" t="s">
         <v>509</v>
@@ -11322,14 +11133,9 @@
       <c r="N257" s="3"/>
       <c r="O257" s="3"/>
       <c r="P257" s="3"/>
-      <c r="Q257" s="7"/>
-      <c r="R257" s="7"/>
-      <c r="S257" s="7"/>
-      <c r="T257" s="7"/>
-      <c r="U257" s="7"/>
     </row>
     <row r="258" spans="1:21" ht="15">
-      <c r="A258" s="7">
+      <c r="A258">
         <v>279</v>
       </c>
       <c r="B258" s="2">
@@ -11351,7 +11157,6 @@
         <v>106</v>
       </c>
       <c r="H258" s="3"/>
-      <c r="I258" s="7"/>
       <c r="J258" s="3"/>
       <c r="K258" s="6"/>
       <c r="L258" s="3"/>
@@ -11359,18 +11164,15 @@
       <c r="N258" s="3"/>
       <c r="O258" s="3"/>
       <c r="P258" s="3"/>
-      <c r="Q258" s="7" t="s">
+      <c r="Q258" t="s">
         <v>61</v>
       </c>
-      <c r="R258" s="7" t="s">
+      <c r="R258" t="s">
         <v>510</v>
       </c>
-      <c r="S258" s="7"/>
-      <c r="T258" s="7"/>
-      <c r="U258" s="7"/>
     </row>
     <row r="259" spans="1:21" ht="15">
-      <c r="A259" s="7">
+      <c r="A259">
         <v>280</v>
       </c>
       <c r="B259" s="2">
@@ -11392,7 +11194,6 @@
         <v>82</v>
       </c>
       <c r="H259" s="3"/>
-      <c r="I259" s="7"/>
       <c r="J259" s="3"/>
       <c r="K259" s="6"/>
       <c r="L259" s="3"/>
@@ -11402,14 +11203,9 @@
       <c r="N259" s="3"/>
       <c r="O259" s="3"/>
       <c r="P259" s="3"/>
-      <c r="Q259" s="7"/>
-      <c r="R259" s="7"/>
-      <c r="S259" s="7"/>
-      <c r="T259" s="7"/>
-      <c r="U259" s="7"/>
     </row>
     <row r="260" spans="1:21" ht="15">
-      <c r="A260" s="7">
+      <c r="A260">
         <v>281</v>
       </c>
       <c r="B260" s="2">
@@ -11431,7 +11227,7 @@
         <v>60</v>
       </c>
       <c r="H260" s="3"/>
-      <c r="I260" s="7" t="s">
+      <c r="I260" t="s">
         <v>61</v>
       </c>
       <c r="J260" s="3" t="s">
@@ -11443,14 +11239,9 @@
       <c r="N260" s="3"/>
       <c r="O260" s="3"/>
       <c r="P260" s="3"/>
-      <c r="Q260" s="7"/>
-      <c r="R260" s="7"/>
-      <c r="S260" s="7"/>
-      <c r="T260" s="7"/>
-      <c r="U260" s="7"/>
     </row>
     <row r="261" spans="1:21" ht="15">
-      <c r="A261" s="7">
+      <c r="A261">
         <v>282</v>
       </c>
       <c r="B261" s="2">
@@ -11472,7 +11263,6 @@
         <v>38</v>
       </c>
       <c r="H261" s="3"/>
-      <c r="I261" s="7"/>
       <c r="J261" s="3"/>
       <c r="K261" s="6" t="s">
         <v>513</v>
@@ -11482,14 +11272,9 @@
       <c r="N261" s="3"/>
       <c r="O261" s="3"/>
       <c r="P261" s="3"/>
-      <c r="Q261" s="7"/>
-      <c r="R261" s="7"/>
-      <c r="S261" s="7"/>
-      <c r="T261" s="7"/>
-      <c r="U261" s="7"/>
     </row>
     <row r="262" spans="1:21" ht="15">
-      <c r="A262" s="7">
+      <c r="A262">
         <v>283</v>
       </c>
       <c r="B262" s="2">
@@ -11511,7 +11296,7 @@
         <v>60</v>
       </c>
       <c r="H262" s="3"/>
-      <c r="I262" s="7" t="s">
+      <c r="I262" t="s">
         <v>61</v>
       </c>
       <c r="J262" s="3" t="s">
@@ -11523,14 +11308,9 @@
       <c r="N262" s="3"/>
       <c r="O262" s="3"/>
       <c r="P262" s="3"/>
-      <c r="Q262" s="7"/>
-      <c r="R262" s="7"/>
-      <c r="S262" s="7"/>
-      <c r="T262" s="7"/>
-      <c r="U262" s="7"/>
     </row>
     <row r="263" spans="1:21" ht="15">
-      <c r="A263" s="7">
+      <c r="A263">
         <v>284</v>
       </c>
       <c r="B263" s="2">
@@ -11552,7 +11332,6 @@
         <v>82</v>
       </c>
       <c r="H263" s="3"/>
-      <c r="I263" s="7"/>
       <c r="J263" s="3"/>
       <c r="K263" s="6"/>
       <c r="L263" s="3"/>
@@ -11562,14 +11341,9 @@
       <c r="N263" s="3"/>
       <c r="O263" s="3"/>
       <c r="P263" s="3"/>
-      <c r="Q263" s="7"/>
-      <c r="R263" s="7"/>
-      <c r="S263" s="7"/>
-      <c r="T263" s="7"/>
-      <c r="U263" s="7"/>
     </row>
     <row r="264" spans="1:21" ht="15">
-      <c r="A264" s="7">
+      <c r="A264">
         <v>285</v>
       </c>
       <c r="B264" s="2">
@@ -11591,7 +11365,7 @@
         <v>60</v>
       </c>
       <c r="H264" s="3"/>
-      <c r="I264" s="7" t="s">
+      <c r="I264" t="s">
         <v>61</v>
       </c>
       <c r="J264" s="3" t="s">
@@ -11603,14 +11377,9 @@
       <c r="N264" s="3"/>
       <c r="O264" s="3"/>
       <c r="P264" s="3"/>
-      <c r="Q264" s="7"/>
-      <c r="R264" s="7"/>
-      <c r="S264" s="7"/>
-      <c r="T264" s="7"/>
-      <c r="U264" s="7"/>
     </row>
     <row r="265" spans="1:21" ht="15">
-      <c r="A265" s="7">
+      <c r="A265">
         <v>286</v>
       </c>
       <c r="B265" s="2">
@@ -11632,7 +11401,6 @@
         <v>38</v>
       </c>
       <c r="H265" s="3"/>
-      <c r="I265" s="7"/>
       <c r="J265" s="3"/>
       <c r="K265" s="6" t="s">
         <v>517</v>
@@ -11642,14 +11410,9 @@
       <c r="N265" s="3"/>
       <c r="O265" s="3"/>
       <c r="P265" s="3"/>
-      <c r="Q265" s="7"/>
-      <c r="R265" s="7"/>
-      <c r="S265" s="7"/>
-      <c r="T265" s="7"/>
-      <c r="U265" s="7"/>
     </row>
     <row r="266" spans="1:21" ht="15">
-      <c r="A266" s="7">
+      <c r="A266">
         <v>287</v>
       </c>
       <c r="B266" s="2">
@@ -11673,7 +11436,6 @@
       <c r="H266" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="I266" s="7"/>
       <c r="J266" s="3"/>
       <c r="K266" s="6"/>
       <c r="L266" s="3"/>
@@ -11681,14 +11443,9 @@
       <c r="N266" s="3"/>
       <c r="O266" s="3"/>
       <c r="P266" s="3"/>
-      <c r="Q266" s="7"/>
-      <c r="R266" s="7"/>
-      <c r="S266" s="7"/>
-      <c r="T266" s="7"/>
-      <c r="U266" s="7"/>
     </row>
     <row r="267" spans="1:21" ht="15">
-      <c r="A267" s="7">
+      <c r="A267">
         <v>288</v>
       </c>
       <c r="B267" s="2">
@@ -11710,7 +11467,6 @@
         <v>33</v>
       </c>
       <c r="H267" s="3"/>
-      <c r="I267" s="7"/>
       <c r="J267" s="3"/>
       <c r="K267" s="6"/>
       <c r="L267" s="3"/>
@@ -11720,14 +11476,9 @@
         <v>519</v>
       </c>
       <c r="P267" s="3"/>
-      <c r="Q267" s="7"/>
-      <c r="R267" s="7"/>
-      <c r="S267" s="7"/>
-      <c r="T267" s="7"/>
-      <c r="U267" s="7"/>
     </row>
     <row r="268" spans="1:21" ht="15">
-      <c r="A268" s="7">
+      <c r="A268">
         <v>289</v>
       </c>
       <c r="B268" s="2">
@@ -11749,7 +11500,6 @@
         <v>106</v>
       </c>
       <c r="H268" s="3"/>
-      <c r="I268" s="7"/>
       <c r="J268" s="3"/>
       <c r="K268" s="6"/>
       <c r="L268" s="3"/>
@@ -11757,18 +11507,15 @@
       <c r="N268" s="3"/>
       <c r="O268" s="3"/>
       <c r="P268" s="3"/>
-      <c r="Q268" s="7" t="s">
+      <c r="Q268" t="s">
         <v>61</v>
       </c>
-      <c r="R268" s="7" t="s">
+      <c r="R268" t="s">
         <v>520</v>
       </c>
-      <c r="S268" s="7"/>
-      <c r="T268" s="7"/>
-      <c r="U268" s="7"/>
     </row>
     <row r="269" spans="1:21" ht="15">
-      <c r="A269" s="7">
+      <c r="A269">
         <v>290</v>
       </c>
       <c r="B269" s="2">
@@ -11790,7 +11537,7 @@
         <v>60</v>
       </c>
       <c r="H269" s="3"/>
-      <c r="I269" s="7" t="s">
+      <c r="I269" t="s">
         <v>61</v>
       </c>
       <c r="J269" s="3" t="s">
@@ -11802,14 +11549,9 @@
       <c r="N269" s="3"/>
       <c r="O269" s="3"/>
       <c r="P269" s="3"/>
-      <c r="Q269" s="7"/>
-      <c r="R269" s="7"/>
-      <c r="S269" s="7"/>
-      <c r="T269" s="7"/>
-      <c r="U269" s="7"/>
     </row>
     <row r="270" spans="1:21" ht="15">
-      <c r="A270" s="7">
+      <c r="A270">
         <v>291</v>
       </c>
       <c r="B270" s="2">
@@ -11831,7 +11573,6 @@
         <v>288</v>
       </c>
       <c r="H270" s="3"/>
-      <c r="I270" s="7"/>
       <c r="J270" s="3"/>
       <c r="K270" s="6"/>
       <c r="L270" s="3"/>
@@ -11839,16 +11580,12 @@
       <c r="N270" s="3"/>
       <c r="O270" s="3"/>
       <c r="P270" s="3"/>
-      <c r="Q270" s="7"/>
-      <c r="R270" s="7"/>
-      <c r="S270" s="7"/>
-      <c r="T270" s="7"/>
-      <c r="U270" s="7" t="s">
+      <c r="U270" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="271" spans="1:21" ht="15">
-      <c r="A271" s="7">
+      <c r="A271">
         <v>292</v>
       </c>
       <c r="B271" s="2">
@@ -11870,7 +11607,6 @@
         <v>33</v>
       </c>
       <c r="H271" s="3"/>
-      <c r="I271" s="7"/>
       <c r="J271" s="3"/>
       <c r="K271" s="6"/>
       <c r="L271" s="3"/>
@@ -11880,14 +11616,9 @@
         <v>523</v>
       </c>
       <c r="P271" s="3"/>
-      <c r="Q271" s="7"/>
-      <c r="R271" s="7"/>
-      <c r="S271" s="7"/>
-      <c r="T271" s="7"/>
-      <c r="U271" s="7"/>
     </row>
     <row r="272" spans="1:21" ht="15">
-      <c r="A272" s="7">
+      <c r="A272">
         <v>293</v>
       </c>
       <c r="B272" s="2">
@@ -11909,7 +11640,6 @@
         <v>286</v>
       </c>
       <c r="H272" s="3"/>
-      <c r="I272" s="7"/>
       <c r="J272" s="3"/>
       <c r="K272" s="6"/>
       <c r="L272" s="3"/>
@@ -11917,16 +11647,12 @@
       <c r="N272" s="3"/>
       <c r="O272" s="3"/>
       <c r="P272" s="3"/>
-      <c r="Q272" s="7"/>
-      <c r="R272" s="7"/>
-      <c r="S272" s="7"/>
-      <c r="T272" s="7" t="s">
+      <c r="T272" t="s">
         <v>524</v>
       </c>
-      <c r="U272" s="7"/>
     </row>
     <row r="273" spans="1:21" ht="15">
-      <c r="A273" s="7">
+      <c r="A273">
         <v>294</v>
       </c>
       <c r="B273" s="2">
@@ -11948,7 +11674,6 @@
         <v>106</v>
       </c>
       <c r="H273" s="3"/>
-      <c r="I273" s="7"/>
       <c r="J273" s="3"/>
       <c r="K273" s="6"/>
       <c r="L273" s="3"/>
@@ -11956,18 +11681,15 @@
       <c r="N273" s="3"/>
       <c r="O273" s="3"/>
       <c r="P273" s="3"/>
-      <c r="Q273" s="7" t="s">
+      <c r="Q273" t="s">
         <v>61</v>
       </c>
-      <c r="R273" s="7" t="s">
+      <c r="R273" t="s">
         <v>525</v>
       </c>
-      <c r="S273" s="7"/>
-      <c r="T273" s="7"/>
-      <c r="U273" s="7"/>
     </row>
     <row r="274" spans="1:21" ht="15">
-      <c r="A274" s="7">
+      <c r="A274">
         <v>295</v>
       </c>
       <c r="B274" s="2">
@@ -11989,7 +11711,6 @@
         <v>288</v>
       </c>
       <c r="H274" s="3"/>
-      <c r="I274" s="7"/>
       <c r="J274" s="3"/>
       <c r="K274" s="6"/>
       <c r="L274" s="3"/>
@@ -11997,16 +11718,12 @@
       <c r="N274" s="3"/>
       <c r="O274" s="3"/>
       <c r="P274" s="3"/>
-      <c r="Q274" s="7"/>
-      <c r="R274" s="7"/>
-      <c r="S274" s="7"/>
-      <c r="T274" s="7"/>
-      <c r="U274" s="7" t="s">
+      <c r="U274" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="275" spans="1:21" ht="15">
-      <c r="A275" s="7">
+      <c r="A275">
         <v>296</v>
       </c>
       <c r="B275" s="2">
@@ -12028,7 +11745,6 @@
         <v>106</v>
       </c>
       <c r="H275" s="3"/>
-      <c r="I275" s="7"/>
       <c r="J275" s="3"/>
       <c r="K275" s="6"/>
       <c r="L275" s="3"/>
@@ -12036,18 +11752,15 @@
       <c r="N275" s="3"/>
       <c r="O275" s="3"/>
       <c r="P275" s="3"/>
-      <c r="Q275" s="7" t="s">
+      <c r="Q275" t="s">
         <v>61</v>
       </c>
-      <c r="R275" s="7" t="s">
+      <c r="R275" t="s">
         <v>527</v>
       </c>
-      <c r="S275" s="7"/>
-      <c r="T275" s="7"/>
-      <c r="U275" s="7"/>
     </row>
     <row r="276" spans="1:21" ht="15">
-      <c r="A276" s="7">
+      <c r="A276">
         <v>297</v>
       </c>
       <c r="B276" s="2">
@@ -12069,7 +11782,6 @@
         <v>38</v>
       </c>
       <c r="H276" s="3"/>
-      <c r="I276" s="7"/>
       <c r="J276" s="3"/>
       <c r="K276" s="6" t="s">
         <v>528</v>
@@ -12079,14 +11791,9 @@
       <c r="N276" s="3"/>
       <c r="O276" s="3"/>
       <c r="P276" s="3"/>
-      <c r="Q276" s="7"/>
-      <c r="R276" s="7"/>
-      <c r="S276" s="7"/>
-      <c r="T276" s="7"/>
-      <c r="U276" s="7"/>
     </row>
     <row r="277" spans="1:21" ht="15">
-      <c r="A277" s="7">
+      <c r="A277">
         <v>298</v>
       </c>
       <c r="B277" s="2">
@@ -12110,7 +11817,6 @@
       <c r="H277" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="I277" s="7"/>
       <c r="J277" s="3"/>
       <c r="K277" s="6"/>
       <c r="L277" s="3"/>
@@ -12118,14 +11824,9 @@
       <c r="N277" s="3"/>
       <c r="O277" s="3"/>
       <c r="P277" s="3"/>
-      <c r="Q277" s="7"/>
-      <c r="R277" s="7"/>
-      <c r="S277" s="7"/>
-      <c r="T277" s="7"/>
-      <c r="U277" s="7"/>
     </row>
     <row r="278" spans="1:21" ht="15">
-      <c r="A278" s="7">
+      <c r="A278">
         <v>299</v>
       </c>
       <c r="B278" s="2">
@@ -12147,7 +11848,6 @@
         <v>33</v>
       </c>
       <c r="H278" s="3"/>
-      <c r="I278" s="7"/>
       <c r="J278" s="3"/>
       <c r="K278" s="6"/>
       <c r="L278" s="3"/>
@@ -12157,14 +11857,9 @@
         <v>530</v>
       </c>
       <c r="P278" s="3"/>
-      <c r="Q278" s="7"/>
-      <c r="R278" s="7"/>
-      <c r="S278" s="7"/>
-      <c r="T278" s="7"/>
-      <c r="U278" s="7"/>
     </row>
     <row r="279" spans="1:21" ht="15">
-      <c r="A279" s="7">
+      <c r="A279">
         <v>300</v>
       </c>
       <c r="B279" s="2">
@@ -12186,7 +11881,6 @@
         <v>38</v>
       </c>
       <c r="H279" s="3"/>
-      <c r="I279" s="7"/>
       <c r="J279" s="3"/>
       <c r="K279" s="6" t="s">
         <v>531</v>
@@ -12196,14 +11890,9 @@
       <c r="N279" s="3"/>
       <c r="O279" s="3"/>
       <c r="P279" s="3"/>
-      <c r="Q279" s="7"/>
-      <c r="R279" s="7"/>
-      <c r="S279" s="7"/>
-      <c r="T279" s="7"/>
-      <c r="U279" s="7"/>
     </row>
     <row r="280" spans="1:21" ht="15">
-      <c r="A280" s="7">
+      <c r="A280">
         <v>301</v>
       </c>
       <c r="B280" s="2">
@@ -12225,7 +11914,6 @@
         <v>217</v>
       </c>
       <c r="H280" s="3"/>
-      <c r="I280" s="7"/>
       <c r="J280" s="3"/>
       <c r="K280" s="6"/>
       <c r="L280" s="3"/>
@@ -12235,14 +11923,9 @@
       </c>
       <c r="O280" s="3"/>
       <c r="P280" s="3"/>
-      <c r="Q280" s="7"/>
-      <c r="R280" s="7"/>
-      <c r="S280" s="7"/>
-      <c r="T280" s="7"/>
-      <c r="U280" s="7"/>
     </row>
     <row r="281" spans="1:21" ht="15">
-      <c r="A281" s="7">
+      <c r="A281">
         <v>302</v>
       </c>
       <c r="B281" s="2">
@@ -12266,7 +11949,6 @@
       <c r="H281" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="I281" s="7"/>
       <c r="J281" s="3"/>
       <c r="K281" s="6"/>
       <c r="L281" s="3"/>
@@ -12274,14 +11956,9 @@
       <c r="N281" s="3"/>
       <c r="O281" s="3"/>
       <c r="P281" s="3"/>
-      <c r="Q281" s="7"/>
-      <c r="R281" s="7"/>
-      <c r="S281" s="7"/>
-      <c r="T281" s="7"/>
-      <c r="U281" s="7"/>
     </row>
     <row r="282" spans="1:21" ht="15">
-      <c r="A282" s="7">
+      <c r="A282">
         <v>303</v>
       </c>
       <c r="B282" s="2">
@@ -12303,7 +11980,7 @@
         <v>60</v>
       </c>
       <c r="H282" s="3"/>
-      <c r="I282" s="7" t="s">
+      <c r="I282" t="s">
         <v>61</v>
       </c>
       <c r="J282" s="3" t="s">
@@ -12315,14 +11992,9 @@
       <c r="N282" s="3"/>
       <c r="O282" s="3"/>
       <c r="P282" s="3"/>
-      <c r="Q282" s="7"/>
-      <c r="R282" s="7"/>
-      <c r="S282" s="7"/>
-      <c r="T282" s="7"/>
-      <c r="U282" s="7"/>
     </row>
     <row r="283" spans="1:21" ht="15">
-      <c r="A283" s="7">
+      <c r="A283">
         <v>304</v>
       </c>
       <c r="B283" s="2">
@@ -12344,7 +12016,6 @@
         <v>106</v>
       </c>
       <c r="H283" s="3"/>
-      <c r="I283" s="7"/>
       <c r="J283" s="3"/>
       <c r="K283" s="6"/>
       <c r="L283" s="3"/>
@@ -12352,16 +12023,12 @@
       <c r="N283" s="3"/>
       <c r="O283" s="3"/>
       <c r="P283" s="3"/>
-      <c r="Q283" s="7" t="s">
+      <c r="Q283" t="s">
         <v>107</v>
       </c>
-      <c r="R283" s="7"/>
-      <c r="S283" s="7"/>
-      <c r="T283" s="7"/>
-      <c r="U283" s="7"/>
     </row>
     <row r="284" spans="1:21" ht="15">
-      <c r="A284" s="7">
+      <c r="A284">
         <v>306</v>
       </c>
       <c r="B284" s="2">
@@ -12383,7 +12050,7 @@
         <v>60</v>
       </c>
       <c r="H284" s="3"/>
-      <c r="I284" s="7" t="s">
+      <c r="I284" t="s">
         <v>61</v>
       </c>
       <c r="J284" s="3" t="s">
@@ -12395,13 +12062,361 @@
       <c r="N284" s="3"/>
       <c r="O284" s="3"/>
       <c r="P284" s="3"/>
-      <c r="Q284" s="7"/>
-      <c r="R284" s="7"/>
-      <c r="S284" s="7"/>
-      <c r="T284" s="7"/>
-      <c r="U284" s="7"/>
-    </row>
-    <row r="285" spans="1:21" ht="15"/>
+    </row>
+    <row r="285" spans="1:21" ht="15">
+      <c r="A285" s="7">
+        <v>307</v>
+      </c>
+      <c r="B285" s="2">
+        <v>46268.354282407403</v>
+      </c>
+      <c r="C285" s="2">
+        <v>46268.354988425897</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F285" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H285" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="I285" s="7"/>
+      <c r="J285" s="3"/>
+      <c r="K285" s="6"/>
+      <c r="L285" s="3"/>
+      <c r="M285" s="3"/>
+      <c r="N285" s="3"/>
+      <c r="O285" s="3"/>
+      <c r="P285" s="3"/>
+      <c r="Q285" s="7"/>
+      <c r="R285" s="7"/>
+      <c r="S285" s="7"/>
+      <c r="T285" s="7"/>
+      <c r="U285" s="7"/>
+    </row>
+    <row r="286" spans="1:21" ht="15">
+      <c r="A286" s="7">
+        <v>308</v>
+      </c>
+      <c r="B286" s="2">
+        <v>46268.548437500001</v>
+      </c>
+      <c r="C286" s="2">
+        <v>46268.549155092602</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E286" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F286" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H286" s="3"/>
+      <c r="I286" s="7"/>
+      <c r="J286" s="3"/>
+      <c r="K286" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="L286" s="3"/>
+      <c r="M286" s="3"/>
+      <c r="N286" s="3"/>
+      <c r="O286" s="3"/>
+      <c r="P286" s="3"/>
+      <c r="Q286" s="7"/>
+      <c r="R286" s="7"/>
+      <c r="S286" s="7"/>
+      <c r="T286" s="7"/>
+      <c r="U286" s="7"/>
+    </row>
+    <row r="287" spans="1:21" ht="15">
+      <c r="A287" s="7">
+        <v>309</v>
+      </c>
+      <c r="B287" s="2">
+        <v>46268.551793981504</v>
+      </c>
+      <c r="C287" s="2">
+        <v>46268.553055555603</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F287" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="G287" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H287" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="I287" s="7"/>
+      <c r="J287" s="3"/>
+      <c r="K287" s="6"/>
+      <c r="L287" s="3"/>
+      <c r="M287" s="3"/>
+      <c r="N287" s="3"/>
+      <c r="O287" s="3"/>
+      <c r="P287" s="3"/>
+      <c r="Q287" s="7"/>
+      <c r="R287" s="7"/>
+      <c r="S287" s="7"/>
+      <c r="T287" s="7"/>
+      <c r="U287" s="7"/>
+    </row>
+    <row r="288" spans="1:21" ht="15">
+      <c r="A288" s="7">
+        <v>310</v>
+      </c>
+      <c r="B288" s="2">
+        <v>46268.554259259297</v>
+      </c>
+      <c r="C288" s="2">
+        <v>46268.554872685199</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F288" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H288" s="3"/>
+      <c r="I288" s="7"/>
+      <c r="J288" s="3"/>
+      <c r="K288" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="L288" s="3"/>
+      <c r="M288" s="3"/>
+      <c r="N288" s="3"/>
+      <c r="O288" s="3"/>
+      <c r="P288" s="3"/>
+      <c r="Q288" s="7"/>
+      <c r="R288" s="7"/>
+      <c r="S288" s="7"/>
+      <c r="T288" s="7"/>
+      <c r="U288" s="7"/>
+    </row>
+    <row r="289" spans="1:21" ht="15">
+      <c r="A289" s="7">
+        <v>311</v>
+      </c>
+      <c r="B289" s="2">
+        <v>46268.554108796299</v>
+      </c>
+      <c r="C289" s="2">
+        <v>46268.555266203701</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F289" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H289" s="3"/>
+      <c r="I289" s="7"/>
+      <c r="J289" s="3"/>
+      <c r="K289" s="6"/>
+      <c r="L289" s="3"/>
+      <c r="M289" s="3"/>
+      <c r="N289" s="3"/>
+      <c r="O289" s="3"/>
+      <c r="P289" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="Q289" s="7"/>
+      <c r="R289" s="7"/>
+      <c r="S289" s="7"/>
+      <c r="T289" s="7"/>
+      <c r="U289" s="7"/>
+    </row>
+    <row r="290" spans="1:21" ht="15">
+      <c r="A290" s="7">
+        <v>312</v>
+      </c>
+      <c r="B290" s="2">
+        <v>46268.5570717593</v>
+      </c>
+      <c r="C290" s="2">
+        <v>46268.557442129597</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="E290" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="F290" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="G290" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H290" s="3"/>
+      <c r="I290" s="7"/>
+      <c r="J290" s="3"/>
+      <c r="K290" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="L290" s="3"/>
+      <c r="M290" s="3"/>
+      <c r="N290" s="3"/>
+      <c r="O290" s="3"/>
+      <c r="P290" s="3"/>
+      <c r="Q290" s="7"/>
+      <c r="R290" s="7"/>
+      <c r="S290" s="7"/>
+      <c r="T290" s="7"/>
+      <c r="U290" s="7"/>
+    </row>
+    <row r="291" spans="1:21" ht="15">
+      <c r="A291" s="7">
+        <v>313</v>
+      </c>
+      <c r="B291" s="2">
+        <v>46268.561712962997</v>
+      </c>
+      <c r="C291" s="2">
+        <v>46268.562199074098</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F291" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H291" s="3"/>
+      <c r="I291" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J291" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="K291" s="6"/>
+      <c r="L291" s="3"/>
+      <c r="M291" s="3"/>
+      <c r="N291" s="3"/>
+      <c r="O291" s="3"/>
+      <c r="P291" s="3"/>
+      <c r="Q291" s="7"/>
+      <c r="R291" s="7"/>
+      <c r="S291" s="7"/>
+      <c r="T291" s="7"/>
+      <c r="U291" s="7"/>
+    </row>
+    <row r="292" spans="1:21" ht="15">
+      <c r="A292" s="7">
+        <v>314</v>
+      </c>
+      <c r="B292" s="2">
+        <v>46268.562662037002</v>
+      </c>
+      <c r="C292" s="2">
+        <v>46268.562962962998</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E292" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F292" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H292" s="3"/>
+      <c r="I292" s="7"/>
+      <c r="J292" s="3"/>
+      <c r="K292" s="6"/>
+      <c r="L292" s="3"/>
+      <c r="M292" s="3"/>
+      <c r="N292" s="3"/>
+      <c r="O292" s="3"/>
+      <c r="P292" s="3"/>
+      <c r="Q292" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="R292" s="7"/>
+      <c r="S292" s="7"/>
+      <c r="T292" s="7"/>
+      <c r="U292" s="7"/>
+    </row>
+    <row r="293" spans="1:21" ht="15">
+      <c r="A293" s="7">
+        <v>315</v>
+      </c>
+      <c r="B293" s="2">
+        <v>46268.562962962998</v>
+      </c>
+      <c r="C293" s="2">
+        <v>46268.563101851803</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H293" s="3"/>
+      <c r="I293" s="7"/>
+      <c r="J293" s="3"/>
+      <c r="K293" s="6"/>
+      <c r="L293" s="3"/>
+      <c r="M293" s="3"/>
+      <c r="N293" s="3"/>
+      <c r="O293" s="3"/>
+      <c r="P293" s="3"/>
+      <c r="Q293" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="R293" s="7"/>
+      <c r="S293" s="7"/>
+      <c r="T293" s="7"/>
+      <c r="U293" s="7"/>
+    </row>
+    <row r="294" spans="1:21" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="348" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7A9C1B7-E6EC-4B93-A9E3-29178CDA3E68}"/>
+  <xr:revisionPtr revIDLastSave="351" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{445F7845-FEFA-4D5F-A892-658EB369E7D9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="544">
   <si>
     <t>Id</t>
   </si>
@@ -1665,6 +1665,9 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Echegaray.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20CEMTRAM%204.jpg</t>
   </si>
 </sst>
 </file>
@@ -1799,8 +1802,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U293" totalsRowShown="0">
-  <autoFilter ref="A1:U293" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U294" totalsRowShown="0">
+  <autoFilter ref="A1:U294" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1953,7 +1956,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="315" latestEventMarker="550">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="316" latestEventMarker="551">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2278,7 +2281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U294"/>
+  <dimension ref="A1:U295"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -12416,7 +12419,46 @@
       <c r="T293" s="7"/>
       <c r="U293" s="7"/>
     </row>
-    <row r="294" spans="1:21" ht="15"/>
+    <row r="294" spans="1:21" ht="15">
+      <c r="A294" s="7">
+        <v>316</v>
+      </c>
+      <c r="B294" s="2">
+        <v>46268.567662037</v>
+      </c>
+      <c r="C294" s="2">
+        <v>46268.567986111098</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E294" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H294" s="3"/>
+      <c r="I294" s="7"/>
+      <c r="J294" s="3"/>
+      <c r="K294" s="6"/>
+      <c r="L294" s="3"/>
+      <c r="M294" s="3"/>
+      <c r="N294" s="3"/>
+      <c r="O294" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="P294" s="3"/>
+      <c r="Q294" s="7"/>
+      <c r="R294" s="7"/>
+      <c r="S294" s="7"/>
+      <c r="T294" s="7"/>
+      <c r="U294" s="7"/>
+    </row>
+    <row r="295" spans="1:21" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="351" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{445F7845-FEFA-4D5F-A892-658EB369E7D9}"/>
+  <xr:revisionPtr revIDLastSave="363" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6D897CA-49CB-4279-B552-50B568410E13}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="546">
   <si>
     <t>Id</t>
   </si>
@@ -1668,13 +1668,19 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20CEMTRAM%204.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Starbucks%20Echegaray.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Echegaray.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1802,8 +1808,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U294" totalsRowShown="0">
-  <autoFilter ref="A1:U294" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U296" totalsRowShown="0">
+  <autoFilter ref="A1:U296" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1956,7 +1962,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="316" latestEventMarker="551">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="318" latestEventMarker="553">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2281,23 +2287,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U295"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <dimension ref="A1:U296"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" customWidth="1"/>
     <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.1796875" customWidth="1"/>
+    <col min="5" max="5" width="35.1796875" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="19" customWidth="1"/>
-    <col min="19" max="19" width="42.140625" customWidth="1"/>
+    <col min="19" max="19" width="42.1796875" customWidth="1"/>
     <col min="20" max="21" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2362,7 +2368,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>13</v>
       </c>
@@ -2388,7 +2394,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>17</v>
       </c>
@@ -2421,7 +2427,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2454,7 +2460,7 @@
       </c>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>20</v>
       </c>
@@ -2487,7 +2493,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>21</v>
       </c>
@@ -2520,7 +2526,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>22</v>
       </c>
@@ -2553,7 +2559,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>23</v>
       </c>
@@ -2587,7 +2593,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>24</v>
       </c>
@@ -2621,7 +2627,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>25</v>
       </c>
@@ -2655,7 +2661,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>26</v>
       </c>
@@ -2688,7 +2694,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>27</v>
       </c>
@@ -2724,7 +2730,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>28</v>
       </c>
@@ -2757,7 +2763,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>29</v>
       </c>
@@ -2791,7 +2797,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>30</v>
       </c>
@@ -2824,7 +2830,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>31</v>
       </c>
@@ -2857,7 +2863,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>32</v>
       </c>
@@ -2891,7 +2897,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>33</v>
       </c>
@@ -2924,7 +2930,7 @@
       </c>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>34</v>
       </c>
@@ -2957,7 +2963,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>35</v>
       </c>
@@ -2990,7 +2996,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>36</v>
       </c>
@@ -3023,7 +3029,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>37</v>
       </c>
@@ -3057,7 +3063,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>38</v>
       </c>
@@ -3091,7 +3097,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>39</v>
       </c>
@@ -3125,7 +3131,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>40</v>
       </c>
@@ -3159,7 +3165,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>41</v>
       </c>
@@ -3192,7 +3198,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>42</v>
       </c>
@@ -3226,7 +3232,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>43</v>
       </c>
@@ -3260,7 +3266,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>44</v>
       </c>
@@ -3294,7 +3300,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>45</v>
       </c>
@@ -3328,7 +3334,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>46</v>
       </c>
@@ -3362,7 +3368,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>47</v>
       </c>
@@ -3396,7 +3402,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>48</v>
       </c>
@@ -3429,7 +3435,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>49</v>
       </c>
@@ -3463,7 +3469,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>50</v>
       </c>
@@ -3497,7 +3503,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>51</v>
       </c>
@@ -3531,7 +3537,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>52</v>
       </c>
@@ -3564,7 +3570,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>54</v>
       </c>
@@ -3597,7 +3603,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>55</v>
       </c>
@@ -3630,7 +3636,7 @@
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>56</v>
       </c>
@@ -3664,7 +3670,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>57</v>
       </c>
@@ -3698,7 +3704,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>58</v>
       </c>
@@ -3732,7 +3738,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>59</v>
       </c>
@@ -3766,7 +3772,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>60</v>
       </c>
@@ -3800,7 +3806,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>61</v>
       </c>
@@ -3834,7 +3840,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>62</v>
       </c>
@@ -3868,7 +3874,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>63</v>
       </c>
@@ -3902,7 +3908,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>65</v>
       </c>
@@ -3936,7 +3942,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>66</v>
       </c>
@@ -3970,7 +3976,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>67</v>
       </c>
@@ -4003,7 +4009,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>68</v>
       </c>
@@ -4036,7 +4042,7 @@
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>69</v>
       </c>
@@ -4070,7 +4076,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>70</v>
       </c>
@@ -4104,7 +4110,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>71</v>
       </c>
@@ -4138,7 +4144,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>72</v>
       </c>
@@ -4172,7 +4178,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>73</v>
       </c>
@@ -4206,7 +4212,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>74</v>
       </c>
@@ -4240,7 +4246,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>75</v>
       </c>
@@ -4274,7 +4280,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>76</v>
       </c>
@@ -4308,7 +4314,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>77</v>
       </c>
@@ -4341,7 +4347,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>78</v>
       </c>
@@ -4375,7 +4381,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>79</v>
       </c>
@@ -4409,7 +4415,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>80</v>
       </c>
@@ -4443,7 +4449,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>81</v>
       </c>
@@ -4477,7 +4483,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>84</v>
       </c>
@@ -4511,7 +4517,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>85</v>
       </c>
@@ -4544,7 +4550,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>86</v>
       </c>
@@ -4577,7 +4583,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>88</v>
       </c>
@@ -4610,7 +4616,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>89</v>
       </c>
@@ -4643,7 +4649,7 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>90</v>
       </c>
@@ -4677,7 +4683,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>91</v>
       </c>
@@ -4711,7 +4717,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>92</v>
       </c>
@@ -4747,7 +4753,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>93</v>
       </c>
@@ -4780,7 +4786,7 @@
       </c>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>94</v>
       </c>
@@ -4813,7 +4819,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>95</v>
       </c>
@@ -4846,7 +4852,7 @@
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>96</v>
       </c>
@@ -4880,7 +4886,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>97</v>
       </c>
@@ -4913,7 +4919,7 @@
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>98</v>
       </c>
@@ -4947,7 +4953,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>99</v>
       </c>
@@ -4980,7 +4986,7 @@
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>100</v>
       </c>
@@ -5014,7 +5020,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>102</v>
       </c>
@@ -5050,7 +5056,7 @@
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>103</v>
       </c>
@@ -5083,7 +5089,7 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>104</v>
       </c>
@@ -5117,7 +5123,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>105</v>
       </c>
@@ -5153,7 +5159,7 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>106</v>
       </c>
@@ -5187,7 +5193,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>107</v>
       </c>
@@ -5220,7 +5226,7 @@
       </c>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>108</v>
       </c>
@@ -5254,7 +5260,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>109</v>
       </c>
@@ -5288,7 +5294,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>110</v>
       </c>
@@ -5321,7 +5327,7 @@
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>111</v>
       </c>
@@ -5355,7 +5361,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>112</v>
       </c>
@@ -5388,7 +5394,7 @@
       </c>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>113</v>
       </c>
@@ -5422,7 +5428,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>114</v>
       </c>
@@ -5456,7 +5462,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>115</v>
       </c>
@@ -5489,7 +5495,7 @@
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>116</v>
       </c>
@@ -5522,7 +5528,7 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>117</v>
       </c>
@@ -5555,7 +5561,7 @@
       </c>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:21">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>118</v>
       </c>
@@ -5588,7 +5594,7 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:21">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>119</v>
       </c>
@@ -5621,7 +5627,7 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
     </row>
-    <row r="99" spans="1:21">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>120</v>
       </c>
@@ -5654,7 +5660,7 @@
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
     </row>
-    <row r="100" spans="1:21">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>121</v>
       </c>
@@ -5688,7 +5694,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="101" spans="1:21">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>122</v>
       </c>
@@ -5721,7 +5727,7 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:21">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>123</v>
       </c>
@@ -5755,7 +5761,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="103" spans="1:21">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>124</v>
       </c>
@@ -5789,7 +5795,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="104" spans="1:21">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>125</v>
       </c>
@@ -5823,7 +5829,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:21">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>126</v>
       </c>
@@ -5857,7 +5863,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="106" spans="1:21">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>127</v>
       </c>
@@ -5890,7 +5896,7 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:21">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>128</v>
       </c>
@@ -5926,7 +5932,7 @@
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
     </row>
-    <row r="108" spans="1:21">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>129</v>
       </c>
@@ -5960,7 +5966,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="109" spans="1:21">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>130</v>
       </c>
@@ -5996,7 +6002,7 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:21">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>131</v>
       </c>
@@ -6029,7 +6035,7 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:21">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>132</v>
       </c>
@@ -6063,7 +6069,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="112" spans="1:21">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>133</v>
       </c>
@@ -6097,7 +6103,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>134</v>
       </c>
@@ -6131,7 +6137,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>135</v>
       </c>
@@ -6165,7 +6171,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>136</v>
       </c>
@@ -6199,7 +6205,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>137</v>
       </c>
@@ -6233,7 +6239,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>138</v>
       </c>
@@ -6267,7 +6273,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>139</v>
       </c>
@@ -6301,7 +6307,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>140</v>
       </c>
@@ -6335,7 +6341,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>141</v>
       </c>
@@ -6368,7 +6374,7 @@
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>142</v>
       </c>
@@ -6402,7 +6408,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="122" spans="1:19">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>143</v>
       </c>
@@ -6435,7 +6441,7 @@
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>144</v>
       </c>
@@ -6469,7 +6475,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>145</v>
       </c>
@@ -6502,7 +6508,7 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:19">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>146</v>
       </c>
@@ -6536,7 +6542,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="126" spans="1:19">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>147</v>
       </c>
@@ -6569,7 +6575,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>148</v>
       </c>
@@ -6606,7 +6612,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="128" spans="1:19">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>149</v>
       </c>
@@ -6640,7 +6646,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="129" spans="1:19">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>150</v>
       </c>
@@ -6674,7 +6680,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="130" spans="1:19">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>151</v>
       </c>
@@ -6708,7 +6714,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="131" spans="1:19">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>152</v>
       </c>
@@ -6742,7 +6748,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="132" spans="1:19">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>153</v>
       </c>
@@ -6775,7 +6781,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="133" spans="1:19">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>154</v>
       </c>
@@ -6809,7 +6815,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="134" spans="1:19">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>155</v>
       </c>
@@ -6843,7 +6849,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="135" spans="1:19">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>156</v>
       </c>
@@ -6880,7 +6886,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="136" spans="1:19">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>157</v>
       </c>
@@ -6913,7 +6919,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="137" spans="1:19">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>158</v>
       </c>
@@ -6947,7 +6953,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="138" spans="1:19">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>159</v>
       </c>
@@ -6984,7 +6990,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="139" spans="1:19">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>160</v>
       </c>
@@ -7020,7 +7026,7 @@
       <c r="O139" s="3"/>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="1:19">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>161</v>
       </c>
@@ -7053,7 +7059,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="141" spans="1:19">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>162</v>
       </c>
@@ -7089,7 +7095,7 @@
       <c r="O141" s="3"/>
       <c r="P141" s="3"/>
     </row>
-    <row r="142" spans="1:19">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>163</v>
       </c>
@@ -7125,7 +7131,7 @@
       <c r="O142" s="3"/>
       <c r="P142" s="3"/>
     </row>
-    <row r="143" spans="1:19">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>164</v>
       </c>
@@ -7158,7 +7164,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="144" spans="1:19">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>165</v>
       </c>
@@ -7195,7 +7201,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>166</v>
       </c>
@@ -7231,7 +7237,7 @@
       <c r="O145" s="3"/>
       <c r="P145" s="3"/>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>167</v>
       </c>
@@ -7267,7 +7273,7 @@
       <c r="O146" s="3"/>
       <c r="P146" s="3"/>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>168</v>
       </c>
@@ -7303,7 +7309,7 @@
       <c r="O147" s="3"/>
       <c r="P147" s="3"/>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>169</v>
       </c>
@@ -7339,7 +7345,7 @@
       <c r="O148" s="3"/>
       <c r="P148" s="3"/>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>170</v>
       </c>
@@ -7375,7 +7381,7 @@
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>171</v>
       </c>
@@ -7411,7 +7417,7 @@
       <c r="O150" s="3"/>
       <c r="P150" s="3"/>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>172</v>
       </c>
@@ -7447,7 +7453,7 @@
       <c r="O151" s="3"/>
       <c r="P151" s="3"/>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>173</v>
       </c>
@@ -7483,7 +7489,7 @@
       <c r="O152" s="3"/>
       <c r="P152" s="3"/>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>174</v>
       </c>
@@ -7519,7 +7525,7 @@
       <c r="O153" s="3"/>
       <c r="P153" s="3"/>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>175</v>
       </c>
@@ -7555,7 +7561,7 @@
       <c r="O154" s="3"/>
       <c r="P154" s="3"/>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>176</v>
       </c>
@@ -7591,7 +7597,7 @@
       <c r="O155" s="3"/>
       <c r="P155" s="3"/>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>177</v>
       </c>
@@ -7627,7 +7633,7 @@
       <c r="O156" s="3"/>
       <c r="P156" s="3"/>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>178</v>
       </c>
@@ -7663,7 +7669,7 @@
       <c r="O157" s="3"/>
       <c r="P157" s="3"/>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>179</v>
       </c>
@@ -7699,7 +7705,7 @@
       <c r="O158" s="3"/>
       <c r="P158" s="3"/>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>180</v>
       </c>
@@ -7735,7 +7741,7 @@
       <c r="O159" s="3"/>
       <c r="P159" s="3"/>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>181</v>
       </c>
@@ -7771,7 +7777,7 @@
       <c r="O160" s="3"/>
       <c r="P160" s="3"/>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>182</v>
       </c>
@@ -7807,7 +7813,7 @@
       <c r="O161" s="3"/>
       <c r="P161" s="3"/>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>183</v>
       </c>
@@ -7843,7 +7849,7 @@
       <c r="O162" s="3"/>
       <c r="P162" s="3"/>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>184</v>
       </c>
@@ -7877,7 +7883,7 @@
       <c r="O163" s="3"/>
       <c r="P163" s="3"/>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>185</v>
       </c>
@@ -7913,7 +7919,7 @@
       <c r="O164" s="3"/>
       <c r="P164" s="3"/>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>186</v>
       </c>
@@ -7949,7 +7955,7 @@
       <c r="O165" s="3"/>
       <c r="P165" s="3"/>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>187</v>
       </c>
@@ -7985,7 +7991,7 @@
       <c r="O166" s="3"/>
       <c r="P166" s="3"/>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>188</v>
       </c>
@@ -8021,7 +8027,7 @@
       <c r="O167" s="3"/>
       <c r="P167" s="3"/>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>189</v>
       </c>
@@ -8057,7 +8063,7 @@
       <c r="O168" s="3"/>
       <c r="P168" s="3"/>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>190</v>
       </c>
@@ -8093,7 +8099,7 @@
       <c r="O169" s="3"/>
       <c r="P169" s="3"/>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>191</v>
       </c>
@@ -8129,7 +8135,7 @@
       <c r="O170" s="3"/>
       <c r="P170" s="3"/>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>192</v>
       </c>
@@ -8165,7 +8171,7 @@
       <c r="O171" s="3"/>
       <c r="P171" s="3"/>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>193</v>
       </c>
@@ -8201,7 +8207,7 @@
       <c r="O172" s="3"/>
       <c r="P172" s="3"/>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>194</v>
       </c>
@@ -8237,7 +8243,7 @@
       <c r="O173" s="3"/>
       <c r="P173" s="3"/>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>195</v>
       </c>
@@ -8273,7 +8279,7 @@
       <c r="O174" s="3"/>
       <c r="P174" s="3"/>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>196</v>
       </c>
@@ -8309,7 +8315,7 @@
       <c r="O175" s="3"/>
       <c r="P175" s="3"/>
     </row>
-    <row r="176" spans="1:16">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>197</v>
       </c>
@@ -8345,7 +8351,7 @@
       <c r="O176" s="3"/>
       <c r="P176" s="3"/>
     </row>
-    <row r="177" spans="1:16">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>198</v>
       </c>
@@ -8381,7 +8387,7 @@
       <c r="O177" s="3"/>
       <c r="P177" s="3"/>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>199</v>
       </c>
@@ -8417,7 +8423,7 @@
       <c r="O178" s="3"/>
       <c r="P178" s="3"/>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>200</v>
       </c>
@@ -8453,7 +8459,7 @@
       <c r="O179" s="3"/>
       <c r="P179" s="3"/>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>201</v>
       </c>
@@ -8489,7 +8495,7 @@
       <c r="O180" s="3"/>
       <c r="P180" s="3"/>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>202</v>
       </c>
@@ -8525,7 +8531,7 @@
       <c r="O181" s="3"/>
       <c r="P181" s="3"/>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>203</v>
       </c>
@@ -8561,7 +8567,7 @@
       <c r="O182" s="3"/>
       <c r="P182" s="3"/>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>204</v>
       </c>
@@ -8597,7 +8603,7 @@
       <c r="O183" s="3"/>
       <c r="P183" s="3"/>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>205</v>
       </c>
@@ -8633,7 +8639,7 @@
       <c r="O184" s="3"/>
       <c r="P184" s="3"/>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>206</v>
       </c>
@@ -8669,7 +8675,7 @@
       <c r="O185" s="3"/>
       <c r="P185" s="3"/>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>207</v>
       </c>
@@ -8702,7 +8708,7 @@
       <c r="O186" s="3"/>
       <c r="P186" s="3"/>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>208</v>
       </c>
@@ -8738,7 +8744,7 @@
       <c r="O187" s="3"/>
       <c r="P187" s="3"/>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>209</v>
       </c>
@@ -8772,7 +8778,7 @@
       <c r="O188" s="3"/>
       <c r="P188" s="3"/>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>210</v>
       </c>
@@ -8808,7 +8814,7 @@
       <c r="O189" s="3"/>
       <c r="P189" s="3"/>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>211</v>
       </c>
@@ -8844,7 +8850,7 @@
       <c r="O190" s="3"/>
       <c r="P190" s="3"/>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>212</v>
       </c>
@@ -8880,7 +8886,7 @@
       <c r="O191" s="3"/>
       <c r="P191" s="3"/>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>213</v>
       </c>
@@ -8913,7 +8919,7 @@
       <c r="O192" s="3"/>
       <c r="P192" s="3"/>
     </row>
-    <row r="193" spans="1:20">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>214</v>
       </c>
@@ -8947,7 +8953,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="194" spans="1:20">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>215</v>
       </c>
@@ -8983,7 +8989,7 @@
       <c r="O194" s="3"/>
       <c r="P194" s="3"/>
     </row>
-    <row r="195" spans="1:20">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>216</v>
       </c>
@@ -9019,7 +9025,7 @@
       <c r="O195" s="3"/>
       <c r="P195" s="3"/>
     </row>
-    <row r="196" spans="1:20">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>217</v>
       </c>
@@ -9055,7 +9061,7 @@
       <c r="O196" s="3"/>
       <c r="P196" s="3"/>
     </row>
-    <row r="197" spans="1:20">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>218</v>
       </c>
@@ -9091,7 +9097,7 @@
       <c r="O197" s="3"/>
       <c r="P197" s="3"/>
     </row>
-    <row r="198" spans="1:20">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>219</v>
       </c>
@@ -9124,7 +9130,7 @@
       <c r="O198" s="3"/>
       <c r="P198" s="3"/>
     </row>
-    <row r="199" spans="1:20">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>220</v>
       </c>
@@ -9158,7 +9164,7 @@
       <c r="O199" s="3"/>
       <c r="P199" s="3"/>
     </row>
-    <row r="200" spans="1:20">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>221</v>
       </c>
@@ -9195,7 +9201,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="201" spans="1:20">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>222</v>
       </c>
@@ -9231,7 +9237,7 @@
       <c r="O201" s="3"/>
       <c r="P201" s="3"/>
     </row>
-    <row r="202" spans="1:20">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>223</v>
       </c>
@@ -9264,7 +9270,7 @@
       <c r="O202" s="3"/>
       <c r="P202" s="3"/>
     </row>
-    <row r="203" spans="1:20">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>224</v>
       </c>
@@ -9300,7 +9306,7 @@
       <c r="O203" s="3"/>
       <c r="P203" s="3"/>
     </row>
-    <row r="204" spans="1:20">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>225</v>
       </c>
@@ -9336,7 +9342,7 @@
       <c r="O204" s="3"/>
       <c r="P204" s="3"/>
     </row>
-    <row r="205" spans="1:20">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>226</v>
       </c>
@@ -9369,7 +9375,7 @@
       <c r="O205" s="3"/>
       <c r="P205" s="3"/>
     </row>
-    <row r="206" spans="1:20">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>227</v>
       </c>
@@ -9402,7 +9408,7 @@
       <c r="O206" s="3"/>
       <c r="P206" s="3"/>
     </row>
-    <row r="207" spans="1:20">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>228</v>
       </c>
@@ -9435,7 +9441,7 @@
       <c r="O207" s="3"/>
       <c r="P207" s="3"/>
     </row>
-    <row r="208" spans="1:20">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>229</v>
       </c>
@@ -9472,7 +9478,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="209" spans="1:19">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>230</v>
       </c>
@@ -9506,7 +9512,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="210" spans="1:19">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>231</v>
       </c>
@@ -9543,7 +9549,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="211" spans="1:19">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>232</v>
       </c>
@@ -9580,7 +9586,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="212" spans="1:19">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>233</v>
       </c>
@@ -9617,7 +9623,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="213" spans="1:19">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>234</v>
       </c>
@@ -9651,7 +9657,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="214" spans="1:19">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>235</v>
       </c>
@@ -9688,7 +9694,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="215" spans="1:19">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>236</v>
       </c>
@@ -9721,7 +9727,7 @@
       <c r="O215" s="3"/>
       <c r="P215" s="3"/>
     </row>
-    <row r="216" spans="1:19">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>237</v>
       </c>
@@ -9754,7 +9760,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="217" spans="1:19">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>238</v>
       </c>
@@ -9787,7 +9793,7 @@
       <c r="O217" s="3"/>
       <c r="P217" s="3"/>
     </row>
-    <row r="218" spans="1:19">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>239</v>
       </c>
@@ -9820,7 +9826,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="219" spans="1:19">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>240</v>
       </c>
@@ -9856,7 +9862,7 @@
       <c r="O219" s="3"/>
       <c r="P219" s="3"/>
     </row>
-    <row r="220" spans="1:19" ht="15">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>241</v>
       </c>
@@ -9889,7 +9895,7 @@
       <c r="O220" s="3"/>
       <c r="P220" s="3"/>
     </row>
-    <row r="221" spans="1:19" ht="15">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>242</v>
       </c>
@@ -9922,7 +9928,7 @@
       <c r="O221" s="3"/>
       <c r="P221" s="3"/>
     </row>
-    <row r="222" spans="1:19" ht="15">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>243</v>
       </c>
@@ -9955,7 +9961,7 @@
       </c>
       <c r="P222" s="3"/>
     </row>
-    <row r="223" spans="1:19" ht="15">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>244</v>
       </c>
@@ -9988,7 +9994,7 @@
       <c r="O223" s="3"/>
       <c r="P223" s="3"/>
     </row>
-    <row r="224" spans="1:19" ht="15">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>245</v>
       </c>
@@ -10021,7 +10027,7 @@
       </c>
       <c r="P224" s="3"/>
     </row>
-    <row r="225" spans="1:21" ht="15">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>246</v>
       </c>
@@ -10054,7 +10060,7 @@
       <c r="O225" s="3"/>
       <c r="P225" s="3"/>
     </row>
-    <row r="226" spans="1:21" ht="15">
+    <row r="226" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>247</v>
       </c>
@@ -10087,7 +10093,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="227" spans="1:21" ht="15">
+    <row r="227" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>248</v>
       </c>
@@ -10120,7 +10126,7 @@
       <c r="O227" s="3"/>
       <c r="P227" s="3"/>
     </row>
-    <row r="228" spans="1:21" ht="15">
+    <row r="228" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>249</v>
       </c>
@@ -10153,7 +10159,7 @@
       <c r="O228" s="3"/>
       <c r="P228" s="3"/>
     </row>
-    <row r="229" spans="1:21" ht="15">
+    <row r="229" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>250</v>
       </c>
@@ -10186,7 +10192,7 @@
       <c r="O229" s="3"/>
       <c r="P229" s="3"/>
     </row>
-    <row r="230" spans="1:21" ht="15">
+    <row r="230" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>251</v>
       </c>
@@ -10219,7 +10225,7 @@
       <c r="O230" s="3"/>
       <c r="P230" s="3"/>
     </row>
-    <row r="231" spans="1:21" ht="15">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>252</v>
       </c>
@@ -10255,7 +10261,7 @@
       <c r="O231" s="3"/>
       <c r="P231" s="3"/>
     </row>
-    <row r="232" spans="1:21" ht="15">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>253</v>
       </c>
@@ -10288,7 +10294,7 @@
       <c r="O232" s="3"/>
       <c r="P232" s="3"/>
     </row>
-    <row r="233" spans="1:21" ht="15">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>254</v>
       </c>
@@ -10325,7 +10331,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="234" spans="1:21" ht="15">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>255</v>
       </c>
@@ -10361,7 +10367,7 @@
       <c r="O234" s="3"/>
       <c r="P234" s="3"/>
     </row>
-    <row r="235" spans="1:21" ht="15">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>256</v>
       </c>
@@ -10397,7 +10403,7 @@
       <c r="O235" s="3"/>
       <c r="P235" s="3"/>
     </row>
-    <row r="236" spans="1:21" ht="15">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>257</v>
       </c>
@@ -10431,7 +10437,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="237" spans="1:21" ht="15">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>258</v>
       </c>
@@ -10465,7 +10471,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="238" spans="1:21" ht="15">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>259</v>
       </c>
@@ -10498,7 +10504,7 @@
       <c r="O238" s="3"/>
       <c r="P238" s="3"/>
     </row>
-    <row r="239" spans="1:21" ht="15">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>260</v>
       </c>
@@ -10531,7 +10537,7 @@
       <c r="O239" s="3"/>
       <c r="P239" s="3"/>
     </row>
-    <row r="240" spans="1:21" ht="15">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>261</v>
       </c>
@@ -10564,7 +10570,7 @@
       <c r="O240" s="3"/>
       <c r="P240" s="3"/>
     </row>
-    <row r="241" spans="1:20" ht="15">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>262</v>
       </c>
@@ -10597,7 +10603,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="242" spans="1:20" ht="15">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>263</v>
       </c>
@@ -10633,7 +10639,7 @@
       <c r="O242" s="3"/>
       <c r="P242" s="3"/>
     </row>
-    <row r="243" spans="1:20" ht="15">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>264</v>
       </c>
@@ -10666,7 +10672,7 @@
       </c>
       <c r="P243" s="3"/>
     </row>
-    <row r="244" spans="1:20" ht="15">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>265</v>
       </c>
@@ -10699,7 +10705,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="245" spans="1:20" ht="15">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>266</v>
       </c>
@@ -10733,7 +10739,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="246" spans="1:20" ht="15">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>267</v>
       </c>
@@ -10766,7 +10772,7 @@
       <c r="O246" s="3"/>
       <c r="P246" s="3"/>
     </row>
-    <row r="247" spans="1:20" ht="15">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>268</v>
       </c>
@@ -10799,7 +10805,7 @@
       <c r="O247" s="3"/>
       <c r="P247" s="3"/>
     </row>
-    <row r="248" spans="1:20" ht="15">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>269</v>
       </c>
@@ -10835,7 +10841,7 @@
       <c r="O248" s="3"/>
       <c r="P248" s="3"/>
     </row>
-    <row r="249" spans="1:20" ht="15">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>270</v>
       </c>
@@ -10868,7 +10874,7 @@
       </c>
       <c r="P249" s="3"/>
     </row>
-    <row r="250" spans="1:20" ht="15">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>271</v>
       </c>
@@ -10902,7 +10908,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="251" spans="1:20" ht="15">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>272</v>
       </c>
@@ -10935,7 +10941,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="252" spans="1:20" ht="15">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>273</v>
       </c>
@@ -10968,7 +10974,7 @@
       <c r="O252" s="3"/>
       <c r="P252" s="3"/>
     </row>
-    <row r="253" spans="1:20" ht="15">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>274</v>
       </c>
@@ -11001,7 +11007,7 @@
       <c r="O253" s="3"/>
       <c r="P253" s="3"/>
     </row>
-    <row r="254" spans="1:20" ht="15">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>275</v>
       </c>
@@ -11035,7 +11041,7 @@
       <c r="O254" s="3"/>
       <c r="P254" s="3"/>
     </row>
-    <row r="255" spans="1:20" ht="15">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>276</v>
       </c>
@@ -11071,7 +11077,7 @@
       <c r="O255" s="3"/>
       <c r="P255" s="3"/>
     </row>
-    <row r="256" spans="1:20" ht="15">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>277</v>
       </c>
@@ -11104,7 +11110,7 @@
       <c r="O256" s="3"/>
       <c r="P256" s="3"/>
     </row>
-    <row r="257" spans="1:21" ht="15">
+    <row r="257" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>278</v>
       </c>
@@ -11137,7 +11143,7 @@
       <c r="O257" s="3"/>
       <c r="P257" s="3"/>
     </row>
-    <row r="258" spans="1:21" ht="15">
+    <row r="258" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>279</v>
       </c>
@@ -11174,7 +11180,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="259" spans="1:21" ht="15">
+    <row r="259" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>280</v>
       </c>
@@ -11207,7 +11213,7 @@
       <c r="O259" s="3"/>
       <c r="P259" s="3"/>
     </row>
-    <row r="260" spans="1:21" ht="15">
+    <row r="260" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>281</v>
       </c>
@@ -11243,7 +11249,7 @@
       <c r="O260" s="3"/>
       <c r="P260" s="3"/>
     </row>
-    <row r="261" spans="1:21" ht="15">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>282</v>
       </c>
@@ -11276,7 +11282,7 @@
       <c r="O261" s="3"/>
       <c r="P261" s="3"/>
     </row>
-    <row r="262" spans="1:21" ht="15">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>283</v>
       </c>
@@ -11312,7 +11318,7 @@
       <c r="O262" s="3"/>
       <c r="P262" s="3"/>
     </row>
-    <row r="263" spans="1:21" ht="15">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>284</v>
       </c>
@@ -11345,7 +11351,7 @@
       <c r="O263" s="3"/>
       <c r="P263" s="3"/>
     </row>
-    <row r="264" spans="1:21" ht="15">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>285</v>
       </c>
@@ -11381,7 +11387,7 @@
       <c r="O264" s="3"/>
       <c r="P264" s="3"/>
     </row>
-    <row r="265" spans="1:21" ht="15">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>286</v>
       </c>
@@ -11414,7 +11420,7 @@
       <c r="O265" s="3"/>
       <c r="P265" s="3"/>
     </row>
-    <row r="266" spans="1:21" ht="15">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>287</v>
       </c>
@@ -11447,7 +11453,7 @@
       <c r="O266" s="3"/>
       <c r="P266" s="3"/>
     </row>
-    <row r="267" spans="1:21" ht="15">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>288</v>
       </c>
@@ -11480,7 +11486,7 @@
       </c>
       <c r="P267" s="3"/>
     </row>
-    <row r="268" spans="1:21" ht="15">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>289</v>
       </c>
@@ -11517,7 +11523,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="269" spans="1:21" ht="15">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>290</v>
       </c>
@@ -11553,7 +11559,7 @@
       <c r="O269" s="3"/>
       <c r="P269" s="3"/>
     </row>
-    <row r="270" spans="1:21" ht="15">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>291</v>
       </c>
@@ -11587,7 +11593,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="271" spans="1:21" ht="15">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>292</v>
       </c>
@@ -11620,7 +11626,7 @@
       </c>
       <c r="P271" s="3"/>
     </row>
-    <row r="272" spans="1:21" ht="15">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>293</v>
       </c>
@@ -11654,7 +11660,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="273" spans="1:21" ht="15">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>294</v>
       </c>
@@ -11691,7 +11697,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="274" spans="1:21" ht="15">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>295</v>
       </c>
@@ -11725,7 +11731,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="275" spans="1:21" ht="15">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>296</v>
       </c>
@@ -11762,7 +11768,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="276" spans="1:21" ht="15">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>297</v>
       </c>
@@ -11795,7 +11801,7 @@
       <c r="O276" s="3"/>
       <c r="P276" s="3"/>
     </row>
-    <row r="277" spans="1:21" ht="15">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>298</v>
       </c>
@@ -11828,7 +11834,7 @@
       <c r="O277" s="3"/>
       <c r="P277" s="3"/>
     </row>
-    <row r="278" spans="1:21" ht="15">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>299</v>
       </c>
@@ -11861,7 +11867,7 @@
       </c>
       <c r="P278" s="3"/>
     </row>
-    <row r="279" spans="1:21" ht="15">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>300</v>
       </c>
@@ -11894,7 +11900,7 @@
       <c r="O279" s="3"/>
       <c r="P279" s="3"/>
     </row>
-    <row r="280" spans="1:21" ht="15">
+    <row r="280" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>301</v>
       </c>
@@ -11927,7 +11933,7 @@
       <c r="O280" s="3"/>
       <c r="P280" s="3"/>
     </row>
-    <row r="281" spans="1:21" ht="15">
+    <row r="281" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>302</v>
       </c>
@@ -11960,7 +11966,7 @@
       <c r="O281" s="3"/>
       <c r="P281" s="3"/>
     </row>
-    <row r="282" spans="1:21" ht="15">
+    <row r="282" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>303</v>
       </c>
@@ -11996,7 +12002,7 @@
       <c r="O282" s="3"/>
       <c r="P282" s="3"/>
     </row>
-    <row r="283" spans="1:21" ht="15">
+    <row r="283" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>304</v>
       </c>
@@ -12030,7 +12036,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="284" spans="1:21" ht="15">
+    <row r="284" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>306</v>
       </c>
@@ -12066,8 +12072,8 @@
       <c r="O284" s="3"/>
       <c r="P284" s="3"/>
     </row>
-    <row r="285" spans="1:21" ht="15">
-      <c r="A285" s="7">
+    <row r="285" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A285">
         <v>307</v>
       </c>
       <c r="B285" s="2">
@@ -12091,7 +12097,6 @@
       <c r="H285" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="I285" s="7"/>
       <c r="J285" s="3"/>
       <c r="K285" s="6"/>
       <c r="L285" s="3"/>
@@ -12099,14 +12104,9 @@
       <c r="N285" s="3"/>
       <c r="O285" s="3"/>
       <c r="P285" s="3"/>
-      <c r="Q285" s="7"/>
-      <c r="R285" s="7"/>
-      <c r="S285" s="7"/>
-      <c r="T285" s="7"/>
-      <c r="U285" s="7"/>
-    </row>
-    <row r="286" spans="1:21" ht="15">
-      <c r="A286" s="7">
+    </row>
+    <row r="286" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A286">
         <v>308</v>
       </c>
       <c r="B286" s="2">
@@ -12128,7 +12128,6 @@
         <v>38</v>
       </c>
       <c r="H286" s="3"/>
-      <c r="I286" s="7"/>
       <c r="J286" s="3"/>
       <c r="K286" s="6" t="s">
         <v>537</v>
@@ -12138,14 +12137,9 @@
       <c r="N286" s="3"/>
       <c r="O286" s="3"/>
       <c r="P286" s="3"/>
-      <c r="Q286" s="7"/>
-      <c r="R286" s="7"/>
-      <c r="S286" s="7"/>
-      <c r="T286" s="7"/>
-      <c r="U286" s="7"/>
-    </row>
-    <row r="287" spans="1:21" ht="15">
-      <c r="A287" s="7">
+    </row>
+    <row r="287" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A287">
         <v>309</v>
       </c>
       <c r="B287" s="2">
@@ -12169,7 +12163,6 @@
       <c r="H287" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="I287" s="7"/>
       <c r="J287" s="3"/>
       <c r="K287" s="6"/>
       <c r="L287" s="3"/>
@@ -12177,14 +12170,9 @@
       <c r="N287" s="3"/>
       <c r="O287" s="3"/>
       <c r="P287" s="3"/>
-      <c r="Q287" s="7"/>
-      <c r="R287" s="7"/>
-      <c r="S287" s="7"/>
-      <c r="T287" s="7"/>
-      <c r="U287" s="7"/>
-    </row>
-    <row r="288" spans="1:21" ht="15">
-      <c r="A288" s="7">
+    </row>
+    <row r="288" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A288">
         <v>310</v>
       </c>
       <c r="B288" s="2">
@@ -12206,7 +12194,6 @@
         <v>38</v>
       </c>
       <c r="H288" s="3"/>
-      <c r="I288" s="7"/>
       <c r="J288" s="3"/>
       <c r="K288" s="6" t="s">
         <v>539</v>
@@ -12216,14 +12203,9 @@
       <c r="N288" s="3"/>
       <c r="O288" s="3"/>
       <c r="P288" s="3"/>
-      <c r="Q288" s="7"/>
-      <c r="R288" s="7"/>
-      <c r="S288" s="7"/>
-      <c r="T288" s="7"/>
-      <c r="U288" s="7"/>
-    </row>
-    <row r="289" spans="1:21" ht="15">
-      <c r="A289" s="7">
+    </row>
+    <row r="289" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A289">
         <v>311</v>
       </c>
       <c r="B289" s="2">
@@ -12245,7 +12227,6 @@
         <v>41</v>
       </c>
       <c r="H289" s="3"/>
-      <c r="I289" s="7"/>
       <c r="J289" s="3"/>
       <c r="K289" s="6"/>
       <c r="L289" s="3"/>
@@ -12255,14 +12236,9 @@
       <c r="P289" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="Q289" s="7"/>
-      <c r="R289" s="7"/>
-      <c r="S289" s="7"/>
-      <c r="T289" s="7"/>
-      <c r="U289" s="7"/>
-    </row>
-    <row r="290" spans="1:21" ht="15">
-      <c r="A290" s="7">
+    </row>
+    <row r="290" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A290">
         <v>312</v>
       </c>
       <c r="B290" s="2">
@@ -12284,7 +12260,6 @@
         <v>38</v>
       </c>
       <c r="H290" s="3"/>
-      <c r="I290" s="7"/>
       <c r="J290" s="3"/>
       <c r="K290" s="6" t="s">
         <v>541</v>
@@ -12294,14 +12269,9 @@
       <c r="N290" s="3"/>
       <c r="O290" s="3"/>
       <c r="P290" s="3"/>
-      <c r="Q290" s="7"/>
-      <c r="R290" s="7"/>
-      <c r="S290" s="7"/>
-      <c r="T290" s="7"/>
-      <c r="U290" s="7"/>
-    </row>
-    <row r="291" spans="1:21" ht="15">
-      <c r="A291" s="7">
+    </row>
+    <row r="291" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A291">
         <v>313</v>
       </c>
       <c r="B291" s="2">
@@ -12323,7 +12293,7 @@
         <v>60</v>
       </c>
       <c r="H291" s="3"/>
-      <c r="I291" s="7" t="s">
+      <c r="I291" t="s">
         <v>61</v>
       </c>
       <c r="J291" s="3" t="s">
@@ -12335,14 +12305,9 @@
       <c r="N291" s="3"/>
       <c r="O291" s="3"/>
       <c r="P291" s="3"/>
-      <c r="Q291" s="7"/>
-      <c r="R291" s="7"/>
-      <c r="S291" s="7"/>
-      <c r="T291" s="7"/>
-      <c r="U291" s="7"/>
-    </row>
-    <row r="292" spans="1:21" ht="15">
-      <c r="A292" s="7">
+    </row>
+    <row r="292" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A292">
         <v>314</v>
       </c>
       <c r="B292" s="2">
@@ -12364,7 +12329,6 @@
         <v>106</v>
       </c>
       <c r="H292" s="3"/>
-      <c r="I292" s="7"/>
       <c r="J292" s="3"/>
       <c r="K292" s="6"/>
       <c r="L292" s="3"/>
@@ -12372,16 +12336,12 @@
       <c r="N292" s="3"/>
       <c r="O292" s="3"/>
       <c r="P292" s="3"/>
-      <c r="Q292" s="7" t="s">
+      <c r="Q292" t="s">
         <v>107</v>
       </c>
-      <c r="R292" s="7"/>
-      <c r="S292" s="7"/>
-      <c r="T292" s="7"/>
-      <c r="U292" s="7"/>
-    </row>
-    <row r="293" spans="1:21" ht="15">
-      <c r="A293" s="7">
+    </row>
+    <row r="293" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A293">
         <v>315</v>
       </c>
       <c r="B293" s="2">
@@ -12403,7 +12363,6 @@
         <v>106</v>
       </c>
       <c r="H293" s="3"/>
-      <c r="I293" s="7"/>
       <c r="J293" s="3"/>
       <c r="K293" s="6"/>
       <c r="L293" s="3"/>
@@ -12411,16 +12370,12 @@
       <c r="N293" s="3"/>
       <c r="O293" s="3"/>
       <c r="P293" s="3"/>
-      <c r="Q293" s="7" t="s">
+      <c r="Q293" t="s">
         <v>107</v>
       </c>
-      <c r="R293" s="7"/>
-      <c r="S293" s="7"/>
-      <c r="T293" s="7"/>
-      <c r="U293" s="7"/>
-    </row>
-    <row r="294" spans="1:21" ht="15">
-      <c r="A294" s="7">
+    </row>
+    <row r="294" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A294">
         <v>316</v>
       </c>
       <c r="B294" s="2">
@@ -12442,7 +12397,6 @@
         <v>33</v>
       </c>
       <c r="H294" s="3"/>
-      <c r="I294" s="7"/>
       <c r="J294" s="3"/>
       <c r="K294" s="6"/>
       <c r="L294" s="3"/>
@@ -12452,13 +12406,87 @@
         <v>543</v>
       </c>
       <c r="P294" s="3"/>
-      <c r="Q294" s="7"/>
-      <c r="R294" s="7"/>
-      <c r="S294" s="7"/>
-      <c r="T294" s="7"/>
-      <c r="U294" s="7"/>
-    </row>
-    <row r="295" spans="1:21" ht="15"/>
+    </row>
+    <row r="295" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A295" s="7">
+        <v>317</v>
+      </c>
+      <c r="B295" s="2">
+        <v>46268.562291666698</v>
+      </c>
+      <c r="C295" s="2">
+        <v>46268.571041666699</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F295" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G295" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H295" s="3"/>
+      <c r="I295" s="7"/>
+      <c r="J295" s="3"/>
+      <c r="K295" s="6"/>
+      <c r="L295" s="3"/>
+      <c r="M295" s="3"/>
+      <c r="N295" s="3"/>
+      <c r="O295" s="3"/>
+      <c r="P295" s="3"/>
+      <c r="Q295" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R295" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="S295" s="7"/>
+      <c r="T295" s="7"/>
+      <c r="U295" s="7"/>
+    </row>
+    <row r="296" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A296" s="7">
+        <v>318</v>
+      </c>
+      <c r="B296" s="2">
+        <v>46268.571238425902</v>
+      </c>
+      <c r="C296" s="2">
+        <v>46268.572361111103</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E296" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H296" s="3"/>
+      <c r="I296" s="7"/>
+      <c r="J296" s="3"/>
+      <c r="K296" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="L296" s="3"/>
+      <c r="M296" s="3"/>
+      <c r="N296" s="3"/>
+      <c r="O296" s="3"/>
+      <c r="P296" s="3"/>
+      <c r="Q296" s="7"/>
+      <c r="R296" s="7"/>
+      <c r="S296" s="7"/>
+      <c r="T296" s="7"/>
+      <c r="U296" s="7"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="363" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6D897CA-49CB-4279-B552-50B568410E13}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C01C6D-BCA7-435A-BC1D-1BC14B56AEF3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="553">
   <si>
     <t>Id</t>
   </si>
@@ -1674,13 +1674,34 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Echegaray.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38176@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks DT Periferico Satelite</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260903-WA0017_Starbucks%20DT%20Perifer.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG_3923_Starbucks%20CEMTRAM%204.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17884648749153020018020140049704_Starbucks%20DT%20Perifer.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/17884649102538417106894466458342_Starbucks%20DT%20Perifer.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17884649537715577155901761431956_Starbucks%20DT%20Perifer.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1808,8 +1829,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U296" totalsRowShown="0">
-  <autoFilter ref="A1:U296" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U301" totalsRowShown="0">
+  <autoFilter ref="A1:U301" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1962,7 +1983,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="318" latestEventMarker="553">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="323" latestEventMarker="558">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2287,23 +2308,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U296"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:U302"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="7.7265625" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
     <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.1796875" customWidth="1"/>
-    <col min="5" max="5" width="35.1796875" customWidth="1"/>
-    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="19" customWidth="1"/>
-    <col min="19" max="19" width="42.1796875" customWidth="1"/>
+    <col min="19" max="19" width="42.140625" customWidth="1"/>
     <col min="20" max="21" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2368,7 +2389,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>13</v>
       </c>
@@ -2394,7 +2415,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>17</v>
       </c>
@@ -2427,7 +2448,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2460,7 +2481,7 @@
       </c>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21">
       <c r="A5">
         <v>20</v>
       </c>
@@ -2493,7 +2514,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>21</v>
       </c>
@@ -2526,7 +2547,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>22</v>
       </c>
@@ -2559,7 +2580,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>23</v>
       </c>
@@ -2593,7 +2614,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>24</v>
       </c>
@@ -2627,7 +2648,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>25</v>
       </c>
@@ -2661,7 +2682,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21">
       <c r="A11">
         <v>26</v>
       </c>
@@ -2694,7 +2715,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21">
       <c r="A12">
         <v>27</v>
       </c>
@@ -2730,7 +2751,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21">
       <c r="A13">
         <v>28</v>
       </c>
@@ -2763,7 +2784,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21">
       <c r="A14">
         <v>29</v>
       </c>
@@ -2797,7 +2818,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21">
       <c r="A15">
         <v>30</v>
       </c>
@@ -2830,7 +2851,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21">
       <c r="A16">
         <v>31</v>
       </c>
@@ -2863,7 +2884,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19">
       <c r="A17">
         <v>32</v>
       </c>
@@ -2897,7 +2918,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19">
       <c r="A18">
         <v>33</v>
       </c>
@@ -2930,7 +2951,7 @@
       </c>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>34</v>
       </c>
@@ -2963,7 +2984,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>35</v>
       </c>
@@ -2996,7 +3017,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>36</v>
       </c>
@@ -3029,7 +3050,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>37</v>
       </c>
@@ -3063,7 +3084,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>38</v>
       </c>
@@ -3097,7 +3118,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>39</v>
       </c>
@@ -3131,7 +3152,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>40</v>
       </c>
@@ -3165,7 +3186,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>41</v>
       </c>
@@ -3198,7 +3219,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>42</v>
       </c>
@@ -3232,7 +3253,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>43</v>
       </c>
@@ -3266,7 +3287,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19">
       <c r="A29">
         <v>44</v>
       </c>
@@ -3300,7 +3321,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19">
       <c r="A30">
         <v>45</v>
       </c>
@@ -3334,7 +3355,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19">
       <c r="A31">
         <v>46</v>
       </c>
@@ -3368,7 +3389,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19">
       <c r="A32">
         <v>47</v>
       </c>
@@ -3402,7 +3423,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19">
       <c r="A33">
         <v>48</v>
       </c>
@@ -3435,7 +3456,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>49</v>
       </c>
@@ -3469,7 +3490,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>50</v>
       </c>
@@ -3503,7 +3524,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>51</v>
       </c>
@@ -3537,7 +3558,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>52</v>
       </c>
@@ -3570,7 +3591,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>54</v>
       </c>
@@ -3603,7 +3624,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>55</v>
       </c>
@@ -3636,7 +3657,7 @@
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>56</v>
       </c>
@@ -3670,7 +3691,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>57</v>
       </c>
@@ -3704,7 +3725,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>58</v>
       </c>
@@ -3738,7 +3759,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>59</v>
       </c>
@@ -3772,7 +3793,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19">
       <c r="A44">
         <v>60</v>
       </c>
@@ -3806,7 +3827,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19">
       <c r="A45">
         <v>61</v>
       </c>
@@ -3840,7 +3861,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19">
       <c r="A46">
         <v>62</v>
       </c>
@@ -3874,7 +3895,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19">
       <c r="A47">
         <v>63</v>
       </c>
@@ -3908,7 +3929,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19">
       <c r="A48">
         <v>65</v>
       </c>
@@ -3942,7 +3963,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>66</v>
       </c>
@@ -3976,7 +3997,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>67</v>
       </c>
@@ -4009,7 +4030,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>68</v>
       </c>
@@ -4042,7 +4063,7 @@
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>69</v>
       </c>
@@ -4076,7 +4097,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>70</v>
       </c>
@@ -4110,7 +4131,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>71</v>
       </c>
@@ -4144,7 +4165,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>72</v>
       </c>
@@ -4178,7 +4199,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>73</v>
       </c>
@@ -4212,7 +4233,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>74</v>
       </c>
@@ -4246,7 +4267,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>75</v>
       </c>
@@ -4280,7 +4301,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19">
       <c r="A59">
         <v>76</v>
       </c>
@@ -4314,7 +4335,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19">
       <c r="A60">
         <v>77</v>
       </c>
@@ -4347,7 +4368,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19">
       <c r="A61">
         <v>78</v>
       </c>
@@ -4381,7 +4402,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19">
       <c r="A62">
         <v>79</v>
       </c>
@@ -4415,7 +4436,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19">
       <c r="A63">
         <v>80</v>
       </c>
@@ -4449,7 +4470,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>81</v>
       </c>
@@ -4483,7 +4504,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>84</v>
       </c>
@@ -4517,7 +4538,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>85</v>
       </c>
@@ -4550,7 +4571,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>86</v>
       </c>
@@ -4583,7 +4604,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>88</v>
       </c>
@@ -4616,7 +4637,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>89</v>
       </c>
@@ -4649,7 +4670,7 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>90</v>
       </c>
@@ -4683,7 +4704,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>91</v>
       </c>
@@ -4717,7 +4738,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>92</v>
       </c>
@@ -4753,7 +4774,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>93</v>
       </c>
@@ -4786,7 +4807,7 @@
       </c>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:19">
       <c r="A74">
         <v>94</v>
       </c>
@@ -4819,7 +4840,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19">
       <c r="A75">
         <v>95</v>
       </c>
@@ -4852,7 +4873,7 @@
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19">
       <c r="A76">
         <v>96</v>
       </c>
@@ -4886,7 +4907,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19">
       <c r="A77">
         <v>97</v>
       </c>
@@ -4919,7 +4940,7 @@
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19">
       <c r="A78">
         <v>98</v>
       </c>
@@ -4953,7 +4974,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>99</v>
       </c>
@@ -4986,7 +5007,7 @@
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>100</v>
       </c>
@@ -5020,7 +5041,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>102</v>
       </c>
@@ -5056,7 +5077,7 @@
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>103</v>
       </c>
@@ -5089,7 +5110,7 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>104</v>
       </c>
@@ -5123,7 +5144,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>105</v>
       </c>
@@ -5159,7 +5180,7 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>106</v>
       </c>
@@ -5193,7 +5214,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>107</v>
       </c>
@@ -5226,7 +5247,7 @@
       </c>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>108</v>
       </c>
@@ -5260,7 +5281,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>109</v>
       </c>
@@ -5294,7 +5315,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:19">
       <c r="A89">
         <v>110</v>
       </c>
@@ -5327,7 +5348,7 @@
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:19">
       <c r="A90">
         <v>111</v>
       </c>
@@ -5361,7 +5382,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:19">
       <c r="A91">
         <v>112</v>
       </c>
@@ -5394,7 +5415,7 @@
       </c>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:19">
       <c r="A92">
         <v>113</v>
       </c>
@@ -5428,7 +5449,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:19">
       <c r="A93">
         <v>114</v>
       </c>
@@ -5462,7 +5483,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:19">
       <c r="A94">
         <v>115</v>
       </c>
@@ -5495,7 +5516,7 @@
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:19">
       <c r="A95">
         <v>116</v>
       </c>
@@ -5528,7 +5549,7 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:19">
       <c r="A96">
         <v>117</v>
       </c>
@@ -5561,7 +5582,7 @@
       </c>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:21">
       <c r="A97">
         <v>118</v>
       </c>
@@ -5594,7 +5615,7 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:21">
       <c r="A98">
         <v>119</v>
       </c>
@@ -5627,7 +5648,7 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:21">
       <c r="A99">
         <v>120</v>
       </c>
@@ -5660,7 +5681,7 @@
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:21">
       <c r="A100">
         <v>121</v>
       </c>
@@ -5694,7 +5715,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:21">
       <c r="A101">
         <v>122</v>
       </c>
@@ -5727,7 +5748,7 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:21">
       <c r="A102">
         <v>123</v>
       </c>
@@ -5761,7 +5782,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:21">
       <c r="A103">
         <v>124</v>
       </c>
@@ -5795,7 +5816,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:21">
       <c r="A104">
         <v>125</v>
       </c>
@@ -5829,7 +5850,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:21">
       <c r="A105">
         <v>126</v>
       </c>
@@ -5863,7 +5884,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:21">
       <c r="A106">
         <v>127</v>
       </c>
@@ -5896,7 +5917,7 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:21">
       <c r="A107">
         <v>128</v>
       </c>
@@ -5932,7 +5953,7 @@
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:21">
       <c r="A108">
         <v>129</v>
       </c>
@@ -5966,7 +5987,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:21">
       <c r="A109">
         <v>130</v>
       </c>
@@ -6002,7 +6023,7 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:21">
       <c r="A110">
         <v>131</v>
       </c>
@@ -6035,7 +6056,7 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:21">
       <c r="A111">
         <v>132</v>
       </c>
@@ -6069,7 +6090,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:21">
       <c r="A112">
         <v>133</v>
       </c>
@@ -6103,7 +6124,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:19">
       <c r="A113">
         <v>134</v>
       </c>
@@ -6137,7 +6158,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:19">
       <c r="A114">
         <v>135</v>
       </c>
@@ -6171,7 +6192,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:19">
       <c r="A115">
         <v>136</v>
       </c>
@@ -6205,7 +6226,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:19">
       <c r="A116">
         <v>137</v>
       </c>
@@ -6239,7 +6260,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:19">
       <c r="A117">
         <v>138</v>
       </c>
@@ -6273,7 +6294,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:19">
       <c r="A118">
         <v>139</v>
       </c>
@@ -6307,7 +6328,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:19">
       <c r="A119">
         <v>140</v>
       </c>
@@ -6341,7 +6362,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:19">
       <c r="A120">
         <v>141</v>
       </c>
@@ -6374,7 +6395,7 @@
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:19">
       <c r="A121">
         <v>142</v>
       </c>
@@ -6408,7 +6429,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:19">
       <c r="A122">
         <v>143</v>
       </c>
@@ -6441,7 +6462,7 @@
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:19">
       <c r="A123">
         <v>144</v>
       </c>
@@ -6475,7 +6496,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:19">
       <c r="A124">
         <v>145</v>
       </c>
@@ -6508,7 +6529,7 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:19">
       <c r="A125">
         <v>146</v>
       </c>
@@ -6542,7 +6563,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:19">
       <c r="A126">
         <v>147</v>
       </c>
@@ -6575,7 +6596,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:19">
       <c r="A127">
         <v>148</v>
       </c>
@@ -6612,7 +6633,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:19">
       <c r="A128">
         <v>149</v>
       </c>
@@ -6646,7 +6667,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:19">
       <c r="A129">
         <v>150</v>
       </c>
@@ -6680,7 +6701,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:19">
       <c r="A130">
         <v>151</v>
       </c>
@@ -6714,7 +6735,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:19">
       <c r="A131">
         <v>152</v>
       </c>
@@ -6748,7 +6769,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:19">
       <c r="A132">
         <v>153</v>
       </c>
@@ -6781,7 +6802,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:19">
       <c r="A133">
         <v>154</v>
       </c>
@@ -6815,7 +6836,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:19">
       <c r="A134">
         <v>155</v>
       </c>
@@ -6849,7 +6870,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:19">
       <c r="A135">
         <v>156</v>
       </c>
@@ -6886,7 +6907,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:19">
       <c r="A136">
         <v>157</v>
       </c>
@@ -6919,7 +6940,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:19">
       <c r="A137">
         <v>158</v>
       </c>
@@ -6953,7 +6974,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:19">
       <c r="A138">
         <v>159</v>
       </c>
@@ -6990,7 +7011,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:19">
       <c r="A139">
         <v>160</v>
       </c>
@@ -7026,7 +7047,7 @@
       <c r="O139" s="3"/>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:19">
       <c r="A140">
         <v>161</v>
       </c>
@@ -7059,7 +7080,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:19">
       <c r="A141">
         <v>162</v>
       </c>
@@ -7095,7 +7116,7 @@
       <c r="O141" s="3"/>
       <c r="P141" s="3"/>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:19">
       <c r="A142">
         <v>163</v>
       </c>
@@ -7131,7 +7152,7 @@
       <c r="O142" s="3"/>
       <c r="P142" s="3"/>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:19">
       <c r="A143">
         <v>164</v>
       </c>
@@ -7164,7 +7185,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:19">
       <c r="A144">
         <v>165</v>
       </c>
@@ -7201,7 +7222,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16">
       <c r="A145">
         <v>166</v>
       </c>
@@ -7237,7 +7258,7 @@
       <c r="O145" s="3"/>
       <c r="P145" s="3"/>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16">
       <c r="A146">
         <v>167</v>
       </c>
@@ -7273,7 +7294,7 @@
       <c r="O146" s="3"/>
       <c r="P146" s="3"/>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16">
       <c r="A147">
         <v>168</v>
       </c>
@@ -7309,7 +7330,7 @@
       <c r="O147" s="3"/>
       <c r="P147" s="3"/>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16">
       <c r="A148">
         <v>169</v>
       </c>
@@ -7345,7 +7366,7 @@
       <c r="O148" s="3"/>
       <c r="P148" s="3"/>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16">
       <c r="A149">
         <v>170</v>
       </c>
@@ -7381,7 +7402,7 @@
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16">
       <c r="A150">
         <v>171</v>
       </c>
@@ -7417,7 +7438,7 @@
       <c r="O150" s="3"/>
       <c r="P150" s="3"/>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16">
       <c r="A151">
         <v>172</v>
       </c>
@@ -7453,7 +7474,7 @@
       <c r="O151" s="3"/>
       <c r="P151" s="3"/>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16">
       <c r="A152">
         <v>173</v>
       </c>
@@ -7489,7 +7510,7 @@
       <c r="O152" s="3"/>
       <c r="P152" s="3"/>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16">
       <c r="A153">
         <v>174</v>
       </c>
@@ -7525,7 +7546,7 @@
       <c r="O153" s="3"/>
       <c r="P153" s="3"/>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16">
       <c r="A154">
         <v>175</v>
       </c>
@@ -7561,7 +7582,7 @@
       <c r="O154" s="3"/>
       <c r="P154" s="3"/>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16">
       <c r="A155">
         <v>176</v>
       </c>
@@ -7597,7 +7618,7 @@
       <c r="O155" s="3"/>
       <c r="P155" s="3"/>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16">
       <c r="A156">
         <v>177</v>
       </c>
@@ -7633,7 +7654,7 @@
       <c r="O156" s="3"/>
       <c r="P156" s="3"/>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16">
       <c r="A157">
         <v>178</v>
       </c>
@@ -7669,7 +7690,7 @@
       <c r="O157" s="3"/>
       <c r="P157" s="3"/>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16">
       <c r="A158">
         <v>179</v>
       </c>
@@ -7705,7 +7726,7 @@
       <c r="O158" s="3"/>
       <c r="P158" s="3"/>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16">
       <c r="A159">
         <v>180</v>
       </c>
@@ -7741,7 +7762,7 @@
       <c r="O159" s="3"/>
       <c r="P159" s="3"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16">
       <c r="A160">
         <v>181</v>
       </c>
@@ -7777,7 +7798,7 @@
       <c r="O160" s="3"/>
       <c r="P160" s="3"/>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16">
       <c r="A161">
         <v>182</v>
       </c>
@@ -7813,7 +7834,7 @@
       <c r="O161" s="3"/>
       <c r="P161" s="3"/>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16">
       <c r="A162">
         <v>183</v>
       </c>
@@ -7849,7 +7870,7 @@
       <c r="O162" s="3"/>
       <c r="P162" s="3"/>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16">
       <c r="A163">
         <v>184</v>
       </c>
@@ -7883,7 +7904,7 @@
       <c r="O163" s="3"/>
       <c r="P163" s="3"/>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16">
       <c r="A164">
         <v>185</v>
       </c>
@@ -7919,7 +7940,7 @@
       <c r="O164" s="3"/>
       <c r="P164" s="3"/>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16">
       <c r="A165">
         <v>186</v>
       </c>
@@ -7955,7 +7976,7 @@
       <c r="O165" s="3"/>
       <c r="P165" s="3"/>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:16">
       <c r="A166">
         <v>187</v>
       </c>
@@ -7991,7 +8012,7 @@
       <c r="O166" s="3"/>
       <c r="P166" s="3"/>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16">
       <c r="A167">
         <v>188</v>
       </c>
@@ -8027,7 +8048,7 @@
       <c r="O167" s="3"/>
       <c r="P167" s="3"/>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16">
       <c r="A168">
         <v>189</v>
       </c>
@@ -8063,7 +8084,7 @@
       <c r="O168" s="3"/>
       <c r="P168" s="3"/>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16">
       <c r="A169">
         <v>190</v>
       </c>
@@ -8099,7 +8120,7 @@
       <c r="O169" s="3"/>
       <c r="P169" s="3"/>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16">
       <c r="A170">
         <v>191</v>
       </c>
@@ -8135,7 +8156,7 @@
       <c r="O170" s="3"/>
       <c r="P170" s="3"/>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16">
       <c r="A171">
         <v>192</v>
       </c>
@@ -8171,7 +8192,7 @@
       <c r="O171" s="3"/>
       <c r="P171" s="3"/>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16">
       <c r="A172">
         <v>193</v>
       </c>
@@ -8207,7 +8228,7 @@
       <c r="O172" s="3"/>
       <c r="P172" s="3"/>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16">
       <c r="A173">
         <v>194</v>
       </c>
@@ -8243,7 +8264,7 @@
       <c r="O173" s="3"/>
       <c r="P173" s="3"/>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16">
       <c r="A174">
         <v>195</v>
       </c>
@@ -8279,7 +8300,7 @@
       <c r="O174" s="3"/>
       <c r="P174" s="3"/>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16">
       <c r="A175">
         <v>196</v>
       </c>
@@ -8315,7 +8336,7 @@
       <c r="O175" s="3"/>
       <c r="P175" s="3"/>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16">
       <c r="A176">
         <v>197</v>
       </c>
@@ -8351,7 +8372,7 @@
       <c r="O176" s="3"/>
       <c r="P176" s="3"/>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16">
       <c r="A177">
         <v>198</v>
       </c>
@@ -8387,7 +8408,7 @@
       <c r="O177" s="3"/>
       <c r="P177" s="3"/>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16">
       <c r="A178">
         <v>199</v>
       </c>
@@ -8423,7 +8444,7 @@
       <c r="O178" s="3"/>
       <c r="P178" s="3"/>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16">
       <c r="A179">
         <v>200</v>
       </c>
@@ -8459,7 +8480,7 @@
       <c r="O179" s="3"/>
       <c r="P179" s="3"/>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:16">
       <c r="A180">
         <v>201</v>
       </c>
@@ -8495,7 +8516,7 @@
       <c r="O180" s="3"/>
       <c r="P180" s="3"/>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:16">
       <c r="A181">
         <v>202</v>
       </c>
@@ -8531,7 +8552,7 @@
       <c r="O181" s="3"/>
       <c r="P181" s="3"/>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16">
       <c r="A182">
         <v>203</v>
       </c>
@@ -8567,7 +8588,7 @@
       <c r="O182" s="3"/>
       <c r="P182" s="3"/>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16">
       <c r="A183">
         <v>204</v>
       </c>
@@ -8603,7 +8624,7 @@
       <c r="O183" s="3"/>
       <c r="P183" s="3"/>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16">
       <c r="A184">
         <v>205</v>
       </c>
@@ -8639,7 +8660,7 @@
       <c r="O184" s="3"/>
       <c r="P184" s="3"/>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16">
       <c r="A185">
         <v>206</v>
       </c>
@@ -8675,7 +8696,7 @@
       <c r="O185" s="3"/>
       <c r="P185" s="3"/>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16">
       <c r="A186">
         <v>207</v>
       </c>
@@ -8708,7 +8729,7 @@
       <c r="O186" s="3"/>
       <c r="P186" s="3"/>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16">
       <c r="A187">
         <v>208</v>
       </c>
@@ -8744,7 +8765,7 @@
       <c r="O187" s="3"/>
       <c r="P187" s="3"/>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16">
       <c r="A188">
         <v>209</v>
       </c>
@@ -8778,7 +8799,7 @@
       <c r="O188" s="3"/>
       <c r="P188" s="3"/>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16">
       <c r="A189">
         <v>210</v>
       </c>
@@ -8814,7 +8835,7 @@
       <c r="O189" s="3"/>
       <c r="P189" s="3"/>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16">
       <c r="A190">
         <v>211</v>
       </c>
@@ -8850,7 +8871,7 @@
       <c r="O190" s="3"/>
       <c r="P190" s="3"/>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16">
       <c r="A191">
         <v>212</v>
       </c>
@@ -8886,7 +8907,7 @@
       <c r="O191" s="3"/>
       <c r="P191" s="3"/>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16">
       <c r="A192">
         <v>213</v>
       </c>
@@ -8919,7 +8940,7 @@
       <c r="O192" s="3"/>
       <c r="P192" s="3"/>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:20">
       <c r="A193">
         <v>214</v>
       </c>
@@ -8953,7 +8974,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:20">
       <c r="A194">
         <v>215</v>
       </c>
@@ -8989,7 +9010,7 @@
       <c r="O194" s="3"/>
       <c r="P194" s="3"/>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:20">
       <c r="A195">
         <v>216</v>
       </c>
@@ -9025,7 +9046,7 @@
       <c r="O195" s="3"/>
       <c r="P195" s="3"/>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:20">
       <c r="A196">
         <v>217</v>
       </c>
@@ -9061,7 +9082,7 @@
       <c r="O196" s="3"/>
       <c r="P196" s="3"/>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:20">
       <c r="A197">
         <v>218</v>
       </c>
@@ -9097,7 +9118,7 @@
       <c r="O197" s="3"/>
       <c r="P197" s="3"/>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:20">
       <c r="A198">
         <v>219</v>
       </c>
@@ -9130,7 +9151,7 @@
       <c r="O198" s="3"/>
       <c r="P198" s="3"/>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:20">
       <c r="A199">
         <v>220</v>
       </c>
@@ -9164,7 +9185,7 @@
       <c r="O199" s="3"/>
       <c r="P199" s="3"/>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:20">
       <c r="A200">
         <v>221</v>
       </c>
@@ -9201,7 +9222,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:20">
       <c r="A201">
         <v>222</v>
       </c>
@@ -9237,7 +9258,7 @@
       <c r="O201" s="3"/>
       <c r="P201" s="3"/>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:20">
       <c r="A202">
         <v>223</v>
       </c>
@@ -9270,7 +9291,7 @@
       <c r="O202" s="3"/>
       <c r="P202" s="3"/>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:20">
       <c r="A203">
         <v>224</v>
       </c>
@@ -9306,7 +9327,7 @@
       <c r="O203" s="3"/>
       <c r="P203" s="3"/>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:20">
       <c r="A204">
         <v>225</v>
       </c>
@@ -9342,7 +9363,7 @@
       <c r="O204" s="3"/>
       <c r="P204" s="3"/>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:20">
       <c r="A205">
         <v>226</v>
       </c>
@@ -9375,7 +9396,7 @@
       <c r="O205" s="3"/>
       <c r="P205" s="3"/>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:20">
       <c r="A206">
         <v>227</v>
       </c>
@@ -9408,7 +9429,7 @@
       <c r="O206" s="3"/>
       <c r="P206" s="3"/>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:20">
       <c r="A207">
         <v>228</v>
       </c>
@@ -9441,7 +9462,7 @@
       <c r="O207" s="3"/>
       <c r="P207" s="3"/>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:20">
       <c r="A208">
         <v>229</v>
       </c>
@@ -9478,7 +9499,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:19">
       <c r="A209">
         <v>230</v>
       </c>
@@ -9512,7 +9533,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:19">
       <c r="A210">
         <v>231</v>
       </c>
@@ -9549,7 +9570,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:19">
       <c r="A211">
         <v>232</v>
       </c>
@@ -9586,7 +9607,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:19">
       <c r="A212">
         <v>233</v>
       </c>
@@ -9623,7 +9644,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:19">
       <c r="A213">
         <v>234</v>
       </c>
@@ -9657,7 +9678,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:19">
       <c r="A214">
         <v>235</v>
       </c>
@@ -9694,7 +9715,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:19">
       <c r="A215">
         <v>236</v>
       </c>
@@ -9727,7 +9748,7 @@
       <c r="O215" s="3"/>
       <c r="P215" s="3"/>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:19">
       <c r="A216">
         <v>237</v>
       </c>
@@ -9760,7 +9781,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:19">
       <c r="A217">
         <v>238</v>
       </c>
@@ -9793,7 +9814,7 @@
       <c r="O217" s="3"/>
       <c r="P217" s="3"/>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:19">
       <c r="A218">
         <v>239</v>
       </c>
@@ -9826,7 +9847,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:19">
       <c r="A219">
         <v>240</v>
       </c>
@@ -9862,7 +9883,7 @@
       <c r="O219" s="3"/>
       <c r="P219" s="3"/>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:19" ht="15">
       <c r="A220">
         <v>241</v>
       </c>
@@ -9895,7 +9916,7 @@
       <c r="O220" s="3"/>
       <c r="P220" s="3"/>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:19" ht="15">
       <c r="A221">
         <v>242</v>
       </c>
@@ -9928,7 +9949,7 @@
       <c r="O221" s="3"/>
       <c r="P221" s="3"/>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:19" ht="15">
       <c r="A222">
         <v>243</v>
       </c>
@@ -9961,7 +9982,7 @@
       </c>
       <c r="P222" s="3"/>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:19" ht="15">
       <c r="A223">
         <v>244</v>
       </c>
@@ -9994,7 +10015,7 @@
       <c r="O223" s="3"/>
       <c r="P223" s="3"/>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:19" ht="15">
       <c r="A224">
         <v>245</v>
       </c>
@@ -10027,7 +10048,7 @@
       </c>
       <c r="P224" s="3"/>
     </row>
-    <row r="225" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:21" ht="15">
       <c r="A225">
         <v>246</v>
       </c>
@@ -10060,7 +10081,7 @@
       <c r="O225" s="3"/>
       <c r="P225" s="3"/>
     </row>
-    <row r="226" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:21" ht="15">
       <c r="A226">
         <v>247</v>
       </c>
@@ -10093,7 +10114,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:21" ht="15">
       <c r="A227">
         <v>248</v>
       </c>
@@ -10126,7 +10147,7 @@
       <c r="O227" s="3"/>
       <c r="P227" s="3"/>
     </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:21" ht="15">
       <c r="A228">
         <v>249</v>
       </c>
@@ -10159,7 +10180,7 @@
       <c r="O228" s="3"/>
       <c r="P228" s="3"/>
     </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:21" ht="15">
       <c r="A229">
         <v>250</v>
       </c>
@@ -10192,7 +10213,7 @@
       <c r="O229" s="3"/>
       <c r="P229" s="3"/>
     </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:21" ht="15">
       <c r="A230">
         <v>251</v>
       </c>
@@ -10225,7 +10246,7 @@
       <c r="O230" s="3"/>
       <c r="P230" s="3"/>
     </row>
-    <row r="231" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:21" ht="15">
       <c r="A231">
         <v>252</v>
       </c>
@@ -10261,7 +10282,7 @@
       <c r="O231" s="3"/>
       <c r="P231" s="3"/>
     </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:21" ht="15">
       <c r="A232">
         <v>253</v>
       </c>
@@ -10294,7 +10315,7 @@
       <c r="O232" s="3"/>
       <c r="P232" s="3"/>
     </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:21" ht="15">
       <c r="A233">
         <v>254</v>
       </c>
@@ -10331,7 +10352,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:21" ht="15">
       <c r="A234">
         <v>255</v>
       </c>
@@ -10367,7 +10388,7 @@
       <c r="O234" s="3"/>
       <c r="P234" s="3"/>
     </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:21" ht="15">
       <c r="A235">
         <v>256</v>
       </c>
@@ -10403,7 +10424,7 @@
       <c r="O235" s="3"/>
       <c r="P235" s="3"/>
     </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:21" ht="15">
       <c r="A236">
         <v>257</v>
       </c>
@@ -10437,7 +10458,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:21" ht="15">
       <c r="A237">
         <v>258</v>
       </c>
@@ -10471,7 +10492,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:21" ht="15">
       <c r="A238">
         <v>259</v>
       </c>
@@ -10504,7 +10525,7 @@
       <c r="O238" s="3"/>
       <c r="P238" s="3"/>
     </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:21" ht="15">
       <c r="A239">
         <v>260</v>
       </c>
@@ -10537,7 +10558,7 @@
       <c r="O239" s="3"/>
       <c r="P239" s="3"/>
     </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:21" ht="15">
       <c r="A240">
         <v>261</v>
       </c>
@@ -10570,7 +10591,7 @@
       <c r="O240" s="3"/>
       <c r="P240" s="3"/>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:20" ht="15">
       <c r="A241">
         <v>262</v>
       </c>
@@ -10603,7 +10624,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:20" ht="15">
       <c r="A242">
         <v>263</v>
       </c>
@@ -10639,7 +10660,7 @@
       <c r="O242" s="3"/>
       <c r="P242" s="3"/>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:20" ht="15">
       <c r="A243">
         <v>264</v>
       </c>
@@ -10672,7 +10693,7 @@
       </c>
       <c r="P243" s="3"/>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:20" ht="15">
       <c r="A244">
         <v>265</v>
       </c>
@@ -10705,7 +10726,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:20" ht="15">
       <c r="A245">
         <v>266</v>
       </c>
@@ -10739,7 +10760,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:20" ht="15">
       <c r="A246">
         <v>267</v>
       </c>
@@ -10772,7 +10793,7 @@
       <c r="O246" s="3"/>
       <c r="P246" s="3"/>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:20" ht="15">
       <c r="A247">
         <v>268</v>
       </c>
@@ -10805,7 +10826,7 @@
       <c r="O247" s="3"/>
       <c r="P247" s="3"/>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:20" ht="15">
       <c r="A248">
         <v>269</v>
       </c>
@@ -10841,7 +10862,7 @@
       <c r="O248" s="3"/>
       <c r="P248" s="3"/>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:20" ht="15">
       <c r="A249">
         <v>270</v>
       </c>
@@ -10874,7 +10895,7 @@
       </c>
       <c r="P249" s="3"/>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:20" ht="15">
       <c r="A250">
         <v>271</v>
       </c>
@@ -10908,7 +10929,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:20" ht="15">
       <c r="A251">
         <v>272</v>
       </c>
@@ -10941,7 +10962,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:20" ht="15">
       <c r="A252">
         <v>273</v>
       </c>
@@ -10974,7 +10995,7 @@
       <c r="O252" s="3"/>
       <c r="P252" s="3"/>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:20" ht="15">
       <c r="A253">
         <v>274</v>
       </c>
@@ -11007,7 +11028,7 @@
       <c r="O253" s="3"/>
       <c r="P253" s="3"/>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:20" ht="15">
       <c r="A254">
         <v>275</v>
       </c>
@@ -11041,7 +11062,7 @@
       <c r="O254" s="3"/>
       <c r="P254" s="3"/>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:20" ht="15">
       <c r="A255">
         <v>276</v>
       </c>
@@ -11077,7 +11098,7 @@
       <c r="O255" s="3"/>
       <c r="P255" s="3"/>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:20" ht="15">
       <c r="A256">
         <v>277</v>
       </c>
@@ -11110,7 +11131,7 @@
       <c r="O256" s="3"/>
       <c r="P256" s="3"/>
     </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:21" ht="15">
       <c r="A257">
         <v>278</v>
       </c>
@@ -11143,7 +11164,7 @@
       <c r="O257" s="3"/>
       <c r="P257" s="3"/>
     </row>
-    <row r="258" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:21" ht="15">
       <c r="A258">
         <v>279</v>
       </c>
@@ -11180,7 +11201,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:21" ht="15">
       <c r="A259">
         <v>280</v>
       </c>
@@ -11213,7 +11234,7 @@
       <c r="O259" s="3"/>
       <c r="P259" s="3"/>
     </row>
-    <row r="260" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:21" ht="15">
       <c r="A260">
         <v>281</v>
       </c>
@@ -11249,7 +11270,7 @@
       <c r="O260" s="3"/>
       <c r="P260" s="3"/>
     </row>
-    <row r="261" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:21" ht="15">
       <c r="A261">
         <v>282</v>
       </c>
@@ -11282,7 +11303,7 @@
       <c r="O261" s="3"/>
       <c r="P261" s="3"/>
     </row>
-    <row r="262" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:21" ht="15">
       <c r="A262">
         <v>283</v>
       </c>
@@ -11318,7 +11339,7 @@
       <c r="O262" s="3"/>
       <c r="P262" s="3"/>
     </row>
-    <row r="263" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:21" ht="15">
       <c r="A263">
         <v>284</v>
       </c>
@@ -11351,7 +11372,7 @@
       <c r="O263" s="3"/>
       <c r="P263" s="3"/>
     </row>
-    <row r="264" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:21" ht="15">
       <c r="A264">
         <v>285</v>
       </c>
@@ -11387,7 +11408,7 @@
       <c r="O264" s="3"/>
       <c r="P264" s="3"/>
     </row>
-    <row r="265" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:21" ht="15">
       <c r="A265">
         <v>286</v>
       </c>
@@ -11420,7 +11441,7 @@
       <c r="O265" s="3"/>
       <c r="P265" s="3"/>
     </row>
-    <row r="266" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:21" ht="15">
       <c r="A266">
         <v>287</v>
       </c>
@@ -11453,7 +11474,7 @@
       <c r="O266" s="3"/>
       <c r="P266" s="3"/>
     </row>
-    <row r="267" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:21" ht="15">
       <c r="A267">
         <v>288</v>
       </c>
@@ -11486,7 +11507,7 @@
       </c>
       <c r="P267" s="3"/>
     </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:21" ht="15">
       <c r="A268">
         <v>289</v>
       </c>
@@ -11523,7 +11544,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="269" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:21" ht="15">
       <c r="A269">
         <v>290</v>
       </c>
@@ -11559,7 +11580,7 @@
       <c r="O269" s="3"/>
       <c r="P269" s="3"/>
     </row>
-    <row r="270" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:21" ht="15">
       <c r="A270">
         <v>291</v>
       </c>
@@ -11593,7 +11614,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="271" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:21" ht="15">
       <c r="A271">
         <v>292</v>
       </c>
@@ -11626,7 +11647,7 @@
       </c>
       <c r="P271" s="3"/>
     </row>
-    <row r="272" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:21" ht="15">
       <c r="A272">
         <v>293</v>
       </c>
@@ -11660,7 +11681,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="273" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:21" ht="15">
       <c r="A273">
         <v>294</v>
       </c>
@@ -11697,7 +11718,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="274" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:21" ht="15">
       <c r="A274">
         <v>295</v>
       </c>
@@ -11731,7 +11752,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="275" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:21" ht="15">
       <c r="A275">
         <v>296</v>
       </c>
@@ -11768,7 +11789,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="276" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:21" ht="15">
       <c r="A276">
         <v>297</v>
       </c>
@@ -11801,7 +11822,7 @@
       <c r="O276" s="3"/>
       <c r="P276" s="3"/>
     </row>
-    <row r="277" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:21" ht="15">
       <c r="A277">
         <v>298</v>
       </c>
@@ -11834,7 +11855,7 @@
       <c r="O277" s="3"/>
       <c r="P277" s="3"/>
     </row>
-    <row r="278" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:21" ht="15">
       <c r="A278">
         <v>299</v>
       </c>
@@ -11867,7 +11888,7 @@
       </c>
       <c r="P278" s="3"/>
     </row>
-    <row r="279" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:21" ht="15">
       <c r="A279">
         <v>300</v>
       </c>
@@ -11900,7 +11921,7 @@
       <c r="O279" s="3"/>
       <c r="P279" s="3"/>
     </row>
-    <row r="280" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:21" ht="15">
       <c r="A280">
         <v>301</v>
       </c>
@@ -11933,7 +11954,7 @@
       <c r="O280" s="3"/>
       <c r="P280" s="3"/>
     </row>
-    <row r="281" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:21" ht="15">
       <c r="A281">
         <v>302</v>
       </c>
@@ -11966,7 +11987,7 @@
       <c r="O281" s="3"/>
       <c r="P281" s="3"/>
     </row>
-    <row r="282" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:21" ht="15">
       <c r="A282">
         <v>303</v>
       </c>
@@ -12002,7 +12023,7 @@
       <c r="O282" s="3"/>
       <c r="P282" s="3"/>
     </row>
-    <row r="283" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:21" ht="15">
       <c r="A283">
         <v>304</v>
       </c>
@@ -12036,7 +12057,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="284" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:21" ht="15">
       <c r="A284">
         <v>306</v>
       </c>
@@ -12072,8 +12093,8 @@
       <c r="O284" s="3"/>
       <c r="P284" s="3"/>
     </row>
-    <row r="285" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A285">
+    <row r="285" spans="1:21" ht="15">
+      <c r="A285" s="7">
         <v>307</v>
       </c>
       <c r="B285" s="2">
@@ -12097,6 +12118,7 @@
       <c r="H285" s="3" t="s">
         <v>536</v>
       </c>
+      <c r="I285" s="7"/>
       <c r="J285" s="3"/>
       <c r="K285" s="6"/>
       <c r="L285" s="3"/>
@@ -12104,9 +12126,14 @@
       <c r="N285" s="3"/>
       <c r="O285" s="3"/>
       <c r="P285" s="3"/>
-    </row>
-    <row r="286" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A286">
+      <c r="Q285" s="7"/>
+      <c r="R285" s="7"/>
+      <c r="S285" s="7"/>
+      <c r="T285" s="7"/>
+      <c r="U285" s="7"/>
+    </row>
+    <row r="286" spans="1:21" ht="15">
+      <c r="A286" s="7">
         <v>308</v>
       </c>
       <c r="B286" s="2">
@@ -12128,6 +12155,7 @@
         <v>38</v>
       </c>
       <c r="H286" s="3"/>
+      <c r="I286" s="7"/>
       <c r="J286" s="3"/>
       <c r="K286" s="6" t="s">
         <v>537</v>
@@ -12137,9 +12165,14 @@
       <c r="N286" s="3"/>
       <c r="O286" s="3"/>
       <c r="P286" s="3"/>
-    </row>
-    <row r="287" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A287">
+      <c r="Q286" s="7"/>
+      <c r="R286" s="7"/>
+      <c r="S286" s="7"/>
+      <c r="T286" s="7"/>
+      <c r="U286" s="7"/>
+    </row>
+    <row r="287" spans="1:21" ht="15">
+      <c r="A287" s="7">
         <v>309</v>
       </c>
       <c r="B287" s="2">
@@ -12163,6 +12196,7 @@
       <c r="H287" s="3" t="s">
         <v>538</v>
       </c>
+      <c r="I287" s="7"/>
       <c r="J287" s="3"/>
       <c r="K287" s="6"/>
       <c r="L287" s="3"/>
@@ -12170,9 +12204,14 @@
       <c r="N287" s="3"/>
       <c r="O287" s="3"/>
       <c r="P287" s="3"/>
-    </row>
-    <row r="288" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A288">
+      <c r="Q287" s="7"/>
+      <c r="R287" s="7"/>
+      <c r="S287" s="7"/>
+      <c r="T287" s="7"/>
+      <c r="U287" s="7"/>
+    </row>
+    <row r="288" spans="1:21" ht="15">
+      <c r="A288" s="7">
         <v>310</v>
       </c>
       <c r="B288" s="2">
@@ -12194,6 +12233,7 @@
         <v>38</v>
       </c>
       <c r="H288" s="3"/>
+      <c r="I288" s="7"/>
       <c r="J288" s="3"/>
       <c r="K288" s="6" t="s">
         <v>539</v>
@@ -12203,9 +12243,14 @@
       <c r="N288" s="3"/>
       <c r="O288" s="3"/>
       <c r="P288" s="3"/>
-    </row>
-    <row r="289" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A289">
+      <c r="Q288" s="7"/>
+      <c r="R288" s="7"/>
+      <c r="S288" s="7"/>
+      <c r="T288" s="7"/>
+      <c r="U288" s="7"/>
+    </row>
+    <row r="289" spans="1:21" ht="15">
+      <c r="A289" s="7">
         <v>311</v>
       </c>
       <c r="B289" s="2">
@@ -12227,6 +12272,7 @@
         <v>41</v>
       </c>
       <c r="H289" s="3"/>
+      <c r="I289" s="7"/>
       <c r="J289" s="3"/>
       <c r="K289" s="6"/>
       <c r="L289" s="3"/>
@@ -12236,9 +12282,14 @@
       <c r="P289" s="3" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="290" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A290">
+      <c r="Q289" s="7"/>
+      <c r="R289" s="7"/>
+      <c r="S289" s="7"/>
+      <c r="T289" s="7"/>
+      <c r="U289" s="7"/>
+    </row>
+    <row r="290" spans="1:21" ht="15">
+      <c r="A290" s="7">
         <v>312</v>
       </c>
       <c r="B290" s="2">
@@ -12260,6 +12311,7 @@
         <v>38</v>
       </c>
       <c r="H290" s="3"/>
+      <c r="I290" s="7"/>
       <c r="J290" s="3"/>
       <c r="K290" s="6" t="s">
         <v>541</v>
@@ -12269,9 +12321,14 @@
       <c r="N290" s="3"/>
       <c r="O290" s="3"/>
       <c r="P290" s="3"/>
-    </row>
-    <row r="291" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A291">
+      <c r="Q290" s="7"/>
+      <c r="R290" s="7"/>
+      <c r="S290" s="7"/>
+      <c r="T290" s="7"/>
+      <c r="U290" s="7"/>
+    </row>
+    <row r="291" spans="1:21" ht="15">
+      <c r="A291" s="7">
         <v>313</v>
       </c>
       <c r="B291" s="2">
@@ -12293,7 +12350,7 @@
         <v>60</v>
       </c>
       <c r="H291" s="3"/>
-      <c r="I291" t="s">
+      <c r="I291" s="7" t="s">
         <v>61</v>
       </c>
       <c r="J291" s="3" t="s">
@@ -12305,9 +12362,14 @@
       <c r="N291" s="3"/>
       <c r="O291" s="3"/>
       <c r="P291" s="3"/>
-    </row>
-    <row r="292" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A292">
+      <c r="Q291" s="7"/>
+      <c r="R291" s="7"/>
+      <c r="S291" s="7"/>
+      <c r="T291" s="7"/>
+      <c r="U291" s="7"/>
+    </row>
+    <row r="292" spans="1:21" ht="15">
+      <c r="A292" s="7">
         <v>314</v>
       </c>
       <c r="B292" s="2">
@@ -12329,6 +12391,7 @@
         <v>106</v>
       </c>
       <c r="H292" s="3"/>
+      <c r="I292" s="7"/>
       <c r="J292" s="3"/>
       <c r="K292" s="6"/>
       <c r="L292" s="3"/>
@@ -12336,12 +12399,16 @@
       <c r="N292" s="3"/>
       <c r="O292" s="3"/>
       <c r="P292" s="3"/>
-      <c r="Q292" t="s">
+      <c r="Q292" s="7" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="293" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A293">
+      <c r="R292" s="7"/>
+      <c r="S292" s="7"/>
+      <c r="T292" s="7"/>
+      <c r="U292" s="7"/>
+    </row>
+    <row r="293" spans="1:21" ht="15">
+      <c r="A293" s="7">
         <v>315</v>
       </c>
       <c r="B293" s="2">
@@ -12363,6 +12430,7 @@
         <v>106</v>
       </c>
       <c r="H293" s="3"/>
+      <c r="I293" s="7"/>
       <c r="J293" s="3"/>
       <c r="K293" s="6"/>
       <c r="L293" s="3"/>
@@ -12370,12 +12438,16 @@
       <c r="N293" s="3"/>
       <c r="O293" s="3"/>
       <c r="P293" s="3"/>
-      <c r="Q293" t="s">
+      <c r="Q293" s="7" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="294" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A294">
+      <c r="R293" s="7"/>
+      <c r="S293" s="7"/>
+      <c r="T293" s="7"/>
+      <c r="U293" s="7"/>
+    </row>
+    <row r="294" spans="1:21" ht="15">
+      <c r="A294" s="7">
         <v>316</v>
       </c>
       <c r="B294" s="2">
@@ -12397,6 +12469,7 @@
         <v>33</v>
       </c>
       <c r="H294" s="3"/>
+      <c r="I294" s="7"/>
       <c r="J294" s="3"/>
       <c r="K294" s="6"/>
       <c r="L294" s="3"/>
@@ -12406,8 +12479,13 @@
         <v>543</v>
       </c>
       <c r="P294" s="3"/>
-    </row>
-    <row r="295" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="Q294" s="7"/>
+      <c r="R294" s="7"/>
+      <c r="S294" s="7"/>
+      <c r="T294" s="7"/>
+      <c r="U294" s="7"/>
+    </row>
+    <row r="295" spans="1:21" ht="15">
       <c r="A295" s="7">
         <v>317</v>
       </c>
@@ -12448,7 +12526,7 @@
       <c r="T295" s="7"/>
       <c r="U295" s="7"/>
     </row>
-    <row r="296" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:21" ht="15">
       <c r="A296" s="7">
         <v>318</v>
       </c>
@@ -12487,6 +12565,206 @@
       <c r="T296" s="7"/>
       <c r="U296" s="7"/>
     </row>
+    <row r="297" spans="1:21" ht="15">
+      <c r="A297" s="7">
+        <v>319</v>
+      </c>
+      <c r="B297" s="2">
+        <v>46268.572835648098</v>
+      </c>
+      <c r="C297" s="2">
+        <v>46268.573634259301</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F297" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H297" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="I297" s="7"/>
+      <c r="J297" s="3"/>
+      <c r="K297" s="6"/>
+      <c r="L297" s="3"/>
+      <c r="M297" s="3"/>
+      <c r="N297" s="3"/>
+      <c r="O297" s="3"/>
+      <c r="P297" s="3"/>
+      <c r="Q297" s="7"/>
+      <c r="R297" s="7"/>
+      <c r="S297" s="7"/>
+      <c r="T297" s="7"/>
+      <c r="U297" s="7"/>
+    </row>
+    <row r="298" spans="1:21" ht="15">
+      <c r="A298" s="7">
+        <v>320</v>
+      </c>
+      <c r="B298" s="2">
+        <v>46268.5700462963</v>
+      </c>
+      <c r="C298" s="2">
+        <v>46268.573877314797</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H298" s="3"/>
+      <c r="I298" s="7"/>
+      <c r="J298" s="3"/>
+      <c r="K298" s="6"/>
+      <c r="L298" s="3"/>
+      <c r="M298" s="3"/>
+      <c r="N298" s="3"/>
+      <c r="O298" s="3"/>
+      <c r="P298" s="3"/>
+      <c r="Q298" s="7"/>
+      <c r="R298" s="7"/>
+      <c r="S298" s="7"/>
+      <c r="T298" s="7"/>
+      <c r="U298" s="7" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="299" spans="1:21" ht="15">
+      <c r="A299" s="7">
+        <v>321</v>
+      </c>
+      <c r="B299" s="2">
+        <v>46268.573750000003</v>
+      </c>
+      <c r="C299" s="2">
+        <v>46268.575104166703</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H299" s="3"/>
+      <c r="I299" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J299" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="K299" s="6"/>
+      <c r="L299" s="3"/>
+      <c r="M299" s="3"/>
+      <c r="N299" s="3"/>
+      <c r="O299" s="3"/>
+      <c r="P299" s="3"/>
+      <c r="Q299" s="7"/>
+      <c r="R299" s="7"/>
+      <c r="S299" s="7"/>
+      <c r="T299" s="7"/>
+      <c r="U299" s="7"/>
+    </row>
+    <row r="300" spans="1:21" ht="15">
+      <c r="A300" s="7">
+        <v>322</v>
+      </c>
+      <c r="B300" s="2">
+        <v>46268.575138888897</v>
+      </c>
+      <c r="C300" s="2">
+        <v>46268.575520833299</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E300" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H300" s="3"/>
+      <c r="I300" s="7"/>
+      <c r="J300" s="3"/>
+      <c r="K300" s="6"/>
+      <c r="L300" s="3"/>
+      <c r="M300" s="3"/>
+      <c r="N300" s="3"/>
+      <c r="O300" s="3"/>
+      <c r="P300" s="3"/>
+      <c r="Q300" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="R300" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="S300" s="7"/>
+      <c r="T300" s="7"/>
+      <c r="U300" s="7"/>
+    </row>
+    <row r="301" spans="1:21" ht="15">
+      <c r="A301" s="7">
+        <v>323</v>
+      </c>
+      <c r="B301" s="2">
+        <v>46268.575567129599</v>
+      </c>
+      <c r="C301" s="2">
+        <v>46268.576122685197</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F301" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G301" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H301" s="3"/>
+      <c r="I301" s="7"/>
+      <c r="J301" s="3"/>
+      <c r="K301" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="L301" s="3"/>
+      <c r="M301" s="3"/>
+      <c r="N301" s="3"/>
+      <c r="O301" s="3"/>
+      <c r="P301" s="3"/>
+      <c r="Q301" s="7"/>
+      <c r="R301" s="7"/>
+      <c r="S301" s="7"/>
+      <c r="T301" s="7"/>
+      <c r="U301" s="7"/>
+    </row>
+    <row r="302" spans="1:21" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12C01C6D-BCA7-435A-BC1D-1BC14B56AEF3}"/>
+  <xr:revisionPtr revIDLastSave="363" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6D897CA-49CB-4279-B552-50B568410E13}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="546">
   <si>
     <t>Id</t>
   </si>
@@ -1674,34 +1674,13 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Echegaray.jpg</t>
-  </si>
-  <si>
-    <t>sbmx38176@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks DT Periferico Satelite</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260903-WA0017_Starbucks%20DT%20Perifer.jpg</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG_3923_Starbucks%20CEMTRAM%204.jpeg</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/17884648749153020018020140049704_Starbucks%20DT%20Perifer.jpg</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/17884649102538417106894466458342_Starbucks%20DT%20Perifer.jpg</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17884649537715577155901761431956_Starbucks%20DT%20Perifer.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1829,8 +1808,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U301" totalsRowShown="0">
-  <autoFilter ref="A1:U301" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U296" totalsRowShown="0">
+  <autoFilter ref="A1:U296" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -1983,7 +1962,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="323" latestEventMarker="558">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="318" latestEventMarker="553">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2308,23 +2287,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U302"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <dimension ref="A1:U296"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" customWidth="1"/>
     <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.1796875" customWidth="1"/>
+    <col min="5" max="5" width="35.1796875" customWidth="1"/>
+    <col min="6" max="6" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="20" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="15" width="20" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="19" customWidth="1"/>
-    <col min="19" max="19" width="42.140625" customWidth="1"/>
+    <col min="19" max="19" width="42.1796875" customWidth="1"/>
     <col min="20" max="21" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2389,7 +2368,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>13</v>
       </c>
@@ -2415,7 +2394,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>17</v>
       </c>
@@ -2448,7 +2427,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2481,7 +2460,7 @@
       </c>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>20</v>
       </c>
@@ -2514,7 +2493,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>21</v>
       </c>
@@ -2547,7 +2526,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>22</v>
       </c>
@@ -2580,7 +2559,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>23</v>
       </c>
@@ -2614,7 +2593,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>24</v>
       </c>
@@ -2648,7 +2627,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>25</v>
       </c>
@@ -2682,7 +2661,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>26</v>
       </c>
@@ -2715,7 +2694,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>27</v>
       </c>
@@ -2751,7 +2730,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>28</v>
       </c>
@@ -2784,7 +2763,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>29</v>
       </c>
@@ -2818,7 +2797,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>30</v>
       </c>
@@ -2851,7 +2830,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>31</v>
       </c>
@@ -2884,7 +2863,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>32</v>
       </c>
@@ -2918,7 +2897,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>33</v>
       </c>
@@ -2951,7 +2930,7 @@
       </c>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>34</v>
       </c>
@@ -2984,7 +2963,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>35</v>
       </c>
@@ -3017,7 +2996,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>36</v>
       </c>
@@ -3050,7 +3029,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>37</v>
       </c>
@@ -3084,7 +3063,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>38</v>
       </c>
@@ -3118,7 +3097,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>39</v>
       </c>
@@ -3152,7 +3131,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>40</v>
       </c>
@@ -3186,7 +3165,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>41</v>
       </c>
@@ -3219,7 +3198,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>42</v>
       </c>
@@ -3253,7 +3232,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>43</v>
       </c>
@@ -3287,7 +3266,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>44</v>
       </c>
@@ -3321,7 +3300,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>45</v>
       </c>
@@ -3355,7 +3334,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>46</v>
       </c>
@@ -3389,7 +3368,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>47</v>
       </c>
@@ -3423,7 +3402,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>48</v>
       </c>
@@ -3456,7 +3435,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>49</v>
       </c>
@@ -3490,7 +3469,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>50</v>
       </c>
@@ -3524,7 +3503,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>51</v>
       </c>
@@ -3558,7 +3537,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>52</v>
       </c>
@@ -3591,7 +3570,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>54</v>
       </c>
@@ -3624,7 +3603,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>55</v>
       </c>
@@ -3657,7 +3636,7 @@
       </c>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>56</v>
       </c>
@@ -3691,7 +3670,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>57</v>
       </c>
@@ -3725,7 +3704,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>58</v>
       </c>
@@ -3759,7 +3738,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>59</v>
       </c>
@@ -3793,7 +3772,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>60</v>
       </c>
@@ -3827,7 +3806,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>61</v>
       </c>
@@ -3861,7 +3840,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>62</v>
       </c>
@@ -3895,7 +3874,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>63</v>
       </c>
@@ -3929,7 +3908,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>65</v>
       </c>
@@ -3963,7 +3942,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>66</v>
       </c>
@@ -3997,7 +3976,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>67</v>
       </c>
@@ -4030,7 +4009,7 @@
       <c r="O50" s="3"/>
       <c r="P50" s="3"/>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>68</v>
       </c>
@@ -4063,7 +4042,7 @@
       <c r="O51" s="3"/>
       <c r="P51" s="3"/>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>69</v>
       </c>
@@ -4097,7 +4076,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>70</v>
       </c>
@@ -4131,7 +4110,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>71</v>
       </c>
@@ -4165,7 +4144,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>72</v>
       </c>
@@ -4199,7 +4178,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>73</v>
       </c>
@@ -4233,7 +4212,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>74</v>
       </c>
@@ -4267,7 +4246,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>75</v>
       </c>
@@ -4301,7 +4280,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>76</v>
       </c>
@@ -4335,7 +4314,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>77</v>
       </c>
@@ -4368,7 +4347,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>78</v>
       </c>
@@ -4402,7 +4381,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>79</v>
       </c>
@@ -4436,7 +4415,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>80</v>
       </c>
@@ -4470,7 +4449,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>81</v>
       </c>
@@ -4504,7 +4483,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>84</v>
       </c>
@@ -4538,7 +4517,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>85</v>
       </c>
@@ -4571,7 +4550,7 @@
       <c r="O66" s="3"/>
       <c r="P66" s="3"/>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>86</v>
       </c>
@@ -4604,7 +4583,7 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>88</v>
       </c>
@@ -4637,7 +4616,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>89</v>
       </c>
@@ -4670,7 +4649,7 @@
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>90</v>
       </c>
@@ -4704,7 +4683,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>91</v>
       </c>
@@ -4738,7 +4717,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>92</v>
       </c>
@@ -4774,7 +4753,7 @@
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>93</v>
       </c>
@@ -4807,7 +4786,7 @@
       </c>
       <c r="P73" s="3"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>94</v>
       </c>
@@ -4840,7 +4819,7 @@
       <c r="O74" s="3"/>
       <c r="P74" s="3"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>95</v>
       </c>
@@ -4873,7 +4852,7 @@
       <c r="O75" s="3"/>
       <c r="P75" s="3"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>96</v>
       </c>
@@ -4907,7 +4886,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>97</v>
       </c>
@@ -4940,7 +4919,7 @@
       <c r="O77" s="3"/>
       <c r="P77" s="3"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>98</v>
       </c>
@@ -4974,7 +4953,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>99</v>
       </c>
@@ -5007,7 +4986,7 @@
       <c r="O79" s="3"/>
       <c r="P79" s="3"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>100</v>
       </c>
@@ -5041,7 +5020,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>102</v>
       </c>
@@ -5077,7 +5056,7 @@
       <c r="O81" s="3"/>
       <c r="P81" s="3"/>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>103</v>
       </c>
@@ -5110,7 +5089,7 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>104</v>
       </c>
@@ -5144,7 +5123,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>105</v>
       </c>
@@ -5180,7 +5159,7 @@
       <c r="O84" s="3"/>
       <c r="P84" s="3"/>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>106</v>
       </c>
@@ -5214,7 +5193,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>107</v>
       </c>
@@ -5247,7 +5226,7 @@
       </c>
       <c r="P86" s="3"/>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>108</v>
       </c>
@@ -5281,7 +5260,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>109</v>
       </c>
@@ -5315,7 +5294,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>110</v>
       </c>
@@ -5348,7 +5327,7 @@
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>111</v>
       </c>
@@ -5382,7 +5361,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>112</v>
       </c>
@@ -5415,7 +5394,7 @@
       </c>
       <c r="P91" s="3"/>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>113</v>
       </c>
@@ -5449,7 +5428,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>114</v>
       </c>
@@ -5483,7 +5462,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>115</v>
       </c>
@@ -5516,7 +5495,7 @@
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>116</v>
       </c>
@@ -5549,7 +5528,7 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>117</v>
       </c>
@@ -5582,7 +5561,7 @@
       </c>
       <c r="P96" s="3"/>
     </row>
-    <row r="97" spans="1:21">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>118</v>
       </c>
@@ -5615,7 +5594,7 @@
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
     </row>
-    <row r="98" spans="1:21">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>119</v>
       </c>
@@ -5648,7 +5627,7 @@
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
     </row>
-    <row r="99" spans="1:21">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>120</v>
       </c>
@@ -5681,7 +5660,7 @@
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
     </row>
-    <row r="100" spans="1:21">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>121</v>
       </c>
@@ -5715,7 +5694,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="101" spans="1:21">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>122</v>
       </c>
@@ -5748,7 +5727,7 @@
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
     </row>
-    <row r="102" spans="1:21">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>123</v>
       </c>
@@ -5782,7 +5761,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="103" spans="1:21">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>124</v>
       </c>
@@ -5816,7 +5795,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="104" spans="1:21">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>125</v>
       </c>
@@ -5850,7 +5829,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:21">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>126</v>
       </c>
@@ -5884,7 +5863,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="106" spans="1:21">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>127</v>
       </c>
@@ -5917,7 +5896,7 @@
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
     </row>
-    <row r="107" spans="1:21">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>128</v>
       </c>
@@ -5953,7 +5932,7 @@
       <c r="O107" s="3"/>
       <c r="P107" s="3"/>
     </row>
-    <row r="108" spans="1:21">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>129</v>
       </c>
@@ -5987,7 +5966,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="109" spans="1:21">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>130</v>
       </c>
@@ -6023,7 +6002,7 @@
       <c r="O109" s="3"/>
       <c r="P109" s="3"/>
     </row>
-    <row r="110" spans="1:21">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>131</v>
       </c>
@@ -6056,7 +6035,7 @@
       <c r="O110" s="3"/>
       <c r="P110" s="3"/>
     </row>
-    <row r="111" spans="1:21">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>132</v>
       </c>
@@ -6090,7 +6069,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="112" spans="1:21">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>133</v>
       </c>
@@ -6124,7 +6103,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>134</v>
       </c>
@@ -6158,7 +6137,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>135</v>
       </c>
@@ -6192,7 +6171,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>136</v>
       </c>
@@ -6226,7 +6205,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>137</v>
       </c>
@@ -6260,7 +6239,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>138</v>
       </c>
@@ -6294,7 +6273,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>139</v>
       </c>
@@ -6328,7 +6307,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>140</v>
       </c>
@@ -6362,7 +6341,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>141</v>
       </c>
@@ -6395,7 +6374,7 @@
       <c r="O120" s="3"/>
       <c r="P120" s="3"/>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>142</v>
       </c>
@@ -6429,7 +6408,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="122" spans="1:19">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>143</v>
       </c>
@@ -6462,7 +6441,7 @@
       <c r="O122" s="3"/>
       <c r="P122" s="3"/>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>144</v>
       </c>
@@ -6496,7 +6475,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>145</v>
       </c>
@@ -6529,7 +6508,7 @@
       <c r="O124" s="3"/>
       <c r="P124" s="3"/>
     </row>
-    <row r="125" spans="1:19">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>146</v>
       </c>
@@ -6563,7 +6542,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="126" spans="1:19">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>147</v>
       </c>
@@ -6596,7 +6575,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>148</v>
       </c>
@@ -6633,7 +6612,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="128" spans="1:19">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>149</v>
       </c>
@@ -6667,7 +6646,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="129" spans="1:19">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>150</v>
       </c>
@@ -6701,7 +6680,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="130" spans="1:19">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>151</v>
       </c>
@@ -6735,7 +6714,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="131" spans="1:19">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>152</v>
       </c>
@@ -6769,7 +6748,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="132" spans="1:19">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>153</v>
       </c>
@@ -6802,7 +6781,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="133" spans="1:19">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>154</v>
       </c>
@@ -6836,7 +6815,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="134" spans="1:19">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>155</v>
       </c>
@@ -6870,7 +6849,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="135" spans="1:19">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>156</v>
       </c>
@@ -6907,7 +6886,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="136" spans="1:19">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>157</v>
       </c>
@@ -6940,7 +6919,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="137" spans="1:19">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>158</v>
       </c>
@@ -6974,7 +6953,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="138" spans="1:19">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>159</v>
       </c>
@@ -7011,7 +6990,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="139" spans="1:19">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>160</v>
       </c>
@@ -7047,7 +7026,7 @@
       <c r="O139" s="3"/>
       <c r="P139" s="3"/>
     </row>
-    <row r="140" spans="1:19">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>161</v>
       </c>
@@ -7080,7 +7059,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="141" spans="1:19">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>162</v>
       </c>
@@ -7116,7 +7095,7 @@
       <c r="O141" s="3"/>
       <c r="P141" s="3"/>
     </row>
-    <row r="142" spans="1:19">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>163</v>
       </c>
@@ -7152,7 +7131,7 @@
       <c r="O142" s="3"/>
       <c r="P142" s="3"/>
     </row>
-    <row r="143" spans="1:19">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>164</v>
       </c>
@@ -7185,7 +7164,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="144" spans="1:19">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>165</v>
       </c>
@@ -7222,7 +7201,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>166</v>
       </c>
@@ -7258,7 +7237,7 @@
       <c r="O145" s="3"/>
       <c r="P145" s="3"/>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>167</v>
       </c>
@@ -7294,7 +7273,7 @@
       <c r="O146" s="3"/>
       <c r="P146" s="3"/>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>168</v>
       </c>
@@ -7330,7 +7309,7 @@
       <c r="O147" s="3"/>
       <c r="P147" s="3"/>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>169</v>
       </c>
@@ -7366,7 +7345,7 @@
       <c r="O148" s="3"/>
       <c r="P148" s="3"/>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>170</v>
       </c>
@@ -7402,7 +7381,7 @@
       <c r="O149" s="3"/>
       <c r="P149" s="3"/>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>171</v>
       </c>
@@ -7438,7 +7417,7 @@
       <c r="O150" s="3"/>
       <c r="P150" s="3"/>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>172</v>
       </c>
@@ -7474,7 +7453,7 @@
       <c r="O151" s="3"/>
       <c r="P151" s="3"/>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>173</v>
       </c>
@@ -7510,7 +7489,7 @@
       <c r="O152" s="3"/>
       <c r="P152" s="3"/>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>174</v>
       </c>
@@ -7546,7 +7525,7 @@
       <c r="O153" s="3"/>
       <c r="P153" s="3"/>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>175</v>
       </c>
@@ -7582,7 +7561,7 @@
       <c r="O154" s="3"/>
       <c r="P154" s="3"/>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>176</v>
       </c>
@@ -7618,7 +7597,7 @@
       <c r="O155" s="3"/>
       <c r="P155" s="3"/>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>177</v>
       </c>
@@ -7654,7 +7633,7 @@
       <c r="O156" s="3"/>
       <c r="P156" s="3"/>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>178</v>
       </c>
@@ -7690,7 +7669,7 @@
       <c r="O157" s="3"/>
       <c r="P157" s="3"/>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>179</v>
       </c>
@@ -7726,7 +7705,7 @@
       <c r="O158" s="3"/>
       <c r="P158" s="3"/>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>180</v>
       </c>
@@ -7762,7 +7741,7 @@
       <c r="O159" s="3"/>
       <c r="P159" s="3"/>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>181</v>
       </c>
@@ -7798,7 +7777,7 @@
       <c r="O160" s="3"/>
       <c r="P160" s="3"/>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>182</v>
       </c>
@@ -7834,7 +7813,7 @@
       <c r="O161" s="3"/>
       <c r="P161" s="3"/>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>183</v>
       </c>
@@ -7870,7 +7849,7 @@
       <c r="O162" s="3"/>
       <c r="P162" s="3"/>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>184</v>
       </c>
@@ -7904,7 +7883,7 @@
       <c r="O163" s="3"/>
       <c r="P163" s="3"/>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>185</v>
       </c>
@@ -7940,7 +7919,7 @@
       <c r="O164" s="3"/>
       <c r="P164" s="3"/>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>186</v>
       </c>
@@ -7976,7 +7955,7 @@
       <c r="O165" s="3"/>
       <c r="P165" s="3"/>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>187</v>
       </c>
@@ -8012,7 +7991,7 @@
       <c r="O166" s="3"/>
       <c r="P166" s="3"/>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>188</v>
       </c>
@@ -8048,7 +8027,7 @@
       <c r="O167" s="3"/>
       <c r="P167" s="3"/>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>189</v>
       </c>
@@ -8084,7 +8063,7 @@
       <c r="O168" s="3"/>
       <c r="P168" s="3"/>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>190</v>
       </c>
@@ -8120,7 +8099,7 @@
       <c r="O169" s="3"/>
       <c r="P169" s="3"/>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>191</v>
       </c>
@@ -8156,7 +8135,7 @@
       <c r="O170" s="3"/>
       <c r="P170" s="3"/>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>192</v>
       </c>
@@ -8192,7 +8171,7 @@
       <c r="O171" s="3"/>
       <c r="P171" s="3"/>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>193</v>
       </c>
@@ -8228,7 +8207,7 @@
       <c r="O172" s="3"/>
       <c r="P172" s="3"/>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>194</v>
       </c>
@@ -8264,7 +8243,7 @@
       <c r="O173" s="3"/>
       <c r="P173" s="3"/>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>195</v>
       </c>
@@ -8300,7 +8279,7 @@
       <c r="O174" s="3"/>
       <c r="P174" s="3"/>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>196</v>
       </c>
@@ -8336,7 +8315,7 @@
       <c r="O175" s="3"/>
       <c r="P175" s="3"/>
     </row>
-    <row r="176" spans="1:16">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>197</v>
       </c>
@@ -8372,7 +8351,7 @@
       <c r="O176" s="3"/>
       <c r="P176" s="3"/>
     </row>
-    <row r="177" spans="1:16">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>198</v>
       </c>
@@ -8408,7 +8387,7 @@
       <c r="O177" s="3"/>
       <c r="P177" s="3"/>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>199</v>
       </c>
@@ -8444,7 +8423,7 @@
       <c r="O178" s="3"/>
       <c r="P178" s="3"/>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>200</v>
       </c>
@@ -8480,7 +8459,7 @@
       <c r="O179" s="3"/>
       <c r="P179" s="3"/>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>201</v>
       </c>
@@ -8516,7 +8495,7 @@
       <c r="O180" s="3"/>
       <c r="P180" s="3"/>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>202</v>
       </c>
@@ -8552,7 +8531,7 @@
       <c r="O181" s="3"/>
       <c r="P181" s="3"/>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>203</v>
       </c>
@@ -8588,7 +8567,7 @@
       <c r="O182" s="3"/>
       <c r="P182" s="3"/>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>204</v>
       </c>
@@ -8624,7 +8603,7 @@
       <c r="O183" s="3"/>
       <c r="P183" s="3"/>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>205</v>
       </c>
@@ -8660,7 +8639,7 @@
       <c r="O184" s="3"/>
       <c r="P184" s="3"/>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>206</v>
       </c>
@@ -8696,7 +8675,7 @@
       <c r="O185" s="3"/>
       <c r="P185" s="3"/>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>207</v>
       </c>
@@ -8729,7 +8708,7 @@
       <c r="O186" s="3"/>
       <c r="P186" s="3"/>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>208</v>
       </c>
@@ -8765,7 +8744,7 @@
       <c r="O187" s="3"/>
       <c r="P187" s="3"/>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>209</v>
       </c>
@@ -8799,7 +8778,7 @@
       <c r="O188" s="3"/>
       <c r="P188" s="3"/>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>210</v>
       </c>
@@ -8835,7 +8814,7 @@
       <c r="O189" s="3"/>
       <c r="P189" s="3"/>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>211</v>
       </c>
@@ -8871,7 +8850,7 @@
       <c r="O190" s="3"/>
       <c r="P190" s="3"/>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>212</v>
       </c>
@@ -8907,7 +8886,7 @@
       <c r="O191" s="3"/>
       <c r="P191" s="3"/>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>213</v>
       </c>
@@ -8940,7 +8919,7 @@
       <c r="O192" s="3"/>
       <c r="P192" s="3"/>
     </row>
-    <row r="193" spans="1:20">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>214</v>
       </c>
@@ -8974,7 +8953,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="194" spans="1:20">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>215</v>
       </c>
@@ -9010,7 +8989,7 @@
       <c r="O194" s="3"/>
       <c r="P194" s="3"/>
     </row>
-    <row r="195" spans="1:20">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>216</v>
       </c>
@@ -9046,7 +9025,7 @@
       <c r="O195" s="3"/>
       <c r="P195" s="3"/>
     </row>
-    <row r="196" spans="1:20">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>217</v>
       </c>
@@ -9082,7 +9061,7 @@
       <c r="O196" s="3"/>
       <c r="P196" s="3"/>
     </row>
-    <row r="197" spans="1:20">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>218</v>
       </c>
@@ -9118,7 +9097,7 @@
       <c r="O197" s="3"/>
       <c r="P197" s="3"/>
     </row>
-    <row r="198" spans="1:20">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>219</v>
       </c>
@@ -9151,7 +9130,7 @@
       <c r="O198" s="3"/>
       <c r="P198" s="3"/>
     </row>
-    <row r="199" spans="1:20">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>220</v>
       </c>
@@ -9185,7 +9164,7 @@
       <c r="O199" s="3"/>
       <c r="P199" s="3"/>
     </row>
-    <row r="200" spans="1:20">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>221</v>
       </c>
@@ -9222,7 +9201,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="201" spans="1:20">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>222</v>
       </c>
@@ -9258,7 +9237,7 @@
       <c r="O201" s="3"/>
       <c r="P201" s="3"/>
     </row>
-    <row r="202" spans="1:20">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>223</v>
       </c>
@@ -9291,7 +9270,7 @@
       <c r="O202" s="3"/>
       <c r="P202" s="3"/>
     </row>
-    <row r="203" spans="1:20">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>224</v>
       </c>
@@ -9327,7 +9306,7 @@
       <c r="O203" s="3"/>
       <c r="P203" s="3"/>
     </row>
-    <row r="204" spans="1:20">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>225</v>
       </c>
@@ -9363,7 +9342,7 @@
       <c r="O204" s="3"/>
       <c r="P204" s="3"/>
     </row>
-    <row r="205" spans="1:20">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>226</v>
       </c>
@@ -9396,7 +9375,7 @@
       <c r="O205" s="3"/>
       <c r="P205" s="3"/>
     </row>
-    <row r="206" spans="1:20">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>227</v>
       </c>
@@ -9429,7 +9408,7 @@
       <c r="O206" s="3"/>
       <c r="P206" s="3"/>
     </row>
-    <row r="207" spans="1:20">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>228</v>
       </c>
@@ -9462,7 +9441,7 @@
       <c r="O207" s="3"/>
       <c r="P207" s="3"/>
     </row>
-    <row r="208" spans="1:20">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>229</v>
       </c>
@@ -9499,7 +9478,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="209" spans="1:19">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>230</v>
       </c>
@@ -9533,7 +9512,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="210" spans="1:19">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>231</v>
       </c>
@@ -9570,7 +9549,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="211" spans="1:19">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>232</v>
       </c>
@@ -9607,7 +9586,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="212" spans="1:19">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>233</v>
       </c>
@@ -9644,7 +9623,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="213" spans="1:19">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>234</v>
       </c>
@@ -9678,7 +9657,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="214" spans="1:19">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>235</v>
       </c>
@@ -9715,7 +9694,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="215" spans="1:19">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>236</v>
       </c>
@@ -9748,7 +9727,7 @@
       <c r="O215" s="3"/>
       <c r="P215" s="3"/>
     </row>
-    <row r="216" spans="1:19">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>237</v>
       </c>
@@ -9781,7 +9760,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="217" spans="1:19">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>238</v>
       </c>
@@ -9814,7 +9793,7 @@
       <c r="O217" s="3"/>
       <c r="P217" s="3"/>
     </row>
-    <row r="218" spans="1:19">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>239</v>
       </c>
@@ -9847,7 +9826,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="219" spans="1:19">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>240</v>
       </c>
@@ -9883,7 +9862,7 @@
       <c r="O219" s="3"/>
       <c r="P219" s="3"/>
     </row>
-    <row r="220" spans="1:19" ht="15">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>241</v>
       </c>
@@ -9916,7 +9895,7 @@
       <c r="O220" s="3"/>
       <c r="P220" s="3"/>
     </row>
-    <row r="221" spans="1:19" ht="15">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>242</v>
       </c>
@@ -9949,7 +9928,7 @@
       <c r="O221" s="3"/>
       <c r="P221" s="3"/>
     </row>
-    <row r="222" spans="1:19" ht="15">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>243</v>
       </c>
@@ -9982,7 +9961,7 @@
       </c>
       <c r="P222" s="3"/>
     </row>
-    <row r="223" spans="1:19" ht="15">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>244</v>
       </c>
@@ -10015,7 +9994,7 @@
       <c r="O223" s="3"/>
       <c r="P223" s="3"/>
     </row>
-    <row r="224" spans="1:19" ht="15">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>245</v>
       </c>
@@ -10048,7 +10027,7 @@
       </c>
       <c r="P224" s="3"/>
     </row>
-    <row r="225" spans="1:21" ht="15">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>246</v>
       </c>
@@ -10081,7 +10060,7 @@
       <c r="O225" s="3"/>
       <c r="P225" s="3"/>
     </row>
-    <row r="226" spans="1:21" ht="15">
+    <row r="226" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>247</v>
       </c>
@@ -10114,7 +10093,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="227" spans="1:21" ht="15">
+    <row r="227" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>248</v>
       </c>
@@ -10147,7 +10126,7 @@
       <c r="O227" s="3"/>
       <c r="P227" s="3"/>
     </row>
-    <row r="228" spans="1:21" ht="15">
+    <row r="228" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>249</v>
       </c>
@@ -10180,7 +10159,7 @@
       <c r="O228" s="3"/>
       <c r="P228" s="3"/>
     </row>
-    <row r="229" spans="1:21" ht="15">
+    <row r="229" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>250</v>
       </c>
@@ -10213,7 +10192,7 @@
       <c r="O229" s="3"/>
       <c r="P229" s="3"/>
     </row>
-    <row r="230" spans="1:21" ht="15">
+    <row r="230" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>251</v>
       </c>
@@ -10246,7 +10225,7 @@
       <c r="O230" s="3"/>
       <c r="P230" s="3"/>
     </row>
-    <row r="231" spans="1:21" ht="15">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>252</v>
       </c>
@@ -10282,7 +10261,7 @@
       <c r="O231" s="3"/>
       <c r="P231" s="3"/>
     </row>
-    <row r="232" spans="1:21" ht="15">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>253</v>
       </c>
@@ -10315,7 +10294,7 @@
       <c r="O232" s="3"/>
       <c r="P232" s="3"/>
     </row>
-    <row r="233" spans="1:21" ht="15">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>254</v>
       </c>
@@ -10352,7 +10331,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="234" spans="1:21" ht="15">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>255</v>
       </c>
@@ -10388,7 +10367,7 @@
       <c r="O234" s="3"/>
       <c r="P234" s="3"/>
     </row>
-    <row r="235" spans="1:21" ht="15">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>256</v>
       </c>
@@ -10424,7 +10403,7 @@
       <c r="O235" s="3"/>
       <c r="P235" s="3"/>
     </row>
-    <row r="236" spans="1:21" ht="15">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>257</v>
       </c>
@@ -10458,7 +10437,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="237" spans="1:21" ht="15">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>258</v>
       </c>
@@ -10492,7 +10471,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="238" spans="1:21" ht="15">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>259</v>
       </c>
@@ -10525,7 +10504,7 @@
       <c r="O238" s="3"/>
       <c r="P238" s="3"/>
     </row>
-    <row r="239" spans="1:21" ht="15">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>260</v>
       </c>
@@ -10558,7 +10537,7 @@
       <c r="O239" s="3"/>
       <c r="P239" s="3"/>
     </row>
-    <row r="240" spans="1:21" ht="15">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>261</v>
       </c>
@@ -10591,7 +10570,7 @@
       <c r="O240" s="3"/>
       <c r="P240" s="3"/>
     </row>
-    <row r="241" spans="1:20" ht="15">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>262</v>
       </c>
@@ -10624,7 +10603,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="242" spans="1:20" ht="15">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>263</v>
       </c>
@@ -10660,7 +10639,7 @@
       <c r="O242" s="3"/>
       <c r="P242" s="3"/>
     </row>
-    <row r="243" spans="1:20" ht="15">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>264</v>
       </c>
@@ -10693,7 +10672,7 @@
       </c>
       <c r="P243" s="3"/>
     </row>
-    <row r="244" spans="1:20" ht="15">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>265</v>
       </c>
@@ -10726,7 +10705,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="245" spans="1:20" ht="15">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>266</v>
       </c>
@@ -10760,7 +10739,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="246" spans="1:20" ht="15">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>267</v>
       </c>
@@ -10793,7 +10772,7 @@
       <c r="O246" s="3"/>
       <c r="P246" s="3"/>
     </row>
-    <row r="247" spans="1:20" ht="15">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>268</v>
       </c>
@@ -10826,7 +10805,7 @@
       <c r="O247" s="3"/>
       <c r="P247" s="3"/>
     </row>
-    <row r="248" spans="1:20" ht="15">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>269</v>
       </c>
@@ -10862,7 +10841,7 @@
       <c r="O248" s="3"/>
       <c r="P248" s="3"/>
     </row>
-    <row r="249" spans="1:20" ht="15">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>270</v>
       </c>
@@ -10895,7 +10874,7 @@
       </c>
       <c r="P249" s="3"/>
     </row>
-    <row r="250" spans="1:20" ht="15">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>271</v>
       </c>
@@ -10929,7 +10908,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="251" spans="1:20" ht="15">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>272</v>
       </c>
@@ -10962,7 +10941,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="252" spans="1:20" ht="15">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>273</v>
       </c>
@@ -10995,7 +10974,7 @@
       <c r="O252" s="3"/>
       <c r="P252" s="3"/>
     </row>
-    <row r="253" spans="1:20" ht="15">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>274</v>
       </c>
@@ -11028,7 +11007,7 @@
       <c r="O253" s="3"/>
       <c r="P253" s="3"/>
     </row>
-    <row r="254" spans="1:20" ht="15">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>275</v>
       </c>
@@ -11062,7 +11041,7 @@
       <c r="O254" s="3"/>
       <c r="P254" s="3"/>
     </row>
-    <row r="255" spans="1:20" ht="15">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>276</v>
       </c>
@@ -11098,7 +11077,7 @@
       <c r="O255" s="3"/>
       <c r="P255" s="3"/>
     </row>
-    <row r="256" spans="1:20" ht="15">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>277</v>
       </c>
@@ -11131,7 +11110,7 @@
       <c r="O256" s="3"/>
       <c r="P256" s="3"/>
     </row>
-    <row r="257" spans="1:21" ht="15">
+    <row r="257" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>278</v>
       </c>
@@ -11164,7 +11143,7 @@
       <c r="O257" s="3"/>
       <c r="P257" s="3"/>
     </row>
-    <row r="258" spans="1:21" ht="15">
+    <row r="258" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>279</v>
       </c>
@@ -11201,7 +11180,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="259" spans="1:21" ht="15">
+    <row r="259" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>280</v>
       </c>
@@ -11234,7 +11213,7 @@
       <c r="O259" s="3"/>
       <c r="P259" s="3"/>
     </row>
-    <row r="260" spans="1:21" ht="15">
+    <row r="260" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>281</v>
       </c>
@@ -11270,7 +11249,7 @@
       <c r="O260" s="3"/>
       <c r="P260" s="3"/>
     </row>
-    <row r="261" spans="1:21" ht="15">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>282</v>
       </c>
@@ -11303,7 +11282,7 @@
       <c r="O261" s="3"/>
       <c r="P261" s="3"/>
     </row>
-    <row r="262" spans="1:21" ht="15">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>283</v>
       </c>
@@ -11339,7 +11318,7 @@
       <c r="O262" s="3"/>
       <c r="P262" s="3"/>
     </row>
-    <row r="263" spans="1:21" ht="15">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>284</v>
       </c>
@@ -11372,7 +11351,7 @@
       <c r="O263" s="3"/>
       <c r="P263" s="3"/>
     </row>
-    <row r="264" spans="1:21" ht="15">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>285</v>
       </c>
@@ -11408,7 +11387,7 @@
       <c r="O264" s="3"/>
       <c r="P264" s="3"/>
     </row>
-    <row r="265" spans="1:21" ht="15">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>286</v>
       </c>
@@ -11441,7 +11420,7 @@
       <c r="O265" s="3"/>
       <c r="P265" s="3"/>
     </row>
-    <row r="266" spans="1:21" ht="15">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>287</v>
       </c>
@@ -11474,7 +11453,7 @@
       <c r="O266" s="3"/>
       <c r="P266" s="3"/>
     </row>
-    <row r="267" spans="1:21" ht="15">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>288</v>
       </c>
@@ -11507,7 +11486,7 @@
       </c>
       <c r="P267" s="3"/>
     </row>
-    <row r="268" spans="1:21" ht="15">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>289</v>
       </c>
@@ -11544,7 +11523,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="269" spans="1:21" ht="15">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>290</v>
       </c>
@@ -11580,7 +11559,7 @@
       <c r="O269" s="3"/>
       <c r="P269" s="3"/>
     </row>
-    <row r="270" spans="1:21" ht="15">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>291</v>
       </c>
@@ -11614,7 +11593,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="271" spans="1:21" ht="15">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>292</v>
       </c>
@@ -11647,7 +11626,7 @@
       </c>
       <c r="P271" s="3"/>
     </row>
-    <row r="272" spans="1:21" ht="15">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>293</v>
       </c>
@@ -11681,7 +11660,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="273" spans="1:21" ht="15">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>294</v>
       </c>
@@ -11718,7 +11697,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="274" spans="1:21" ht="15">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>295</v>
       </c>
@@ -11752,7 +11731,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="275" spans="1:21" ht="15">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>296</v>
       </c>
@@ -11789,7 +11768,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="276" spans="1:21" ht="15">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>297</v>
       </c>
@@ -11822,7 +11801,7 @@
       <c r="O276" s="3"/>
       <c r="P276" s="3"/>
     </row>
-    <row r="277" spans="1:21" ht="15">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>298</v>
       </c>
@@ -11855,7 +11834,7 @@
       <c r="O277" s="3"/>
       <c r="P277" s="3"/>
     </row>
-    <row r="278" spans="1:21" ht="15">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>299</v>
       </c>
@@ -11888,7 +11867,7 @@
       </c>
       <c r="P278" s="3"/>
     </row>
-    <row r="279" spans="1:21" ht="15">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>300</v>
       </c>
@@ -11921,7 +11900,7 @@
       <c r="O279" s="3"/>
       <c r="P279" s="3"/>
     </row>
-    <row r="280" spans="1:21" ht="15">
+    <row r="280" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>301</v>
       </c>
@@ -11954,7 +11933,7 @@
       <c r="O280" s="3"/>
       <c r="P280" s="3"/>
     </row>
-    <row r="281" spans="1:21" ht="15">
+    <row r="281" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>302</v>
       </c>
@@ -11987,7 +11966,7 @@
       <c r="O281" s="3"/>
       <c r="P281" s="3"/>
     </row>
-    <row r="282" spans="1:21" ht="15">
+    <row r="282" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>303</v>
       </c>
@@ -12023,7 +12002,7 @@
       <c r="O282" s="3"/>
       <c r="P282" s="3"/>
     </row>
-    <row r="283" spans="1:21" ht="15">
+    <row r="283" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>304</v>
       </c>
@@ -12057,7 +12036,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="284" spans="1:21" ht="15">
+    <row r="284" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>306</v>
       </c>
@@ -12093,8 +12072,8 @@
       <c r="O284" s="3"/>
       <c r="P284" s="3"/>
     </row>
-    <row r="285" spans="1:21" ht="15">
-      <c r="A285" s="7">
+    <row r="285" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A285">
         <v>307</v>
       </c>
       <c r="B285" s="2">
@@ -12118,7 +12097,6 @@
       <c r="H285" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="I285" s="7"/>
       <c r="J285" s="3"/>
       <c r="K285" s="6"/>
       <c r="L285" s="3"/>
@@ -12126,14 +12104,9 @@
       <c r="N285" s="3"/>
       <c r="O285" s="3"/>
       <c r="P285" s="3"/>
-      <c r="Q285" s="7"/>
-      <c r="R285" s="7"/>
-      <c r="S285" s="7"/>
-      <c r="T285" s="7"/>
-      <c r="U285" s="7"/>
-    </row>
-    <row r="286" spans="1:21" ht="15">
-      <c r="A286" s="7">
+    </row>
+    <row r="286" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A286">
         <v>308</v>
       </c>
       <c r="B286" s="2">
@@ -12155,7 +12128,6 @@
         <v>38</v>
       </c>
       <c r="H286" s="3"/>
-      <c r="I286" s="7"/>
       <c r="J286" s="3"/>
       <c r="K286" s="6" t="s">
         <v>537</v>
@@ -12165,14 +12137,9 @@
       <c r="N286" s="3"/>
       <c r="O286" s="3"/>
       <c r="P286" s="3"/>
-      <c r="Q286" s="7"/>
-      <c r="R286" s="7"/>
-      <c r="S286" s="7"/>
-      <c r="T286" s="7"/>
-      <c r="U286" s="7"/>
-    </row>
-    <row r="287" spans="1:21" ht="15">
-      <c r="A287" s="7">
+    </row>
+    <row r="287" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A287">
         <v>309</v>
       </c>
       <c r="B287" s="2">
@@ -12196,7 +12163,6 @@
       <c r="H287" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="I287" s="7"/>
       <c r="J287" s="3"/>
       <c r="K287" s="6"/>
       <c r="L287" s="3"/>
@@ -12204,14 +12170,9 @@
       <c r="N287" s="3"/>
       <c r="O287" s="3"/>
       <c r="P287" s="3"/>
-      <c r="Q287" s="7"/>
-      <c r="R287" s="7"/>
-      <c r="S287" s="7"/>
-      <c r="T287" s="7"/>
-      <c r="U287" s="7"/>
-    </row>
-    <row r="288" spans="1:21" ht="15">
-      <c r="A288" s="7">
+    </row>
+    <row r="288" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A288">
         <v>310</v>
       </c>
       <c r="B288" s="2">
@@ -12233,7 +12194,6 @@
         <v>38</v>
       </c>
       <c r="H288" s="3"/>
-      <c r="I288" s="7"/>
       <c r="J288" s="3"/>
       <c r="K288" s="6" t="s">
         <v>539</v>
@@ -12243,14 +12203,9 @@
       <c r="N288" s="3"/>
       <c r="O288" s="3"/>
       <c r="P288" s="3"/>
-      <c r="Q288" s="7"/>
-      <c r="R288" s="7"/>
-      <c r="S288" s="7"/>
-      <c r="T288" s="7"/>
-      <c r="U288" s="7"/>
-    </row>
-    <row r="289" spans="1:21" ht="15">
-      <c r="A289" s="7">
+    </row>
+    <row r="289" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A289">
         <v>311</v>
       </c>
       <c r="B289" s="2">
@@ -12272,7 +12227,6 @@
         <v>41</v>
       </c>
       <c r="H289" s="3"/>
-      <c r="I289" s="7"/>
       <c r="J289" s="3"/>
       <c r="K289" s="6"/>
       <c r="L289" s="3"/>
@@ -12282,14 +12236,9 @@
       <c r="P289" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="Q289" s="7"/>
-      <c r="R289" s="7"/>
-      <c r="S289" s="7"/>
-      <c r="T289" s="7"/>
-      <c r="U289" s="7"/>
-    </row>
-    <row r="290" spans="1:21" ht="15">
-      <c r="A290" s="7">
+    </row>
+    <row r="290" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A290">
         <v>312</v>
       </c>
       <c r="B290" s="2">
@@ -12311,7 +12260,6 @@
         <v>38</v>
       </c>
       <c r="H290" s="3"/>
-      <c r="I290" s="7"/>
       <c r="J290" s="3"/>
       <c r="K290" s="6" t="s">
         <v>541</v>
@@ -12321,14 +12269,9 @@
       <c r="N290" s="3"/>
       <c r="O290" s="3"/>
       <c r="P290" s="3"/>
-      <c r="Q290" s="7"/>
-      <c r="R290" s="7"/>
-      <c r="S290" s="7"/>
-      <c r="T290" s="7"/>
-      <c r="U290" s="7"/>
-    </row>
-    <row r="291" spans="1:21" ht="15">
-      <c r="A291" s="7">
+    </row>
+    <row r="291" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A291">
         <v>313</v>
       </c>
       <c r="B291" s="2">
@@ -12350,7 +12293,7 @@
         <v>60</v>
       </c>
       <c r="H291" s="3"/>
-      <c r="I291" s="7" t="s">
+      <c r="I291" t="s">
         <v>61</v>
       </c>
       <c r="J291" s="3" t="s">
@@ -12362,14 +12305,9 @@
       <c r="N291" s="3"/>
       <c r="O291" s="3"/>
       <c r="P291" s="3"/>
-      <c r="Q291" s="7"/>
-      <c r="R291" s="7"/>
-      <c r="S291" s="7"/>
-      <c r="T291" s="7"/>
-      <c r="U291" s="7"/>
-    </row>
-    <row r="292" spans="1:21" ht="15">
-      <c r="A292" s="7">
+    </row>
+    <row r="292" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A292">
         <v>314</v>
       </c>
       <c r="B292" s="2">
@@ -12391,7 +12329,6 @@
         <v>106</v>
       </c>
       <c r="H292" s="3"/>
-      <c r="I292" s="7"/>
       <c r="J292" s="3"/>
       <c r="K292" s="6"/>
       <c r="L292" s="3"/>
@@ -12399,16 +12336,12 @@
       <c r="N292" s="3"/>
       <c r="O292" s="3"/>
       <c r="P292" s="3"/>
-      <c r="Q292" s="7" t="s">
+      <c r="Q292" t="s">
         <v>107</v>
       </c>
-      <c r="R292" s="7"/>
-      <c r="S292" s="7"/>
-      <c r="T292" s="7"/>
-      <c r="U292" s="7"/>
-    </row>
-    <row r="293" spans="1:21" ht="15">
-      <c r="A293" s="7">
+    </row>
+    <row r="293" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A293">
         <v>315</v>
       </c>
       <c r="B293" s="2">
@@ -12430,7 +12363,6 @@
         <v>106</v>
       </c>
       <c r="H293" s="3"/>
-      <c r="I293" s="7"/>
       <c r="J293" s="3"/>
       <c r="K293" s="6"/>
       <c r="L293" s="3"/>
@@ -12438,16 +12370,12 @@
       <c r="N293" s="3"/>
       <c r="O293" s="3"/>
       <c r="P293" s="3"/>
-      <c r="Q293" s="7" t="s">
+      <c r="Q293" t="s">
         <v>107</v>
       </c>
-      <c r="R293" s="7"/>
-      <c r="S293" s="7"/>
-      <c r="T293" s="7"/>
-      <c r="U293" s="7"/>
-    </row>
-    <row r="294" spans="1:21" ht="15">
-      <c r="A294" s="7">
+    </row>
+    <row r="294" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A294">
         <v>316</v>
       </c>
       <c r="B294" s="2">
@@ -12469,7 +12397,6 @@
         <v>33</v>
       </c>
       <c r="H294" s="3"/>
-      <c r="I294" s="7"/>
       <c r="J294" s="3"/>
       <c r="K294" s="6"/>
       <c r="L294" s="3"/>
@@ -12479,13 +12406,8 @@
         <v>543</v>
       </c>
       <c r="P294" s="3"/>
-      <c r="Q294" s="7"/>
-      <c r="R294" s="7"/>
-      <c r="S294" s="7"/>
-      <c r="T294" s="7"/>
-      <c r="U294" s="7"/>
-    </row>
-    <row r="295" spans="1:21" ht="15">
+    </row>
+    <row r="295" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A295" s="7">
         <v>317</v>
       </c>
@@ -12526,7 +12448,7 @@
       <c r="T295" s="7"/>
       <c r="U295" s="7"/>
     </row>
-    <row r="296" spans="1:21" ht="15">
+    <row r="296" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A296" s="7">
         <v>318</v>
       </c>
@@ -12565,206 +12487,6 @@
       <c r="T296" s="7"/>
       <c r="U296" s="7"/>
     </row>
-    <row r="297" spans="1:21" ht="15">
-      <c r="A297" s="7">
-        <v>319</v>
-      </c>
-      <c r="B297" s="2">
-        <v>46268.572835648098</v>
-      </c>
-      <c r="C297" s="2">
-        <v>46268.573634259301</v>
-      </c>
-      <c r="D297" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="E297" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="F297" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="G297" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H297" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="I297" s="7"/>
-      <c r="J297" s="3"/>
-      <c r="K297" s="6"/>
-      <c r="L297" s="3"/>
-      <c r="M297" s="3"/>
-      <c r="N297" s="3"/>
-      <c r="O297" s="3"/>
-      <c r="P297" s="3"/>
-      <c r="Q297" s="7"/>
-      <c r="R297" s="7"/>
-      <c r="S297" s="7"/>
-      <c r="T297" s="7"/>
-      <c r="U297" s="7"/>
-    </row>
-    <row r="298" spans="1:21" ht="15">
-      <c r="A298" s="7">
-        <v>320</v>
-      </c>
-      <c r="B298" s="2">
-        <v>46268.5700462963</v>
-      </c>
-      <c r="C298" s="2">
-        <v>46268.573877314797</v>
-      </c>
-      <c r="D298" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E298" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F298" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G298" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="H298" s="3"/>
-      <c r="I298" s="7"/>
-      <c r="J298" s="3"/>
-      <c r="K298" s="6"/>
-      <c r="L298" s="3"/>
-      <c r="M298" s="3"/>
-      <c r="N298" s="3"/>
-      <c r="O298" s="3"/>
-      <c r="P298" s="3"/>
-      <c r="Q298" s="7"/>
-      <c r="R298" s="7"/>
-      <c r="S298" s="7"/>
-      <c r="T298" s="7"/>
-      <c r="U298" s="7" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="299" spans="1:21" ht="15">
-      <c r="A299" s="7">
-        <v>321</v>
-      </c>
-      <c r="B299" s="2">
-        <v>46268.573750000003</v>
-      </c>
-      <c r="C299" s="2">
-        <v>46268.575104166703</v>
-      </c>
-      <c r="D299" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="E299" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="F299" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="G299" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="H299" s="3"/>
-      <c r="I299" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="J299" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="K299" s="6"/>
-      <c r="L299" s="3"/>
-      <c r="M299" s="3"/>
-      <c r="N299" s="3"/>
-      <c r="O299" s="3"/>
-      <c r="P299" s="3"/>
-      <c r="Q299" s="7"/>
-      <c r="R299" s="7"/>
-      <c r="S299" s="7"/>
-      <c r="T299" s="7"/>
-      <c r="U299" s="7"/>
-    </row>
-    <row r="300" spans="1:21" ht="15">
-      <c r="A300" s="7">
-        <v>322</v>
-      </c>
-      <c r="B300" s="2">
-        <v>46268.575138888897</v>
-      </c>
-      <c r="C300" s="2">
-        <v>46268.575520833299</v>
-      </c>
-      <c r="D300" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="E300" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="G300" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H300" s="3"/>
-      <c r="I300" s="7"/>
-      <c r="J300" s="3"/>
-      <c r="K300" s="6"/>
-      <c r="L300" s="3"/>
-      <c r="M300" s="3"/>
-      <c r="N300" s="3"/>
-      <c r="O300" s="3"/>
-      <c r="P300" s="3"/>
-      <c r="Q300" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="R300" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="S300" s="7"/>
-      <c r="T300" s="7"/>
-      <c r="U300" s="7"/>
-    </row>
-    <row r="301" spans="1:21" ht="15">
-      <c r="A301" s="7">
-        <v>323</v>
-      </c>
-      <c r="B301" s="2">
-        <v>46268.575567129599</v>
-      </c>
-      <c r="C301" s="2">
-        <v>46268.576122685197</v>
-      </c>
-      <c r="D301" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="E301" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="F301" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="G301" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H301" s="3"/>
-      <c r="I301" s="7"/>
-      <c r="J301" s="3"/>
-      <c r="K301" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="L301" s="3"/>
-      <c r="M301" s="3"/>
-      <c r="N301" s="3"/>
-      <c r="O301" s="3"/>
-      <c r="P301" s="3"/>
-      <c r="Q301" s="7"/>
-      <c r="R301" s="7"/>
-      <c r="S301" s="7"/>
-      <c r="T301" s="7"/>
-      <c r="U301" s="7"/>
-    </row>
-    <row r="302" spans="1:21" ht="15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="457" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ACB2FC0-7190-47D2-9CDB-413828CEE0A7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03122E5D-6915-4225-9754-381492BCCAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1818,7 +1818,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1831,10 +1831,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -13745,7 +13741,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="321" spans="1:23">
+    <row r="321" spans="1:20">
       <c r="A321">
         <v>343</v>
       </c>
@@ -13783,7 +13779,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="322" spans="1:23">
+    <row r="322" spans="1:20">
       <c r="A322">
         <v>344</v>
       </c>
@@ -13817,7 +13813,7 @@
       <c r="P322" s="2"/>
       <c r="R322" s="2"/>
     </row>
-    <row r="323" spans="1:23">
+    <row r="323" spans="1:20">
       <c r="A323">
         <v>345</v>
       </c>
@@ -13851,8 +13847,8 @@
       </c>
       <c r="R323" s="2"/>
     </row>
-    <row r="324" spans="1:23">
-      <c r="A324" s="8">
+    <row r="324" spans="1:20">
+      <c r="A324">
         <v>354</v>
       </c>
       <c r="B324" s="1">
@@ -13868,32 +13864,26 @@
         <v>226</v>
       </c>
       <c r="F324" s="7"/>
-      <c r="G324" s="9">
+      <c r="G324" s="6">
         <v>38859</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I324" s="2"/>
-      <c r="J324" s="8"/>
       <c r="K324" s="2"/>
       <c r="L324" s="4"/>
       <c r="M324" s="2"/>
       <c r="N324" s="2"/>
       <c r="O324" s="2"/>
       <c r="P324" s="2"/>
-      <c r="Q324" s="8"/>
       <c r="R324" s="2"/>
-      <c r="S324" s="8" t="s">
+      <c r="S324" t="s">
         <v>109</v>
       </c>
-      <c r="T324" s="8"/>
-      <c r="U324" s="8"/>
-      <c r="V324" s="8"/>
-      <c r="W324" s="8"/>
-    </row>
-    <row r="325" spans="1:23">
-      <c r="A325" s="8">
+    </row>
+    <row r="325" spans="1:20">
+      <c r="A325">
         <v>355</v>
       </c>
       <c r="B325" s="1">
@@ -13909,34 +13899,29 @@
         <v>102</v>
       </c>
       <c r="F325" s="7"/>
-      <c r="G325" s="9">
+      <c r="G325" s="6">
         <v>38656</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I325" s="2"/>
-      <c r="J325" s="8"/>
       <c r="K325" s="2"/>
       <c r="L325" s="4"/>
       <c r="M325" s="2"/>
       <c r="N325" s="2"/>
       <c r="O325" s="2"/>
       <c r="P325" s="2"/>
-      <c r="Q325" s="8"/>
       <c r="R325" s="2"/>
-      <c r="S325" s="8" t="s">
+      <c r="S325" t="s">
         <v>63</v>
       </c>
-      <c r="T325" s="8" t="s">
+      <c r="T325" t="s">
         <v>577</v>
       </c>
-      <c r="U325" s="8"/>
-      <c r="V325" s="8"/>
-      <c r="W325" s="8"/>
-    </row>
-    <row r="326" spans="1:23">
-      <c r="A326" s="8">
+    </row>
+    <row r="326" spans="1:20">
+      <c r="A326">
         <v>356</v>
       </c>
       <c r="B326" s="1">
@@ -13952,14 +13937,13 @@
         <v>336</v>
       </c>
       <c r="F326" s="7"/>
-      <c r="G326" s="9">
+      <c r="G326" s="6">
         <v>38811</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I326" s="2"/>
-      <c r="J326" s="8"/>
       <c r="K326" s="2"/>
       <c r="L326" s="4" t="s">
         <v>578</v>
@@ -13968,18 +13952,12 @@
       <c r="N326" s="2"/>
       <c r="O326" s="2"/>
       <c r="P326" s="2"/>
-      <c r="Q326" s="8"/>
       <c r="R326" s="2"/>
-      <c r="S326" s="8"/>
-      <c r="T326" s="8"/>
-      <c r="U326" s="8"/>
-      <c r="V326" s="8"/>
-      <c r="W326" s="8"/>
-    </row>
-    <row r="327" spans="1:23"/>
-    <row r="328" spans="1:23"/>
-    <row r="329" spans="1:23"/>
-    <row r="330" spans="1:23"/>
+    </row>
+    <row r="327" spans="1:20"/>
+    <row r="328" spans="1:20"/>
+    <row r="329" spans="1:20"/>
+    <row r="330" spans="1:20"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03122E5D-6915-4225-9754-381492BCCAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0762F891-E470-46EB-8915-6E84F7E62806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1741" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="582">
   <si>
     <t>Id</t>
   </si>
@@ -1773,6 +1773,15 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Plaza%20Tepe.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Samara%20Sat.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/77637881-DC91-45B6-AB36-93908365CBED-17812-00_Starbucks%20Samara%20Sat.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/D4C03A94-E2C6-4852-BCE9-9B1022A8FC2F_Starbucks%20Plaza%20Sate.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1818,7 +1827,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1831,6 +1840,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1921,8 +1934,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W326" totalsRowShown="0">
-  <autoFilter ref="A1:W326" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W329" totalsRowShown="0">
+  <autoFilter ref="A1:W329" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2089,7 +2102,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="356" latestEventMarker="623">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="359" latestEventMarker="626">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -13741,7 +13754,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="321" spans="1:20">
+    <row r="321" spans="1:23">
       <c r="A321">
         <v>343</v>
       </c>
@@ -13779,7 +13792,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="322" spans="1:20">
+    <row r="322" spans="1:23">
       <c r="A322">
         <v>344</v>
       </c>
@@ -13813,7 +13826,7 @@
       <c r="P322" s="2"/>
       <c r="R322" s="2"/>
     </row>
-    <row r="323" spans="1:20">
+    <row r="323" spans="1:23">
       <c r="A323">
         <v>345</v>
       </c>
@@ -13847,7 +13860,7 @@
       </c>
       <c r="R323" s="2"/>
     </row>
-    <row r="324" spans="1:20">
+    <row r="324" spans="1:23">
       <c r="A324">
         <v>354</v>
       </c>
@@ -13882,7 +13895,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="325" spans="1:20">
+    <row r="325" spans="1:23">
       <c r="A325">
         <v>355</v>
       </c>
@@ -13920,7 +13933,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="326" spans="1:20">
+    <row r="326" spans="1:23">
       <c r="A326">
         <v>356</v>
       </c>
@@ -13954,10 +13967,130 @@
       <c r="P326" s="2"/>
       <c r="R326" s="2"/>
     </row>
-    <row r="327" spans="1:20"/>
-    <row r="328" spans="1:20"/>
-    <row r="329" spans="1:20"/>
-    <row r="330" spans="1:20"/>
+    <row r="327" spans="1:23">
+      <c r="A327" s="8">
+        <v>357</v>
+      </c>
+      <c r="B327" s="1">
+        <v>46269.571666666699</v>
+      </c>
+      <c r="C327" s="1">
+        <v>46269.5730092593</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F327" s="7"/>
+      <c r="G327" s="9">
+        <v>43152</v>
+      </c>
+      <c r="H327" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I327" s="2"/>
+      <c r="J327" s="8"/>
+      <c r="K327" s="2"/>
+      <c r="L327" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="M327" s="2"/>
+      <c r="N327" s="2"/>
+      <c r="O327" s="2"/>
+      <c r="P327" s="2"/>
+      <c r="Q327" s="8"/>
+      <c r="R327" s="2"/>
+      <c r="S327" s="8"/>
+      <c r="T327" s="8"/>
+      <c r="U327" s="8"/>
+      <c r="V327" s="8"/>
+      <c r="W327" s="8"/>
+    </row>
+    <row r="328" spans="1:23">
+      <c r="A328" s="8">
+        <v>358</v>
+      </c>
+      <c r="B328" s="1">
+        <v>46269.574062500003</v>
+      </c>
+      <c r="C328" s="1">
+        <v>46269.577847222201</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F328" s="7"/>
+      <c r="G328" s="9">
+        <v>43152</v>
+      </c>
+      <c r="H328" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I328" s="2"/>
+      <c r="J328" s="8"/>
+      <c r="K328" s="2"/>
+      <c r="L328" s="4"/>
+      <c r="M328" s="2"/>
+      <c r="N328" s="2"/>
+      <c r="O328" s="2"/>
+      <c r="P328" s="2"/>
+      <c r="Q328" s="8"/>
+      <c r="R328" s="2"/>
+      <c r="S328" s="8"/>
+      <c r="T328" s="8"/>
+      <c r="U328" s="8"/>
+      <c r="V328" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="W328" s="8"/>
+    </row>
+    <row r="329" spans="1:23">
+      <c r="A329" s="8">
+        <v>359</v>
+      </c>
+      <c r="B329" s="1">
+        <v>46269.430081018501</v>
+      </c>
+      <c r="C329" s="1">
+        <v>46269.580949074101</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E329" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F329" s="7"/>
+      <c r="G329" s="9">
+        <v>38859</v>
+      </c>
+      <c r="H329" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I329" s="2"/>
+      <c r="J329" s="8"/>
+      <c r="K329" s="2"/>
+      <c r="L329" s="4"/>
+      <c r="M329" s="2"/>
+      <c r="N329" s="2"/>
+      <c r="O329" s="2"/>
+      <c r="P329" s="2"/>
+      <c r="Q329" s="8"/>
+      <c r="R329" s="2"/>
+      <c r="S329" s="8"/>
+      <c r="T329" s="8"/>
+      <c r="U329" s="8"/>
+      <c r="V329" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="W329" s="8"/>
+    </row>
+    <row r="330" spans="1:23"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0762F891-E470-46EB-8915-6E84F7E62806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F4043E4-D444-450D-B8D1-F72087914B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1753" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="583">
   <si>
     <t>Id</t>
   </si>
@@ -1782,6 +1782,9 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/D4C03A94-E2C6-4852-BCE9-9B1022A8FC2F_Starbucks%20Plaza%20Sate.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/image_Starbucks%20Plaza%20Sate.jpg</t>
   </si>
 </sst>
 </file>
@@ -1934,8 +1937,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W329" totalsRowShown="0">
-  <autoFilter ref="A1:W329" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W330" totalsRowShown="0">
+  <autoFilter ref="A1:W330" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2102,7 +2105,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="359" latestEventMarker="626">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="360" latestEventMarker="627">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -14090,7 +14093,47 @@
       </c>
       <c r="W329" s="8"/>
     </row>
-    <row r="330" spans="1:23"/>
+    <row r="330" spans="1:23">
+      <c r="A330" s="8">
+        <v>360</v>
+      </c>
+      <c r="B330" s="1">
+        <v>46269.580995370401</v>
+      </c>
+      <c r="C330" s="1">
+        <v>46269.585324074098</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F330" s="7"/>
+      <c r="G330" s="9">
+        <v>38859</v>
+      </c>
+      <c r="H330" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I330" s="2"/>
+      <c r="J330" s="8"/>
+      <c r="K330" s="2"/>
+      <c r="L330" s="4"/>
+      <c r="M330" s="2"/>
+      <c r="N330" s="2"/>
+      <c r="O330" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="P330" s="2"/>
+      <c r="Q330" s="8"/>
+      <c r="R330" s="2"/>
+      <c r="S330" s="8"/>
+      <c r="T330" s="8"/>
+      <c r="U330" s="8"/>
+      <c r="V330" s="8"/>
+      <c r="W330" s="8"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F4043E4-D444-450D-B8D1-F72087914B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{68DD37FC-05F6-42BC-A921-3DEB205032DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="584">
   <si>
     <t>Id</t>
   </si>
@@ -1785,6 +1785,9 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/image_Starbucks%20Plaza%20Sate.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/tempImage4GFBTV_Starbucks%20Tlalnepant.jpg</t>
   </si>
 </sst>
 </file>
@@ -1937,8 +1940,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W330" totalsRowShown="0">
-  <autoFilter ref="A1:W330" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W331" totalsRowShown="0">
+  <autoFilter ref="A1:W331" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2105,7 +2108,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="360" latestEventMarker="627">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="361" latestEventMarker="628">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2434,7 +2437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W330"/>
+  <dimension ref="A1:W331"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -13971,7 +13974,7 @@
       <c r="R326" s="2"/>
     </row>
     <row r="327" spans="1:23">
-      <c r="A327" s="8">
+      <c r="A327">
         <v>357</v>
       </c>
       <c r="B327" s="1">
@@ -13987,14 +13990,13 @@
         <v>177</v>
       </c>
       <c r="F327" s="7"/>
-      <c r="G327" s="9">
+      <c r="G327" s="6">
         <v>43152</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I327" s="2"/>
-      <c r="J327" s="8"/>
       <c r="K327" s="2"/>
       <c r="L327" s="4" t="s">
         <v>579</v>
@@ -14003,16 +14005,10 @@
       <c r="N327" s="2"/>
       <c r="O327" s="2"/>
       <c r="P327" s="2"/>
-      <c r="Q327" s="8"/>
       <c r="R327" s="2"/>
-      <c r="S327" s="8"/>
-      <c r="T327" s="8"/>
-      <c r="U327" s="8"/>
-      <c r="V327" s="8"/>
-      <c r="W327" s="8"/>
     </row>
     <row r="328" spans="1:23">
-      <c r="A328" s="8">
+      <c r="A328">
         <v>358</v>
       </c>
       <c r="B328" s="1">
@@ -14028,32 +14024,26 @@
         <v>177</v>
       </c>
       <c r="F328" s="7"/>
-      <c r="G328" s="9">
+      <c r="G328" s="6">
         <v>43152</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>288</v>
       </c>
       <c r="I328" s="2"/>
-      <c r="J328" s="8"/>
       <c r="K328" s="2"/>
       <c r="L328" s="4"/>
       <c r="M328" s="2"/>
       <c r="N328" s="2"/>
       <c r="O328" s="2"/>
       <c r="P328" s="2"/>
-      <c r="Q328" s="8"/>
       <c r="R328" s="2"/>
-      <c r="S328" s="8"/>
-      <c r="T328" s="8"/>
-      <c r="U328" s="8"/>
-      <c r="V328" s="8" t="s">
+      <c r="V328" t="s">
         <v>580</v>
       </c>
-      <c r="W328" s="8"/>
     </row>
     <row r="329" spans="1:23">
-      <c r="A329" s="8">
+      <c r="A329">
         <v>359</v>
       </c>
       <c r="B329" s="1">
@@ -14069,32 +14059,26 @@
         <v>226</v>
       </c>
       <c r="F329" s="7"/>
-      <c r="G329" s="9">
+      <c r="G329" s="6">
         <v>38859</v>
       </c>
       <c r="H329" s="2" t="s">
         <v>288</v>
       </c>
       <c r="I329" s="2"/>
-      <c r="J329" s="8"/>
       <c r="K329" s="2"/>
       <c r="L329" s="4"/>
       <c r="M329" s="2"/>
       <c r="N329" s="2"/>
       <c r="O329" s="2"/>
       <c r="P329" s="2"/>
-      <c r="Q329" s="8"/>
       <c r="R329" s="2"/>
-      <c r="S329" s="8"/>
-      <c r="T329" s="8"/>
-      <c r="U329" s="8"/>
-      <c r="V329" s="8" t="s">
+      <c r="V329" t="s">
         <v>581</v>
       </c>
-      <c r="W329" s="8"/>
     </row>
     <row r="330" spans="1:23">
-      <c r="A330" s="8">
+      <c r="A330">
         <v>360</v>
       </c>
       <c r="B330" s="1">
@@ -14110,14 +14094,13 @@
         <v>226</v>
       </c>
       <c r="F330" s="7"/>
-      <c r="G330" s="9">
+      <c r="G330" s="6">
         <v>38859</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I330" s="2"/>
-      <c r="J330" s="8"/>
       <c r="K330" s="2"/>
       <c r="L330" s="4"/>
       <c r="M330" s="2"/>
@@ -14126,13 +14109,48 @@
         <v>582</v>
       </c>
       <c r="P330" s="2"/>
-      <c r="Q330" s="8"/>
       <c r="R330" s="2"/>
-      <c r="S330" s="8"/>
-      <c r="T330" s="8"/>
-      <c r="U330" s="8"/>
-      <c r="V330" s="8"/>
-      <c r="W330" s="8"/>
+    </row>
+    <row r="331" spans="1:23" ht="15" customHeight="1">
+      <c r="A331" s="8">
+        <v>361</v>
+      </c>
+      <c r="B331" s="1">
+        <v>46269.603206018503</v>
+      </c>
+      <c r="C331" s="1">
+        <v>46269.604756944398</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E331" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F331" s="7"/>
+      <c r="G331" s="9">
+        <v>38606</v>
+      </c>
+      <c r="H331" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I331" s="2"/>
+      <c r="J331" s="8"/>
+      <c r="K331" s="2"/>
+      <c r="L331" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="M331" s="2"/>
+      <c r="N331" s="2"/>
+      <c r="O331" s="2"/>
+      <c r="P331" s="2"/>
+      <c r="Q331" s="8"/>
+      <c r="R331" s="2"/>
+      <c r="S331" s="8"/>
+      <c r="T331" s="8"/>
+      <c r="U331" s="8"/>
+      <c r="V331" s="8"/>
+      <c r="W331" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68DD37FC-05F6-42BC-A921-3DEB205032DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D4D86A1-4403-4411-AC25-488C64CDC1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="585">
   <si>
     <t>Id</t>
   </si>
@@ -1788,6 +1788,9 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/tempImage4GFBTV_Starbucks%20Tlalnepant.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/1788554948149872242229798504483_Sergio%20Daniel%20Parra.jpg</t>
   </si>
 </sst>
 </file>
@@ -1833,7 +1836,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1846,10 +1849,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1940,8 +1939,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W331" totalsRowShown="0">
-  <autoFilter ref="A1:W331" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W332" totalsRowShown="0">
+  <autoFilter ref="A1:W332" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2108,7 +2107,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="361" latestEventMarker="628">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="362" latestEventMarker="629">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2437,7 +2436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W331"/>
+  <dimension ref="A1:W332"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -13760,7 +13759,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="321" spans="1:23">
+    <row r="321" spans="1:22">
       <c r="A321">
         <v>343</v>
       </c>
@@ -13798,7 +13797,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="322" spans="1:23">
+    <row r="322" spans="1:22">
       <c r="A322">
         <v>344</v>
       </c>
@@ -13832,7 +13831,7 @@
       <c r="P322" s="2"/>
       <c r="R322" s="2"/>
     </row>
-    <row r="323" spans="1:23">
+    <row r="323" spans="1:22">
       <c r="A323">
         <v>345</v>
       </c>
@@ -13866,7 +13865,7 @@
       </c>
       <c r="R323" s="2"/>
     </row>
-    <row r="324" spans="1:23">
+    <row r="324" spans="1:22">
       <c r="A324">
         <v>354</v>
       </c>
@@ -13901,7 +13900,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="325" spans="1:23">
+    <row r="325" spans="1:22">
       <c r="A325">
         <v>355</v>
       </c>
@@ -13939,7 +13938,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="326" spans="1:23">
+    <row r="326" spans="1:22">
       <c r="A326">
         <v>356</v>
       </c>
@@ -13973,7 +13972,7 @@
       <c r="P326" s="2"/>
       <c r="R326" s="2"/>
     </row>
-    <row r="327" spans="1:23">
+    <row r="327" spans="1:22">
       <c r="A327">
         <v>357</v>
       </c>
@@ -14007,7 +14006,7 @@
       <c r="P327" s="2"/>
       <c r="R327" s="2"/>
     </row>
-    <row r="328" spans="1:23">
+    <row r="328" spans="1:22">
       <c r="A328">
         <v>358</v>
       </c>
@@ -14042,7 +14041,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="329" spans="1:23">
+    <row r="329" spans="1:22">
       <c r="A329">
         <v>359</v>
       </c>
@@ -14077,7 +14076,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="330" spans="1:23">
+    <row r="330" spans="1:22">
       <c r="A330">
         <v>360</v>
       </c>
@@ -14111,8 +14110,8 @@
       <c r="P330" s="2"/>
       <c r="R330" s="2"/>
     </row>
-    <row r="331" spans="1:23" ht="15" customHeight="1">
-      <c r="A331" s="8">
+    <row r="331" spans="1:22" ht="15" customHeight="1">
+      <c r="A331">
         <v>361</v>
       </c>
       <c r="B331" s="1">
@@ -14128,14 +14127,13 @@
         <v>172</v>
       </c>
       <c r="F331" s="7"/>
-      <c r="G331" s="9">
+      <c r="G331" s="6">
         <v>38606</v>
       </c>
       <c r="H331" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I331" s="2"/>
-      <c r="J331" s="8"/>
       <c r="K331" s="2"/>
       <c r="L331" s="4" t="s">
         <v>583</v>
@@ -14144,13 +14142,41 @@
       <c r="N331" s="2"/>
       <c r="O331" s="2"/>
       <c r="P331" s="2"/>
-      <c r="Q331" s="8"/>
       <c r="R331" s="2"/>
-      <c r="S331" s="8"/>
-      <c r="T331" s="8"/>
-      <c r="U331" s="8"/>
-      <c r="V331" s="8"/>
-      <c r="W331" s="8"/>
+    </row>
+    <row r="332" spans="1:22" ht="15" customHeight="1">
+      <c r="A332">
+        <v>362</v>
+      </c>
+      <c r="B332" s="1">
+        <v>46269.617337962998</v>
+      </c>
+      <c r="C332" s="1">
+        <v>46269.617719907401</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E332" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F332" s="7"/>
+      <c r="G332" s="6">
+        <v>38561</v>
+      </c>
+      <c r="H332" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I332" s="2"/>
+      <c r="K332" s="2"/>
+      <c r="L332" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="M332" s="2"/>
+      <c r="N332" s="2"/>
+      <c r="O332" s="2"/>
+      <c r="P332" s="2"/>
+      <c r="R332" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D4D86A1-4403-4411-AC25-488C64CDC1F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="494" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41784C8C-E8CB-489F-AE1F-DF832F1DEBC7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="593">
   <si>
     <t>Id</t>
   </si>
@@ -1791,6 +1791,30 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/1788554948149872242229798504483_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Gustavo%20Ba.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Gustavo%20Ba.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/image_Starbucks%20Gustavo%20Ba.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/449B2D8B-6CC9-4185-8738-B3D9B03C0C25_Starbucks%20Gustavo%20Ba.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/604FF46D-6839-4C78-A9F0-C6A330CB3A2A_Starbucks%20Gustavo%20Ba.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/E4F70B6D-476F-42B2-A3E4-1661B63F0AA8_Starbucks%20Gustavo%20Ba.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20CC%20Plaza%20S.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG-20260904-WA0019_Fany%20Jeovana%20Echever.jpg</t>
   </si>
 </sst>
 </file>
@@ -1836,7 +1860,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1849,6 +1873,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1939,8 +1967,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W332" totalsRowShown="0">
-  <autoFilter ref="A1:W332" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W340" totalsRowShown="0">
+  <autoFilter ref="A1:W340" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2107,7 +2135,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="362" latestEventMarker="629">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="370" latestEventMarker="637">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2436,7 +2464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W332"/>
+  <dimension ref="A1:W340"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -13759,7 +13787,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="321" spans="1:22">
+    <row r="321" spans="1:23">
       <c r="A321">
         <v>343</v>
       </c>
@@ -13797,7 +13825,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="322" spans="1:22">
+    <row r="322" spans="1:23">
       <c r="A322">
         <v>344</v>
       </c>
@@ -13831,7 +13859,7 @@
       <c r="P322" s="2"/>
       <c r="R322" s="2"/>
     </row>
-    <row r="323" spans="1:22">
+    <row r="323" spans="1:23">
       <c r="A323">
         <v>345</v>
       </c>
@@ -13865,7 +13893,7 @@
       </c>
       <c r="R323" s="2"/>
     </row>
-    <row r="324" spans="1:22">
+    <row r="324" spans="1:23">
       <c r="A324">
         <v>354</v>
       </c>
@@ -13900,7 +13928,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="325" spans="1:22">
+    <row r="325" spans="1:23">
       <c r="A325">
         <v>355</v>
       </c>
@@ -13938,7 +13966,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="326" spans="1:22">
+    <row r="326" spans="1:23">
       <c r="A326">
         <v>356</v>
       </c>
@@ -13972,7 +14000,7 @@
       <c r="P326" s="2"/>
       <c r="R326" s="2"/>
     </row>
-    <row r="327" spans="1:22">
+    <row r="327" spans="1:23">
       <c r="A327">
         <v>357</v>
       </c>
@@ -14006,7 +14034,7 @@
       <c r="P327" s="2"/>
       <c r="R327" s="2"/>
     </row>
-    <row r="328" spans="1:22">
+    <row r="328" spans="1:23">
       <c r="A328">
         <v>358</v>
       </c>
@@ -14041,7 +14069,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="329" spans="1:22">
+    <row r="329" spans="1:23">
       <c r="A329">
         <v>359</v>
       </c>
@@ -14076,7 +14104,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="330" spans="1:22">
+    <row r="330" spans="1:23">
       <c r="A330">
         <v>360</v>
       </c>
@@ -14110,7 +14138,7 @@
       <c r="P330" s="2"/>
       <c r="R330" s="2"/>
     </row>
-    <row r="331" spans="1:22" ht="15" customHeight="1">
+    <row r="331" spans="1:23" ht="15" customHeight="1">
       <c r="A331">
         <v>361</v>
       </c>
@@ -14144,7 +14172,7 @@
       <c r="P331" s="2"/>
       <c r="R331" s="2"/>
     </row>
-    <row r="332" spans="1:22" ht="15" customHeight="1">
+    <row r="332" spans="1:23" ht="15" customHeight="1">
       <c r="A332">
         <v>362</v>
       </c>
@@ -14177,6 +14205,314 @@
       <c r="O332" s="2"/>
       <c r="P332" s="2"/>
       <c r="R332" s="2"/>
+    </row>
+    <row r="333" spans="1:23" ht="15" customHeight="1">
+      <c r="A333">
+        <v>363</v>
+      </c>
+      <c r="B333" s="1">
+        <v>46269.660162036998</v>
+      </c>
+      <c r="C333" s="1">
+        <v>46269.660567129598</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F333" s="7"/>
+      <c r="G333" s="6">
+        <v>38770</v>
+      </c>
+      <c r="H333" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I333" s="2"/>
+      <c r="K333" s="2"/>
+      <c r="L333" s="4"/>
+      <c r="M333" s="2"/>
+      <c r="N333" s="2"/>
+      <c r="O333" s="2"/>
+      <c r="P333" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="R333" s="2"/>
+    </row>
+    <row r="334" spans="1:23" ht="15" customHeight="1">
+      <c r="A334">
+        <v>364</v>
+      </c>
+      <c r="B334" s="1">
+        <v>46269.661597222199</v>
+      </c>
+      <c r="C334" s="1">
+        <v>46269.662673611099</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F334" s="7"/>
+      <c r="G334" s="6">
+        <v>38770</v>
+      </c>
+      <c r="H334" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I334" s="2"/>
+      <c r="K334" s="2"/>
+      <c r="L334" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="M334" s="2"/>
+      <c r="N334" s="2"/>
+      <c r="O334" s="2"/>
+      <c r="P334" s="2"/>
+      <c r="R334" s="2"/>
+    </row>
+    <row r="335" spans="1:23" ht="15" customHeight="1">
+      <c r="A335">
+        <v>365</v>
+      </c>
+      <c r="B335" s="1">
+        <v>46269.6628009259</v>
+      </c>
+      <c r="C335" s="1">
+        <v>46269.667557870402</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E335" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F335" s="7"/>
+      <c r="G335" s="6">
+        <v>38770</v>
+      </c>
+      <c r="H335" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I335" s="2"/>
+      <c r="K335" s="2"/>
+      <c r="L335" s="4"/>
+      <c r="M335" s="2"/>
+      <c r="N335" s="2"/>
+      <c r="O335" s="2"/>
+      <c r="P335" s="2"/>
+      <c r="R335" s="2"/>
+      <c r="V335" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="336" spans="1:23" ht="15" customHeight="1">
+      <c r="A336" s="8">
+        <v>366</v>
+      </c>
+      <c r="B336" s="1">
+        <v>46269.667997685203</v>
+      </c>
+      <c r="C336" s="1">
+        <v>46269.674236111103</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F336" s="7"/>
+      <c r="G336" s="9">
+        <v>38770</v>
+      </c>
+      <c r="H336" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I336" s="2"/>
+      <c r="J336" s="8"/>
+      <c r="K336" s="2"/>
+      <c r="L336" s="4"/>
+      <c r="M336" s="2"/>
+      <c r="N336" s="2"/>
+      <c r="O336" s="2"/>
+      <c r="P336" s="2"/>
+      <c r="Q336" s="8"/>
+      <c r="R336" s="2"/>
+      <c r="S336" s="8"/>
+      <c r="T336" s="8"/>
+      <c r="U336" s="8"/>
+      <c r="V336" s="8"/>
+      <c r="W336" s="8" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="337" spans="1:23" ht="15" customHeight="1">
+      <c r="A337" s="8">
+        <v>367</v>
+      </c>
+      <c r="B337" s="1">
+        <v>46269.6817592593</v>
+      </c>
+      <c r="C337" s="1">
+        <v>46269.682870370401</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E337" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F337" s="7"/>
+      <c r="G337" s="9">
+        <v>38770</v>
+      </c>
+      <c r="H337" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I337" s="2"/>
+      <c r="J337" s="8"/>
+      <c r="K337" s="2"/>
+      <c r="L337" s="4"/>
+      <c r="M337" s="2"/>
+      <c r="N337" s="2"/>
+      <c r="O337" s="2"/>
+      <c r="P337" s="2"/>
+      <c r="Q337" s="8"/>
+      <c r="R337" s="2"/>
+      <c r="S337" s="8"/>
+      <c r="T337" s="8"/>
+      <c r="U337" s="8"/>
+      <c r="V337" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="W337" s="8"/>
+    </row>
+    <row r="338" spans="1:23" ht="15" customHeight="1">
+      <c r="A338" s="8">
+        <v>368</v>
+      </c>
+      <c r="B338" s="1">
+        <v>46269.683680555601</v>
+      </c>
+      <c r="C338" s="1">
+        <v>46269.690995370402</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E338" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F338" s="7"/>
+      <c r="G338" s="9">
+        <v>38770</v>
+      </c>
+      <c r="H338" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I338" s="2"/>
+      <c r="J338" s="8"/>
+      <c r="K338" s="2"/>
+      <c r="L338" s="4"/>
+      <c r="M338" s="2"/>
+      <c r="N338" s="2"/>
+      <c r="O338" s="2"/>
+      <c r="P338" s="2"/>
+      <c r="Q338" s="8"/>
+      <c r="R338" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="S338" s="8"/>
+      <c r="T338" s="8"/>
+      <c r="U338" s="8"/>
+      <c r="V338" s="8"/>
+      <c r="W338" s="8"/>
+    </row>
+    <row r="339" spans="1:23" ht="15" customHeight="1">
+      <c r="A339" s="8">
+        <v>369</v>
+      </c>
+      <c r="B339" s="1">
+        <v>46269.7656712963</v>
+      </c>
+      <c r="C339" s="1">
+        <v>46269.767384259299</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F339" s="7"/>
+      <c r="G339" s="9">
+        <v>38427</v>
+      </c>
+      <c r="H339" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I339" s="2"/>
+      <c r="J339" s="8"/>
+      <c r="K339" s="2"/>
+      <c r="L339" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="M339" s="2"/>
+      <c r="N339" s="2"/>
+      <c r="O339" s="2"/>
+      <c r="P339" s="2"/>
+      <c r="Q339" s="8"/>
+      <c r="R339" s="2"/>
+      <c r="S339" s="8"/>
+      <c r="T339" s="8"/>
+      <c r="U339" s="8"/>
+      <c r="V339" s="8"/>
+      <c r="W339" s="8"/>
+    </row>
+    <row r="340" spans="1:23" ht="15" customHeight="1">
+      <c r="A340" s="8">
+        <v>370</v>
+      </c>
+      <c r="B340" s="1">
+        <v>46269.914432870399</v>
+      </c>
+      <c r="C340" s="1">
+        <v>46269.915115740703</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F340" s="7"/>
+      <c r="G340" s="9">
+        <v>38529</v>
+      </c>
+      <c r="H340" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I340" s="2"/>
+      <c r="J340" s="8"/>
+      <c r="K340" s="2"/>
+      <c r="L340" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="M340" s="2"/>
+      <c r="N340" s="2"/>
+      <c r="O340" s="2"/>
+      <c r="P340" s="2"/>
+      <c r="Q340" s="8"/>
+      <c r="R340" s="2"/>
+      <c r="S340" s="8"/>
+      <c r="T340" s="8"/>
+      <c r="U340" s="8"/>
+      <c r="V340" s="8"/>
+      <c r="W340" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="494" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41784C8C-E8CB-489F-AE1F-DF832F1DEBC7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{573BEA49-46E1-46B6-B7F9-665526B7709A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1909" uniqueCount="620">
   <si>
     <t>Id</t>
   </si>
@@ -1815,6 +1815,87 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG-20260904-WA0019_Fany%20Jeovana%20Echever.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Plaza%20Las.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/17886394169909160235633164055208_Starbucks%20CC%20Coalcal.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_9320_Luis%20Javier%20Perez%20Mo.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/17886397788937423535907483567847_Starbucks%20CC%20Coalcal.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/2CD491FC-7EE5-49C4-9101-DE7B818F26BC_Luis%20Javier%20Perez%20Mo.jpeg</t>
+  </si>
+  <si>
+    <t>diego.conde@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Diego Conde Merino</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/1788640034758807631619559867257_Diego%20Conde%20Merino.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/6AD52E0D-9163-4157-A165-4C0CBC9F7E4E_Luis%20Javier%20Perez%20Mo.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/17886402341237422908394977108879_Diego%20Conde%20Merino.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/Screenshot_20260905_143131_Files%20by%20Google_Diego%20Conde%20Merino.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17886404808591749302941338929157_Starbucks%20CC%20Coalcal.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/17886408066858641893297510548828_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/C92A4618-D3A5-4823-8CBF-1AD285746931_Luis%20Javier%20Perez%20Mo.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17886410047936037737254724727295_Starbucks%20CC%20Coalcal.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/8A032FEF-0839-47F7-9F4F-CBCE9AA32000_Starbucks%20Plaza%20Las.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/A92C30A6-5DE0-4BA6-A4F5-4BA68A644BD8_Starbucks%20Plaza%20Las.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/F1C952F4-AFB4-44B7-948D-C668BE421487_Starbucks%20Plaza%20Las.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/image_Starbucks%20Plaza%20Las.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Plaza%20Las.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/image_Starbucks%20Plaza%20Las.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/Picsart_26-09-05_15-30-56-023_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/21BD8321-581E-46F4-AC5A-5B48995EFCC8_Luis%20Javier%20Perez%20Mo.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/Picsart_26-09-05_16-35-04-116_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17886625512234388451212248496328_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG-20260905-WA0040_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Plaza%20Sate.jpg</t>
   </si>
 </sst>
 </file>
@@ -1860,7 +1941,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1873,10 +1954,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1967,8 +2044,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W340" totalsRowShown="0">
-  <autoFilter ref="A1:W340" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W368" totalsRowShown="0">
+  <autoFilter ref="A1:W368" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2135,7 +2212,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="370" latestEventMarker="637">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="398" latestEventMarker="665">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2464,7 +2541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W340"/>
+  <dimension ref="A1:W368"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -14310,7 +14387,7 @@
       </c>
     </row>
     <row r="336" spans="1:23" ht="15" customHeight="1">
-      <c r="A336" s="8">
+      <c r="A336">
         <v>366</v>
       </c>
       <c r="B336" s="1">
@@ -14326,32 +14403,26 @@
         <v>185</v>
       </c>
       <c r="F336" s="7"/>
-      <c r="G336" s="9">
+      <c r="G336" s="6">
         <v>38770</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>290</v>
       </c>
       <c r="I336" s="2"/>
-      <c r="J336" s="8"/>
       <c r="K336" s="2"/>
       <c r="L336" s="4"/>
       <c r="M336" s="2"/>
       <c r="N336" s="2"/>
       <c r="O336" s="2"/>
       <c r="P336" s="2"/>
-      <c r="Q336" s="8"/>
       <c r="R336" s="2"/>
-      <c r="S336" s="8"/>
-      <c r="T336" s="8"/>
-      <c r="U336" s="8"/>
-      <c r="V336" s="8"/>
-      <c r="W336" s="8" t="s">
+      <c r="W336" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="15" customHeight="1">
-      <c r="A337" s="8">
+    <row r="337" spans="1:22" ht="15" customHeight="1">
+      <c r="A337">
         <v>367</v>
       </c>
       <c r="B337" s="1">
@@ -14367,32 +14438,26 @@
         <v>185</v>
       </c>
       <c r="F337" s="7"/>
-      <c r="G337" s="9">
+      <c r="G337" s="6">
         <v>38770</v>
       </c>
       <c r="H337" s="2" t="s">
         <v>288</v>
       </c>
       <c r="I337" s="2"/>
-      <c r="J337" s="8"/>
       <c r="K337" s="2"/>
       <c r="L337" s="4"/>
       <c r="M337" s="2"/>
       <c r="N337" s="2"/>
       <c r="O337" s="2"/>
       <c r="P337" s="2"/>
-      <c r="Q337" s="8"/>
       <c r="R337" s="2"/>
-      <c r="S337" s="8"/>
-      <c r="T337" s="8"/>
-      <c r="U337" s="8"/>
-      <c r="V337" s="8" t="s">
+      <c r="V337" t="s">
         <v>589</v>
       </c>
-      <c r="W337" s="8"/>
-    </row>
-    <row r="338" spans="1:23" ht="15" customHeight="1">
-      <c r="A338" s="8">
+    </row>
+    <row r="338" spans="1:22" ht="15" customHeight="1">
+      <c r="A338">
         <v>368</v>
       </c>
       <c r="B338" s="1">
@@ -14408,32 +14473,25 @@
         <v>185</v>
       </c>
       <c r="F338" s="7"/>
-      <c r="G338" s="9">
+      <c r="G338" s="6">
         <v>38770</v>
       </c>
       <c r="H338" s="2" t="s">
         <v>43</v>
       </c>
       <c r="I338" s="2"/>
-      <c r="J338" s="8"/>
       <c r="K338" s="2"/>
       <c r="L338" s="4"/>
       <c r="M338" s="2"/>
       <c r="N338" s="2"/>
       <c r="O338" s="2"/>
       <c r="P338" s="2"/>
-      <c r="Q338" s="8"/>
       <c r="R338" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="S338" s="8"/>
-      <c r="T338" s="8"/>
-      <c r="U338" s="8"/>
-      <c r="V338" s="8"/>
-      <c r="W338" s="8"/>
-    </row>
-    <row r="339" spans="1:23" ht="15" customHeight="1">
-      <c r="A339" s="8">
+    </row>
+    <row r="339" spans="1:22" ht="15" customHeight="1">
+      <c r="A339">
         <v>369</v>
       </c>
       <c r="B339" s="1">
@@ -14449,14 +14507,13 @@
         <v>189</v>
       </c>
       <c r="F339" s="7"/>
-      <c r="G339" s="9">
+      <c r="G339" s="6">
         <v>38427</v>
       </c>
       <c r="H339" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I339" s="2"/>
-      <c r="J339" s="8"/>
       <c r="K339" s="2"/>
       <c r="L339" s="4" t="s">
         <v>591</v>
@@ -14465,16 +14522,10 @@
       <c r="N339" s="2"/>
       <c r="O339" s="2"/>
       <c r="P339" s="2"/>
-      <c r="Q339" s="8"/>
       <c r="R339" s="2"/>
-      <c r="S339" s="8"/>
-      <c r="T339" s="8"/>
-      <c r="U339" s="8"/>
-      <c r="V339" s="8"/>
-      <c r="W339" s="8"/>
-    </row>
-    <row r="340" spans="1:23" ht="15" customHeight="1">
-      <c r="A340" s="8">
+    </row>
+    <row r="340" spans="1:22" ht="15" customHeight="1">
+      <c r="A340">
         <v>370</v>
       </c>
       <c r="B340" s="1">
@@ -14490,14 +14541,13 @@
         <v>365</v>
       </c>
       <c r="F340" s="7"/>
-      <c r="G340" s="9">
+      <c r="G340" s="6">
         <v>38529</v>
       </c>
       <c r="H340" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I340" s="2"/>
-      <c r="J340" s="8"/>
       <c r="K340" s="2"/>
       <c r="L340" s="4" t="s">
         <v>592</v>
@@ -14506,13 +14556,967 @@
       <c r="N340" s="2"/>
       <c r="O340" s="2"/>
       <c r="P340" s="2"/>
-      <c r="Q340" s="8"/>
       <c r="R340" s="2"/>
-      <c r="S340" s="8"/>
-      <c r="T340" s="8"/>
-      <c r="U340" s="8"/>
-      <c r="V340" s="8"/>
-      <c r="W340" s="8"/>
+    </row>
+    <row r="341" spans="1:22" ht="15" customHeight="1">
+      <c r="A341">
+        <v>371</v>
+      </c>
+      <c r="B341" s="1">
+        <v>46270.592476851903</v>
+      </c>
+      <c r="C341" s="1">
+        <v>46270.594328703701</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E341" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F341" s="7"/>
+      <c r="G341" s="6">
+        <v>38546</v>
+      </c>
+      <c r="H341" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I341" s="2"/>
+      <c r="K341" s="2"/>
+      <c r="L341" s="4"/>
+      <c r="M341" s="2"/>
+      <c r="N341" s="2"/>
+      <c r="O341" s="2"/>
+      <c r="P341" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="R341" s="2"/>
+    </row>
+    <row r="342" spans="1:22" ht="15" customHeight="1">
+      <c r="A342">
+        <v>372</v>
+      </c>
+      <c r="B342" s="1">
+        <v>46270.5944675926</v>
+      </c>
+      <c r="C342" s="1">
+        <v>46270.596354166701</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E342" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F342" s="7"/>
+      <c r="G342" s="6">
+        <v>38401</v>
+      </c>
+      <c r="H342" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I342" s="2"/>
+      <c r="K342" s="2"/>
+      <c r="L342" s="4"/>
+      <c r="M342" s="2"/>
+      <c r="N342" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="O342" s="2"/>
+      <c r="P342" s="2"/>
+      <c r="R342" s="2"/>
+    </row>
+    <row r="343" spans="1:22" ht="15" customHeight="1">
+      <c r="A343">
+        <v>373</v>
+      </c>
+      <c r="B343" s="1">
+        <v>46270.599745370397</v>
+      </c>
+      <c r="C343" s="1">
+        <v>46270.600474537001</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E343" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F343" s="7"/>
+      <c r="G343" s="6">
+        <v>43193</v>
+      </c>
+      <c r="H343" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I343" s="2"/>
+      <c r="K343" s="2"/>
+      <c r="L343" s="4"/>
+      <c r="M343" s="2"/>
+      <c r="N343" s="2"/>
+      <c r="O343" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="P343" s="2"/>
+      <c r="R343" s="2"/>
+    </row>
+    <row r="344" spans="1:22" ht="15" customHeight="1">
+      <c r="A344">
+        <v>374</v>
+      </c>
+      <c r="B344" s="1">
+        <v>46270.592604166697</v>
+      </c>
+      <c r="C344" s="1">
+        <v>46270.601354166698</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E344" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F344" s="7"/>
+      <c r="G344" s="6">
+        <v>38401</v>
+      </c>
+      <c r="H344" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I344" s="2"/>
+      <c r="K344" s="2"/>
+      <c r="L344" s="4"/>
+      <c r="M344" s="2"/>
+      <c r="N344" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="O344" s="2"/>
+      <c r="P344" s="2"/>
+      <c r="R344" s="2"/>
+    </row>
+    <row r="345" spans="1:22" ht="15" customHeight="1">
+      <c r="A345">
+        <v>375</v>
+      </c>
+      <c r="B345" s="1">
+        <v>46270.600509259297</v>
+      </c>
+      <c r="C345" s="1">
+        <v>46270.602037037002</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F345" s="7"/>
+      <c r="G345" s="6">
+        <v>43193</v>
+      </c>
+      <c r="H345" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I345" s="2"/>
+      <c r="K345" s="2"/>
+      <c r="L345" s="4"/>
+      <c r="M345" s="2"/>
+      <c r="N345" s="2"/>
+      <c r="O345" s="2"/>
+      <c r="P345" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="R345" s="2"/>
+    </row>
+    <row r="346" spans="1:22" ht="15" customHeight="1">
+      <c r="A346">
+        <v>376</v>
+      </c>
+      <c r="B346" s="1">
+        <v>46270.6020601852</v>
+      </c>
+      <c r="C346" s="1">
+        <v>46270.602222222202</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E346" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F346" s="7"/>
+      <c r="G346" s="6">
+        <v>43193</v>
+      </c>
+      <c r="H346" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I346" s="2"/>
+      <c r="K346" s="2"/>
+      <c r="L346" s="4"/>
+      <c r="M346" s="2"/>
+      <c r="N346" s="2"/>
+      <c r="O346" s="2"/>
+      <c r="P346" s="2"/>
+      <c r="R346" s="2"/>
+      <c r="S346" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="347" spans="1:22" ht="15" customHeight="1">
+      <c r="A347">
+        <v>377</v>
+      </c>
+      <c r="B347" s="1">
+        <v>46270.6019675926</v>
+      </c>
+      <c r="C347" s="1">
+        <v>46270.602546296301</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E347" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="F347" s="7"/>
+      <c r="G347" s="6">
+        <v>38339</v>
+      </c>
+      <c r="H347" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I347" s="2"/>
+      <c r="K347" s="2"/>
+      <c r="L347" s="4"/>
+      <c r="M347" s="2"/>
+      <c r="N347" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="O347" s="2"/>
+      <c r="P347" s="2"/>
+      <c r="R347" s="2"/>
+    </row>
+    <row r="348" spans="1:22" ht="15" customHeight="1">
+      <c r="A348">
+        <v>378</v>
+      </c>
+      <c r="B348" s="1">
+        <v>46270.602245370399</v>
+      </c>
+      <c r="C348" s="1">
+        <v>46270.603761574101</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E348" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F348" s="7"/>
+      <c r="G348" s="6">
+        <v>43193</v>
+      </c>
+      <c r="H348" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I348" s="2"/>
+      <c r="K348" s="2"/>
+      <c r="L348" s="4"/>
+      <c r="M348" s="2"/>
+      <c r="N348" s="2"/>
+      <c r="O348" s="2"/>
+      <c r="P348" s="2"/>
+      <c r="R348" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="349" spans="1:22" ht="15" customHeight="1">
+      <c r="A349">
+        <v>379</v>
+      </c>
+      <c r="B349" s="1">
+        <v>46270.604386574101</v>
+      </c>
+      <c r="C349" s="1">
+        <v>46270.604861111096</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E349" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="F349" s="7"/>
+      <c r="G349" s="6">
+        <v>38339</v>
+      </c>
+      <c r="H349" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I349" s="2"/>
+      <c r="K349" s="2"/>
+      <c r="L349" s="4"/>
+      <c r="M349" s="2"/>
+      <c r="N349" s="2"/>
+      <c r="O349" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="P349" s="2"/>
+      <c r="R349" s="2"/>
+    </row>
+    <row r="350" spans="1:22" ht="15" customHeight="1">
+      <c r="A350">
+        <v>380</v>
+      </c>
+      <c r="B350" s="1">
+        <v>46270.605300925898</v>
+      </c>
+      <c r="C350" s="1">
+        <v>46270.605729166702</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E350" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="F350" s="7"/>
+      <c r="G350" s="6">
+        <v>38339</v>
+      </c>
+      <c r="H350" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I350" s="2"/>
+      <c r="K350" s="2"/>
+      <c r="L350" s="4"/>
+      <c r="M350" s="2"/>
+      <c r="N350" s="2"/>
+      <c r="O350" s="2"/>
+      <c r="P350" s="2"/>
+      <c r="R350" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="351" spans="1:22" ht="15" customHeight="1">
+      <c r="A351">
+        <v>381</v>
+      </c>
+      <c r="B351" s="1">
+        <v>46270.601689814801</v>
+      </c>
+      <c r="C351" s="1">
+        <v>46270.607951388898</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E351" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F351" s="7"/>
+      <c r="G351" s="6">
+        <v>38401</v>
+      </c>
+      <c r="H351" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I351" s="2"/>
+      <c r="K351" s="2"/>
+      <c r="L351" s="4"/>
+      <c r="M351" s="2"/>
+      <c r="N351" s="2"/>
+      <c r="O351" s="2"/>
+      <c r="P351" s="2"/>
+      <c r="R351" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="352" spans="1:22" ht="15" customHeight="1">
+      <c r="A352">
+        <v>382</v>
+      </c>
+      <c r="B352" s="1">
+        <v>46270.610937500001</v>
+      </c>
+      <c r="C352" s="1">
+        <v>46270.611932870401</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E352" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F352" s="7"/>
+      <c r="G352" s="6">
+        <v>38515</v>
+      </c>
+      <c r="H352" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I352" s="2"/>
+      <c r="K352" s="2"/>
+      <c r="L352" s="4"/>
+      <c r="M352" s="2"/>
+      <c r="N352" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="O352" s="2"/>
+      <c r="P352" s="2"/>
+      <c r="R352" s="2"/>
+    </row>
+    <row r="353" spans="1:23" ht="15" customHeight="1">
+      <c r="A353">
+        <v>383</v>
+      </c>
+      <c r="B353" s="1">
+        <v>46270.612719907404</v>
+      </c>
+      <c r="C353" s="1">
+        <v>46270.612881944398</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E353" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F353" s="7"/>
+      <c r="G353" s="6">
+        <v>43193</v>
+      </c>
+      <c r="H353" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I353" s="2"/>
+      <c r="K353" s="2"/>
+      <c r="L353" s="4"/>
+      <c r="M353" s="2"/>
+      <c r="N353" s="2"/>
+      <c r="O353" s="2"/>
+      <c r="P353" s="2"/>
+      <c r="R353" s="2"/>
+      <c r="W353" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="354" spans="1:23" ht="15" customHeight="1">
+      <c r="A354">
+        <v>384</v>
+      </c>
+      <c r="B354" s="1">
+        <v>46270.612743055601</v>
+      </c>
+      <c r="C354" s="1">
+        <v>46270.613854166702</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F354" s="7"/>
+      <c r="G354" s="6">
+        <v>38401</v>
+      </c>
+      <c r="H354" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I354" s="2"/>
+      <c r="K354" s="2"/>
+      <c r="L354" s="4"/>
+      <c r="M354" s="2"/>
+      <c r="N354" s="2"/>
+      <c r="O354" s="2"/>
+      <c r="P354" s="2"/>
+      <c r="R354" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="355" spans="1:23" ht="15" customHeight="1">
+      <c r="A355">
+        <v>385</v>
+      </c>
+      <c r="B355" s="1">
+        <v>46270.594375000001</v>
+      </c>
+      <c r="C355" s="1">
+        <v>46270.620509259301</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F355" s="7"/>
+      <c r="G355" s="6">
+        <v>38456</v>
+      </c>
+      <c r="H355" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I355" s="2"/>
+      <c r="K355" s="2"/>
+      <c r="L355" s="4"/>
+      <c r="M355" s="2"/>
+      <c r="N355" s="2"/>
+      <c r="O355" s="2"/>
+      <c r="P355" s="2"/>
+      <c r="R355" s="2"/>
+      <c r="W355" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="356" spans="1:23" ht="15" customHeight="1">
+      <c r="A356">
+        <v>386</v>
+      </c>
+      <c r="B356" s="1">
+        <v>46270.620543981502</v>
+      </c>
+      <c r="C356" s="1">
+        <v>46270.621759259302</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E356" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F356" s="7"/>
+      <c r="G356" s="6">
+        <v>38456</v>
+      </c>
+      <c r="H356" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I356" s="2"/>
+      <c r="K356" s="2"/>
+      <c r="L356" s="4"/>
+      <c r="M356" s="2"/>
+      <c r="N356" s="2"/>
+      <c r="O356" s="2"/>
+      <c r="P356" s="2"/>
+      <c r="R356" s="2"/>
+      <c r="V356" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="357" spans="1:23" ht="15" customHeight="1">
+      <c r="A357">
+        <v>387</v>
+      </c>
+      <c r="B357" s="1">
+        <v>46270.621886574103</v>
+      </c>
+      <c r="C357" s="1">
+        <v>46270.622731481497</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F357" s="7"/>
+      <c r="G357" s="6">
+        <v>38456</v>
+      </c>
+      <c r="H357" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I357" s="2"/>
+      <c r="K357" s="2"/>
+      <c r="L357" s="4"/>
+      <c r="M357" s="2"/>
+      <c r="N357" s="2"/>
+      <c r="O357" s="2"/>
+      <c r="P357" s="2"/>
+      <c r="R357" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="358" spans="1:23" ht="15" customHeight="1">
+      <c r="A358">
+        <v>388</v>
+      </c>
+      <c r="B358" s="1">
+        <v>46270.6227546296</v>
+      </c>
+      <c r="C358" s="1">
+        <v>46270.623090277797</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E358" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F358" s="7"/>
+      <c r="G358" s="6">
+        <v>38456</v>
+      </c>
+      <c r="H358" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I358" s="2"/>
+      <c r="K358" s="2"/>
+      <c r="L358" s="4"/>
+      <c r="M358" s="2"/>
+      <c r="N358" s="2"/>
+      <c r="O358" s="2"/>
+      <c r="P358" s="2"/>
+      <c r="R358" s="2"/>
+      <c r="S358" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="359" spans="1:23" ht="15" customHeight="1">
+      <c r="A359">
+        <v>389</v>
+      </c>
+      <c r="B359" s="1">
+        <v>46270.623136574097</v>
+      </c>
+      <c r="C359" s="1">
+        <v>46270.624085648102</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E359" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F359" s="7"/>
+      <c r="G359" s="6">
+        <v>38456</v>
+      </c>
+      <c r="H359" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I359" s="2"/>
+      <c r="K359" s="2"/>
+      <c r="L359" s="4"/>
+      <c r="M359" s="2"/>
+      <c r="N359" s="2"/>
+      <c r="O359" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="P359" s="2"/>
+      <c r="R359" s="2"/>
+    </row>
+    <row r="360" spans="1:23" ht="15" customHeight="1">
+      <c r="A360">
+        <v>390</v>
+      </c>
+      <c r="B360" s="1">
+        <v>46270.624618055597</v>
+      </c>
+      <c r="C360" s="1">
+        <v>46270.624942129602</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E360" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F360" s="7"/>
+      <c r="G360" s="6">
+        <v>38456</v>
+      </c>
+      <c r="H360" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I360" s="2"/>
+      <c r="K360" s="2"/>
+      <c r="L360" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="M360" s="2"/>
+      <c r="N360" s="2"/>
+      <c r="O360" s="2"/>
+      <c r="P360" s="2"/>
+      <c r="R360" s="2"/>
+    </row>
+    <row r="361" spans="1:23" ht="15" customHeight="1">
+      <c r="A361">
+        <v>391</v>
+      </c>
+      <c r="B361" s="1">
+        <v>46270.6250462963</v>
+      </c>
+      <c r="C361" s="1">
+        <v>46270.625625000001</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E361" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F361" s="7"/>
+      <c r="G361" s="6">
+        <v>38456</v>
+      </c>
+      <c r="H361" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I361" s="2"/>
+      <c r="K361" s="2"/>
+      <c r="L361" s="4"/>
+      <c r="M361" s="2"/>
+      <c r="N361" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="O361" s="2"/>
+      <c r="P361" s="2"/>
+      <c r="R361" s="2"/>
+    </row>
+    <row r="362" spans="1:23" ht="15" customHeight="1">
+      <c r="A362">
+        <v>392</v>
+      </c>
+      <c r="B362" s="1">
+        <v>46270.622997685197</v>
+      </c>
+      <c r="C362" s="1">
+        <v>46270.627766203703</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E362" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F362" s="7"/>
+      <c r="G362" s="6">
+        <v>38604</v>
+      </c>
+      <c r="H362" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I362" s="2"/>
+      <c r="K362" s="2"/>
+      <c r="L362" s="4"/>
+      <c r="M362" s="2"/>
+      <c r="N362" s="2"/>
+      <c r="O362" s="2"/>
+      <c r="P362" s="2"/>
+      <c r="R362" s="2"/>
+      <c r="S362" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="363" spans="1:23" ht="15" customHeight="1">
+      <c r="A363">
+        <v>393</v>
+      </c>
+      <c r="B363" s="1">
+        <v>46270.648553240702</v>
+      </c>
+      <c r="C363" s="1">
+        <v>46270.6491087963</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E363" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F363" s="7"/>
+      <c r="G363" s="6">
+        <v>38604</v>
+      </c>
+      <c r="H363" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I363" s="2"/>
+      <c r="K363" s="2"/>
+      <c r="L363" s="4"/>
+      <c r="M363" s="2"/>
+      <c r="N363" s="2"/>
+      <c r="O363" s="2"/>
+      <c r="P363" s="2"/>
+      <c r="R363" s="2"/>
+      <c r="W363" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="364" spans="1:23" ht="15" customHeight="1">
+      <c r="A364">
+        <v>394</v>
+      </c>
+      <c r="B364" s="1">
+        <v>46270.817175925898</v>
+      </c>
+      <c r="C364" s="1">
+        <v>46270.818680555603</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E364" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F364" s="7"/>
+      <c r="G364" s="6">
+        <v>43193</v>
+      </c>
+      <c r="H364" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I364" s="2"/>
+      <c r="K364" s="2"/>
+      <c r="L364" s="4"/>
+      <c r="M364" s="2"/>
+      <c r="N364" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="O364" s="2"/>
+      <c r="P364" s="2"/>
+      <c r="R364" s="2"/>
+    </row>
+    <row r="365" spans="1:23" ht="15" customHeight="1">
+      <c r="A365">
+        <v>395</v>
+      </c>
+      <c r="B365" s="1">
+        <v>46270.8301041667</v>
+      </c>
+      <c r="C365" s="1">
+        <v>46270.830543981501</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E365" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F365" s="7"/>
+      <c r="G365" s="6">
+        <v>38604</v>
+      </c>
+      <c r="H365" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I365" s="2"/>
+      <c r="K365" s="2"/>
+      <c r="L365" s="4"/>
+      <c r="M365" s="2"/>
+      <c r="N365" s="2"/>
+      <c r="O365" s="2"/>
+      <c r="P365" s="2"/>
+      <c r="R365" s="2"/>
+      <c r="V365" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="366" spans="1:23" ht="15" customHeight="1">
+      <c r="A366">
+        <v>396</v>
+      </c>
+      <c r="B366" s="1">
+        <v>46270.862615740698</v>
+      </c>
+      <c r="C366" s="1">
+        <v>46270.864201388897</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E366" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F366" s="7"/>
+      <c r="G366" s="6">
+        <v>38604</v>
+      </c>
+      <c r="H366" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I366" s="2"/>
+      <c r="K366" s="2"/>
+      <c r="L366" s="4"/>
+      <c r="M366" s="2"/>
+      <c r="N366" s="2"/>
+      <c r="O366" s="2"/>
+      <c r="P366" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="R366" s="2"/>
+    </row>
+    <row r="367" spans="1:23" ht="15" customHeight="1">
+      <c r="A367">
+        <v>397</v>
+      </c>
+      <c r="B367" s="1">
+        <v>46270.869178240697</v>
+      </c>
+      <c r="C367" s="1">
+        <v>46270.869942129597</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F367" s="7"/>
+      <c r="G367" s="6">
+        <v>38604</v>
+      </c>
+      <c r="H367" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I367" s="2"/>
+      <c r="K367" s="2"/>
+      <c r="L367" s="4"/>
+      <c r="M367" s="2"/>
+      <c r="N367" s="2"/>
+      <c r="O367" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="P367" s="2"/>
+      <c r="R367" s="2"/>
+    </row>
+    <row r="368" spans="1:23" ht="15" customHeight="1">
+      <c r="A368">
+        <v>398</v>
+      </c>
+      <c r="B368" s="1">
+        <v>46270.882349537002</v>
+      </c>
+      <c r="C368" s="1">
+        <v>46270.883449074099</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E368" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F368" s="7"/>
+      <c r="G368" s="6">
+        <v>38859</v>
+      </c>
+      <c r="H368" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I368" s="2"/>
+      <c r="K368" s="2"/>
+      <c r="L368" s="4"/>
+      <c r="M368" s="2"/>
+      <c r="N368" s="2"/>
+      <c r="O368" s="2"/>
+      <c r="P368" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="R368" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{573BEA49-46E1-46B6-B7F9-665526B7709A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17DB7E8D-7758-474A-B279-3E2B5927762E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1909" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1925" uniqueCount="624">
   <si>
     <t>Id</t>
   </si>
@@ -1896,6 +1896,18 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Plaza%20Sate.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/Picsart_26-09-06_14-48-31-593_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/Picsart_26-09-06_14-49-28-478_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG-20260906-WA0011_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG-20260906-WA0013_Starbucks%20Cosmopol.jpg</t>
   </si>
 </sst>
 </file>
@@ -1941,7 +1953,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1954,6 +1966,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2044,8 +2060,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W368" totalsRowShown="0">
-  <autoFilter ref="A1:W368" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W372" totalsRowShown="0">
+  <autoFilter ref="A1:W372" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2212,7 +2228,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="398" latestEventMarker="665">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="402" latestEventMarker="669">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2541,7 +2557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W368"/>
+  <dimension ref="A1:W372"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -15518,6 +15534,170 @@
       </c>
       <c r="R368" s="2"/>
     </row>
+    <row r="369" spans="1:23" ht="15" customHeight="1">
+      <c r="A369" s="8">
+        <v>399</v>
+      </c>
+      <c r="B369" s="1">
+        <v>46271.618148148104</v>
+      </c>
+      <c r="C369" s="1">
+        <v>46271.6188541667</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E369" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F369" s="7"/>
+      <c r="G369" s="9">
+        <v>38515</v>
+      </c>
+      <c r="H369" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I369" s="2"/>
+      <c r="J369" s="8"/>
+      <c r="K369" s="2"/>
+      <c r="L369" s="4"/>
+      <c r="M369" s="2"/>
+      <c r="N369" s="2"/>
+      <c r="O369" s="2"/>
+      <c r="P369" s="2"/>
+      <c r="Q369" s="8"/>
+      <c r="R369" s="2"/>
+      <c r="S369" s="8"/>
+      <c r="T369" s="8"/>
+      <c r="U369" s="8"/>
+      <c r="V369" s="8"/>
+      <c r="W369" s="8" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="370" spans="1:23" ht="15" customHeight="1">
+      <c r="A370" s="8">
+        <v>400</v>
+      </c>
+      <c r="B370" s="1">
+        <v>46271.619189814803</v>
+      </c>
+      <c r="C370" s="1">
+        <v>46271.619583333297</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F370" s="7"/>
+      <c r="G370" s="9">
+        <v>38515</v>
+      </c>
+      <c r="H370" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I370" s="2"/>
+      <c r="J370" s="8"/>
+      <c r="K370" s="2"/>
+      <c r="L370" s="4"/>
+      <c r="M370" s="2"/>
+      <c r="N370" s="2"/>
+      <c r="O370" s="2"/>
+      <c r="P370" s="2"/>
+      <c r="Q370" s="8"/>
+      <c r="R370" s="2"/>
+      <c r="S370" s="8"/>
+      <c r="T370" s="8"/>
+      <c r="U370" s="8"/>
+      <c r="V370" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="W370" s="8"/>
+    </row>
+    <row r="371" spans="1:23" ht="15" customHeight="1">
+      <c r="A371" s="8">
+        <v>401</v>
+      </c>
+      <c r="B371" s="1">
+        <v>46271.672337962998</v>
+      </c>
+      <c r="C371" s="1">
+        <v>46271.672488425902</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E371" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F371" s="7"/>
+      <c r="G371" s="9">
+        <v>38604</v>
+      </c>
+      <c r="H371" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I371" s="2"/>
+      <c r="J371" s="8"/>
+      <c r="K371" s="2"/>
+      <c r="L371" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="M371" s="2"/>
+      <c r="N371" s="2"/>
+      <c r="O371" s="2"/>
+      <c r="P371" s="2"/>
+      <c r="Q371" s="8"/>
+      <c r="R371" s="2"/>
+      <c r="S371" s="8"/>
+      <c r="T371" s="8"/>
+      <c r="U371" s="8"/>
+      <c r="V371" s="8"/>
+      <c r="W371" s="8"/>
+    </row>
+    <row r="372" spans="1:23" ht="15" customHeight="1">
+      <c r="A372" s="8">
+        <v>402</v>
+      </c>
+      <c r="B372" s="1">
+        <v>46271.677974537</v>
+      </c>
+      <c r="C372" s="1">
+        <v>46271.678414351903</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E372" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F372" s="7"/>
+      <c r="G372" s="9">
+        <v>38604</v>
+      </c>
+      <c r="H372" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I372" s="2"/>
+      <c r="J372" s="8"/>
+      <c r="K372" s="2"/>
+      <c r="L372" s="4"/>
+      <c r="M372" s="2"/>
+      <c r="N372" s="2"/>
+      <c r="O372" s="2"/>
+      <c r="P372" s="2"/>
+      <c r="Q372" s="8"/>
+      <c r="R372" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="S372" s="8"/>
+      <c r="T372" s="8"/>
+      <c r="U372" s="8"/>
+      <c r="V372" s="8"/>
+      <c r="W372" s="8"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17DB7E8D-7758-474A-B279-3E2B5927762E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="514" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09846731-5FF9-4503-8E2E-B96686F0823F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1925" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="628">
   <si>
     <t>Id</t>
   </si>
@@ -1908,6 +1908,18 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG-20260906-WA0013_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/Picsart_26-09-06_17-57-37-140_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/1788739727317895779702940691672_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17887406613962135575800186175848_Starbucks%20CC%20Coalcal.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_0904_Starbucks%20Gustavo%20Ba.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2060,8 +2072,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W372" totalsRowShown="0">
-  <autoFilter ref="A1:W372" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W376" totalsRowShown="0">
+  <autoFilter ref="A1:W376" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2228,7 +2240,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="402" latestEventMarker="669">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="406" latestEventMarker="673">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2557,7 +2569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W372"/>
+  <dimension ref="A1:W376"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -15535,7 +15547,7 @@
       <c r="R368" s="2"/>
     </row>
     <row r="369" spans="1:23" ht="15" customHeight="1">
-      <c r="A369" s="8">
+      <c r="A369">
         <v>399</v>
       </c>
       <c r="B369" s="1">
@@ -15551,32 +15563,26 @@
         <v>239</v>
       </c>
       <c r="F369" s="7"/>
-      <c r="G369" s="9">
+      <c r="G369" s="6">
         <v>38515</v>
       </c>
       <c r="H369" s="2" t="s">
         <v>290</v>
       </c>
       <c r="I369" s="2"/>
-      <c r="J369" s="8"/>
       <c r="K369" s="2"/>
       <c r="L369" s="4"/>
       <c r="M369" s="2"/>
       <c r="N369" s="2"/>
       <c r="O369" s="2"/>
       <c r="P369" s="2"/>
-      <c r="Q369" s="8"/>
       <c r="R369" s="2"/>
-      <c r="S369" s="8"/>
-      <c r="T369" s="8"/>
-      <c r="U369" s="8"/>
-      <c r="V369" s="8"/>
-      <c r="W369" s="8" t="s">
+      <c r="W369" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="370" spans="1:23" ht="15" customHeight="1">
-      <c r="A370" s="8">
+      <c r="A370">
         <v>400</v>
       </c>
       <c r="B370" s="1">
@@ -15592,32 +15598,26 @@
         <v>239</v>
       </c>
       <c r="F370" s="7"/>
-      <c r="G370" s="9">
+      <c r="G370" s="6">
         <v>38515</v>
       </c>
       <c r="H370" s="2" t="s">
         <v>288</v>
       </c>
       <c r="I370" s="2"/>
-      <c r="J370" s="8"/>
       <c r="K370" s="2"/>
       <c r="L370" s="4"/>
       <c r="M370" s="2"/>
       <c r="N370" s="2"/>
       <c r="O370" s="2"/>
       <c r="P370" s="2"/>
-      <c r="Q370" s="8"/>
       <c r="R370" s="2"/>
-      <c r="S370" s="8"/>
-      <c r="T370" s="8"/>
-      <c r="U370" s="8"/>
-      <c r="V370" s="8" t="s">
+      <c r="V370" t="s">
         <v>621</v>
       </c>
-      <c r="W370" s="8"/>
     </row>
     <row r="371" spans="1:23" ht="15" customHeight="1">
-      <c r="A371" s="8">
+      <c r="A371">
         <v>401</v>
       </c>
       <c r="B371" s="1">
@@ -15633,14 +15633,13 @@
         <v>146</v>
       </c>
       <c r="F371" s="7"/>
-      <c r="G371" s="9">
+      <c r="G371" s="6">
         <v>38604</v>
       </c>
       <c r="H371" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I371" s="2"/>
-      <c r="J371" s="8"/>
       <c r="K371" s="2"/>
       <c r="L371" s="4" t="s">
         <v>622</v>
@@ -15649,16 +15648,10 @@
       <c r="N371" s="2"/>
       <c r="O371" s="2"/>
       <c r="P371" s="2"/>
-      <c r="Q371" s="8"/>
       <c r="R371" s="2"/>
-      <c r="S371" s="8"/>
-      <c r="T371" s="8"/>
-      <c r="U371" s="8"/>
-      <c r="V371" s="8"/>
-      <c r="W371" s="8"/>
     </row>
     <row r="372" spans="1:23" ht="15" customHeight="1">
-      <c r="A372" s="8">
+      <c r="A372">
         <v>402</v>
       </c>
       <c r="B372" s="1">
@@ -15674,29 +15667,186 @@
         <v>146</v>
       </c>
       <c r="F372" s="7"/>
-      <c r="G372" s="9">
+      <c r="G372" s="6">
         <v>38604</v>
       </c>
       <c r="H372" s="2" t="s">
         <v>43</v>
       </c>
       <c r="I372" s="2"/>
-      <c r="J372" s="8"/>
       <c r="K372" s="2"/>
       <c r="L372" s="4"/>
       <c r="M372" s="2"/>
       <c r="N372" s="2"/>
       <c r="O372" s="2"/>
       <c r="P372" s="2"/>
-      <c r="Q372" s="8"/>
       <c r="R372" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="S372" s="8"/>
-      <c r="T372" s="8"/>
-      <c r="U372" s="8"/>
-      <c r="V372" s="8"/>
-      <c r="W372" s="8"/>
+    </row>
+    <row r="373" spans="1:23" ht="15" customHeight="1">
+      <c r="A373" s="8">
+        <v>403</v>
+      </c>
+      <c r="B373" s="1">
+        <v>46271.748981481498</v>
+      </c>
+      <c r="C373" s="1">
+        <v>46271.749780092599</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E373" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F373" s="7"/>
+      <c r="G373" s="9">
+        <v>38604</v>
+      </c>
+      <c r="H373" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I373" s="2"/>
+      <c r="J373" s="8"/>
+      <c r="K373" s="2"/>
+      <c r="L373" s="4"/>
+      <c r="M373" s="2"/>
+      <c r="N373" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="O373" s="2"/>
+      <c r="P373" s="2"/>
+      <c r="Q373" s="8"/>
+      <c r="R373" s="2"/>
+      <c r="S373" s="8"/>
+      <c r="T373" s="8"/>
+      <c r="U373" s="8"/>
+      <c r="V373" s="8"/>
+      <c r="W373" s="8"/>
+    </row>
+    <row r="374" spans="1:23" ht="15" customHeight="1">
+      <c r="A374" s="8">
+        <v>404</v>
+      </c>
+      <c r="B374" s="1">
+        <v>46271.756006944401</v>
+      </c>
+      <c r="C374" s="1">
+        <v>46271.7563310185</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E374" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F374" s="7"/>
+      <c r="G374" s="9">
+        <v>38515</v>
+      </c>
+      <c r="H374" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I374" s="2"/>
+      <c r="J374" s="8"/>
+      <c r="K374" s="2"/>
+      <c r="L374" s="4"/>
+      <c r="M374" s="2"/>
+      <c r="N374" s="2"/>
+      <c r="O374" s="2"/>
+      <c r="P374" s="2"/>
+      <c r="Q374" s="8"/>
+      <c r="R374" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="S374" s="8"/>
+      <c r="T374" s="8"/>
+      <c r="U374" s="8"/>
+      <c r="V374" s="8"/>
+      <c r="W374" s="8"/>
+    </row>
+    <row r="375" spans="1:23" ht="15" customHeight="1">
+      <c r="A375" s="8">
+        <v>405</v>
+      </c>
+      <c r="B375" s="1">
+        <v>46271.766574074099</v>
+      </c>
+      <c r="C375" s="1">
+        <v>46271.767731481501</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E375" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F375" s="7"/>
+      <c r="G375" s="9">
+        <v>38401</v>
+      </c>
+      <c r="H375" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I375" s="2"/>
+      <c r="J375" s="8"/>
+      <c r="K375" s="2"/>
+      <c r="L375" s="4"/>
+      <c r="M375" s="2"/>
+      <c r="N375" s="2"/>
+      <c r="O375" s="2"/>
+      <c r="P375" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="Q375" s="8"/>
+      <c r="R375" s="2"/>
+      <c r="S375" s="8"/>
+      <c r="T375" s="8"/>
+      <c r="U375" s="8"/>
+      <c r="V375" s="8"/>
+      <c r="W375" s="8"/>
+    </row>
+    <row r="376" spans="1:23" ht="15" customHeight="1">
+      <c r="A376" s="8">
+        <v>406</v>
+      </c>
+      <c r="B376" s="1">
+        <v>46271.768379629597</v>
+      </c>
+      <c r="C376" s="1">
+        <v>46271.779016203698</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E376" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F376" s="7"/>
+      <c r="G376" s="9">
+        <v>38770</v>
+      </c>
+      <c r="H376" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I376" s="2"/>
+      <c r="J376" s="8"/>
+      <c r="K376" s="2"/>
+      <c r="L376" s="4"/>
+      <c r="M376" s="2"/>
+      <c r="N376" s="2"/>
+      <c r="O376" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="P376" s="2"/>
+      <c r="Q376" s="8"/>
+      <c r="R376" s="2"/>
+      <c r="S376" s="8"/>
+      <c r="T376" s="8"/>
+      <c r="U376" s="8"/>
+      <c r="V376" s="8"/>
+      <c r="W376" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="514" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09846731-5FF9-4503-8E2E-B96686F0823F}"/>
+  <xr:revisionPtr revIDLastSave="517" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E7E99AB-AA62-443F-A5DD-4CFA5A2BCD61}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="646">
   <si>
     <t>Id</t>
   </si>
@@ -1920,6 +1920,60 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_0904_Starbucks%20Gustavo%20Ba.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_5545_Starbucks%20Satelite.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/9A729A71-7627-4892-BF21-ED5E5C5061C8_Starbucks%20CC%20Plaza%20S.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG_5643_Starbucks%20CC%20Plaza%20S.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Luna%20Park.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/1788747067233360042900904479853_Starbucks%20DT%20Perifer.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/17887473300492506688684312010443_Starbucks%20DT%20Perifer.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/17887474604164927405576950043020_Starbucks%20DT%20Perifer.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_3605_Starbucks%20Galerias%20P.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Galerias%20P.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/IMG20260906203729_Starbucks%20DT%20Perifer.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/IMG_2411_Starbucks%20Mega%20Izcal.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG_2604_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/image_Starbucks%20Luna%20Park.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/8608b1d3-0a23-4bde-8437-22dc23a5767c_Starbucks%20Samara%20Sat.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_5651_Starbucks%20CC%20Plaza%20S.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_5654_Starbucks%20CC%20Plaza%20S.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/8031EDA3-058C-44C3-AF9C-5FA6F6C76130_Starbucks%20Samara%20Sat.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/ed825cca-9421-415e-9460-1ac29c24db58_Starbucks%20Samara%20Sat.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2072,8 +2126,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W376" totalsRowShown="0">
-  <autoFilter ref="A1:W376" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W394" totalsRowShown="0">
+  <autoFilter ref="A1:W394" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2240,7 +2294,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="406" latestEventMarker="673">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="424" latestEventMarker="691">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2569,7 +2623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W376"/>
+  <dimension ref="A1:W394"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -15685,7 +15739,7 @@
       </c>
     </row>
     <row r="373" spans="1:23" ht="15" customHeight="1">
-      <c r="A373" s="8">
+      <c r="A373">
         <v>403</v>
       </c>
       <c r="B373" s="1">
@@ -15701,14 +15755,13 @@
         <v>146</v>
       </c>
       <c r="F373" s="7"/>
-      <c r="G373" s="9">
+      <c r="G373" s="6">
         <v>38604</v>
       </c>
       <c r="H373" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I373" s="2"/>
-      <c r="J373" s="8"/>
       <c r="K373" s="2"/>
       <c r="L373" s="4"/>
       <c r="M373" s="2"/>
@@ -15717,16 +15770,10 @@
       </c>
       <c r="O373" s="2"/>
       <c r="P373" s="2"/>
-      <c r="Q373" s="8"/>
       <c r="R373" s="2"/>
-      <c r="S373" s="8"/>
-      <c r="T373" s="8"/>
-      <c r="U373" s="8"/>
-      <c r="V373" s="8"/>
-      <c r="W373" s="8"/>
     </row>
     <row r="374" spans="1:23" ht="15" customHeight="1">
-      <c r="A374" s="8">
+      <c r="A374">
         <v>404</v>
       </c>
       <c r="B374" s="1">
@@ -15742,32 +15789,25 @@
         <v>239</v>
       </c>
       <c r="F374" s="7"/>
-      <c r="G374" s="9">
+      <c r="G374" s="6">
         <v>38515</v>
       </c>
       <c r="H374" s="2" t="s">
         <v>43</v>
       </c>
       <c r="I374" s="2"/>
-      <c r="J374" s="8"/>
       <c r="K374" s="2"/>
       <c r="L374" s="4"/>
       <c r="M374" s="2"/>
       <c r="N374" s="2"/>
       <c r="O374" s="2"/>
       <c r="P374" s="2"/>
-      <c r="Q374" s="8"/>
       <c r="R374" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="S374" s="8"/>
-      <c r="T374" s="8"/>
-      <c r="U374" s="8"/>
-      <c r="V374" s="8"/>
-      <c r="W374" s="8"/>
     </row>
     <row r="375" spans="1:23" ht="15" customHeight="1">
-      <c r="A375" s="8">
+      <c r="A375">
         <v>405</v>
       </c>
       <c r="B375" s="1">
@@ -15783,14 +15823,13 @@
         <v>222</v>
       </c>
       <c r="F375" s="7"/>
-      <c r="G375" s="9">
+      <c r="G375" s="6">
         <v>38401</v>
       </c>
       <c r="H375" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I375" s="2"/>
-      <c r="J375" s="8"/>
       <c r="K375" s="2"/>
       <c r="L375" s="4"/>
       <c r="M375" s="2"/>
@@ -15799,16 +15838,10 @@
       <c r="P375" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="Q375" s="8"/>
       <c r="R375" s="2"/>
-      <c r="S375" s="8"/>
-      <c r="T375" s="8"/>
-      <c r="U375" s="8"/>
-      <c r="V375" s="8"/>
-      <c r="W375" s="8"/>
     </row>
     <row r="376" spans="1:23" ht="15" customHeight="1">
-      <c r="A376" s="8">
+      <c r="A376">
         <v>406</v>
       </c>
       <c r="B376" s="1">
@@ -15824,14 +15857,13 @@
         <v>185</v>
       </c>
       <c r="F376" s="7"/>
-      <c r="G376" s="9">
+      <c r="G376" s="6">
         <v>38770</v>
       </c>
       <c r="H376" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I376" s="2"/>
-      <c r="J376" s="8"/>
       <c r="K376" s="2"/>
       <c r="L376" s="4"/>
       <c r="M376" s="2"/>
@@ -15840,13 +15872,747 @@
         <v>627</v>
       </c>
       <c r="P376" s="2"/>
-      <c r="Q376" s="8"/>
       <c r="R376" s="2"/>
-      <c r="S376" s="8"/>
-      <c r="T376" s="8"/>
-      <c r="U376" s="8"/>
-      <c r="V376" s="8"/>
-      <c r="W376" s="8"/>
+    </row>
+    <row r="377" spans="1:23" ht="15" customHeight="1">
+      <c r="A377" s="8">
+        <v>407</v>
+      </c>
+      <c r="B377" s="1">
+        <v>46271.789247685199</v>
+      </c>
+      <c r="C377" s="1">
+        <v>46271.789791666699</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E377" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F377" s="7"/>
+      <c r="G377" s="9">
+        <v>38117</v>
+      </c>
+      <c r="H377" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I377" s="2"/>
+      <c r="J377" s="8"/>
+      <c r="K377" s="2"/>
+      <c r="L377" s="4"/>
+      <c r="M377" s="2"/>
+      <c r="N377" s="2"/>
+      <c r="O377" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="P377" s="2"/>
+      <c r="Q377" s="8"/>
+      <c r="R377" s="2"/>
+      <c r="S377" s="8"/>
+      <c r="T377" s="8"/>
+      <c r="U377" s="8"/>
+      <c r="V377" s="8"/>
+      <c r="W377" s="8"/>
+    </row>
+    <row r="378" spans="1:23" ht="15" customHeight="1">
+      <c r="A378" s="8">
+        <v>408</v>
+      </c>
+      <c r="B378" s="1">
+        <v>46271.825497685197</v>
+      </c>
+      <c r="C378" s="1">
+        <v>46271.828182870398</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E378" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F378" s="7"/>
+      <c r="G378" s="9">
+        <v>38427</v>
+      </c>
+      <c r="H378" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I378" s="2"/>
+      <c r="J378" s="8"/>
+      <c r="K378" s="2"/>
+      <c r="L378" s="4"/>
+      <c r="M378" s="2"/>
+      <c r="N378" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="O378" s="2"/>
+      <c r="P378" s="2"/>
+      <c r="Q378" s="8"/>
+      <c r="R378" s="2"/>
+      <c r="S378" s="8"/>
+      <c r="T378" s="8"/>
+      <c r="U378" s="8"/>
+      <c r="V378" s="8"/>
+      <c r="W378" s="8"/>
+    </row>
+    <row r="379" spans="1:23" ht="15" customHeight="1">
+      <c r="A379" s="8">
+        <v>409</v>
+      </c>
+      <c r="B379" s="1">
+        <v>46271.828449074099</v>
+      </c>
+      <c r="C379" s="1">
+        <v>46271.829502314802</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E379" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F379" s="7"/>
+      <c r="G379" s="9">
+        <v>38427</v>
+      </c>
+      <c r="H379" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I379" s="2"/>
+      <c r="J379" s="8"/>
+      <c r="K379" s="2"/>
+      <c r="L379" s="4"/>
+      <c r="M379" s="2"/>
+      <c r="N379" s="2"/>
+      <c r="O379" s="2"/>
+      <c r="P379" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="Q379" s="8"/>
+      <c r="R379" s="2"/>
+      <c r="S379" s="8"/>
+      <c r="T379" s="8"/>
+      <c r="U379" s="8"/>
+      <c r="V379" s="8"/>
+      <c r="W379" s="8"/>
+    </row>
+    <row r="380" spans="1:23" ht="15" customHeight="1">
+      <c r="A380" s="8">
+        <v>410</v>
+      </c>
+      <c r="B380" s="1">
+        <v>46271.8362037037</v>
+      </c>
+      <c r="C380" s="1">
+        <v>46271.839803240699</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E380" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F380" s="7"/>
+      <c r="G380" s="9">
+        <v>38368</v>
+      </c>
+      <c r="H380" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I380" s="2"/>
+      <c r="J380" s="8"/>
+      <c r="K380" s="2"/>
+      <c r="L380" s="4"/>
+      <c r="M380" s="2"/>
+      <c r="N380" s="2"/>
+      <c r="O380" s="2"/>
+      <c r="P380" s="2"/>
+      <c r="Q380" s="8"/>
+      <c r="R380" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="S380" s="8"/>
+      <c r="T380" s="8"/>
+      <c r="U380" s="8"/>
+      <c r="V380" s="8"/>
+      <c r="W380" s="8"/>
+    </row>
+    <row r="381" spans="1:23" ht="15" customHeight="1">
+      <c r="A381" s="8">
+        <v>411</v>
+      </c>
+      <c r="B381" s="1">
+        <v>46271.839421296303</v>
+      </c>
+      <c r="C381" s="1">
+        <v>46271.843229166698</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E381" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F381" s="7"/>
+      <c r="G381" s="9">
+        <v>38176</v>
+      </c>
+      <c r="H381" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I381" s="2"/>
+      <c r="J381" s="8"/>
+      <c r="K381" s="2"/>
+      <c r="L381" s="4"/>
+      <c r="M381" s="2"/>
+      <c r="N381" s="2"/>
+      <c r="O381" s="2"/>
+      <c r="P381" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="Q381" s="8"/>
+      <c r="R381" s="2"/>
+      <c r="S381" s="8"/>
+      <c r="T381" s="8"/>
+      <c r="U381" s="8"/>
+      <c r="V381" s="8"/>
+      <c r="W381" s="8"/>
+    </row>
+    <row r="382" spans="1:23" ht="15" customHeight="1">
+      <c r="A382" s="8">
+        <v>412</v>
+      </c>
+      <c r="B382" s="1">
+        <v>46271.845138888901</v>
+      </c>
+      <c r="C382" s="1">
+        <v>46271.845185185201</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E382" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F382" s="7"/>
+      <c r="G382" s="9">
+        <v>38176</v>
+      </c>
+      <c r="H382" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I382" s="2"/>
+      <c r="J382" s="8"/>
+      <c r="K382" s="2"/>
+      <c r="L382" s="4"/>
+      <c r="M382" s="2"/>
+      <c r="N382" s="2"/>
+      <c r="O382" s="2"/>
+      <c r="P382" s="2"/>
+      <c r="Q382" s="8"/>
+      <c r="R382" s="2"/>
+      <c r="S382" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="T382" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="U382" s="8"/>
+      <c r="V382" s="8"/>
+      <c r="W382" s="8"/>
+    </row>
+    <row r="383" spans="1:23" ht="15" customHeight="1">
+      <c r="A383" s="8">
+        <v>413</v>
+      </c>
+      <c r="B383" s="1">
+        <v>46271.845254629603</v>
+      </c>
+      <c r="C383" s="1">
+        <v>46271.847777777803</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E383" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F383" s="7"/>
+      <c r="G383" s="9">
+        <v>38176</v>
+      </c>
+      <c r="H383" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I383" s="2"/>
+      <c r="J383" s="8"/>
+      <c r="K383" s="2"/>
+      <c r="L383" s="4"/>
+      <c r="M383" s="2"/>
+      <c r="N383" s="2"/>
+      <c r="O383" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="P383" s="2"/>
+      <c r="Q383" s="8"/>
+      <c r="R383" s="2"/>
+      <c r="S383" s="8"/>
+      <c r="T383" s="8"/>
+      <c r="U383" s="8"/>
+      <c r="V383" s="8"/>
+      <c r="W383" s="8"/>
+    </row>
+    <row r="384" spans="1:23" ht="15" customHeight="1">
+      <c r="A384" s="8">
+        <v>414</v>
+      </c>
+      <c r="B384" s="1">
+        <v>46271.8461805556</v>
+      </c>
+      <c r="C384" s="1">
+        <v>46271.848182870403</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E384" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F384" s="7"/>
+      <c r="G384" s="9">
+        <v>38894</v>
+      </c>
+      <c r="H384" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I384" s="2"/>
+      <c r="J384" s="8"/>
+      <c r="K384" s="2"/>
+      <c r="L384" s="4"/>
+      <c r="M384" s="2"/>
+      <c r="N384" s="2"/>
+      <c r="O384" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="P384" s="2"/>
+      <c r="Q384" s="8"/>
+      <c r="R384" s="2"/>
+      <c r="S384" s="8"/>
+      <c r="T384" s="8"/>
+      <c r="U384" s="8"/>
+      <c r="V384" s="8"/>
+      <c r="W384" s="8"/>
+    </row>
+    <row r="385" spans="1:23" ht="15" customHeight="1">
+      <c r="A385" s="8">
+        <v>415</v>
+      </c>
+      <c r="B385" s="1">
+        <v>46271.848252314798</v>
+      </c>
+      <c r="C385" s="1">
+        <v>46271.848923611098</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E385" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F385" s="7"/>
+      <c r="G385" s="9">
+        <v>38894</v>
+      </c>
+      <c r="H385" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I385" s="2"/>
+      <c r="J385" s="8"/>
+      <c r="K385" s="2"/>
+      <c r="L385" s="4"/>
+      <c r="M385" s="2"/>
+      <c r="N385" s="2"/>
+      <c r="O385" s="2"/>
+      <c r="P385" s="2"/>
+      <c r="Q385" s="8"/>
+      <c r="R385" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="S385" s="8"/>
+      <c r="T385" s="8"/>
+      <c r="U385" s="8"/>
+      <c r="V385" s="8"/>
+      <c r="W385" s="8"/>
+    </row>
+    <row r="386" spans="1:23" ht="15" customHeight="1">
+      <c r="A386" s="8">
+        <v>416</v>
+      </c>
+      <c r="B386" s="1">
+        <v>46271.850370370397</v>
+      </c>
+      <c r="C386" s="1">
+        <v>46271.859814814801</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E386" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F386" s="7"/>
+      <c r="G386" s="9">
+        <v>38176</v>
+      </c>
+      <c r="H386" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I386" s="2"/>
+      <c r="J386" s="8"/>
+      <c r="K386" s="2"/>
+      <c r="L386" s="4"/>
+      <c r="M386" s="2"/>
+      <c r="N386" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="O386" s="2"/>
+      <c r="P386" s="2"/>
+      <c r="Q386" s="8"/>
+      <c r="R386" s="2"/>
+      <c r="S386" s="8"/>
+      <c r="T386" s="8"/>
+      <c r="U386" s="8"/>
+      <c r="V386" s="8"/>
+      <c r="W386" s="8"/>
+    </row>
+    <row r="387" spans="1:23" ht="15" customHeight="1">
+      <c r="A387" s="8">
+        <v>417</v>
+      </c>
+      <c r="B387" s="1">
+        <v>46271.879965277803</v>
+      </c>
+      <c r="C387" s="1">
+        <v>46271.880902777797</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E387" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F387" s="7"/>
+      <c r="G387" s="9">
+        <v>38333</v>
+      </c>
+      <c r="H387" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I387" s="2"/>
+      <c r="J387" s="8"/>
+      <c r="K387" s="2"/>
+      <c r="L387" s="4"/>
+      <c r="M387" s="2"/>
+      <c r="N387" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="O387" s="2"/>
+      <c r="P387" s="2"/>
+      <c r="Q387" s="8"/>
+      <c r="R387" s="2"/>
+      <c r="S387" s="8"/>
+      <c r="T387" s="8"/>
+      <c r="U387" s="8"/>
+      <c r="V387" s="8"/>
+      <c r="W387" s="8"/>
+    </row>
+    <row r="388" spans="1:23" ht="15" customHeight="1">
+      <c r="A388" s="8">
+        <v>418</v>
+      </c>
+      <c r="B388" s="1">
+        <v>46271.895590277803</v>
+      </c>
+      <c r="C388" s="1">
+        <v>46271.8960069444</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E388" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F388" s="7"/>
+      <c r="G388" s="9">
+        <v>38333</v>
+      </c>
+      <c r="H388" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I388" s="2"/>
+      <c r="J388" s="8"/>
+      <c r="K388" s="2"/>
+      <c r="L388" s="4"/>
+      <c r="M388" s="2"/>
+      <c r="N388" s="2"/>
+      <c r="O388" s="2"/>
+      <c r="P388" s="2"/>
+      <c r="Q388" s="8"/>
+      <c r="R388" s="2"/>
+      <c r="S388" s="8"/>
+      <c r="T388" s="8"/>
+      <c r="U388" s="8"/>
+      <c r="V388" s="8"/>
+      <c r="W388" s="8" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="389" spans="1:23" ht="15" customHeight="1">
+      <c r="A389" s="8">
+        <v>419</v>
+      </c>
+      <c r="B389" s="1">
+        <v>46271.914618055598</v>
+      </c>
+      <c r="C389" s="1">
+        <v>46271.916261574101</v>
+      </c>
+      <c r="D389" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E389" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F389" s="7"/>
+      <c r="G389" s="9">
+        <v>38368</v>
+      </c>
+      <c r="H389" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I389" s="2"/>
+      <c r="J389" s="8"/>
+      <c r="K389" s="2"/>
+      <c r="L389" s="4"/>
+      <c r="M389" s="2"/>
+      <c r="N389" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="O389" s="2"/>
+      <c r="P389" s="2"/>
+      <c r="Q389" s="8"/>
+      <c r="R389" s="2"/>
+      <c r="S389" s="8"/>
+      <c r="T389" s="8"/>
+      <c r="U389" s="8"/>
+      <c r="V389" s="8"/>
+      <c r="W389" s="8"/>
+    </row>
+    <row r="390" spans="1:23" ht="15" customHeight="1">
+      <c r="A390" s="8">
+        <v>420</v>
+      </c>
+      <c r="B390" s="1">
+        <v>46272.005937499998</v>
+      </c>
+      <c r="C390" s="1">
+        <v>46272.008368055598</v>
+      </c>
+      <c r="D390" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E390" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F390" s="7"/>
+      <c r="G390" s="9">
+        <v>43152</v>
+      </c>
+      <c r="H390" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I390" s="2"/>
+      <c r="J390" s="8"/>
+      <c r="K390" s="2"/>
+      <c r="L390" s="4"/>
+      <c r="M390" s="2"/>
+      <c r="N390" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="O390" s="2"/>
+      <c r="P390" s="2"/>
+      <c r="Q390" s="8"/>
+      <c r="R390" s="2"/>
+      <c r="S390" s="8"/>
+      <c r="T390" s="8"/>
+      <c r="U390" s="8"/>
+      <c r="V390" s="8"/>
+      <c r="W390" s="8"/>
+    </row>
+    <row r="391" spans="1:23" ht="15" customHeight="1">
+      <c r="A391" s="8">
+        <v>421</v>
+      </c>
+      <c r="B391" s="1">
+        <v>46272.009525463</v>
+      </c>
+      <c r="C391" s="1">
+        <v>46272.009965277801</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E391" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F391" s="7"/>
+      <c r="G391" s="9">
+        <v>38427</v>
+      </c>
+      <c r="H391" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I391" s="2"/>
+      <c r="J391" s="8"/>
+      <c r="K391" s="2"/>
+      <c r="L391" s="4"/>
+      <c r="M391" s="2"/>
+      <c r="N391" s="2"/>
+      <c r="O391" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="P391" s="2"/>
+      <c r="Q391" s="8"/>
+      <c r="R391" s="2"/>
+      <c r="S391" s="8"/>
+      <c r="T391" s="8"/>
+      <c r="U391" s="8"/>
+      <c r="V391" s="8"/>
+      <c r="W391" s="8"/>
+    </row>
+    <row r="392" spans="1:23" ht="15" customHeight="1">
+      <c r="A392" s="8">
+        <v>422</v>
+      </c>
+      <c r="B392" s="1">
+        <v>46272.0100578704</v>
+      </c>
+      <c r="C392" s="1">
+        <v>46272.011967592603</v>
+      </c>
+      <c r="D392" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E392" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F392" s="7"/>
+      <c r="G392" s="9">
+        <v>38427</v>
+      </c>
+      <c r="H392" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I392" s="2"/>
+      <c r="J392" s="8"/>
+      <c r="K392" s="2"/>
+      <c r="L392" s="4"/>
+      <c r="M392" s="2"/>
+      <c r="N392" s="2"/>
+      <c r="O392" s="2"/>
+      <c r="P392" s="2"/>
+      <c r="Q392" s="8"/>
+      <c r="R392" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="S392" s="8"/>
+      <c r="T392" s="8"/>
+      <c r="U392" s="8"/>
+      <c r="V392" s="8"/>
+      <c r="W392" s="8"/>
+    </row>
+    <row r="393" spans="1:23" ht="15" customHeight="1">
+      <c r="A393" s="8">
+        <v>423</v>
+      </c>
+      <c r="B393" s="1">
+        <v>46272.018634259301</v>
+      </c>
+      <c r="C393" s="1">
+        <v>46272.019004629597</v>
+      </c>
+      <c r="D393" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E393" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F393" s="7"/>
+      <c r="G393" s="9">
+        <v>44152</v>
+      </c>
+      <c r="H393" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I393" s="2"/>
+      <c r="J393" s="8"/>
+      <c r="K393" s="2"/>
+      <c r="L393" s="4"/>
+      <c r="M393" s="2"/>
+      <c r="N393" s="2"/>
+      <c r="O393" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="P393" s="2"/>
+      <c r="Q393" s="8"/>
+      <c r="R393" s="2"/>
+      <c r="S393" s="8"/>
+      <c r="T393" s="8"/>
+      <c r="U393" s="8"/>
+      <c r="V393" s="8"/>
+      <c r="W393" s="8"/>
+    </row>
+    <row r="394" spans="1:23" ht="15" customHeight="1">
+      <c r="A394" s="8">
+        <v>424</v>
+      </c>
+      <c r="B394" s="1">
+        <v>46272.019571759301</v>
+      </c>
+      <c r="C394" s="1">
+        <v>46272.020439814798</v>
+      </c>
+      <c r="D394" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E394" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F394" s="7"/>
+      <c r="G394" s="9">
+        <v>43152</v>
+      </c>
+      <c r="H394" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I394" s="2"/>
+      <c r="J394" s="8"/>
+      <c r="K394" s="2"/>
+      <c r="L394" s="4"/>
+      <c r="M394" s="2"/>
+      <c r="N394" s="2"/>
+      <c r="O394" s="2"/>
+      <c r="P394" s="2"/>
+      <c r="Q394" s="8"/>
+      <c r="R394" s="2"/>
+      <c r="S394" s="8"/>
+      <c r="T394" s="8"/>
+      <c r="U394" s="8"/>
+      <c r="V394" s="8"/>
+      <c r="W394" s="8" t="s">
+        <v>645</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="517" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E7E99AB-AA62-443F-A5DD-4CFA5A2BCD61}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A66FBD1-9389-40F3-AA6C-F142955EBB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2019,7 +2019,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2032,10 +2032,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -15875,7 +15871,7 @@
       <c r="R376" s="2"/>
     </row>
     <row r="377" spans="1:23" ht="15" customHeight="1">
-      <c r="A377" s="8">
+      <c r="A377">
         <v>407</v>
       </c>
       <c r="B377" s="1">
@@ -15891,14 +15887,13 @@
         <v>115</v>
       </c>
       <c r="F377" s="7"/>
-      <c r="G377" s="9">
+      <c r="G377" s="6">
         <v>38117</v>
       </c>
       <c r="H377" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I377" s="2"/>
-      <c r="J377" s="8"/>
       <c r="K377" s="2"/>
       <c r="L377" s="4"/>
       <c r="M377" s="2"/>
@@ -15907,16 +15902,10 @@
         <v>628</v>
       </c>
       <c r="P377" s="2"/>
-      <c r="Q377" s="8"/>
       <c r="R377" s="2"/>
-      <c r="S377" s="8"/>
-      <c r="T377" s="8"/>
-      <c r="U377" s="8"/>
-      <c r="V377" s="8"/>
-      <c r="W377" s="8"/>
     </row>
     <row r="378" spans="1:23" ht="15" customHeight="1">
-      <c r="A378" s="8">
+      <c r="A378">
         <v>408</v>
       </c>
       <c r="B378" s="1">
@@ -15932,14 +15921,13 @@
         <v>189</v>
       </c>
       <c r="F378" s="7"/>
-      <c r="G378" s="9">
+      <c r="G378" s="6">
         <v>38427</v>
       </c>
       <c r="H378" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I378" s="2"/>
-      <c r="J378" s="8"/>
       <c r="K378" s="2"/>
       <c r="L378" s="4"/>
       <c r="M378" s="2"/>
@@ -15948,16 +15936,10 @@
       </c>
       <c r="O378" s="2"/>
       <c r="P378" s="2"/>
-      <c r="Q378" s="8"/>
       <c r="R378" s="2"/>
-      <c r="S378" s="8"/>
-      <c r="T378" s="8"/>
-      <c r="U378" s="8"/>
-      <c r="V378" s="8"/>
-      <c r="W378" s="8"/>
     </row>
     <row r="379" spans="1:23" ht="15" customHeight="1">
-      <c r="A379" s="8">
+      <c r="A379">
         <v>409</v>
       </c>
       <c r="B379" s="1">
@@ -15973,14 +15955,13 @@
         <v>189</v>
       </c>
       <c r="F379" s="7"/>
-      <c r="G379" s="9">
+      <c r="G379" s="6">
         <v>38427</v>
       </c>
       <c r="H379" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I379" s="2"/>
-      <c r="J379" s="8"/>
       <c r="K379" s="2"/>
       <c r="L379" s="4"/>
       <c r="M379" s="2"/>
@@ -15989,16 +15970,10 @@
       <c r="P379" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="Q379" s="8"/>
       <c r="R379" s="2"/>
-      <c r="S379" s="8"/>
-      <c r="T379" s="8"/>
-      <c r="U379" s="8"/>
-      <c r="V379" s="8"/>
-      <c r="W379" s="8"/>
     </row>
     <row r="380" spans="1:23" ht="15" customHeight="1">
-      <c r="A380" s="8">
+      <c r="A380">
         <v>410</v>
       </c>
       <c r="B380" s="1">
@@ -16014,32 +15989,25 @@
         <v>66</v>
       </c>
       <c r="F380" s="7"/>
-      <c r="G380" s="9">
+      <c r="G380" s="6">
         <v>38368</v>
       </c>
       <c r="H380" s="2" t="s">
         <v>43</v>
       </c>
       <c r="I380" s="2"/>
-      <c r="J380" s="8"/>
       <c r="K380" s="2"/>
       <c r="L380" s="4"/>
       <c r="M380" s="2"/>
       <c r="N380" s="2"/>
       <c r="O380" s="2"/>
       <c r="P380" s="2"/>
-      <c r="Q380" s="8"/>
       <c r="R380" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="S380" s="8"/>
-      <c r="T380" s="8"/>
-      <c r="U380" s="8"/>
-      <c r="V380" s="8"/>
-      <c r="W380" s="8"/>
     </row>
     <row r="381" spans="1:23" ht="15" customHeight="1">
-      <c r="A381" s="8">
+      <c r="A381">
         <v>411</v>
       </c>
       <c r="B381" s="1">
@@ -16055,14 +16023,13 @@
         <v>549</v>
       </c>
       <c r="F381" s="7"/>
-      <c r="G381" s="9">
+      <c r="G381" s="6">
         <v>38176</v>
       </c>
       <c r="H381" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I381" s="2"/>
-      <c r="J381" s="8"/>
       <c r="K381" s="2"/>
       <c r="L381" s="4"/>
       <c r="M381" s="2"/>
@@ -16071,16 +16038,10 @@
       <c r="P381" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="Q381" s="8"/>
       <c r="R381" s="2"/>
-      <c r="S381" s="8"/>
-      <c r="T381" s="8"/>
-      <c r="U381" s="8"/>
-      <c r="V381" s="8"/>
-      <c r="W381" s="8"/>
     </row>
     <row r="382" spans="1:23" ht="15" customHeight="1">
-      <c r="A382" s="8">
+      <c r="A382">
         <v>412</v>
       </c>
       <c r="B382" s="1">
@@ -16096,34 +16057,29 @@
         <v>549</v>
       </c>
       <c r="F382" s="7"/>
-      <c r="G382" s="9">
+      <c r="G382" s="6">
         <v>38176</v>
       </c>
       <c r="H382" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I382" s="2"/>
-      <c r="J382" s="8"/>
       <c r="K382" s="2"/>
       <c r="L382" s="4"/>
       <c r="M382" s="2"/>
       <c r="N382" s="2"/>
       <c r="O382" s="2"/>
       <c r="P382" s="2"/>
-      <c r="Q382" s="8"/>
       <c r="R382" s="2"/>
-      <c r="S382" s="8" t="s">
+      <c r="S382" t="s">
         <v>63</v>
       </c>
-      <c r="T382" s="8" t="s">
+      <c r="T382" t="s">
         <v>633</v>
       </c>
-      <c r="U382" s="8"/>
-      <c r="V382" s="8"/>
-      <c r="W382" s="8"/>
     </row>
     <row r="383" spans="1:23" ht="15" customHeight="1">
-      <c r="A383" s="8">
+      <c r="A383">
         <v>413</v>
       </c>
       <c r="B383" s="1">
@@ -16139,14 +16095,13 @@
         <v>549</v>
       </c>
       <c r="F383" s="7"/>
-      <c r="G383" s="9">
+      <c r="G383" s="6">
         <v>38176</v>
       </c>
       <c r="H383" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I383" s="2"/>
-      <c r="J383" s="8"/>
       <c r="K383" s="2"/>
       <c r="L383" s="4"/>
       <c r="M383" s="2"/>
@@ -16155,16 +16110,10 @@
         <v>634</v>
       </c>
       <c r="P383" s="2"/>
-      <c r="Q383" s="8"/>
       <c r="R383" s="2"/>
-      <c r="S383" s="8"/>
-      <c r="T383" s="8"/>
-      <c r="U383" s="8"/>
-      <c r="V383" s="8"/>
-      <c r="W383" s="8"/>
     </row>
     <row r="384" spans="1:23" ht="15" customHeight="1">
-      <c r="A384" s="8">
+      <c r="A384">
         <v>414</v>
       </c>
       <c r="B384" s="1">
@@ -16180,14 +16129,13 @@
         <v>38</v>
       </c>
       <c r="F384" s="7"/>
-      <c r="G384" s="9">
+      <c r="G384" s="6">
         <v>38894</v>
       </c>
       <c r="H384" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I384" s="2"/>
-      <c r="J384" s="8"/>
       <c r="K384" s="2"/>
       <c r="L384" s="4"/>
       <c r="M384" s="2"/>
@@ -16196,16 +16144,10 @@
         <v>635</v>
       </c>
       <c r="P384" s="2"/>
-      <c r="Q384" s="8"/>
       <c r="R384" s="2"/>
-      <c r="S384" s="8"/>
-      <c r="T384" s="8"/>
-      <c r="U384" s="8"/>
-      <c r="V384" s="8"/>
-      <c r="W384" s="8"/>
     </row>
     <row r="385" spans="1:23" ht="15" customHeight="1">
-      <c r="A385" s="8">
+      <c r="A385">
         <v>415</v>
       </c>
       <c r="B385" s="1">
@@ -16221,32 +16163,25 @@
         <v>38</v>
       </c>
       <c r="F385" s="7"/>
-      <c r="G385" s="9">
+      <c r="G385" s="6">
         <v>38894</v>
       </c>
       <c r="H385" s="2" t="s">
         <v>43</v>
       </c>
       <c r="I385" s="2"/>
-      <c r="J385" s="8"/>
       <c r="K385" s="2"/>
       <c r="L385" s="4"/>
       <c r="M385" s="2"/>
       <c r="N385" s="2"/>
       <c r="O385" s="2"/>
       <c r="P385" s="2"/>
-      <c r="Q385" s="8"/>
       <c r="R385" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="S385" s="8"/>
-      <c r="T385" s="8"/>
-      <c r="U385" s="8"/>
-      <c r="V385" s="8"/>
-      <c r="W385" s="8"/>
     </row>
     <row r="386" spans="1:23" ht="15" customHeight="1">
-      <c r="A386" s="8">
+      <c r="A386">
         <v>416</v>
       </c>
       <c r="B386" s="1">
@@ -16262,14 +16197,13 @@
         <v>549</v>
       </c>
       <c r="F386" s="7"/>
-      <c r="G386" s="9">
+      <c r="G386" s="6">
         <v>38176</v>
       </c>
       <c r="H386" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I386" s="2"/>
-      <c r="J386" s="8"/>
       <c r="K386" s="2"/>
       <c r="L386" s="4"/>
       <c r="M386" s="2"/>
@@ -16278,16 +16212,10 @@
       </c>
       <c r="O386" s="2"/>
       <c r="P386" s="2"/>
-      <c r="Q386" s="8"/>
       <c r="R386" s="2"/>
-      <c r="S386" s="8"/>
-      <c r="T386" s="8"/>
-      <c r="U386" s="8"/>
-      <c r="V386" s="8"/>
-      <c r="W386" s="8"/>
     </row>
     <row r="387" spans="1:23" ht="15" customHeight="1">
-      <c r="A387" s="8">
+      <c r="A387">
         <v>417</v>
       </c>
       <c r="B387" s="1">
@@ -16303,14 +16231,13 @@
         <v>24</v>
       </c>
       <c r="F387" s="7"/>
-      <c r="G387" s="9">
+      <c r="G387" s="6">
         <v>38333</v>
       </c>
       <c r="H387" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I387" s="2"/>
-      <c r="J387" s="8"/>
       <c r="K387" s="2"/>
       <c r="L387" s="4"/>
       <c r="M387" s="2"/>
@@ -16319,16 +16246,10 @@
       </c>
       <c r="O387" s="2"/>
       <c r="P387" s="2"/>
-      <c r="Q387" s="8"/>
       <c r="R387" s="2"/>
-      <c r="S387" s="8"/>
-      <c r="T387" s="8"/>
-      <c r="U387" s="8"/>
-      <c r="V387" s="8"/>
-      <c r="W387" s="8"/>
     </row>
     <row r="388" spans="1:23" ht="15" customHeight="1">
-      <c r="A388" s="8">
+      <c r="A388">
         <v>418</v>
       </c>
       <c r="B388" s="1">
@@ -16344,32 +16265,26 @@
         <v>24</v>
       </c>
       <c r="F388" s="7"/>
-      <c r="G388" s="9">
+      <c r="G388" s="6">
         <v>38333</v>
       </c>
       <c r="H388" s="2" t="s">
         <v>290</v>
       </c>
       <c r="I388" s="2"/>
-      <c r="J388" s="8"/>
       <c r="K388" s="2"/>
       <c r="L388" s="4"/>
       <c r="M388" s="2"/>
       <c r="N388" s="2"/>
       <c r="O388" s="2"/>
       <c r="P388" s="2"/>
-      <c r="Q388" s="8"/>
       <c r="R388" s="2"/>
-      <c r="S388" s="8"/>
-      <c r="T388" s="8"/>
-      <c r="U388" s="8"/>
-      <c r="V388" s="8"/>
-      <c r="W388" s="8" t="s">
+      <c r="W388" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="389" spans="1:23" ht="15" customHeight="1">
-      <c r="A389" s="8">
+      <c r="A389">
         <v>419</v>
       </c>
       <c r="B389" s="1">
@@ -16385,14 +16300,13 @@
         <v>66</v>
       </c>
       <c r="F389" s="7"/>
-      <c r="G389" s="9">
+      <c r="G389" s="6">
         <v>38368</v>
       </c>
       <c r="H389" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I389" s="2"/>
-      <c r="J389" s="8"/>
       <c r="K389" s="2"/>
       <c r="L389" s="4"/>
       <c r="M389" s="2"/>
@@ -16401,16 +16315,10 @@
       </c>
       <c r="O389" s="2"/>
       <c r="P389" s="2"/>
-      <c r="Q389" s="8"/>
       <c r="R389" s="2"/>
-      <c r="S389" s="8"/>
-      <c r="T389" s="8"/>
-      <c r="U389" s="8"/>
-      <c r="V389" s="8"/>
-      <c r="W389" s="8"/>
     </row>
     <row r="390" spans="1:23" ht="15" customHeight="1">
-      <c r="A390" s="8">
+      <c r="A390">
         <v>420</v>
       </c>
       <c r="B390" s="1">
@@ -16426,14 +16334,13 @@
         <v>177</v>
       </c>
       <c r="F390" s="7"/>
-      <c r="G390" s="9">
+      <c r="G390" s="6">
         <v>43152</v>
       </c>
       <c r="H390" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I390" s="2"/>
-      <c r="J390" s="8"/>
       <c r="K390" s="2"/>
       <c r="L390" s="4"/>
       <c r="M390" s="2"/>
@@ -16442,16 +16349,10 @@
       </c>
       <c r="O390" s="2"/>
       <c r="P390" s="2"/>
-      <c r="Q390" s="8"/>
       <c r="R390" s="2"/>
-      <c r="S390" s="8"/>
-      <c r="T390" s="8"/>
-      <c r="U390" s="8"/>
-      <c r="V390" s="8"/>
-      <c r="W390" s="8"/>
     </row>
     <row r="391" spans="1:23" ht="15" customHeight="1">
-      <c r="A391" s="8">
+      <c r="A391">
         <v>421</v>
       </c>
       <c r="B391" s="1">
@@ -16467,14 +16368,13 @@
         <v>189</v>
       </c>
       <c r="F391" s="7"/>
-      <c r="G391" s="9">
+      <c r="G391" s="6">
         <v>38427</v>
       </c>
       <c r="H391" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I391" s="2"/>
-      <c r="J391" s="8"/>
       <c r="K391" s="2"/>
       <c r="L391" s="4"/>
       <c r="M391" s="2"/>
@@ -16483,16 +16383,10 @@
         <v>642</v>
       </c>
       <c r="P391" s="2"/>
-      <c r="Q391" s="8"/>
       <c r="R391" s="2"/>
-      <c r="S391" s="8"/>
-      <c r="T391" s="8"/>
-      <c r="U391" s="8"/>
-      <c r="V391" s="8"/>
-      <c r="W391" s="8"/>
     </row>
     <row r="392" spans="1:23" ht="15" customHeight="1">
-      <c r="A392" s="8">
+      <c r="A392">
         <v>422</v>
       </c>
       <c r="B392" s="1">
@@ -16508,32 +16402,25 @@
         <v>189</v>
       </c>
       <c r="F392" s="7"/>
-      <c r="G392" s="9">
+      <c r="G392" s="6">
         <v>38427</v>
       </c>
       <c r="H392" s="2" t="s">
         <v>43</v>
       </c>
       <c r="I392" s="2"/>
-      <c r="J392" s="8"/>
       <c r="K392" s="2"/>
       <c r="L392" s="4"/>
       <c r="M392" s="2"/>
       <c r="N392" s="2"/>
       <c r="O392" s="2"/>
       <c r="P392" s="2"/>
-      <c r="Q392" s="8"/>
       <c r="R392" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="S392" s="8"/>
-      <c r="T392" s="8"/>
-      <c r="U392" s="8"/>
-      <c r="V392" s="8"/>
-      <c r="W392" s="8"/>
     </row>
     <row r="393" spans="1:23" ht="15" customHeight="1">
-      <c r="A393" s="8">
+      <c r="A393">
         <v>423</v>
       </c>
       <c r="B393" s="1">
@@ -16549,14 +16436,13 @@
         <v>177</v>
       </c>
       <c r="F393" s="7"/>
-      <c r="G393" s="9">
+      <c r="G393" s="6">
         <v>44152</v>
       </c>
       <c r="H393" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I393" s="2"/>
-      <c r="J393" s="8"/>
       <c r="K393" s="2"/>
       <c r="L393" s="4"/>
       <c r="M393" s="2"/>
@@ -16565,16 +16451,10 @@
         <v>644</v>
       </c>
       <c r="P393" s="2"/>
-      <c r="Q393" s="8"/>
       <c r="R393" s="2"/>
-      <c r="S393" s="8"/>
-      <c r="T393" s="8"/>
-      <c r="U393" s="8"/>
-      <c r="V393" s="8"/>
-      <c r="W393" s="8"/>
     </row>
     <row r="394" spans="1:23" ht="15" customHeight="1">
-      <c r="A394" s="8">
+      <c r="A394">
         <v>424</v>
       </c>
       <c r="B394" s="1">
@@ -16590,27 +16470,21 @@
         <v>177</v>
       </c>
       <c r="F394" s="7"/>
-      <c r="G394" s="9">
+      <c r="G394" s="6">
         <v>43152</v>
       </c>
       <c r="H394" s="2" t="s">
         <v>290</v>
       </c>
       <c r="I394" s="2"/>
-      <c r="J394" s="8"/>
       <c r="K394" s="2"/>
       <c r="L394" s="4"/>
       <c r="M394" s="2"/>
       <c r="N394" s="2"/>
       <c r="O394" s="2"/>
       <c r="P394" s="2"/>
-      <c r="Q394" s="8"/>
       <c r="R394" s="2"/>
-      <c r="S394" s="8"/>
-      <c r="T394" s="8"/>
-      <c r="U394" s="8"/>
-      <c r="V394" s="8"/>
-      <c r="W394" s="8" t="s">
+      <c r="W394" t="s">
         <v>645</v>
       </c>
     </row>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A66FBD1-9389-40F3-AA6C-F142955EBB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{477A32C6-DED8-D848-898B-3AF68929AD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1980,7 +1980,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2620,21 +2620,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W394"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="1"/>
-    <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
-    <col min="6" max="6" width="7.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="19" customWidth="1"/>
-    <col min="17" max="17" width="42.140625" customWidth="1"/>
-    <col min="18" max="19" width="19" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" customWidth="1"/>
+    <col min="2" max="3" width="20.04296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.07421875" customWidth="1"/>
+    <col min="5" max="5" width="35.109375" customWidth="1"/>
+    <col min="6" max="6" width="7.80078125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.01171875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="20.04296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="18.96484375" customWidth="1"/>
+    <col min="17" max="17" width="42.10546875" customWidth="1"/>
+    <col min="18" max="19" width="18.96484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>13</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>17</v>
       </c>
@@ -2766,7 +2766,7 @@
       <c r="P3" s="2"/>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>20</v>
       </c>
@@ -2834,7 +2834,7 @@
       <c r="P5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>21</v>
       </c>
@@ -2868,7 +2868,7 @@
       <c r="P6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>22</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>23</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>24</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>25</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>26</v>
       </c>
@@ -3041,7 +3041,7 @@
       <c r="P11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>27</v>
       </c>
@@ -3078,7 +3078,7 @@
       <c r="P12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>28</v>
       </c>
@@ -3112,7 +3112,7 @@
       <c r="P13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>29</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>30</v>
       </c>
@@ -3181,7 +3181,7 @@
       <c r="P15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>31</v>
       </c>
@@ -3215,7 +3215,7 @@
       <c r="P16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>32</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>33</v>
       </c>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>34</v>
       </c>
@@ -3318,7 +3318,7 @@
       <c r="P19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>35</v>
       </c>
@@ -3352,7 +3352,7 @@
       <c r="P20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>36</v>
       </c>
@@ -3386,7 +3386,7 @@
       <c r="P21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>37</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>38</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>39</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>40</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>41</v>
       </c>
@@ -3560,7 +3560,7 @@
       <c r="P26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>42</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>43</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>44</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>45</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>46</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>47</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>48</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>49</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>50</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>51</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>52</v>
       </c>
@@ -3943,7 +3943,7 @@
       <c r="P37" s="2"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>54</v>
       </c>
@@ -3977,7 +3977,7 @@
       <c r="P38" s="2"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>55</v>
       </c>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>56</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>57</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>58</v>
       </c>
@@ -4116,7 +4116,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>59</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>60</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>61</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>62</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>63</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>65</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>66</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>67</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="P50" s="2"/>
       <c r="R50" s="2"/>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>68</v>
       </c>
@@ -4429,7 +4429,7 @@
       <c r="P51" s="2"/>
       <c r="R51" s="2"/>
     </row>
-    <row r="52" spans="1:21">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>69</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>70</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="1:21">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>71</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="55" spans="1:21">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>72</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="56" spans="1:21">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>73</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:21">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>74</v>
       </c>
@@ -4639,7 +4639,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="58" spans="1:21">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>75</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="59" spans="1:21">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>76</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="60" spans="1:21">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>77</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:21">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>78</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="62" spans="1:21">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>79</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="63" spans="1:21">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>80</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="64" spans="1:21">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>81</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="65" spans="1:21">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>84</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="66" spans="1:21">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>85</v>
       </c>
@@ -4952,7 +4952,7 @@
       <c r="P66" s="2"/>
       <c r="R66" s="2"/>
     </row>
-    <row r="67" spans="1:21">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>86</v>
       </c>
@@ -4986,7 +4986,7 @@
       <c r="P67" s="2"/>
       <c r="R67" s="2"/>
     </row>
-    <row r="68" spans="1:21">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>88</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="69" spans="1:21">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>89</v>
       </c>
@@ -5054,7 +5054,7 @@
       <c r="P69" s="2"/>
       <c r="R69" s="2"/>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>90</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="71" spans="1:21">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>91</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="72" spans="1:21">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>92</v>
       </c>
@@ -5161,7 +5161,7 @@
       <c r="P72" s="2"/>
       <c r="R72" s="2"/>
     </row>
-    <row r="73" spans="1:21">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>93</v>
       </c>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="R73" s="2"/>
     </row>
-    <row r="74" spans="1:21">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>94</v>
       </c>
@@ -5229,7 +5229,7 @@
       <c r="P74" s="2"/>
       <c r="R74" s="2"/>
     </row>
-    <row r="75" spans="1:21">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>95</v>
       </c>
@@ -5263,7 +5263,7 @@
       <c r="P75" s="2"/>
       <c r="R75" s="2"/>
     </row>
-    <row r="76" spans="1:21">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>96</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="77" spans="1:21">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>97</v>
       </c>
@@ -5332,7 +5332,7 @@
       <c r="P77" s="2"/>
       <c r="R77" s="2"/>
     </row>
-    <row r="78" spans="1:21">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>98</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79" spans="1:21">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>99</v>
       </c>
@@ -5401,7 +5401,7 @@
       <c r="P79" s="2"/>
       <c r="R79" s="2"/>
     </row>
-    <row r="80" spans="1:21">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>100</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="81" spans="1:21">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>102</v>
       </c>
@@ -5473,7 +5473,7 @@
       <c r="P81" s="2"/>
       <c r="R81" s="2"/>
     </row>
-    <row r="82" spans="1:21">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>103</v>
       </c>
@@ -5507,7 +5507,7 @@
       <c r="P82" s="2"/>
       <c r="R82" s="2"/>
     </row>
-    <row r="83" spans="1:21">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>104</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="84" spans="1:21">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>105</v>
       </c>
@@ -5579,7 +5579,7 @@
       <c r="P84" s="2"/>
       <c r="R84" s="2"/>
     </row>
-    <row r="85" spans="1:21">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>106</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="86" spans="1:21">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>107</v>
       </c>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="R86" s="2"/>
     </row>
-    <row r="87" spans="1:21">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>108</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>109</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>110</v>
       </c>
@@ -5752,7 +5752,7 @@
       <c r="P89" s="2"/>
       <c r="R89" s="2"/>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>111</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>112</v>
       </c>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="R91" s="2"/>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>113</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="93" spans="1:21">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>114</v>
       </c>
@@ -5891,7 +5891,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="94" spans="1:21">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>115</v>
       </c>
@@ -5925,7 +5925,7 @@
       <c r="P94" s="2"/>
       <c r="R94" s="2"/>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>116</v>
       </c>
@@ -5959,7 +5959,7 @@
       <c r="P95" s="2"/>
       <c r="R95" s="2"/>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>117</v>
       </c>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="R96" s="2"/>
     </row>
-    <row r="97" spans="1:23">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>118</v>
       </c>
@@ -6027,7 +6027,7 @@
       <c r="P97" s="2"/>
       <c r="R97" s="2"/>
     </row>
-    <row r="98" spans="1:23">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>119</v>
       </c>
@@ -6061,7 +6061,7 @@
       <c r="P98" s="2"/>
       <c r="R98" s="2"/>
     </row>
-    <row r="99" spans="1:23">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>120</v>
       </c>
@@ -6095,7 +6095,7 @@
       <c r="P99" s="2"/>
       <c r="R99" s="2"/>
     </row>
-    <row r="100" spans="1:23">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>121</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="101" spans="1:23">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>122</v>
       </c>
@@ -6164,7 +6164,7 @@
       <c r="P101" s="2"/>
       <c r="R101" s="2"/>
     </row>
-    <row r="102" spans="1:23">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>123</v>
       </c>
@@ -6199,7 +6199,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="103" spans="1:23">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>124</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="104" spans="1:23">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>125</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="105" spans="1:23">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>126</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="106" spans="1:23">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>127</v>
       </c>
@@ -6338,7 +6338,7 @@
       <c r="P106" s="2"/>
       <c r="R106" s="2"/>
     </row>
-    <row r="107" spans="1:23">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>128</v>
       </c>
@@ -6375,7 +6375,7 @@
       <c r="P107" s="2"/>
       <c r="R107" s="2"/>
     </row>
-    <row r="108" spans="1:23">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>129</v>
       </c>
@@ -6410,7 +6410,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="109" spans="1:23">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>130</v>
       </c>
@@ -6447,7 +6447,7 @@
       <c r="P109" s="2"/>
       <c r="R109" s="2"/>
     </row>
-    <row r="110" spans="1:23">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>131</v>
       </c>
@@ -6481,7 +6481,7 @@
       <c r="P110" s="2"/>
       <c r="R110" s="2"/>
     </row>
-    <row r="111" spans="1:23">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>132</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="112" spans="1:23">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>133</v>
       </c>
@@ -6551,7 +6551,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="1:21">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>134</v>
       </c>
@@ -6586,7 +6586,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="114" spans="1:21">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>135</v>
       </c>
@@ -6621,7 +6621,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="115" spans="1:21">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>136</v>
       </c>
@@ -6656,7 +6656,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="116" spans="1:21">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>137</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" spans="1:21">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>138</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="118" spans="1:21">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>139</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="119" spans="1:21">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>140</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="120" spans="1:21">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>141</v>
       </c>
@@ -6830,7 +6830,7 @@
       <c r="P120" s="2"/>
       <c r="R120" s="2"/>
     </row>
-    <row r="121" spans="1:21">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>142</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="122" spans="1:21">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>143</v>
       </c>
@@ -6899,7 +6899,7 @@
       <c r="P122" s="2"/>
       <c r="R122" s="2"/>
     </row>
-    <row r="123" spans="1:21">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>144</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="124" spans="1:21">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>145</v>
       </c>
@@ -6968,7 +6968,7 @@
       <c r="P124" s="2"/>
       <c r="R124" s="2"/>
     </row>
-    <row r="125" spans="1:21">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>146</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="126" spans="1:21">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>147</v>
       </c>
@@ -7037,7 +7037,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="127" spans="1:21">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>148</v>
       </c>
@@ -7075,7 +7075,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="128" spans="1:21">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>149</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="129" spans="1:21">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>150</v>
       </c>
@@ -7145,7 +7145,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="130" spans="1:21">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>151</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="131" spans="1:21">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>152</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="132" spans="1:21">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>153</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="133" spans="1:21">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>154</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="134" spans="1:21">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>155</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="135" spans="1:21">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>156</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="136" spans="1:21">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>157</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="137" spans="1:21">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>158</v>
       </c>
@@ -7426,7 +7426,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:21">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>159</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="139" spans="1:21">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>160</v>
       </c>
@@ -7501,7 +7501,7 @@
       <c r="P139" s="2"/>
       <c r="R139" s="2"/>
     </row>
-    <row r="140" spans="1:21">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>161</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="141" spans="1:21">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>162</v>
       </c>
@@ -7572,7 +7572,7 @@
       <c r="P141" s="2"/>
       <c r="R141" s="2"/>
     </row>
-    <row r="142" spans="1:21">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>163</v>
       </c>
@@ -7609,7 +7609,7 @@
       <c r="P142" s="2"/>
       <c r="R142" s="2"/>
     </row>
-    <row r="143" spans="1:21">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>164</v>
       </c>
@@ -7643,7 +7643,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="144" spans="1:21">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>165</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="145" spans="1:18">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>166</v>
       </c>
@@ -7718,7 +7718,7 @@
       <c r="P145" s="2"/>
       <c r="R145" s="2"/>
     </row>
-    <row r="146" spans="1:18">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>167</v>
       </c>
@@ -7755,7 +7755,7 @@
       <c r="P146" s="2"/>
       <c r="R146" s="2"/>
     </row>
-    <row r="147" spans="1:18">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>168</v>
       </c>
@@ -7792,7 +7792,7 @@
       <c r="P147" s="2"/>
       <c r="R147" s="2"/>
     </row>
-    <row r="148" spans="1:18">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>169</v>
       </c>
@@ -7829,7 +7829,7 @@
       <c r="P148" s="2"/>
       <c r="R148" s="2"/>
     </row>
-    <row r="149" spans="1:18">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>170</v>
       </c>
@@ -7866,7 +7866,7 @@
       <c r="P149" s="2"/>
       <c r="R149" s="2"/>
     </row>
-    <row r="150" spans="1:18">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>171</v>
       </c>
@@ -7903,7 +7903,7 @@
       <c r="P150" s="2"/>
       <c r="R150" s="2"/>
     </row>
-    <row r="151" spans="1:18">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>172</v>
       </c>
@@ -7940,7 +7940,7 @@
       <c r="P151" s="2"/>
       <c r="R151" s="2"/>
     </row>
-    <row r="152" spans="1:18">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>173</v>
       </c>
@@ -7977,7 +7977,7 @@
       <c r="P152" s="2"/>
       <c r="R152" s="2"/>
     </row>
-    <row r="153" spans="1:18">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>174</v>
       </c>
@@ -8014,7 +8014,7 @@
       <c r="P153" s="2"/>
       <c r="R153" s="2"/>
     </row>
-    <row r="154" spans="1:18">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>175</v>
       </c>
@@ -8051,7 +8051,7 @@
       <c r="P154" s="2"/>
       <c r="R154" s="2"/>
     </row>
-    <row r="155" spans="1:18">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>176</v>
       </c>
@@ -8088,7 +8088,7 @@
       <c r="P155" s="2"/>
       <c r="R155" s="2"/>
     </row>
-    <row r="156" spans="1:18">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>177</v>
       </c>
@@ -8125,7 +8125,7 @@
       <c r="P156" s="2"/>
       <c r="R156" s="2"/>
     </row>
-    <row r="157" spans="1:18">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>178</v>
       </c>
@@ -8162,7 +8162,7 @@
       <c r="P157" s="2"/>
       <c r="R157" s="2"/>
     </row>
-    <row r="158" spans="1:18">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>179</v>
       </c>
@@ -8199,7 +8199,7 @@
       <c r="P158" s="2"/>
       <c r="R158" s="2"/>
     </row>
-    <row r="159" spans="1:18">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>180</v>
       </c>
@@ -8236,7 +8236,7 @@
       <c r="P159" s="2"/>
       <c r="R159" s="2"/>
     </row>
-    <row r="160" spans="1:18">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>181</v>
       </c>
@@ -8273,7 +8273,7 @@
       <c r="P160" s="2"/>
       <c r="R160" s="2"/>
     </row>
-    <row r="161" spans="1:18">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>182</v>
       </c>
@@ -8310,7 +8310,7 @@
       <c r="P161" s="2"/>
       <c r="R161" s="2"/>
     </row>
-    <row r="162" spans="1:18">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>183</v>
       </c>
@@ -8347,7 +8347,7 @@
       <c r="P162" s="2"/>
       <c r="R162" s="2"/>
     </row>
-    <row r="163" spans="1:18">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>184</v>
       </c>
@@ -8382,7 +8382,7 @@
       <c r="P163" s="2"/>
       <c r="R163" s="2"/>
     </row>
-    <row r="164" spans="1:18">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>185</v>
       </c>
@@ -8419,7 +8419,7 @@
       <c r="P164" s="2"/>
       <c r="R164" s="2"/>
     </row>
-    <row r="165" spans="1:18">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>186</v>
       </c>
@@ -8456,7 +8456,7 @@
       <c r="P165" s="2"/>
       <c r="R165" s="2"/>
     </row>
-    <row r="166" spans="1:18">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>187</v>
       </c>
@@ -8493,7 +8493,7 @@
       <c r="P166" s="2"/>
       <c r="R166" s="2"/>
     </row>
-    <row r="167" spans="1:18">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>188</v>
       </c>
@@ -8530,7 +8530,7 @@
       <c r="P167" s="2"/>
       <c r="R167" s="2"/>
     </row>
-    <row r="168" spans="1:18">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>189</v>
       </c>
@@ -8567,7 +8567,7 @@
       <c r="P168" s="2"/>
       <c r="R168" s="2"/>
     </row>
-    <row r="169" spans="1:18">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>190</v>
       </c>
@@ -8604,7 +8604,7 @@
       <c r="P169" s="2"/>
       <c r="R169" s="2"/>
     </row>
-    <row r="170" spans="1:18">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>191</v>
       </c>
@@ -8641,7 +8641,7 @@
       <c r="P170" s="2"/>
       <c r="R170" s="2"/>
     </row>
-    <row r="171" spans="1:18">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>192</v>
       </c>
@@ -8678,7 +8678,7 @@
       <c r="P171" s="2"/>
       <c r="R171" s="2"/>
     </row>
-    <row r="172" spans="1:18">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>193</v>
       </c>
@@ -8715,7 +8715,7 @@
       <c r="P172" s="2"/>
       <c r="R172" s="2"/>
     </row>
-    <row r="173" spans="1:18">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>194</v>
       </c>
@@ -8752,7 +8752,7 @@
       <c r="P173" s="2"/>
       <c r="R173" s="2"/>
     </row>
-    <row r="174" spans="1:18">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>195</v>
       </c>
@@ -8789,7 +8789,7 @@
       <c r="P174" s="2"/>
       <c r="R174" s="2"/>
     </row>
-    <row r="175" spans="1:18">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>196</v>
       </c>
@@ -8826,7 +8826,7 @@
       <c r="P175" s="2"/>
       <c r="R175" s="2"/>
     </row>
-    <row r="176" spans="1:18">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>197</v>
       </c>
@@ -8863,7 +8863,7 @@
       <c r="P176" s="2"/>
       <c r="R176" s="2"/>
     </row>
-    <row r="177" spans="1:18">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>198</v>
       </c>
@@ -8900,7 +8900,7 @@
       <c r="P177" s="2"/>
       <c r="R177" s="2"/>
     </row>
-    <row r="178" spans="1:18">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>199</v>
       </c>
@@ -8937,7 +8937,7 @@
       <c r="P178" s="2"/>
       <c r="R178" s="2"/>
     </row>
-    <row r="179" spans="1:18">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>200</v>
       </c>
@@ -8974,7 +8974,7 @@
       <c r="P179" s="2"/>
       <c r="R179" s="2"/>
     </row>
-    <row r="180" spans="1:18">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>201</v>
       </c>
@@ -9011,7 +9011,7 @@
       <c r="P180" s="2"/>
       <c r="R180" s="2"/>
     </row>
-    <row r="181" spans="1:18">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>202</v>
       </c>
@@ -9048,7 +9048,7 @@
       <c r="P181" s="2"/>
       <c r="R181" s="2"/>
     </row>
-    <row r="182" spans="1:18">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>203</v>
       </c>
@@ -9085,7 +9085,7 @@
       <c r="P182" s="2"/>
       <c r="R182" s="2"/>
     </row>
-    <row r="183" spans="1:18">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>204</v>
       </c>
@@ -9122,7 +9122,7 @@
       <c r="P183" s="2"/>
       <c r="R183" s="2"/>
     </row>
-    <row r="184" spans="1:18">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>205</v>
       </c>
@@ -9159,7 +9159,7 @@
       <c r="P184" s="2"/>
       <c r="R184" s="2"/>
     </row>
-    <row r="185" spans="1:18">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>206</v>
       </c>
@@ -9196,7 +9196,7 @@
       <c r="P185" s="2"/>
       <c r="R185" s="2"/>
     </row>
-    <row r="186" spans="1:18">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>207</v>
       </c>
@@ -9230,7 +9230,7 @@
       <c r="P186" s="2"/>
       <c r="R186" s="2"/>
     </row>
-    <row r="187" spans="1:18">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>208</v>
       </c>
@@ -9267,7 +9267,7 @@
       <c r="P187" s="2"/>
       <c r="R187" s="2"/>
     </row>
-    <row r="188" spans="1:18">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>209</v>
       </c>
@@ -9302,7 +9302,7 @@
       <c r="P188" s="2"/>
       <c r="R188" s="2"/>
     </row>
-    <row r="189" spans="1:18">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>210</v>
       </c>
@@ -9339,7 +9339,7 @@
       <c r="P189" s="2"/>
       <c r="R189" s="2"/>
     </row>
-    <row r="190" spans="1:18">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>211</v>
       </c>
@@ -9376,7 +9376,7 @@
       <c r="P190" s="2"/>
       <c r="R190" s="2"/>
     </row>
-    <row r="191" spans="1:18">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>212</v>
       </c>
@@ -9413,7 +9413,7 @@
       <c r="P191" s="2"/>
       <c r="R191" s="2"/>
     </row>
-    <row r="192" spans="1:18">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>213</v>
       </c>
@@ -9447,7 +9447,7 @@
       <c r="P192" s="2"/>
       <c r="R192" s="2"/>
     </row>
-    <row r="193" spans="1:22">
+    <row r="193" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>214</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="194" spans="1:22">
+    <row r="194" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>215</v>
       </c>
@@ -9519,7 +9519,7 @@
       <c r="P194" s="2"/>
       <c r="R194" s="2"/>
     </row>
-    <row r="195" spans="1:22">
+    <row r="195" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>216</v>
       </c>
@@ -9556,7 +9556,7 @@
       <c r="P195" s="2"/>
       <c r="R195" s="2"/>
     </row>
-    <row r="196" spans="1:22">
+    <row r="196" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>217</v>
       </c>
@@ -9593,7 +9593,7 @@
       <c r="P196" s="2"/>
       <c r="R196" s="2"/>
     </row>
-    <row r="197" spans="1:22">
+    <row r="197" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>218</v>
       </c>
@@ -9630,7 +9630,7 @@
       <c r="P197" s="2"/>
       <c r="R197" s="2"/>
     </row>
-    <row r="198" spans="1:22">
+    <row r="198" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>219</v>
       </c>
@@ -9664,7 +9664,7 @@
       <c r="P198" s="2"/>
       <c r="R198" s="2"/>
     </row>
-    <row r="199" spans="1:22">
+    <row r="199" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>220</v>
       </c>
@@ -9699,7 +9699,7 @@
       <c r="P199" s="2"/>
       <c r="R199" s="2"/>
     </row>
-    <row r="200" spans="1:22">
+    <row r="200" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>221</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="201" spans="1:22">
+    <row r="201" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>222</v>
       </c>
@@ -9774,7 +9774,7 @@
       <c r="P201" s="2"/>
       <c r="R201" s="2"/>
     </row>
-    <row r="202" spans="1:22">
+    <row r="202" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>223</v>
       </c>
@@ -9808,7 +9808,7 @@
       <c r="P202" s="2"/>
       <c r="R202" s="2"/>
     </row>
-    <row r="203" spans="1:22">
+    <row r="203" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>224</v>
       </c>
@@ -9845,7 +9845,7 @@
       <c r="P203" s="2"/>
       <c r="R203" s="2"/>
     </row>
-    <row r="204" spans="1:22">
+    <row r="204" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>225</v>
       </c>
@@ -9882,7 +9882,7 @@
       <c r="P204" s="2"/>
       <c r="R204" s="2"/>
     </row>
-    <row r="205" spans="1:22">
+    <row r="205" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>226</v>
       </c>
@@ -9916,7 +9916,7 @@
       <c r="P205" s="2"/>
       <c r="R205" s="2"/>
     </row>
-    <row r="206" spans="1:22">
+    <row r="206" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>227</v>
       </c>
@@ -9950,7 +9950,7 @@
       <c r="P206" s="2"/>
       <c r="R206" s="2"/>
     </row>
-    <row r="207" spans="1:22">
+    <row r="207" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>228</v>
       </c>
@@ -9984,7 +9984,7 @@
       <c r="P207" s="2"/>
       <c r="R207" s="2"/>
     </row>
-    <row r="208" spans="1:22">
+    <row r="208" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>229</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="209" spans="1:21">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>230</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="210" spans="1:21">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>231</v>
       </c>
@@ -10095,7 +10095,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="211" spans="1:21">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>232</v>
       </c>
@@ -10133,7 +10133,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="212" spans="1:21">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>233</v>
       </c>
@@ -10171,7 +10171,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="213" spans="1:21">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>234</v>
       </c>
@@ -10206,7 +10206,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="214" spans="1:21">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>235</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="215" spans="1:21">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>236</v>
       </c>
@@ -10278,7 +10278,7 @@
       <c r="P215" s="2"/>
       <c r="R215" s="2"/>
     </row>
-    <row r="216" spans="1:21">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>237</v>
       </c>
@@ -10312,7 +10312,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="217" spans="1:21">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>238</v>
       </c>
@@ -10346,7 +10346,7 @@
       <c r="P217" s="2"/>
       <c r="R217" s="2"/>
     </row>
-    <row r="218" spans="1:21">
+    <row r="218" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>239</v>
       </c>
@@ -10380,7 +10380,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="219" spans="1:21">
+    <row r="219" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>240</v>
       </c>
@@ -10417,7 +10417,7 @@
       <c r="P219" s="2"/>
       <c r="R219" s="2"/>
     </row>
-    <row r="220" spans="1:21">
+    <row r="220" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>241</v>
       </c>
@@ -10451,7 +10451,7 @@
       <c r="P220" s="2"/>
       <c r="R220" s="2"/>
     </row>
-    <row r="221" spans="1:21">
+    <row r="221" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>242</v>
       </c>
@@ -10485,7 +10485,7 @@
       <c r="P221" s="2"/>
       <c r="R221" s="2"/>
     </row>
-    <row r="222" spans="1:21">
+    <row r="222" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>243</v>
       </c>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="R222" s="2"/>
     </row>
-    <row r="223" spans="1:21">
+    <row r="223" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>244</v>
       </c>
@@ -10553,7 +10553,7 @@
       <c r="P223" s="2"/>
       <c r="R223" s="2"/>
     </row>
-    <row r="224" spans="1:21">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>245</v>
       </c>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="R224" s="2"/>
     </row>
-    <row r="225" spans="1:23">
+    <row r="225" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>246</v>
       </c>
@@ -10621,7 +10621,7 @@
       <c r="P225" s="2"/>
       <c r="R225" s="2"/>
     </row>
-    <row r="226" spans="1:23">
+    <row r="226" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>247</v>
       </c>
@@ -10655,7 +10655,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="227" spans="1:23">
+    <row r="227" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>248</v>
       </c>
@@ -10689,7 +10689,7 @@
       <c r="P227" s="2"/>
       <c r="R227" s="2"/>
     </row>
-    <row r="228" spans="1:23">
+    <row r="228" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>249</v>
       </c>
@@ -10723,7 +10723,7 @@
       <c r="P228" s="2"/>
       <c r="R228" s="2"/>
     </row>
-    <row r="229" spans="1:23">
+    <row r="229" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>250</v>
       </c>
@@ -10757,7 +10757,7 @@
       <c r="P229" s="2"/>
       <c r="R229" s="2"/>
     </row>
-    <row r="230" spans="1:23">
+    <row r="230" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>251</v>
       </c>
@@ -10791,7 +10791,7 @@
       <c r="P230" s="2"/>
       <c r="R230" s="2"/>
     </row>
-    <row r="231" spans="1:23">
+    <row r="231" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>252</v>
       </c>
@@ -10828,7 +10828,7 @@
       <c r="P231" s="2"/>
       <c r="R231" s="2"/>
     </row>
-    <row r="232" spans="1:23">
+    <row r="232" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>253</v>
       </c>
@@ -10862,7 +10862,7 @@
       <c r="P232" s="2"/>
       <c r="R232" s="2"/>
     </row>
-    <row r="233" spans="1:23">
+    <row r="233" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>254</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="234" spans="1:23">
+    <row r="234" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>255</v>
       </c>
@@ -10937,7 +10937,7 @@
       <c r="P234" s="2"/>
       <c r="R234" s="2"/>
     </row>
-    <row r="235" spans="1:23">
+    <row r="235" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>256</v>
       </c>
@@ -10974,7 +10974,7 @@
       <c r="P235" s="2"/>
       <c r="R235" s="2"/>
     </row>
-    <row r="236" spans="1:23">
+    <row r="236" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>257</v>
       </c>
@@ -11009,7 +11009,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="237" spans="1:23">
+    <row r="237" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>258</v>
       </c>
@@ -11044,7 +11044,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="238" spans="1:23">
+    <row r="238" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>259</v>
       </c>
@@ -11078,7 +11078,7 @@
       <c r="P238" s="2"/>
       <c r="R238" s="2"/>
     </row>
-    <row r="239" spans="1:23">
+    <row r="239" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>260</v>
       </c>
@@ -11112,7 +11112,7 @@
       <c r="P239" s="2"/>
       <c r="R239" s="2"/>
     </row>
-    <row r="240" spans="1:23">
+    <row r="240" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>261</v>
       </c>
@@ -11146,7 +11146,7 @@
       <c r="P240" s="2"/>
       <c r="R240" s="2"/>
     </row>
-    <row r="241" spans="1:22">
+    <row r="241" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>262</v>
       </c>
@@ -11180,7 +11180,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="242" spans="1:22">
+    <row r="242" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>263</v>
       </c>
@@ -11217,7 +11217,7 @@
       <c r="P242" s="2"/>
       <c r="R242" s="2"/>
     </row>
-    <row r="243" spans="1:22">
+    <row r="243" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>264</v>
       </c>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="R243" s="2"/>
     </row>
-    <row r="244" spans="1:22">
+    <row r="244" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>265</v>
       </c>
@@ -11285,7 +11285,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="245" spans="1:22">
+    <row r="245" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>266</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="246" spans="1:22">
+    <row r="246" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>267</v>
       </c>
@@ -11354,7 +11354,7 @@
       <c r="P246" s="2"/>
       <c r="R246" s="2"/>
     </row>
-    <row r="247" spans="1:22">
+    <row r="247" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>268</v>
       </c>
@@ -11388,7 +11388,7 @@
       <c r="P247" s="2"/>
       <c r="R247" s="2"/>
     </row>
-    <row r="248" spans="1:22">
+    <row r="248" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>269</v>
       </c>
@@ -11425,7 +11425,7 @@
       <c r="P248" s="2"/>
       <c r="R248" s="2"/>
     </row>
-    <row r="249" spans="1:22">
+    <row r="249" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>270</v>
       </c>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="R249" s="2"/>
     </row>
-    <row r="250" spans="1:22">
+    <row r="250" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>271</v>
       </c>
@@ -11494,7 +11494,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="251" spans="1:22">
+    <row r="251" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>272</v>
       </c>
@@ -11528,7 +11528,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="252" spans="1:22">
+    <row r="252" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>273</v>
       </c>
@@ -11562,7 +11562,7 @@
       <c r="P252" s="2"/>
       <c r="R252" s="2"/>
     </row>
-    <row r="253" spans="1:22">
+    <row r="253" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>274</v>
       </c>
@@ -11596,7 +11596,7 @@
       <c r="P253" s="2"/>
       <c r="R253" s="2"/>
     </row>
-    <row r="254" spans="1:22">
+    <row r="254" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>275</v>
       </c>
@@ -11631,7 +11631,7 @@
       <c r="P254" s="2"/>
       <c r="R254" s="2"/>
     </row>
-    <row r="255" spans="1:22">
+    <row r="255" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>276</v>
       </c>
@@ -11668,7 +11668,7 @@
       <c r="P255" s="2"/>
       <c r="R255" s="2"/>
     </row>
-    <row r="256" spans="1:22">
+    <row r="256" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>277</v>
       </c>
@@ -11702,7 +11702,7 @@
       <c r="P256" s="2"/>
       <c r="R256" s="2"/>
     </row>
-    <row r="257" spans="1:23">
+    <row r="257" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>278</v>
       </c>
@@ -11736,7 +11736,7 @@
       <c r="P257" s="2"/>
       <c r="R257" s="2"/>
     </row>
-    <row r="258" spans="1:23">
+    <row r="258" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>279</v>
       </c>
@@ -11774,7 +11774,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="259" spans="1:23">
+    <row r="259" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>280</v>
       </c>
@@ -11808,7 +11808,7 @@
       <c r="P259" s="2"/>
       <c r="R259" s="2"/>
     </row>
-    <row r="260" spans="1:23">
+    <row r="260" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>281</v>
       </c>
@@ -11845,7 +11845,7 @@
       <c r="P260" s="2"/>
       <c r="R260" s="2"/>
     </row>
-    <row r="261" spans="1:23">
+    <row r="261" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>282</v>
       </c>
@@ -11879,7 +11879,7 @@
       <c r="P261" s="2"/>
       <c r="R261" s="2"/>
     </row>
-    <row r="262" spans="1:23">
+    <row r="262" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>283</v>
       </c>
@@ -11916,7 +11916,7 @@
       <c r="P262" s="2"/>
       <c r="R262" s="2"/>
     </row>
-    <row r="263" spans="1:23">
+    <row r="263" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>284</v>
       </c>
@@ -11950,7 +11950,7 @@
       <c r="P263" s="2"/>
       <c r="R263" s="2"/>
     </row>
-    <row r="264" spans="1:23">
+    <row r="264" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>285</v>
       </c>
@@ -11987,7 +11987,7 @@
       <c r="P264" s="2"/>
       <c r="R264" s="2"/>
     </row>
-    <row r="265" spans="1:23">
+    <row r="265" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>286</v>
       </c>
@@ -12021,7 +12021,7 @@
       <c r="P265" s="2"/>
       <c r="R265" s="2"/>
     </row>
-    <row r="266" spans="1:23">
+    <row r="266" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>287</v>
       </c>
@@ -12055,7 +12055,7 @@
       <c r="P266" s="2"/>
       <c r="R266" s="2"/>
     </row>
-    <row r="267" spans="1:23">
+    <row r="267" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>288</v>
       </c>
@@ -12089,7 +12089,7 @@
       </c>
       <c r="R267" s="2"/>
     </row>
-    <row r="268" spans="1:23">
+    <row r="268" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>289</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="269" spans="1:23">
+    <row r="269" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>290</v>
       </c>
@@ -12164,7 +12164,7 @@
       <c r="P269" s="2"/>
       <c r="R269" s="2"/>
     </row>
-    <row r="270" spans="1:23">
+    <row r="270" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>291</v>
       </c>
@@ -12199,7 +12199,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="271" spans="1:23">
+    <row r="271" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>292</v>
       </c>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="R271" s="2"/>
     </row>
-    <row r="272" spans="1:23">
+    <row r="272" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>293</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="273" spans="1:23">
+    <row r="273" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>294</v>
       </c>
@@ -12306,7 +12306,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="274" spans="1:23">
+    <row r="274" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>295</v>
       </c>
@@ -12341,7 +12341,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="275" spans="1:23">
+    <row r="275" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>296</v>
       </c>
@@ -12379,7 +12379,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="276" spans="1:23">
+    <row r="276" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>297</v>
       </c>
@@ -12413,7 +12413,7 @@
       <c r="P276" s="2"/>
       <c r="R276" s="2"/>
     </row>
-    <row r="277" spans="1:23">
+    <row r="277" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>298</v>
       </c>
@@ -12447,7 +12447,7 @@
       <c r="P277" s="2"/>
       <c r="R277" s="2"/>
     </row>
-    <row r="278" spans="1:23">
+    <row r="278" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>299</v>
       </c>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="R278" s="2"/>
     </row>
-    <row r="279" spans="1:23">
+    <row r="279" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>300</v>
       </c>
@@ -12515,7 +12515,7 @@
       <c r="P279" s="2"/>
       <c r="R279" s="2"/>
     </row>
-    <row r="280" spans="1:23">
+    <row r="280" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>301</v>
       </c>
@@ -12549,7 +12549,7 @@
       <c r="P280" s="2"/>
       <c r="R280" s="2"/>
     </row>
-    <row r="281" spans="1:23">
+    <row r="281" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>302</v>
       </c>
@@ -12583,7 +12583,7 @@
       <c r="P281" s="2"/>
       <c r="R281" s="2"/>
     </row>
-    <row r="282" spans="1:23">
+    <row r="282" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>303</v>
       </c>
@@ -12620,7 +12620,7 @@
       <c r="P282" s="2"/>
       <c r="R282" s="2"/>
     </row>
-    <row r="283" spans="1:23">
+    <row r="283" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>304</v>
       </c>
@@ -12655,7 +12655,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="284" spans="1:23">
+    <row r="284" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>306</v>
       </c>
@@ -12692,7 +12692,7 @@
       <c r="P284" s="2"/>
       <c r="R284" s="2"/>
     </row>
-    <row r="285" spans="1:23">
+    <row r="285" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>307</v>
       </c>
@@ -12726,7 +12726,7 @@
       <c r="P285" s="2"/>
       <c r="R285" s="2"/>
     </row>
-    <row r="286" spans="1:23">
+    <row r="286" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>308</v>
       </c>
@@ -12760,7 +12760,7 @@
       <c r="P286" s="2"/>
       <c r="R286" s="2"/>
     </row>
-    <row r="287" spans="1:23">
+    <row r="287" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>309</v>
       </c>
@@ -12794,7 +12794,7 @@
       <c r="P287" s="2"/>
       <c r="R287" s="2"/>
     </row>
-    <row r="288" spans="1:23">
+    <row r="288" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>310</v>
       </c>
@@ -12828,7 +12828,7 @@
       <c r="P288" s="2"/>
       <c r="R288" s="2"/>
     </row>
-    <row r="289" spans="1:23">
+    <row r="289" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>311</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="290" spans="1:23">
+    <row r="290" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>312</v>
       </c>
@@ -12896,7 +12896,7 @@
       <c r="P290" s="2"/>
       <c r="R290" s="2"/>
     </row>
-    <row r="291" spans="1:23">
+    <row r="291" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>313</v>
       </c>
@@ -12933,7 +12933,7 @@
       <c r="P291" s="2"/>
       <c r="R291" s="2"/>
     </row>
-    <row r="292" spans="1:23">
+    <row r="292" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>314</v>
       </c>
@@ -12968,7 +12968,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="293" spans="1:23">
+    <row r="293" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>315</v>
       </c>
@@ -13003,7 +13003,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="294" spans="1:23">
+    <row r="294" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>316</v>
       </c>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="R294" s="2"/>
     </row>
-    <row r="295" spans="1:23">
+    <row r="295" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>317</v>
       </c>
@@ -13075,7 +13075,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="296" spans="1:23">
+    <row r="296" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>318</v>
       </c>
@@ -13109,7 +13109,7 @@
       <c r="P296" s="2"/>
       <c r="R296" s="2"/>
     </row>
-    <row r="297" spans="1:23">
+    <row r="297" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>319</v>
       </c>
@@ -13143,7 +13143,7 @@
       <c r="P297" s="2"/>
       <c r="R297" s="2"/>
     </row>
-    <row r="298" spans="1:23">
+    <row r="298" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>320</v>
       </c>
@@ -13178,7 +13178,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="299" spans="1:23">
+    <row r="299" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>321</v>
       </c>
@@ -13215,7 +13215,7 @@
       <c r="P299" s="2"/>
       <c r="R299" s="2"/>
     </row>
-    <row r="300" spans="1:23">
+    <row r="300" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>322</v>
       </c>
@@ -13253,7 +13253,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="301" spans="1:23">
+    <row r="301" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>323</v>
       </c>
@@ -13287,7 +13287,7 @@
       <c r="P301" s="2"/>
       <c r="R301" s="2"/>
     </row>
-    <row r="302" spans="1:23">
+    <row r="302" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>324</v>
       </c>
@@ -13321,7 +13321,7 @@
       <c r="P302" s="2"/>
       <c r="R302" s="2"/>
     </row>
-    <row r="303" spans="1:23">
+    <row r="303" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>325</v>
       </c>
@@ -13355,7 +13355,7 @@
       <c r="P303" s="2"/>
       <c r="R303" s="2"/>
     </row>
-    <row r="304" spans="1:23">
+    <row r="304" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>326</v>
       </c>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="R304" s="2"/>
     </row>
-    <row r="305" spans="1:23">
+    <row r="305" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>327</v>
       </c>
@@ -13423,7 +13423,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="306" spans="1:23">
+    <row r="306" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>328</v>
       </c>
@@ -13457,7 +13457,7 @@
       <c r="P306" s="2"/>
       <c r="R306" s="2"/>
     </row>
-    <row r="307" spans="1:23">
+    <row r="307" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>329</v>
       </c>
@@ -13491,7 +13491,7 @@
       <c r="P307" s="2"/>
       <c r="R307" s="2"/>
     </row>
-    <row r="308" spans="1:23">
+    <row r="308" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>330</v>
       </c>
@@ -13525,7 +13525,7 @@
       <c r="P308" s="2"/>
       <c r="R308" s="2"/>
     </row>
-    <row r="309" spans="1:23">
+    <row r="309" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>331</v>
       </c>
@@ -13562,7 +13562,7 @@
       <c r="P309" s="2"/>
       <c r="R309" s="2"/>
     </row>
-    <row r="310" spans="1:23">
+    <row r="310" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>332</v>
       </c>
@@ -13596,7 +13596,7 @@
       <c r="P310" s="2"/>
       <c r="R310" s="2"/>
     </row>
-    <row r="311" spans="1:23">
+    <row r="311" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>333</v>
       </c>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="R311" s="2"/>
     </row>
-    <row r="312" spans="1:23">
+    <row r="312" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>334</v>
       </c>
@@ -13664,7 +13664,7 @@
       <c r="P312" s="2"/>
       <c r="R312" s="2"/>
     </row>
-    <row r="313" spans="1:23">
+    <row r="313" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>335</v>
       </c>
@@ -13698,7 +13698,7 @@
       <c r="P313" s="2"/>
       <c r="R313" s="2"/>
     </row>
-    <row r="314" spans="1:23">
+    <row r="314" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>336</v>
       </c>
@@ -13732,7 +13732,7 @@
       <c r="P314" s="2"/>
       <c r="R314" s="2"/>
     </row>
-    <row r="315" spans="1:23">
+    <row r="315" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>337</v>
       </c>
@@ -13767,7 +13767,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="316" spans="1:23">
+    <row r="316" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>338</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="317" spans="1:23">
+    <row r="317" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>339</v>
       </c>
@@ -13836,7 +13836,7 @@
       <c r="P317" s="2"/>
       <c r="R317" s="2"/>
     </row>
-    <row r="318" spans="1:23">
+    <row r="318" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>340</v>
       </c>
@@ -13870,7 +13870,7 @@
       <c r="P318" s="2"/>
       <c r="R318" s="2"/>
     </row>
-    <row r="319" spans="1:23">
+    <row r="319" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>341</v>
       </c>
@@ -13907,7 +13907,7 @@
       <c r="P319" s="2"/>
       <c r="R319" s="2"/>
     </row>
-    <row r="320" spans="1:23">
+    <row r="320" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>342</v>
       </c>
@@ -13942,7 +13942,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="321" spans="1:23">
+    <row r="321" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>343</v>
       </c>
@@ -13980,7 +13980,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="322" spans="1:23">
+    <row r="322" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>344</v>
       </c>
@@ -14014,7 +14014,7 @@
       <c r="P322" s="2"/>
       <c r="R322" s="2"/>
     </row>
-    <row r="323" spans="1:23">
+    <row r="323" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>345</v>
       </c>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="R323" s="2"/>
     </row>
-    <row r="324" spans="1:23">
+    <row r="324" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>354</v>
       </c>
@@ -14083,7 +14083,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="325" spans="1:23">
+    <row r="325" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>355</v>
       </c>
@@ -14121,7 +14121,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="326" spans="1:23">
+    <row r="326" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>356</v>
       </c>
@@ -14155,7 +14155,7 @@
       <c r="P326" s="2"/>
       <c r="R326" s="2"/>
     </row>
-    <row r="327" spans="1:23">
+    <row r="327" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>357</v>
       </c>
@@ -14189,7 +14189,7 @@
       <c r="P327" s="2"/>
       <c r="R327" s="2"/>
     </row>
-    <row r="328" spans="1:23">
+    <row r="328" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>358</v>
       </c>
@@ -14224,7 +14224,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="329" spans="1:23">
+    <row r="329" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>359</v>
       </c>
@@ -14259,7 +14259,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="330" spans="1:23">
+    <row r="330" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>360</v>
       </c>
@@ -14293,7 +14293,7 @@
       <c r="P330" s="2"/>
       <c r="R330" s="2"/>
     </row>
-    <row r="331" spans="1:23" ht="15" customHeight="1">
+    <row r="331" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>361</v>
       </c>
@@ -14327,7 +14327,7 @@
       <c r="P331" s="2"/>
       <c r="R331" s="2"/>
     </row>
-    <row r="332" spans="1:23" ht="15" customHeight="1">
+    <row r="332" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>362</v>
       </c>
@@ -14361,7 +14361,7 @@
       <c r="P332" s="2"/>
       <c r="R332" s="2"/>
     </row>
-    <row r="333" spans="1:23" ht="15" customHeight="1">
+    <row r="333" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>363</v>
       </c>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="R333" s="2"/>
     </row>
-    <row r="334" spans="1:23" ht="15" customHeight="1">
+    <row r="334" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>364</v>
       </c>
@@ -14429,7 +14429,7 @@
       <c r="P334" s="2"/>
       <c r="R334" s="2"/>
     </row>
-    <row r="335" spans="1:23" ht="15" customHeight="1">
+    <row r="335" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>365</v>
       </c>
@@ -14464,7 +14464,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="15" customHeight="1">
+    <row r="336" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>366</v>
       </c>
@@ -14499,7 +14499,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="337" spans="1:22" ht="15" customHeight="1">
+    <row r="337" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>367</v>
       </c>
@@ -14534,7 +14534,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="338" spans="1:22" ht="15" customHeight="1">
+    <row r="338" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>368</v>
       </c>
@@ -14568,7 +14568,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="339" spans="1:22" ht="15" customHeight="1">
+    <row r="339" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>369</v>
       </c>
@@ -14602,7 +14602,7 @@
       <c r="P339" s="2"/>
       <c r="R339" s="2"/>
     </row>
-    <row r="340" spans="1:22" ht="15" customHeight="1">
+    <row r="340" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>370</v>
       </c>
@@ -14636,7 +14636,7 @@
       <c r="P340" s="2"/>
       <c r="R340" s="2"/>
     </row>
-    <row r="341" spans="1:22" ht="15" customHeight="1">
+    <row r="341" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>371</v>
       </c>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="R341" s="2"/>
     </row>
-    <row r="342" spans="1:22" ht="15" customHeight="1">
+    <row r="342" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>372</v>
       </c>
@@ -14704,7 +14704,7 @@
       <c r="P342" s="2"/>
       <c r="R342" s="2"/>
     </row>
-    <row r="343" spans="1:22" ht="15" customHeight="1">
+    <row r="343" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>373</v>
       </c>
@@ -14738,7 +14738,7 @@
       <c r="P343" s="2"/>
       <c r="R343" s="2"/>
     </row>
-    <row r="344" spans="1:22" ht="15" customHeight="1">
+    <row r="344" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>374</v>
       </c>
@@ -14772,7 +14772,7 @@
       <c r="P344" s="2"/>
       <c r="R344" s="2"/>
     </row>
-    <row r="345" spans="1:22" ht="15" customHeight="1">
+    <row r="345" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>375</v>
       </c>
@@ -14806,7 +14806,7 @@
       </c>
       <c r="R345" s="2"/>
     </row>
-    <row r="346" spans="1:22" ht="15" customHeight="1">
+    <row r="346" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>376</v>
       </c>
@@ -14841,7 +14841,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="347" spans="1:22" ht="15" customHeight="1">
+    <row r="347" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>377</v>
       </c>
@@ -14875,7 +14875,7 @@
       <c r="P347" s="2"/>
       <c r="R347" s="2"/>
     </row>
-    <row r="348" spans="1:22" ht="15" customHeight="1">
+    <row r="348" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>378</v>
       </c>
@@ -14909,7 +14909,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="349" spans="1:22" ht="15" customHeight="1">
+    <row r="349" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>379</v>
       </c>
@@ -14943,7 +14943,7 @@
       <c r="P349" s="2"/>
       <c r="R349" s="2"/>
     </row>
-    <row r="350" spans="1:22" ht="15" customHeight="1">
+    <row r="350" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>380</v>
       </c>
@@ -14977,7 +14977,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="351" spans="1:22" ht="15" customHeight="1">
+    <row r="351" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>381</v>
       </c>
@@ -15011,7 +15011,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="352" spans="1:22" ht="15" customHeight="1">
+    <row r="352" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>382</v>
       </c>
@@ -15045,7 +15045,7 @@
       <c r="P352" s="2"/>
       <c r="R352" s="2"/>
     </row>
-    <row r="353" spans="1:23" ht="15" customHeight="1">
+    <row r="353" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>383</v>
       </c>
@@ -15080,7 +15080,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="15" customHeight="1">
+    <row r="354" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>384</v>
       </c>
@@ -15114,7 +15114,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="355" spans="1:23" ht="15" customHeight="1">
+    <row r="355" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>385</v>
       </c>
@@ -15149,7 +15149,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="356" spans="1:23" ht="15" customHeight="1">
+    <row r="356" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>386</v>
       </c>
@@ -15184,7 +15184,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="357" spans="1:23" ht="15" customHeight="1">
+    <row r="357" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>387</v>
       </c>
@@ -15218,7 +15218,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="15" customHeight="1">
+    <row r="358" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>388</v>
       </c>
@@ -15253,7 +15253,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="359" spans="1:23" ht="15" customHeight="1">
+    <row r="359" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>389</v>
       </c>
@@ -15287,7 +15287,7 @@
       <c r="P359" s="2"/>
       <c r="R359" s="2"/>
     </row>
-    <row r="360" spans="1:23" ht="15" customHeight="1">
+    <row r="360" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>390</v>
       </c>
@@ -15321,7 +15321,7 @@
       <c r="P360" s="2"/>
       <c r="R360" s="2"/>
     </row>
-    <row r="361" spans="1:23" ht="15" customHeight="1">
+    <row r="361" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>391</v>
       </c>
@@ -15355,7 +15355,7 @@
       <c r="P361" s="2"/>
       <c r="R361" s="2"/>
     </row>
-    <row r="362" spans="1:23" ht="15" customHeight="1">
+    <row r="362" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>392</v>
       </c>
@@ -15390,7 +15390,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="363" spans="1:23" ht="15" customHeight="1">
+    <row r="363" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>393</v>
       </c>
@@ -15425,7 +15425,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="364" spans="1:23" ht="15" customHeight="1">
+    <row r="364" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>394</v>
       </c>
@@ -15459,7 +15459,7 @@
       <c r="P364" s="2"/>
       <c r="R364" s="2"/>
     </row>
-    <row r="365" spans="1:23" ht="15" customHeight="1">
+    <row r="365" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>395</v>
       </c>
@@ -15494,7 +15494,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="366" spans="1:23" ht="15" customHeight="1">
+    <row r="366" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>396</v>
       </c>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="R366" s="2"/>
     </row>
-    <row r="367" spans="1:23" ht="15" customHeight="1">
+    <row r="367" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>397</v>
       </c>
@@ -15562,7 +15562,7 @@
       <c r="P367" s="2"/>
       <c r="R367" s="2"/>
     </row>
-    <row r="368" spans="1:23" ht="15" customHeight="1">
+    <row r="368" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>398</v>
       </c>
@@ -15596,7 +15596,7 @@
       </c>
       <c r="R368" s="2"/>
     </row>
-    <row r="369" spans="1:23" ht="15" customHeight="1">
+    <row r="369" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>399</v>
       </c>
@@ -15631,7 +15631,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="370" spans="1:23" ht="15" customHeight="1">
+    <row r="370" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>400</v>
       </c>
@@ -15666,7 +15666,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="371" spans="1:23" ht="15" customHeight="1">
+    <row r="371" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>401</v>
       </c>
@@ -15700,7 +15700,7 @@
       <c r="P371" s="2"/>
       <c r="R371" s="2"/>
     </row>
-    <row r="372" spans="1:23" ht="15" customHeight="1">
+    <row r="372" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>402</v>
       </c>
@@ -15734,7 +15734,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="373" spans="1:23" ht="15" customHeight="1">
+    <row r="373" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>403</v>
       </c>
@@ -15768,7 +15768,7 @@
       <c r="P373" s="2"/>
       <c r="R373" s="2"/>
     </row>
-    <row r="374" spans="1:23" ht="15" customHeight="1">
+    <row r="374" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>404</v>
       </c>
@@ -15802,7 +15802,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="375" spans="1:23" ht="15" customHeight="1">
+    <row r="375" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>405</v>
       </c>
@@ -15836,7 +15836,7 @@
       </c>
       <c r="R375" s="2"/>
     </row>
-    <row r="376" spans="1:23" ht="15" customHeight="1">
+    <row r="376" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>406</v>
       </c>
@@ -15870,7 +15870,7 @@
       <c r="P376" s="2"/>
       <c r="R376" s="2"/>
     </row>
-    <row r="377" spans="1:23" ht="15" customHeight="1">
+    <row r="377" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>407</v>
       </c>
@@ -15904,7 +15904,7 @@
       <c r="P377" s="2"/>
       <c r="R377" s="2"/>
     </row>
-    <row r="378" spans="1:23" ht="15" customHeight="1">
+    <row r="378" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>408</v>
       </c>
@@ -15938,7 +15938,7 @@
       <c r="P378" s="2"/>
       <c r="R378" s="2"/>
     </row>
-    <row r="379" spans="1:23" ht="15" customHeight="1">
+    <row r="379" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>409</v>
       </c>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="R379" s="2"/>
     </row>
-    <row r="380" spans="1:23" ht="15" customHeight="1">
+    <row r="380" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>410</v>
       </c>
@@ -16006,7 +16006,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="381" spans="1:23" ht="15" customHeight="1">
+    <row r="381" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>411</v>
       </c>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="R381" s="2"/>
     </row>
-    <row r="382" spans="1:23" ht="15" customHeight="1">
+    <row r="382" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>412</v>
       </c>
@@ -16078,7 +16078,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="383" spans="1:23" ht="15" customHeight="1">
+    <row r="383" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>413</v>
       </c>
@@ -16112,7 +16112,7 @@
       <c r="P383" s="2"/>
       <c r="R383" s="2"/>
     </row>
-    <row r="384" spans="1:23" ht="15" customHeight="1">
+    <row r="384" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>414</v>
       </c>
@@ -16146,7 +16146,7 @@
       <c r="P384" s="2"/>
       <c r="R384" s="2"/>
     </row>
-    <row r="385" spans="1:23" ht="15" customHeight="1">
+    <row r="385" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>415</v>
       </c>
@@ -16180,7 +16180,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="386" spans="1:23" ht="15" customHeight="1">
+    <row r="386" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>416</v>
       </c>
@@ -16214,7 +16214,7 @@
       <c r="P386" s="2"/>
       <c r="R386" s="2"/>
     </row>
-    <row r="387" spans="1:23" ht="15" customHeight="1">
+    <row r="387" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>417</v>
       </c>
@@ -16248,7 +16248,7 @@
       <c r="P387" s="2"/>
       <c r="R387" s="2"/>
     </row>
-    <row r="388" spans="1:23" ht="15" customHeight="1">
+    <row r="388" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>418</v>
       </c>
@@ -16283,7 +16283,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="389" spans="1:23" ht="15" customHeight="1">
+    <row r="389" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>419</v>
       </c>
@@ -16317,7 +16317,7 @@
       <c r="P389" s="2"/>
       <c r="R389" s="2"/>
     </row>
-    <row r="390" spans="1:23" ht="15" customHeight="1">
+    <row r="390" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>420</v>
       </c>
@@ -16351,7 +16351,7 @@
       <c r="P390" s="2"/>
       <c r="R390" s="2"/>
     </row>
-    <row r="391" spans="1:23" ht="15" customHeight="1">
+    <row r="391" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>421</v>
       </c>
@@ -16385,7 +16385,7 @@
       <c r="P391" s="2"/>
       <c r="R391" s="2"/>
     </row>
-    <row r="392" spans="1:23" ht="15" customHeight="1">
+    <row r="392" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>422</v>
       </c>
@@ -16419,7 +16419,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="393" spans="1:23" ht="15" customHeight="1">
+    <row r="393" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>423</v>
       </c>
@@ -16437,7 +16437,7 @@
       </c>
       <c r="F393" s="7"/>
       <c r="G393" s="6">
-        <v>44152</v>
+        <v>43152</v>
       </c>
       <c r="H393" s="2" t="s">
         <v>219</v>
@@ -16453,7 +16453,7 @@
       <c r="P393" s="2"/>
       <c r="R393" s="2"/>
     </row>
-    <row r="394" spans="1:23" ht="15" customHeight="1">
+    <row r="394" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>424</v>
       </c>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{477A32C6-DED8-D848-898B-3AF68929AD67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB2AD1A2-ED5C-4F09-B447-3A5A5EE79553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="676">
   <si>
     <t>Id</t>
   </si>
@@ -1974,13 +1974,103 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/ed825cca-9421-415e-9460-1ac29c24db58_Starbucks%20Samara%20Sat.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/E2F41C8C-DBDB-446A-B625-7BA674A7739D_Starbucks%20Punta%20Nort.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_6355_Starbucks%20Arboledas.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Villas%20de.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/image_Starbucks%20Arboledas.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/3bc117ec-6b80-4f94-8384-1f70d943cd06_Starbucks%20Villas%20de.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38792@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Pasaje Tlalnepantla</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Pasaje%20Tla.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%201/image_Starbucks%20Pasaje%20Tla.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_5381_Starbucks%20Pasaje%20Tla.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Vanessa%20Carre%C3%B1o%20Rios.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Starbucks%20Pasaje%20Tla.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/E1936408-A8E5-4BF7-B725-129F6F24340C_Starbucks%20Punta%20Nort.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Punta%20Nort.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/659F0550-8495-4147-AEFA-7A8F76808DA3_Starbucks%20El%20Rosario.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Punta%20Nort.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/image_Starbucks%20Punta%20Nort.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/20471A6A-9FA4-4670-98EB-5C5DA5139FBC_Starbucks%20Pasaje%20Tla.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Starbucks%20Punta%20Nort.jpg</t>
+  </si>
+  <si>
+    <t>julian.flores@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Julian Alejandro Flores Garcia</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Julian%20Alejandro%20Flo.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/image_Starbucks%20Punta%20Nort.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Pasaje%20Tla.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/image_Starbucks%20Punta%20Nort.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_4292_Julian%20Alejandro%20Flo.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/image_Starbucks%20Pasaje%20Tla.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Pasaje%20Tla.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/77A8A83F-5E61-45D8-8DAD-49E2D8F601CE_Starbucks%20Pasaje%20Tla.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/6532E230-1F45-4DCB-B525-B1AD550D1784_Starbucks%20Pasaje%20Tla.jpeg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2019,7 +2109,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2032,6 +2122,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2122,8 +2216,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W394" totalsRowShown="0">
-  <autoFilter ref="A1:W394" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W421" totalsRowShown="0">
+  <autoFilter ref="A1:W421" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2290,7 +2384,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="424" latestEventMarker="691">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="451" latestEventMarker="718">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2619,22 +2713,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W394"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:W421"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" customWidth="1"/>
-    <col min="2" max="3" width="20.04296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.07421875" customWidth="1"/>
-    <col min="5" max="5" width="35.109375" customWidth="1"/>
-    <col min="6" max="6" width="7.80078125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.01171875" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="20.04296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="18.96484375" customWidth="1"/>
-    <col min="17" max="17" width="42.10546875" customWidth="1"/>
-    <col min="18" max="19" width="18.96484375" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="19" customWidth="1"/>
+    <col min="17" max="17" width="42.140625" customWidth="1"/>
+    <col min="18" max="19" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2705,7 +2799,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>13</v>
       </c>
@@ -2732,7 +2826,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>17</v>
       </c>
@@ -2766,7 +2860,7 @@
       <c r="P3" s="2"/>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>18</v>
       </c>
@@ -2800,7 +2894,7 @@
       </c>
       <c r="R4" s="2"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>20</v>
       </c>
@@ -2834,7 +2928,7 @@
       <c r="P5" s="2"/>
       <c r="R5" s="2"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>21</v>
       </c>
@@ -2868,7 +2962,7 @@
       <c r="P6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>22</v>
       </c>
@@ -2902,7 +2996,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>23</v>
       </c>
@@ -2937,7 +3031,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>24</v>
       </c>
@@ -2972,7 +3066,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>25</v>
       </c>
@@ -3007,7 +3101,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>26</v>
       </c>
@@ -3041,7 +3135,7 @@
       <c r="P11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>27</v>
       </c>
@@ -3078,7 +3172,7 @@
       <c r="P12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>28</v>
       </c>
@@ -3112,7 +3206,7 @@
       <c r="P13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23">
       <c r="A14">
         <v>29</v>
       </c>
@@ -3147,7 +3241,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23">
       <c r="A15">
         <v>30</v>
       </c>
@@ -3181,7 +3275,7 @@
       <c r="P15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23">
       <c r="A16">
         <v>31</v>
       </c>
@@ -3215,7 +3309,7 @@
       <c r="P16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21">
       <c r="A17">
         <v>32</v>
       </c>
@@ -3250,7 +3344,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21">
       <c r="A18">
         <v>33</v>
       </c>
@@ -3284,7 +3378,7 @@
       </c>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21">
       <c r="A19">
         <v>34</v>
       </c>
@@ -3318,7 +3412,7 @@
       <c r="P19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21">
       <c r="A20">
         <v>35</v>
       </c>
@@ -3352,7 +3446,7 @@
       <c r="P20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21">
       <c r="A21">
         <v>36</v>
       </c>
@@ -3386,7 +3480,7 @@
       <c r="P21" s="2"/>
       <c r="R21" s="2"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21">
       <c r="A22">
         <v>37</v>
       </c>
@@ -3421,7 +3515,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21">
       <c r="A23">
         <v>38</v>
       </c>
@@ -3456,7 +3550,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21">
       <c r="A24">
         <v>39</v>
       </c>
@@ -3491,7 +3585,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21">
       <c r="A25">
         <v>40</v>
       </c>
@@ -3526,7 +3620,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21">
       <c r="A26">
         <v>41</v>
       </c>
@@ -3560,7 +3654,7 @@
       <c r="P26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21">
       <c r="A27">
         <v>42</v>
       </c>
@@ -3595,7 +3689,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21">
       <c r="A28">
         <v>43</v>
       </c>
@@ -3630,7 +3724,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21">
       <c r="A29">
         <v>44</v>
       </c>
@@ -3665,7 +3759,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21">
       <c r="A30">
         <v>45</v>
       </c>
@@ -3700,7 +3794,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21">
       <c r="A31">
         <v>46</v>
       </c>
@@ -3735,7 +3829,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21">
       <c r="A32">
         <v>47</v>
       </c>
@@ -3770,7 +3864,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21">
       <c r="A33">
         <v>48</v>
       </c>
@@ -3804,7 +3898,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:21">
       <c r="A34">
         <v>49</v>
       </c>
@@ -3839,7 +3933,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21">
       <c r="A35">
         <v>50</v>
       </c>
@@ -3874,7 +3968,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21">
       <c r="A36">
         <v>51</v>
       </c>
@@ -3909,7 +4003,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:21">
       <c r="A37">
         <v>52</v>
       </c>
@@ -3943,7 +4037,7 @@
       <c r="P37" s="2"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:21">
       <c r="A38">
         <v>54</v>
       </c>
@@ -3977,7 +4071,7 @@
       <c r="P38" s="2"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:21">
       <c r="A39">
         <v>55</v>
       </c>
@@ -4011,7 +4105,7 @@
       </c>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:21">
       <c r="A40">
         <v>56</v>
       </c>
@@ -4046,7 +4140,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:21">
       <c r="A41">
         <v>57</v>
       </c>
@@ -4081,7 +4175,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21">
       <c r="A42">
         <v>58</v>
       </c>
@@ -4116,7 +4210,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21">
       <c r="A43">
         <v>59</v>
       </c>
@@ -4151,7 +4245,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:21">
       <c r="A44">
         <v>60</v>
       </c>
@@ -4186,7 +4280,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21">
       <c r="A45">
         <v>61</v>
       </c>
@@ -4221,7 +4315,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21">
       <c r="A46">
         <v>62</v>
       </c>
@@ -4256,7 +4350,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:21">
       <c r="A47">
         <v>63</v>
       </c>
@@ -4291,7 +4385,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:21">
       <c r="A48">
         <v>65</v>
       </c>
@@ -4326,7 +4420,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21">
       <c r="A49">
         <v>66</v>
       </c>
@@ -4361,7 +4455,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21">
       <c r="A50">
         <v>67</v>
       </c>
@@ -4395,7 +4489,7 @@
       <c r="P50" s="2"/>
       <c r="R50" s="2"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:21">
       <c r="A51">
         <v>68</v>
       </c>
@@ -4429,7 +4523,7 @@
       <c r="P51" s="2"/>
       <c r="R51" s="2"/>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:21">
       <c r="A52">
         <v>69</v>
       </c>
@@ -4464,7 +4558,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21">
       <c r="A53">
         <v>70</v>
       </c>
@@ -4499,7 +4593,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21">
       <c r="A54">
         <v>71</v>
       </c>
@@ -4534,7 +4628,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21">
       <c r="A55">
         <v>72</v>
       </c>
@@ -4569,7 +4663,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:21">
       <c r="A56">
         <v>73</v>
       </c>
@@ -4604,7 +4698,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:21">
       <c r="A57">
         <v>74</v>
       </c>
@@ -4639,7 +4733,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21">
       <c r="A58">
         <v>75</v>
       </c>
@@ -4674,7 +4768,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21">
       <c r="A59">
         <v>76</v>
       </c>
@@ -4709,7 +4803,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21">
       <c r="A60">
         <v>77</v>
       </c>
@@ -4743,7 +4837,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:21">
       <c r="A61">
         <v>78</v>
       </c>
@@ -4778,7 +4872,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:21">
       <c r="A62">
         <v>79</v>
       </c>
@@ -4813,7 +4907,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:21">
       <c r="A63">
         <v>80</v>
       </c>
@@ -4848,7 +4942,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:21">
       <c r="A64">
         <v>81</v>
       </c>
@@ -4883,7 +4977,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:21">
       <c r="A65">
         <v>84</v>
       </c>
@@ -4918,7 +5012,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:21">
       <c r="A66">
         <v>85</v>
       </c>
@@ -4952,7 +5046,7 @@
       <c r="P66" s="2"/>
       <c r="R66" s="2"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:21">
       <c r="A67">
         <v>86</v>
       </c>
@@ -4986,7 +5080,7 @@
       <c r="P67" s="2"/>
       <c r="R67" s="2"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:21">
       <c r="A68">
         <v>88</v>
       </c>
@@ -5020,7 +5114,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:21">
       <c r="A69">
         <v>89</v>
       </c>
@@ -5054,7 +5148,7 @@
       <c r="P69" s="2"/>
       <c r="R69" s="2"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:21">
       <c r="A70">
         <v>90</v>
       </c>
@@ -5089,7 +5183,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:21">
       <c r="A71">
         <v>91</v>
       </c>
@@ -5124,7 +5218,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:21">
       <c r="A72">
         <v>92</v>
       </c>
@@ -5161,7 +5255,7 @@
       <c r="P72" s="2"/>
       <c r="R72" s="2"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:21">
       <c r="A73">
         <v>93</v>
       </c>
@@ -5195,7 +5289,7 @@
       </c>
       <c r="R73" s="2"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:21">
       <c r="A74">
         <v>94</v>
       </c>
@@ -5229,7 +5323,7 @@
       <c r="P74" s="2"/>
       <c r="R74" s="2"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:21">
       <c r="A75">
         <v>95</v>
       </c>
@@ -5263,7 +5357,7 @@
       <c r="P75" s="2"/>
       <c r="R75" s="2"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:21">
       <c r="A76">
         <v>96</v>
       </c>
@@ -5298,7 +5392,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:21">
       <c r="A77">
         <v>97</v>
       </c>
@@ -5332,7 +5426,7 @@
       <c r="P77" s="2"/>
       <c r="R77" s="2"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:21">
       <c r="A78">
         <v>98</v>
       </c>
@@ -5367,7 +5461,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:21">
       <c r="A79">
         <v>99</v>
       </c>
@@ -5401,7 +5495,7 @@
       <c r="P79" s="2"/>
       <c r="R79" s="2"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:21">
       <c r="A80">
         <v>100</v>
       </c>
@@ -5436,7 +5530,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:21">
       <c r="A81">
         <v>102</v>
       </c>
@@ -5473,7 +5567,7 @@
       <c r="P81" s="2"/>
       <c r="R81" s="2"/>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:21">
       <c r="A82">
         <v>103</v>
       </c>
@@ -5507,7 +5601,7 @@
       <c r="P82" s="2"/>
       <c r="R82" s="2"/>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:21">
       <c r="A83">
         <v>104</v>
       </c>
@@ -5542,7 +5636,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:21">
       <c r="A84">
         <v>105</v>
       </c>
@@ -5579,7 +5673,7 @@
       <c r="P84" s="2"/>
       <c r="R84" s="2"/>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:21">
       <c r="A85">
         <v>106</v>
       </c>
@@ -5614,7 +5708,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:21">
       <c r="A86">
         <v>107</v>
       </c>
@@ -5648,7 +5742,7 @@
       </c>
       <c r="R86" s="2"/>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:21">
       <c r="A87">
         <v>108</v>
       </c>
@@ -5683,7 +5777,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:21">
       <c r="A88">
         <v>109</v>
       </c>
@@ -5718,7 +5812,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:21">
       <c r="A89">
         <v>110</v>
       </c>
@@ -5752,7 +5846,7 @@
       <c r="P89" s="2"/>
       <c r="R89" s="2"/>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:21">
       <c r="A90">
         <v>111</v>
       </c>
@@ -5787,7 +5881,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:21">
       <c r="A91">
         <v>112</v>
       </c>
@@ -5821,7 +5915,7 @@
       </c>
       <c r="R91" s="2"/>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:21">
       <c r="A92">
         <v>113</v>
       </c>
@@ -5856,7 +5950,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:21">
       <c r="A93">
         <v>114</v>
       </c>
@@ -5891,7 +5985,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:21">
       <c r="A94">
         <v>115</v>
       </c>
@@ -5925,7 +6019,7 @@
       <c r="P94" s="2"/>
       <c r="R94" s="2"/>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:21">
       <c r="A95">
         <v>116</v>
       </c>
@@ -5959,7 +6053,7 @@
       <c r="P95" s="2"/>
       <c r="R95" s="2"/>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:21">
       <c r="A96">
         <v>117</v>
       </c>
@@ -5993,7 +6087,7 @@
       </c>
       <c r="R96" s="2"/>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:23">
       <c r="A97">
         <v>118</v>
       </c>
@@ -6027,7 +6121,7 @@
       <c r="P97" s="2"/>
       <c r="R97" s="2"/>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:23">
       <c r="A98">
         <v>119</v>
       </c>
@@ -6061,7 +6155,7 @@
       <c r="P98" s="2"/>
       <c r="R98" s="2"/>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:23">
       <c r="A99">
         <v>120</v>
       </c>
@@ -6095,7 +6189,7 @@
       <c r="P99" s="2"/>
       <c r="R99" s="2"/>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:23">
       <c r="A100">
         <v>121</v>
       </c>
@@ -6130,7 +6224,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:23">
       <c r="A101">
         <v>122</v>
       </c>
@@ -6164,7 +6258,7 @@
       <c r="P101" s="2"/>
       <c r="R101" s="2"/>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:23">
       <c r="A102">
         <v>123</v>
       </c>
@@ -6199,7 +6293,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:23">
       <c r="A103">
         <v>124</v>
       </c>
@@ -6234,7 +6328,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:23">
       <c r="A104">
         <v>125</v>
       </c>
@@ -6269,7 +6363,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:23">
       <c r="A105">
         <v>126</v>
       </c>
@@ -6304,7 +6398,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:23">
       <c r="A106">
         <v>127</v>
       </c>
@@ -6338,7 +6432,7 @@
       <c r="P106" s="2"/>
       <c r="R106" s="2"/>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:23">
       <c r="A107">
         <v>128</v>
       </c>
@@ -6375,7 +6469,7 @@
       <c r="P107" s="2"/>
       <c r="R107" s="2"/>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:23">
       <c r="A108">
         <v>129</v>
       </c>
@@ -6410,7 +6504,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:23">
       <c r="A109">
         <v>130</v>
       </c>
@@ -6447,7 +6541,7 @@
       <c r="P109" s="2"/>
       <c r="R109" s="2"/>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:23">
       <c r="A110">
         <v>131</v>
       </c>
@@ -6481,7 +6575,7 @@
       <c r="P110" s="2"/>
       <c r="R110" s="2"/>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:23">
       <c r="A111">
         <v>132</v>
       </c>
@@ -6516,7 +6610,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:23">
       <c r="A112">
         <v>133</v>
       </c>
@@ -6551,7 +6645,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:21">
       <c r="A113">
         <v>134</v>
       </c>
@@ -6586,7 +6680,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:21">
       <c r="A114">
         <v>135</v>
       </c>
@@ -6621,7 +6715,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:21">
       <c r="A115">
         <v>136</v>
       </c>
@@ -6656,7 +6750,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:21">
       <c r="A116">
         <v>137</v>
       </c>
@@ -6691,7 +6785,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:21">
       <c r="A117">
         <v>138</v>
       </c>
@@ -6726,7 +6820,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:21">
       <c r="A118">
         <v>139</v>
       </c>
@@ -6761,7 +6855,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:21">
       <c r="A119">
         <v>140</v>
       </c>
@@ -6796,7 +6890,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:21">
       <c r="A120">
         <v>141</v>
       </c>
@@ -6830,7 +6924,7 @@
       <c r="P120" s="2"/>
       <c r="R120" s="2"/>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:21">
       <c r="A121">
         <v>142</v>
       </c>
@@ -6865,7 +6959,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:21">
       <c r="A122">
         <v>143</v>
       </c>
@@ -6899,7 +6993,7 @@
       <c r="P122" s="2"/>
       <c r="R122" s="2"/>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:21">
       <c r="A123">
         <v>144</v>
       </c>
@@ -6934,7 +7028,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:21">
       <c r="A124">
         <v>145</v>
       </c>
@@ -6968,7 +7062,7 @@
       <c r="P124" s="2"/>
       <c r="R124" s="2"/>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:21">
       <c r="A125">
         <v>146</v>
       </c>
@@ -7003,7 +7097,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:21">
       <c r="A126">
         <v>147</v>
       </c>
@@ -7037,7 +7131,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:21">
       <c r="A127">
         <v>148</v>
       </c>
@@ -7075,7 +7169,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:21">
       <c r="A128">
         <v>149</v>
       </c>
@@ -7110,7 +7204,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:21">
       <c r="A129">
         <v>150</v>
       </c>
@@ -7145,7 +7239,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:21">
       <c r="A130">
         <v>151</v>
       </c>
@@ -7180,7 +7274,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:21">
       <c r="A131">
         <v>152</v>
       </c>
@@ -7215,7 +7309,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:21">
       <c r="A132">
         <v>153</v>
       </c>
@@ -7249,7 +7343,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:21">
       <c r="A133">
         <v>154</v>
       </c>
@@ -7284,7 +7378,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:21">
       <c r="A134">
         <v>155</v>
       </c>
@@ -7319,7 +7413,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:21">
       <c r="A135">
         <v>156</v>
       </c>
@@ -7357,7 +7451,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:21">
       <c r="A136">
         <v>157</v>
       </c>
@@ -7391,7 +7485,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:21">
       <c r="A137">
         <v>158</v>
       </c>
@@ -7426,7 +7520,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:21">
       <c r="A138">
         <v>159</v>
       </c>
@@ -7464,7 +7558,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:21">
       <c r="A139">
         <v>160</v>
       </c>
@@ -7501,7 +7595,7 @@
       <c r="P139" s="2"/>
       <c r="R139" s="2"/>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:21">
       <c r="A140">
         <v>161</v>
       </c>
@@ -7535,7 +7629,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:21">
       <c r="A141">
         <v>162</v>
       </c>
@@ -7572,7 +7666,7 @@
       <c r="P141" s="2"/>
       <c r="R141" s="2"/>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:21">
       <c r="A142">
         <v>163</v>
       </c>
@@ -7609,7 +7703,7 @@
       <c r="P142" s="2"/>
       <c r="R142" s="2"/>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:21">
       <c r="A143">
         <v>164</v>
       </c>
@@ -7643,7 +7737,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:21">
       <c r="A144">
         <v>165</v>
       </c>
@@ -7681,7 +7775,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:18">
       <c r="A145">
         <v>166</v>
       </c>
@@ -7718,7 +7812,7 @@
       <c r="P145" s="2"/>
       <c r="R145" s="2"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:18">
       <c r="A146">
         <v>167</v>
       </c>
@@ -7755,7 +7849,7 @@
       <c r="P146" s="2"/>
       <c r="R146" s="2"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:18">
       <c r="A147">
         <v>168</v>
       </c>
@@ -7792,7 +7886,7 @@
       <c r="P147" s="2"/>
       <c r="R147" s="2"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:18">
       <c r="A148">
         <v>169</v>
       </c>
@@ -7829,7 +7923,7 @@
       <c r="P148" s="2"/>
       <c r="R148" s="2"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:18">
       <c r="A149">
         <v>170</v>
       </c>
@@ -7866,7 +7960,7 @@
       <c r="P149" s="2"/>
       <c r="R149" s="2"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:18">
       <c r="A150">
         <v>171</v>
       </c>
@@ -7903,7 +7997,7 @@
       <c r="P150" s="2"/>
       <c r="R150" s="2"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:18">
       <c r="A151">
         <v>172</v>
       </c>
@@ -7940,7 +8034,7 @@
       <c r="P151" s="2"/>
       <c r="R151" s="2"/>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:18">
       <c r="A152">
         <v>173</v>
       </c>
@@ -7977,7 +8071,7 @@
       <c r="P152" s="2"/>
       <c r="R152" s="2"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:18">
       <c r="A153">
         <v>174</v>
       </c>
@@ -8014,7 +8108,7 @@
       <c r="P153" s="2"/>
       <c r="R153" s="2"/>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:18">
       <c r="A154">
         <v>175</v>
       </c>
@@ -8051,7 +8145,7 @@
       <c r="P154" s="2"/>
       <c r="R154" s="2"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:18">
       <c r="A155">
         <v>176</v>
       </c>
@@ -8088,7 +8182,7 @@
       <c r="P155" s="2"/>
       <c r="R155" s="2"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:18">
       <c r="A156">
         <v>177</v>
       </c>
@@ -8125,7 +8219,7 @@
       <c r="P156" s="2"/>
       <c r="R156" s="2"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:18">
       <c r="A157">
         <v>178</v>
       </c>
@@ -8162,7 +8256,7 @@
       <c r="P157" s="2"/>
       <c r="R157" s="2"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:18">
       <c r="A158">
         <v>179</v>
       </c>
@@ -8199,7 +8293,7 @@
       <c r="P158" s="2"/>
       <c r="R158" s="2"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:18">
       <c r="A159">
         <v>180</v>
       </c>
@@ -8236,7 +8330,7 @@
       <c r="P159" s="2"/>
       <c r="R159" s="2"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:18">
       <c r="A160">
         <v>181</v>
       </c>
@@ -8273,7 +8367,7 @@
       <c r="P160" s="2"/>
       <c r="R160" s="2"/>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:18">
       <c r="A161">
         <v>182</v>
       </c>
@@ -8310,7 +8404,7 @@
       <c r="P161" s="2"/>
       <c r="R161" s="2"/>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:18">
       <c r="A162">
         <v>183</v>
       </c>
@@ -8347,7 +8441,7 @@
       <c r="P162" s="2"/>
       <c r="R162" s="2"/>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:18">
       <c r="A163">
         <v>184</v>
       </c>
@@ -8382,7 +8476,7 @@
       <c r="P163" s="2"/>
       <c r="R163" s="2"/>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:18">
       <c r="A164">
         <v>185</v>
       </c>
@@ -8419,7 +8513,7 @@
       <c r="P164" s="2"/>
       <c r="R164" s="2"/>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:18">
       <c r="A165">
         <v>186</v>
       </c>
@@ -8456,7 +8550,7 @@
       <c r="P165" s="2"/>
       <c r="R165" s="2"/>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:18">
       <c r="A166">
         <v>187</v>
       </c>
@@ -8493,7 +8587,7 @@
       <c r="P166" s="2"/>
       <c r="R166" s="2"/>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:18">
       <c r="A167">
         <v>188</v>
       </c>
@@ -8530,7 +8624,7 @@
       <c r="P167" s="2"/>
       <c r="R167" s="2"/>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:18">
       <c r="A168">
         <v>189</v>
       </c>
@@ -8567,7 +8661,7 @@
       <c r="P168" s="2"/>
       <c r="R168" s="2"/>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:18">
       <c r="A169">
         <v>190</v>
       </c>
@@ -8604,7 +8698,7 @@
       <c r="P169" s="2"/>
       <c r="R169" s="2"/>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:18">
       <c r="A170">
         <v>191</v>
       </c>
@@ -8641,7 +8735,7 @@
       <c r="P170" s="2"/>
       <c r="R170" s="2"/>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:18">
       <c r="A171">
         <v>192</v>
       </c>
@@ -8678,7 +8772,7 @@
       <c r="P171" s="2"/>
       <c r="R171" s="2"/>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:18">
       <c r="A172">
         <v>193</v>
       </c>
@@ -8715,7 +8809,7 @@
       <c r="P172" s="2"/>
       <c r="R172" s="2"/>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:18">
       <c r="A173">
         <v>194</v>
       </c>
@@ -8752,7 +8846,7 @@
       <c r="P173" s="2"/>
       <c r="R173" s="2"/>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:18">
       <c r="A174">
         <v>195</v>
       </c>
@@ -8789,7 +8883,7 @@
       <c r="P174" s="2"/>
       <c r="R174" s="2"/>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:18">
       <c r="A175">
         <v>196</v>
       </c>
@@ -8826,7 +8920,7 @@
       <c r="P175" s="2"/>
       <c r="R175" s="2"/>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:18">
       <c r="A176">
         <v>197</v>
       </c>
@@ -8863,7 +8957,7 @@
       <c r="P176" s="2"/>
       <c r="R176" s="2"/>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:18">
       <c r="A177">
         <v>198</v>
       </c>
@@ -8900,7 +8994,7 @@
       <c r="P177" s="2"/>
       <c r="R177" s="2"/>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:18">
       <c r="A178">
         <v>199</v>
       </c>
@@ -8937,7 +9031,7 @@
       <c r="P178" s="2"/>
       <c r="R178" s="2"/>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:18">
       <c r="A179">
         <v>200</v>
       </c>
@@ -8974,7 +9068,7 @@
       <c r="P179" s="2"/>
       <c r="R179" s="2"/>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:18">
       <c r="A180">
         <v>201</v>
       </c>
@@ -9011,7 +9105,7 @@
       <c r="P180" s="2"/>
       <c r="R180" s="2"/>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:18">
       <c r="A181">
         <v>202</v>
       </c>
@@ -9048,7 +9142,7 @@
       <c r="P181" s="2"/>
       <c r="R181" s="2"/>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:18">
       <c r="A182">
         <v>203</v>
       </c>
@@ -9085,7 +9179,7 @@
       <c r="P182" s="2"/>
       <c r="R182" s="2"/>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:18">
       <c r="A183">
         <v>204</v>
       </c>
@@ -9122,7 +9216,7 @@
       <c r="P183" s="2"/>
       <c r="R183" s="2"/>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:18">
       <c r="A184">
         <v>205</v>
       </c>
@@ -9159,7 +9253,7 @@
       <c r="P184" s="2"/>
       <c r="R184" s="2"/>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:18">
       <c r="A185">
         <v>206</v>
       </c>
@@ -9196,7 +9290,7 @@
       <c r="P185" s="2"/>
       <c r="R185" s="2"/>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:18">
       <c r="A186">
         <v>207</v>
       </c>
@@ -9230,7 +9324,7 @@
       <c r="P186" s="2"/>
       <c r="R186" s="2"/>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:18">
       <c r="A187">
         <v>208</v>
       </c>
@@ -9267,7 +9361,7 @@
       <c r="P187" s="2"/>
       <c r="R187" s="2"/>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:18">
       <c r="A188">
         <v>209</v>
       </c>
@@ -9302,7 +9396,7 @@
       <c r="P188" s="2"/>
       <c r="R188" s="2"/>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:18">
       <c r="A189">
         <v>210</v>
       </c>
@@ -9339,7 +9433,7 @@
       <c r="P189" s="2"/>
       <c r="R189" s="2"/>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:18">
       <c r="A190">
         <v>211</v>
       </c>
@@ -9376,7 +9470,7 @@
       <c r="P190" s="2"/>
       <c r="R190" s="2"/>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:18">
       <c r="A191">
         <v>212</v>
       </c>
@@ -9413,7 +9507,7 @@
       <c r="P191" s="2"/>
       <c r="R191" s="2"/>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:18">
       <c r="A192">
         <v>213</v>
       </c>
@@ -9447,7 +9541,7 @@
       <c r="P192" s="2"/>
       <c r="R192" s="2"/>
     </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:22">
       <c r="A193">
         <v>214</v>
       </c>
@@ -9482,7 +9576,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:22">
       <c r="A194">
         <v>215</v>
       </c>
@@ -9519,7 +9613,7 @@
       <c r="P194" s="2"/>
       <c r="R194" s="2"/>
     </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:22">
       <c r="A195">
         <v>216</v>
       </c>
@@ -9556,7 +9650,7 @@
       <c r="P195" s="2"/>
       <c r="R195" s="2"/>
     </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:22">
       <c r="A196">
         <v>217</v>
       </c>
@@ -9593,7 +9687,7 @@
       <c r="P196" s="2"/>
       <c r="R196" s="2"/>
     </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:22">
       <c r="A197">
         <v>218</v>
       </c>
@@ -9630,7 +9724,7 @@
       <c r="P197" s="2"/>
       <c r="R197" s="2"/>
     </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:22">
       <c r="A198">
         <v>219</v>
       </c>
@@ -9664,7 +9758,7 @@
       <c r="P198" s="2"/>
       <c r="R198" s="2"/>
     </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:22">
       <c r="A199">
         <v>220</v>
       </c>
@@ -9699,7 +9793,7 @@
       <c r="P199" s="2"/>
       <c r="R199" s="2"/>
     </row>
-    <row r="200" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:22">
       <c r="A200">
         <v>221</v>
       </c>
@@ -9737,7 +9831,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:22">
       <c r="A201">
         <v>222</v>
       </c>
@@ -9774,7 +9868,7 @@
       <c r="P201" s="2"/>
       <c r="R201" s="2"/>
     </row>
-    <row r="202" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:22">
       <c r="A202">
         <v>223</v>
       </c>
@@ -9808,7 +9902,7 @@
       <c r="P202" s="2"/>
       <c r="R202" s="2"/>
     </row>
-    <row r="203" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:22">
       <c r="A203">
         <v>224</v>
       </c>
@@ -9845,7 +9939,7 @@
       <c r="P203" s="2"/>
       <c r="R203" s="2"/>
     </row>
-    <row r="204" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:22">
       <c r="A204">
         <v>225</v>
       </c>
@@ -9882,7 +9976,7 @@
       <c r="P204" s="2"/>
       <c r="R204" s="2"/>
     </row>
-    <row r="205" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:22">
       <c r="A205">
         <v>226</v>
       </c>
@@ -9916,7 +10010,7 @@
       <c r="P205" s="2"/>
       <c r="R205" s="2"/>
     </row>
-    <row r="206" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:22">
       <c r="A206">
         <v>227</v>
       </c>
@@ -9950,7 +10044,7 @@
       <c r="P206" s="2"/>
       <c r="R206" s="2"/>
     </row>
-    <row r="207" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:22">
       <c r="A207">
         <v>228</v>
       </c>
@@ -9984,7 +10078,7 @@
       <c r="P207" s="2"/>
       <c r="R207" s="2"/>
     </row>
-    <row r="208" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:22">
       <c r="A208">
         <v>229</v>
       </c>
@@ -10022,7 +10116,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:21">
       <c r="A209">
         <v>230</v>
       </c>
@@ -10057,7 +10151,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:21">
       <c r="A210">
         <v>231</v>
       </c>
@@ -10095,7 +10189,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:21">
       <c r="A211">
         <v>232</v>
       </c>
@@ -10133,7 +10227,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:21">
       <c r="A212">
         <v>233</v>
       </c>
@@ -10171,7 +10265,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:21">
       <c r="A213">
         <v>234</v>
       </c>
@@ -10206,7 +10300,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:21">
       <c r="A214">
         <v>235</v>
       </c>
@@ -10244,7 +10338,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:21">
       <c r="A215">
         <v>236</v>
       </c>
@@ -10278,7 +10372,7 @@
       <c r="P215" s="2"/>
       <c r="R215" s="2"/>
     </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:21">
       <c r="A216">
         <v>237</v>
       </c>
@@ -10312,7 +10406,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:21">
       <c r="A217">
         <v>238</v>
       </c>
@@ -10346,7 +10440,7 @@
       <c r="P217" s="2"/>
       <c r="R217" s="2"/>
     </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:21">
       <c r="A218">
         <v>239</v>
       </c>
@@ -10380,7 +10474,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:21">
       <c r="A219">
         <v>240</v>
       </c>
@@ -10417,7 +10511,7 @@
       <c r="P219" s="2"/>
       <c r="R219" s="2"/>
     </row>
-    <row r="220" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:21">
       <c r="A220">
         <v>241</v>
       </c>
@@ -10451,7 +10545,7 @@
       <c r="P220" s="2"/>
       <c r="R220" s="2"/>
     </row>
-    <row r="221" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:21">
       <c r="A221">
         <v>242</v>
       </c>
@@ -10485,7 +10579,7 @@
       <c r="P221" s="2"/>
       <c r="R221" s="2"/>
     </row>
-    <row r="222" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:21">
       <c r="A222">
         <v>243</v>
       </c>
@@ -10519,7 +10613,7 @@
       </c>
       <c r="R222" s="2"/>
     </row>
-    <row r="223" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:21">
       <c r="A223">
         <v>244</v>
       </c>
@@ -10553,7 +10647,7 @@
       <c r="P223" s="2"/>
       <c r="R223" s="2"/>
     </row>
-    <row r="224" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:21">
       <c r="A224">
         <v>245</v>
       </c>
@@ -10587,7 +10681,7 @@
       </c>
       <c r="R224" s="2"/>
     </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:23">
       <c r="A225">
         <v>246</v>
       </c>
@@ -10621,7 +10715,7 @@
       <c r="P225" s="2"/>
       <c r="R225" s="2"/>
     </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:23">
       <c r="A226">
         <v>247</v>
       </c>
@@ -10655,7 +10749,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:23">
       <c r="A227">
         <v>248</v>
       </c>
@@ -10689,7 +10783,7 @@
       <c r="P227" s="2"/>
       <c r="R227" s="2"/>
     </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:23">
       <c r="A228">
         <v>249</v>
       </c>
@@ -10723,7 +10817,7 @@
       <c r="P228" s="2"/>
       <c r="R228" s="2"/>
     </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:23">
       <c r="A229">
         <v>250</v>
       </c>
@@ -10757,7 +10851,7 @@
       <c r="P229" s="2"/>
       <c r="R229" s="2"/>
     </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:23">
       <c r="A230">
         <v>251</v>
       </c>
@@ -10791,7 +10885,7 @@
       <c r="P230" s="2"/>
       <c r="R230" s="2"/>
     </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:23">
       <c r="A231">
         <v>252</v>
       </c>
@@ -10828,7 +10922,7 @@
       <c r="P231" s="2"/>
       <c r="R231" s="2"/>
     </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:23">
       <c r="A232">
         <v>253</v>
       </c>
@@ -10862,7 +10956,7 @@
       <c r="P232" s="2"/>
       <c r="R232" s="2"/>
     </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:23">
       <c r="A233">
         <v>254</v>
       </c>
@@ -10900,7 +10994,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:23">
       <c r="A234">
         <v>255</v>
       </c>
@@ -10937,7 +11031,7 @@
       <c r="P234" s="2"/>
       <c r="R234" s="2"/>
     </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:23">
       <c r="A235">
         <v>256</v>
       </c>
@@ -10974,7 +11068,7 @@
       <c r="P235" s="2"/>
       <c r="R235" s="2"/>
     </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:23">
       <c r="A236">
         <v>257</v>
       </c>
@@ -11009,7 +11103,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:23">
       <c r="A237">
         <v>258</v>
       </c>
@@ -11044,7 +11138,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:23">
       <c r="A238">
         <v>259</v>
       </c>
@@ -11078,7 +11172,7 @@
       <c r="P238" s="2"/>
       <c r="R238" s="2"/>
     </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:23">
       <c r="A239">
         <v>260</v>
       </c>
@@ -11112,7 +11206,7 @@
       <c r="P239" s="2"/>
       <c r="R239" s="2"/>
     </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:23">
       <c r="A240">
         <v>261</v>
       </c>
@@ -11146,7 +11240,7 @@
       <c r="P240" s="2"/>
       <c r="R240" s="2"/>
     </row>
-    <row r="241" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:22">
       <c r="A241">
         <v>262</v>
       </c>
@@ -11180,7 +11274,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="242" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:22">
       <c r="A242">
         <v>263</v>
       </c>
@@ -11217,7 +11311,7 @@
       <c r="P242" s="2"/>
       <c r="R242" s="2"/>
     </row>
-    <row r="243" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:22">
       <c r="A243">
         <v>264</v>
       </c>
@@ -11251,7 +11345,7 @@
       </c>
       <c r="R243" s="2"/>
     </row>
-    <row r="244" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:22">
       <c r="A244">
         <v>265</v>
       </c>
@@ -11285,7 +11379,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="245" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:22">
       <c r="A245">
         <v>266</v>
       </c>
@@ -11320,7 +11414,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="246" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:22">
       <c r="A246">
         <v>267</v>
       </c>
@@ -11354,7 +11448,7 @@
       <c r="P246" s="2"/>
       <c r="R246" s="2"/>
     </row>
-    <row r="247" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:22">
       <c r="A247">
         <v>268</v>
       </c>
@@ -11388,7 +11482,7 @@
       <c r="P247" s="2"/>
       <c r="R247" s="2"/>
     </row>
-    <row r="248" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:22">
       <c r="A248">
         <v>269</v>
       </c>
@@ -11425,7 +11519,7 @@
       <c r="P248" s="2"/>
       <c r="R248" s="2"/>
     </row>
-    <row r="249" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:22">
       <c r="A249">
         <v>270</v>
       </c>
@@ -11459,7 +11553,7 @@
       </c>
       <c r="R249" s="2"/>
     </row>
-    <row r="250" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:22">
       <c r="A250">
         <v>271</v>
       </c>
@@ -11494,7 +11588,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="251" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:22">
       <c r="A251">
         <v>272</v>
       </c>
@@ -11528,7 +11622,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="252" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:22">
       <c r="A252">
         <v>273</v>
       </c>
@@ -11562,7 +11656,7 @@
       <c r="P252" s="2"/>
       <c r="R252" s="2"/>
     </row>
-    <row r="253" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:22">
       <c r="A253">
         <v>274</v>
       </c>
@@ -11596,7 +11690,7 @@
       <c r="P253" s="2"/>
       <c r="R253" s="2"/>
     </row>
-    <row r="254" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:22">
       <c r="A254">
         <v>275</v>
       </c>
@@ -11631,7 +11725,7 @@
       <c r="P254" s="2"/>
       <c r="R254" s="2"/>
     </row>
-    <row r="255" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:22">
       <c r="A255">
         <v>276</v>
       </c>
@@ -11668,7 +11762,7 @@
       <c r="P255" s="2"/>
       <c r="R255" s="2"/>
     </row>
-    <row r="256" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:22">
       <c r="A256">
         <v>277</v>
       </c>
@@ -11702,7 +11796,7 @@
       <c r="P256" s="2"/>
       <c r="R256" s="2"/>
     </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:23">
       <c r="A257">
         <v>278</v>
       </c>
@@ -11736,7 +11830,7 @@
       <c r="P257" s="2"/>
       <c r="R257" s="2"/>
     </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:23">
       <c r="A258">
         <v>279</v>
       </c>
@@ -11774,7 +11868,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:23">
       <c r="A259">
         <v>280</v>
       </c>
@@ -11808,7 +11902,7 @@
       <c r="P259" s="2"/>
       <c r="R259" s="2"/>
     </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:23">
       <c r="A260">
         <v>281</v>
       </c>
@@ -11845,7 +11939,7 @@
       <c r="P260" s="2"/>
       <c r="R260" s="2"/>
     </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:23">
       <c r="A261">
         <v>282</v>
       </c>
@@ -11879,7 +11973,7 @@
       <c r="P261" s="2"/>
       <c r="R261" s="2"/>
     </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:23">
       <c r="A262">
         <v>283</v>
       </c>
@@ -11916,7 +12010,7 @@
       <c r="P262" s="2"/>
       <c r="R262" s="2"/>
     </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:23">
       <c r="A263">
         <v>284</v>
       </c>
@@ -11950,7 +12044,7 @@
       <c r="P263" s="2"/>
       <c r="R263" s="2"/>
     </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:23">
       <c r="A264">
         <v>285</v>
       </c>
@@ -11987,7 +12081,7 @@
       <c r="P264" s="2"/>
       <c r="R264" s="2"/>
     </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:23">
       <c r="A265">
         <v>286</v>
       </c>
@@ -12021,7 +12115,7 @@
       <c r="P265" s="2"/>
       <c r="R265" s="2"/>
     </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:23">
       <c r="A266">
         <v>287</v>
       </c>
@@ -12055,7 +12149,7 @@
       <c r="P266" s="2"/>
       <c r="R266" s="2"/>
     </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:23">
       <c r="A267">
         <v>288</v>
       </c>
@@ -12089,7 +12183,7 @@
       </c>
       <c r="R267" s="2"/>
     </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:23">
       <c r="A268">
         <v>289</v>
       </c>
@@ -12127,7 +12221,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:23">
       <c r="A269">
         <v>290</v>
       </c>
@@ -12164,7 +12258,7 @@
       <c r="P269" s="2"/>
       <c r="R269" s="2"/>
     </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:23">
       <c r="A270">
         <v>291</v>
       </c>
@@ -12199,7 +12293,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:23">
       <c r="A271">
         <v>292</v>
       </c>
@@ -12233,7 +12327,7 @@
       </c>
       <c r="R271" s="2"/>
     </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:23">
       <c r="A272">
         <v>293</v>
       </c>
@@ -12268,7 +12362,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="273" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:23">
       <c r="A273">
         <v>294</v>
       </c>
@@ -12306,7 +12400,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="274" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:23">
       <c r="A274">
         <v>295</v>
       </c>
@@ -12341,7 +12435,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="275" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:23">
       <c r="A275">
         <v>296</v>
       </c>
@@ -12379,7 +12473,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="276" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:23">
       <c r="A276">
         <v>297</v>
       </c>
@@ -12413,7 +12507,7 @@
       <c r="P276" s="2"/>
       <c r="R276" s="2"/>
     </row>
-    <row r="277" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:23">
       <c r="A277">
         <v>298</v>
       </c>
@@ -12447,7 +12541,7 @@
       <c r="P277" s="2"/>
       <c r="R277" s="2"/>
     </row>
-    <row r="278" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:23">
       <c r="A278">
         <v>299</v>
       </c>
@@ -12481,7 +12575,7 @@
       </c>
       <c r="R278" s="2"/>
     </row>
-    <row r="279" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:23">
       <c r="A279">
         <v>300</v>
       </c>
@@ -12515,7 +12609,7 @@
       <c r="P279" s="2"/>
       <c r="R279" s="2"/>
     </row>
-    <row r="280" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:23">
       <c r="A280">
         <v>301</v>
       </c>
@@ -12549,7 +12643,7 @@
       <c r="P280" s="2"/>
       <c r="R280" s="2"/>
     </row>
-    <row r="281" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:23">
       <c r="A281">
         <v>302</v>
       </c>
@@ -12583,7 +12677,7 @@
       <c r="P281" s="2"/>
       <c r="R281" s="2"/>
     </row>
-    <row r="282" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:23">
       <c r="A282">
         <v>303</v>
       </c>
@@ -12620,7 +12714,7 @@
       <c r="P282" s="2"/>
       <c r="R282" s="2"/>
     </row>
-    <row r="283" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:23">
       <c r="A283">
         <v>304</v>
       </c>
@@ -12655,7 +12749,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="284" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:23">
       <c r="A284">
         <v>306</v>
       </c>
@@ -12692,7 +12786,7 @@
       <c r="P284" s="2"/>
       <c r="R284" s="2"/>
     </row>
-    <row r="285" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:23">
       <c r="A285">
         <v>307</v>
       </c>
@@ -12726,7 +12820,7 @@
       <c r="P285" s="2"/>
       <c r="R285" s="2"/>
     </row>
-    <row r="286" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:23">
       <c r="A286">
         <v>308</v>
       </c>
@@ -12760,7 +12854,7 @@
       <c r="P286" s="2"/>
       <c r="R286" s="2"/>
     </row>
-    <row r="287" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:23">
       <c r="A287">
         <v>309</v>
       </c>
@@ -12794,7 +12888,7 @@
       <c r="P287" s="2"/>
       <c r="R287" s="2"/>
     </row>
-    <row r="288" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:23">
       <c r="A288">
         <v>310</v>
       </c>
@@ -12828,7 +12922,7 @@
       <c r="P288" s="2"/>
       <c r="R288" s="2"/>
     </row>
-    <row r="289" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:23">
       <c r="A289">
         <v>311</v>
       </c>
@@ -12862,7 +12956,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="290" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:23">
       <c r="A290">
         <v>312</v>
       </c>
@@ -12896,7 +12990,7 @@
       <c r="P290" s="2"/>
       <c r="R290" s="2"/>
     </row>
-    <row r="291" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:23">
       <c r="A291">
         <v>313</v>
       </c>
@@ -12933,7 +13027,7 @@
       <c r="P291" s="2"/>
       <c r="R291" s="2"/>
     </row>
-    <row r="292" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:23">
       <c r="A292">
         <v>314</v>
       </c>
@@ -12968,7 +13062,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="293" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:23">
       <c r="A293">
         <v>315</v>
       </c>
@@ -13003,7 +13097,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="294" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:23">
       <c r="A294">
         <v>316</v>
       </c>
@@ -13037,7 +13131,7 @@
       </c>
       <c r="R294" s="2"/>
     </row>
-    <row r="295" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:23">
       <c r="A295">
         <v>317</v>
       </c>
@@ -13075,7 +13169,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="296" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:23">
       <c r="A296">
         <v>318</v>
       </c>
@@ -13109,7 +13203,7 @@
       <c r="P296" s="2"/>
       <c r="R296" s="2"/>
     </row>
-    <row r="297" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:23">
       <c r="A297">
         <v>319</v>
       </c>
@@ -13143,7 +13237,7 @@
       <c r="P297" s="2"/>
       <c r="R297" s="2"/>
     </row>
-    <row r="298" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:23">
       <c r="A298">
         <v>320</v>
       </c>
@@ -13178,7 +13272,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="299" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:23">
       <c r="A299">
         <v>321</v>
       </c>
@@ -13215,7 +13309,7 @@
       <c r="P299" s="2"/>
       <c r="R299" s="2"/>
     </row>
-    <row r="300" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:23">
       <c r="A300">
         <v>322</v>
       </c>
@@ -13253,7 +13347,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="301" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:23">
       <c r="A301">
         <v>323</v>
       </c>
@@ -13287,7 +13381,7 @@
       <c r="P301" s="2"/>
       <c r="R301" s="2"/>
     </row>
-    <row r="302" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:23">
       <c r="A302">
         <v>324</v>
       </c>
@@ -13321,7 +13415,7 @@
       <c r="P302" s="2"/>
       <c r="R302" s="2"/>
     </row>
-    <row r="303" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:23">
       <c r="A303">
         <v>325</v>
       </c>
@@ -13355,7 +13449,7 @@
       <c r="P303" s="2"/>
       <c r="R303" s="2"/>
     </row>
-    <row r="304" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:23">
       <c r="A304">
         <v>326</v>
       </c>
@@ -13389,7 +13483,7 @@
       </c>
       <c r="R304" s="2"/>
     </row>
-    <row r="305" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:23">
       <c r="A305">
         <v>327</v>
       </c>
@@ -13423,7 +13517,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="306" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:23">
       <c r="A306">
         <v>328</v>
       </c>
@@ -13457,7 +13551,7 @@
       <c r="P306" s="2"/>
       <c r="R306" s="2"/>
     </row>
-    <row r="307" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:23">
       <c r="A307">
         <v>329</v>
       </c>
@@ -13491,7 +13585,7 @@
       <c r="P307" s="2"/>
       <c r="R307" s="2"/>
     </row>
-    <row r="308" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:23">
       <c r="A308">
         <v>330</v>
       </c>
@@ -13525,7 +13619,7 @@
       <c r="P308" s="2"/>
       <c r="R308" s="2"/>
     </row>
-    <row r="309" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:23">
       <c r="A309">
         <v>331</v>
       </c>
@@ -13562,7 +13656,7 @@
       <c r="P309" s="2"/>
       <c r="R309" s="2"/>
     </row>
-    <row r="310" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:23">
       <c r="A310">
         <v>332</v>
       </c>
@@ -13596,7 +13690,7 @@
       <c r="P310" s="2"/>
       <c r="R310" s="2"/>
     </row>
-    <row r="311" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:23">
       <c r="A311">
         <v>333</v>
       </c>
@@ -13630,7 +13724,7 @@
       </c>
       <c r="R311" s="2"/>
     </row>
-    <row r="312" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:23">
       <c r="A312">
         <v>334</v>
       </c>
@@ -13664,7 +13758,7 @@
       <c r="P312" s="2"/>
       <c r="R312" s="2"/>
     </row>
-    <row r="313" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:23">
       <c r="A313">
         <v>335</v>
       </c>
@@ -13698,7 +13792,7 @@
       <c r="P313" s="2"/>
       <c r="R313" s="2"/>
     </row>
-    <row r="314" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:23">
       <c r="A314">
         <v>336</v>
       </c>
@@ -13732,7 +13826,7 @@
       <c r="P314" s="2"/>
       <c r="R314" s="2"/>
     </row>
-    <row r="315" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:23">
       <c r="A315">
         <v>337</v>
       </c>
@@ -13767,7 +13861,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="316" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:23">
       <c r="A316">
         <v>338</v>
       </c>
@@ -13802,7 +13896,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="317" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:23">
       <c r="A317">
         <v>339</v>
       </c>
@@ -13836,7 +13930,7 @@
       <c r="P317" s="2"/>
       <c r="R317" s="2"/>
     </row>
-    <row r="318" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:23">
       <c r="A318">
         <v>340</v>
       </c>
@@ -13870,7 +13964,7 @@
       <c r="P318" s="2"/>
       <c r="R318" s="2"/>
     </row>
-    <row r="319" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:23">
       <c r="A319">
         <v>341</v>
       </c>
@@ -13907,7 +14001,7 @@
       <c r="P319" s="2"/>
       <c r="R319" s="2"/>
     </row>
-    <row r="320" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:23">
       <c r="A320">
         <v>342</v>
       </c>
@@ -13942,7 +14036,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="321" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:23">
       <c r="A321">
         <v>343</v>
       </c>
@@ -13980,7 +14074,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="322" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:23">
       <c r="A322">
         <v>344</v>
       </c>
@@ -14014,7 +14108,7 @@
       <c r="P322" s="2"/>
       <c r="R322" s="2"/>
     </row>
-    <row r="323" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:23">
       <c r="A323">
         <v>345</v>
       </c>
@@ -14048,7 +14142,7 @@
       </c>
       <c r="R323" s="2"/>
     </row>
-    <row r="324" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:23">
       <c r="A324">
         <v>354</v>
       </c>
@@ -14083,7 +14177,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="325" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:23">
       <c r="A325">
         <v>355</v>
       </c>
@@ -14121,7 +14215,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="326" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:23">
       <c r="A326">
         <v>356</v>
       </c>
@@ -14155,7 +14249,7 @@
       <c r="P326" s="2"/>
       <c r="R326" s="2"/>
     </row>
-    <row r="327" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:23">
       <c r="A327">
         <v>357</v>
       </c>
@@ -14189,7 +14283,7 @@
       <c r="P327" s="2"/>
       <c r="R327" s="2"/>
     </row>
-    <row r="328" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:23">
       <c r="A328">
         <v>358</v>
       </c>
@@ -14224,7 +14318,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="329" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:23">
       <c r="A329">
         <v>359</v>
       </c>
@@ -14259,7 +14353,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="330" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:23">
       <c r="A330">
         <v>360</v>
       </c>
@@ -14293,7 +14387,7 @@
       <c r="P330" s="2"/>
       <c r="R330" s="2"/>
     </row>
-    <row r="331" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:23" ht="15" customHeight="1">
       <c r="A331">
         <v>361</v>
       </c>
@@ -14327,7 +14421,7 @@
       <c r="P331" s="2"/>
       <c r="R331" s="2"/>
     </row>
-    <row r="332" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:23" ht="15" customHeight="1">
       <c r="A332">
         <v>362</v>
       </c>
@@ -14361,7 +14455,7 @@
       <c r="P332" s="2"/>
       <c r="R332" s="2"/>
     </row>
-    <row r="333" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:23" ht="15" customHeight="1">
       <c r="A333">
         <v>363</v>
       </c>
@@ -14395,7 +14489,7 @@
       </c>
       <c r="R333" s="2"/>
     </row>
-    <row r="334" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:23" ht="15" customHeight="1">
       <c r="A334">
         <v>364</v>
       </c>
@@ -14429,7 +14523,7 @@
       <c r="P334" s="2"/>
       <c r="R334" s="2"/>
     </row>
-    <row r="335" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:23" ht="15" customHeight="1">
       <c r="A335">
         <v>365</v>
       </c>
@@ -14464,7 +14558,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="336" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:23" ht="15" customHeight="1">
       <c r="A336">
         <v>366</v>
       </c>
@@ -14499,7 +14593,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="337" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:22" ht="15" customHeight="1">
       <c r="A337">
         <v>367</v>
       </c>
@@ -14534,7 +14628,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="338" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:22" ht="15" customHeight="1">
       <c r="A338">
         <v>368</v>
       </c>
@@ -14568,7 +14662,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="339" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:22" ht="15" customHeight="1">
       <c r="A339">
         <v>369</v>
       </c>
@@ -14602,7 +14696,7 @@
       <c r="P339" s="2"/>
       <c r="R339" s="2"/>
     </row>
-    <row r="340" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:22" ht="15" customHeight="1">
       <c r="A340">
         <v>370</v>
       </c>
@@ -14636,7 +14730,7 @@
       <c r="P340" s="2"/>
       <c r="R340" s="2"/>
     </row>
-    <row r="341" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:22" ht="15" customHeight="1">
       <c r="A341">
         <v>371</v>
       </c>
@@ -14670,7 +14764,7 @@
       </c>
       <c r="R341" s="2"/>
     </row>
-    <row r="342" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:22" ht="15" customHeight="1">
       <c r="A342">
         <v>372</v>
       </c>
@@ -14704,7 +14798,7 @@
       <c r="P342" s="2"/>
       <c r="R342" s="2"/>
     </row>
-    <row r="343" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:22" ht="15" customHeight="1">
       <c r="A343">
         <v>373</v>
       </c>
@@ -14738,7 +14832,7 @@
       <c r="P343" s="2"/>
       <c r="R343" s="2"/>
     </row>
-    <row r="344" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:22" ht="15" customHeight="1">
       <c r="A344">
         <v>374</v>
       </c>
@@ -14772,7 +14866,7 @@
       <c r="P344" s="2"/>
       <c r="R344" s="2"/>
     </row>
-    <row r="345" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:22" ht="15" customHeight="1">
       <c r="A345">
         <v>375</v>
       </c>
@@ -14806,7 +14900,7 @@
       </c>
       <c r="R345" s="2"/>
     </row>
-    <row r="346" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:22" ht="15" customHeight="1">
       <c r="A346">
         <v>376</v>
       </c>
@@ -14841,7 +14935,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="347" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:22" ht="15" customHeight="1">
       <c r="A347">
         <v>377</v>
       </c>
@@ -14875,7 +14969,7 @@
       <c r="P347" s="2"/>
       <c r="R347" s="2"/>
     </row>
-    <row r="348" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:22" ht="15" customHeight="1">
       <c r="A348">
         <v>378</v>
       </c>
@@ -14909,7 +15003,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="349" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:22" ht="15" customHeight="1">
       <c r="A349">
         <v>379</v>
       </c>
@@ -14943,7 +15037,7 @@
       <c r="P349" s="2"/>
       <c r="R349" s="2"/>
     </row>
-    <row r="350" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:22" ht="15" customHeight="1">
       <c r="A350">
         <v>380</v>
       </c>
@@ -14977,7 +15071,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="351" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:22" ht="15" customHeight="1">
       <c r="A351">
         <v>381</v>
       </c>
@@ -15011,7 +15105,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="352" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:22" ht="15" customHeight="1">
       <c r="A352">
         <v>382</v>
       </c>
@@ -15045,7 +15139,7 @@
       <c r="P352" s="2"/>
       <c r="R352" s="2"/>
     </row>
-    <row r="353" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:23" ht="15" customHeight="1">
       <c r="A353">
         <v>383</v>
       </c>
@@ -15080,7 +15174,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="354" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:23" ht="15" customHeight="1">
       <c r="A354">
         <v>384</v>
       </c>
@@ -15114,7 +15208,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="355" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:23" ht="15" customHeight="1">
       <c r="A355">
         <v>385</v>
       </c>
@@ -15149,7 +15243,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="356" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:23" ht="15" customHeight="1">
       <c r="A356">
         <v>386</v>
       </c>
@@ -15184,7 +15278,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="357" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:23" ht="15" customHeight="1">
       <c r="A357">
         <v>387</v>
       </c>
@@ -15218,7 +15312,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="358" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:23" ht="15" customHeight="1">
       <c r="A358">
         <v>388</v>
       </c>
@@ -15253,7 +15347,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="359" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:23" ht="15" customHeight="1">
       <c r="A359">
         <v>389</v>
       </c>
@@ -15287,7 +15381,7 @@
       <c r="P359" s="2"/>
       <c r="R359" s="2"/>
     </row>
-    <row r="360" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:23" ht="15" customHeight="1">
       <c r="A360">
         <v>390</v>
       </c>
@@ -15321,7 +15415,7 @@
       <c r="P360" s="2"/>
       <c r="R360" s="2"/>
     </row>
-    <row r="361" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:23" ht="15" customHeight="1">
       <c r="A361">
         <v>391</v>
       </c>
@@ -15355,7 +15449,7 @@
       <c r="P361" s="2"/>
       <c r="R361" s="2"/>
     </row>
-    <row r="362" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:23" ht="15" customHeight="1">
       <c r="A362">
         <v>392</v>
       </c>
@@ -15390,7 +15484,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="363" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:23" ht="15" customHeight="1">
       <c r="A363">
         <v>393</v>
       </c>
@@ -15425,7 +15519,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="364" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:23" ht="15" customHeight="1">
       <c r="A364">
         <v>394</v>
       </c>
@@ -15459,7 +15553,7 @@
       <c r="P364" s="2"/>
       <c r="R364" s="2"/>
     </row>
-    <row r="365" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:23" ht="15" customHeight="1">
       <c r="A365">
         <v>395</v>
       </c>
@@ -15494,7 +15588,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="366" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:23" ht="15" customHeight="1">
       <c r="A366">
         <v>396</v>
       </c>
@@ -15528,7 +15622,7 @@
       </c>
       <c r="R366" s="2"/>
     </row>
-    <row r="367" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:23" ht="15" customHeight="1">
       <c r="A367">
         <v>397</v>
       </c>
@@ -15562,7 +15656,7 @@
       <c r="P367" s="2"/>
       <c r="R367" s="2"/>
     </row>
-    <row r="368" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:23" ht="15" customHeight="1">
       <c r="A368">
         <v>398</v>
       </c>
@@ -15596,7 +15690,7 @@
       </c>
       <c r="R368" s="2"/>
     </row>
-    <row r="369" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:23" ht="15" customHeight="1">
       <c r="A369">
         <v>399</v>
       </c>
@@ -15631,7 +15725,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="370" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:23" ht="15" customHeight="1">
       <c r="A370">
         <v>400</v>
       </c>
@@ -15666,7 +15760,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="371" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:23" ht="15" customHeight="1">
       <c r="A371">
         <v>401</v>
       </c>
@@ -15700,7 +15794,7 @@
       <c r="P371" s="2"/>
       <c r="R371" s="2"/>
     </row>
-    <row r="372" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:23" ht="15" customHeight="1">
       <c r="A372">
         <v>402</v>
       </c>
@@ -15734,7 +15828,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="373" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:23" ht="15" customHeight="1">
       <c r="A373">
         <v>403</v>
       </c>
@@ -15768,7 +15862,7 @@
       <c r="P373" s="2"/>
       <c r="R373" s="2"/>
     </row>
-    <row r="374" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:23" ht="15" customHeight="1">
       <c r="A374">
         <v>404</v>
       </c>
@@ -15802,7 +15896,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="375" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:23" ht="15" customHeight="1">
       <c r="A375">
         <v>405</v>
       </c>
@@ -15836,7 +15930,7 @@
       </c>
       <c r="R375" s="2"/>
     </row>
-    <row r="376" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:23" ht="15" customHeight="1">
       <c r="A376">
         <v>406</v>
       </c>
@@ -15870,7 +15964,7 @@
       <c r="P376" s="2"/>
       <c r="R376" s="2"/>
     </row>
-    <row r="377" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:23" ht="15" customHeight="1">
       <c r="A377">
         <v>407</v>
       </c>
@@ -15904,7 +15998,7 @@
       <c r="P377" s="2"/>
       <c r="R377" s="2"/>
     </row>
-    <row r="378" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:23" ht="15" customHeight="1">
       <c r="A378">
         <v>408</v>
       </c>
@@ -15938,7 +16032,7 @@
       <c r="P378" s="2"/>
       <c r="R378" s="2"/>
     </row>
-    <row r="379" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:23" ht="15" customHeight="1">
       <c r="A379">
         <v>409</v>
       </c>
@@ -15972,7 +16066,7 @@
       </c>
       <c r="R379" s="2"/>
     </row>
-    <row r="380" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:23" ht="15" customHeight="1">
       <c r="A380">
         <v>410</v>
       </c>
@@ -16006,7 +16100,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="381" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:23" ht="15" customHeight="1">
       <c r="A381">
         <v>411</v>
       </c>
@@ -16040,7 +16134,7 @@
       </c>
       <c r="R381" s="2"/>
     </row>
-    <row r="382" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:23" ht="15" customHeight="1">
       <c r="A382">
         <v>412</v>
       </c>
@@ -16078,7 +16172,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="383" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:23" ht="15" customHeight="1">
       <c r="A383">
         <v>413</v>
       </c>
@@ -16112,7 +16206,7 @@
       <c r="P383" s="2"/>
       <c r="R383" s="2"/>
     </row>
-    <row r="384" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:23" ht="15" customHeight="1">
       <c r="A384">
         <v>414</v>
       </c>
@@ -16146,7 +16240,7 @@
       <c r="P384" s="2"/>
       <c r="R384" s="2"/>
     </row>
-    <row r="385" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:23" ht="15" customHeight="1">
       <c r="A385">
         <v>415</v>
       </c>
@@ -16180,7 +16274,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="386" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:23" ht="15" customHeight="1">
       <c r="A386">
         <v>416</v>
       </c>
@@ -16214,7 +16308,7 @@
       <c r="P386" s="2"/>
       <c r="R386" s="2"/>
     </row>
-    <row r="387" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:23" ht="15" customHeight="1">
       <c r="A387">
         <v>417</v>
       </c>
@@ -16248,7 +16342,7 @@
       <c r="P387" s="2"/>
       <c r="R387" s="2"/>
     </row>
-    <row r="388" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:23" ht="15" customHeight="1">
       <c r="A388">
         <v>418</v>
       </c>
@@ -16283,7 +16377,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="389" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:23" ht="15" customHeight="1">
       <c r="A389">
         <v>419</v>
       </c>
@@ -16317,7 +16411,7 @@
       <c r="P389" s="2"/>
       <c r="R389" s="2"/>
     </row>
-    <row r="390" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:23" ht="15" customHeight="1">
       <c r="A390">
         <v>420</v>
       </c>
@@ -16351,7 +16445,7 @@
       <c r="P390" s="2"/>
       <c r="R390" s="2"/>
     </row>
-    <row r="391" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:23" ht="15" customHeight="1">
       <c r="A391">
         <v>421</v>
       </c>
@@ -16385,7 +16479,7 @@
       <c r="P391" s="2"/>
       <c r="R391" s="2"/>
     </row>
-    <row r="392" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:23" ht="15" customHeight="1">
       <c r="A392">
         <v>422</v>
       </c>
@@ -16419,7 +16513,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="393" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:23" ht="15" customHeight="1">
       <c r="A393">
         <v>423</v>
       </c>
@@ -16453,7 +16547,7 @@
       <c r="P393" s="2"/>
       <c r="R393" s="2"/>
     </row>
-    <row r="394" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:23" ht="15" customHeight="1">
       <c r="A394">
         <v>424</v>
       </c>
@@ -16487,6 +16581,1119 @@
       <c r="W394" t="s">
         <v>645</v>
       </c>
+    </row>
+    <row r="395" spans="1:23" ht="15" customHeight="1">
+      <c r="A395" s="8">
+        <v>425</v>
+      </c>
+      <c r="B395" s="1">
+        <v>46272.433969907397</v>
+      </c>
+      <c r="C395" s="1">
+        <v>46272.4350694444</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E395" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F395" s="7"/>
+      <c r="G395" s="9">
+        <v>38136</v>
+      </c>
+      <c r="H395" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I395" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="J395" s="8"/>
+      <c r="K395" s="2"/>
+      <c r="L395" s="4"/>
+      <c r="M395" s="2"/>
+      <c r="N395" s="2"/>
+      <c r="O395" s="2"/>
+      <c r="P395" s="2"/>
+      <c r="Q395" s="8"/>
+      <c r="R395" s="2"/>
+      <c r="S395" s="8"/>
+      <c r="T395" s="8"/>
+      <c r="U395" s="8"/>
+      <c r="V395" s="8"/>
+      <c r="W395" s="8"/>
+    </row>
+    <row r="396" spans="1:23" ht="15" customHeight="1">
+      <c r="A396" s="8">
+        <v>426</v>
+      </c>
+      <c r="B396" s="1">
+        <v>46272.433657407397</v>
+      </c>
+      <c r="C396" s="1">
+        <v>46272.435173611098</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E396" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F396" s="7"/>
+      <c r="G396" s="9">
+        <v>38186</v>
+      </c>
+      <c r="H396" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I396" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="J396" s="8"/>
+      <c r="K396" s="2"/>
+      <c r="L396" s="4"/>
+      <c r="M396" s="2"/>
+      <c r="N396" s="2"/>
+      <c r="O396" s="2"/>
+      <c r="P396" s="2"/>
+      <c r="Q396" s="8"/>
+      <c r="R396" s="2"/>
+      <c r="S396" s="8"/>
+      <c r="T396" s="8"/>
+      <c r="U396" s="8"/>
+      <c r="V396" s="8"/>
+      <c r="W396" s="8"/>
+    </row>
+    <row r="397" spans="1:23" ht="15" customHeight="1">
+      <c r="A397" s="8">
+        <v>427</v>
+      </c>
+      <c r="B397" s="1">
+        <v>46272.434062499997</v>
+      </c>
+      <c r="C397" s="1">
+        <v>46272.435185185197</v>
+      </c>
+      <c r="D397" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E397" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F397" s="7"/>
+      <c r="G397" s="9">
+        <v>38694</v>
+      </c>
+      <c r="H397" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I397" s="2"/>
+      <c r="J397" s="8"/>
+      <c r="K397" s="2"/>
+      <c r="L397" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="M397" s="2"/>
+      <c r="N397" s="2"/>
+      <c r="O397" s="2"/>
+      <c r="P397" s="2"/>
+      <c r="Q397" s="8"/>
+      <c r="R397" s="2"/>
+      <c r="S397" s="8"/>
+      <c r="T397" s="8"/>
+      <c r="U397" s="8"/>
+      <c r="V397" s="8"/>
+      <c r="W397" s="8"/>
+    </row>
+    <row r="398" spans="1:23" ht="15" customHeight="1">
+      <c r="A398" s="8">
+        <v>428</v>
+      </c>
+      <c r="B398" s="1">
+        <v>46272.435266203698</v>
+      </c>
+      <c r="C398" s="1">
+        <v>46272.435960648101</v>
+      </c>
+      <c r="D398" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E398" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F398" s="7"/>
+      <c r="G398" s="9">
+        <v>38186</v>
+      </c>
+      <c r="H398" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I398" s="2"/>
+      <c r="J398" s="8"/>
+      <c r="K398" s="2"/>
+      <c r="L398" s="4"/>
+      <c r="M398" s="2"/>
+      <c r="N398" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="O398" s="2"/>
+      <c r="P398" s="2"/>
+      <c r="Q398" s="8"/>
+      <c r="R398" s="2"/>
+      <c r="S398" s="8"/>
+      <c r="T398" s="8"/>
+      <c r="U398" s="8"/>
+      <c r="V398" s="8"/>
+      <c r="W398" s="8"/>
+    </row>
+    <row r="399" spans="1:23" ht="15" customHeight="1">
+      <c r="A399" s="8">
+        <v>429</v>
+      </c>
+      <c r="B399" s="1">
+        <v>46272.435983796298</v>
+      </c>
+      <c r="C399" s="1">
+        <v>46272.4362847222</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E399" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F399" s="7"/>
+      <c r="G399" s="9">
+        <v>38186</v>
+      </c>
+      <c r="H399" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I399" s="2"/>
+      <c r="J399" s="8"/>
+      <c r="K399" s="2"/>
+      <c r="L399" s="4"/>
+      <c r="M399" s="2"/>
+      <c r="N399" s="2"/>
+      <c r="O399" s="2"/>
+      <c r="P399" s="2"/>
+      <c r="Q399" s="8"/>
+      <c r="R399" s="2"/>
+      <c r="S399" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="T399" s="8"/>
+      <c r="U399" s="8"/>
+      <c r="V399" s="8"/>
+      <c r="W399" s="8"/>
+    </row>
+    <row r="400" spans="1:23" ht="15" customHeight="1">
+      <c r="A400" s="8">
+        <v>430</v>
+      </c>
+      <c r="B400" s="1">
+        <v>46272.4358796296</v>
+      </c>
+      <c r="C400" s="1">
+        <v>46272.4368287037</v>
+      </c>
+      <c r="D400" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E400" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F400" s="7"/>
+      <c r="G400" s="9">
+        <v>38694</v>
+      </c>
+      <c r="H400" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I400" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="J400" s="8"/>
+      <c r="K400" s="2"/>
+      <c r="L400" s="4"/>
+      <c r="M400" s="2"/>
+      <c r="N400" s="2"/>
+      <c r="O400" s="2"/>
+      <c r="P400" s="2"/>
+      <c r="Q400" s="8"/>
+      <c r="R400" s="2"/>
+      <c r="S400" s="8"/>
+      <c r="T400" s="8"/>
+      <c r="U400" s="8"/>
+      <c r="V400" s="8"/>
+      <c r="W400" s="8"/>
+    </row>
+    <row r="401" spans="1:23" ht="15" customHeight="1">
+      <c r="A401" s="8">
+        <v>431</v>
+      </c>
+      <c r="B401" s="1">
+        <v>46272.436180555596</v>
+      </c>
+      <c r="C401" s="1">
+        <v>46272.436863425901</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E401" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F401" s="7"/>
+      <c r="G401" s="9">
+        <v>38792</v>
+      </c>
+      <c r="H401" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I401" s="2"/>
+      <c r="J401" s="8"/>
+      <c r="K401" s="2"/>
+      <c r="L401" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="M401" s="2"/>
+      <c r="N401" s="2"/>
+      <c r="O401" s="2"/>
+      <c r="P401" s="2"/>
+      <c r="Q401" s="8"/>
+      <c r="R401" s="2"/>
+      <c r="S401" s="8"/>
+      <c r="T401" s="8"/>
+      <c r="U401" s="8"/>
+      <c r="V401" s="8"/>
+      <c r="W401" s="8"/>
+    </row>
+    <row r="402" spans="1:23" ht="15" customHeight="1">
+      <c r="A402" s="8">
+        <v>432</v>
+      </c>
+      <c r="B402" s="1">
+        <v>46272.437037037002</v>
+      </c>
+      <c r="C402" s="1">
+        <v>46272.438831018502</v>
+      </c>
+      <c r="D402" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E402" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F402" s="7"/>
+      <c r="G402" s="9">
+        <v>38792</v>
+      </c>
+      <c r="H402" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I402" s="2"/>
+      <c r="J402" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K402" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="L402" s="4"/>
+      <c r="M402" s="2"/>
+      <c r="N402" s="2"/>
+      <c r="O402" s="2"/>
+      <c r="P402" s="2"/>
+      <c r="Q402" s="8"/>
+      <c r="R402" s="2"/>
+      <c r="S402" s="8"/>
+      <c r="T402" s="8"/>
+      <c r="U402" s="8"/>
+      <c r="V402" s="8"/>
+      <c r="W402" s="8"/>
+    </row>
+    <row r="403" spans="1:23" ht="15" customHeight="1">
+      <c r="A403" s="8">
+        <v>433</v>
+      </c>
+      <c r="B403" s="1">
+        <v>46272.439143518503</v>
+      </c>
+      <c r="C403" s="1">
+        <v>46272.439826388902</v>
+      </c>
+      <c r="D403" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E403" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F403" s="7"/>
+      <c r="G403" s="9">
+        <v>38792</v>
+      </c>
+      <c r="H403" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I403" s="2"/>
+      <c r="J403" s="8"/>
+      <c r="K403" s="2"/>
+      <c r="L403" s="4"/>
+      <c r="M403" s="2"/>
+      <c r="N403" s="2"/>
+      <c r="O403" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="P403" s="2"/>
+      <c r="Q403" s="8"/>
+      <c r="R403" s="2"/>
+      <c r="S403" s="8"/>
+      <c r="T403" s="8"/>
+      <c r="U403" s="8"/>
+      <c r="V403" s="8"/>
+      <c r="W403" s="8"/>
+    </row>
+    <row r="404" spans="1:23" ht="15" customHeight="1">
+      <c r="A404" s="8">
+        <v>434</v>
+      </c>
+      <c r="B404" s="1">
+        <v>46272.437025462998</v>
+      </c>
+      <c r="C404" s="1">
+        <v>46272.439826388902</v>
+      </c>
+      <c r="D404" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E404" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F404" s="7"/>
+      <c r="G404" s="9">
+        <v>38677</v>
+      </c>
+      <c r="H404" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I404" s="2"/>
+      <c r="J404" s="8"/>
+      <c r="K404" s="2"/>
+      <c r="L404" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="M404" s="2"/>
+      <c r="N404" s="2"/>
+      <c r="O404" s="2"/>
+      <c r="P404" s="2"/>
+      <c r="Q404" s="8"/>
+      <c r="R404" s="2"/>
+      <c r="S404" s="8"/>
+      <c r="T404" s="8"/>
+      <c r="U404" s="8"/>
+      <c r="V404" s="8"/>
+      <c r="W404" s="8"/>
+    </row>
+    <row r="405" spans="1:23" ht="15" customHeight="1">
+      <c r="A405" s="8">
+        <v>435</v>
+      </c>
+      <c r="B405" s="1">
+        <v>46272.439918981501</v>
+      </c>
+      <c r="C405" s="1">
+        <v>46272.440451388902</v>
+      </c>
+      <c r="D405" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E405" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F405" s="7"/>
+      <c r="G405" s="9">
+        <v>38792</v>
+      </c>
+      <c r="H405" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I405" s="2"/>
+      <c r="J405" s="8"/>
+      <c r="K405" s="2"/>
+      <c r="L405" s="4"/>
+      <c r="M405" s="2"/>
+      <c r="N405" s="2"/>
+      <c r="O405" s="2"/>
+      <c r="P405" s="2"/>
+      <c r="Q405" s="8"/>
+      <c r="R405" s="2"/>
+      <c r="S405" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="T405" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="U405" s="8"/>
+      <c r="V405" s="8"/>
+      <c r="W405" s="8"/>
+    </row>
+    <row r="406" spans="1:23" ht="15" customHeight="1">
+      <c r="A406" s="8">
+        <v>436</v>
+      </c>
+      <c r="B406" s="1">
+        <v>46272.441238425898</v>
+      </c>
+      <c r="C406" s="1">
+        <v>46272.441620370402</v>
+      </c>
+      <c r="D406" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E406" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F406" s="7"/>
+      <c r="G406" s="9">
+        <v>38136</v>
+      </c>
+      <c r="H406" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I406" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="J406" s="8"/>
+      <c r="K406" s="2"/>
+      <c r="L406" s="4"/>
+      <c r="M406" s="2"/>
+      <c r="N406" s="2"/>
+      <c r="O406" s="2"/>
+      <c r="P406" s="2"/>
+      <c r="Q406" s="8"/>
+      <c r="R406" s="2"/>
+      <c r="S406" s="8"/>
+      <c r="T406" s="8"/>
+      <c r="U406" s="8"/>
+      <c r="V406" s="8"/>
+      <c r="W406" s="8"/>
+    </row>
+    <row r="407" spans="1:23" ht="15" customHeight="1">
+      <c r="A407" s="8">
+        <v>437</v>
+      </c>
+      <c r="B407" s="1">
+        <v>46272.441921296297</v>
+      </c>
+      <c r="C407" s="1">
+        <v>46272.442604166703</v>
+      </c>
+      <c r="D407" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E407" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F407" s="7"/>
+      <c r="G407" s="9">
+        <v>38136</v>
+      </c>
+      <c r="H407" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I407" s="2"/>
+      <c r="J407" s="8"/>
+      <c r="K407" s="2"/>
+      <c r="L407" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="M407" s="2"/>
+      <c r="N407" s="2"/>
+      <c r="O407" s="2"/>
+      <c r="P407" s="2"/>
+      <c r="Q407" s="8"/>
+      <c r="R407" s="2"/>
+      <c r="S407" s="8"/>
+      <c r="T407" s="8"/>
+      <c r="U407" s="8"/>
+      <c r="V407" s="8"/>
+      <c r="W407" s="8"/>
+    </row>
+    <row r="408" spans="1:23" ht="15" customHeight="1">
+      <c r="A408" s="8">
+        <v>438</v>
+      </c>
+      <c r="B408" s="1">
+        <v>46272.440543981502</v>
+      </c>
+      <c r="C408" s="1">
+        <v>46272.442905092597</v>
+      </c>
+      <c r="D408" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E408" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F408" s="7"/>
+      <c r="G408" s="9">
+        <v>38458</v>
+      </c>
+      <c r="H408" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I408" s="2"/>
+      <c r="J408" s="8"/>
+      <c r="K408" s="2"/>
+      <c r="L408" s="4"/>
+      <c r="M408" s="2"/>
+      <c r="N408" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="O408" s="2"/>
+      <c r="P408" s="2"/>
+      <c r="Q408" s="8"/>
+      <c r="R408" s="2"/>
+      <c r="S408" s="8"/>
+      <c r="T408" s="8"/>
+      <c r="U408" s="8"/>
+      <c r="V408" s="8"/>
+      <c r="W408" s="8"/>
+    </row>
+    <row r="409" spans="1:23" ht="15" customHeight="1">
+      <c r="A409" s="8">
+        <v>439</v>
+      </c>
+      <c r="B409" s="1">
+        <v>46272.445590277799</v>
+      </c>
+      <c r="C409" s="1">
+        <v>46272.446006944403</v>
+      </c>
+      <c r="D409" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E409" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F409" s="7"/>
+      <c r="G409" s="9">
+        <v>38136</v>
+      </c>
+      <c r="H409" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I409" s="2"/>
+      <c r="J409" s="8"/>
+      <c r="K409" s="2"/>
+      <c r="L409" s="4"/>
+      <c r="M409" s="2"/>
+      <c r="N409" s="2"/>
+      <c r="O409" s="2"/>
+      <c r="P409" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="Q409" s="8"/>
+      <c r="R409" s="2"/>
+      <c r="S409" s="8"/>
+      <c r="T409" s="8"/>
+      <c r="U409" s="8"/>
+      <c r="V409" s="8"/>
+      <c r="W409" s="8"/>
+    </row>
+    <row r="410" spans="1:23" ht="15" customHeight="1">
+      <c r="A410" s="8">
+        <v>440</v>
+      </c>
+      <c r="B410" s="1">
+        <v>46272.446111111101</v>
+      </c>
+      <c r="C410" s="1">
+        <v>46272.446643518502</v>
+      </c>
+      <c r="D410" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E410" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F410" s="7"/>
+      <c r="G410" s="9">
+        <v>38136</v>
+      </c>
+      <c r="H410" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I410" s="2"/>
+      <c r="J410" s="8"/>
+      <c r="K410" s="2"/>
+      <c r="L410" s="4"/>
+      <c r="M410" s="2"/>
+      <c r="N410" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="O410" s="2"/>
+      <c r="P410" s="2"/>
+      <c r="Q410" s="8"/>
+      <c r="R410" s="2"/>
+      <c r="S410" s="8"/>
+      <c r="T410" s="8"/>
+      <c r="U410" s="8"/>
+      <c r="V410" s="8"/>
+      <c r="W410" s="8"/>
+    </row>
+    <row r="411" spans="1:23" ht="15" customHeight="1">
+      <c r="A411" s="8">
+        <v>441</v>
+      </c>
+      <c r="B411" s="1">
+        <v>46272.440706018497</v>
+      </c>
+      <c r="C411" s="1">
+        <v>46272.447071759299</v>
+      </c>
+      <c r="D411" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E411" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F411" s="7"/>
+      <c r="G411" s="9">
+        <v>38792</v>
+      </c>
+      <c r="H411" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I411" s="2"/>
+      <c r="J411" s="8"/>
+      <c r="K411" s="2"/>
+      <c r="L411" s="4"/>
+      <c r="M411" s="2"/>
+      <c r="N411" s="2"/>
+      <c r="O411" s="2"/>
+      <c r="P411" s="2"/>
+      <c r="Q411" s="8"/>
+      <c r="R411" s="2"/>
+      <c r="S411" s="8"/>
+      <c r="T411" s="8"/>
+      <c r="U411" s="8"/>
+      <c r="V411" s="8"/>
+      <c r="W411" s="8" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="412" spans="1:23" ht="15" customHeight="1">
+      <c r="A412" s="8">
+        <v>442</v>
+      </c>
+      <c r="B412" s="1">
+        <v>46272.446712962999</v>
+      </c>
+      <c r="C412" s="1">
+        <v>46272.447256944397</v>
+      </c>
+      <c r="D412" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E412" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F412" s="7"/>
+      <c r="G412" s="9">
+        <v>38136</v>
+      </c>
+      <c r="H412" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I412" s="2"/>
+      <c r="J412" s="8"/>
+      <c r="K412" s="2"/>
+      <c r="L412" s="4"/>
+      <c r="M412" s="2"/>
+      <c r="N412" s="2"/>
+      <c r="O412" s="2"/>
+      <c r="P412" s="2"/>
+      <c r="Q412" s="8"/>
+      <c r="R412" s="2"/>
+      <c r="S412" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="T412" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="U412" s="8"/>
+      <c r="V412" s="8"/>
+      <c r="W412" s="8"/>
+    </row>
+    <row r="413" spans="1:23" ht="15" customHeight="1">
+      <c r="A413" s="8">
+        <v>443</v>
+      </c>
+      <c r="B413" s="1">
+        <v>46272.445428240702</v>
+      </c>
+      <c r="C413" s="1">
+        <v>46272.4475578704</v>
+      </c>
+      <c r="D413" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E413" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F413" s="7"/>
+      <c r="G413" s="9">
+        <v>38205</v>
+      </c>
+      <c r="H413" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I413" s="2"/>
+      <c r="J413" s="8"/>
+      <c r="K413" s="2"/>
+      <c r="L413" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="M413" s="2"/>
+      <c r="N413" s="2"/>
+      <c r="O413" s="2"/>
+      <c r="P413" s="2"/>
+      <c r="Q413" s="8"/>
+      <c r="R413" s="2"/>
+      <c r="S413" s="8"/>
+      <c r="T413" s="8"/>
+      <c r="U413" s="8"/>
+      <c r="V413" s="8"/>
+      <c r="W413" s="8"/>
+    </row>
+    <row r="414" spans="1:23" ht="15" customHeight="1">
+      <c r="A414" s="8">
+        <v>444</v>
+      </c>
+      <c r="B414" s="1">
+        <v>46272.447534722203</v>
+      </c>
+      <c r="C414" s="1">
+        <v>46272.447893518503</v>
+      </c>
+      <c r="D414" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E414" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F414" s="7"/>
+      <c r="G414" s="9">
+        <v>38136</v>
+      </c>
+      <c r="H414" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I414" s="2"/>
+      <c r="J414" s="8"/>
+      <c r="K414" s="2"/>
+      <c r="L414" s="4"/>
+      <c r="M414" s="2"/>
+      <c r="N414" s="2"/>
+      <c r="O414" s="2"/>
+      <c r="P414" s="2"/>
+      <c r="Q414" s="8"/>
+      <c r="R414" s="2"/>
+      <c r="S414" s="8"/>
+      <c r="T414" s="8"/>
+      <c r="U414" s="8"/>
+      <c r="V414" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="W414" s="8"/>
+    </row>
+    <row r="415" spans="1:23" ht="15" customHeight="1">
+      <c r="A415" s="8">
+        <v>445</v>
+      </c>
+      <c r="B415" s="1">
+        <v>46272.447476851899</v>
+      </c>
+      <c r="C415" s="1">
+        <v>46272.448032407403</v>
+      </c>
+      <c r="D415" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E415" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F415" s="7"/>
+      <c r="G415" s="9">
+        <v>38792</v>
+      </c>
+      <c r="H415" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I415" s="2"/>
+      <c r="J415" s="8"/>
+      <c r="K415" s="2"/>
+      <c r="L415" s="4"/>
+      <c r="M415" s="2"/>
+      <c r="N415" s="2"/>
+      <c r="O415" s="2"/>
+      <c r="P415" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="Q415" s="8"/>
+      <c r="R415" s="2"/>
+      <c r="S415" s="8"/>
+      <c r="T415" s="8"/>
+      <c r="U415" s="8"/>
+      <c r="V415" s="8"/>
+      <c r="W415" s="8"/>
+    </row>
+    <row r="416" spans="1:23" ht="15" customHeight="1">
+      <c r="A416" s="8">
+        <v>446</v>
+      </c>
+      <c r="B416" s="1">
+        <v>46272.448020833297</v>
+      </c>
+      <c r="C416" s="1">
+        <v>46272.448506944398</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E416" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F416" s="7"/>
+      <c r="G416" s="9">
+        <v>38136</v>
+      </c>
+      <c r="H416" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I416" s="2"/>
+      <c r="J416" s="8"/>
+      <c r="K416" s="2"/>
+      <c r="L416" s="4"/>
+      <c r="M416" s="2"/>
+      <c r="N416" s="2"/>
+      <c r="O416" s="2"/>
+      <c r="P416" s="2"/>
+      <c r="Q416" s="8"/>
+      <c r="R416" s="2"/>
+      <c r="S416" s="8"/>
+      <c r="T416" s="8"/>
+      <c r="U416" s="8"/>
+      <c r="V416" s="8"/>
+      <c r="W416" s="8" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="417" spans="1:23" ht="15" customHeight="1">
+      <c r="A417" s="8">
+        <v>447</v>
+      </c>
+      <c r="B417" s="1">
+        <v>46272.447650463</v>
+      </c>
+      <c r="C417" s="1">
+        <v>46272.448564814797</v>
+      </c>
+      <c r="D417" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E417" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F417" s="7"/>
+      <c r="G417" s="9">
+        <v>38205</v>
+      </c>
+      <c r="H417" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I417" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="J417" s="8"/>
+      <c r="K417" s="2"/>
+      <c r="L417" s="4"/>
+      <c r="M417" s="2"/>
+      <c r="N417" s="2"/>
+      <c r="O417" s="2"/>
+      <c r="P417" s="2"/>
+      <c r="Q417" s="8"/>
+      <c r="R417" s="2"/>
+      <c r="S417" s="8"/>
+      <c r="T417" s="8"/>
+      <c r="U417" s="8"/>
+      <c r="V417" s="8"/>
+      <c r="W417" s="8"/>
+    </row>
+    <row r="418" spans="1:23" ht="15" customHeight="1">
+      <c r="A418" s="8">
+        <v>448</v>
+      </c>
+      <c r="B418" s="1">
+        <v>46272.448275463001</v>
+      </c>
+      <c r="C418" s="1">
+        <v>46272.448657407404</v>
+      </c>
+      <c r="D418" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E418" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F418" s="7"/>
+      <c r="G418" s="9">
+        <v>38792</v>
+      </c>
+      <c r="H418" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I418" s="2"/>
+      <c r="J418" s="8"/>
+      <c r="K418" s="2"/>
+      <c r="L418" s="4"/>
+      <c r="M418" s="2"/>
+      <c r="N418" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="O418" s="2"/>
+      <c r="P418" s="2"/>
+      <c r="Q418" s="8"/>
+      <c r="R418" s="2"/>
+      <c r="S418" s="8"/>
+      <c r="T418" s="8"/>
+      <c r="U418" s="8"/>
+      <c r="V418" s="8"/>
+      <c r="W418" s="8"/>
+    </row>
+    <row r="419" spans="1:23" ht="15" customHeight="1">
+      <c r="A419" s="8">
+        <v>449</v>
+      </c>
+      <c r="B419" s="1">
+        <v>46272.448738425897</v>
+      </c>
+      <c r="C419" s="1">
+        <v>46272.449166666702</v>
+      </c>
+      <c r="D419" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E419" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F419" s="7"/>
+      <c r="G419" s="9">
+        <v>38792</v>
+      </c>
+      <c r="H419" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I419" s="2"/>
+      <c r="J419" s="8"/>
+      <c r="K419" s="2"/>
+      <c r="L419" s="4"/>
+      <c r="M419" s="2"/>
+      <c r="N419" s="2"/>
+      <c r="O419" s="2"/>
+      <c r="P419" s="2"/>
+      <c r="Q419" s="8"/>
+      <c r="R419" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="S419" s="8"/>
+      <c r="T419" s="8"/>
+      <c r="U419" s="8"/>
+      <c r="V419" s="8"/>
+      <c r="W419" s="8"/>
+    </row>
+    <row r="420" spans="1:23" ht="15" customHeight="1">
+      <c r="A420" s="8">
+        <v>450</v>
+      </c>
+      <c r="B420" s="1">
+        <v>46272.449259259301</v>
+      </c>
+      <c r="C420" s="1">
+        <v>46272.4508333333</v>
+      </c>
+      <c r="D420" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E420" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F420" s="7"/>
+      <c r="G420" s="9">
+        <v>38792</v>
+      </c>
+      <c r="H420" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I420" s="2"/>
+      <c r="J420" s="8"/>
+      <c r="K420" s="2"/>
+      <c r="L420" s="4"/>
+      <c r="M420" s="2"/>
+      <c r="N420" s="2"/>
+      <c r="O420" s="2"/>
+      <c r="P420" s="2"/>
+      <c r="Q420" s="8"/>
+      <c r="R420" s="2"/>
+      <c r="S420" s="8"/>
+      <c r="T420" s="8"/>
+      <c r="U420" s="8"/>
+      <c r="V420" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="W420" s="8"/>
+    </row>
+    <row r="421" spans="1:23" ht="15" customHeight="1">
+      <c r="A421" s="8">
+        <v>451</v>
+      </c>
+      <c r="B421" s="1">
+        <v>46272.451018518499</v>
+      </c>
+      <c r="C421" s="1">
+        <v>46272.4546990741</v>
+      </c>
+      <c r="D421" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E421" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F421" s="7"/>
+      <c r="G421" s="9">
+        <v>38792</v>
+      </c>
+      <c r="H421" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I421" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="J421" s="8"/>
+      <c r="K421" s="2"/>
+      <c r="L421" s="4"/>
+      <c r="M421" s="2"/>
+      <c r="N421" s="2"/>
+      <c r="O421" s="2"/>
+      <c r="P421" s="2"/>
+      <c r="Q421" s="8"/>
+      <c r="R421" s="2"/>
+      <c r="S421" s="8"/>
+      <c r="T421" s="8"/>
+      <c r="U421" s="8"/>
+      <c r="V421" s="8"/>
+      <c r="W421" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB2AD1A2-ED5C-4F09-B447-3A5A5EE79553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F758FDF7-9CCC-4FCC-98C2-2FFEE0C934FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="683">
   <si>
     <t>Id</t>
   </si>
@@ -2064,6 +2064,27 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/6532E230-1F45-4DCB-B525-B1AD550D1784_Starbucks%20Pasaje%20Tla.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx43132@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Vista Norte</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260831-WA0080_Starbucks%20Plaza%20Vist.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Vanessa%20Carre%C3%B1o%20Rios%201.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG-20260907-WA0051_Starbucks%20Plaza%20Vist.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_7742_Starbucks%20Jinetes.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/09958b48-f7a6-48a5-847c-462e72013062_Berenice%20Ivon%20Sanche.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2216,8 +2237,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W421" totalsRowShown="0">
-  <autoFilter ref="A1:W421" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W426" totalsRowShown="0">
+  <autoFilter ref="A1:W426" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2384,7 +2405,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="451" latestEventMarker="718">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="456" latestEventMarker="723">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2713,7 +2734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W421"/>
+  <dimension ref="A1:W426"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -17695,6 +17716,211 @@
       <c r="V421" s="8"/>
       <c r="W421" s="8"/>
     </row>
+    <row r="422" spans="1:23" ht="15" customHeight="1">
+      <c r="A422" s="8">
+        <v>452</v>
+      </c>
+      <c r="B422" s="1">
+        <v>46272.456226851798</v>
+      </c>
+      <c r="C422" s="1">
+        <v>46272.456724536998</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E422" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="F422" s="7"/>
+      <c r="G422" s="9">
+        <v>43132</v>
+      </c>
+      <c r="H422" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I422" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="J422" s="8"/>
+      <c r="K422" s="2"/>
+      <c r="L422" s="4"/>
+      <c r="M422" s="2"/>
+      <c r="N422" s="2"/>
+      <c r="O422" s="2"/>
+      <c r="P422" s="2"/>
+      <c r="Q422" s="8"/>
+      <c r="R422" s="2"/>
+      <c r="S422" s="8"/>
+      <c r="T422" s="8"/>
+      <c r="U422" s="8"/>
+      <c r="V422" s="8"/>
+      <c r="W422" s="8"/>
+    </row>
+    <row r="423" spans="1:23" ht="15" customHeight="1">
+      <c r="A423" s="8">
+        <v>453</v>
+      </c>
+      <c r="B423" s="1">
+        <v>46272.456377314797</v>
+      </c>
+      <c r="C423" s="1">
+        <v>46272.457442129598</v>
+      </c>
+      <c r="D423" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E423" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F423" s="7"/>
+      <c r="G423" s="9">
+        <v>38677</v>
+      </c>
+      <c r="H423" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I423" s="2"/>
+      <c r="J423" s="8"/>
+      <c r="K423" s="2"/>
+      <c r="L423" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="M423" s="2"/>
+      <c r="N423" s="2"/>
+      <c r="O423" s="2"/>
+      <c r="P423" s="2"/>
+      <c r="Q423" s="8"/>
+      <c r="R423" s="2"/>
+      <c r="S423" s="8"/>
+      <c r="T423" s="8"/>
+      <c r="U423" s="8"/>
+      <c r="V423" s="8"/>
+      <c r="W423" s="8"/>
+    </row>
+    <row r="424" spans="1:23" ht="15" customHeight="1">
+      <c r="A424" s="8">
+        <v>454</v>
+      </c>
+      <c r="B424" s="1">
+        <v>46272.457037036998</v>
+      </c>
+      <c r="C424" s="1">
+        <v>46272.458055555602</v>
+      </c>
+      <c r="D424" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E424" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="F424" s="7"/>
+      <c r="G424" s="9">
+        <v>43132</v>
+      </c>
+      <c r="H424" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I424" s="2"/>
+      <c r="J424" s="8"/>
+      <c r="K424" s="2"/>
+      <c r="L424" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="M424" s="2"/>
+      <c r="N424" s="2"/>
+      <c r="O424" s="2"/>
+      <c r="P424" s="2"/>
+      <c r="Q424" s="8"/>
+      <c r="R424" s="2"/>
+      <c r="S424" s="8"/>
+      <c r="T424" s="8"/>
+      <c r="U424" s="8"/>
+      <c r="V424" s="8"/>
+      <c r="W424" s="8"/>
+    </row>
+    <row r="425" spans="1:23" ht="15" customHeight="1">
+      <c r="A425" s="8">
+        <v>455</v>
+      </c>
+      <c r="B425" s="1">
+        <v>46272.457604166702</v>
+      </c>
+      <c r="C425" s="1">
+        <v>46272.458530092597</v>
+      </c>
+      <c r="D425" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E425" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F425" s="7"/>
+      <c r="G425" s="9">
+        <v>38661</v>
+      </c>
+      <c r="H425" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I425" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="J425" s="8"/>
+      <c r="K425" s="2"/>
+      <c r="L425" s="4"/>
+      <c r="M425" s="2"/>
+      <c r="N425" s="2"/>
+      <c r="O425" s="2"/>
+      <c r="P425" s="2"/>
+      <c r="Q425" s="8"/>
+      <c r="R425" s="2"/>
+      <c r="S425" s="8"/>
+      <c r="T425" s="8"/>
+      <c r="U425" s="8"/>
+      <c r="V425" s="8"/>
+      <c r="W425" s="8"/>
+    </row>
+    <row r="426" spans="1:23" ht="15" customHeight="1">
+      <c r="A426" s="8">
+        <v>456</v>
+      </c>
+      <c r="B426" s="1">
+        <v>46272.461087962998</v>
+      </c>
+      <c r="C426" s="1">
+        <v>46272.465312499997</v>
+      </c>
+      <c r="D426" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E426" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F426" s="7"/>
+      <c r="G426" s="9">
+        <v>38651</v>
+      </c>
+      <c r="H426" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I426" s="2"/>
+      <c r="J426" s="8"/>
+      <c r="K426" s="2"/>
+      <c r="L426" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="M426" s="2"/>
+      <c r="N426" s="2"/>
+      <c r="O426" s="2"/>
+      <c r="P426" s="2"/>
+      <c r="Q426" s="8"/>
+      <c r="R426" s="2"/>
+      <c r="S426" s="8"/>
+      <c r="T426" s="8"/>
+      <c r="U426" s="8"/>
+      <c r="V426" s="8"/>
+      <c r="W426" s="8"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F758FDF7-9CCC-4FCC-98C2-2FFEE0C934FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76BAB7DB-A6E2-48AD-9C69-A6229C2CEC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="696">
   <si>
     <t>Id</t>
   </si>
@@ -2085,6 +2085,45 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/09958b48-f7a6-48a5-847c-462e72013062_Berenice%20Ivon%20Sanche.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/485376cb-f64a-441a-ae1f-a847ec8e0cea_Berenice%20Ivon%20Sanche.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38527@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Camarones</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Camarones.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_2393_Starbucks%20Camarones.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx43195@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Parque Jardín Kiosko</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260907-WA0055_Starbucks%20Parque%20Jar.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/7C802EC3-F134-42E0-B7AD-213014CF1F05_Starbucks%20Arboledas.png</t>
+  </si>
+  <si>
+    <t>david.zaragoza@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>David Zaragoza Diaz</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/WhatsApp%20Image%202026-09-07%20at%2011.33.13%20AM_David%20Zaragoza%20Diaz.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Arboledas.jpg</t>
   </si>
 </sst>
 </file>
@@ -2237,8 +2276,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W426" totalsRowShown="0">
-  <autoFilter ref="A1:W426" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W434" totalsRowShown="0">
+  <autoFilter ref="A1:W434" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2405,7 +2444,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="456" latestEventMarker="723">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="464" latestEventMarker="731">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2734,13 +2773,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W426"/>
+  <dimension ref="A1:W434"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
     <col min="2" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.140625" customWidth="1"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="5" max="5" width="31.5703125" customWidth="1"/>
     <col min="6" max="6" width="7.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="13" width="20" bestFit="1" customWidth="1"/>
@@ -16604,7 +16643,7 @@
       </c>
     </row>
     <row r="395" spans="1:23" ht="15" customHeight="1">
-      <c r="A395" s="8">
+      <c r="A395">
         <v>425</v>
       </c>
       <c r="B395" s="1">
@@ -16620,7 +16659,7 @@
         <v>264</v>
       </c>
       <c r="F395" s="7"/>
-      <c r="G395" s="9">
+      <c r="G395" s="6">
         <v>38136</v>
       </c>
       <c r="H395" s="2" t="s">
@@ -16629,23 +16668,16 @@
       <c r="I395" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="J395" s="8"/>
       <c r="K395" s="2"/>
       <c r="L395" s="4"/>
       <c r="M395" s="2"/>
       <c r="N395" s="2"/>
       <c r="O395" s="2"/>
       <c r="P395" s="2"/>
-      <c r="Q395" s="8"/>
       <c r="R395" s="2"/>
-      <c r="S395" s="8"/>
-      <c r="T395" s="8"/>
-      <c r="U395" s="8"/>
-      <c r="V395" s="8"/>
-      <c r="W395" s="8"/>
     </row>
     <row r="396" spans="1:23" ht="15" customHeight="1">
-      <c r="A396" s="8">
+      <c r="A396">
         <v>426</v>
       </c>
       <c r="B396" s="1">
@@ -16661,7 +16693,7 @@
         <v>212</v>
       </c>
       <c r="F396" s="7"/>
-      <c r="G396" s="9">
+      <c r="G396" s="6">
         <v>38186</v>
       </c>
       <c r="H396" s="2" t="s">
@@ -16670,23 +16702,16 @@
       <c r="I396" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="J396" s="8"/>
       <c r="K396" s="2"/>
       <c r="L396" s="4"/>
       <c r="M396" s="2"/>
       <c r="N396" s="2"/>
       <c r="O396" s="2"/>
       <c r="P396" s="2"/>
-      <c r="Q396" s="8"/>
       <c r="R396" s="2"/>
-      <c r="S396" s="8"/>
-      <c r="T396" s="8"/>
-      <c r="U396" s="8"/>
-      <c r="V396" s="8"/>
-      <c r="W396" s="8"/>
     </row>
     <row r="397" spans="1:23" ht="15" customHeight="1">
-      <c r="A397" s="8">
+      <c r="A397">
         <v>427</v>
       </c>
       <c r="B397" s="1">
@@ -16702,14 +16727,13 @@
         <v>204</v>
       </c>
       <c r="F397" s="7"/>
-      <c r="G397" s="9">
+      <c r="G397" s="6">
         <v>38694</v>
       </c>
       <c r="H397" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I397" s="2"/>
-      <c r="J397" s="8"/>
       <c r="K397" s="2"/>
       <c r="L397" s="4" t="s">
         <v>648</v>
@@ -16718,16 +16742,10 @@
       <c r="N397" s="2"/>
       <c r="O397" s="2"/>
       <c r="P397" s="2"/>
-      <c r="Q397" s="8"/>
       <c r="R397" s="2"/>
-      <c r="S397" s="8"/>
-      <c r="T397" s="8"/>
-      <c r="U397" s="8"/>
-      <c r="V397" s="8"/>
-      <c r="W397" s="8"/>
     </row>
     <row r="398" spans="1:23" ht="15" customHeight="1">
-      <c r="A398" s="8">
+      <c r="A398">
         <v>428</v>
       </c>
       <c r="B398" s="1">
@@ -16743,14 +16761,13 @@
         <v>212</v>
       </c>
       <c r="F398" s="7"/>
-      <c r="G398" s="9">
+      <c r="G398" s="6">
         <v>38186</v>
       </c>
       <c r="H398" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I398" s="2"/>
-      <c r="J398" s="8"/>
       <c r="K398" s="2"/>
       <c r="L398" s="4"/>
       <c r="M398" s="2"/>
@@ -16759,16 +16776,10 @@
       </c>
       <c r="O398" s="2"/>
       <c r="P398" s="2"/>
-      <c r="Q398" s="8"/>
       <c r="R398" s="2"/>
-      <c r="S398" s="8"/>
-      <c r="T398" s="8"/>
-      <c r="U398" s="8"/>
-      <c r="V398" s="8"/>
-      <c r="W398" s="8"/>
     </row>
     <row r="399" spans="1:23" ht="15" customHeight="1">
-      <c r="A399" s="8">
+      <c r="A399">
         <v>429</v>
       </c>
       <c r="B399" s="1">
@@ -16784,32 +16795,26 @@
         <v>212</v>
       </c>
       <c r="F399" s="7"/>
-      <c r="G399" s="9">
+      <c r="G399" s="6">
         <v>38186</v>
       </c>
       <c r="H399" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I399" s="2"/>
-      <c r="J399" s="8"/>
       <c r="K399" s="2"/>
       <c r="L399" s="4"/>
       <c r="M399" s="2"/>
       <c r="N399" s="2"/>
       <c r="O399" s="2"/>
       <c r="P399" s="2"/>
-      <c r="Q399" s="8"/>
       <c r="R399" s="2"/>
-      <c r="S399" s="8" t="s">
+      <c r="S399" t="s">
         <v>109</v>
       </c>
-      <c r="T399" s="8"/>
-      <c r="U399" s="8"/>
-      <c r="V399" s="8"/>
-      <c r="W399" s="8"/>
     </row>
     <row r="400" spans="1:23" ht="15" customHeight="1">
-      <c r="A400" s="8">
+      <c r="A400">
         <v>430</v>
       </c>
       <c r="B400" s="1">
@@ -16825,7 +16830,7 @@
         <v>204</v>
       </c>
       <c r="F400" s="7"/>
-      <c r="G400" s="9">
+      <c r="G400" s="6">
         <v>38694</v>
       </c>
       <c r="H400" s="2" t="s">
@@ -16834,23 +16839,16 @@
       <c r="I400" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="J400" s="8"/>
       <c r="K400" s="2"/>
       <c r="L400" s="4"/>
       <c r="M400" s="2"/>
       <c r="N400" s="2"/>
       <c r="O400" s="2"/>
       <c r="P400" s="2"/>
-      <c r="Q400" s="8"/>
       <c r="R400" s="2"/>
-      <c r="S400" s="8"/>
-      <c r="T400" s="8"/>
-      <c r="U400" s="8"/>
-      <c r="V400" s="8"/>
-      <c r="W400" s="8"/>
     </row>
     <row r="401" spans="1:23" ht="15" customHeight="1">
-      <c r="A401" s="8">
+      <c r="A401">
         <v>431</v>
       </c>
       <c r="B401" s="1">
@@ -16866,14 +16864,13 @@
         <v>652</v>
       </c>
       <c r="F401" s="7"/>
-      <c r="G401" s="9">
+      <c r="G401" s="6">
         <v>38792</v>
       </c>
       <c r="H401" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I401" s="2"/>
-      <c r="J401" s="8"/>
       <c r="K401" s="2"/>
       <c r="L401" s="4" t="s">
         <v>653</v>
@@ -16882,16 +16879,10 @@
       <c r="N401" s="2"/>
       <c r="O401" s="2"/>
       <c r="P401" s="2"/>
-      <c r="Q401" s="8"/>
       <c r="R401" s="2"/>
-      <c r="S401" s="8"/>
-      <c r="T401" s="8"/>
-      <c r="U401" s="8"/>
-      <c r="V401" s="8"/>
-      <c r="W401" s="8"/>
     </row>
     <row r="402" spans="1:23" ht="15" customHeight="1">
-      <c r="A402" s="8">
+      <c r="A402">
         <v>432</v>
       </c>
       <c r="B402" s="1">
@@ -16907,14 +16898,14 @@
         <v>652</v>
       </c>
       <c r="F402" s="7"/>
-      <c r="G402" s="9">
+      <c r="G402" s="6">
         <v>38792</v>
       </c>
       <c r="H402" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I402" s="2"/>
-      <c r="J402" s="8" t="s">
+      <c r="J402" t="s">
         <v>63</v>
       </c>
       <c r="K402" s="2" t="s">
@@ -16925,16 +16916,10 @@
       <c r="N402" s="2"/>
       <c r="O402" s="2"/>
       <c r="P402" s="2"/>
-      <c r="Q402" s="8"/>
       <c r="R402" s="2"/>
-      <c r="S402" s="8"/>
-      <c r="T402" s="8"/>
-      <c r="U402" s="8"/>
-      <c r="V402" s="8"/>
-      <c r="W402" s="8"/>
     </row>
     <row r="403" spans="1:23" ht="15" customHeight="1">
-      <c r="A403" s="8">
+      <c r="A403">
         <v>433</v>
       </c>
       <c r="B403" s="1">
@@ -16950,14 +16935,13 @@
         <v>652</v>
       </c>
       <c r="F403" s="7"/>
-      <c r="G403" s="9">
+      <c r="G403" s="6">
         <v>38792</v>
       </c>
       <c r="H403" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I403" s="2"/>
-      <c r="J403" s="8"/>
       <c r="K403" s="2"/>
       <c r="L403" s="4"/>
       <c r="M403" s="2"/>
@@ -16966,16 +16950,10 @@
         <v>655</v>
       </c>
       <c r="P403" s="2"/>
-      <c r="Q403" s="8"/>
       <c r="R403" s="2"/>
-      <c r="S403" s="8"/>
-      <c r="T403" s="8"/>
-      <c r="U403" s="8"/>
-      <c r="V403" s="8"/>
-      <c r="W403" s="8"/>
     </row>
     <row r="404" spans="1:23" ht="15" customHeight="1">
-      <c r="A404" s="8">
+      <c r="A404">
         <v>434</v>
       </c>
       <c r="B404" s="1">
@@ -16991,14 +16969,13 @@
         <v>92</v>
       </c>
       <c r="F404" s="7"/>
-      <c r="G404" s="9">
+      <c r="G404" s="6">
         <v>38677</v>
       </c>
       <c r="H404" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I404" s="2"/>
-      <c r="J404" s="8"/>
       <c r="K404" s="2"/>
       <c r="L404" s="4" t="s">
         <v>656</v>
@@ -17007,16 +16984,10 @@
       <c r="N404" s="2"/>
       <c r="O404" s="2"/>
       <c r="P404" s="2"/>
-      <c r="Q404" s="8"/>
       <c r="R404" s="2"/>
-      <c r="S404" s="8"/>
-      <c r="T404" s="8"/>
-      <c r="U404" s="8"/>
-      <c r="V404" s="8"/>
-      <c r="W404" s="8"/>
     </row>
     <row r="405" spans="1:23" ht="15" customHeight="1">
-      <c r="A405" s="8">
+      <c r="A405">
         <v>435</v>
       </c>
       <c r="B405" s="1">
@@ -17032,34 +17003,29 @@
         <v>652</v>
       </c>
       <c r="F405" s="7"/>
-      <c r="G405" s="9">
+      <c r="G405" s="6">
         <v>38792</v>
       </c>
       <c r="H405" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I405" s="2"/>
-      <c r="J405" s="8"/>
       <c r="K405" s="2"/>
       <c r="L405" s="4"/>
       <c r="M405" s="2"/>
       <c r="N405" s="2"/>
       <c r="O405" s="2"/>
       <c r="P405" s="2"/>
-      <c r="Q405" s="8"/>
       <c r="R405" s="2"/>
-      <c r="S405" s="8" t="s">
+      <c r="S405" t="s">
         <v>63</v>
       </c>
-      <c r="T405" s="8" t="s">
+      <c r="T405" t="s">
         <v>657</v>
       </c>
-      <c r="U405" s="8"/>
-      <c r="V405" s="8"/>
-      <c r="W405" s="8"/>
     </row>
     <row r="406" spans="1:23" ht="15" customHeight="1">
-      <c r="A406" s="8">
+      <c r="A406">
         <v>436</v>
       </c>
       <c r="B406" s="1">
@@ -17075,7 +17041,7 @@
         <v>264</v>
       </c>
       <c r="F406" s="7"/>
-      <c r="G406" s="9">
+      <c r="G406" s="6">
         <v>38136</v>
       </c>
       <c r="H406" s="2" t="s">
@@ -17084,23 +17050,16 @@
       <c r="I406" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="J406" s="8"/>
       <c r="K406" s="2"/>
       <c r="L406" s="4"/>
       <c r="M406" s="2"/>
       <c r="N406" s="2"/>
       <c r="O406" s="2"/>
       <c r="P406" s="2"/>
-      <c r="Q406" s="8"/>
       <c r="R406" s="2"/>
-      <c r="S406" s="8"/>
-      <c r="T406" s="8"/>
-      <c r="U406" s="8"/>
-      <c r="V406" s="8"/>
-      <c r="W406" s="8"/>
     </row>
     <row r="407" spans="1:23" ht="15" customHeight="1">
-      <c r="A407" s="8">
+      <c r="A407">
         <v>437</v>
       </c>
       <c r="B407" s="1">
@@ -17116,14 +17075,13 @@
         <v>264</v>
       </c>
       <c r="F407" s="7"/>
-      <c r="G407" s="9">
+      <c r="G407" s="6">
         <v>38136</v>
       </c>
       <c r="H407" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I407" s="2"/>
-      <c r="J407" s="8"/>
       <c r="K407" s="2"/>
       <c r="L407" s="4" t="s">
         <v>659</v>
@@ -17132,16 +17090,10 @@
       <c r="N407" s="2"/>
       <c r="O407" s="2"/>
       <c r="P407" s="2"/>
-      <c r="Q407" s="8"/>
       <c r="R407" s="2"/>
-      <c r="S407" s="8"/>
-      <c r="T407" s="8"/>
-      <c r="U407" s="8"/>
-      <c r="V407" s="8"/>
-      <c r="W407" s="8"/>
     </row>
     <row r="408" spans="1:23" ht="15" customHeight="1">
-      <c r="A408" s="8">
+      <c r="A408">
         <v>438</v>
       </c>
       <c r="B408" s="1">
@@ -17157,14 +17109,13 @@
         <v>193</v>
       </c>
       <c r="F408" s="7"/>
-      <c r="G408" s="9">
+      <c r="G408" s="6">
         <v>38458</v>
       </c>
       <c r="H408" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I408" s="2"/>
-      <c r="J408" s="8"/>
       <c r="K408" s="2"/>
       <c r="L408" s="4"/>
       <c r="M408" s="2"/>
@@ -17173,16 +17124,10 @@
       </c>
       <c r="O408" s="2"/>
       <c r="P408" s="2"/>
-      <c r="Q408" s="8"/>
       <c r="R408" s="2"/>
-      <c r="S408" s="8"/>
-      <c r="T408" s="8"/>
-      <c r="U408" s="8"/>
-      <c r="V408" s="8"/>
-      <c r="W408" s="8"/>
     </row>
     <row r="409" spans="1:23" ht="15" customHeight="1">
-      <c r="A409" s="8">
+      <c r="A409">
         <v>439</v>
       </c>
       <c r="B409" s="1">
@@ -17198,14 +17143,13 @@
         <v>264</v>
       </c>
       <c r="F409" s="7"/>
-      <c r="G409" s="9">
+      <c r="G409" s="6">
         <v>38136</v>
       </c>
       <c r="H409" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I409" s="2"/>
-      <c r="J409" s="8"/>
       <c r="K409" s="2"/>
       <c r="L409" s="4"/>
       <c r="M409" s="2"/>
@@ -17214,16 +17158,10 @@
       <c r="P409" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="Q409" s="8"/>
       <c r="R409" s="2"/>
-      <c r="S409" s="8"/>
-      <c r="T409" s="8"/>
-      <c r="U409" s="8"/>
-      <c r="V409" s="8"/>
-      <c r="W409" s="8"/>
     </row>
     <row r="410" spans="1:23" ht="15" customHeight="1">
-      <c r="A410" s="8">
+      <c r="A410">
         <v>440</v>
       </c>
       <c r="B410" s="1">
@@ -17239,14 +17177,13 @@
         <v>264</v>
       </c>
       <c r="F410" s="7"/>
-      <c r="G410" s="9">
+      <c r="G410" s="6">
         <v>38136</v>
       </c>
       <c r="H410" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I410" s="2"/>
-      <c r="J410" s="8"/>
       <c r="K410" s="2"/>
       <c r="L410" s="4"/>
       <c r="M410" s="2"/>
@@ -17255,16 +17192,10 @@
       </c>
       <c r="O410" s="2"/>
       <c r="P410" s="2"/>
-      <c r="Q410" s="8"/>
       <c r="R410" s="2"/>
-      <c r="S410" s="8"/>
-      <c r="T410" s="8"/>
-      <c r="U410" s="8"/>
-      <c r="V410" s="8"/>
-      <c r="W410" s="8"/>
     </row>
     <row r="411" spans="1:23" ht="15" customHeight="1">
-      <c r="A411" s="8">
+      <c r="A411">
         <v>441</v>
       </c>
       <c r="B411" s="1">
@@ -17280,32 +17211,26 @@
         <v>652</v>
       </c>
       <c r="F411" s="7"/>
-      <c r="G411" s="9">
+      <c r="G411" s="6">
         <v>38792</v>
       </c>
       <c r="H411" s="2" t="s">
         <v>290</v>
       </c>
       <c r="I411" s="2"/>
-      <c r="J411" s="8"/>
       <c r="K411" s="2"/>
       <c r="L411" s="4"/>
       <c r="M411" s="2"/>
       <c r="N411" s="2"/>
       <c r="O411" s="2"/>
       <c r="P411" s="2"/>
-      <c r="Q411" s="8"/>
       <c r="R411" s="2"/>
-      <c r="S411" s="8"/>
-      <c r="T411" s="8"/>
-      <c r="U411" s="8"/>
-      <c r="V411" s="8"/>
-      <c r="W411" s="8" t="s">
+      <c r="W411" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="412" spans="1:23" ht="15" customHeight="1">
-      <c r="A412" s="8">
+      <c r="A412">
         <v>442</v>
       </c>
       <c r="B412" s="1">
@@ -17321,34 +17246,29 @@
         <v>264</v>
       </c>
       <c r="F412" s="7"/>
-      <c r="G412" s="9">
+      <c r="G412" s="6">
         <v>38136</v>
       </c>
       <c r="H412" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I412" s="2"/>
-      <c r="J412" s="8"/>
       <c r="K412" s="2"/>
       <c r="L412" s="4"/>
       <c r="M412" s="2"/>
       <c r="N412" s="2"/>
       <c r="O412" s="2"/>
       <c r="P412" s="2"/>
-      <c r="Q412" s="8"/>
       <c r="R412" s="2"/>
-      <c r="S412" s="8" t="s">
+      <c r="S412" t="s">
         <v>63</v>
       </c>
-      <c r="T412" s="8" t="s">
+      <c r="T412" t="s">
         <v>664</v>
       </c>
-      <c r="U412" s="8"/>
-      <c r="V412" s="8"/>
-      <c r="W412" s="8"/>
     </row>
     <row r="413" spans="1:23" ht="15" customHeight="1">
-      <c r="A413" s="8">
+      <c r="A413">
         <v>443</v>
       </c>
       <c r="B413" s="1">
@@ -17364,14 +17284,13 @@
         <v>666</v>
       </c>
       <c r="F413" s="7"/>
-      <c r="G413" s="9">
+      <c r="G413" s="6">
         <v>38205</v>
       </c>
       <c r="H413" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I413" s="2"/>
-      <c r="J413" s="8"/>
       <c r="K413" s="2"/>
       <c r="L413" s="4" t="s">
         <v>667</v>
@@ -17380,16 +17299,10 @@
       <c r="N413" s="2"/>
       <c r="O413" s="2"/>
       <c r="P413" s="2"/>
-      <c r="Q413" s="8"/>
       <c r="R413" s="2"/>
-      <c r="S413" s="8"/>
-      <c r="T413" s="8"/>
-      <c r="U413" s="8"/>
-      <c r="V413" s="8"/>
-      <c r="W413" s="8"/>
     </row>
     <row r="414" spans="1:23" ht="15" customHeight="1">
-      <c r="A414" s="8">
+      <c r="A414">
         <v>444</v>
       </c>
       <c r="B414" s="1">
@@ -17405,32 +17318,26 @@
         <v>264</v>
       </c>
       <c r="F414" s="7"/>
-      <c r="G414" s="9">
+      <c r="G414" s="6">
         <v>38136</v>
       </c>
       <c r="H414" s="2" t="s">
         <v>288</v>
       </c>
       <c r="I414" s="2"/>
-      <c r="J414" s="8"/>
       <c r="K414" s="2"/>
       <c r="L414" s="4"/>
       <c r="M414" s="2"/>
       <c r="N414" s="2"/>
       <c r="O414" s="2"/>
       <c r="P414" s="2"/>
-      <c r="Q414" s="8"/>
       <c r="R414" s="2"/>
-      <c r="S414" s="8"/>
-      <c r="T414" s="8"/>
-      <c r="U414" s="8"/>
-      <c r="V414" s="8" t="s">
+      <c r="V414" t="s">
         <v>668</v>
       </c>
-      <c r="W414" s="8"/>
     </row>
     <row r="415" spans="1:23" ht="15" customHeight="1">
-      <c r="A415" s="8">
+      <c r="A415">
         <v>445</v>
       </c>
       <c r="B415" s="1">
@@ -17446,14 +17353,13 @@
         <v>652</v>
       </c>
       <c r="F415" s="7"/>
-      <c r="G415" s="9">
+      <c r="G415" s="6">
         <v>38792</v>
       </c>
       <c r="H415" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I415" s="2"/>
-      <c r="J415" s="8"/>
       <c r="K415" s="2"/>
       <c r="L415" s="4"/>
       <c r="M415" s="2"/>
@@ -17462,16 +17368,10 @@
       <c r="P415" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="Q415" s="8"/>
       <c r="R415" s="2"/>
-      <c r="S415" s="8"/>
-      <c r="T415" s="8"/>
-      <c r="U415" s="8"/>
-      <c r="V415" s="8"/>
-      <c r="W415" s="8"/>
     </row>
     <row r="416" spans="1:23" ht="15" customHeight="1">
-      <c r="A416" s="8">
+      <c r="A416">
         <v>446</v>
       </c>
       <c r="B416" s="1">
@@ -17487,32 +17387,26 @@
         <v>264</v>
       </c>
       <c r="F416" s="7"/>
-      <c r="G416" s="9">
+      <c r="G416" s="6">
         <v>38136</v>
       </c>
       <c r="H416" s="2" t="s">
         <v>290</v>
       </c>
       <c r="I416" s="2"/>
-      <c r="J416" s="8"/>
       <c r="K416" s="2"/>
       <c r="L416" s="4"/>
       <c r="M416" s="2"/>
       <c r="N416" s="2"/>
       <c r="O416" s="2"/>
       <c r="P416" s="2"/>
-      <c r="Q416" s="8"/>
       <c r="R416" s="2"/>
-      <c r="S416" s="8"/>
-      <c r="T416" s="8"/>
-      <c r="U416" s="8"/>
-      <c r="V416" s="8"/>
-      <c r="W416" s="8" t="s">
+      <c r="W416" t="s">
         <v>670</v>
       </c>
     </row>
     <row r="417" spans="1:23" ht="15" customHeight="1">
-      <c r="A417" s="8">
+      <c r="A417">
         <v>447</v>
       </c>
       <c r="B417" s="1">
@@ -17528,7 +17422,7 @@
         <v>666</v>
       </c>
       <c r="F417" s="7"/>
-      <c r="G417" s="9">
+      <c r="G417" s="6">
         <v>38205</v>
       </c>
       <c r="H417" s="2" t="s">
@@ -17537,23 +17431,16 @@
       <c r="I417" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="J417" s="8"/>
       <c r="K417" s="2"/>
       <c r="L417" s="4"/>
       <c r="M417" s="2"/>
       <c r="N417" s="2"/>
       <c r="O417" s="2"/>
       <c r="P417" s="2"/>
-      <c r="Q417" s="8"/>
       <c r="R417" s="2"/>
-      <c r="S417" s="8"/>
-      <c r="T417" s="8"/>
-      <c r="U417" s="8"/>
-      <c r="V417" s="8"/>
-      <c r="W417" s="8"/>
     </row>
     <row r="418" spans="1:23" ht="15" customHeight="1">
-      <c r="A418" s="8">
+      <c r="A418">
         <v>448</v>
       </c>
       <c r="B418" s="1">
@@ -17569,14 +17456,13 @@
         <v>652</v>
       </c>
       <c r="F418" s="7"/>
-      <c r="G418" s="9">
+      <c r="G418" s="6">
         <v>38792</v>
       </c>
       <c r="H418" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I418" s="2"/>
-      <c r="J418" s="8"/>
       <c r="K418" s="2"/>
       <c r="L418" s="4"/>
       <c r="M418" s="2"/>
@@ -17585,16 +17471,10 @@
       </c>
       <c r="O418" s="2"/>
       <c r="P418" s="2"/>
-      <c r="Q418" s="8"/>
       <c r="R418" s="2"/>
-      <c r="S418" s="8"/>
-      <c r="T418" s="8"/>
-      <c r="U418" s="8"/>
-      <c r="V418" s="8"/>
-      <c r="W418" s="8"/>
     </row>
     <row r="419" spans="1:23" ht="15" customHeight="1">
-      <c r="A419" s="8">
+      <c r="A419">
         <v>449</v>
       </c>
       <c r="B419" s="1">
@@ -17610,32 +17490,25 @@
         <v>652</v>
       </c>
       <c r="F419" s="7"/>
-      <c r="G419" s="9">
+      <c r="G419" s="6">
         <v>38792</v>
       </c>
       <c r="H419" s="2" t="s">
         <v>43</v>
       </c>
       <c r="I419" s="2"/>
-      <c r="J419" s="8"/>
       <c r="K419" s="2"/>
       <c r="L419" s="4"/>
       <c r="M419" s="2"/>
       <c r="N419" s="2"/>
       <c r="O419" s="2"/>
       <c r="P419" s="2"/>
-      <c r="Q419" s="8"/>
       <c r="R419" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="S419" s="8"/>
-      <c r="T419" s="8"/>
-      <c r="U419" s="8"/>
-      <c r="V419" s="8"/>
-      <c r="W419" s="8"/>
     </row>
     <row r="420" spans="1:23" ht="15" customHeight="1">
-      <c r="A420" s="8">
+      <c r="A420">
         <v>450</v>
       </c>
       <c r="B420" s="1">
@@ -17651,32 +17524,26 @@
         <v>652</v>
       </c>
       <c r="F420" s="7"/>
-      <c r="G420" s="9">
+      <c r="G420" s="6">
         <v>38792</v>
       </c>
       <c r="H420" s="2" t="s">
         <v>288</v>
       </c>
       <c r="I420" s="2"/>
-      <c r="J420" s="8"/>
       <c r="K420" s="2"/>
       <c r="L420" s="4"/>
       <c r="M420" s="2"/>
       <c r="N420" s="2"/>
       <c r="O420" s="2"/>
       <c r="P420" s="2"/>
-      <c r="Q420" s="8"/>
       <c r="R420" s="2"/>
-      <c r="S420" s="8"/>
-      <c r="T420" s="8"/>
-      <c r="U420" s="8"/>
-      <c r="V420" s="8" t="s">
+      <c r="V420" t="s">
         <v>674</v>
       </c>
-      <c r="W420" s="8"/>
     </row>
     <row r="421" spans="1:23" ht="15" customHeight="1">
-      <c r="A421" s="8">
+      <c r="A421">
         <v>451</v>
       </c>
       <c r="B421" s="1">
@@ -17692,7 +17559,7 @@
         <v>652</v>
       </c>
       <c r="F421" s="7"/>
-      <c r="G421" s="9">
+      <c r="G421" s="6">
         <v>38792</v>
       </c>
       <c r="H421" s="2" t="s">
@@ -17701,23 +17568,16 @@
       <c r="I421" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="J421" s="8"/>
       <c r="K421" s="2"/>
       <c r="L421" s="4"/>
       <c r="M421" s="2"/>
       <c r="N421" s="2"/>
       <c r="O421" s="2"/>
       <c r="P421" s="2"/>
-      <c r="Q421" s="8"/>
       <c r="R421" s="2"/>
-      <c r="S421" s="8"/>
-      <c r="T421" s="8"/>
-      <c r="U421" s="8"/>
-      <c r="V421" s="8"/>
-      <c r="W421" s="8"/>
     </row>
     <row r="422" spans="1:23" ht="15" customHeight="1">
-      <c r="A422" s="8">
+      <c r="A422">
         <v>452</v>
       </c>
       <c r="B422" s="1">
@@ -17733,7 +17593,7 @@
         <v>677</v>
       </c>
       <c r="F422" s="7"/>
-      <c r="G422" s="9">
+      <c r="G422" s="6">
         <v>43132</v>
       </c>
       <c r="H422" s="2" t="s">
@@ -17742,23 +17602,16 @@
       <c r="I422" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="J422" s="8"/>
       <c r="K422" s="2"/>
       <c r="L422" s="4"/>
       <c r="M422" s="2"/>
       <c r="N422" s="2"/>
       <c r="O422" s="2"/>
       <c r="P422" s="2"/>
-      <c r="Q422" s="8"/>
       <c r="R422" s="2"/>
-      <c r="S422" s="8"/>
-      <c r="T422" s="8"/>
-      <c r="U422" s="8"/>
-      <c r="V422" s="8"/>
-      <c r="W422" s="8"/>
     </row>
     <row r="423" spans="1:23" ht="15" customHeight="1">
-      <c r="A423" s="8">
+      <c r="A423">
         <v>453</v>
       </c>
       <c r="B423" s="1">
@@ -17774,14 +17627,13 @@
         <v>92</v>
       </c>
       <c r="F423" s="7"/>
-      <c r="G423" s="9">
+      <c r="G423" s="6">
         <v>38677</v>
       </c>
       <c r="H423" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I423" s="2"/>
-      <c r="J423" s="8"/>
       <c r="K423" s="2"/>
       <c r="L423" s="4" t="s">
         <v>679</v>
@@ -17790,16 +17642,10 @@
       <c r="N423" s="2"/>
       <c r="O423" s="2"/>
       <c r="P423" s="2"/>
-      <c r="Q423" s="8"/>
       <c r="R423" s="2"/>
-      <c r="S423" s="8"/>
-      <c r="T423" s="8"/>
-      <c r="U423" s="8"/>
-      <c r="V423" s="8"/>
-      <c r="W423" s="8"/>
     </row>
     <row r="424" spans="1:23" ht="15" customHeight="1">
-      <c r="A424" s="8">
+      <c r="A424">
         <v>454</v>
       </c>
       <c r="B424" s="1">
@@ -17815,14 +17661,13 @@
         <v>677</v>
       </c>
       <c r="F424" s="7"/>
-      <c r="G424" s="9">
+      <c r="G424" s="6">
         <v>43132</v>
       </c>
       <c r="H424" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I424" s="2"/>
-      <c r="J424" s="8"/>
       <c r="K424" s="2"/>
       <c r="L424" s="4" t="s">
         <v>680</v>
@@ -17831,16 +17676,10 @@
       <c r="N424" s="2"/>
       <c r="O424" s="2"/>
       <c r="P424" s="2"/>
-      <c r="Q424" s="8"/>
       <c r="R424" s="2"/>
-      <c r="S424" s="8"/>
-      <c r="T424" s="8"/>
-      <c r="U424" s="8"/>
-      <c r="V424" s="8"/>
-      <c r="W424" s="8"/>
     </row>
     <row r="425" spans="1:23" ht="15" customHeight="1">
-      <c r="A425" s="8">
+      <c r="A425">
         <v>455</v>
       </c>
       <c r="B425" s="1">
@@ -17856,7 +17695,7 @@
         <v>407</v>
       </c>
       <c r="F425" s="7"/>
-      <c r="G425" s="9">
+      <c r="G425" s="6">
         <v>38661</v>
       </c>
       <c r="H425" s="2" t="s">
@@ -17865,23 +17704,16 @@
       <c r="I425" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="J425" s="8"/>
       <c r="K425" s="2"/>
       <c r="L425" s="4"/>
       <c r="M425" s="2"/>
       <c r="N425" s="2"/>
       <c r="O425" s="2"/>
       <c r="P425" s="2"/>
-      <c r="Q425" s="8"/>
       <c r="R425" s="2"/>
-      <c r="S425" s="8"/>
-      <c r="T425" s="8"/>
-      <c r="U425" s="8"/>
-      <c r="V425" s="8"/>
-      <c r="W425" s="8"/>
     </row>
     <row r="426" spans="1:23" ht="15" customHeight="1">
-      <c r="A426" s="8">
+      <c r="A426">
         <v>456</v>
       </c>
       <c r="B426" s="1">
@@ -17897,14 +17729,13 @@
         <v>385</v>
       </c>
       <c r="F426" s="7"/>
-      <c r="G426" s="9">
+      <c r="G426" s="6">
         <v>38651</v>
       </c>
       <c r="H426" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I426" s="2"/>
-      <c r="J426" s="8"/>
       <c r="K426" s="2"/>
       <c r="L426" s="4" t="s">
         <v>682</v>
@@ -17913,13 +17744,321 @@
       <c r="N426" s="2"/>
       <c r="O426" s="2"/>
       <c r="P426" s="2"/>
-      <c r="Q426" s="8"/>
       <c r="R426" s="2"/>
-      <c r="S426" s="8"/>
-      <c r="T426" s="8"/>
-      <c r="U426" s="8"/>
-      <c r="V426" s="8"/>
-      <c r="W426" s="8"/>
+    </row>
+    <row r="427" spans="1:23" ht="15" customHeight="1">
+      <c r="A427">
+        <v>457</v>
+      </c>
+      <c r="B427" s="1">
+        <v>46272.466435185197</v>
+      </c>
+      <c r="C427" s="1">
+        <v>46272.466944444401</v>
+      </c>
+      <c r="D427" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E427" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F427" s="7"/>
+      <c r="G427" s="6">
+        <v>38651</v>
+      </c>
+      <c r="H427" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I427" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="K427" s="2"/>
+      <c r="L427" s="4"/>
+      <c r="M427" s="2"/>
+      <c r="N427" s="2"/>
+      <c r="O427" s="2"/>
+      <c r="P427" s="2"/>
+      <c r="R427" s="2"/>
+    </row>
+    <row r="428" spans="1:23" ht="15" customHeight="1">
+      <c r="A428">
+        <v>458</v>
+      </c>
+      <c r="B428" s="1">
+        <v>46272.471319444398</v>
+      </c>
+      <c r="C428" s="1">
+        <v>46272.472060185202</v>
+      </c>
+      <c r="D428" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E428" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F428" s="7"/>
+      <c r="G428" s="6">
+        <v>38527</v>
+      </c>
+      <c r="H428" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I428" s="2"/>
+      <c r="K428" s="2"/>
+      <c r="L428" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="M428" s="2"/>
+      <c r="N428" s="2"/>
+      <c r="O428" s="2"/>
+      <c r="P428" s="2"/>
+      <c r="R428" s="2"/>
+    </row>
+    <row r="429" spans="1:23" ht="15" customHeight="1">
+      <c r="A429" s="8">
+        <v>459</v>
+      </c>
+      <c r="B429" s="1">
+        <v>46272.472175925897</v>
+      </c>
+      <c r="C429" s="1">
+        <v>46272.473738425899</v>
+      </c>
+      <c r="D429" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E429" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F429" s="7"/>
+      <c r="G429" s="9">
+        <v>38527</v>
+      </c>
+      <c r="H429" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I429" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="J429" s="8"/>
+      <c r="K429" s="2"/>
+      <c r="L429" s="4"/>
+      <c r="M429" s="2"/>
+      <c r="N429" s="2"/>
+      <c r="O429" s="2"/>
+      <c r="P429" s="2"/>
+      <c r="Q429" s="8"/>
+      <c r="R429" s="2"/>
+      <c r="S429" s="8"/>
+      <c r="T429" s="8"/>
+      <c r="U429" s="8"/>
+      <c r="V429" s="8"/>
+      <c r="W429" s="8"/>
+    </row>
+    <row r="430" spans="1:23" ht="15" customHeight="1">
+      <c r="A430" s="8">
+        <v>460</v>
+      </c>
+      <c r="B430" s="1">
+        <v>46272.459247685198</v>
+      </c>
+      <c r="C430" s="1">
+        <v>46272.474780092598</v>
+      </c>
+      <c r="D430" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="E430" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="F430" s="7"/>
+      <c r="G430" s="9">
+        <v>43195</v>
+      </c>
+      <c r="H430" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I430" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="J430" s="8"/>
+      <c r="K430" s="2"/>
+      <c r="L430" s="4"/>
+      <c r="M430" s="2"/>
+      <c r="N430" s="2"/>
+      <c r="O430" s="2"/>
+      <c r="P430" s="2"/>
+      <c r="Q430" s="8"/>
+      <c r="R430" s="2"/>
+      <c r="S430" s="8"/>
+      <c r="T430" s="8"/>
+      <c r="U430" s="8"/>
+      <c r="V430" s="8"/>
+      <c r="W430" s="8"/>
+    </row>
+    <row r="431" spans="1:23" ht="15" customHeight="1">
+      <c r="A431" s="8">
+        <v>461</v>
+      </c>
+      <c r="B431" s="1">
+        <v>46272.475613425901</v>
+      </c>
+      <c r="C431" s="1">
+        <v>46272.4786805556</v>
+      </c>
+      <c r="D431" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E431" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F431" s="7"/>
+      <c r="G431" s="9">
+        <v>38186</v>
+      </c>
+      <c r="H431" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I431" s="2"/>
+      <c r="J431" s="8"/>
+      <c r="K431" s="2"/>
+      <c r="L431" s="4"/>
+      <c r="M431" s="2"/>
+      <c r="N431" s="2"/>
+      <c r="O431" s="2"/>
+      <c r="P431" s="2"/>
+      <c r="Q431" s="8"/>
+      <c r="R431" s="2"/>
+      <c r="S431" s="8"/>
+      <c r="T431" s="8"/>
+      <c r="U431" s="8"/>
+      <c r="V431" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="W431" s="8"/>
+    </row>
+    <row r="432" spans="1:23" ht="15" customHeight="1">
+      <c r="A432" s="8">
+        <v>462</v>
+      </c>
+      <c r="B432" s="1">
+        <v>46272.475925925901</v>
+      </c>
+      <c r="C432" s="1">
+        <v>46272.482326388897</v>
+      </c>
+      <c r="D432" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="E432" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="F432" s="7"/>
+      <c r="G432" s="9">
+        <v>43111</v>
+      </c>
+      <c r="H432" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I432" s="2"/>
+      <c r="J432" s="8"/>
+      <c r="K432" s="2"/>
+      <c r="L432" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="M432" s="2"/>
+      <c r="N432" s="2"/>
+      <c r="O432" s="2"/>
+      <c r="P432" s="2"/>
+      <c r="Q432" s="8"/>
+      <c r="R432" s="2"/>
+      <c r="S432" s="8"/>
+      <c r="T432" s="8"/>
+      <c r="U432" s="8"/>
+      <c r="V432" s="8"/>
+      <c r="W432" s="8"/>
+    </row>
+    <row r="433" spans="1:23" ht="15" customHeight="1">
+      <c r="A433" s="8">
+        <v>463</v>
+      </c>
+      <c r="B433" s="1">
+        <v>46272.481539351902</v>
+      </c>
+      <c r="C433" s="1">
+        <v>46272.4827083333</v>
+      </c>
+      <c r="D433" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E433" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F433" s="7"/>
+      <c r="G433" s="9">
+        <v>38186</v>
+      </c>
+      <c r="H433" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I433" s="2"/>
+      <c r="J433" s="8"/>
+      <c r="K433" s="2"/>
+      <c r="L433" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="M433" s="2"/>
+      <c r="N433" s="2"/>
+      <c r="O433" s="2"/>
+      <c r="P433" s="2"/>
+      <c r="Q433" s="8"/>
+      <c r="R433" s="2"/>
+      <c r="S433" s="8"/>
+      <c r="T433" s="8"/>
+      <c r="U433" s="8"/>
+      <c r="V433" s="8"/>
+      <c r="W433" s="8"/>
+    </row>
+    <row r="434" spans="1:23" ht="15" customHeight="1">
+      <c r="A434" s="8">
+        <v>464</v>
+      </c>
+      <c r="B434" s="1">
+        <v>46272.483553240701</v>
+      </c>
+      <c r="C434" s="1">
+        <v>46272.483738425901</v>
+      </c>
+      <c r="D434" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E434" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F434" s="7"/>
+      <c r="G434" s="9">
+        <v>38186</v>
+      </c>
+      <c r="H434" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I434" s="2"/>
+      <c r="J434" s="8"/>
+      <c r="K434" s="2"/>
+      <c r="L434" s="4"/>
+      <c r="M434" s="2"/>
+      <c r="N434" s="2"/>
+      <c r="O434" s="2"/>
+      <c r="P434" s="2"/>
+      <c r="Q434" s="8"/>
+      <c r="R434" s="2"/>
+      <c r="S434" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="T434" s="8"/>
+      <c r="U434" s="8"/>
+      <c r="V434" s="8"/>
+      <c r="W434" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76BAB7DB-A6E2-48AD-9C69-A6229C2CEC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="608" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0EC43F5-6605-44A4-BFF2-3DC9549AD0D2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="712">
   <si>
     <t>Id</t>
   </si>
@@ -2124,6 +2124,54 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Arboledas.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/WhatsApp%20Image%202026-09-07%20at%2011.38.52%20AM_David%20Zaragoza%20Diaz.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38837@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Centenario Azcapotzalco</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/26e50d2b-ae8b-4195-a827-57d5de82afc1_Starbucks%20Centenario.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17888034243178221132431890749495_Starbucks%20ITESM%20Esta.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_4146_Starbucks%20Centenario.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/17888034809164712871293404843376_Starbucks%20ITESM%20Esta.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17888035142947337509447204271497_Starbucks%20ITESM%20Esta.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/IMG20260907115346_Starbucks%20ITESM%20Esta.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/17888037540311615881938190252673_Starbucks%20ITESM%20Esta.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/20260907_102933-COLLAGE_Starbucks%20Bellavista.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17888038421675296352950727748968_Starbucks%20Bellavista.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_8339_Eduardo%20David%20Reyes.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_8583_Eduardo%20David%20Reyes.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_7767_Hector%20Ruben%20Estevez.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/27D9EAC8-E700-4193-96B3-490F9E06F2D4_Hector%20Ruben%20Estevez.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2276,8 +2324,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W434" totalsRowShown="0">
-  <autoFilter ref="A1:W434" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W448" totalsRowShown="0">
+  <autoFilter ref="A1:W448" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2444,7 +2492,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="464" latestEventMarker="731">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="478" latestEventMarker="745">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2773,7 +2821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W434"/>
+  <dimension ref="A1:W448"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -18060,6 +18108,580 @@
       <c r="V434" s="8"/>
       <c r="W434" s="8"/>
     </row>
+    <row r="435" spans="1:23" ht="15" customHeight="1">
+      <c r="A435" s="8">
+        <v>465</v>
+      </c>
+      <c r="B435" s="1">
+        <v>46272.483761574098</v>
+      </c>
+      <c r="C435" s="1">
+        <v>46272.486122685201</v>
+      </c>
+      <c r="D435" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="E435" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="F435" s="7"/>
+      <c r="G435" s="9">
+        <v>43111</v>
+      </c>
+      <c r="H435" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I435" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="J435" s="8"/>
+      <c r="K435" s="2"/>
+      <c r="L435" s="4"/>
+      <c r="M435" s="2"/>
+      <c r="N435" s="2"/>
+      <c r="O435" s="2"/>
+      <c r="P435" s="2"/>
+      <c r="Q435" s="8"/>
+      <c r="R435" s="2"/>
+      <c r="S435" s="8"/>
+      <c r="T435" s="8"/>
+      <c r="U435" s="8"/>
+      <c r="V435" s="8"/>
+      <c r="W435" s="8"/>
+    </row>
+    <row r="436" spans="1:23" ht="15" customHeight="1">
+      <c r="A436" s="8">
+        <v>466</v>
+      </c>
+      <c r="B436" s="1">
+        <v>46272.492002314801</v>
+      </c>
+      <c r="C436" s="1">
+        <v>46272.493182870399</v>
+      </c>
+      <c r="D436" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="E436" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="F436" s="7"/>
+      <c r="G436" s="9">
+        <v>38837</v>
+      </c>
+      <c r="H436" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I436" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="J436" s="8"/>
+      <c r="K436" s="2"/>
+      <c r="L436" s="4"/>
+      <c r="M436" s="2"/>
+      <c r="N436" s="2"/>
+      <c r="O436" s="2"/>
+      <c r="P436" s="2"/>
+      <c r="Q436" s="8"/>
+      <c r="R436" s="2"/>
+      <c r="S436" s="8"/>
+      <c r="T436" s="8"/>
+      <c r="U436" s="8"/>
+      <c r="V436" s="8"/>
+      <c r="W436" s="8"/>
+    </row>
+    <row r="437" spans="1:23" ht="15" customHeight="1">
+      <c r="A437" s="8">
+        <v>467</v>
+      </c>
+      <c r="B437" s="1">
+        <v>46272.4930439815</v>
+      </c>
+      <c r="C437" s="1">
+        <v>46272.493726851899</v>
+      </c>
+      <c r="D437" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E437" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F437" s="7"/>
+      <c r="G437" s="9">
+        <v>38230</v>
+      </c>
+      <c r="H437" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I437" s="2"/>
+      <c r="J437" s="8"/>
+      <c r="K437" s="2"/>
+      <c r="L437" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="M437" s="2"/>
+      <c r="N437" s="2"/>
+      <c r="O437" s="2"/>
+      <c r="P437" s="2"/>
+      <c r="Q437" s="8"/>
+      <c r="R437" s="2"/>
+      <c r="S437" s="8"/>
+      <c r="T437" s="8"/>
+      <c r="U437" s="8"/>
+      <c r="V437" s="8"/>
+      <c r="W437" s="8"/>
+    </row>
+    <row r="438" spans="1:23" ht="15" customHeight="1">
+      <c r="A438" s="8">
+        <v>468</v>
+      </c>
+      <c r="B438" s="1">
+        <v>46272.493287037003</v>
+      </c>
+      <c r="C438" s="1">
+        <v>46272.494039351797</v>
+      </c>
+      <c r="D438" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="E438" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="F438" s="7"/>
+      <c r="G438" s="9">
+        <v>38837</v>
+      </c>
+      <c r="H438" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I438" s="2"/>
+      <c r="J438" s="8"/>
+      <c r="K438" s="2"/>
+      <c r="L438" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="M438" s="2"/>
+      <c r="N438" s="2"/>
+      <c r="O438" s="2"/>
+      <c r="P438" s="2"/>
+      <c r="Q438" s="8"/>
+      <c r="R438" s="2"/>
+      <c r="S438" s="8"/>
+      <c r="T438" s="8"/>
+      <c r="U438" s="8"/>
+      <c r="V438" s="8"/>
+      <c r="W438" s="8"/>
+    </row>
+    <row r="439" spans="1:23" ht="15" customHeight="1">
+      <c r="A439" s="8">
+        <v>469</v>
+      </c>
+      <c r="B439" s="1">
+        <v>46272.493796296301</v>
+      </c>
+      <c r="C439" s="1">
+        <v>46272.4941666667</v>
+      </c>
+      <c r="D439" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E439" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F439" s="7"/>
+      <c r="G439" s="9">
+        <v>38230</v>
+      </c>
+      <c r="H439" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I439" s="2"/>
+      <c r="J439" s="8"/>
+      <c r="K439" s="2"/>
+      <c r="L439" s="4"/>
+      <c r="M439" s="2"/>
+      <c r="N439" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="O439" s="2"/>
+      <c r="P439" s="2"/>
+      <c r="Q439" s="8"/>
+      <c r="R439" s="2"/>
+      <c r="S439" s="8"/>
+      <c r="T439" s="8"/>
+      <c r="U439" s="8"/>
+      <c r="V439" s="8"/>
+      <c r="W439" s="8"/>
+    </row>
+    <row r="440" spans="1:23" ht="15" customHeight="1">
+      <c r="A440" s="8">
+        <v>470</v>
+      </c>
+      <c r="B440" s="1">
+        <v>46272.494201388901</v>
+      </c>
+      <c r="C440" s="1">
+        <v>46272.494733796302</v>
+      </c>
+      <c r="D440" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E440" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F440" s="7"/>
+      <c r="G440" s="9">
+        <v>38230</v>
+      </c>
+      <c r="H440" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I440" s="2"/>
+      <c r="J440" s="8"/>
+      <c r="K440" s="2"/>
+      <c r="L440" s="4"/>
+      <c r="M440" s="2"/>
+      <c r="N440" s="2"/>
+      <c r="O440" s="2"/>
+      <c r="P440" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="Q440" s="8"/>
+      <c r="R440" s="2"/>
+      <c r="S440" s="8"/>
+      <c r="T440" s="8"/>
+      <c r="U440" s="8"/>
+      <c r="V440" s="8"/>
+      <c r="W440" s="8"/>
+    </row>
+    <row r="441" spans="1:23" ht="15" customHeight="1">
+      <c r="A441" s="8">
+        <v>471</v>
+      </c>
+      <c r="B441" s="1">
+        <v>46272.494768518503</v>
+      </c>
+      <c r="C441" s="1">
+        <v>46272.496793981503</v>
+      </c>
+      <c r="D441" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E441" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F441" s="7"/>
+      <c r="G441" s="9">
+        <v>38230</v>
+      </c>
+      <c r="H441" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I441" s="2"/>
+      <c r="J441" s="8"/>
+      <c r="K441" s="2"/>
+      <c r="L441" s="4"/>
+      <c r="M441" s="2"/>
+      <c r="N441" s="2"/>
+      <c r="O441" s="2"/>
+      <c r="P441" s="2"/>
+      <c r="Q441" s="8"/>
+      <c r="R441" s="2"/>
+      <c r="S441" s="8"/>
+      <c r="T441" s="8"/>
+      <c r="U441" s="8"/>
+      <c r="V441" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="W441" s="8"/>
+    </row>
+    <row r="442" spans="1:23" ht="15" customHeight="1">
+      <c r="A442" s="8">
+        <v>472</v>
+      </c>
+      <c r="B442" s="1">
+        <v>46272.496840277803</v>
+      </c>
+      <c r="C442" s="1">
+        <v>46272.497418981497</v>
+      </c>
+      <c r="D442" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E442" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F442" s="7"/>
+      <c r="G442" s="9">
+        <v>38230</v>
+      </c>
+      <c r="H442" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="I442" s="2"/>
+      <c r="J442" s="8"/>
+      <c r="K442" s="2"/>
+      <c r="L442" s="4"/>
+      <c r="M442" s="2"/>
+      <c r="N442" s="2"/>
+      <c r="O442" s="2"/>
+      <c r="P442" s="2"/>
+      <c r="Q442" s="8"/>
+      <c r="R442" s="2"/>
+      <c r="S442" s="8"/>
+      <c r="T442" s="8"/>
+      <c r="U442" s="8"/>
+      <c r="V442" s="8"/>
+      <c r="W442" s="8" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="443" spans="1:23" ht="15" customHeight="1">
+      <c r="A443" s="8">
+        <v>473</v>
+      </c>
+      <c r="B443" s="1">
+        <v>46272.496747685203</v>
+      </c>
+      <c r="C443" s="1">
+        <v>46272.497581018499</v>
+      </c>
+      <c r="D443" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E443" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F443" s="7"/>
+      <c r="G443" s="9">
+        <v>38149</v>
+      </c>
+      <c r="H443" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I443" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="J443" s="8"/>
+      <c r="K443" s="2"/>
+      <c r="L443" s="4"/>
+      <c r="M443" s="2"/>
+      <c r="N443" s="2"/>
+      <c r="O443" s="2"/>
+      <c r="P443" s="2"/>
+      <c r="Q443" s="8"/>
+      <c r="R443" s="2"/>
+      <c r="S443" s="8"/>
+      <c r="T443" s="8"/>
+      <c r="U443" s="8"/>
+      <c r="V443" s="8"/>
+      <c r="W443" s="8"/>
+    </row>
+    <row r="444" spans="1:23" ht="15" customHeight="1">
+      <c r="A444" s="8">
+        <v>474</v>
+      </c>
+      <c r="B444" s="1">
+        <v>46272.497766203698</v>
+      </c>
+      <c r="C444" s="1">
+        <v>46272.499675925901</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E444" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F444" s="7"/>
+      <c r="G444" s="9">
+        <v>38149</v>
+      </c>
+      <c r="H444" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I444" s="2"/>
+      <c r="J444" s="8"/>
+      <c r="K444" s="2"/>
+      <c r="L444" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="M444" s="2"/>
+      <c r="N444" s="2"/>
+      <c r="O444" s="2"/>
+      <c r="P444" s="2"/>
+      <c r="Q444" s="8"/>
+      <c r="R444" s="2"/>
+      <c r="S444" s="8"/>
+      <c r="T444" s="8"/>
+      <c r="U444" s="8"/>
+      <c r="V444" s="8"/>
+      <c r="W444" s="8"/>
+    </row>
+    <row r="445" spans="1:23" ht="15" customHeight="1">
+      <c r="A445" s="8">
+        <v>475</v>
+      </c>
+      <c r="B445" s="1">
+        <v>46272.499490740702</v>
+      </c>
+      <c r="C445" s="1">
+        <v>46272.500069444402</v>
+      </c>
+      <c r="D445" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E445" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F445" s="7"/>
+      <c r="G445" s="9">
+        <v>38507</v>
+      </c>
+      <c r="H445" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I445" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="J445" s="8"/>
+      <c r="K445" s="2"/>
+      <c r="L445" s="4"/>
+      <c r="M445" s="2"/>
+      <c r="N445" s="2"/>
+      <c r="O445" s="2"/>
+      <c r="P445" s="2"/>
+      <c r="Q445" s="8"/>
+      <c r="R445" s="2"/>
+      <c r="S445" s="8"/>
+      <c r="T445" s="8"/>
+      <c r="U445" s="8"/>
+      <c r="V445" s="8"/>
+      <c r="W445" s="8"/>
+    </row>
+    <row r="446" spans="1:23" ht="15" customHeight="1">
+      <c r="A446" s="8">
+        <v>476</v>
+      </c>
+      <c r="B446" s="1">
+        <v>46272.500173611101</v>
+      </c>
+      <c r="C446" s="1">
+        <v>46272.5004513889</v>
+      </c>
+      <c r="D446" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E446" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F446" s="7"/>
+      <c r="G446" s="9">
+        <v>38507</v>
+      </c>
+      <c r="H446" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I446" s="2"/>
+      <c r="J446" s="8"/>
+      <c r="K446" s="2"/>
+      <c r="L446" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="M446" s="2"/>
+      <c r="N446" s="2"/>
+      <c r="O446" s="2"/>
+      <c r="P446" s="2"/>
+      <c r="Q446" s="8"/>
+      <c r="R446" s="2"/>
+      <c r="S446" s="8"/>
+      <c r="T446" s="8"/>
+      <c r="U446" s="8"/>
+      <c r="V446" s="8"/>
+      <c r="W446" s="8"/>
+    </row>
+    <row r="447" spans="1:23" ht="15" customHeight="1">
+      <c r="A447" s="8">
+        <v>477</v>
+      </c>
+      <c r="B447" s="1">
+        <v>46272.4995023148</v>
+      </c>
+      <c r="C447" s="1">
+        <v>46272.500567129602</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E447" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F447" s="7"/>
+      <c r="G447" s="9">
+        <v>38142</v>
+      </c>
+      <c r="H447" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I447" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="J447" s="8"/>
+      <c r="K447" s="2"/>
+      <c r="L447" s="4"/>
+      <c r="M447" s="2"/>
+      <c r="N447" s="2"/>
+      <c r="O447" s="2"/>
+      <c r="P447" s="2"/>
+      <c r="Q447" s="8"/>
+      <c r="R447" s="2"/>
+      <c r="S447" s="8"/>
+      <c r="T447" s="8"/>
+      <c r="U447" s="8"/>
+      <c r="V447" s="8"/>
+      <c r="W447" s="8"/>
+    </row>
+    <row r="448" spans="1:23" ht="15" customHeight="1">
+      <c r="A448" s="8">
+        <v>478</v>
+      </c>
+      <c r="B448" s="1">
+        <v>46272.500914351898</v>
+      </c>
+      <c r="C448" s="1">
+        <v>46272.501377314802</v>
+      </c>
+      <c r="D448" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E448" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F448" s="7"/>
+      <c r="G448" s="9">
+        <v>38142</v>
+      </c>
+      <c r="H448" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I448" s="2"/>
+      <c r="J448" s="8"/>
+      <c r="K448" s="2"/>
+      <c r="L448" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="M448" s="2"/>
+      <c r="N448" s="2"/>
+      <c r="O448" s="2"/>
+      <c r="P448" s="2"/>
+      <c r="Q448" s="8"/>
+      <c r="R448" s="2"/>
+      <c r="S448" s="8"/>
+      <c r="T448" s="8"/>
+      <c r="U448" s="8"/>
+      <c r="V448" s="8"/>
+      <c r="W448" s="8"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="608" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0EC43F5-6605-44A4-BFF2-3DC9549AD0D2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F19671C4-D837-4B8C-964E-C2F536B3ADBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2297" uniqueCount="730">
   <si>
     <t>Id</t>
   </si>
@@ -2172,6 +2172,60 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/27D9EAC8-E700-4193-96B3-490F9E06F2D4_Hector%20Ruben%20Estevez.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Vanessa%20Carre%C3%B1o%20Rios%202.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_0885_Starbucks%20Atizapan.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_1296_Starbucks%20Atizapan.png</t>
+  </si>
+  <si>
+    <t>SBMX38207@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Parque Lindavista Kiosko</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/Screenshot_20260907_122505_Gallery_Starbucks%20Parque%20Lin.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_5666_Starbucks%20Atana%20Lind.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_2455_Starbucks%20Sor%20Juana.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Atana%20Lind.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_9130_Starbucks%20Plaza%20Loma.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/9282DEF8-CED4-4140-9462-86514489A73E_Starbucks%20Star%20Medic.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_0319_Starbucks%20Star%20Medic.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17888066110471268602420797512510_Kevin%20Arturo%20Suarez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/20260907_101257_Kevin%20Arturo%20Suarez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_9414_Starbucks%20Plaza%20Loma.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/70555_Juan%20Jose%20Santiago%20D.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/70558_Juan%20Jose%20Santiago%20D.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260907-WA0024_Starbucks%20CC%20Lomas%20V.jpg</t>
   </si>
 </sst>
 </file>
@@ -2324,8 +2378,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W448" totalsRowShown="0">
-  <autoFilter ref="A1:W448" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W464" totalsRowShown="0">
+  <autoFilter ref="A1:W464" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2492,7 +2546,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="478" latestEventMarker="745">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="494" latestEventMarker="761">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2821,7 +2875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W448"/>
+  <dimension ref="A1:W464"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -18682,6 +18736,662 @@
       <c r="V448" s="8"/>
       <c r="W448" s="8"/>
     </row>
+    <row r="449" spans="1:23" ht="15" customHeight="1">
+      <c r="A449" s="8">
+        <v>479</v>
+      </c>
+      <c r="B449" s="1">
+        <v>46272.505949074097</v>
+      </c>
+      <c r="C449" s="1">
+        <v>46272.506712962997</v>
+      </c>
+      <c r="D449" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E449" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F449" s="7"/>
+      <c r="G449" s="9">
+        <v>38677</v>
+      </c>
+      <c r="H449" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I449" s="2"/>
+      <c r="J449" s="8"/>
+      <c r="K449" s="2"/>
+      <c r="L449" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="M449" s="2"/>
+      <c r="N449" s="2"/>
+      <c r="O449" s="2"/>
+      <c r="P449" s="2"/>
+      <c r="Q449" s="8"/>
+      <c r="R449" s="2"/>
+      <c r="S449" s="8"/>
+      <c r="T449" s="8"/>
+      <c r="U449" s="8"/>
+      <c r="V449" s="8"/>
+      <c r="W449" s="8"/>
+    </row>
+    <row r="450" spans="1:23" ht="15" customHeight="1">
+      <c r="A450" s="8">
+        <v>480</v>
+      </c>
+      <c r="B450" s="1">
+        <v>46272.515046296299</v>
+      </c>
+      <c r="C450" s="1">
+        <v>46272.516226851803</v>
+      </c>
+      <c r="D450" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E450" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F450" s="7"/>
+      <c r="G450" s="9">
+        <v>43043</v>
+      </c>
+      <c r="H450" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I450" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="J450" s="8"/>
+      <c r="K450" s="2"/>
+      <c r="L450" s="4"/>
+      <c r="M450" s="2"/>
+      <c r="N450" s="2"/>
+      <c r="O450" s="2"/>
+      <c r="P450" s="2"/>
+      <c r="Q450" s="8"/>
+      <c r="R450" s="2"/>
+      <c r="S450" s="8"/>
+      <c r="T450" s="8"/>
+      <c r="U450" s="8"/>
+      <c r="V450" s="8"/>
+      <c r="W450" s="8"/>
+    </row>
+    <row r="451" spans="1:23" ht="15" customHeight="1">
+      <c r="A451" s="8">
+        <v>481</v>
+      </c>
+      <c r="B451" s="1">
+        <v>46272.517465277801</v>
+      </c>
+      <c r="C451" s="1">
+        <v>46272.517719907402</v>
+      </c>
+      <c r="D451" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E451" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F451" s="7"/>
+      <c r="G451" s="9">
+        <v>43043</v>
+      </c>
+      <c r="H451" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I451" s="2"/>
+      <c r="J451" s="8"/>
+      <c r="K451" s="2"/>
+      <c r="L451" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="M451" s="2"/>
+      <c r="N451" s="2"/>
+      <c r="O451" s="2"/>
+      <c r="P451" s="2"/>
+      <c r="Q451" s="8"/>
+      <c r="R451" s="2"/>
+      <c r="S451" s="8"/>
+      <c r="T451" s="8"/>
+      <c r="U451" s="8"/>
+      <c r="V451" s="8"/>
+      <c r="W451" s="8"/>
+    </row>
+    <row r="452" spans="1:23" ht="15" customHeight="1">
+      <c r="A452" s="8">
+        <v>482</v>
+      </c>
+      <c r="B452" s="1">
+        <v>46272.515787037002</v>
+      </c>
+      <c r="C452" s="1">
+        <v>46272.518032407403</v>
+      </c>
+      <c r="D452" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="E452" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="F452" s="7"/>
+      <c r="G452" s="9">
+        <v>38207</v>
+      </c>
+      <c r="H452" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I452" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="J452" s="8"/>
+      <c r="K452" s="2"/>
+      <c r="L452" s="4"/>
+      <c r="M452" s="2"/>
+      <c r="N452" s="2"/>
+      <c r="O452" s="2"/>
+      <c r="P452" s="2"/>
+      <c r="Q452" s="8"/>
+      <c r="R452" s="2"/>
+      <c r="S452" s="8"/>
+      <c r="T452" s="8"/>
+      <c r="U452" s="8"/>
+      <c r="V452" s="8"/>
+      <c r="W452" s="8"/>
+    </row>
+    <row r="453" spans="1:23" ht="15" customHeight="1">
+      <c r="A453" s="8">
+        <v>483</v>
+      </c>
+      <c r="B453" s="1">
+        <v>46272.519247685203</v>
+      </c>
+      <c r="C453" s="1">
+        <v>46272.521111111098</v>
+      </c>
+      <c r="D453" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E453" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F453" s="7"/>
+      <c r="G453" s="9">
+        <v>43194</v>
+      </c>
+      <c r="H453" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I453" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="J453" s="8"/>
+      <c r="K453" s="2"/>
+      <c r="L453" s="4"/>
+      <c r="M453" s="2"/>
+      <c r="N453" s="2"/>
+      <c r="O453" s="2"/>
+      <c r="P453" s="2"/>
+      <c r="Q453" s="8"/>
+      <c r="R453" s="2"/>
+      <c r="S453" s="8"/>
+      <c r="T453" s="8"/>
+      <c r="U453" s="8"/>
+      <c r="V453" s="8"/>
+      <c r="W453" s="8"/>
+    </row>
+    <row r="454" spans="1:23" ht="15" customHeight="1">
+      <c r="A454" s="8">
+        <v>484</v>
+      </c>
+      <c r="B454" s="1">
+        <v>46272.489050925898</v>
+      </c>
+      <c r="C454" s="1">
+        <v>46272.5218634259</v>
+      </c>
+      <c r="D454" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E454" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F454" s="7"/>
+      <c r="G454" s="9">
+        <v>38442</v>
+      </c>
+      <c r="H454" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I454" s="2"/>
+      <c r="J454" s="8"/>
+      <c r="K454" s="2"/>
+      <c r="L454" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="M454" s="2"/>
+      <c r="N454" s="2"/>
+      <c r="O454" s="2"/>
+      <c r="P454" s="2"/>
+      <c r="Q454" s="8"/>
+      <c r="R454" s="2"/>
+      <c r="S454" s="8"/>
+      <c r="T454" s="8"/>
+      <c r="U454" s="8"/>
+      <c r="V454" s="8"/>
+      <c r="W454" s="8"/>
+    </row>
+    <row r="455" spans="1:23" ht="15" customHeight="1">
+      <c r="A455" s="8">
+        <v>485</v>
+      </c>
+      <c r="B455" s="1">
+        <v>46272.5211921296</v>
+      </c>
+      <c r="C455" s="1">
+        <v>46272.5222685185</v>
+      </c>
+      <c r="D455" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E455" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F455" s="7"/>
+      <c r="G455" s="9">
+        <v>43194</v>
+      </c>
+      <c r="H455" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I455" s="2"/>
+      <c r="J455" s="8"/>
+      <c r="K455" s="2"/>
+      <c r="L455" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="M455" s="2"/>
+      <c r="N455" s="2"/>
+      <c r="O455" s="2"/>
+      <c r="P455" s="2"/>
+      <c r="Q455" s="8"/>
+      <c r="R455" s="2"/>
+      <c r="S455" s="8"/>
+      <c r="T455" s="8"/>
+      <c r="U455" s="8"/>
+      <c r="V455" s="8"/>
+      <c r="W455" s="8"/>
+    </row>
+    <row r="456" spans="1:23" ht="15" customHeight="1">
+      <c r="A456" s="8">
+        <v>486</v>
+      </c>
+      <c r="B456" s="1">
+        <v>46272.518773148098</v>
+      </c>
+      <c r="C456" s="1">
+        <v>46272.527546296304</v>
+      </c>
+      <c r="D456" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E456" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F456" s="7"/>
+      <c r="G456" s="9">
+        <v>38270</v>
+      </c>
+      <c r="H456" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I456" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="J456" s="8"/>
+      <c r="K456" s="2"/>
+      <c r="L456" s="4"/>
+      <c r="M456" s="2"/>
+      <c r="N456" s="2"/>
+      <c r="O456" s="2"/>
+      <c r="P456" s="2"/>
+      <c r="Q456" s="8"/>
+      <c r="R456" s="2"/>
+      <c r="S456" s="8"/>
+      <c r="T456" s="8"/>
+      <c r="U456" s="8"/>
+      <c r="V456" s="8"/>
+      <c r="W456" s="8"/>
+    </row>
+    <row r="457" spans="1:23" ht="15" customHeight="1">
+      <c r="A457" s="8">
+        <v>487</v>
+      </c>
+      <c r="B457" s="1">
+        <v>46272.527175925898</v>
+      </c>
+      <c r="C457" s="1">
+        <v>46272.527557870402</v>
+      </c>
+      <c r="D457" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E457" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F457" s="7"/>
+      <c r="G457" s="9">
+        <v>38925</v>
+      </c>
+      <c r="H457" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I457" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="J457" s="8"/>
+      <c r="K457" s="2"/>
+      <c r="L457" s="4"/>
+      <c r="M457" s="2"/>
+      <c r="N457" s="2"/>
+      <c r="O457" s="2"/>
+      <c r="P457" s="2"/>
+      <c r="Q457" s="8"/>
+      <c r="R457" s="2"/>
+      <c r="S457" s="8"/>
+      <c r="T457" s="8"/>
+      <c r="U457" s="8"/>
+      <c r="V457" s="8"/>
+      <c r="W457" s="8"/>
+    </row>
+    <row r="458" spans="1:23" ht="15" customHeight="1">
+      <c r="A458" s="8">
+        <v>488</v>
+      </c>
+      <c r="B458" s="1">
+        <v>46272.528333333299</v>
+      </c>
+      <c r="C458" s="1">
+        <v>46272.530115740701</v>
+      </c>
+      <c r="D458" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E458" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F458" s="7"/>
+      <c r="G458" s="9">
+        <v>38925</v>
+      </c>
+      <c r="H458" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I458" s="2"/>
+      <c r="J458" s="8"/>
+      <c r="K458" s="2"/>
+      <c r="L458" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="M458" s="2"/>
+      <c r="N458" s="2"/>
+      <c r="O458" s="2"/>
+      <c r="P458" s="2"/>
+      <c r="Q458" s="8"/>
+      <c r="R458" s="2"/>
+      <c r="S458" s="8"/>
+      <c r="T458" s="8"/>
+      <c r="U458" s="8"/>
+      <c r="V458" s="8"/>
+      <c r="W458" s="8"/>
+    </row>
+    <row r="459" spans="1:23" ht="15" customHeight="1">
+      <c r="A459" s="8">
+        <v>489</v>
+      </c>
+      <c r="B459" s="1">
+        <v>46272.529965277798</v>
+      </c>
+      <c r="C459" s="1">
+        <v>46272.531064814801</v>
+      </c>
+      <c r="D459" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E459" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F459" s="7"/>
+      <c r="G459" s="9">
+        <v>43130</v>
+      </c>
+      <c r="H459" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I459" s="2"/>
+      <c r="J459" s="8"/>
+      <c r="K459" s="2"/>
+      <c r="L459" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="M459" s="2"/>
+      <c r="N459" s="2"/>
+      <c r="O459" s="2"/>
+      <c r="P459" s="2"/>
+      <c r="Q459" s="8"/>
+      <c r="R459" s="2"/>
+      <c r="S459" s="8"/>
+      <c r="T459" s="8"/>
+      <c r="U459" s="8"/>
+      <c r="V459" s="8"/>
+      <c r="W459" s="8"/>
+    </row>
+    <row r="460" spans="1:23" ht="15" customHeight="1">
+      <c r="A460" s="8">
+        <v>490</v>
+      </c>
+      <c r="B460" s="1">
+        <v>46272.532141203701</v>
+      </c>
+      <c r="C460" s="1">
+        <v>46272.5325115741</v>
+      </c>
+      <c r="D460" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E460" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F460" s="7"/>
+      <c r="G460" s="9">
+        <v>43130</v>
+      </c>
+      <c r="H460" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I460" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="J460" s="8"/>
+      <c r="K460" s="2"/>
+      <c r="L460" s="4"/>
+      <c r="M460" s="2"/>
+      <c r="N460" s="2"/>
+      <c r="O460" s="2"/>
+      <c r="P460" s="2"/>
+      <c r="Q460" s="8"/>
+      <c r="R460" s="2"/>
+      <c r="S460" s="8"/>
+      <c r="T460" s="8"/>
+      <c r="U460" s="8"/>
+      <c r="V460" s="8"/>
+      <c r="W460" s="8"/>
+    </row>
+    <row r="461" spans="1:23" ht="15" customHeight="1">
+      <c r="A461" s="8">
+        <v>491</v>
+      </c>
+      <c r="B461" s="1">
+        <v>46272.532349537003</v>
+      </c>
+      <c r="C461" s="1">
+        <v>46272.532754629603</v>
+      </c>
+      <c r="D461" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E461" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F461" s="7"/>
+      <c r="G461" s="9">
+        <v>38270</v>
+      </c>
+      <c r="H461" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I461" s="2"/>
+      <c r="J461" s="8"/>
+      <c r="K461" s="2"/>
+      <c r="L461" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="M461" s="2"/>
+      <c r="N461" s="2"/>
+      <c r="O461" s="2"/>
+      <c r="P461" s="2"/>
+      <c r="Q461" s="8"/>
+      <c r="R461" s="2"/>
+      <c r="S461" s="8"/>
+      <c r="T461" s="8"/>
+      <c r="U461" s="8"/>
+      <c r="V461" s="8"/>
+      <c r="W461" s="8"/>
+    </row>
+    <row r="462" spans="1:23" ht="15" customHeight="1">
+      <c r="A462" s="8">
+        <v>492</v>
+      </c>
+      <c r="B462" s="1">
+        <v>46272.533981481502</v>
+      </c>
+      <c r="C462" s="1">
+        <v>46272.535856481503</v>
+      </c>
+      <c r="D462" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E462" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F462" s="7"/>
+      <c r="G462" s="9">
+        <v>38119</v>
+      </c>
+      <c r="H462" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I462" s="2"/>
+      <c r="J462" s="8"/>
+      <c r="K462" s="2"/>
+      <c r="L462" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="M462" s="2"/>
+      <c r="N462" s="2"/>
+      <c r="O462" s="2"/>
+      <c r="P462" s="2"/>
+      <c r="Q462" s="8"/>
+      <c r="R462" s="2"/>
+      <c r="S462" s="8"/>
+      <c r="T462" s="8"/>
+      <c r="U462" s="8"/>
+      <c r="V462" s="8"/>
+      <c r="W462" s="8"/>
+    </row>
+    <row r="463" spans="1:23" ht="15" customHeight="1">
+      <c r="A463" s="8">
+        <v>493</v>
+      </c>
+      <c r="B463" s="1">
+        <v>46272.538506944402</v>
+      </c>
+      <c r="C463" s="1">
+        <v>46272.538773148102</v>
+      </c>
+      <c r="D463" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E463" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F463" s="7"/>
+      <c r="G463" s="9">
+        <v>38119</v>
+      </c>
+      <c r="H463" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I463" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="J463" s="8"/>
+      <c r="K463" s="2"/>
+      <c r="L463" s="4"/>
+      <c r="M463" s="2"/>
+      <c r="N463" s="2"/>
+      <c r="O463" s="2"/>
+      <c r="P463" s="2"/>
+      <c r="Q463" s="8"/>
+      <c r="R463" s="2"/>
+      <c r="S463" s="8"/>
+      <c r="T463" s="8"/>
+      <c r="U463" s="8"/>
+      <c r="V463" s="8"/>
+      <c r="W463" s="8"/>
+    </row>
+    <row r="464" spans="1:23" ht="15" customHeight="1">
+      <c r="A464" s="8">
+        <v>494</v>
+      </c>
+      <c r="B464" s="1">
+        <v>46272.529965277798</v>
+      </c>
+      <c r="C464" s="1">
+        <v>46272.539085648197</v>
+      </c>
+      <c r="D464" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E464" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F464" s="7"/>
+      <c r="G464" s="9">
+        <v>38394</v>
+      </c>
+      <c r="H464" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I464" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="J464" s="8"/>
+      <c r="K464" s="2"/>
+      <c r="L464" s="4"/>
+      <c r="M464" s="2"/>
+      <c r="N464" s="2"/>
+      <c r="O464" s="2"/>
+      <c r="P464" s="2"/>
+      <c r="Q464" s="8"/>
+      <c r="R464" s="2"/>
+      <c r="S464" s="8"/>
+      <c r="T464" s="8"/>
+      <c r="U464" s="8"/>
+      <c r="V464" s="8"/>
+      <c r="W464" s="8"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F19671C4-D837-4B8C-964E-C2F536B3ADBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAAD6A8C-1303-48C4-8B08-BD31FE5E10B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2297" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2345" uniqueCount="746">
   <si>
     <t>Id</t>
   </si>
@@ -2226,6 +2226,54 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260907-WA0024_Starbucks%20CC%20Lomas%20V.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38371@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Montevideo</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Montevideo.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_0927_Starbucks%20Montevideo.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/478850BE-4A10-4AC6-843D-2F2B72EB6F2E_Starbucks%20San%20Mateo.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_9501_Starbucks%20San%20Mateo.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17888084952872226994173080450649_Starbucks%20CC%20Lomas%20V.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/90ba097c-017e-4201-b1f9-d425427041e7_Starbucks%20Zona%20Azul.JPG</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_6080_Starbucks%20Zona%20Azul.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17888088383147887170538297263886_Starbucks%20CC%20Lomas%20V.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38546@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Patio Claveria</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/image_Starbucks%20Patio%20Clav.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17888088882043603573908946577854_Carlos%20Cortes%20Aguila.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Patio%20Clav.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG-20260907-WA0082_Carlos%20Cortes%20Aguila.jpg</t>
   </si>
 </sst>
 </file>
@@ -2271,7 +2319,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2284,10 +2332,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2378,8 +2422,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W464" totalsRowShown="0">
-  <autoFilter ref="A1:W464" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W476" totalsRowShown="0">
+  <autoFilter ref="A1:W476" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -2546,7 +2590,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="494" latestEventMarker="761">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="506" latestEventMarker="773">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2875,7 +2919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W464"/>
+  <dimension ref="A1:W476"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -17507,7 +17551,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="417" spans="1:23" ht="15" customHeight="1">
+    <row r="417" spans="1:22" ht="15" customHeight="1">
       <c r="A417">
         <v>447</v>
       </c>
@@ -17541,7 +17585,7 @@
       <c r="P417" s="2"/>
       <c r="R417" s="2"/>
     </row>
-    <row r="418" spans="1:23" ht="15" customHeight="1">
+    <row r="418" spans="1:22" ht="15" customHeight="1">
       <c r="A418">
         <v>448</v>
       </c>
@@ -17575,7 +17619,7 @@
       <c r="P418" s="2"/>
       <c r="R418" s="2"/>
     </row>
-    <row r="419" spans="1:23" ht="15" customHeight="1">
+    <row r="419" spans="1:22" ht="15" customHeight="1">
       <c r="A419">
         <v>449</v>
       </c>
@@ -17609,7 +17653,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="420" spans="1:23" ht="15" customHeight="1">
+    <row r="420" spans="1:22" ht="15" customHeight="1">
       <c r="A420">
         <v>450</v>
       </c>
@@ -17644,7 +17688,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="421" spans="1:23" ht="15" customHeight="1">
+    <row r="421" spans="1:22" ht="15" customHeight="1">
       <c r="A421">
         <v>451</v>
       </c>
@@ -17678,7 +17722,7 @@
       <c r="P421" s="2"/>
       <c r="R421" s="2"/>
     </row>
-    <row r="422" spans="1:23" ht="15" customHeight="1">
+    <row r="422" spans="1:22" ht="15" customHeight="1">
       <c r="A422">
         <v>452</v>
       </c>
@@ -17712,7 +17756,7 @@
       <c r="P422" s="2"/>
       <c r="R422" s="2"/>
     </row>
-    <row r="423" spans="1:23" ht="15" customHeight="1">
+    <row r="423" spans="1:22" ht="15" customHeight="1">
       <c r="A423">
         <v>453</v>
       </c>
@@ -17746,7 +17790,7 @@
       <c r="P423" s="2"/>
       <c r="R423" s="2"/>
     </row>
-    <row r="424" spans="1:23" ht="15" customHeight="1">
+    <row r="424" spans="1:22" ht="15" customHeight="1">
       <c r="A424">
         <v>454</v>
       </c>
@@ -17780,7 +17824,7 @@
       <c r="P424" s="2"/>
       <c r="R424" s="2"/>
     </row>
-    <row r="425" spans="1:23" ht="15" customHeight="1">
+    <row r="425" spans="1:22" ht="15" customHeight="1">
       <c r="A425">
         <v>455</v>
       </c>
@@ -17814,7 +17858,7 @@
       <c r="P425" s="2"/>
       <c r="R425" s="2"/>
     </row>
-    <row r="426" spans="1:23" ht="15" customHeight="1">
+    <row r="426" spans="1:22" ht="15" customHeight="1">
       <c r="A426">
         <v>456</v>
       </c>
@@ -17848,7 +17892,7 @@
       <c r="P426" s="2"/>
       <c r="R426" s="2"/>
     </row>
-    <row r="427" spans="1:23" ht="15" customHeight="1">
+    <row r="427" spans="1:22" ht="15" customHeight="1">
       <c r="A427">
         <v>457</v>
       </c>
@@ -17882,7 +17926,7 @@
       <c r="P427" s="2"/>
       <c r="R427" s="2"/>
     </row>
-    <row r="428" spans="1:23" ht="15" customHeight="1">
+    <row r="428" spans="1:22" ht="15" customHeight="1">
       <c r="A428">
         <v>458</v>
       </c>
@@ -17916,8 +17960,8 @@
       <c r="P428" s="2"/>
       <c r="R428" s="2"/>
     </row>
-    <row r="429" spans="1:23" ht="15" customHeight="1">
-      <c r="A429" s="8">
+    <row r="429" spans="1:22" ht="15" customHeight="1">
+      <c r="A429">
         <v>459</v>
       </c>
       <c r="B429" s="1">
@@ -17933,7 +17977,7 @@
         <v>685</v>
       </c>
       <c r="F429" s="7"/>
-      <c r="G429" s="9">
+      <c r="G429" s="6">
         <v>38527</v>
       </c>
       <c r="H429" s="2" t="s">
@@ -17942,23 +17986,16 @@
       <c r="I429" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="J429" s="8"/>
       <c r="K429" s="2"/>
       <c r="L429" s="4"/>
       <c r="M429" s="2"/>
       <c r="N429" s="2"/>
       <c r="O429" s="2"/>
       <c r="P429" s="2"/>
-      <c r="Q429" s="8"/>
       <c r="R429" s="2"/>
-      <c r="S429" s="8"/>
-      <c r="T429" s="8"/>
-      <c r="U429" s="8"/>
-      <c r="V429" s="8"/>
-      <c r="W429" s="8"/>
-    </row>
-    <row r="430" spans="1:23" ht="15" customHeight="1">
-      <c r="A430" s="8">
+    </row>
+    <row r="430" spans="1:22" ht="15" customHeight="1">
+      <c r="A430">
         <v>460</v>
       </c>
       <c r="B430" s="1">
@@ -17974,7 +18011,7 @@
         <v>689</v>
       </c>
       <c r="F430" s="7"/>
-      <c r="G430" s="9">
+      <c r="G430" s="6">
         <v>43195</v>
       </c>
       <c r="H430" s="2" t="s">
@@ -17983,23 +18020,16 @@
       <c r="I430" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="J430" s="8"/>
       <c r="K430" s="2"/>
       <c r="L430" s="4"/>
       <c r="M430" s="2"/>
       <c r="N430" s="2"/>
       <c r="O430" s="2"/>
       <c r="P430" s="2"/>
-      <c r="Q430" s="8"/>
       <c r="R430" s="2"/>
-      <c r="S430" s="8"/>
-      <c r="T430" s="8"/>
-      <c r="U430" s="8"/>
-      <c r="V430" s="8"/>
-      <c r="W430" s="8"/>
-    </row>
-    <row r="431" spans="1:23" ht="15" customHeight="1">
-      <c r="A431" s="8">
+    </row>
+    <row r="431" spans="1:22" ht="15" customHeight="1">
+      <c r="A431">
         <v>461</v>
       </c>
       <c r="B431" s="1">
@@ -18015,32 +18045,26 @@
         <v>212</v>
       </c>
       <c r="F431" s="7"/>
-      <c r="G431" s="9">
+      <c r="G431" s="6">
         <v>38186</v>
       </c>
       <c r="H431" s="2" t="s">
         <v>288</v>
       </c>
       <c r="I431" s="2"/>
-      <c r="J431" s="8"/>
       <c r="K431" s="2"/>
       <c r="L431" s="4"/>
       <c r="M431" s="2"/>
       <c r="N431" s="2"/>
       <c r="O431" s="2"/>
       <c r="P431" s="2"/>
-      <c r="Q431" s="8"/>
       <c r="R431" s="2"/>
-      <c r="S431" s="8"/>
-      <c r="T431" s="8"/>
-      <c r="U431" s="8"/>
-      <c r="V431" s="8" t="s">
+      <c r="V431" t="s">
         <v>691</v>
       </c>
-      <c r="W431" s="8"/>
-    </row>
-    <row r="432" spans="1:23" ht="15" customHeight="1">
-      <c r="A432" s="8">
+    </row>
+    <row r="432" spans="1:22" ht="15" customHeight="1">
+      <c r="A432">
         <v>462</v>
       </c>
       <c r="B432" s="1">
@@ -18056,14 +18080,13 @@
         <v>693</v>
       </c>
       <c r="F432" s="7"/>
-      <c r="G432" s="9">
+      <c r="G432" s="6">
         <v>43111</v>
       </c>
       <c r="H432" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I432" s="2"/>
-      <c r="J432" s="8"/>
       <c r="K432" s="2"/>
       <c r="L432" s="4" t="s">
         <v>694</v>
@@ -18072,16 +18095,10 @@
       <c r="N432" s="2"/>
       <c r="O432" s="2"/>
       <c r="P432" s="2"/>
-      <c r="Q432" s="8"/>
       <c r="R432" s="2"/>
-      <c r="S432" s="8"/>
-      <c r="T432" s="8"/>
-      <c r="U432" s="8"/>
-      <c r="V432" s="8"/>
-      <c r="W432" s="8"/>
     </row>
     <row r="433" spans="1:23" ht="15" customHeight="1">
-      <c r="A433" s="8">
+      <c r="A433">
         <v>463</v>
       </c>
       <c r="B433" s="1">
@@ -18097,14 +18114,13 @@
         <v>212</v>
       </c>
       <c r="F433" s="7"/>
-      <c r="G433" s="9">
+      <c r="G433" s="6">
         <v>38186</v>
       </c>
       <c r="H433" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I433" s="2"/>
-      <c r="J433" s="8"/>
       <c r="K433" s="2"/>
       <c r="L433" s="4" t="s">
         <v>695</v>
@@ -18113,16 +18129,10 @@
       <c r="N433" s="2"/>
       <c r="O433" s="2"/>
       <c r="P433" s="2"/>
-      <c r="Q433" s="8"/>
       <c r="R433" s="2"/>
-      <c r="S433" s="8"/>
-      <c r="T433" s="8"/>
-      <c r="U433" s="8"/>
-      <c r="V433" s="8"/>
-      <c r="W433" s="8"/>
     </row>
     <row r="434" spans="1:23" ht="15" customHeight="1">
-      <c r="A434" s="8">
+      <c r="A434">
         <v>464</v>
       </c>
       <c r="B434" s="1">
@@ -18138,32 +18148,26 @@
         <v>212</v>
       </c>
       <c r="F434" s="7"/>
-      <c r="G434" s="9">
+      <c r="G434" s="6">
         <v>38186</v>
       </c>
       <c r="H434" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I434" s="2"/>
-      <c r="J434" s="8"/>
       <c r="K434" s="2"/>
       <c r="L434" s="4"/>
       <c r="M434" s="2"/>
       <c r="N434" s="2"/>
       <c r="O434" s="2"/>
       <c r="P434" s="2"/>
-      <c r="Q434" s="8"/>
       <c r="R434" s="2"/>
-      <c r="S434" s="8" t="s">
+      <c r="S434" t="s">
         <v>109</v>
       </c>
-      <c r="T434" s="8"/>
-      <c r="U434" s="8"/>
-      <c r="V434" s="8"/>
-      <c r="W434" s="8"/>
     </row>
     <row r="435" spans="1:23" ht="15" customHeight="1">
-      <c r="A435" s="8">
+      <c r="A435">
         <v>465</v>
       </c>
       <c r="B435" s="1">
@@ -18179,7 +18183,7 @@
         <v>693</v>
       </c>
       <c r="F435" s="7"/>
-      <c r="G435" s="9">
+      <c r="G435" s="6">
         <v>43111</v>
       </c>
       <c r="H435" s="2" t="s">
@@ -18188,23 +18192,16 @@
       <c r="I435" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="J435" s="8"/>
       <c r="K435" s="2"/>
       <c r="L435" s="4"/>
       <c r="M435" s="2"/>
       <c r="N435" s="2"/>
       <c r="O435" s="2"/>
       <c r="P435" s="2"/>
-      <c r="Q435" s="8"/>
       <c r="R435" s="2"/>
-      <c r="S435" s="8"/>
-      <c r="T435" s="8"/>
-      <c r="U435" s="8"/>
-      <c r="V435" s="8"/>
-      <c r="W435" s="8"/>
     </row>
     <row r="436" spans="1:23" ht="15" customHeight="1">
-      <c r="A436" s="8">
+      <c r="A436">
         <v>466</v>
       </c>
       <c r="B436" s="1">
@@ -18220,7 +18217,7 @@
         <v>698</v>
       </c>
       <c r="F436" s="7"/>
-      <c r="G436" s="9">
+      <c r="G436" s="6">
         <v>38837</v>
       </c>
       <c r="H436" s="2" t="s">
@@ -18229,23 +18226,16 @@
       <c r="I436" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="J436" s="8"/>
       <c r="K436" s="2"/>
       <c r="L436" s="4"/>
       <c r="M436" s="2"/>
       <c r="N436" s="2"/>
       <c r="O436" s="2"/>
       <c r="P436" s="2"/>
-      <c r="Q436" s="8"/>
       <c r="R436" s="2"/>
-      <c r="S436" s="8"/>
-      <c r="T436" s="8"/>
-      <c r="U436" s="8"/>
-      <c r="V436" s="8"/>
-      <c r="W436" s="8"/>
     </row>
     <row r="437" spans="1:23" ht="15" customHeight="1">
-      <c r="A437" s="8">
+      <c r="A437">
         <v>467</v>
       </c>
       <c r="B437" s="1">
@@ -18261,14 +18251,13 @@
         <v>356</v>
       </c>
       <c r="F437" s="7"/>
-      <c r="G437" s="9">
+      <c r="G437" s="6">
         <v>38230</v>
       </c>
       <c r="H437" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I437" s="2"/>
-      <c r="J437" s="8"/>
       <c r="K437" s="2"/>
       <c r="L437" s="4" t="s">
         <v>700</v>
@@ -18277,16 +18266,10 @@
       <c r="N437" s="2"/>
       <c r="O437" s="2"/>
       <c r="P437" s="2"/>
-      <c r="Q437" s="8"/>
       <c r="R437" s="2"/>
-      <c r="S437" s="8"/>
-      <c r="T437" s="8"/>
-      <c r="U437" s="8"/>
-      <c r="V437" s="8"/>
-      <c r="W437" s="8"/>
     </row>
     <row r="438" spans="1:23" ht="15" customHeight="1">
-      <c r="A438" s="8">
+      <c r="A438">
         <v>468</v>
       </c>
       <c r="B438" s="1">
@@ -18302,14 +18285,13 @@
         <v>698</v>
       </c>
       <c r="F438" s="7"/>
-      <c r="G438" s="9">
+      <c r="G438" s="6">
         <v>38837</v>
       </c>
       <c r="H438" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I438" s="2"/>
-      <c r="J438" s="8"/>
       <c r="K438" s="2"/>
       <c r="L438" s="4" t="s">
         <v>701</v>
@@ -18318,16 +18300,10 @@
       <c r="N438" s="2"/>
       <c r="O438" s="2"/>
       <c r="P438" s="2"/>
-      <c r="Q438" s="8"/>
       <c r="R438" s="2"/>
-      <c r="S438" s="8"/>
-      <c r="T438" s="8"/>
-      <c r="U438" s="8"/>
-      <c r="V438" s="8"/>
-      <c r="W438" s="8"/>
     </row>
     <row r="439" spans="1:23" ht="15" customHeight="1">
-      <c r="A439" s="8">
+      <c r="A439">
         <v>469</v>
       </c>
       <c r="B439" s="1">
@@ -18343,14 +18319,13 @@
         <v>356</v>
       </c>
       <c r="F439" s="7"/>
-      <c r="G439" s="9">
+      <c r="G439" s="6">
         <v>38230</v>
       </c>
       <c r="H439" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I439" s="2"/>
-      <c r="J439" s="8"/>
       <c r="K439" s="2"/>
       <c r="L439" s="4"/>
       <c r="M439" s="2"/>
@@ -18359,16 +18334,10 @@
       </c>
       <c r="O439" s="2"/>
       <c r="P439" s="2"/>
-      <c r="Q439" s="8"/>
       <c r="R439" s="2"/>
-      <c r="S439" s="8"/>
-      <c r="T439" s="8"/>
-      <c r="U439" s="8"/>
-      <c r="V439" s="8"/>
-      <c r="W439" s="8"/>
     </row>
     <row r="440" spans="1:23" ht="15" customHeight="1">
-      <c r="A440" s="8">
+      <c r="A440">
         <v>470</v>
       </c>
       <c r="B440" s="1">
@@ -18384,14 +18353,13 @@
         <v>356</v>
       </c>
       <c r="F440" s="7"/>
-      <c r="G440" s="9">
+      <c r="G440" s="6">
         <v>38230</v>
       </c>
       <c r="H440" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I440" s="2"/>
-      <c r="J440" s="8"/>
       <c r="K440" s="2"/>
       <c r="L440" s="4"/>
       <c r="M440" s="2"/>
@@ -18400,16 +18368,10 @@
       <c r="P440" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="Q440" s="8"/>
       <c r="R440" s="2"/>
-      <c r="S440" s="8"/>
-      <c r="T440" s="8"/>
-      <c r="U440" s="8"/>
-      <c r="V440" s="8"/>
-      <c r="W440" s="8"/>
     </row>
     <row r="441" spans="1:23" ht="15" customHeight="1">
-      <c r="A441" s="8">
+      <c r="A441">
         <v>471</v>
       </c>
       <c r="B441" s="1">
@@ -18425,32 +18387,26 @@
         <v>356</v>
       </c>
       <c r="F441" s="7"/>
-      <c r="G441" s="9">
+      <c r="G441" s="6">
         <v>38230</v>
       </c>
       <c r="H441" s="2" t="s">
         <v>288</v>
       </c>
       <c r="I441" s="2"/>
-      <c r="J441" s="8"/>
       <c r="K441" s="2"/>
       <c r="L441" s="4"/>
       <c r="M441" s="2"/>
       <c r="N441" s="2"/>
       <c r="O441" s="2"/>
       <c r="P441" s="2"/>
-      <c r="Q441" s="8"/>
       <c r="R441" s="2"/>
-      <c r="S441" s="8"/>
-      <c r="T441" s="8"/>
-      <c r="U441" s="8"/>
-      <c r="V441" s="8" t="s">
+      <c r="V441" t="s">
         <v>704</v>
       </c>
-      <c r="W441" s="8"/>
     </row>
     <row r="442" spans="1:23" ht="15" customHeight="1">
-      <c r="A442" s="8">
+      <c r="A442">
         <v>472</v>
       </c>
       <c r="B442" s="1">
@@ -18466,32 +18422,26 @@
         <v>356</v>
       </c>
       <c r="F442" s="7"/>
-      <c r="G442" s="9">
+      <c r="G442" s="6">
         <v>38230</v>
       </c>
       <c r="H442" s="2" t="s">
         <v>290</v>
       </c>
       <c r="I442" s="2"/>
-      <c r="J442" s="8"/>
       <c r="K442" s="2"/>
       <c r="L442" s="4"/>
       <c r="M442" s="2"/>
       <c r="N442" s="2"/>
       <c r="O442" s="2"/>
       <c r="P442" s="2"/>
-      <c r="Q442" s="8"/>
       <c r="R442" s="2"/>
-      <c r="S442" s="8"/>
-      <c r="T442" s="8"/>
-      <c r="U442" s="8"/>
-      <c r="V442" s="8"/>
-      <c r="W442" s="8" t="s">
+      <c r="W442" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="443" spans="1:23" ht="15" customHeight="1">
-      <c r="A443" s="8">
+      <c r="A443">
         <v>473</v>
       </c>
       <c r="B443" s="1">
@@ -18507,7 +18457,7 @@
         <v>132</v>
       </c>
       <c r="F443" s="7"/>
-      <c r="G443" s="9">
+      <c r="G443" s="6">
         <v>38149</v>
       </c>
       <c r="H443" s="2" t="s">
@@ -18516,23 +18466,16 @@
       <c r="I443" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="J443" s="8"/>
       <c r="K443" s="2"/>
       <c r="L443" s="4"/>
       <c r="M443" s="2"/>
       <c r="N443" s="2"/>
       <c r="O443" s="2"/>
       <c r="P443" s="2"/>
-      <c r="Q443" s="8"/>
       <c r="R443" s="2"/>
-      <c r="S443" s="8"/>
-      <c r="T443" s="8"/>
-      <c r="U443" s="8"/>
-      <c r="V443" s="8"/>
-      <c r="W443" s="8"/>
     </row>
     <row r="444" spans="1:23" ht="15" customHeight="1">
-      <c r="A444" s="8">
+      <c r="A444">
         <v>474</v>
       </c>
       <c r="B444" s="1">
@@ -18548,14 +18491,13 @@
         <v>132</v>
       </c>
       <c r="F444" s="7"/>
-      <c r="G444" s="9">
+      <c r="G444" s="6">
         <v>38149</v>
       </c>
       <c r="H444" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I444" s="2"/>
-      <c r="J444" s="8"/>
       <c r="K444" s="2"/>
       <c r="L444" s="4" t="s">
         <v>707</v>
@@ -18564,16 +18506,10 @@
       <c r="N444" s="2"/>
       <c r="O444" s="2"/>
       <c r="P444" s="2"/>
-      <c r="Q444" s="8"/>
       <c r="R444" s="2"/>
-      <c r="S444" s="8"/>
-      <c r="T444" s="8"/>
-      <c r="U444" s="8"/>
-      <c r="V444" s="8"/>
-      <c r="W444" s="8"/>
     </row>
     <row r="445" spans="1:23" ht="15" customHeight="1">
-      <c r="A445" s="8">
+      <c r="A445">
         <v>475</v>
       </c>
       <c r="B445" s="1">
@@ -18589,7 +18525,7 @@
         <v>348</v>
       </c>
       <c r="F445" s="7"/>
-      <c r="G445" s="9">
+      <c r="G445" s="6">
         <v>38507</v>
       </c>
       <c r="H445" s="2" t="s">
@@ -18598,23 +18534,16 @@
       <c r="I445" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="J445" s="8"/>
       <c r="K445" s="2"/>
       <c r="L445" s="4"/>
       <c r="M445" s="2"/>
       <c r="N445" s="2"/>
       <c r="O445" s="2"/>
       <c r="P445" s="2"/>
-      <c r="Q445" s="8"/>
       <c r="R445" s="2"/>
-      <c r="S445" s="8"/>
-      <c r="T445" s="8"/>
-      <c r="U445" s="8"/>
-      <c r="V445" s="8"/>
-      <c r="W445" s="8"/>
     </row>
     <row r="446" spans="1:23" ht="15" customHeight="1">
-      <c r="A446" s="8">
+      <c r="A446">
         <v>476</v>
       </c>
       <c r="B446" s="1">
@@ -18630,14 +18559,13 @@
         <v>348</v>
       </c>
       <c r="F446" s="7"/>
-      <c r="G446" s="9">
+      <c r="G446" s="6">
         <v>38507</v>
       </c>
       <c r="H446" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I446" s="2"/>
-      <c r="J446" s="8"/>
       <c r="K446" s="2"/>
       <c r="L446" s="4" t="s">
         <v>709</v>
@@ -18646,16 +18574,10 @@
       <c r="N446" s="2"/>
       <c r="O446" s="2"/>
       <c r="P446" s="2"/>
-      <c r="Q446" s="8"/>
       <c r="R446" s="2"/>
-      <c r="S446" s="8"/>
-      <c r="T446" s="8"/>
-      <c r="U446" s="8"/>
-      <c r="V446" s="8"/>
-      <c r="W446" s="8"/>
     </row>
     <row r="447" spans="1:23" ht="15" customHeight="1">
-      <c r="A447" s="8">
+      <c r="A447">
         <v>477</v>
       </c>
       <c r="B447" s="1">
@@ -18671,7 +18593,7 @@
         <v>51</v>
       </c>
       <c r="F447" s="7"/>
-      <c r="G447" s="9">
+      <c r="G447" s="6">
         <v>38142</v>
       </c>
       <c r="H447" s="2" t="s">
@@ -18680,23 +18602,16 @@
       <c r="I447" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="J447" s="8"/>
       <c r="K447" s="2"/>
       <c r="L447" s="4"/>
       <c r="M447" s="2"/>
       <c r="N447" s="2"/>
       <c r="O447" s="2"/>
       <c r="P447" s="2"/>
-      <c r="Q447" s="8"/>
       <c r="R447" s="2"/>
-      <c r="S447" s="8"/>
-      <c r="T447" s="8"/>
-      <c r="U447" s="8"/>
-      <c r="V447" s="8"/>
-      <c r="W447" s="8"/>
     </row>
     <row r="448" spans="1:23" ht="15" customHeight="1">
-      <c r="A448" s="8">
+      <c r="A448">
         <v>478</v>
       </c>
       <c r="B448" s="1">
@@ -18712,14 +18627,13 @@
         <v>51</v>
       </c>
       <c r="F448" s="7"/>
-      <c r="G448" s="9">
+      <c r="G448" s="6">
         <v>38142</v>
       </c>
       <c r="H448" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I448" s="2"/>
-      <c r="J448" s="8"/>
       <c r="K448" s="2"/>
       <c r="L448" s="4" t="s">
         <v>711</v>
@@ -18728,16 +18642,10 @@
       <c r="N448" s="2"/>
       <c r="O448" s="2"/>
       <c r="P448" s="2"/>
-      <c r="Q448" s="8"/>
       <c r="R448" s="2"/>
-      <c r="S448" s="8"/>
-      <c r="T448" s="8"/>
-      <c r="U448" s="8"/>
-      <c r="V448" s="8"/>
-      <c r="W448" s="8"/>
-    </row>
-    <row r="449" spans="1:23" ht="15" customHeight="1">
-      <c r="A449" s="8">
+    </row>
+    <row r="449" spans="1:18" ht="15" customHeight="1">
+      <c r="A449">
         <v>479</v>
       </c>
       <c r="B449" s="1">
@@ -18753,14 +18661,13 @@
         <v>92</v>
       </c>
       <c r="F449" s="7"/>
-      <c r="G449" s="9">
+      <c r="G449" s="6">
         <v>38677</v>
       </c>
       <c r="H449" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I449" s="2"/>
-      <c r="J449" s="8"/>
       <c r="K449" s="2"/>
       <c r="L449" s="4" t="s">
         <v>712</v>
@@ -18769,16 +18676,10 @@
       <c r="N449" s="2"/>
       <c r="O449" s="2"/>
       <c r="P449" s="2"/>
-      <c r="Q449" s="8"/>
       <c r="R449" s="2"/>
-      <c r="S449" s="8"/>
-      <c r="T449" s="8"/>
-      <c r="U449" s="8"/>
-      <c r="V449" s="8"/>
-      <c r="W449" s="8"/>
-    </row>
-    <row r="450" spans="1:23" ht="15" customHeight="1">
-      <c r="A450" s="8">
+    </row>
+    <row r="450" spans="1:18" ht="15" customHeight="1">
+      <c r="A450">
         <v>480</v>
       </c>
       <c r="B450" s="1">
@@ -18794,7 +18695,7 @@
         <v>320</v>
       </c>
       <c r="F450" s="7"/>
-      <c r="G450" s="9">
+      <c r="G450" s="6">
         <v>43043</v>
       </c>
       <c r="H450" s="2" t="s">
@@ -18803,23 +18704,16 @@
       <c r="I450" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="J450" s="8"/>
       <c r="K450" s="2"/>
       <c r="L450" s="4"/>
       <c r="M450" s="2"/>
       <c r="N450" s="2"/>
       <c r="O450" s="2"/>
       <c r="P450" s="2"/>
-      <c r="Q450" s="8"/>
       <c r="R450" s="2"/>
-      <c r="S450" s="8"/>
-      <c r="T450" s="8"/>
-      <c r="U450" s="8"/>
-      <c r="V450" s="8"/>
-      <c r="W450" s="8"/>
-    </row>
-    <row r="451" spans="1:23" ht="15" customHeight="1">
-      <c r="A451" s="8">
+    </row>
+    <row r="451" spans="1:18" ht="15" customHeight="1">
+      <c r="A451">
         <v>481</v>
       </c>
       <c r="B451" s="1">
@@ -18835,14 +18729,13 @@
         <v>320</v>
       </c>
       <c r="F451" s="7"/>
-      <c r="G451" s="9">
+      <c r="G451" s="6">
         <v>43043</v>
       </c>
       <c r="H451" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I451" s="2"/>
-      <c r="J451" s="8"/>
       <c r="K451" s="2"/>
       <c r="L451" s="4" t="s">
         <v>714</v>
@@ -18851,16 +18744,10 @@
       <c r="N451" s="2"/>
       <c r="O451" s="2"/>
       <c r="P451" s="2"/>
-      <c r="Q451" s="8"/>
       <c r="R451" s="2"/>
-      <c r="S451" s="8"/>
-      <c r="T451" s="8"/>
-      <c r="U451" s="8"/>
-      <c r="V451" s="8"/>
-      <c r="W451" s="8"/>
-    </row>
-    <row r="452" spans="1:23" ht="15" customHeight="1">
-      <c r="A452" s="8">
+    </row>
+    <row r="452" spans="1:18" ht="15" customHeight="1">
+      <c r="A452">
         <v>482</v>
       </c>
       <c r="B452" s="1">
@@ -18876,7 +18763,7 @@
         <v>716</v>
       </c>
       <c r="F452" s="7"/>
-      <c r="G452" s="9">
+      <c r="G452" s="6">
         <v>38207</v>
       </c>
       <c r="H452" s="2" t="s">
@@ -18885,23 +18772,16 @@
       <c r="I452" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="J452" s="8"/>
       <c r="K452" s="2"/>
       <c r="L452" s="4"/>
       <c r="M452" s="2"/>
       <c r="N452" s="2"/>
       <c r="O452" s="2"/>
       <c r="P452" s="2"/>
-      <c r="Q452" s="8"/>
       <c r="R452" s="2"/>
-      <c r="S452" s="8"/>
-      <c r="T452" s="8"/>
-      <c r="U452" s="8"/>
-      <c r="V452" s="8"/>
-      <c r="W452" s="8"/>
-    </row>
-    <row r="453" spans="1:23" ht="15" customHeight="1">
-      <c r="A453" s="8">
+    </row>
+    <row r="453" spans="1:18" ht="15" customHeight="1">
+      <c r="A453">
         <v>483</v>
       </c>
       <c r="B453" s="1">
@@ -18917,7 +18797,7 @@
         <v>29</v>
       </c>
       <c r="F453" s="7"/>
-      <c r="G453" s="9">
+      <c r="G453" s="6">
         <v>43194</v>
       </c>
       <c r="H453" s="2" t="s">
@@ -18926,23 +18806,16 @@
       <c r="I453" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="J453" s="8"/>
       <c r="K453" s="2"/>
       <c r="L453" s="4"/>
       <c r="M453" s="2"/>
       <c r="N453" s="2"/>
       <c r="O453" s="2"/>
       <c r="P453" s="2"/>
-      <c r="Q453" s="8"/>
       <c r="R453" s="2"/>
-      <c r="S453" s="8"/>
-      <c r="T453" s="8"/>
-      <c r="U453" s="8"/>
-      <c r="V453" s="8"/>
-      <c r="W453" s="8"/>
-    </row>
-    <row r="454" spans="1:23" ht="15" customHeight="1">
-      <c r="A454" s="8">
+    </row>
+    <row r="454" spans="1:18" ht="15" customHeight="1">
+      <c r="A454">
         <v>484</v>
       </c>
       <c r="B454" s="1">
@@ -18958,14 +18831,13 @@
         <v>232</v>
       </c>
       <c r="F454" s="7"/>
-      <c r="G454" s="9">
+      <c r="G454" s="6">
         <v>38442</v>
       </c>
       <c r="H454" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I454" s="2"/>
-      <c r="J454" s="8"/>
       <c r="K454" s="2"/>
       <c r="L454" s="4" t="s">
         <v>719</v>
@@ -18974,16 +18846,10 @@
       <c r="N454" s="2"/>
       <c r="O454" s="2"/>
       <c r="P454" s="2"/>
-      <c r="Q454" s="8"/>
       <c r="R454" s="2"/>
-      <c r="S454" s="8"/>
-      <c r="T454" s="8"/>
-      <c r="U454" s="8"/>
-      <c r="V454" s="8"/>
-      <c r="W454" s="8"/>
-    </row>
-    <row r="455" spans="1:23" ht="15" customHeight="1">
-      <c r="A455" s="8">
+    </row>
+    <row r="455" spans="1:18" ht="15" customHeight="1">
+      <c r="A455">
         <v>485</v>
       </c>
       <c r="B455" s="1">
@@ -18999,14 +18865,13 @@
         <v>29</v>
       </c>
       <c r="F455" s="7"/>
-      <c r="G455" s="9">
+      <c r="G455" s="6">
         <v>43194</v>
       </c>
       <c r="H455" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I455" s="2"/>
-      <c r="J455" s="8"/>
       <c r="K455" s="2"/>
       <c r="L455" s="4" t="s">
         <v>720</v>
@@ -19015,16 +18880,10 @@
       <c r="N455" s="2"/>
       <c r="O455" s="2"/>
       <c r="P455" s="2"/>
-      <c r="Q455" s="8"/>
       <c r="R455" s="2"/>
-      <c r="S455" s="8"/>
-      <c r="T455" s="8"/>
-      <c r="U455" s="8"/>
-      <c r="V455" s="8"/>
-      <c r="W455" s="8"/>
-    </row>
-    <row r="456" spans="1:23" ht="15" customHeight="1">
-      <c r="A456" s="8">
+    </row>
+    <row r="456" spans="1:18" ht="15" customHeight="1">
+      <c r="A456">
         <v>486</v>
       </c>
       <c r="B456" s="1">
@@ -19040,7 +18899,7 @@
         <v>503</v>
       </c>
       <c r="F456" s="7"/>
-      <c r="G456" s="9">
+      <c r="G456" s="6">
         <v>38270</v>
       </c>
       <c r="H456" s="2" t="s">
@@ -19049,23 +18908,16 @@
       <c r="I456" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="J456" s="8"/>
       <c r="K456" s="2"/>
       <c r="L456" s="4"/>
       <c r="M456" s="2"/>
       <c r="N456" s="2"/>
       <c r="O456" s="2"/>
       <c r="P456" s="2"/>
-      <c r="Q456" s="8"/>
       <c r="R456" s="2"/>
-      <c r="S456" s="8"/>
-      <c r="T456" s="8"/>
-      <c r="U456" s="8"/>
-      <c r="V456" s="8"/>
-      <c r="W456" s="8"/>
-    </row>
-    <row r="457" spans="1:23" ht="15" customHeight="1">
-      <c r="A457" s="8">
+    </row>
+    <row r="457" spans="1:18" ht="15" customHeight="1">
+      <c r="A457">
         <v>487</v>
       </c>
       <c r="B457" s="1">
@@ -19081,7 +18933,7 @@
         <v>46</v>
       </c>
       <c r="F457" s="7"/>
-      <c r="G457" s="9">
+      <c r="G457" s="6">
         <v>38925</v>
       </c>
       <c r="H457" s="2" t="s">
@@ -19090,23 +18942,16 @@
       <c r="I457" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="J457" s="8"/>
       <c r="K457" s="2"/>
       <c r="L457" s="4"/>
       <c r="M457" s="2"/>
       <c r="N457" s="2"/>
       <c r="O457" s="2"/>
       <c r="P457" s="2"/>
-      <c r="Q457" s="8"/>
       <c r="R457" s="2"/>
-      <c r="S457" s="8"/>
-      <c r="T457" s="8"/>
-      <c r="U457" s="8"/>
-      <c r="V457" s="8"/>
-      <c r="W457" s="8"/>
-    </row>
-    <row r="458" spans="1:23" ht="15" customHeight="1">
-      <c r="A458" s="8">
+    </row>
+    <row r="458" spans="1:18" ht="15" customHeight="1">
+      <c r="A458">
         <v>488</v>
       </c>
       <c r="B458" s="1">
@@ -19122,14 +18967,13 @@
         <v>46</v>
       </c>
       <c r="F458" s="7"/>
-      <c r="G458" s="9">
+      <c r="G458" s="6">
         <v>38925</v>
       </c>
       <c r="H458" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I458" s="2"/>
-      <c r="J458" s="8"/>
       <c r="K458" s="2"/>
       <c r="L458" s="4" t="s">
         <v>723</v>
@@ -19138,16 +18982,10 @@
       <c r="N458" s="2"/>
       <c r="O458" s="2"/>
       <c r="P458" s="2"/>
-      <c r="Q458" s="8"/>
       <c r="R458" s="2"/>
-      <c r="S458" s="8"/>
-      <c r="T458" s="8"/>
-      <c r="U458" s="8"/>
-      <c r="V458" s="8"/>
-      <c r="W458" s="8"/>
-    </row>
-    <row r="459" spans="1:23" ht="15" customHeight="1">
-      <c r="A459" s="8">
+    </row>
+    <row r="459" spans="1:18" ht="15" customHeight="1">
+      <c r="A459">
         <v>489</v>
       </c>
       <c r="B459" s="1">
@@ -19163,14 +19001,13 @@
         <v>197</v>
       </c>
       <c r="F459" s="7"/>
-      <c r="G459" s="9">
+      <c r="G459" s="6">
         <v>43130</v>
       </c>
       <c r="H459" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I459" s="2"/>
-      <c r="J459" s="8"/>
       <c r="K459" s="2"/>
       <c r="L459" s="4" t="s">
         <v>724</v>
@@ -19179,16 +19016,10 @@
       <c r="N459" s="2"/>
       <c r="O459" s="2"/>
       <c r="P459" s="2"/>
-      <c r="Q459" s="8"/>
       <c r="R459" s="2"/>
-      <c r="S459" s="8"/>
-      <c r="T459" s="8"/>
-      <c r="U459" s="8"/>
-      <c r="V459" s="8"/>
-      <c r="W459" s="8"/>
-    </row>
-    <row r="460" spans="1:23" ht="15" customHeight="1">
-      <c r="A460" s="8">
+    </row>
+    <row r="460" spans="1:18" ht="15" customHeight="1">
+      <c r="A460">
         <v>490</v>
       </c>
       <c r="B460" s="1">
@@ -19204,7 +19035,7 @@
         <v>197</v>
       </c>
       <c r="F460" s="7"/>
-      <c r="G460" s="9">
+      <c r="G460" s="6">
         <v>43130</v>
       </c>
       <c r="H460" s="2" t="s">
@@ -19213,23 +19044,16 @@
       <c r="I460" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="J460" s="8"/>
       <c r="K460" s="2"/>
       <c r="L460" s="4"/>
       <c r="M460" s="2"/>
       <c r="N460" s="2"/>
       <c r="O460" s="2"/>
       <c r="P460" s="2"/>
-      <c r="Q460" s="8"/>
       <c r="R460" s="2"/>
-      <c r="S460" s="8"/>
-      <c r="T460" s="8"/>
-      <c r="U460" s="8"/>
-      <c r="V460" s="8"/>
-      <c r="W460" s="8"/>
-    </row>
-    <row r="461" spans="1:23" ht="15" customHeight="1">
-      <c r="A461" s="8">
+    </row>
+    <row r="461" spans="1:18" ht="15" customHeight="1">
+      <c r="A461">
         <v>491</v>
       </c>
       <c r="B461" s="1">
@@ -19245,14 +19069,13 @@
         <v>503</v>
       </c>
       <c r="F461" s="7"/>
-      <c r="G461" s="9">
+      <c r="G461" s="6">
         <v>38270</v>
       </c>
       <c r="H461" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I461" s="2"/>
-      <c r="J461" s="8"/>
       <c r="K461" s="2"/>
       <c r="L461" s="4" t="s">
         <v>726</v>
@@ -19261,16 +19084,10 @@
       <c r="N461" s="2"/>
       <c r="O461" s="2"/>
       <c r="P461" s="2"/>
-      <c r="Q461" s="8"/>
       <c r="R461" s="2"/>
-      <c r="S461" s="8"/>
-      <c r="T461" s="8"/>
-      <c r="U461" s="8"/>
-      <c r="V461" s="8"/>
-      <c r="W461" s="8"/>
-    </row>
-    <row r="462" spans="1:23" ht="15" customHeight="1">
-      <c r="A462" s="8">
+    </row>
+    <row r="462" spans="1:18" ht="15" customHeight="1">
+      <c r="A462">
         <v>492</v>
       </c>
       <c r="B462" s="1">
@@ -19286,14 +19103,13 @@
         <v>155</v>
       </c>
       <c r="F462" s="7"/>
-      <c r="G462" s="9">
+      <c r="G462" s="6">
         <v>38119</v>
       </c>
       <c r="H462" s="2" t="s">
         <v>40</v>
       </c>
       <c r="I462" s="2"/>
-      <c r="J462" s="8"/>
       <c r="K462" s="2"/>
       <c r="L462" s="4" t="s">
         <v>727</v>
@@ -19302,16 +19118,10 @@
       <c r="N462" s="2"/>
       <c r="O462" s="2"/>
       <c r="P462" s="2"/>
-      <c r="Q462" s="8"/>
       <c r="R462" s="2"/>
-      <c r="S462" s="8"/>
-      <c r="T462" s="8"/>
-      <c r="U462" s="8"/>
-      <c r="V462" s="8"/>
-      <c r="W462" s="8"/>
-    </row>
-    <row r="463" spans="1:23" ht="15" customHeight="1">
-      <c r="A463" s="8">
+    </row>
+    <row r="463" spans="1:18" ht="15" customHeight="1">
+      <c r="A463">
         <v>493</v>
       </c>
       <c r="B463" s="1">
@@ -19327,7 +19137,7 @@
         <v>155</v>
       </c>
       <c r="F463" s="7"/>
-      <c r="G463" s="9">
+      <c r="G463" s="6">
         <v>38119</v>
       </c>
       <c r="H463" s="2" t="s">
@@ -19336,23 +19146,16 @@
       <c r="I463" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="J463" s="8"/>
       <c r="K463" s="2"/>
       <c r="L463" s="4"/>
       <c r="M463" s="2"/>
       <c r="N463" s="2"/>
       <c r="O463" s="2"/>
       <c r="P463" s="2"/>
-      <c r="Q463" s="8"/>
       <c r="R463" s="2"/>
-      <c r="S463" s="8"/>
-      <c r="T463" s="8"/>
-      <c r="U463" s="8"/>
-      <c r="V463" s="8"/>
-      <c r="W463" s="8"/>
-    </row>
-    <row r="464" spans="1:23" ht="15" customHeight="1">
-      <c r="A464" s="8">
+    </row>
+    <row r="464" spans="1:18" ht="15" customHeight="1">
+      <c r="A464">
         <v>494</v>
       </c>
       <c r="B464" s="1">
@@ -19368,7 +19171,7 @@
         <v>55</v>
       </c>
       <c r="F464" s="7"/>
-      <c r="G464" s="9">
+      <c r="G464" s="6">
         <v>38394</v>
       </c>
       <c r="H464" s="2" t="s">
@@ -19377,20 +19180,421 @@
       <c r="I464" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="J464" s="8"/>
       <c r="K464" s="2"/>
       <c r="L464" s="4"/>
       <c r="M464" s="2"/>
       <c r="N464" s="2"/>
       <c r="O464" s="2"/>
       <c r="P464" s="2"/>
-      <c r="Q464" s="8"/>
       <c r="R464" s="2"/>
-      <c r="S464" s="8"/>
-      <c r="T464" s="8"/>
-      <c r="U464" s="8"/>
-      <c r="V464" s="8"/>
-      <c r="W464" s="8"/>
+    </row>
+    <row r="465" spans="1:18" ht="15" customHeight="1">
+      <c r="A465">
+        <v>495</v>
+      </c>
+      <c r="B465" s="1">
+        <v>46272.528599537</v>
+      </c>
+      <c r="C465" s="1">
+        <v>46272.541932870401</v>
+      </c>
+      <c r="D465" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="E465" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F465" s="7"/>
+      <c r="G465" s="6">
+        <v>38471</v>
+      </c>
+      <c r="H465" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I465" s="2"/>
+      <c r="K465" s="2"/>
+      <c r="L465" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="M465" s="2"/>
+      <c r="N465" s="2"/>
+      <c r="O465" s="2"/>
+      <c r="P465" s="2"/>
+      <c r="R465" s="2"/>
+    </row>
+    <row r="466" spans="1:18" ht="15" customHeight="1">
+      <c r="A466">
+        <v>496</v>
+      </c>
+      <c r="B466" s="1">
+        <v>46272.542210648098</v>
+      </c>
+      <c r="C466" s="1">
+        <v>46272.542951388903</v>
+      </c>
+      <c r="D466" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="E466" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F466" s="7"/>
+      <c r="G466" s="6">
+        <v>38371</v>
+      </c>
+      <c r="H466" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I466" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="K466" s="2"/>
+      <c r="L466" s="4"/>
+      <c r="M466" s="2"/>
+      <c r="N466" s="2"/>
+      <c r="O466" s="2"/>
+      <c r="P466" s="2"/>
+      <c r="R466" s="2"/>
+    </row>
+    <row r="467" spans="1:18" ht="15" customHeight="1">
+      <c r="A467">
+        <v>497</v>
+      </c>
+      <c r="B467" s="1">
+        <v>46272.546122685198</v>
+      </c>
+      <c r="C467" s="1">
+        <v>46272.546342592599</v>
+      </c>
+      <c r="D467" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E467" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F467" s="7"/>
+      <c r="G467" s="6">
+        <v>38266</v>
+      </c>
+      <c r="H467" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I467" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="K467" s="2"/>
+      <c r="L467" s="4"/>
+      <c r="M467" s="2"/>
+      <c r="N467" s="2"/>
+      <c r="O467" s="2"/>
+      <c r="P467" s="2"/>
+      <c r="R467" s="2"/>
+    </row>
+    <row r="468" spans="1:18" ht="15" customHeight="1">
+      <c r="A468">
+        <v>498</v>
+      </c>
+      <c r="B468" s="1">
+        <v>46272.548703703702</v>
+      </c>
+      <c r="C468" s="1">
+        <v>46272.5489930556</v>
+      </c>
+      <c r="D468" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E468" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F468" s="7"/>
+      <c r="G468" s="6">
+        <v>38266</v>
+      </c>
+      <c r="H468" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I468" s="2"/>
+      <c r="K468" s="2"/>
+      <c r="L468" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="M468" s="2"/>
+      <c r="N468" s="2"/>
+      <c r="O468" s="2"/>
+      <c r="P468" s="2"/>
+      <c r="R468" s="2"/>
+    </row>
+    <row r="469" spans="1:18" ht="15" customHeight="1">
+      <c r="A469">
+        <v>499</v>
+      </c>
+      <c r="B469" s="1">
+        <v>46272.551921296297</v>
+      </c>
+      <c r="C469" s="1">
+        <v>46272.5523032407</v>
+      </c>
+      <c r="D469" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E469" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F469" s="7"/>
+      <c r="G469" s="6">
+        <v>38394</v>
+      </c>
+      <c r="H469" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I469" s="2"/>
+      <c r="K469" s="2"/>
+      <c r="L469" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="M469" s="2"/>
+      <c r="N469" s="2"/>
+      <c r="O469" s="2"/>
+      <c r="P469" s="2"/>
+      <c r="R469" s="2"/>
+    </row>
+    <row r="470" spans="1:18" ht="15" customHeight="1">
+      <c r="A470">
+        <v>500</v>
+      </c>
+      <c r="B470" s="1">
+        <v>46272.552592592598</v>
+      </c>
+      <c r="C470" s="1">
+        <v>46272.553356481498</v>
+      </c>
+      <c r="D470" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E470" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F470" s="7"/>
+      <c r="G470" s="6">
+        <v>38115</v>
+      </c>
+      <c r="H470" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I470" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="K470" s="2"/>
+      <c r="L470" s="4"/>
+      <c r="M470" s="2"/>
+      <c r="N470" s="2"/>
+      <c r="O470" s="2"/>
+      <c r="P470" s="2"/>
+      <c r="R470" s="2"/>
+    </row>
+    <row r="471" spans="1:18" ht="15" customHeight="1">
+      <c r="A471">
+        <v>501</v>
+      </c>
+      <c r="B471" s="1">
+        <v>46272.554155092599</v>
+      </c>
+      <c r="C471" s="1">
+        <v>46272.5545486111</v>
+      </c>
+      <c r="D471" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E471" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F471" s="7"/>
+      <c r="G471" s="6">
+        <v>38115</v>
+      </c>
+      <c r="H471" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I471" s="2"/>
+      <c r="K471" s="2"/>
+      <c r="L471" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="M471" s="2"/>
+      <c r="N471" s="2"/>
+      <c r="O471" s="2"/>
+      <c r="P471" s="2"/>
+      <c r="R471" s="2"/>
+    </row>
+    <row r="472" spans="1:18" ht="15" customHeight="1">
+      <c r="A472">
+        <v>502</v>
+      </c>
+      <c r="B472" s="1">
+        <v>46272.555729166699</v>
+      </c>
+      <c r="C472" s="1">
+        <v>46272.556284722203</v>
+      </c>
+      <c r="D472" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E472" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F472" s="7"/>
+      <c r="G472" s="6">
+        <v>38394</v>
+      </c>
+      <c r="H472" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I472" s="2"/>
+      <c r="K472" s="2"/>
+      <c r="L472" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="M472" s="2"/>
+      <c r="N472" s="2"/>
+      <c r="O472" s="2"/>
+      <c r="P472" s="2"/>
+      <c r="R472" s="2"/>
+    </row>
+    <row r="473" spans="1:18" ht="15" customHeight="1">
+      <c r="A473">
+        <v>503</v>
+      </c>
+      <c r="B473" s="1">
+        <v>46272.556030092601</v>
+      </c>
+      <c r="C473" s="1">
+        <v>46272.557824074102</v>
+      </c>
+      <c r="D473" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="E473" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="F473" s="7"/>
+      <c r="G473" s="6">
+        <v>38546</v>
+      </c>
+      <c r="H473" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I473" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="K473" s="2"/>
+      <c r="L473" s="4"/>
+      <c r="M473" s="2"/>
+      <c r="N473" s="2"/>
+      <c r="O473" s="2"/>
+      <c r="P473" s="2"/>
+      <c r="R473" s="2"/>
+    </row>
+    <row r="474" spans="1:18" ht="15" customHeight="1">
+      <c r="A474">
+        <v>504</v>
+      </c>
+      <c r="B474" s="1">
+        <v>46272.555266203701</v>
+      </c>
+      <c r="C474" s="1">
+        <v>46272.557939814797</v>
+      </c>
+      <c r="D474" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E474" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F474" s="7"/>
+      <c r="G474" s="6">
+        <v>38363</v>
+      </c>
+      <c r="H474" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I474" s="2"/>
+      <c r="K474" s="2"/>
+      <c r="L474" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="M474" s="2"/>
+      <c r="N474" s="2"/>
+      <c r="O474" s="2"/>
+      <c r="P474" s="2"/>
+      <c r="R474" s="2"/>
+    </row>
+    <row r="475" spans="1:18" ht="15" customHeight="1">
+      <c r="A475">
+        <v>505</v>
+      </c>
+      <c r="B475" s="1">
+        <v>46272.557962963001</v>
+      </c>
+      <c r="C475" s="1">
+        <v>46272.558379629598</v>
+      </c>
+      <c r="D475" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="E475" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="F475" s="7"/>
+      <c r="G475" s="6">
+        <v>38546</v>
+      </c>
+      <c r="H475" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I475" s="2"/>
+      <c r="K475" s="2"/>
+      <c r="L475" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="M475" s="2"/>
+      <c r="N475" s="2"/>
+      <c r="O475" s="2"/>
+      <c r="P475" s="2"/>
+      <c r="R475" s="2"/>
+    </row>
+    <row r="476" spans="1:18" ht="15" customHeight="1">
+      <c r="A476">
+        <v>506</v>
+      </c>
+      <c r="B476" s="1">
+        <v>46272.558113425897</v>
+      </c>
+      <c r="C476" s="1">
+        <v>46272.559004629598</v>
+      </c>
+      <c r="D476" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E476" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F476" s="7"/>
+      <c r="G476" s="6">
+        <v>38363</v>
+      </c>
+      <c r="H476" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I476" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="K476" s="2"/>
+      <c r="L476" s="4"/>
+      <c r="M476" s="2"/>
+      <c r="N476" s="2"/>
+      <c r="O476" s="2"/>
+      <c r="P476" s="2"/>
+      <c r="R476" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39E53031-8A1D-4261-8404-6CCA24CF543E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FAAF426-8825-484B-8385-4F101F47C40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2428" uniqueCount="766">
   <si>
     <t>Id</t>
   </si>
@@ -2325,6 +2325,15 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Sor%20Juana.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_5835_Maria%20Fernanda%20Reyes.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_2461_Starbucks%20Sor%20Juana.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Maria%20Fernanda%20Reyes.jpg</t>
   </si>
 </sst>
 </file>
@@ -2480,8 +2489,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X492" totalsRowShown="0">
-  <autoFilter ref="A1:X492" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X496" totalsRowShown="0">
+  <autoFilter ref="A1:X496" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="21">
       <extLst>
@@ -2655,7 +2664,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="522" latestEventMarker="793">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="526" latestEventMarker="797">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2985,7 +2994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X492"/>
+  <dimension ref="A1:X496"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -20279,6 +20288,176 @@
       <c r="W492" s="8"/>
       <c r="X492" s="8"/>
     </row>
+    <row r="493" spans="1:24" ht="15" customHeight="1">
+      <c r="A493" s="8">
+        <v>523</v>
+      </c>
+      <c r="B493" s="1">
+        <v>46272.608541666697</v>
+      </c>
+      <c r="C493" s="1">
+        <v>46272.608819444402</v>
+      </c>
+      <c r="D493" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E493" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F493" s="7"/>
+      <c r="G493" s="9">
+        <v>38442</v>
+      </c>
+      <c r="H493" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I493" s="2"/>
+      <c r="J493" s="8"/>
+      <c r="K493" s="2"/>
+      <c r="L493" s="8"/>
+      <c r="M493" s="4"/>
+      <c r="N493" s="2"/>
+      <c r="O493" s="2"/>
+      <c r="P493" s="2"/>
+      <c r="Q493" s="2"/>
+      <c r="R493" s="8"/>
+      <c r="S493" s="2"/>
+      <c r="T493" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="U493" s="8"/>
+      <c r="V493" s="8"/>
+      <c r="W493" s="8"/>
+      <c r="X493" s="8"/>
+    </row>
+    <row r="494" spans="1:24" ht="15" customHeight="1">
+      <c r="A494" s="8">
+        <v>524</v>
+      </c>
+      <c r="B494" s="1">
+        <v>46272.61</v>
+      </c>
+      <c r="C494" s="1">
+        <v>46272.610347222202</v>
+      </c>
+      <c r="D494" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E494" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F494" s="7"/>
+      <c r="G494" s="9">
+        <v>38535</v>
+      </c>
+      <c r="H494" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I494" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="J494" s="8"/>
+      <c r="K494" s="2"/>
+      <c r="L494" s="8"/>
+      <c r="M494" s="4"/>
+      <c r="N494" s="2"/>
+      <c r="O494" s="2"/>
+      <c r="P494" s="2"/>
+      <c r="Q494" s="2"/>
+      <c r="R494" s="8"/>
+      <c r="S494" s="2"/>
+      <c r="T494" s="8"/>
+      <c r="U494" s="8"/>
+      <c r="V494" s="8"/>
+      <c r="W494" s="8"/>
+      <c r="X494" s="8"/>
+    </row>
+    <row r="495" spans="1:24" ht="15" customHeight="1">
+      <c r="A495" s="8">
+        <v>525</v>
+      </c>
+      <c r="B495" s="1">
+        <v>46272.608946759297</v>
+      </c>
+      <c r="C495" s="1">
+        <v>46272.611099537004</v>
+      </c>
+      <c r="D495" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E495" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F495" s="7"/>
+      <c r="G495" s="9">
+        <v>38442</v>
+      </c>
+      <c r="H495" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I495" s="2"/>
+      <c r="J495" s="8"/>
+      <c r="K495" s="2"/>
+      <c r="L495" s="8"/>
+      <c r="M495" s="4"/>
+      <c r="N495" s="2"/>
+      <c r="O495" s="2"/>
+      <c r="P495" s="2"/>
+      <c r="Q495" s="2"/>
+      <c r="R495" s="8"/>
+      <c r="S495" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="T495" s="8"/>
+      <c r="U495" s="8"/>
+      <c r="V495" s="8"/>
+      <c r="W495" s="8"/>
+      <c r="X495" s="8"/>
+    </row>
+    <row r="496" spans="1:24" ht="15" customHeight="1">
+      <c r="A496" s="8">
+        <v>526</v>
+      </c>
+      <c r="B496" s="1">
+        <v>46272.610555555599</v>
+      </c>
+      <c r="C496" s="1">
+        <v>46272.6121180556</v>
+      </c>
+      <c r="D496" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E496" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F496" s="7"/>
+      <c r="G496" s="9">
+        <v>38535</v>
+      </c>
+      <c r="H496" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I496" s="2"/>
+      <c r="J496" s="8"/>
+      <c r="K496" s="2"/>
+      <c r="L496" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="M496" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="N496" s="2"/>
+      <c r="O496" s="2"/>
+      <c r="P496" s="2"/>
+      <c r="Q496" s="2"/>
+      <c r="R496" s="8"/>
+      <c r="S496" s="2"/>
+      <c r="T496" s="8"/>
+      <c r="U496" s="8"/>
+      <c r="V496" s="8"/>
+      <c r="W496" s="8"/>
+      <c r="X496" s="8"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FAAF426-8825-484B-8385-4F101F47C40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{444B152A-F484-4FB1-8960-839E713FA0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2428" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2440" uniqueCount="769">
   <si>
     <t>Id</t>
   </si>
@@ -2334,6 +2334,15 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Maria%20Fernanda%20Reyes.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/IMG_2467_Starbucks%20Sor%20Juana.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/20260907_144705_Starbucks%20Mundo%20E.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG_2472_Starbucks%20Sor%20Juana.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2489,8 +2498,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X496" totalsRowShown="0">
-  <autoFilter ref="A1:X496" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X499" totalsRowShown="0">
+  <autoFilter ref="A1:X499" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="21">
       <extLst>
@@ -2664,7 +2673,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="526" latestEventMarker="797">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="529" latestEventMarker="800">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2994,7 +3003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X496"/>
+  <dimension ref="A1:X499"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -19286,7 +19295,7 @@
       </c>
       <c r="F465" s="7"/>
       <c r="G465" s="6">
-        <v>38471</v>
+        <v>38371</v>
       </c>
       <c r="H465" s="2" t="s">
         <v>41</v>
@@ -20458,6 +20467,132 @@
       <c r="W496" s="8"/>
       <c r="X496" s="8"/>
     </row>
+    <row r="497" spans="1:24" ht="15" customHeight="1">
+      <c r="A497" s="8">
+        <v>527</v>
+      </c>
+      <c r="B497" s="1">
+        <v>46272.607349537</v>
+      </c>
+      <c r="C497" s="1">
+        <v>46272.616053240701</v>
+      </c>
+      <c r="D497" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E497" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F497" s="7"/>
+      <c r="G497" s="9">
+        <v>38442</v>
+      </c>
+      <c r="H497" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I497" s="2"/>
+      <c r="J497" s="8"/>
+      <c r="K497" s="2"/>
+      <c r="L497" s="8"/>
+      <c r="M497" s="4"/>
+      <c r="N497" s="2"/>
+      <c r="O497" s="2"/>
+      <c r="P497" s="2"/>
+      <c r="Q497" s="2"/>
+      <c r="R497" s="8"/>
+      <c r="S497" s="2"/>
+      <c r="T497" s="8"/>
+      <c r="U497" s="8"/>
+      <c r="V497" s="8"/>
+      <c r="W497" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="X497" s="8"/>
+    </row>
+    <row r="498" spans="1:24" ht="15" customHeight="1">
+      <c r="A498" s="8">
+        <v>528</v>
+      </c>
+      <c r="B498" s="1">
+        <v>46272.613611111097</v>
+      </c>
+      <c r="C498" s="1">
+        <v>46272.616215277798</v>
+      </c>
+      <c r="D498" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E498" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F498" s="7"/>
+      <c r="G498" s="9">
+        <v>38674</v>
+      </c>
+      <c r="H498" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I498" s="2"/>
+      <c r="J498" s="8"/>
+      <c r="K498" s="2"/>
+      <c r="L498" s="8"/>
+      <c r="M498" s="4"/>
+      <c r="N498" s="2"/>
+      <c r="O498" s="2"/>
+      <c r="P498" s="2"/>
+      <c r="Q498" s="2"/>
+      <c r="R498" s="8"/>
+      <c r="S498" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="T498" s="8"/>
+      <c r="U498" s="8"/>
+      <c r="V498" s="8"/>
+      <c r="W498" s="8"/>
+      <c r="X498" s="8"/>
+    </row>
+    <row r="499" spans="1:24" ht="15" customHeight="1">
+      <c r="A499" s="8">
+        <v>529</v>
+      </c>
+      <c r="B499" s="1">
+        <v>46272.616226851896</v>
+      </c>
+      <c r="C499" s="1">
+        <v>46272.620196759301</v>
+      </c>
+      <c r="D499" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E499" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F499" s="7"/>
+      <c r="G499" s="9">
+        <v>38442</v>
+      </c>
+      <c r="H499" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I499" s="2"/>
+      <c r="J499" s="8"/>
+      <c r="K499" s="2"/>
+      <c r="L499" s="8"/>
+      <c r="M499" s="4"/>
+      <c r="N499" s="2"/>
+      <c r="O499" s="2"/>
+      <c r="P499" s="2"/>
+      <c r="Q499" s="2"/>
+      <c r="R499" s="8"/>
+      <c r="S499" s="2"/>
+      <c r="T499" s="8"/>
+      <c r="U499" s="8"/>
+      <c r="V499" s="8"/>
+      <c r="W499" s="8"/>
+      <c r="X499" s="8" t="s">
+        <v>768</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="I37" r:id="rId1" xr:uid="{2AA60945-74AF-4F79-92BA-B611A262ACAE}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{444B152A-F484-4FB1-8960-839E713FA0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="769" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC43986-B713-4EC9-B21D-1455A6498219}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2440" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="777">
   <si>
     <t>Id</t>
   </si>
@@ -2343,6 +2343,30 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG_2472_Starbucks%20Sor%20Juana.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/20260825_133925_Starbucks%20ENCUENTRO.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG-20260907-WA0016_Starbucks%20Eduardo%20Mo.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia/IMG_20260827_222810_Starbucks%20Mundo%20E%20II.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/17888177077593874470024860234504_Starbucks%20Mundo%20E%20II.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17888191181462800467193226669895_Starbucks%20Mundo%20E%20II.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_3454_Starbucks%20Boulevard.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/19BEAFC1-68E0-4714-8D3B-FDAB118B375D_Starbucks%20Viveros%20Sa.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Viveros%20Sa.jpg</t>
   </si>
 </sst>
 </file>
@@ -2498,8 +2522,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X499" totalsRowShown="0">
-  <autoFilter ref="A1:X499" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X509" totalsRowShown="0">
+  <autoFilter ref="A1:X509" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="21">
       <extLst>
@@ -2673,7 +2697,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="529" latestEventMarker="800">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="539" latestEventMarker="810">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -3003,7 +3027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X499"/>
+  <dimension ref="A1:X509"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -19821,7 +19845,7 @@
       <c r="Q480" s="2"/>
       <c r="S480" s="2"/>
     </row>
-    <row r="481" spans="1:24" ht="15" customHeight="1">
+    <row r="481" spans="1:21" ht="15" customHeight="1">
       <c r="A481">
         <v>511</v>
       </c>
@@ -19855,7 +19879,7 @@
       <c r="Q481" s="2"/>
       <c r="S481" s="2"/>
     </row>
-    <row r="482" spans="1:24" ht="15" customHeight="1">
+    <row r="482" spans="1:21" ht="15" customHeight="1">
       <c r="A482">
         <v>512</v>
       </c>
@@ -19889,7 +19913,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="483" spans="1:24" ht="15" customHeight="1">
+    <row r="483" spans="1:21" ht="15" customHeight="1">
       <c r="A483">
         <v>513</v>
       </c>
@@ -19923,7 +19947,7 @@
       <c r="Q483" s="2"/>
       <c r="S483" s="2"/>
     </row>
-    <row r="484" spans="1:24" ht="15" customHeight="1">
+    <row r="484" spans="1:21" ht="15" customHeight="1">
       <c r="A484">
         <v>514</v>
       </c>
@@ -19961,8 +19985,8 @@
         <v>754</v>
       </c>
     </row>
-    <row r="485" spans="1:24" ht="15" customHeight="1">
-      <c r="A485" s="8">
+    <row r="485" spans="1:21" ht="15" customHeight="1">
+      <c r="A485">
         <v>515</v>
       </c>
       <c r="B485" s="1">
@@ -19978,16 +20002,14 @@
         <v>325</v>
       </c>
       <c r="F485" s="7"/>
-      <c r="G485" s="9">
+      <c r="G485" s="6">
         <v>38965</v>
       </c>
       <c r="H485" s="2" t="s">
         <v>220</v>
       </c>
       <c r="I485" s="2"/>
-      <c r="J485" s="8"/>
       <c r="K485" s="2"/>
-      <c r="L485" s="8"/>
       <c r="M485" s="4"/>
       <c r="N485" s="2"/>
       <c r="O485" s="2"/>
@@ -19995,16 +20017,10 @@
         <v>755</v>
       </c>
       <c r="Q485" s="2"/>
-      <c r="R485" s="8"/>
       <c r="S485" s="2"/>
-      <c r="T485" s="8"/>
-      <c r="U485" s="8"/>
-      <c r="V485" s="8"/>
-      <c r="W485" s="8"/>
-      <c r="X485" s="8"/>
-    </row>
-    <row r="486" spans="1:24" ht="15" customHeight="1">
-      <c r="A486" s="8">
+    </row>
+    <row r="486" spans="1:21" ht="15" customHeight="1">
+      <c r="A486">
         <v>516</v>
       </c>
       <c r="B486" s="1">
@@ -20020,16 +20036,14 @@
         <v>325</v>
       </c>
       <c r="F486" s="7"/>
-      <c r="G486" s="9">
+      <c r="G486" s="6">
         <v>38965</v>
       </c>
       <c r="H486" s="2" t="s">
         <v>220</v>
       </c>
       <c r="I486" s="2"/>
-      <c r="J486" s="8"/>
       <c r="K486" s="2"/>
-      <c r="L486" s="8"/>
       <c r="M486" s="4"/>
       <c r="N486" s="2"/>
       <c r="O486" s="2"/>
@@ -20037,16 +20051,10 @@
         <v>756</v>
       </c>
       <c r="Q486" s="2"/>
-      <c r="R486" s="8"/>
       <c r="S486" s="2"/>
-      <c r="T486" s="8"/>
-      <c r="U486" s="8"/>
-      <c r="V486" s="8"/>
-      <c r="W486" s="8"/>
-      <c r="X486" s="8"/>
-    </row>
-    <row r="487" spans="1:24" ht="15" customHeight="1">
-      <c r="A487" s="8">
+    </row>
+    <row r="487" spans="1:21" ht="15" customHeight="1">
+      <c r="A487">
         <v>517</v>
       </c>
       <c r="B487" s="1">
@@ -20062,16 +20070,14 @@
         <v>337</v>
       </c>
       <c r="F487" s="7"/>
-      <c r="G487" s="9">
+      <c r="G487" s="6">
         <v>38811</v>
       </c>
       <c r="H487" s="2" t="s">
         <v>220</v>
       </c>
       <c r="I487" s="2"/>
-      <c r="J487" s="8"/>
       <c r="K487" s="2"/>
-      <c r="L487" s="8"/>
       <c r="M487" s="4"/>
       <c r="N487" s="2"/>
       <c r="O487" s="2"/>
@@ -20079,16 +20085,10 @@
         <v>757</v>
       </c>
       <c r="Q487" s="2"/>
-      <c r="R487" s="8"/>
       <c r="S487" s="2"/>
-      <c r="T487" s="8"/>
-      <c r="U487" s="8"/>
-      <c r="V487" s="8"/>
-      <c r="W487" s="8"/>
-      <c r="X487" s="8"/>
-    </row>
-    <row r="488" spans="1:24" ht="15" customHeight="1">
-      <c r="A488" s="8">
+    </row>
+    <row r="488" spans="1:21" ht="15" customHeight="1">
+      <c r="A488">
         <v>518</v>
       </c>
       <c r="B488" s="1">
@@ -20104,16 +20104,14 @@
         <v>317</v>
       </c>
       <c r="F488" s="7"/>
-      <c r="G488" s="9">
+      <c r="G488" s="6">
         <v>38374</v>
       </c>
       <c r="H488" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I488" s="2"/>
-      <c r="J488" s="8"/>
       <c r="K488" s="2"/>
-      <c r="L488" s="8"/>
       <c r="M488" s="4"/>
       <c r="N488" s="2"/>
       <c r="O488" s="2" t="s">
@@ -20121,16 +20119,10 @@
       </c>
       <c r="P488" s="2"/>
       <c r="Q488" s="2"/>
-      <c r="R488" s="8"/>
       <c r="S488" s="2"/>
-      <c r="T488" s="8"/>
-      <c r="U488" s="8"/>
-      <c r="V488" s="8"/>
-      <c r="W488" s="8"/>
-      <c r="X488" s="8"/>
-    </row>
-    <row r="489" spans="1:24" ht="15" customHeight="1">
-      <c r="A489" s="8">
+    </row>
+    <row r="489" spans="1:21" ht="15" customHeight="1">
+      <c r="A489">
         <v>519</v>
       </c>
       <c r="B489" s="1">
@@ -20146,16 +20138,14 @@
         <v>362</v>
       </c>
       <c r="F489" s="7"/>
-      <c r="G489" s="9">
+      <c r="G489" s="6">
         <v>38995</v>
       </c>
       <c r="H489" s="2" t="s">
         <v>220</v>
       </c>
       <c r="I489" s="2"/>
-      <c r="J489" s="8"/>
       <c r="K489" s="2"/>
-      <c r="L489" s="8"/>
       <c r="M489" s="4"/>
       <c r="N489" s="2"/>
       <c r="O489" s="2"/>
@@ -20163,16 +20153,10 @@
         <v>759</v>
       </c>
       <c r="Q489" s="2"/>
-      <c r="R489" s="8"/>
       <c r="S489" s="2"/>
-      <c r="T489" s="8"/>
-      <c r="U489" s="8"/>
-      <c r="V489" s="8"/>
-      <c r="W489" s="8"/>
-      <c r="X489" s="8"/>
-    </row>
-    <row r="490" spans="1:24" ht="15" customHeight="1">
-      <c r="A490" s="8">
+    </row>
+    <row r="490" spans="1:21" ht="15" customHeight="1">
+      <c r="A490">
         <v>520</v>
       </c>
       <c r="B490" s="1">
@@ -20188,16 +20172,14 @@
         <v>233</v>
       </c>
       <c r="F490" s="7"/>
-      <c r="G490" s="9">
+      <c r="G490" s="6">
         <v>38442</v>
       </c>
       <c r="H490" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I490" s="2"/>
-      <c r="J490" s="8"/>
       <c r="K490" s="2"/>
-      <c r="L490" s="8"/>
       <c r="M490" s="4"/>
       <c r="N490" s="2"/>
       <c r="O490" s="2" t="s">
@@ -20205,16 +20187,10 @@
       </c>
       <c r="P490" s="2"/>
       <c r="Q490" s="2"/>
-      <c r="R490" s="8"/>
       <c r="S490" s="2"/>
-      <c r="T490" s="8"/>
-      <c r="U490" s="8"/>
-      <c r="V490" s="8"/>
-      <c r="W490" s="8"/>
-      <c r="X490" s="8"/>
-    </row>
-    <row r="491" spans="1:24" ht="15" customHeight="1">
-      <c r="A491" s="8">
+    </row>
+    <row r="491" spans="1:21" ht="15" customHeight="1">
+      <c r="A491">
         <v>521</v>
       </c>
       <c r="B491" s="1">
@@ -20230,16 +20206,14 @@
         <v>330</v>
       </c>
       <c r="F491" s="7"/>
-      <c r="G491" s="9">
+      <c r="G491" s="6">
         <v>38460</v>
       </c>
       <c r="H491" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I491" s="2"/>
-      <c r="J491" s="8"/>
       <c r="K491" s="2"/>
-      <c r="L491" s="8"/>
       <c r="M491" s="4"/>
       <c r="N491" s="2"/>
       <c r="O491" s="2" t="s">
@@ -20247,16 +20221,10 @@
       </c>
       <c r="P491" s="2"/>
       <c r="Q491" s="2"/>
-      <c r="R491" s="8"/>
       <c r="S491" s="2"/>
-      <c r="T491" s="8"/>
-      <c r="U491" s="8"/>
-      <c r="V491" s="8"/>
-      <c r="W491" s="8"/>
-      <c r="X491" s="8"/>
-    </row>
-    <row r="492" spans="1:24" ht="15" customHeight="1">
-      <c r="A492" s="8">
+    </row>
+    <row r="492" spans="1:21" ht="15" customHeight="1">
+      <c r="A492">
         <v>522</v>
       </c>
       <c r="B492" s="1">
@@ -20272,16 +20240,14 @@
         <v>233</v>
       </c>
       <c r="F492" s="7"/>
-      <c r="G492" s="9">
+      <c r="G492" s="6">
         <v>38442</v>
       </c>
       <c r="H492" s="2" t="s">
         <v>36</v>
       </c>
       <c r="I492" s="2"/>
-      <c r="J492" s="8"/>
       <c r="K492" s="2"/>
-      <c r="L492" s="8"/>
       <c r="M492" s="4"/>
       <c r="N492" s="2"/>
       <c r="O492" s="2"/>
@@ -20289,16 +20255,10 @@
       <c r="Q492" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="R492" s="8"/>
       <c r="S492" s="2"/>
-      <c r="T492" s="8"/>
-      <c r="U492" s="8"/>
-      <c r="V492" s="8"/>
-      <c r="W492" s="8"/>
-      <c r="X492" s="8"/>
-    </row>
-    <row r="493" spans="1:24" ht="15" customHeight="1">
-      <c r="A493" s="8">
+    </row>
+    <row r="493" spans="1:21" ht="15" customHeight="1">
+      <c r="A493">
         <v>523</v>
       </c>
       <c r="B493" s="1">
@@ -20314,33 +20274,26 @@
         <v>233</v>
       </c>
       <c r="F493" s="7"/>
-      <c r="G493" s="9">
+      <c r="G493" s="6">
         <v>38442</v>
       </c>
       <c r="H493" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I493" s="2"/>
-      <c r="J493" s="8"/>
       <c r="K493" s="2"/>
-      <c r="L493" s="8"/>
       <c r="M493" s="4"/>
       <c r="N493" s="2"/>
       <c r="O493" s="2"/>
       <c r="P493" s="2"/>
       <c r="Q493" s="2"/>
-      <c r="R493" s="8"/>
       <c r="S493" s="2"/>
-      <c r="T493" s="8" t="s">
+      <c r="T493" t="s">
         <v>110</v>
       </c>
-      <c r="U493" s="8"/>
-      <c r="V493" s="8"/>
-      <c r="W493" s="8"/>
-      <c r="X493" s="8"/>
-    </row>
-    <row r="494" spans="1:24" ht="15" customHeight="1">
-      <c r="A494" s="8">
+    </row>
+    <row r="494" spans="1:21" ht="15" customHeight="1">
+      <c r="A494">
         <v>524</v>
       </c>
       <c r="B494" s="1">
@@ -20356,7 +20309,7 @@
         <v>89</v>
       </c>
       <c r="F494" s="7"/>
-      <c r="G494" s="9">
+      <c r="G494" s="6">
         <v>38535</v>
       </c>
       <c r="H494" s="2" t="s">
@@ -20365,24 +20318,16 @@
       <c r="I494" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="J494" s="8"/>
       <c r="K494" s="2"/>
-      <c r="L494" s="8"/>
       <c r="M494" s="4"/>
       <c r="N494" s="2"/>
       <c r="O494" s="2"/>
       <c r="P494" s="2"/>
       <c r="Q494" s="2"/>
-      <c r="R494" s="8"/>
       <c r="S494" s="2"/>
-      <c r="T494" s="8"/>
-      <c r="U494" s="8"/>
-      <c r="V494" s="8"/>
-      <c r="W494" s="8"/>
-      <c r="X494" s="8"/>
-    </row>
-    <row r="495" spans="1:24" ht="15" customHeight="1">
-      <c r="A495" s="8">
+    </row>
+    <row r="495" spans="1:21" ht="15" customHeight="1">
+      <c r="A495">
         <v>525</v>
       </c>
       <c r="B495" s="1">
@@ -20398,33 +20343,25 @@
         <v>233</v>
       </c>
       <c r="F495" s="7"/>
-      <c r="G495" s="9">
+      <c r="G495" s="6">
         <v>38442</v>
       </c>
       <c r="H495" s="2" t="s">
         <v>44</v>
       </c>
       <c r="I495" s="2"/>
-      <c r="J495" s="8"/>
       <c r="K495" s="2"/>
-      <c r="L495" s="8"/>
       <c r="M495" s="4"/>
       <c r="N495" s="2"/>
       <c r="O495" s="2"/>
       <c r="P495" s="2"/>
       <c r="Q495" s="2"/>
-      <c r="R495" s="8"/>
       <c r="S495" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="T495" s="8"/>
-      <c r="U495" s="8"/>
-      <c r="V495" s="8"/>
-      <c r="W495" s="8"/>
-      <c r="X495" s="8"/>
-    </row>
-    <row r="496" spans="1:24" ht="15" customHeight="1">
-      <c r="A496" s="8">
+    </row>
+    <row r="496" spans="1:21" ht="15" customHeight="1">
+      <c r="A496">
         <v>526</v>
       </c>
       <c r="B496" s="1">
@@ -20440,16 +20377,15 @@
         <v>89</v>
       </c>
       <c r="F496" s="7"/>
-      <c r="G496" s="9">
+      <c r="G496" s="6">
         <v>38535</v>
       </c>
       <c r="H496" s="2" t="s">
         <v>41</v>
       </c>
       <c r="I496" s="2"/>
-      <c r="J496" s="8"/>
       <c r="K496" s="2"/>
-      <c r="L496" s="8" t="s">
+      <c r="L496" t="s">
         <v>64</v>
       </c>
       <c r="M496" s="4" t="s">
@@ -20459,16 +20395,10 @@
       <c r="O496" s="2"/>
       <c r="P496" s="2"/>
       <c r="Q496" s="2"/>
-      <c r="R496" s="8"/>
       <c r="S496" s="2"/>
-      <c r="T496" s="8"/>
-      <c r="U496" s="8"/>
-      <c r="V496" s="8"/>
-      <c r="W496" s="8"/>
-      <c r="X496" s="8"/>
     </row>
     <row r="497" spans="1:24" ht="15" customHeight="1">
-      <c r="A497" s="8">
+      <c r="A497">
         <v>527</v>
       </c>
       <c r="B497" s="1">
@@ -20484,33 +20414,26 @@
         <v>233</v>
       </c>
       <c r="F497" s="7"/>
-      <c r="G497" s="9">
+      <c r="G497" s="6">
         <v>38442</v>
       </c>
       <c r="H497" s="2" t="s">
         <v>289</v>
       </c>
       <c r="I497" s="2"/>
-      <c r="J497" s="8"/>
       <c r="K497" s="2"/>
-      <c r="L497" s="8"/>
       <c r="M497" s="4"/>
       <c r="N497" s="2"/>
       <c r="O497" s="2"/>
       <c r="P497" s="2"/>
       <c r="Q497" s="2"/>
-      <c r="R497" s="8"/>
       <c r="S497" s="2"/>
-      <c r="T497" s="8"/>
-      <c r="U497" s="8"/>
-      <c r="V497" s="8"/>
-      <c r="W497" s="8" t="s">
+      <c r="W497" t="s">
         <v>766</v>
       </c>
-      <c r="X497" s="8"/>
     </row>
     <row r="498" spans="1:24" ht="15" customHeight="1">
-      <c r="A498" s="8">
+      <c r="A498">
         <v>528</v>
       </c>
       <c r="B498" s="1">
@@ -20526,33 +20449,25 @@
         <v>259</v>
       </c>
       <c r="F498" s="7"/>
-      <c r="G498" s="9">
+      <c r="G498" s="6">
         <v>38674</v>
       </c>
       <c r="H498" s="2" t="s">
         <v>44</v>
       </c>
       <c r="I498" s="2"/>
-      <c r="J498" s="8"/>
       <c r="K498" s="2"/>
-      <c r="L498" s="8"/>
       <c r="M498" s="4"/>
       <c r="N498" s="2"/>
       <c r="O498" s="2"/>
       <c r="P498" s="2"/>
       <c r="Q498" s="2"/>
-      <c r="R498" s="8"/>
       <c r="S498" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="T498" s="8"/>
-      <c r="U498" s="8"/>
-      <c r="V498" s="8"/>
-      <c r="W498" s="8"/>
-      <c r="X498" s="8"/>
     </row>
     <row r="499" spans="1:24" ht="15" customHeight="1">
-      <c r="A499" s="8">
+      <c r="A499">
         <v>529</v>
       </c>
       <c r="B499" s="1">
@@ -20568,30 +20483,443 @@
         <v>233</v>
       </c>
       <c r="F499" s="7"/>
-      <c r="G499" s="9">
+      <c r="G499" s="6">
         <v>38442</v>
       </c>
       <c r="H499" s="2" t="s">
         <v>291</v>
       </c>
       <c r="I499" s="2"/>
-      <c r="J499" s="8"/>
       <c r="K499" s="2"/>
-      <c r="L499" s="8"/>
       <c r="M499" s="4"/>
       <c r="N499" s="2"/>
       <c r="O499" s="2"/>
       <c r="P499" s="2"/>
       <c r="Q499" s="2"/>
-      <c r="R499" s="8"/>
       <c r="S499" s="2"/>
-      <c r="T499" s="8"/>
-      <c r="U499" s="8"/>
-      <c r="V499" s="8"/>
-      <c r="W499" s="8"/>
-      <c r="X499" s="8" t="s">
+      <c r="X499" t="s">
         <v>768</v>
       </c>
+    </row>
+    <row r="500" spans="1:24" ht="15" customHeight="1">
+      <c r="A500" s="8">
+        <v>530</v>
+      </c>
+      <c r="B500" s="1">
+        <v>46272.6418865741</v>
+      </c>
+      <c r="C500" s="1">
+        <v>46272.643275463</v>
+      </c>
+      <c r="D500" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E500" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F500" s="7"/>
+      <c r="G500" s="9">
+        <v>38903</v>
+      </c>
+      <c r="H500" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I500" s="2"/>
+      <c r="J500" s="8"/>
+      <c r="K500" s="2"/>
+      <c r="L500" s="8"/>
+      <c r="M500" s="4"/>
+      <c r="N500" s="2"/>
+      <c r="O500" s="2"/>
+      <c r="P500" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="Q500" s="2"/>
+      <c r="R500" s="8"/>
+      <c r="S500" s="2"/>
+      <c r="T500" s="8"/>
+      <c r="U500" s="8"/>
+      <c r="V500" s="8"/>
+      <c r="W500" s="8"/>
+      <c r="X500" s="8"/>
+    </row>
+    <row r="501" spans="1:24" ht="15" customHeight="1">
+      <c r="A501" s="8">
+        <v>531</v>
+      </c>
+      <c r="B501" s="1">
+        <v>46272.643993055601</v>
+      </c>
+      <c r="C501" s="1">
+        <v>46272.644259259301</v>
+      </c>
+      <c r="D501" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E501" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F501" s="7"/>
+      <c r="G501" s="9">
+        <v>38341</v>
+      </c>
+      <c r="H501" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I501" s="2"/>
+      <c r="J501" s="8"/>
+      <c r="K501" s="2"/>
+      <c r="L501" s="8"/>
+      <c r="M501" s="4"/>
+      <c r="N501" s="2"/>
+      <c r="O501" s="2"/>
+      <c r="P501" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="Q501" s="2"/>
+      <c r="R501" s="8"/>
+      <c r="S501" s="2"/>
+      <c r="T501" s="8"/>
+      <c r="U501" s="8"/>
+      <c r="V501" s="8"/>
+      <c r="W501" s="8"/>
+      <c r="X501" s="8"/>
+    </row>
+    <row r="502" spans="1:24" ht="15" customHeight="1">
+      <c r="A502" s="8">
+        <v>532</v>
+      </c>
+      <c r="B502" s="1">
+        <v>46272.651111111103</v>
+      </c>
+      <c r="C502" s="1">
+        <v>46272.651990740698</v>
+      </c>
+      <c r="D502" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E502" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F502" s="7"/>
+      <c r="G502" s="9">
+        <v>38845</v>
+      </c>
+      <c r="H502" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I502" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="J502" s="8"/>
+      <c r="K502" s="2"/>
+      <c r="L502" s="8"/>
+      <c r="M502" s="4"/>
+      <c r="N502" s="2"/>
+      <c r="O502" s="2"/>
+      <c r="P502" s="2"/>
+      <c r="Q502" s="2"/>
+      <c r="R502" s="8"/>
+      <c r="S502" s="2"/>
+      <c r="T502" s="8"/>
+      <c r="U502" s="8"/>
+      <c r="V502" s="8"/>
+      <c r="W502" s="8"/>
+      <c r="X502" s="8"/>
+    </row>
+    <row r="503" spans="1:24" ht="15" customHeight="1">
+      <c r="A503" s="8">
+        <v>533</v>
+      </c>
+      <c r="B503" s="1">
+        <v>46272.652673611097</v>
+      </c>
+      <c r="C503" s="1">
+        <v>46272.652858796297</v>
+      </c>
+      <c r="D503" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E503" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F503" s="7"/>
+      <c r="G503" s="9">
+        <v>388445</v>
+      </c>
+      <c r="H503" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I503" s="2"/>
+      <c r="J503" s="8"/>
+      <c r="K503" s="2"/>
+      <c r="L503" s="8"/>
+      <c r="M503" s="4"/>
+      <c r="N503" s="2"/>
+      <c r="O503" s="2"/>
+      <c r="P503" s="2"/>
+      <c r="Q503" s="2"/>
+      <c r="R503" s="8"/>
+      <c r="S503" s="2"/>
+      <c r="T503" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="U503" s="8"/>
+      <c r="V503" s="8"/>
+      <c r="W503" s="8"/>
+      <c r="X503" s="8"/>
+    </row>
+    <row r="504" spans="1:24" ht="15" customHeight="1">
+      <c r="A504" s="8">
+        <v>534</v>
+      </c>
+      <c r="B504" s="1">
+        <v>46272.653101851902</v>
+      </c>
+      <c r="C504" s="1">
+        <v>46272.659050925897</v>
+      </c>
+      <c r="D504" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E504" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F504" s="7"/>
+      <c r="G504" s="9">
+        <v>38845</v>
+      </c>
+      <c r="H504" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I504" s="2"/>
+      <c r="J504" s="8"/>
+      <c r="K504" s="2"/>
+      <c r="L504" s="8"/>
+      <c r="M504" s="4"/>
+      <c r="N504" s="2"/>
+      <c r="O504" s="2"/>
+      <c r="P504" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="Q504" s="2"/>
+      <c r="R504" s="8"/>
+      <c r="S504" s="2"/>
+      <c r="T504" s="8"/>
+      <c r="U504" s="8"/>
+      <c r="V504" s="8"/>
+      <c r="W504" s="8"/>
+      <c r="X504" s="8"/>
+    </row>
+    <row r="505" spans="1:24" ht="15" customHeight="1">
+      <c r="A505" s="8">
+        <v>535</v>
+      </c>
+      <c r="B505" s="1">
+        <v>46272.671296296299</v>
+      </c>
+      <c r="C505" s="1">
+        <v>46272.671574074098</v>
+      </c>
+      <c r="D505" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="E505" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="F505" s="7"/>
+      <c r="G505" s="9">
+        <v>38207</v>
+      </c>
+      <c r="H505" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I505" s="2"/>
+      <c r="J505" s="8"/>
+      <c r="K505" s="2"/>
+      <c r="L505" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="M505" s="4"/>
+      <c r="N505" s="2"/>
+      <c r="O505" s="2"/>
+      <c r="P505" s="2"/>
+      <c r="Q505" s="2"/>
+      <c r="R505" s="8"/>
+      <c r="S505" s="2"/>
+      <c r="T505" s="8"/>
+      <c r="U505" s="8"/>
+      <c r="V505" s="8"/>
+      <c r="W505" s="8"/>
+      <c r="X505" s="8"/>
+    </row>
+    <row r="506" spans="1:24" ht="15" customHeight="1">
+      <c r="A506" s="8">
+        <v>536</v>
+      </c>
+      <c r="B506" s="1">
+        <v>46272.674606481502</v>
+      </c>
+      <c r="C506" s="1">
+        <v>46272.675497685203</v>
+      </c>
+      <c r="D506" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E506" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F506" s="7"/>
+      <c r="G506" s="9">
+        <v>38845</v>
+      </c>
+      <c r="H506" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I506" s="2"/>
+      <c r="J506" s="8"/>
+      <c r="K506" s="2"/>
+      <c r="L506" s="8"/>
+      <c r="M506" s="4"/>
+      <c r="N506" s="2"/>
+      <c r="O506" s="2"/>
+      <c r="P506" s="2"/>
+      <c r="Q506" s="2"/>
+      <c r="R506" s="8"/>
+      <c r="S506" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="T506" s="8"/>
+      <c r="U506" s="8"/>
+      <c r="V506" s="8"/>
+      <c r="W506" s="8"/>
+      <c r="X506" s="8"/>
+    </row>
+    <row r="507" spans="1:24" ht="15" customHeight="1">
+      <c r="A507" s="8">
+        <v>537</v>
+      </c>
+      <c r="B507" s="1">
+        <v>46272.675497685203</v>
+      </c>
+      <c r="C507" s="1">
+        <v>46272.675740740699</v>
+      </c>
+      <c r="D507" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E507" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F507" s="7"/>
+      <c r="G507" s="9">
+        <v>38930</v>
+      </c>
+      <c r="H507" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I507" s="2"/>
+      <c r="J507" s="8"/>
+      <c r="K507" s="2"/>
+      <c r="L507" s="8"/>
+      <c r="M507" s="4"/>
+      <c r="N507" s="2"/>
+      <c r="O507" s="2"/>
+      <c r="P507" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="Q507" s="2"/>
+      <c r="R507" s="8"/>
+      <c r="S507" s="2"/>
+      <c r="T507" s="8"/>
+      <c r="U507" s="8"/>
+      <c r="V507" s="8"/>
+      <c r="W507" s="8"/>
+      <c r="X507" s="8"/>
+    </row>
+    <row r="508" spans="1:24" ht="15" customHeight="1">
+      <c r="A508" s="8">
+        <v>538</v>
+      </c>
+      <c r="B508" s="1">
+        <v>46272.684259259302</v>
+      </c>
+      <c r="C508" s="1">
+        <v>46272.6844444444</v>
+      </c>
+      <c r="D508" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E508" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F508" s="7"/>
+      <c r="G508" s="9">
+        <v>38656</v>
+      </c>
+      <c r="H508" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I508" s="2"/>
+      <c r="J508" s="8"/>
+      <c r="K508" s="2"/>
+      <c r="L508" s="8"/>
+      <c r="M508" s="4"/>
+      <c r="N508" s="2"/>
+      <c r="O508" s="2"/>
+      <c r="P508" s="2"/>
+      <c r="Q508" s="2"/>
+      <c r="R508" s="8"/>
+      <c r="S508" s="2"/>
+      <c r="T508" s="8"/>
+      <c r="U508" s="8"/>
+      <c r="V508" s="8"/>
+      <c r="W508" s="8"/>
+      <c r="X508" s="8" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="509" spans="1:24" ht="15" customHeight="1">
+      <c r="A509" s="8">
+        <v>539</v>
+      </c>
+      <c r="B509" s="1">
+        <v>46272.684490740699</v>
+      </c>
+      <c r="C509" s="1">
+        <v>46272.690439814804</v>
+      </c>
+      <c r="D509" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E509" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F509" s="7"/>
+      <c r="G509" s="9">
+        <v>38656</v>
+      </c>
+      <c r="H509" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I509" s="2"/>
+      <c r="J509" s="8"/>
+      <c r="K509" s="2"/>
+      <c r="L509" s="8"/>
+      <c r="M509" s="4"/>
+      <c r="N509" s="2"/>
+      <c r="O509" s="2"/>
+      <c r="P509" s="2"/>
+      <c r="Q509" s="2"/>
+      <c r="R509" s="8"/>
+      <c r="S509" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="T509" s="8"/>
+      <c r="U509" s="8"/>
+      <c r="V509" s="8"/>
+      <c r="W509" s="8"/>
+      <c r="X509" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="769" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCC43986-B713-4EC9-B21D-1455A6498219}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{40BD8B3D-99B1-4C34-8455-D6BBA1202168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{40BD8B3D-99B1-4C34-8455-D6BBA1202168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="770" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFA90512-33B3-49A7-85E9-BA199C141606}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20645,7 +20645,7 @@
       </c>
       <c r="F503" s="7"/>
       <c r="G503" s="9">
-        <v>388445</v>
+        <v>38845</v>
       </c>
       <c r="H503" s="2" t="s">
         <v>109</v>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="770" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFA90512-33B3-49A7-85E9-BA199C141606}"/>
+  <xr:revisionPtr revIDLastSave="773" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE209689-D7FB-4169-948E-E50EF5DF70B8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="777">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="780">
   <si>
     <t>Id</t>
   </si>
@@ -2367,6 +2367,15 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Viveros%20Sa.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/C3A4D499-91EA-4764-9DBD-BC34F01D8CA6_Starbucks%20Parque%20Tor.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/289179ED-32C6-4486-A68B-D9DC32498222_Starbucks%20Parque%20Tor.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_7626_Starbucks%20Viveros%20Sa.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2522,8 +2531,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X509" totalsRowShown="0">
-  <autoFilter ref="A1:X509" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X513" totalsRowShown="0">
+  <autoFilter ref="A1:X513" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="21">
       <extLst>
@@ -2697,7 +2706,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="539" latestEventMarker="810">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="543" latestEventMarker="814">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -3027,7 +3036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X509"/>
+  <dimension ref="A1:X513"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
@@ -20502,7 +20511,7 @@
       </c>
     </row>
     <row r="500" spans="1:24" ht="15" customHeight="1">
-      <c r="A500" s="8">
+      <c r="A500">
         <v>530</v>
       </c>
       <c r="B500" s="1">
@@ -20518,16 +20527,14 @@
         <v>353</v>
       </c>
       <c r="F500" s="7"/>
-      <c r="G500" s="9">
+      <c r="G500" s="6">
         <v>38903</v>
       </c>
       <c r="H500" s="2" t="s">
         <v>220</v>
       </c>
       <c r="I500" s="2"/>
-      <c r="J500" s="8"/>
       <c r="K500" s="2"/>
-      <c r="L500" s="8"/>
       <c r="M500" s="4"/>
       <c r="N500" s="2"/>
       <c r="O500" s="2"/>
@@ -20535,16 +20542,10 @@
         <v>769</v>
       </c>
       <c r="Q500" s="2"/>
-      <c r="R500" s="8"/>
       <c r="S500" s="2"/>
-      <c r="T500" s="8"/>
-      <c r="U500" s="8"/>
-      <c r="V500" s="8"/>
-      <c r="W500" s="8"/>
-      <c r="X500" s="8"/>
     </row>
     <row r="501" spans="1:24" ht="15" customHeight="1">
-      <c r="A501" s="8">
+      <c r="A501">
         <v>531</v>
       </c>
       <c r="B501" s="1">
@@ -20560,16 +20561,14 @@
         <v>418</v>
       </c>
       <c r="F501" s="7"/>
-      <c r="G501" s="9">
+      <c r="G501" s="6">
         <v>38341</v>
       </c>
       <c r="H501" s="2" t="s">
         <v>220</v>
       </c>
       <c r="I501" s="2"/>
-      <c r="J501" s="8"/>
       <c r="K501" s="2"/>
-      <c r="L501" s="8"/>
       <c r="M501" s="4"/>
       <c r="N501" s="2"/>
       <c r="O501" s="2"/>
@@ -20577,16 +20576,10 @@
         <v>770</v>
       </c>
       <c r="Q501" s="2"/>
-      <c r="R501" s="8"/>
       <c r="S501" s="2"/>
-      <c r="T501" s="8"/>
-      <c r="U501" s="8"/>
-      <c r="V501" s="8"/>
-      <c r="W501" s="8"/>
-      <c r="X501" s="8"/>
     </row>
     <row r="502" spans="1:24" ht="15" customHeight="1">
-      <c r="A502" s="8">
+      <c r="A502">
         <v>532</v>
       </c>
       <c r="B502" s="1">
@@ -20602,7 +20595,7 @@
         <v>249</v>
       </c>
       <c r="F502" s="7"/>
-      <c r="G502" s="9">
+      <c r="G502" s="6">
         <v>38845</v>
       </c>
       <c r="H502" s="2" t="s">
@@ -20611,24 +20604,16 @@
       <c r="I502" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="J502" s="8"/>
       <c r="K502" s="2"/>
-      <c r="L502" s="8"/>
       <c r="M502" s="4"/>
       <c r="N502" s="2"/>
       <c r="O502" s="2"/>
       <c r="P502" s="2"/>
       <c r="Q502" s="2"/>
-      <c r="R502" s="8"/>
       <c r="S502" s="2"/>
-      <c r="T502" s="8"/>
-      <c r="U502" s="8"/>
-      <c r="V502" s="8"/>
-      <c r="W502" s="8"/>
-      <c r="X502" s="8"/>
     </row>
     <row r="503" spans="1:24" ht="15" customHeight="1">
-      <c r="A503" s="8">
+      <c r="A503">
         <v>533</v>
       </c>
       <c r="B503" s="1">
@@ -20644,33 +20629,26 @@
         <v>249</v>
       </c>
       <c r="F503" s="7"/>
-      <c r="G503" s="9">
+      <c r="G503" s="6">
         <v>38845</v>
       </c>
       <c r="H503" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I503" s="2"/>
-      <c r="J503" s="8"/>
       <c r="K503" s="2"/>
-      <c r="L503" s="8"/>
       <c r="M503" s="4"/>
       <c r="N503" s="2"/>
       <c r="O503" s="2"/>
       <c r="P503" s="2"/>
       <c r="Q503" s="2"/>
-      <c r="R503" s="8"/>
       <c r="S503" s="2"/>
-      <c r="T503" s="8" t="s">
+      <c r="T503" t="s">
         <v>110</v>
       </c>
-      <c r="U503" s="8"/>
-      <c r="V503" s="8"/>
-      <c r="W503" s="8"/>
-      <c r="X503" s="8"/>
     </row>
     <row r="504" spans="1:24" ht="15" customHeight="1">
-      <c r="A504" s="8">
+      <c r="A504">
         <v>534</v>
       </c>
       <c r="B504" s="1">
@@ -20686,16 +20664,14 @@
         <v>249</v>
       </c>
       <c r="F504" s="7"/>
-      <c r="G504" s="9">
+      <c r="G504" s="6">
         <v>38845</v>
       </c>
       <c r="H504" s="2" t="s">
         <v>220</v>
       </c>
       <c r="I504" s="2"/>
-      <c r="J504" s="8"/>
       <c r="K504" s="2"/>
-      <c r="L504" s="8"/>
       <c r="M504" s="4"/>
       <c r="N504" s="2"/>
       <c r="O504" s="2"/>
@@ -20703,16 +20679,10 @@
         <v>772</v>
       </c>
       <c r="Q504" s="2"/>
-      <c r="R504" s="8"/>
       <c r="S504" s="2"/>
-      <c r="T504" s="8"/>
-      <c r="U504" s="8"/>
-      <c r="V504" s="8"/>
-      <c r="W504" s="8"/>
-      <c r="X504" s="8"/>
     </row>
     <row r="505" spans="1:24" ht="15" customHeight="1">
-      <c r="A505" s="8">
+      <c r="A505">
         <v>535</v>
       </c>
       <c r="B505" s="1">
@@ -20728,16 +20698,15 @@
         <v>717</v>
       </c>
       <c r="F505" s="7"/>
-      <c r="G505" s="9">
+      <c r="G505" s="6">
         <v>38207</v>
       </c>
       <c r="H505" s="2" t="s">
         <v>41</v>
       </c>
       <c r="I505" s="2"/>
-      <c r="J505" s="8"/>
       <c r="K505" s="2"/>
-      <c r="L505" s="8" t="s">
+      <c r="L505" t="s">
         <v>401</v>
       </c>
       <c r="M505" s="4"/>
@@ -20745,16 +20714,10 @@
       <c r="O505" s="2"/>
       <c r="P505" s="2"/>
       <c r="Q505" s="2"/>
-      <c r="R505" s="8"/>
       <c r="S505" s="2"/>
-      <c r="T505" s="8"/>
-      <c r="U505" s="8"/>
-      <c r="V505" s="8"/>
-      <c r="W505" s="8"/>
-      <c r="X505" s="8"/>
     </row>
     <row r="506" spans="1:24" ht="15" customHeight="1">
-      <c r="A506" s="8">
+      <c r="A506">
         <v>536</v>
       </c>
       <c r="B506" s="1">
@@ -20770,33 +20733,25 @@
         <v>249</v>
       </c>
       <c r="F506" s="7"/>
-      <c r="G506" s="9">
+      <c r="G506" s="6">
         <v>38845</v>
       </c>
       <c r="H506" s="2" t="s">
         <v>44</v>
       </c>
       <c r="I506" s="2"/>
-      <c r="J506" s="8"/>
       <c r="K506" s="2"/>
-      <c r="L506" s="8"/>
       <c r="M506" s="4"/>
       <c r="N506" s="2"/>
       <c r="O506" s="2"/>
       <c r="P506" s="2"/>
       <c r="Q506" s="2"/>
-      <c r="R506" s="8"/>
       <c r="S506" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="T506" s="8"/>
-      <c r="U506" s="8"/>
-      <c r="V506" s="8"/>
-      <c r="W506" s="8"/>
-      <c r="X506" s="8"/>
     </row>
     <row r="507" spans="1:24" ht="15" customHeight="1">
-      <c r="A507" s="8">
+      <c r="A507">
         <v>537</v>
       </c>
       <c r="B507" s="1">
@@ -20812,16 +20767,14 @@
         <v>294</v>
       </c>
       <c r="F507" s="7"/>
-      <c r="G507" s="9">
+      <c r="G507" s="6">
         <v>38930</v>
       </c>
       <c r="H507" s="2" t="s">
         <v>220</v>
       </c>
       <c r="I507" s="2"/>
-      <c r="J507" s="8"/>
       <c r="K507" s="2"/>
-      <c r="L507" s="8"/>
       <c r="M507" s="4"/>
       <c r="N507" s="2"/>
       <c r="O507" s="2"/>
@@ -20829,16 +20782,10 @@
         <v>774</v>
       </c>
       <c r="Q507" s="2"/>
-      <c r="R507" s="8"/>
       <c r="S507" s="2"/>
-      <c r="T507" s="8"/>
-      <c r="U507" s="8"/>
-      <c r="V507" s="8"/>
-      <c r="W507" s="8"/>
-      <c r="X507" s="8"/>
     </row>
     <row r="508" spans="1:24" ht="15" customHeight="1">
-      <c r="A508" s="8">
+      <c r="A508">
         <v>538</v>
       </c>
       <c r="B508" s="1">
@@ -20854,33 +20801,26 @@
         <v>103</v>
       </c>
       <c r="F508" s="7"/>
-      <c r="G508" s="9">
+      <c r="G508" s="6">
         <v>38656</v>
       </c>
       <c r="H508" s="2" t="s">
         <v>291</v>
       </c>
       <c r="I508" s="2"/>
-      <c r="J508" s="8"/>
       <c r="K508" s="2"/>
-      <c r="L508" s="8"/>
       <c r="M508" s="4"/>
       <c r="N508" s="2"/>
       <c r="O508" s="2"/>
       <c r="P508" s="2"/>
       <c r="Q508" s="2"/>
-      <c r="R508" s="8"/>
       <c r="S508" s="2"/>
-      <c r="T508" s="8"/>
-      <c r="U508" s="8"/>
-      <c r="V508" s="8"/>
-      <c r="W508" s="8"/>
-      <c r="X508" s="8" t="s">
+      <c r="X508" t="s">
         <v>775</v>
       </c>
     </row>
     <row r="509" spans="1:24" ht="15" customHeight="1">
-      <c r="A509" s="8">
+      <c r="A509">
         <v>539</v>
       </c>
       <c r="B509" s="1">
@@ -20896,30 +20836,190 @@
         <v>103</v>
       </c>
       <c r="F509" s="7"/>
-      <c r="G509" s="9">
+      <c r="G509" s="6">
         <v>38656</v>
       </c>
       <c r="H509" s="2" t="s">
         <v>44</v>
       </c>
       <c r="I509" s="2"/>
-      <c r="J509" s="8"/>
       <c r="K509" s="2"/>
-      <c r="L509" s="8"/>
       <c r="M509" s="4"/>
       <c r="N509" s="2"/>
       <c r="O509" s="2"/>
       <c r="P509" s="2"/>
       <c r="Q509" s="2"/>
-      <c r="R509" s="8"/>
       <c r="S509" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="T509" s="8"/>
-      <c r="U509" s="8"/>
-      <c r="V509" s="8"/>
-      <c r="W509" s="8"/>
-      <c r="X509" s="8"/>
+    </row>
+    <row r="510" spans="1:24" ht="15" customHeight="1">
+      <c r="A510" s="8">
+        <v>540</v>
+      </c>
+      <c r="B510" s="1">
+        <v>46272.764733796299</v>
+      </c>
+      <c r="C510" s="1">
+        <v>46272.768067129597</v>
+      </c>
+      <c r="D510" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E510" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F510" s="7"/>
+      <c r="G510" s="9">
+        <v>38599</v>
+      </c>
+      <c r="H510" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I510" s="2"/>
+      <c r="J510" s="8"/>
+      <c r="K510" s="2"/>
+      <c r="L510" s="8"/>
+      <c r="M510" s="4"/>
+      <c r="N510" s="2"/>
+      <c r="O510" s="2"/>
+      <c r="P510" s="2"/>
+      <c r="Q510" s="2"/>
+      <c r="R510" s="8"/>
+      <c r="S510" s="2"/>
+      <c r="T510" s="8"/>
+      <c r="U510" s="8"/>
+      <c r="V510" s="8"/>
+      <c r="W510" s="8"/>
+      <c r="X510" s="8" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="511" spans="1:24" ht="15" customHeight="1">
+      <c r="A511" s="8">
+        <v>541</v>
+      </c>
+      <c r="B511" s="1">
+        <v>46272.815937500003</v>
+      </c>
+      <c r="C511" s="1">
+        <v>46272.816064814797</v>
+      </c>
+      <c r="D511" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="E511" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F511" s="7"/>
+      <c r="G511" s="9">
+        <v>43195</v>
+      </c>
+      <c r="H511" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I511" s="2"/>
+      <c r="J511" s="8"/>
+      <c r="K511" s="2"/>
+      <c r="L511" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="M511" s="4"/>
+      <c r="N511" s="2"/>
+      <c r="O511" s="2"/>
+      <c r="P511" s="2"/>
+      <c r="Q511" s="2"/>
+      <c r="R511" s="8"/>
+      <c r="S511" s="2"/>
+      <c r="T511" s="8"/>
+      <c r="U511" s="8"/>
+      <c r="V511" s="8"/>
+      <c r="W511" s="8"/>
+      <c r="X511" s="8"/>
+    </row>
+    <row r="512" spans="1:24" ht="15" customHeight="1">
+      <c r="A512" s="8">
+        <v>542</v>
+      </c>
+      <c r="B512" s="1">
+        <v>46272.768275463</v>
+      </c>
+      <c r="C512" s="1">
+        <v>46272.825671296298</v>
+      </c>
+      <c r="D512" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E512" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F512" s="7"/>
+      <c r="G512" s="9">
+        <v>38590</v>
+      </c>
+      <c r="H512" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I512" s="2"/>
+      <c r="J512" s="8"/>
+      <c r="K512" s="2"/>
+      <c r="L512" s="8"/>
+      <c r="M512" s="4"/>
+      <c r="N512" s="2"/>
+      <c r="O512" s="2"/>
+      <c r="P512" s="2"/>
+      <c r="Q512" s="2"/>
+      <c r="R512" s="8"/>
+      <c r="S512" s="2"/>
+      <c r="T512" s="8"/>
+      <c r="U512" s="8"/>
+      <c r="V512" s="8"/>
+      <c r="W512" s="8" t="s">
+        <v>778</v>
+      </c>
+      <c r="X512" s="8"/>
+    </row>
+    <row r="513" spans="1:24" ht="15" customHeight="1">
+      <c r="A513" s="8">
+        <v>543</v>
+      </c>
+      <c r="B513" s="1">
+        <v>46272.824108796303</v>
+      </c>
+      <c r="C513" s="1">
+        <v>46272.828159722201</v>
+      </c>
+      <c r="D513" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E513" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F513" s="7"/>
+      <c r="G513" s="9">
+        <v>38656</v>
+      </c>
+      <c r="H513" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="I513" s="2"/>
+      <c r="J513" s="8"/>
+      <c r="K513" s="2"/>
+      <c r="L513" s="8"/>
+      <c r="M513" 